--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -829,7 +829,7 @@
                   <c:v>0.09499406612677</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>197.2679587511206</c:v>
+                  <c:v>0.09499406612677</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.0230749358268398</c:v>
@@ -1298,7 +1298,7 @@
                   <c:v>0.08388619620156357</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.27181096736148</c:v>
+                  <c:v>0.08049762046967701</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.05460028906895609</c:v>
@@ -3137,13 +3137,13 @@
         <v>19.7444</v>
       </c>
       <c r="E41">
-        <v>3914.681884765625</v>
+        <v>21.6200008392334</v>
       </c>
       <c r="F41">
-        <v>197.2679587511206</v>
+        <v>0.09499406612677</v>
       </c>
       <c r="G41">
-        <v>19726.8</v>
+        <v>9.5</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -3155,7 +3155,7 @@
         <v>1204.4084</v>
       </c>
       <c r="K41">
-        <v>238795.5949707031</v>
+        <v>1318.820051193237</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5424,7 +5424,7 @@
         <v>0.3841723129918275</v>
       </c>
       <c r="H5" s="2">
-        <v>197.2679587511206</v>
+        <v>0.09499406612677</v>
       </c>
       <c r="I5" s="2">
         <v>0.1093993008088707</v>
@@ -5439,7 +5439,7 @@
         <v>0.0272633809806162</v>
       </c>
       <c r="M5" s="2">
-        <v>10.27181096736148</v>
+        <v>0.08049762046967701</v>
       </c>
     </row>
     <row r="6" spans="1:13">

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -251,16 +251,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$10</c:f>
+              <c:f>grafico_dati!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -287,6 +290,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.0531256149837493</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0722987542781903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -314,10 +320,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -344,16 +350,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$10</c:f>
+              <c:f>grafico_dati!$C$2:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -380,6 +389,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.0304168310728241</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0428394249929064</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -407,10 +419,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -437,16 +449,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$10</c:f>
+              <c:f>grafico_dati!$D$2:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -473,6 +488,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.06367410666717151</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0882345655129961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -500,10 +518,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -530,16 +548,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$10</c:f>
+              <c:f>grafico_dati!$E$2:$E$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -566,6 +587,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-0.0017467721124055</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0262932021058521</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -593,10 +617,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -623,16 +647,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$10</c:f>
+              <c:f>grafico_dati!$F$2:$F$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -686,10 +713,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -716,16 +743,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$10</c:f>
+              <c:f>grafico_dati!$G$2:$G$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -752,6 +782,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.3132982375834958</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3461056849486601</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -779,10 +812,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -809,16 +842,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$10</c:f>
+              <c:f>grafico_dati!$H$2:$H$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -845,6 +881,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.0134013076213126</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0494621599738012</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -872,10 +911,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -902,16 +941,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$10</c:f>
+              <c:f>grafico_dati!$I$2:$I$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -938,6 +980,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.0869581766275182</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.1014012608799923</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -965,10 +1010,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -995,16 +1040,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$10</c:f>
+              <c:f>grafico_dati!$J$2:$J$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1031,6 +1079,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-0.0170064140117878</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.008347671299990299</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1058,10 +1109,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1088,16 +1139,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$10</c:f>
+              <c:f>grafico_dati!$K$2:$K$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1124,6 +1178,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-0.0080602949298627</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0041327233944277</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1151,10 +1208,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1181,16 +1238,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$10</c:f>
+              <c:f>grafico_dati!$L$2:$L$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1217,6 +1277,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-0.0187863399166211</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0019788035208567</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1248,10 +1311,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$10</c:f>
+              <c:f>grafico_dati!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1278,16 +1341,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$10</c:f>
+              <c:f>grafico_dati!$M$2:$M$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.08716234354652008</c:v>
                 </c:pt>
@@ -1314,6 +1380,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.03878100707485044</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.05968402110857607</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1720,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5221,6 +5290,356 @@
       </c>
       <c r="K100">
         <v>3462.222996711731</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>22</v>
+      </c>
+      <c r="D101">
+        <v>50.07</v>
+      </c>
+      <c r="E101">
+        <v>53.68999862670898</v>
+      </c>
+      <c r="F101">
+        <v>0.0722987542781903</v>
+      </c>
+      <c r="G101">
+        <v>7.23</v>
+      </c>
+      <c r="H101" t="s">
+        <v>11</v>
+      </c>
+      <c r="I101">
+        <v>23</v>
+      </c>
+      <c r="J101">
+        <v>1151.61</v>
+      </c>
+      <c r="K101">
+        <v>1234.869968414306</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102">
+        <v>242.3</v>
+      </c>
+      <c r="E102">
+        <v>252.6799926757812</v>
+      </c>
+      <c r="F102">
+        <v>0.0428394249929064</v>
+      </c>
+      <c r="G102">
+        <v>4.28</v>
+      </c>
+      <c r="H102" t="s">
+        <v>12</v>
+      </c>
+      <c r="I102">
+        <v>5</v>
+      </c>
+      <c r="J102">
+        <v>1211.5</v>
+      </c>
+      <c r="K102">
+        <v>1263.399963378906</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B103" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103">
+        <v>38.273</v>
+      </c>
+      <c r="E103">
+        <v>41.65000152587891</v>
+      </c>
+      <c r="F103">
+        <v>0.0882345655129961</v>
+      </c>
+      <c r="G103">
+        <v>8.82</v>
+      </c>
+      <c r="H103" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103">
+        <v>54</v>
+      </c>
+      <c r="J103">
+        <v>2066.742</v>
+      </c>
+      <c r="K103">
+        <v>2249.100082397461</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104">
+        <v>6.5264</v>
+      </c>
+      <c r="E104">
+        <v>6.697999954223633</v>
+      </c>
+      <c r="F104">
+        <v>0.0262932021058521</v>
+      </c>
+      <c r="G104">
+        <v>2.63</v>
+      </c>
+      <c r="H104" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104">
+        <v>276</v>
+      </c>
+      <c r="J104">
+        <v>1801.2864</v>
+      </c>
+      <c r="K104">
+        <v>1848.647987365723</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105">
+        <v>79.86</v>
+      </c>
+      <c r="E105">
+        <v>107.5</v>
+      </c>
+      <c r="F105">
+        <v>0.3461056849486601</v>
+      </c>
+      <c r="G105">
+        <v>34.61</v>
+      </c>
+      <c r="H105" t="s">
+        <v>16</v>
+      </c>
+      <c r="I105">
+        <v>12</v>
+      </c>
+      <c r="J105">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K105">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>28</v>
+      </c>
+      <c r="D106">
+        <v>19.7444</v>
+      </c>
+      <c r="E106">
+        <v>20.72100067138672</v>
+      </c>
+      <c r="F106">
+        <v>0.0494621599738012</v>
+      </c>
+      <c r="G106">
+        <v>4.95</v>
+      </c>
+      <c r="H106" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106">
+        <v>61</v>
+      </c>
+      <c r="J106">
+        <v>1204.4084</v>
+      </c>
+      <c r="K106">
+        <v>1263.98104095459</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B107" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107">
+        <v>128.7814</v>
+      </c>
+      <c r="E107">
+        <v>141.8399963378906</v>
+      </c>
+      <c r="F107">
+        <v>0.1014012608799923</v>
+      </c>
+      <c r="G107">
+        <v>10.14</v>
+      </c>
+      <c r="H107" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107">
+        <v>44</v>
+      </c>
+      <c r="J107">
+        <v>5666.3816</v>
+      </c>
+      <c r="K107">
+        <v>6240.959838867188</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B108" t="s">
+        <v>19</v>
+      </c>
+      <c r="C108" t="s">
+        <v>30</v>
+      </c>
+      <c r="D108">
+        <v>34.0694</v>
+      </c>
+      <c r="E108">
+        <v>33.78499984741211</v>
+      </c>
+      <c r="F108">
+        <v>-0.008347671299990299</v>
+      </c>
+      <c r="G108">
+        <v>-0.83</v>
+      </c>
+      <c r="H108" t="s">
+        <v>19</v>
+      </c>
+      <c r="I108">
+        <v>34</v>
+      </c>
+      <c r="J108">
+        <v>1158.3596</v>
+      </c>
+      <c r="K108">
+        <v>1148.689994812012</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B109" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" t="s">
+        <v>31</v>
+      </c>
+      <c r="D109">
+        <v>69.7119</v>
+      </c>
+      <c r="E109">
+        <v>70</v>
+      </c>
+      <c r="F109">
+        <v>0.0041327233944277</v>
+      </c>
+      <c r="G109">
+        <v>0.41</v>
+      </c>
+      <c r="H109" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109">
+        <v>54</v>
+      </c>
+      <c r="J109">
+        <v>3764.4426</v>
+      </c>
+      <c r="K109">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B110" t="s">
+        <v>21</v>
+      </c>
+      <c r="C110" t="s">
+        <v>32</v>
+      </c>
+      <c r="D110">
+        <v>8.1868</v>
+      </c>
+      <c r="E110">
+        <v>8.203000068664551</v>
+      </c>
+      <c r="F110">
+        <v>0.0019788035208567</v>
+      </c>
+      <c r="G110">
+        <v>0.2</v>
+      </c>
+      <c r="H110" t="s">
+        <v>21</v>
+      </c>
+      <c r="I110">
+        <v>431</v>
+      </c>
+      <c r="J110">
+        <v>3528.5108</v>
+      </c>
+      <c r="K110">
+        <v>3535.493029594421</v>
       </c>
     </row>
   </sheetData>
@@ -5230,7 +5649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -5645,6 +6064,44 @@
       </c>
       <c r="M10" s="2">
         <v>0.03878100707485044</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.0722987542781903</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.0428394249929064</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.0882345655129961</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.0262932021058521</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.3461056849486601</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.0494621599738012</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.1014012608799923</v>
+      </c>
+      <c r="J11" s="2">
+        <v>-0.008347671299990299</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.0041327233944277</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.0019788035208567</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.05968402110857607</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -254,16 +254,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$11</c:f>
+              <c:f>grafico_dati!$B$2:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -293,6 +296,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0722987542781903</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.06610747090304039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -320,10 +326,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -353,16 +359,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$11</c:f>
+              <c:f>grafico_dati!$C$2:$C$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -392,6 +401,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0428394249929064</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.036607503792593</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -419,10 +431,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -452,16 +464,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$11</c:f>
+              <c:f>grafico_dati!$D$2:$D$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -491,6 +506,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0882345655129961</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.0822250194378624</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -518,10 +536,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -551,16 +569,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$11</c:f>
+              <c:f>grafico_dati!$E$2:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -590,6 +611,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0262932021058521</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.0213900296294708</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -617,10 +641,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -650,16 +674,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$11</c:f>
+              <c:f>grafico_dati!$F$2:$F$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -686,6 +713,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-0.0197388770331954</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.009717564216472499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -713,10 +743,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -746,16 +776,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$11</c:f>
+              <c:f>grafico_dati!$G$2:$G$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -785,6 +818,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.3461056849486601</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3305785391463871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -812,10 +848,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -845,16 +881,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$11</c:f>
+              <c:f>grafico_dati!$H$2:$H$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -884,6 +923,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0494621599738012</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.030266761915028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -911,10 +953,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -944,16 +986,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$11</c:f>
+              <c:f>grafico_dati!$I$2:$I$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -983,6 +1028,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.1014012608799923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.0976740477301192</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1010,10 +1058,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1043,16 +1091,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$11</c:f>
+              <c:f>grafico_dati!$J$2:$J$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1082,6 +1133,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>-0.008347671299990299</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.0174467858512009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1109,10 +1163,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1142,16 +1196,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$11</c:f>
+              <c:f>grafico_dati!$K$2:$K$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1181,6 +1238,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0041327233944277</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.000116210011535</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1208,10 +1268,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1241,16 +1301,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$11</c:f>
+              <c:f>grafico_dati!$L$2:$L$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1280,6 +1343,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0019788035208567</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.0076709342304576</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1311,10 +1377,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$11</c:f>
+              <c:f>grafico_dati!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1344,16 +1410,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$11</c:f>
+              <c:f>grafico_dati!$M$2:$M$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.08716234354652008</c:v>
                 </c:pt>
@@ -1383,6 +1452,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.05968402110857607</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.050688625305223</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1789,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5640,6 +5712,391 @@
       </c>
       <c r="K110">
         <v>3535.493029594421</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>22</v>
+      </c>
+      <c r="D111">
+        <v>50.07</v>
+      </c>
+      <c r="E111">
+        <v>53.38000106811523</v>
+      </c>
+      <c r="F111">
+        <v>0.06610747090304039</v>
+      </c>
+      <c r="G111">
+        <v>6.61</v>
+      </c>
+      <c r="H111" t="s">
+        <v>11</v>
+      </c>
+      <c r="I111">
+        <v>23</v>
+      </c>
+      <c r="J111">
+        <v>1151.61</v>
+      </c>
+      <c r="K111">
+        <v>1227.74002456665</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" t="s">
+        <v>23</v>
+      </c>
+      <c r="D112">
+        <v>242.3</v>
+      </c>
+      <c r="E112">
+        <v>251.1699981689453</v>
+      </c>
+      <c r="F112">
+        <v>0.036607503792593</v>
+      </c>
+      <c r="G112">
+        <v>3.66</v>
+      </c>
+      <c r="H112" t="s">
+        <v>12</v>
+      </c>
+      <c r="I112">
+        <v>5</v>
+      </c>
+      <c r="J112">
+        <v>1211.5</v>
+      </c>
+      <c r="K112">
+        <v>1255.849990844727</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B113" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113">
+        <v>38.273</v>
+      </c>
+      <c r="E113">
+        <v>41.41999816894531</v>
+      </c>
+      <c r="F113">
+        <v>0.0822250194378624</v>
+      </c>
+      <c r="G113">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="H113" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113">
+        <v>54</v>
+      </c>
+      <c r="J113">
+        <v>2066.742</v>
+      </c>
+      <c r="K113">
+        <v>2236.679901123047</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" t="s">
+        <v>25</v>
+      </c>
+      <c r="D114">
+        <v>6.5264</v>
+      </c>
+      <c r="E114">
+        <v>6.665999889373779</v>
+      </c>
+      <c r="F114">
+        <v>0.0213900296294708</v>
+      </c>
+      <c r="G114">
+        <v>2.14</v>
+      </c>
+      <c r="H114" t="s">
+        <v>14</v>
+      </c>
+      <c r="I114">
+        <v>276</v>
+      </c>
+      <c r="J114">
+        <v>1801.2864</v>
+      </c>
+      <c r="K114">
+        <v>1839.815969467163</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" t="s">
+        <v>26</v>
+      </c>
+      <c r="D115">
+        <v>197.58</v>
+      </c>
+      <c r="E115">
+        <v>195.6600036621093</v>
+      </c>
+      <c r="F115">
+        <v>-0.009717564216472499</v>
+      </c>
+      <c r="G115">
+        <v>-0.97</v>
+      </c>
+      <c r="H115" t="s">
+        <v>15</v>
+      </c>
+      <c r="I115">
+        <v>4</v>
+      </c>
+      <c r="J115">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K115">
+        <v>782.6400146484374</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="s">
+        <v>27</v>
+      </c>
+      <c r="D116">
+        <v>79.86</v>
+      </c>
+      <c r="E116">
+        <v>106.2600021362305</v>
+      </c>
+      <c r="F116">
+        <v>0.3305785391463871</v>
+      </c>
+      <c r="G116">
+        <v>33.06</v>
+      </c>
+      <c r="H116" t="s">
+        <v>16</v>
+      </c>
+      <c r="I116">
+        <v>12</v>
+      </c>
+      <c r="J116">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K116">
+        <v>1275.120025634766</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B117" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117" t="s">
+        <v>28</v>
+      </c>
+      <c r="D117">
+        <v>19.7444</v>
+      </c>
+      <c r="E117">
+        <v>20.34199905395508</v>
+      </c>
+      <c r="F117">
+        <v>0.030266761915028</v>
+      </c>
+      <c r="G117">
+        <v>3.03</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117">
+        <v>61</v>
+      </c>
+      <c r="J117">
+        <v>1204.4084</v>
+      </c>
+      <c r="K117">
+        <v>1240.86194229126</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B118" t="s">
+        <v>18</v>
+      </c>
+      <c r="C118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D118">
+        <v>128.7814</v>
+      </c>
+      <c r="E118">
+        <v>141.3600006103516</v>
+      </c>
+      <c r="F118">
+        <v>0.0976740477301192</v>
+      </c>
+      <c r="G118">
+        <v>9.77</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118">
+        <v>44</v>
+      </c>
+      <c r="J118">
+        <v>5666.3816</v>
+      </c>
+      <c r="K118">
+        <v>6219.840026855469</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B119" t="s">
+        <v>19</v>
+      </c>
+      <c r="C119" t="s">
+        <v>30</v>
+      </c>
+      <c r="D119">
+        <v>34.0694</v>
+      </c>
+      <c r="E119">
+        <v>33.47499847412109</v>
+      </c>
+      <c r="F119">
+        <v>-0.0174467858512009</v>
+      </c>
+      <c r="G119">
+        <v>-1.74</v>
+      </c>
+      <c r="H119" t="s">
+        <v>19</v>
+      </c>
+      <c r="I119">
+        <v>34</v>
+      </c>
+      <c r="J119">
+        <v>1158.3596</v>
+      </c>
+      <c r="K119">
+        <v>1138.149948120117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B120" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" t="s">
+        <v>31</v>
+      </c>
+      <c r="D120">
+        <v>69.7119</v>
+      </c>
+      <c r="E120">
+        <v>69.72000122070312</v>
+      </c>
+      <c r="F120">
+        <v>0.000116210011535</v>
+      </c>
+      <c r="G120">
+        <v>0.01</v>
+      </c>
+      <c r="H120" t="s">
+        <v>20</v>
+      </c>
+      <c r="I120">
+        <v>54</v>
+      </c>
+      <c r="J120">
+        <v>3764.4426</v>
+      </c>
+      <c r="K120">
+        <v>3764.880065917969</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B121" t="s">
+        <v>21</v>
+      </c>
+      <c r="C121" t="s">
+        <v>32</v>
+      </c>
+      <c r="D121">
+        <v>8.1868</v>
+      </c>
+      <c r="E121">
+        <v>8.12399959564209</v>
+      </c>
+      <c r="F121">
+        <v>-0.0076709342304576</v>
+      </c>
+      <c r="G121">
+        <v>-0.77</v>
+      </c>
+      <c r="H121" t="s">
+        <v>21</v>
+      </c>
+      <c r="I121">
+        <v>431</v>
+      </c>
+      <c r="J121">
+        <v>3528.5108</v>
+      </c>
+      <c r="K121">
+        <v>3501.443825721741</v>
       </c>
     </row>
   </sheetData>
@@ -5649,7 +6106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -6102,6 +6559,47 @@
       </c>
       <c r="M11" s="2">
         <v>0.05968402110857607</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.06610747090304039</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.036607503792593</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.0822250194378624</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.0213900296294708</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-0.009717564216472499</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.3305785391463871</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.030266761915028</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.0976740477301192</v>
+      </c>
+      <c r="J12" s="2">
+        <v>-0.0174467858512009</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.000116210011535</v>
+      </c>
+      <c r="L12" s="2">
+        <v>-0.0076709342304576</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.050688625305223</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -257,16 +257,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$12</c:f>
+              <c:f>grafico_dati!$B$2:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -299,6 +302,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.06610747090304039</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.0559216882741115</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -326,10 +332,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -362,16 +368,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$12</c:f>
+              <c:f>grafico_dati!$C$2:$C$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -404,6 +413,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.036607503792593</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.0366900637284615</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -431,10 +443,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -467,16 +479,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$12</c:f>
+              <c:f>grafico_dati!$D$2:$D$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -509,6 +524,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.0822250194378624</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.0619758173585469</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -536,10 +554,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -572,16 +590,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$12</c:f>
+              <c:f>grafico_dati!$E$2:$E$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -614,6 +635,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.0213900296294708</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.002819334241975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -641,10 +665,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -677,16 +701,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$12</c:f>
+              <c:f>grafico_dati!$F$2:$F$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -716,6 +743,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-0.009717564216472499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.0121470155087496</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -743,10 +773,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -779,16 +809,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$12</c:f>
+              <c:f>grafico_dati!$G$2:$G$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -821,6 +854,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.3305785391463871</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.3245679787039428</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -848,10 +884,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -884,16 +920,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$12</c:f>
+              <c:f>grafico_dati!$H$2:$H$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -926,6 +965,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.030266761915028</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.0256578802436941</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -953,10 +995,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -989,16 +1031,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$12</c:f>
+              <c:f>grafico_dati!$I$2:$I$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1031,6 +1076,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.0976740477301192</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.0925490555953125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1058,10 +1106,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1094,16 +1142,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$12</c:f>
+              <c:f>grafico_dati!$J$2:$J$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1136,6 +1187,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-0.0174467858512009</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.0244911677237766</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1163,10 +1217,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1199,16 +1253,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$12</c:f>
+              <c:f>grafico_dati!$K$2:$K$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1241,6 +1298,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.000116210011535</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.0046175848076377</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1268,10 +1328,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1304,16 +1364,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$12</c:f>
+              <c:f>grafico_dati!$L$2:$L$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1346,6 +1409,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-0.0076709342304576</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.0151219371009677</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1377,10 +1443,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$12</c:f>
+              <c:f>grafico_dati!$A$2:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1413,16 +1479,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$12</c:f>
+              <c:f>grafico_dati!$M$2:$M$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.08716234354652008</c:v>
                 </c:pt>
@@ -1455,6 +1524,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.050688625305223</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.04246482181549616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1861,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5886,7 +5958,7 @@
         <v>790.3200000000001</v>
       </c>
       <c r="K115">
-        <v>782.6400146484374</v>
+        <v>782.6400146484373</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -6097,6 +6169,391 @@
       </c>
       <c r="K121">
         <v>3501.443825721741</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122">
+        <v>50.07</v>
+      </c>
+      <c r="E122">
+        <v>52.86999893188477</v>
+      </c>
+      <c r="F122">
+        <v>0.0559216882741115</v>
+      </c>
+      <c r="G122">
+        <v>5.59</v>
+      </c>
+      <c r="H122" t="s">
+        <v>11</v>
+      </c>
+      <c r="I122">
+        <v>23</v>
+      </c>
+      <c r="J122">
+        <v>1151.61</v>
+      </c>
+      <c r="K122">
+        <v>1216.00997543335</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" t="s">
+        <v>23</v>
+      </c>
+      <c r="D123">
+        <v>242.3</v>
+      </c>
+      <c r="E123">
+        <v>251.1900024414062</v>
+      </c>
+      <c r="F123">
+        <v>0.0366900637284615</v>
+      </c>
+      <c r="G123">
+        <v>3.67</v>
+      </c>
+      <c r="H123" t="s">
+        <v>12</v>
+      </c>
+      <c r="I123">
+        <v>5</v>
+      </c>
+      <c r="J123">
+        <v>1211.5</v>
+      </c>
+      <c r="K123">
+        <v>1255.950012207031</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B124" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" t="s">
+        <v>24</v>
+      </c>
+      <c r="D124">
+        <v>38.273</v>
+      </c>
+      <c r="E124">
+        <v>40.64500045776367</v>
+      </c>
+      <c r="F124">
+        <v>0.0619758173585469</v>
+      </c>
+      <c r="G124">
+        <v>6.2</v>
+      </c>
+      <c r="H124" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124">
+        <v>54</v>
+      </c>
+      <c r="J124">
+        <v>2066.742</v>
+      </c>
+      <c r="K124">
+        <v>2194.830024719238</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B125" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" t="s">
+        <v>25</v>
+      </c>
+      <c r="D125">
+        <v>6.5264</v>
+      </c>
+      <c r="E125">
+        <v>6.507999897003174</v>
+      </c>
+      <c r="F125">
+        <v>-0.002819334241975</v>
+      </c>
+      <c r="G125">
+        <v>-0.28</v>
+      </c>
+      <c r="H125" t="s">
+        <v>14</v>
+      </c>
+      <c r="I125">
+        <v>276</v>
+      </c>
+      <c r="J125">
+        <v>1801.2864</v>
+      </c>
+      <c r="K125">
+        <v>1796.207971572876</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B126" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" t="s">
+        <v>26</v>
+      </c>
+      <c r="D126">
+        <v>197.58</v>
+      </c>
+      <c r="E126">
+        <v>195.1799926757812</v>
+      </c>
+      <c r="F126">
+        <v>-0.0121470155087496</v>
+      </c>
+      <c r="G126">
+        <v>-1.21</v>
+      </c>
+      <c r="H126" t="s">
+        <v>15</v>
+      </c>
+      <c r="I126">
+        <v>4</v>
+      </c>
+      <c r="J126">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K126">
+        <v>780.719970703125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="s">
+        <v>27</v>
+      </c>
+      <c r="D127">
+        <v>79.86</v>
+      </c>
+      <c r="E127">
+        <v>105.7799987792969</v>
+      </c>
+      <c r="F127">
+        <v>0.3245679787039428</v>
+      </c>
+      <c r="G127">
+        <v>32.46</v>
+      </c>
+      <c r="H127" t="s">
+        <v>16</v>
+      </c>
+      <c r="I127">
+        <v>12</v>
+      </c>
+      <c r="J127">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K127">
+        <v>1269.359985351562</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B128" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128">
+        <v>19.7444</v>
+      </c>
+      <c r="E128">
+        <v>20.2509994506836</v>
+      </c>
+      <c r="F128">
+        <v>0.0256578802436941</v>
+      </c>
+      <c r="G128">
+        <v>2.57</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128">
+        <v>61</v>
+      </c>
+      <c r="J128">
+        <v>1204.4084</v>
+      </c>
+      <c r="K128">
+        <v>1235.310966491699</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B129" t="s">
+        <v>18</v>
+      </c>
+      <c r="C129" t="s">
+        <v>29</v>
+      </c>
+      <c r="D129">
+        <v>128.7814</v>
+      </c>
+      <c r="E129">
+        <v>140.6999969482422</v>
+      </c>
+      <c r="F129">
+        <v>0.0925490555953125</v>
+      </c>
+      <c r="G129">
+        <v>9.25</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129">
+        <v>44</v>
+      </c>
+      <c r="J129">
+        <v>5666.3816</v>
+      </c>
+      <c r="K129">
+        <v>6190.799865722656</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B130" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130">
+        <v>34.0694</v>
+      </c>
+      <c r="E130">
+        <v>33.23500061035156</v>
+      </c>
+      <c r="F130">
+        <v>-0.0244911677237766</v>
+      </c>
+      <c r="G130">
+        <v>-2.45</v>
+      </c>
+      <c r="H130" t="s">
+        <v>19</v>
+      </c>
+      <c r="I130">
+        <v>34</v>
+      </c>
+      <c r="J130">
+        <v>1158.3596</v>
+      </c>
+      <c r="K130">
+        <v>1129.990020751953</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="s">
+        <v>20</v>
+      </c>
+      <c r="C131" t="s">
+        <v>31</v>
+      </c>
+      <c r="D131">
+        <v>69.7119</v>
+      </c>
+      <c r="E131">
+        <v>69.38999938964844</v>
+      </c>
+      <c r="F131">
+        <v>-0.0046175848076377</v>
+      </c>
+      <c r="G131">
+        <v>-0.46</v>
+      </c>
+      <c r="H131" t="s">
+        <v>20</v>
+      </c>
+      <c r="I131">
+        <v>54</v>
+      </c>
+      <c r="J131">
+        <v>3764.4426</v>
+      </c>
+      <c r="K131">
+        <v>3747.059967041016</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B132" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" t="s">
+        <v>32</v>
+      </c>
+      <c r="D132">
+        <v>8.1868</v>
+      </c>
+      <c r="E132">
+        <v>8.062999725341797</v>
+      </c>
+      <c r="F132">
+        <v>-0.0151219371009677</v>
+      </c>
+      <c r="G132">
+        <v>-1.51</v>
+      </c>
+      <c r="H132" t="s">
+        <v>21</v>
+      </c>
+      <c r="I132">
+        <v>431</v>
+      </c>
+      <c r="J132">
+        <v>3528.5108</v>
+      </c>
+      <c r="K132">
+        <v>3475.152881622314</v>
       </c>
     </row>
   </sheetData>
@@ -6106,7 +6563,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -6600,6 +7057,47 @@
       </c>
       <c r="M12" s="2">
         <v>0.050688625305223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.0559216882741115</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.0366900637284615</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.0619758173585469</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-0.002819334241975</v>
+      </c>
+      <c r="F13" s="2">
+        <v>-0.0121470155087496</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.3245679787039428</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.0256578802436941</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.0925490555953125</v>
+      </c>
+      <c r="J13" s="2">
+        <v>-0.0244911677237766</v>
+      </c>
+      <c r="K13" s="2">
+        <v>-0.0046175848076377</v>
+      </c>
+      <c r="L13" s="2">
+        <v>-0.0151219371009677</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.04246482181549616</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -260,16 +260,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$13</c:f>
+              <c:f>grafico_dati!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -305,6 +308,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.0559216882741115</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.0507289916187649</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -332,10 +338,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -371,16 +377,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$13</c:f>
+              <c:f>grafico_dati!$C$2:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -416,6 +425,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.0366900637284615</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.029261243869783</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -443,10 +455,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -482,16 +494,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$13</c:f>
+              <c:f>grafico_dati!$D$2:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -527,6 +542,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.0619758173585469</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.0638047749742085</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -554,10 +572,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -593,16 +611,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$13</c:f>
+              <c:f>grafico_dati!$E$2:$E$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -638,6 +659,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>-0.002819334241975</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.0045047472668324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -665,10 +689,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -704,16 +728,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$13</c:f>
+              <c:f>grafico_dati!$F$2:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -746,6 +773,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>-0.0121470155087496</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.0182204892826245</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -773,10 +803,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -812,16 +842,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$13</c:f>
+              <c:f>grafico_dati!$G$2:$G$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -857,6 +890,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.3245679787039428</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.3170548498018506</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -884,10 +920,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -923,16 +959,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$13</c:f>
+              <c:f>grafico_dati!$H$2:$H$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -968,6 +1007,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.0256578802436941</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.0205931337095008</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -995,10 +1037,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1034,16 +1076,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$13</c:f>
+              <c:f>grafico_dati!$I$2:$I$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1079,6 +1124,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.0925490555953125</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.09037483805072249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1106,10 +1154,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1145,16 +1193,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$13</c:f>
+              <c:f>grafico_dati!$J$2:$J$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1190,6 +1241,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>-0.0244911677237766</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.0236106479818125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1217,10 +1271,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1256,16 +1310,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$13</c:f>
+              <c:f>grafico_dati!$K$2:$K$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1301,6 +1358,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>-0.0046175848076377</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.006625841499084</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1328,10 +1388,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1367,16 +1427,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$13</c:f>
+              <c:f>grafico_dati!$L$2:$L$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1412,6 +1475,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>-0.0151219371009677</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.0195191738840457</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1443,10 +1509,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$13</c:f>
+              <c:f>grafico_dati!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1482,16 +1548,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$13</c:f>
+              <c:f>grafico_dati!$M$2:$M$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.08716234354652008</c:v>
                 </c:pt>
@@ -1527,6 +1596,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.04246482181549616</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.03960189634549893</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1933,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5958,7 +6030,7 @@
         <v>790.3200000000001</v>
       </c>
       <c r="K115">
-        <v>782.6400146484373</v>
+        <v>782.6400146484372</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -6413,7 +6485,7 @@
         <v>1204.4084</v>
       </c>
       <c r="K128">
-        <v>1235.310966491699</v>
+        <v>1235.3109664917</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -6554,6 +6626,391 @@
       </c>
       <c r="K132">
         <v>3475.152881622314</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133">
+        <v>50.07</v>
+      </c>
+      <c r="E133">
+        <v>52.61000061035156</v>
+      </c>
+      <c r="F133">
+        <v>0.0507289916187649</v>
+      </c>
+      <c r="G133">
+        <v>5.07</v>
+      </c>
+      <c r="H133" t="s">
+        <v>11</v>
+      </c>
+      <c r="I133">
+        <v>23</v>
+      </c>
+      <c r="J133">
+        <v>1151.61</v>
+      </c>
+      <c r="K133">
+        <v>1210.030014038086</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B134" t="s">
+        <v>12</v>
+      </c>
+      <c r="C134" t="s">
+        <v>23</v>
+      </c>
+      <c r="D134">
+        <v>242.3</v>
+      </c>
+      <c r="E134">
+        <v>249.3899993896484</v>
+      </c>
+      <c r="F134">
+        <v>0.029261243869783</v>
+      </c>
+      <c r="G134">
+        <v>2.93</v>
+      </c>
+      <c r="H134" t="s">
+        <v>12</v>
+      </c>
+      <c r="I134">
+        <v>5</v>
+      </c>
+      <c r="J134">
+        <v>1211.5</v>
+      </c>
+      <c r="K134">
+        <v>1246.949996948242</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B135" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135" t="s">
+        <v>24</v>
+      </c>
+      <c r="D135">
+        <v>38.273</v>
+      </c>
+      <c r="E135">
+        <v>40.71500015258789</v>
+      </c>
+      <c r="F135">
+        <v>0.0638047749742085</v>
+      </c>
+      <c r="G135">
+        <v>6.38</v>
+      </c>
+      <c r="H135" t="s">
+        <v>13</v>
+      </c>
+      <c r="I135">
+        <v>54</v>
+      </c>
+      <c r="J135">
+        <v>2066.742</v>
+      </c>
+      <c r="K135">
+        <v>2198.610008239746</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B136" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" t="s">
+        <v>25</v>
+      </c>
+      <c r="D136">
+        <v>6.5264</v>
+      </c>
+      <c r="E136">
+        <v>6.497000217437744</v>
+      </c>
+      <c r="F136">
+        <v>-0.0045047472668324</v>
+      </c>
+      <c r="G136">
+        <v>-0.45</v>
+      </c>
+      <c r="H136" t="s">
+        <v>14</v>
+      </c>
+      <c r="I136">
+        <v>276</v>
+      </c>
+      <c r="J136">
+        <v>1801.2864</v>
+      </c>
+      <c r="K136">
+        <v>1793.172060012817</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B137" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" t="s">
+        <v>26</v>
+      </c>
+      <c r="D137">
+        <v>197.58</v>
+      </c>
+      <c r="E137">
+        <v>193.979995727539</v>
+      </c>
+      <c r="F137">
+        <v>-0.0182204892826245</v>
+      </c>
+      <c r="G137">
+        <v>-1.82</v>
+      </c>
+      <c r="H137" t="s">
+        <v>15</v>
+      </c>
+      <c r="I137">
+        <v>4</v>
+      </c>
+      <c r="J137">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K137">
+        <v>775.9199829101561</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="s">
+        <v>27</v>
+      </c>
+      <c r="D138">
+        <v>79.86</v>
+      </c>
+      <c r="E138">
+        <v>105.1800003051758</v>
+      </c>
+      <c r="F138">
+        <v>0.3170548498018506</v>
+      </c>
+      <c r="G138">
+        <v>31.71</v>
+      </c>
+      <c r="H138" t="s">
+        <v>16</v>
+      </c>
+      <c r="I138">
+        <v>12</v>
+      </c>
+      <c r="J138">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K138">
+        <v>1262.160003662109</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B139" t="s">
+        <v>17</v>
+      </c>
+      <c r="C139" t="s">
+        <v>28</v>
+      </c>
+      <c r="D139">
+        <v>19.7444</v>
+      </c>
+      <c r="E139">
+        <v>20.15099906921387</v>
+      </c>
+      <c r="F139">
+        <v>0.0205931337095008</v>
+      </c>
+      <c r="G139">
+        <v>2.06</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139">
+        <v>61</v>
+      </c>
+      <c r="J139">
+        <v>1204.4084</v>
+      </c>
+      <c r="K139">
+        <v>1229.210943222046</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B140" t="s">
+        <v>18</v>
+      </c>
+      <c r="C140" t="s">
+        <v>29</v>
+      </c>
+      <c r="D140">
+        <v>128.7814</v>
+      </c>
+      <c r="E140">
+        <v>140.4199981689453</v>
+      </c>
+      <c r="F140">
+        <v>0.09037483805072249</v>
+      </c>
+      <c r="G140">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="H140" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140">
+        <v>44</v>
+      </c>
+      <c r="J140">
+        <v>5666.3816</v>
+      </c>
+      <c r="K140">
+        <v>6178.479919433594</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B141" t="s">
+        <v>19</v>
+      </c>
+      <c r="C141" t="s">
+        <v>30</v>
+      </c>
+      <c r="D141">
+        <v>34.0694</v>
+      </c>
+      <c r="E141">
+        <v>33.26499938964844</v>
+      </c>
+      <c r="F141">
+        <v>-0.0236106479818125</v>
+      </c>
+      <c r="G141">
+        <v>-2.36</v>
+      </c>
+      <c r="H141" t="s">
+        <v>19</v>
+      </c>
+      <c r="I141">
+        <v>34</v>
+      </c>
+      <c r="J141">
+        <v>1158.3596</v>
+      </c>
+      <c r="K141">
+        <v>1131.009979248047</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="A142" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B142" t="s">
+        <v>20</v>
+      </c>
+      <c r="C142" t="s">
+        <v>31</v>
+      </c>
+      <c r="D142">
+        <v>69.7119</v>
+      </c>
+      <c r="E142">
+        <v>69.25</v>
+      </c>
+      <c r="F142">
+        <v>-0.006625841499084</v>
+      </c>
+      <c r="G142">
+        <v>-0.66</v>
+      </c>
+      <c r="H142" t="s">
+        <v>20</v>
+      </c>
+      <c r="I142">
+        <v>54</v>
+      </c>
+      <c r="J142">
+        <v>3764.4426</v>
+      </c>
+      <c r="K142">
+        <v>3739.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B143" t="s">
+        <v>21</v>
+      </c>
+      <c r="C143" t="s">
+        <v>32</v>
+      </c>
+      <c r="D143">
+        <v>8.1868</v>
+      </c>
+      <c r="E143">
+        <v>8.027000427246094</v>
+      </c>
+      <c r="F143">
+        <v>-0.0195191738840457</v>
+      </c>
+      <c r="G143">
+        <v>-1.95</v>
+      </c>
+      <c r="H143" t="s">
+        <v>21</v>
+      </c>
+      <c r="I143">
+        <v>431</v>
+      </c>
+      <c r="J143">
+        <v>3528.5108</v>
+      </c>
+      <c r="K143">
+        <v>3459.637184143066</v>
       </c>
     </row>
   </sheetData>
@@ -6563,7 +7020,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -7098,6 +7555,47 @@
       </c>
       <c r="M13" s="2">
         <v>0.04246482181549616</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.0507289916187649</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.029261243869783</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.0638047749742085</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-0.0045047472668324</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-0.0182204892826245</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.3170548498018506</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.0205931337095008</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.09037483805072249</v>
+      </c>
+      <c r="J14" s="2">
+        <v>-0.0236106479818125</v>
+      </c>
+      <c r="K14" s="2">
+        <v>-0.006625841499084</v>
+      </c>
+      <c r="L14" s="2">
+        <v>-0.0195191738840457</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.03960189634549893</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -263,16 +263,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$14</c:f>
+              <c:f>grafico_dati!$B$2:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -311,6 +314,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.0507289916187649</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.0601158743969381</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -338,10 +344,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -380,16 +386,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$14</c:f>
+              <c:f>grafico_dati!$C$2:$C$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -428,6 +437,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.029261243869783</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.0309533761938003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -455,10 +467,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -497,16 +509,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$14</c:f>
+              <c:f>grafico_dati!$D$2:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -545,6 +560,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.0638047749742085</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.07922034607101031</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -572,10 +590,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -614,16 +632,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$14</c:f>
+              <c:f>grafico_dati!$E$2:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -662,6 +683,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-0.0045047472668324</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.0138820947224851</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -689,10 +713,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -731,16 +755,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$14</c:f>
+              <c:f>grafico_dati!$F$2:$F$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -776,6 +803,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-0.0182204892826245</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.0128555861618949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -803,10 +833,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -845,16 +875,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$14</c:f>
+              <c:f>grafico_dati!$G$2:$G$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -893,6 +926,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.3170548498018506</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3190583062595871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -920,10 +956,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -962,16 +998,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$14</c:f>
+              <c:f>grafico_dati!$H$2:$H$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1010,6 +1049,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.0205931337095008</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.029608419249127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1037,10 +1079,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1079,16 +1121,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$14</c:f>
+              <c:f>grafico_dati!$I$2:$I$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1127,6 +1172,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.09037483805072249</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.0933256126409389</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1154,10 +1202,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1196,16 +1244,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$14</c:f>
+              <c:f>grafico_dati!$J$2:$J$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1244,6 +1295,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-0.0236106479818125</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.0230235974976926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1271,10 +1325,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1313,16 +1367,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$14</c:f>
+              <c:f>grafico_dati!$K$2:$K$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1361,6 +1418,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-0.006625841499084</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.00476106298325</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1388,10 +1448,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1430,16 +1490,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$14</c:f>
+              <c:f>grafico_dati!$L$2:$L$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1478,6 +1541,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-0.0195191738840457</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.0154882958400475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1509,10 +1575,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$14</c:f>
+              <c:f>grafico_dati!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1551,16 +1617,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$14</c:f>
+              <c:f>grafico_dati!$M$2:$M$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.08716234354652008</c:v>
                 </c:pt>
@@ -1599,6 +1668,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.03960189634549893</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.04533109596729723</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2005,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K143"/>
+  <dimension ref="A1:K154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7011,6 +7083,391 @@
       </c>
       <c r="K143">
         <v>3459.637184143066</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>22</v>
+      </c>
+      <c r="D144">
+        <v>50.07</v>
+      </c>
+      <c r="E144">
+        <v>53.08000183105469</v>
+      </c>
+      <c r="F144">
+        <v>0.0601158743969381</v>
+      </c>
+      <c r="G144">
+        <v>6.01</v>
+      </c>
+      <c r="H144" t="s">
+        <v>11</v>
+      </c>
+      <c r="I144">
+        <v>23</v>
+      </c>
+      <c r="J144">
+        <v>1151.61</v>
+      </c>
+      <c r="K144">
+        <v>1220.840042114258</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="A145" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B145" t="s">
+        <v>12</v>
+      </c>
+      <c r="C145" t="s">
+        <v>23</v>
+      </c>
+      <c r="D145">
+        <v>242.3</v>
+      </c>
+      <c r="E145">
+        <v>249.8000030517578</v>
+      </c>
+      <c r="F145">
+        <v>0.0309533761938003</v>
+      </c>
+      <c r="G145">
+        <v>3.1</v>
+      </c>
+      <c r="H145" t="s">
+        <v>12</v>
+      </c>
+      <c r="I145">
+        <v>5</v>
+      </c>
+      <c r="J145">
+        <v>1211.5</v>
+      </c>
+      <c r="K145">
+        <v>1249.000015258789</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
+        <v>24</v>
+      </c>
+      <c r="D146">
+        <v>38.273</v>
+      </c>
+      <c r="E146">
+        <v>41.30500030517578</v>
+      </c>
+      <c r="F146">
+        <v>0.07922034607101031</v>
+      </c>
+      <c r="G146">
+        <v>7.92</v>
+      </c>
+      <c r="H146" t="s">
+        <v>13</v>
+      </c>
+      <c r="I146">
+        <v>54</v>
+      </c>
+      <c r="J146">
+        <v>2066.742</v>
+      </c>
+      <c r="K146">
+        <v>2230.470016479492</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="A147" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B147" t="s">
+        <v>14</v>
+      </c>
+      <c r="C147" t="s">
+        <v>25</v>
+      </c>
+      <c r="D147">
+        <v>6.5264</v>
+      </c>
+      <c r="E147">
+        <v>6.617000102996826</v>
+      </c>
+      <c r="F147">
+        <v>0.0138820947224851</v>
+      </c>
+      <c r="G147">
+        <v>1.39</v>
+      </c>
+      <c r="H147" t="s">
+        <v>14</v>
+      </c>
+      <c r="I147">
+        <v>276</v>
+      </c>
+      <c r="J147">
+        <v>1801.2864</v>
+      </c>
+      <c r="K147">
+        <v>1826.292028427124</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="A148" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B148" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" t="s">
+        <v>26</v>
+      </c>
+      <c r="D148">
+        <v>197.58</v>
+      </c>
+      <c r="E148">
+        <v>195.0399932861328</v>
+      </c>
+      <c r="F148">
+        <v>-0.0128555861618949</v>
+      </c>
+      <c r="G148">
+        <v>-1.29</v>
+      </c>
+      <c r="H148" t="s">
+        <v>15</v>
+      </c>
+      <c r="I148">
+        <v>4</v>
+      </c>
+      <c r="J148">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K148">
+        <v>780.1599731445312</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="A149" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="s">
+        <v>27</v>
+      </c>
+      <c r="D149">
+        <v>79.86</v>
+      </c>
+      <c r="E149">
+        <v>105.3399963378906</v>
+      </c>
+      <c r="F149">
+        <v>0.3190583062595871</v>
+      </c>
+      <c r="G149">
+        <v>31.91</v>
+      </c>
+      <c r="H149" t="s">
+        <v>16</v>
+      </c>
+      <c r="I149">
+        <v>12</v>
+      </c>
+      <c r="J149">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K149">
+        <v>1264.079956054688</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="A150" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B150" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" t="s">
+        <v>28</v>
+      </c>
+      <c r="D150">
+        <v>19.7444</v>
+      </c>
+      <c r="E150">
+        <v>20.32900047302246</v>
+      </c>
+      <c r="F150">
+        <v>0.029608419249127</v>
+      </c>
+      <c r="G150">
+        <v>2.96</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150">
+        <v>61</v>
+      </c>
+      <c r="J150">
+        <v>1204.4084</v>
+      </c>
+      <c r="K150">
+        <v>1240.06902885437</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="A151" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B151" t="s">
+        <v>18</v>
+      </c>
+      <c r="C151" t="s">
+        <v>29</v>
+      </c>
+      <c r="D151">
+        <v>128.7814</v>
+      </c>
+      <c r="E151">
+        <v>140.8000030517578</v>
+      </c>
+      <c r="F151">
+        <v>0.0933256126409389</v>
+      </c>
+      <c r="G151">
+        <v>9.33</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151">
+        <v>44</v>
+      </c>
+      <c r="J151">
+        <v>5666.3816</v>
+      </c>
+      <c r="K151">
+        <v>6195.200134277344</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="A152" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B152" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" t="s">
+        <v>30</v>
+      </c>
+      <c r="D152">
+        <v>34.0694</v>
+      </c>
+      <c r="E152">
+        <v>33.28499984741211</v>
+      </c>
+      <c r="F152">
+        <v>-0.0230235974976926</v>
+      </c>
+      <c r="G152">
+        <v>-2.3</v>
+      </c>
+      <c r="H152" t="s">
+        <v>19</v>
+      </c>
+      <c r="I152">
+        <v>34</v>
+      </c>
+      <c r="J152">
+        <v>1158.3596</v>
+      </c>
+      <c r="K152">
+        <v>1131.689994812012</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
+      <c r="A153" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B153" t="s">
+        <v>20</v>
+      </c>
+      <c r="C153" t="s">
+        <v>31</v>
+      </c>
+      <c r="D153">
+        <v>69.7119</v>
+      </c>
+      <c r="E153">
+        <v>69.37999725341797</v>
+      </c>
+      <c r="F153">
+        <v>-0.00476106298325</v>
+      </c>
+      <c r="G153">
+        <v>-0.48</v>
+      </c>
+      <c r="H153" t="s">
+        <v>20</v>
+      </c>
+      <c r="I153">
+        <v>54</v>
+      </c>
+      <c r="J153">
+        <v>3764.4426</v>
+      </c>
+      <c r="K153">
+        <v>3746.51985168457</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
+      <c r="A154" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B154" t="s">
+        <v>21</v>
+      </c>
+      <c r="C154" t="s">
+        <v>32</v>
+      </c>
+      <c r="D154">
+        <v>8.1868</v>
+      </c>
+      <c r="E154">
+        <v>8.060000419616699</v>
+      </c>
+      <c r="F154">
+        <v>-0.0154882958400475</v>
+      </c>
+      <c r="G154">
+        <v>-1.55</v>
+      </c>
+      <c r="H154" t="s">
+        <v>21</v>
+      </c>
+      <c r="I154">
+        <v>431</v>
+      </c>
+      <c r="J154">
+        <v>3528.5108</v>
+      </c>
+      <c r="K154">
+        <v>3473.860180854797</v>
       </c>
     </row>
   </sheetData>
@@ -7020,7 +7477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -7596,6 +8053,47 @@
       </c>
       <c r="M14" s="2">
         <v>0.03960189634549893</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.0601158743969381</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.0309533761938003</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.07922034607101031</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.0138820947224851</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-0.0128555861618949</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.3190583062595871</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.029608419249127</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.0933256126409389</v>
+      </c>
+      <c r="J15" s="2">
+        <v>-0.0230235974976926</v>
+      </c>
+      <c r="K15" s="2">
+        <v>-0.00476106298325</v>
+      </c>
+      <c r="L15" s="2">
+        <v>-0.0154882958400475</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0.04533109596729723</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -266,16 +266,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$15</c:f>
+              <c:f>grafico_dati!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -317,6 +320,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.0601158743969381</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.0685040942680248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -344,10 +350,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -389,16 +395,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$15</c:f>
+              <c:f>grafico_dati!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -440,6 +449,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.0309533761938003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.0373091058105266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -467,10 +479,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -512,16 +524,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$15</c:f>
+              <c:f>grafico_dati!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -563,6 +578,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.07922034607101031</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.08732008670516531</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -590,10 +608,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -635,16 +653,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$15</c:f>
+              <c:f>grafico_dati!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -686,6 +707,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.0138820947224851</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.0272125515115995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -713,10 +737,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -758,16 +782,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$15</c:f>
+              <c:f>grafico_dati!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -806,6 +833,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>-0.0128555861618949</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.0064783730551786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -833,10 +863,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -878,16 +908,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$15</c:f>
+              <c:f>grafico_dati!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -929,6 +962,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.3190583062595871</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.3295767631502102</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -956,10 +992,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1001,16 +1037,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$15</c:f>
+              <c:f>grafico_dati!$H$2:$H$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1052,6 +1091,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.029608419249127</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.0292538898897936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1079,10 +1121,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1124,16 +1166,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$15</c:f>
+              <c:f>grafico_dati!$I$2:$I$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1175,6 +1220,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.0933256126409389</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.09573277360202299</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1202,10 +1250,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1247,16 +1295,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$15</c:f>
+              <c:f>grafico_dati!$J$2:$J$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1298,6 +1349,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>-0.0230235974976926</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.0168597353670811</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1325,10 +1379,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1370,16 +1424,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$15</c:f>
+              <c:f>grafico_dati!$K$2:$K$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1421,6 +1478,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>-0.00476106298325</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.0033265001106899</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1448,10 +1508,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1493,16 +1553,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$15</c:f>
+              <c:f>grafico_dati!$L$2:$L$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1544,6 +1607,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>-0.0154882958400475</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.0124346462418805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1575,10 +1641,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$15</c:f>
+              <c:f>grafico_dati!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1620,16 +1686,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$15</c:f>
+              <c:f>grafico_dati!$M$2:$M$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.08716234354652008</c:v>
                 </c:pt>
@@ -1671,6 +1740,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.04533109596729723</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.05004144884688144</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2077,7 +2149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K154"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7468,6 +7540,391 @@
       </c>
       <c r="K154">
         <v>3473.860180854797</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
+      <c r="A155" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>22</v>
+      </c>
+      <c r="D155">
+        <v>50.07</v>
+      </c>
+      <c r="E155">
+        <v>53.5</v>
+      </c>
+      <c r="F155">
+        <v>0.0685040942680248</v>
+      </c>
+      <c r="G155">
+        <v>6.85</v>
+      </c>
+      <c r="H155" t="s">
+        <v>11</v>
+      </c>
+      <c r="I155">
+        <v>23</v>
+      </c>
+      <c r="J155">
+        <v>1151.61</v>
+      </c>
+      <c r="K155">
+        <v>1230.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
+      <c r="A156" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B156" t="s">
+        <v>12</v>
+      </c>
+      <c r="C156" t="s">
+        <v>23</v>
+      </c>
+      <c r="D156">
+        <v>242.3</v>
+      </c>
+      <c r="E156">
+        <v>251.3399963378907</v>
+      </c>
+      <c r="F156">
+        <v>0.0373091058105266</v>
+      </c>
+      <c r="G156">
+        <v>3.73</v>
+      </c>
+      <c r="H156" t="s">
+        <v>12</v>
+      </c>
+      <c r="I156">
+        <v>5</v>
+      </c>
+      <c r="J156">
+        <v>1211.5</v>
+      </c>
+      <c r="K156">
+        <v>1256.699981689453</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
+      <c r="A157" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B157" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" t="s">
+        <v>24</v>
+      </c>
+      <c r="D157">
+        <v>38.273</v>
+      </c>
+      <c r="E157">
+        <v>41.6150016784668</v>
+      </c>
+      <c r="F157">
+        <v>0.08732008670516531</v>
+      </c>
+      <c r="G157">
+        <v>8.73</v>
+      </c>
+      <c r="H157" t="s">
+        <v>13</v>
+      </c>
+      <c r="I157">
+        <v>54</v>
+      </c>
+      <c r="J157">
+        <v>2066.742</v>
+      </c>
+      <c r="K157">
+        <v>2247.210090637207</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
+      <c r="A158" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B158" t="s">
+        <v>14</v>
+      </c>
+      <c r="C158" t="s">
+        <v>25</v>
+      </c>
+      <c r="D158">
+        <v>6.5264</v>
+      </c>
+      <c r="E158">
+        <v>6.703999996185303</v>
+      </c>
+      <c r="F158">
+        <v>0.0272125515115995</v>
+      </c>
+      <c r="G158">
+        <v>2.72</v>
+      </c>
+      <c r="H158" t="s">
+        <v>14</v>
+      </c>
+      <c r="I158">
+        <v>276</v>
+      </c>
+      <c r="J158">
+        <v>1801.2864</v>
+      </c>
+      <c r="K158">
+        <v>1850.303998947144</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
+      <c r="A159" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B159" t="s">
+        <v>15</v>
+      </c>
+      <c r="C159" t="s">
+        <v>26</v>
+      </c>
+      <c r="D159">
+        <v>197.58</v>
+      </c>
+      <c r="E159">
+        <v>196.3000030517578</v>
+      </c>
+      <c r="F159">
+        <v>-0.0064783730551786</v>
+      </c>
+      <c r="G159">
+        <v>-0.65</v>
+      </c>
+      <c r="H159" t="s">
+        <v>15</v>
+      </c>
+      <c r="I159">
+        <v>4</v>
+      </c>
+      <c r="J159">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K159">
+        <v>785.2000122070312</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
+      <c r="A160" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="s">
+        <v>27</v>
+      </c>
+      <c r="D160">
+        <v>79.86</v>
+      </c>
+      <c r="E160">
+        <v>106.1800003051758</v>
+      </c>
+      <c r="F160">
+        <v>0.3295767631502102</v>
+      </c>
+      <c r="G160">
+        <v>32.96</v>
+      </c>
+      <c r="H160" t="s">
+        <v>16</v>
+      </c>
+      <c r="I160">
+        <v>12</v>
+      </c>
+      <c r="J160">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K160">
+        <v>1274.160003662109</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
+      <c r="A161" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B161" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" t="s">
+        <v>28</v>
+      </c>
+      <c r="D161">
+        <v>19.7444</v>
+      </c>
+      <c r="E161">
+        <v>20.32200050354004</v>
+      </c>
+      <c r="F161">
+        <v>0.0292538898897936</v>
+      </c>
+      <c r="G161">
+        <v>2.93</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161">
+        <v>61</v>
+      </c>
+      <c r="J161">
+        <v>1204.4084</v>
+      </c>
+      <c r="K161">
+        <v>1239.642030715942</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
+      <c r="A162" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B162" t="s">
+        <v>18</v>
+      </c>
+      <c r="C162" t="s">
+        <v>29</v>
+      </c>
+      <c r="D162">
+        <v>128.7814</v>
+      </c>
+      <c r="E162">
+        <v>141.1100006103516</v>
+      </c>
+      <c r="F162">
+        <v>0.09573277360202299</v>
+      </c>
+      <c r="G162">
+        <v>9.57</v>
+      </c>
+      <c r="H162" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162">
+        <v>44</v>
+      </c>
+      <c r="J162">
+        <v>5666.3816</v>
+      </c>
+      <c r="K162">
+        <v>6208.840026855469</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
+      <c r="A163" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B163" t="s">
+        <v>19</v>
+      </c>
+      <c r="C163" t="s">
+        <v>30</v>
+      </c>
+      <c r="D163">
+        <v>34.0694</v>
+      </c>
+      <c r="E163">
+        <v>33.49499893188477</v>
+      </c>
+      <c r="F163">
+        <v>-0.0168597353670811</v>
+      </c>
+      <c r="G163">
+        <v>-1.69</v>
+      </c>
+      <c r="H163" t="s">
+        <v>19</v>
+      </c>
+      <c r="I163">
+        <v>34</v>
+      </c>
+      <c r="J163">
+        <v>1158.3596</v>
+      </c>
+      <c r="K163">
+        <v>1138.829963684082</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="A164" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B164" t="s">
+        <v>20</v>
+      </c>
+      <c r="C164" t="s">
+        <v>31</v>
+      </c>
+      <c r="D164">
+        <v>69.7119</v>
+      </c>
+      <c r="E164">
+        <v>69.48000335693359</v>
+      </c>
+      <c r="F164">
+        <v>-0.0033265001106899</v>
+      </c>
+      <c r="G164">
+        <v>-0.33</v>
+      </c>
+      <c r="H164" t="s">
+        <v>20</v>
+      </c>
+      <c r="I164">
+        <v>54</v>
+      </c>
+      <c r="J164">
+        <v>3764.4426</v>
+      </c>
+      <c r="K164">
+        <v>3751.920181274414</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
+      <c r="A165" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B165" t="s">
+        <v>21</v>
+      </c>
+      <c r="C165" t="s">
+        <v>32</v>
+      </c>
+      <c r="D165">
+        <v>8.1868</v>
+      </c>
+      <c r="E165">
+        <v>8.085000038146973</v>
+      </c>
+      <c r="F165">
+        <v>-0.0124346462418805</v>
+      </c>
+      <c r="G165">
+        <v>-1.24</v>
+      </c>
+      <c r="H165" t="s">
+        <v>21</v>
+      </c>
+      <c r="I165">
+        <v>431</v>
+      </c>
+      <c r="J165">
+        <v>3528.5108</v>
+      </c>
+      <c r="K165">
+        <v>3484.635016441345</v>
       </c>
     </row>
   </sheetData>
@@ -7477,7 +7934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -8094,6 +8551,47 @@
       </c>
       <c r="M15" s="2">
         <v>0.04533109596729723</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.0685040942680248</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.0373091058105266</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.08732008670516531</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.0272125515115995</v>
+      </c>
+      <c r="F16" s="2">
+        <v>-0.0064783730551786</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.3295767631502102</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.0292538898897936</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.09573277360202299</v>
+      </c>
+      <c r="J16" s="2">
+        <v>-0.0168597353670811</v>
+      </c>
+      <c r="K16" s="2">
+        <v>-0.0033265001106899</v>
+      </c>
+      <c r="L16" s="2">
+        <v>-0.0124346462418805</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0.05004144884688144</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -269,16 +269,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$16</c:f>
+              <c:f>grafico_dati!$B$2:$B$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -323,6 +326,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.0685040942680248</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.0523267151329935</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -350,10 +356,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -398,16 +404,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$16</c:f>
+              <c:f>grafico_dati!$C$2:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -452,6 +461,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.0373091058105266</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.0237309246874031</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -479,10 +491,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -527,16 +539,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$16</c:f>
+              <c:f>grafico_dati!$D$2:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -581,6 +596,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.08732008670516531</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.07974291962844419</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -608,10 +626,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -656,16 +674,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$16</c:f>
+              <c:f>grafico_dati!$E$2:$E$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -710,6 +731,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.0272125515115995</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.0197046166046135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -737,10 +761,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -785,16 +809,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$16</c:f>
+              <c:f>grafico_dati!$F$2:$F$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -836,6 +863,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>-0.0064783730551786</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.0159935308789083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -863,10 +893,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -911,16 +941,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$16</c:f>
+              <c:f>grafico_dati!$G$2:$G$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -965,6 +998,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.3295767631502102</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.3305785391463871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -992,10 +1028,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1040,16 +1076,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$16</c:f>
+              <c:f>grafico_dati!$H$2:$H$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1094,6 +1133,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.0292538898897936</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.02834225676608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1121,10 +1163,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1169,16 +1211,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$16</c:f>
+              <c:f>grafico_dati!$I$2:$I$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1223,6 +1268,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.09573277360202299</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.0887442341352648</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1250,10 +1298,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1298,16 +1346,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$16</c:f>
+              <c:f>grafico_dati!$J$2:$J$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1352,6 +1403,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>-0.0168597353670811</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.034764383243227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1379,10 +1433,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1427,16 +1481,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$16</c:f>
+              <c:f>grafico_dati!$K$2:$K$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1481,6 +1538,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>-0.0033265001106899</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.0110726799670322</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1508,10 +1568,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1556,16 +1616,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$16</c:f>
+              <c:f>grafico_dati!$L$2:$L$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1610,6 +1673,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>-0.0124346462418805</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.0147554618726228</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1641,10 +1707,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$16</c:f>
+              <c:f>grafico_dati!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1689,16 +1755,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$16</c:f>
+              <c:f>grafico_dati!$M$2:$M$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0.08716234354652008</c:v>
                 </c:pt>
@@ -1743,6 +1812,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.05004144884688144</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.04276260357308259</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2149,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7925,6 +7997,391 @@
       </c>
       <c r="K165">
         <v>3484.635016441345</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="A166" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" t="s">
+        <v>22</v>
+      </c>
+      <c r="D166">
+        <v>50.07</v>
+      </c>
+      <c r="E166">
+        <v>52.68999862670898</v>
+      </c>
+      <c r="F166">
+        <v>0.0523267151329935</v>
+      </c>
+      <c r="G166">
+        <v>5.23</v>
+      </c>
+      <c r="H166" t="s">
+        <v>11</v>
+      </c>
+      <c r="I166">
+        <v>23</v>
+      </c>
+      <c r="J166">
+        <v>1151.61</v>
+      </c>
+      <c r="K166">
+        <v>1211.869968414306</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
+      <c r="A167" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B167" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" t="s">
+        <v>23</v>
+      </c>
+      <c r="D167">
+        <v>242.3</v>
+      </c>
+      <c r="E167">
+        <v>248.0500030517578</v>
+      </c>
+      <c r="F167">
+        <v>0.0237309246874031</v>
+      </c>
+      <c r="G167">
+        <v>2.37</v>
+      </c>
+      <c r="H167" t="s">
+        <v>12</v>
+      </c>
+      <c r="I167">
+        <v>5</v>
+      </c>
+      <c r="J167">
+        <v>1211.5</v>
+      </c>
+      <c r="K167">
+        <v>1240.250015258789</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
+      <c r="A168" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B168" t="s">
+        <v>13</v>
+      </c>
+      <c r="C168" t="s">
+        <v>24</v>
+      </c>
+      <c r="D168">
+        <v>38.273</v>
+      </c>
+      <c r="E168">
+        <v>41.32500076293945</v>
+      </c>
+      <c r="F168">
+        <v>0.07974291962844419</v>
+      </c>
+      <c r="G168">
+        <v>7.97</v>
+      </c>
+      <c r="H168" t="s">
+        <v>13</v>
+      </c>
+      <c r="I168">
+        <v>54</v>
+      </c>
+      <c r="J168">
+        <v>2066.742</v>
+      </c>
+      <c r="K168">
+        <v>2231.55004119873</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="A169" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B169" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169" t="s">
+        <v>25</v>
+      </c>
+      <c r="D169">
+        <v>6.5264</v>
+      </c>
+      <c r="E169">
+        <v>6.65500020980835</v>
+      </c>
+      <c r="F169">
+        <v>0.0197046166046135</v>
+      </c>
+      <c r="G169">
+        <v>1.97</v>
+      </c>
+      <c r="H169" t="s">
+        <v>14</v>
+      </c>
+      <c r="I169">
+        <v>276</v>
+      </c>
+      <c r="J169">
+        <v>1801.2864</v>
+      </c>
+      <c r="K169">
+        <v>1836.780057907104</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B170" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170" t="s">
+        <v>26</v>
+      </c>
+      <c r="D170">
+        <v>197.58</v>
+      </c>
+      <c r="E170">
+        <v>194.4199981689453</v>
+      </c>
+      <c r="F170">
+        <v>-0.0159935308789083</v>
+      </c>
+      <c r="G170">
+        <v>-1.6</v>
+      </c>
+      <c r="H170" t="s">
+        <v>15</v>
+      </c>
+      <c r="I170">
+        <v>4</v>
+      </c>
+      <c r="J170">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K170">
+        <v>777.6799926757812</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="s">
+        <v>27</v>
+      </c>
+      <c r="D171">
+        <v>79.86</v>
+      </c>
+      <c r="E171">
+        <v>106.2600021362305</v>
+      </c>
+      <c r="F171">
+        <v>0.3305785391463871</v>
+      </c>
+      <c r="G171">
+        <v>33.06</v>
+      </c>
+      <c r="H171" t="s">
+        <v>16</v>
+      </c>
+      <c r="I171">
+        <v>12</v>
+      </c>
+      <c r="J171">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K171">
+        <v>1275.120025634766</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B172" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" t="s">
+        <v>28</v>
+      </c>
+      <c r="D172">
+        <v>19.7444</v>
+      </c>
+      <c r="E172">
+        <v>20.30400085449219</v>
+      </c>
+      <c r="F172">
+        <v>0.02834225676608</v>
+      </c>
+      <c r="G172">
+        <v>2.83</v>
+      </c>
+      <c r="H172" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172">
+        <v>61</v>
+      </c>
+      <c r="J172">
+        <v>1204.4084</v>
+      </c>
+      <c r="K172">
+        <v>1238.544052124023</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B173" t="s">
+        <v>18</v>
+      </c>
+      <c r="C173" t="s">
+        <v>29</v>
+      </c>
+      <c r="D173">
+        <v>128.7814</v>
+      </c>
+      <c r="E173">
+        <v>140.2100067138672</v>
+      </c>
+      <c r="F173">
+        <v>0.0887442341352648</v>
+      </c>
+      <c r="G173">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H173" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173">
+        <v>44</v>
+      </c>
+      <c r="J173">
+        <v>5666.3816</v>
+      </c>
+      <c r="K173">
+        <v>6169.240295410156</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B174" t="s">
+        <v>19</v>
+      </c>
+      <c r="C174" t="s">
+        <v>30</v>
+      </c>
+      <c r="D174">
+        <v>34.0694</v>
+      </c>
+      <c r="E174">
+        <v>32.8849983215332</v>
+      </c>
+      <c r="F174">
+        <v>-0.034764383243227</v>
+      </c>
+      <c r="G174">
+        <v>-3.48</v>
+      </c>
+      <c r="H174" t="s">
+        <v>19</v>
+      </c>
+      <c r="I174">
+        <v>34</v>
+      </c>
+      <c r="J174">
+        <v>1158.3596</v>
+      </c>
+      <c r="K174">
+        <v>1118.089942932129</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B175" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" t="s">
+        <v>31</v>
+      </c>
+      <c r="D175">
+        <v>69.7119</v>
+      </c>
+      <c r="E175">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="F175">
+        <v>-0.0110726799670322</v>
+      </c>
+      <c r="G175">
+        <v>-1.11</v>
+      </c>
+      <c r="H175" t="s">
+        <v>20</v>
+      </c>
+      <c r="I175">
+        <v>54</v>
+      </c>
+      <c r="J175">
+        <v>3764.4426</v>
+      </c>
+      <c r="K175">
+        <v>3722.760131835938</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B176" t="s">
+        <v>21</v>
+      </c>
+      <c r="C176" t="s">
+        <v>32</v>
+      </c>
+      <c r="D176">
+        <v>8.1868</v>
+      </c>
+      <c r="E176">
+        <v>8.065999984741211</v>
+      </c>
+      <c r="F176">
+        <v>-0.0147554618726228</v>
+      </c>
+      <c r="G176">
+        <v>-1.48</v>
+      </c>
+      <c r="H176" t="s">
+        <v>21</v>
+      </c>
+      <c r="I176">
+        <v>431</v>
+      </c>
+      <c r="J176">
+        <v>3528.5108</v>
+      </c>
+      <c r="K176">
+        <v>3476.445993423462</v>
       </c>
     </row>
   </sheetData>
@@ -7934,7 +8391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -8592,6 +9049,47 @@
       </c>
       <c r="M16" s="2">
         <v>0.05004144884688144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.0523267151329935</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.0237309246874031</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.07974291962844419</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.0197046166046135</v>
+      </c>
+      <c r="F17" s="2">
+        <v>-0.0159935308789083</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.3305785391463871</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.02834225676608</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.0887442341352648</v>
+      </c>
+      <c r="J17" s="2">
+        <v>-0.034764383243227</v>
+      </c>
+      <c r="K17" s="2">
+        <v>-0.0110726799670322</v>
+      </c>
+      <c r="L17" s="2">
+        <v>-0.0147554618726228</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0.04276260357308259</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -272,16 +272,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$17</c:f>
+              <c:f>grafico_dati!$B$2:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -329,6 +332,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.0523267151329935</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.0379468987558042</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -356,10 +362,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -407,16 +413,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$17</c:f>
+              <c:f>grafico_dati!$C$2:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -464,6 +473,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.0237309246874031</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.0012381345439538</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -491,10 +503,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -542,16 +554,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$17</c:f>
+              <c:f>grafico_dati!$D$2:$D$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -599,6 +614,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.07974291962844419</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.0574034233193927</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -626,10 +644,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -677,16 +695,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$17</c:f>
+              <c:f>grafico_dati!$E$2:$E$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -734,6 +755,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.0197046166046135</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.0007048506571925</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -761,10 +785,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -812,16 +836,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$17</c:f>
+              <c:f>grafico_dati!$F$2:$F$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -866,6 +893,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>-0.0159935308789083</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.0440327721286947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -893,10 +923,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -944,16 +974,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$17</c:f>
+              <c:f>grafico_dati!$G$2:$G$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1001,6 +1034,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.3305785391463871</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.2882544108867764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1028,10 +1064,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1079,16 +1115,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$17</c:f>
+              <c:f>grafico_dati!$H$2:$H$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1136,6 +1175,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.02834225676608</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.0076781218192127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1163,10 +1205,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1214,16 +1256,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$17</c:f>
+              <c:f>grafico_dati!$I$2:$I$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1271,6 +1316,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.0887442341352648</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.0710397050799358</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1298,10 +1346,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1349,16 +1397,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$17</c:f>
+              <c:f>grafico_dati!$J$2:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1406,6 +1457,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>-0.034764383243227</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.0623550841862722</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,10 +1487,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1484,16 +1538,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$17</c:f>
+              <c:f>grafico_dati!$K$2:$K$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1541,6 +1598,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>-0.0110726799670322</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.0261347145946612</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1568,10 +1628,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1619,16 +1679,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$17</c:f>
+              <c:f>grafico_dati!$L$2:$L$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1676,6 +1739,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>-0.0147554618726228</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.0331997896793585</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1707,10 +1773,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$17</c:f>
+              <c:f>grafico_dati!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1758,16 +1824,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$17</c:f>
+              <c:f>grafico_dati!$M$2:$M$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.08716234354652008</c:v>
                 </c:pt>
@@ -1815,6 +1884,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.04276260357308259</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.02264088988293422</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2221,7 +2293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:K187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -8382,6 +8454,391 @@
       </c>
       <c r="K176">
         <v>3476.445993423462</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177">
+        <v>50.07</v>
+      </c>
+      <c r="E177">
+        <v>51.97000122070312</v>
+      </c>
+      <c r="F177">
+        <v>0.0379468987558042</v>
+      </c>
+      <c r="G177">
+        <v>3.79</v>
+      </c>
+      <c r="H177" t="s">
+        <v>11</v>
+      </c>
+      <c r="I177">
+        <v>23</v>
+      </c>
+      <c r="J177">
+        <v>1151.61</v>
+      </c>
+      <c r="K177">
+        <v>1195.310028076172</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B178" t="s">
+        <v>12</v>
+      </c>
+      <c r="C178" t="s">
+        <v>23</v>
+      </c>
+      <c r="D178">
+        <v>242.3</v>
+      </c>
+      <c r="E178">
+        <v>242</v>
+      </c>
+      <c r="F178">
+        <v>-0.0012381345439538</v>
+      </c>
+      <c r="G178">
+        <v>-0.12</v>
+      </c>
+      <c r="H178" t="s">
+        <v>12</v>
+      </c>
+      <c r="I178">
+        <v>5</v>
+      </c>
+      <c r="J178">
+        <v>1211.5</v>
+      </c>
+      <c r="K178">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
+      <c r="A179" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B179" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" t="s">
+        <v>24</v>
+      </c>
+      <c r="D179">
+        <v>38.273</v>
+      </c>
+      <c r="E179">
+        <v>40.47000122070312</v>
+      </c>
+      <c r="F179">
+        <v>0.0574034233193927</v>
+      </c>
+      <c r="G179">
+        <v>5.74</v>
+      </c>
+      <c r="H179" t="s">
+        <v>13</v>
+      </c>
+      <c r="I179">
+        <v>54</v>
+      </c>
+      <c r="J179">
+        <v>2066.742</v>
+      </c>
+      <c r="K179">
+        <v>2185.380065917969</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
+      <c r="A180" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B180" t="s">
+        <v>14</v>
+      </c>
+      <c r="C180" t="s">
+        <v>25</v>
+      </c>
+      <c r="D180">
+        <v>6.5264</v>
+      </c>
+      <c r="E180">
+        <v>6.531000137329102</v>
+      </c>
+      <c r="F180">
+        <v>0.0007048506571925</v>
+      </c>
+      <c r="G180">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H180" t="s">
+        <v>14</v>
+      </c>
+      <c r="I180">
+        <v>276</v>
+      </c>
+      <c r="J180">
+        <v>1801.2864</v>
+      </c>
+      <c r="K180">
+        <v>1802.556037902832</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
+      <c r="A181" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" t="s">
+        <v>26</v>
+      </c>
+      <c r="D181">
+        <v>197.58</v>
+      </c>
+      <c r="E181">
+        <v>188.8800048828125</v>
+      </c>
+      <c r="F181">
+        <v>-0.0440327721286947</v>
+      </c>
+      <c r="G181">
+        <v>-4.4</v>
+      </c>
+      <c r="H181" t="s">
+        <v>15</v>
+      </c>
+      <c r="I181">
+        <v>4</v>
+      </c>
+      <c r="J181">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K181">
+        <v>755.52001953125</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
+      <c r="A182" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="s">
+        <v>27</v>
+      </c>
+      <c r="D182">
+        <v>79.86</v>
+      </c>
+      <c r="E182">
+        <v>102.879997253418</v>
+      </c>
+      <c r="F182">
+        <v>0.2882544108867764</v>
+      </c>
+      <c r="G182">
+        <v>28.83</v>
+      </c>
+      <c r="H182" t="s">
+        <v>16</v>
+      </c>
+      <c r="I182">
+        <v>12</v>
+      </c>
+      <c r="J182">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K182">
+        <v>1234.559967041015</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
+      <c r="A183" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B183" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" t="s">
+        <v>28</v>
+      </c>
+      <c r="D183">
+        <v>19.7444</v>
+      </c>
+      <c r="E183">
+        <v>19.89599990844727</v>
+      </c>
+      <c r="F183">
+        <v>0.0076781218192127</v>
+      </c>
+      <c r="G183">
+        <v>0.77</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183">
+        <v>61</v>
+      </c>
+      <c r="J183">
+        <v>1204.4084</v>
+      </c>
+      <c r="K183">
+        <v>1213.655994415283</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
+      <c r="A184" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B184" t="s">
+        <v>18</v>
+      </c>
+      <c r="C184" t="s">
+        <v>29</v>
+      </c>
+      <c r="D184">
+        <v>128.7814</v>
+      </c>
+      <c r="E184">
+        <v>137.9299926757812</v>
+      </c>
+      <c r="F184">
+        <v>0.0710397050799358</v>
+      </c>
+      <c r="G184">
+        <v>7.1</v>
+      </c>
+      <c r="H184" t="s">
+        <v>18</v>
+      </c>
+      <c r="I184">
+        <v>44</v>
+      </c>
+      <c r="J184">
+        <v>5666.3816</v>
+      </c>
+      <c r="K184">
+        <v>6068.919677734375</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11">
+      <c r="A185" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B185" t="s">
+        <v>19</v>
+      </c>
+      <c r="C185" t="s">
+        <v>30</v>
+      </c>
+      <c r="D185">
+        <v>34.0694</v>
+      </c>
+      <c r="E185">
+        <v>31.94499969482422</v>
+      </c>
+      <c r="F185">
+        <v>-0.0623550841862722</v>
+      </c>
+      <c r="G185">
+        <v>-6.24</v>
+      </c>
+      <c r="H185" t="s">
+        <v>19</v>
+      </c>
+      <c r="I185">
+        <v>34</v>
+      </c>
+      <c r="J185">
+        <v>1158.3596</v>
+      </c>
+      <c r="K185">
+        <v>1086.129989624023</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11">
+      <c r="A186" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B186" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" t="s">
+        <v>31</v>
+      </c>
+      <c r="D186">
+        <v>69.7119</v>
+      </c>
+      <c r="E186">
+        <v>67.88999938964844</v>
+      </c>
+      <c r="F186">
+        <v>-0.0261347145946612</v>
+      </c>
+      <c r="G186">
+        <v>-2.61</v>
+      </c>
+      <c r="H186" t="s">
+        <v>20</v>
+      </c>
+      <c r="I186">
+        <v>54</v>
+      </c>
+      <c r="J186">
+        <v>3764.4426</v>
+      </c>
+      <c r="K186">
+        <v>3666.059967041016</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11">
+      <c r="A187" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B187" t="s">
+        <v>21</v>
+      </c>
+      <c r="C187" t="s">
+        <v>32</v>
+      </c>
+      <c r="D187">
+        <v>8.1868</v>
+      </c>
+      <c r="E187">
+        <v>7.914999961853027</v>
+      </c>
+      <c r="F187">
+        <v>-0.0331997896793585</v>
+      </c>
+      <c r="G187">
+        <v>-3.32</v>
+      </c>
+      <c r="H187" t="s">
+        <v>21</v>
+      </c>
+      <c r="I187">
+        <v>431</v>
+      </c>
+      <c r="J187">
+        <v>3528.5108</v>
+      </c>
+      <c r="K187">
+        <v>3411.364983558655</v>
       </c>
     </row>
   </sheetData>
@@ -8391,7 +8848,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -9090,6 +9547,47 @@
       </c>
       <c r="M17" s="2">
         <v>0.04276260357308259</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.0379468987558042</v>
+      </c>
+      <c r="C18" s="2">
+        <v>-0.0012381345439538</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.0574034233193927</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.0007048506571925</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-0.0440327721286947</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.2882544108867764</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.0076781218192127</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.0710397050799358</v>
+      </c>
+      <c r="J18" s="2">
+        <v>-0.0623550841862722</v>
+      </c>
+      <c r="K18" s="2">
+        <v>-0.0261347145946612</v>
+      </c>
+      <c r="L18" s="2">
+        <v>-0.0331997896793585</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0.02264088988293422</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -275,16 +275,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$18</c:f>
+              <c:f>grafico_dati!$B$2:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -335,6 +338,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.0379468987558042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.0191731331994582</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -362,10 +368,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -416,16 +422,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$18</c:f>
+              <c:f>grafico_dati!$C$2:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -476,6 +485,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>-0.0012381345439538</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.0128353180296895</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -503,10 +515,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -557,16 +569,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$18</c:f>
+              <c:f>grafico_dati!$D$2:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -617,6 +632,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.0574034233193927</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.0380686003771935</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -644,10 +662,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -698,16 +716,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$18</c:f>
+              <c:f>grafico_dati!$E$2:$E$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -758,6 +779,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.0007048506571925</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.0184481280140503</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -785,10 +809,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -839,16 +863,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$18</c:f>
+              <c:f>grafico_dati!$F$2:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -896,6 +923,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>-0.0440327721286947</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.0626581792274412</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -923,10 +953,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -977,16 +1007,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$18</c:f>
+              <c:f>grafico_dati!$G$2:$G$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1037,6 +1070,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.2882544108867764</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.2694715408642369</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1064,10 +1100,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1118,16 +1154,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$18</c:f>
+              <c:f>grafico_dati!$H$2:$H$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1178,6 +1217,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.0076781218192127</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.008984854671460899</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1205,10 +1247,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1259,16 +1301,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$18</c:f>
+              <c:f>grafico_dati!$I$2:$I$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1319,6 +1364,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.0710397050799358</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.051196989878117</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1346,10 +1394,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1400,16 +1448,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$18</c:f>
+              <c:f>grafico_dati!$J$2:$J$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1460,6 +1511,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>-0.0623550841862722</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.0701333071561054</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1487,10 +1541,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1541,16 +1595,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$18</c:f>
+              <c:f>grafico_dati!$K$2:$K$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1601,6 +1658,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>-0.0261347145946612</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.0303360681776519</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1628,10 +1688,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1682,16 +1742,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$18</c:f>
+              <c:f>grafico_dati!$L$2:$L$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1742,6 +1805,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>-0.0331997896793585</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.0434602224035267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1773,10 +1839,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$18</c:f>
+              <c:f>grafico_dati!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1827,66 +1893,72 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$18</c:f>
+              <c:f>grafico_dati!$M$2:$M$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>0.08716234354652008</c:v>
+                  <c:v>0.08659212287311968</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.08642337438346992</c:v>
+                  <c:v>0.08575413785832886</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.08388619620156357</c:v>
+                  <c:v>0.08313910176808248</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.08049762046967701</c:v>
+                  <c:v>0.08013679690745534</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.05460028906895609</c:v>
+                  <c:v>0.05511860933311308</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0673126116906817</c:v>
+                  <c:v>0.067733222569895</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0551626975197308</c:v>
+                  <c:v>0.05588978697012448</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.04325666086938806</c:v>
+                  <c:v>0.04393944472218569</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.03878100707485044</c:v>
+                  <c:v>0.03947997164330386</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.05968402110857607</c:v>
+                  <c:v>0.05996044742932116</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.050688625305223</c:v>
+                  <c:v>0.05126016601743588</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.04246482181549616</c:v>
+                  <c:v>0.04322778601843358</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.03960189634549893</c:v>
+                  <c:v>0.04040918396084137</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04533109596729723</c:v>
+                  <c:v>0.04595019140029666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.05004144884688144</c:v>
+                  <c:v>0.05050291159109199</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04276260357308259</c:v>
+                  <c:v>0.04322410959754541</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.02264088988293422</c:v>
+                  <c:v>0.02330435739138426</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.009025881265433133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2293,7 +2365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K187"/>
+  <dimension ref="A1:K198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2602,13 +2674,13 @@
         <v>18</v>
       </c>
       <c r="I9">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J9">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K9">
-        <v>6308.27978515625</v>
+        <v>7311.869750976562</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2672,13 +2744,13 @@
         <v>20</v>
       </c>
       <c r="I11">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J11">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K11">
-        <v>3838.320098876953</v>
+        <v>4406.960113525391</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2987,13 +3059,13 @@
         <v>18</v>
       </c>
       <c r="I20">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J20">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K20">
-        <v>6298.159973144531</v>
+        <v>7300.13996887207</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3057,13 +3129,13 @@
         <v>20</v>
       </c>
       <c r="I22">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J22">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K22">
-        <v>3825.359802246094</v>
+        <v>4392.079772949219</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3372,13 +3444,13 @@
         <v>18</v>
       </c>
       <c r="I31">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J31">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K31">
-        <v>6267.799865722656</v>
+        <v>7264.949844360352</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3442,13 +3514,13 @@
         <v>20</v>
       </c>
       <c r="I33">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J33">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K33">
-        <v>3819.959884643555</v>
+        <v>4385.879867553711</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3757,13 +3829,13 @@
         <v>18</v>
       </c>
       <c r="I42">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J42">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K42">
-        <v>6286.27978515625</v>
+        <v>7286.369750976562</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3827,13 +3899,13 @@
         <v>20</v>
       </c>
       <c r="I44">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J44">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K44">
-        <v>3831.299835205078</v>
+        <v>4398.899810791016</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -4142,13 +4214,13 @@
         <v>18</v>
       </c>
       <c r="I53">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J53">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K53">
-        <v>6220.27978515625</v>
+        <v>7209.869750976562</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4212,13 +4284,13 @@
         <v>20</v>
       </c>
       <c r="I55">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J55">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K55">
-        <v>3794.040115356445</v>
+        <v>4356.120132446289</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4527,13 +4599,13 @@
         <v>18</v>
       </c>
       <c r="I64">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J64">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K64">
-        <v>6288.479919433594</v>
+        <v>7288.919906616211</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4597,13 +4669,13 @@
         <v>20</v>
       </c>
       <c r="I66">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J66">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K66">
-        <v>3829.679901123047</v>
+        <v>4397.039886474609</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -4912,13 +4984,13 @@
         <v>18</v>
       </c>
       <c r="I75">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J75">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K75">
-        <v>6255.919677734375</v>
+        <v>7251.179626464844</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4982,13 +5054,13 @@
         <v>20</v>
       </c>
       <c r="I77">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J77">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K77">
-        <v>3796.200164794922</v>
+        <v>4358.600189208984</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -5297,13 +5369,13 @@
         <v>18</v>
       </c>
       <c r="I86">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J86">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K86">
-        <v>6181.560241699219</v>
+        <v>7164.990280151367</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -5367,13 +5439,13 @@
         <v>20</v>
       </c>
       <c r="I88">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J88">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K88">
-        <v>3751.380065917969</v>
+        <v>4307.140075683594</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -5682,13 +5754,13 @@
         <v>18</v>
       </c>
       <c r="I97">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J97">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K97">
-        <v>6159.119812011719</v>
+        <v>7138.979782104492</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -5752,13 +5824,13 @@
         <v>20</v>
       </c>
       <c r="I99">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J99">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K99">
-        <v>3734.100082397461</v>
+        <v>4287.300094604492</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -6032,13 +6104,13 @@
         <v>18</v>
       </c>
       <c r="I107">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J107">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K107">
-        <v>6240.959838867188</v>
+        <v>7233.839813232422</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -6102,13 +6174,13 @@
         <v>20</v>
       </c>
       <c r="I109">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J109">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K109">
-        <v>3780</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -6417,13 +6489,13 @@
         <v>18</v>
       </c>
       <c r="I118">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J118">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K118">
-        <v>6219.840026855469</v>
+        <v>7209.36003112793</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -6487,13 +6559,13 @@
         <v>20</v>
       </c>
       <c r="I120">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J120">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K120">
-        <v>3764.880065917969</v>
+        <v>4322.640075683594</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -6802,13 +6874,13 @@
         <v>18</v>
       </c>
       <c r="I129">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J129">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K129">
-        <v>6190.799865722656</v>
+        <v>7175.699844360352</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -6872,13 +6944,13 @@
         <v>20</v>
       </c>
       <c r="I131">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J131">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K131">
-        <v>3747.059967041016</v>
+        <v>4302.179962158203</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7187,13 +7259,13 @@
         <v>18</v>
       </c>
       <c r="I140">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J140">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K140">
-        <v>6178.479919433594</v>
+        <v>7161.419906616211</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -7257,13 +7329,13 @@
         <v>20</v>
       </c>
       <c r="I142">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J142">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K142">
-        <v>3739.5</v>
+        <v>4293.5</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -7572,13 +7644,13 @@
         <v>18</v>
       </c>
       <c r="I151">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J151">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K151">
-        <v>6195.200134277344</v>
+        <v>7180.800155639648</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -7642,13 +7714,13 @@
         <v>20</v>
       </c>
       <c r="I153">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J153">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K153">
-        <v>3746.51985168457</v>
+        <v>4301.559829711914</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -7957,13 +8029,13 @@
         <v>18</v>
       </c>
       <c r="I162">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J162">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K162">
-        <v>6208.840026855469</v>
+        <v>7196.61003112793</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -8027,13 +8099,13 @@
         <v>20</v>
       </c>
       <c r="I164">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J164">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K164">
-        <v>3751.920181274414</v>
+        <v>4307.760208129883</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -8342,13 +8414,13 @@
         <v>18</v>
       </c>
       <c r="I173">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J173">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K173">
-        <v>6169.240295410156</v>
+        <v>7150.710342407227</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -8412,13 +8484,13 @@
         <v>20</v>
       </c>
       <c r="I175">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J175">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K175">
-        <v>3722.760131835938</v>
+        <v>4274.280151367188</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -8727,13 +8799,13 @@
         <v>18</v>
       </c>
       <c r="I184">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J184">
-        <v>5666.3816</v>
+        <v>6567.8514</v>
       </c>
       <c r="K184">
-        <v>6068.919677734375</v>
+        <v>7034.429626464844</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -8797,13 +8869,13 @@
         <v>20</v>
       </c>
       <c r="I186">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J186">
-        <v>3764.4426</v>
+        <v>4322.1378</v>
       </c>
       <c r="K186">
-        <v>3666.059967041016</v>
+        <v>4209.179962158203</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -8839,6 +8911,391 @@
       </c>
       <c r="K187">
         <v>3411.364983558655</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
+      <c r="A188" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B188" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" t="s">
+        <v>22</v>
+      </c>
+      <c r="D188">
+        <v>50.07</v>
+      </c>
+      <c r="E188">
+        <v>51.02999877929688</v>
+      </c>
+      <c r="F188">
+        <v>0.0191731331994582</v>
+      </c>
+      <c r="G188">
+        <v>1.92</v>
+      </c>
+      <c r="H188" t="s">
+        <v>11</v>
+      </c>
+      <c r="I188">
+        <v>23</v>
+      </c>
+      <c r="J188">
+        <v>1151.61</v>
+      </c>
+      <c r="K188">
+        <v>1173.689971923828</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
+      <c r="A189" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B189" t="s">
+        <v>12</v>
+      </c>
+      <c r="C189" t="s">
+        <v>23</v>
+      </c>
+      <c r="D189">
+        <v>242.3</v>
+      </c>
+      <c r="E189">
+        <v>239.1900024414062</v>
+      </c>
+      <c r="F189">
+        <v>-0.0128353180296895</v>
+      </c>
+      <c r="G189">
+        <v>-1.28</v>
+      </c>
+      <c r="H189" t="s">
+        <v>12</v>
+      </c>
+      <c r="I189">
+        <v>5</v>
+      </c>
+      <c r="J189">
+        <v>1211.5</v>
+      </c>
+      <c r="K189">
+        <v>1195.950012207031</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
+      <c r="A190" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B190" t="s">
+        <v>13</v>
+      </c>
+      <c r="C190" t="s">
+        <v>24</v>
+      </c>
+      <c r="D190">
+        <v>38.273</v>
+      </c>
+      <c r="E190">
+        <v>39.72999954223633</v>
+      </c>
+      <c r="F190">
+        <v>0.0380686003771935</v>
+      </c>
+      <c r="G190">
+        <v>3.81</v>
+      </c>
+      <c r="H190" t="s">
+        <v>13</v>
+      </c>
+      <c r="I190">
+        <v>54</v>
+      </c>
+      <c r="J190">
+        <v>2066.742</v>
+      </c>
+      <c r="K190">
+        <v>2145.419975280762</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
+      <c r="A191" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B191" t="s">
+        <v>14</v>
+      </c>
+      <c r="C191" t="s">
+        <v>25</v>
+      </c>
+      <c r="D191">
+        <v>6.5264</v>
+      </c>
+      <c r="E191">
+        <v>6.406000137329102</v>
+      </c>
+      <c r="F191">
+        <v>-0.0184481280140503</v>
+      </c>
+      <c r="G191">
+        <v>-1.84</v>
+      </c>
+      <c r="H191" t="s">
+        <v>14</v>
+      </c>
+      <c r="I191">
+        <v>276</v>
+      </c>
+      <c r="J191">
+        <v>1801.2864</v>
+      </c>
+      <c r="K191">
+        <v>1768.056037902832</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11">
+      <c r="A192" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B192" t="s">
+        <v>15</v>
+      </c>
+      <c r="C192" t="s">
+        <v>26</v>
+      </c>
+      <c r="D192">
+        <v>197.58</v>
+      </c>
+      <c r="E192">
+        <v>185.1999969482422</v>
+      </c>
+      <c r="F192">
+        <v>-0.0626581792274412</v>
+      </c>
+      <c r="G192">
+        <v>-6.27</v>
+      </c>
+      <c r="H192" t="s">
+        <v>15</v>
+      </c>
+      <c r="I192">
+        <v>4</v>
+      </c>
+      <c r="J192">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K192">
+        <v>740.7999877929688</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11">
+      <c r="A193" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="s">
+        <v>27</v>
+      </c>
+      <c r="D193">
+        <v>79.86</v>
+      </c>
+      <c r="E193">
+        <v>101.379997253418</v>
+      </c>
+      <c r="F193">
+        <v>0.2694715408642369</v>
+      </c>
+      <c r="G193">
+        <v>26.95</v>
+      </c>
+      <c r="H193" t="s">
+        <v>16</v>
+      </c>
+      <c r="I193">
+        <v>12</v>
+      </c>
+      <c r="J193">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K193">
+        <v>1216.559967041015</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11">
+      <c r="A194" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B194" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194" t="s">
+        <v>28</v>
+      </c>
+      <c r="D194">
+        <v>19.7444</v>
+      </c>
+      <c r="E194">
+        <v>19.5669994354248</v>
+      </c>
+      <c r="F194">
+        <v>-0.008984854671460899</v>
+      </c>
+      <c r="G194">
+        <v>-0.9</v>
+      </c>
+      <c r="H194" t="s">
+        <v>17</v>
+      </c>
+      <c r="I194">
+        <v>61</v>
+      </c>
+      <c r="J194">
+        <v>1204.4084</v>
+      </c>
+      <c r="K194">
+        <v>1193.586965560913</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11">
+      <c r="A195" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B195" t="s">
+        <v>18</v>
+      </c>
+      <c r="C195" t="s">
+        <v>29</v>
+      </c>
+      <c r="D195">
+        <v>129.871</v>
+      </c>
+      <c r="E195">
+        <v>136.5200042724609</v>
+      </c>
+      <c r="F195">
+        <v>0.051196989878117</v>
+      </c>
+      <c r="G195">
+        <v>5.12</v>
+      </c>
+      <c r="H195" t="s">
+        <v>18</v>
+      </c>
+      <c r="I195">
+        <v>51</v>
+      </c>
+      <c r="J195">
+        <v>6623.421</v>
+      </c>
+      <c r="K195">
+        <v>6962.520217895508</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11">
+      <c r="A196" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B196" t="s">
+        <v>19</v>
+      </c>
+      <c r="C196" t="s">
+        <v>30</v>
+      </c>
+      <c r="D196">
+        <v>34.0694</v>
+      </c>
+      <c r="E196">
+        <v>31.68000030517578</v>
+      </c>
+      <c r="F196">
+        <v>-0.0701333071561054</v>
+      </c>
+      <c r="G196">
+        <v>-7.01</v>
+      </c>
+      <c r="H196" t="s">
+        <v>19</v>
+      </c>
+      <c r="I196">
+        <v>34</v>
+      </c>
+      <c r="J196">
+        <v>1158.3596</v>
+      </c>
+      <c r="K196">
+        <v>1077.120010375977</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
+      <c r="A197" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B197" t="s">
+        <v>20</v>
+      </c>
+      <c r="C197" t="s">
+        <v>31</v>
+      </c>
+      <c r="D197">
+        <v>69.4158</v>
+      </c>
+      <c r="E197">
+        <v>67.30999755859375</v>
+      </c>
+      <c r="F197">
+        <v>-0.0303360681776519</v>
+      </c>
+      <c r="G197">
+        <v>-3.03</v>
+      </c>
+      <c r="H197" t="s">
+        <v>20</v>
+      </c>
+      <c r="I197">
+        <v>62</v>
+      </c>
+      <c r="J197">
+        <v>4303.7796</v>
+      </c>
+      <c r="K197">
+        <v>4173.219848632812</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
+      <c r="A198" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B198" t="s">
+        <v>21</v>
+      </c>
+      <c r="C198" t="s">
+        <v>32</v>
+      </c>
+      <c r="D198">
+        <v>8.1868</v>
+      </c>
+      <c r="E198">
+        <v>7.830999851226807</v>
+      </c>
+      <c r="F198">
+        <v>-0.0434602224035267</v>
+      </c>
+      <c r="G198">
+        <v>-4.35</v>
+      </c>
+      <c r="H198" t="s">
+        <v>21</v>
+      </c>
+      <c r="I198">
+        <v>431</v>
+      </c>
+      <c r="J198">
+        <v>3528.5108</v>
+      </c>
+      <c r="K198">
+        <v>3375.160935878754</v>
       </c>
     </row>
   </sheetData>
@@ -8848,7 +9305,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -8934,7 +9391,7 @@
         <v>0.0259197937957051</v>
       </c>
       <c r="M2" s="2">
-        <v>0.08716234354652008</v>
+        <v>0.08659212287311968</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8975,7 +9432,7 @@
         <v>0.0298284746005002</v>
       </c>
       <c r="M3" s="2">
-        <v>0.08642337438346992</v>
+        <v>0.08575413785832886</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9016,7 +9473,7 @@
         <v>0.0267748250023331</v>
       </c>
       <c r="M4" s="2">
-        <v>0.08388619620156357</v>
+        <v>0.08313910176808248</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9057,7 +9514,7 @@
         <v>0.0272633809806162</v>
       </c>
       <c r="M5" s="2">
-        <v>0.08049762046967701</v>
+        <v>0.08013679690745534</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9098,7 +9555,7 @@
         <v>0.0102848375979951</v>
       </c>
       <c r="M6" s="2">
-        <v>0.05460028906895609</v>
+        <v>0.05511860933311308</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9139,7 +9596,7 @@
         <v>0.019812378110106</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0673126116906817</v>
+        <v>0.067733222569895</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9180,7 +9637,7 @@
         <v>0.0115063440329679</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0551626975197308</v>
+        <v>0.05588978697012448</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -9221,7 +9678,7 @@
         <v>-0.0070601810129711</v>
       </c>
       <c r="M9" s="2">
-        <v>0.04325666086938806</v>
+        <v>0.04393944472218569</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -9262,7 +9719,7 @@
         <v>-0.0187863399166211</v>
       </c>
       <c r="M10" s="2">
-        <v>0.03878100707485044</v>
+        <v>0.03947997164330386</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -9300,7 +9757,7 @@
         <v>0.0019788035208567</v>
       </c>
       <c r="M11" s="2">
-        <v>0.05968402110857607</v>
+        <v>0.05996044742932116</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -9341,7 +9798,7 @@
         <v>-0.0076709342304576</v>
       </c>
       <c r="M12" s="2">
-        <v>0.050688625305223</v>
+        <v>0.05126016601743588</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -9382,7 +9839,7 @@
         <v>-0.0151219371009677</v>
       </c>
       <c r="M13" s="2">
-        <v>0.04246482181549616</v>
+        <v>0.04322778601843358</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -9423,7 +9880,7 @@
         <v>-0.0195191738840457</v>
       </c>
       <c r="M14" s="2">
-        <v>0.03960189634549893</v>
+        <v>0.04040918396084137</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -9464,7 +9921,7 @@
         <v>-0.0154882958400475</v>
       </c>
       <c r="M15" s="2">
-        <v>0.04533109596729723</v>
+        <v>0.04595019140029666</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -9505,7 +9962,7 @@
         <v>-0.0124346462418805</v>
       </c>
       <c r="M16" s="2">
-        <v>0.05004144884688144</v>
+        <v>0.05050291159109199</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -9546,7 +10003,7 @@
         <v>-0.0147554618726228</v>
       </c>
       <c r="M17" s="2">
-        <v>0.04276260357308259</v>
+        <v>0.04322410959754541</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -9587,7 +10044,48 @@
         <v>-0.0331997896793585</v>
       </c>
       <c r="M18" s="2">
-        <v>0.02264088988293422</v>
+        <v>0.02330435739138426</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.0191731331994582</v>
+      </c>
+      <c r="C19" s="2">
+        <v>-0.0128353180296895</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.0380686003771935</v>
+      </c>
+      <c r="E19" s="2">
+        <v>-0.0184481280140503</v>
+      </c>
+      <c r="F19" s="2">
+        <v>-0.0626581792274412</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.2694715408642369</v>
+      </c>
+      <c r="H19" s="2">
+        <v>-0.008984854671460899</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.051196989878117</v>
+      </c>
+      <c r="J19" s="2">
+        <v>-0.0701333071561054</v>
+      </c>
+      <c r="K19" s="2">
+        <v>-0.0303360681776519</v>
+      </c>
+      <c r="L19" s="2">
+        <v>-0.0434602224035267</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0.009025881265433133</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -278,16 +278,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$19</c:f>
+              <c:f>grafico_dati!$B$2:$B$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -341,6 +344,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.0191731331994582</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.0319552260624189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -368,10 +374,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -425,16 +431,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$19</c:f>
+              <c:f>grafico_dati!$C$2:$C$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -488,6 +497,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-0.0128353180296895</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.0076351756160042</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -515,10 +527,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -572,16 +584,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$19</c:f>
+              <c:f>grafico_dati!$D$2:$D$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -635,6 +650,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.0380686003771935</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.0485198721844442</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -662,10 +680,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -719,16 +737,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$19</c:f>
+              <c:f>grafico_dati!$E$2:$E$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -782,6 +803,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-0.0184481280140503</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.0092547070193915</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -809,10 +833,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -866,16 +890,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$19</c:f>
+              <c:f>grafico_dati!$F$2:$F$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -926,6 +953,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-0.0626581792274412</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.0521307886461338</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -953,10 +983,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1010,16 +1040,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$19</c:f>
+              <c:f>grafico_dati!$G$2:$G$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1073,6 +1106,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.2694715408642369</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.2844978942030389</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1100,10 +1136,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1157,16 +1193,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$19</c:f>
+              <c:f>grafico_dati!$H$2:$H$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1220,6 +1259,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-0.008984854671460899</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.0014231419781132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1247,10 +1289,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1304,16 +1346,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$19</c:f>
+              <c:f>grafico_dati!$I$2:$I$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1367,6 +1412,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.051196989878117</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.0556629740551439</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1394,10 +1442,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1451,16 +1499,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$19</c:f>
+              <c:f>grafico_dati!$J$2:$J$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1514,6 +1565,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-0.0701333071561054</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.064409704896476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1541,10 +1595,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1598,16 +1652,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$19</c:f>
+              <c:f>grafico_dati!$K$2:$K$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1661,6 +1718,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-0.0303360681776519</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.0250058300102313</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1688,10 +1748,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1745,16 +1805,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$19</c:f>
+              <c:f>grafico_dati!$L$2:$L$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1808,6 +1871,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-0.0434602224035267</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.0360091612883839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1839,10 +1905,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$19</c:f>
+              <c:f>grafico_dati!$A$2:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1896,16 +1962,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$19</c:f>
+              <c:f>grafico_dati!$M$2:$M$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -1959,6 +2028,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.009025881265433133</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.01627949441484677</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2365,7 +2437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K198"/>
+  <dimension ref="A1:K209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -9296,6 +9368,391 @@
       </c>
       <c r="K198">
         <v>3375.160935878754</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11">
+      <c r="A199" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B199" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" t="s">
+        <v>22</v>
+      </c>
+      <c r="D199">
+        <v>50.07</v>
+      </c>
+      <c r="E199">
+        <v>51.66999816894531</v>
+      </c>
+      <c r="F199">
+        <v>0.0319552260624189</v>
+      </c>
+      <c r="G199">
+        <v>3.2</v>
+      </c>
+      <c r="H199" t="s">
+        <v>11</v>
+      </c>
+      <c r="I199">
+        <v>23</v>
+      </c>
+      <c r="J199">
+        <v>1151.61</v>
+      </c>
+      <c r="K199">
+        <v>1188.409957885742</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11">
+      <c r="A200" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B200" t="s">
+        <v>12</v>
+      </c>
+      <c r="C200" t="s">
+        <v>23</v>
+      </c>
+      <c r="D200">
+        <v>242.3</v>
+      </c>
+      <c r="E200">
+        <v>240.4499969482422</v>
+      </c>
+      <c r="F200">
+        <v>-0.0076351756160042</v>
+      </c>
+      <c r="G200">
+        <v>-0.76</v>
+      </c>
+      <c r="H200" t="s">
+        <v>12</v>
+      </c>
+      <c r="I200">
+        <v>5</v>
+      </c>
+      <c r="J200">
+        <v>1211.5</v>
+      </c>
+      <c r="K200">
+        <v>1202.249984741211</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
+      <c r="A201" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B201" t="s">
+        <v>13</v>
+      </c>
+      <c r="C201" t="s">
+        <v>24</v>
+      </c>
+      <c r="D201">
+        <v>38.273</v>
+      </c>
+      <c r="E201">
+        <v>40.13000106811523</v>
+      </c>
+      <c r="F201">
+        <v>0.0485198721844442</v>
+      </c>
+      <c r="G201">
+        <v>4.85</v>
+      </c>
+      <c r="H201" t="s">
+        <v>13</v>
+      </c>
+      <c r="I201">
+        <v>54</v>
+      </c>
+      <c r="J201">
+        <v>2066.742</v>
+      </c>
+      <c r="K201">
+        <v>2167.020057678223</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
+      <c r="A202" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B202" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202" t="s">
+        <v>25</v>
+      </c>
+      <c r="D202">
+        <v>6.5264</v>
+      </c>
+      <c r="E202">
+        <v>6.466000080108643</v>
+      </c>
+      <c r="F202">
+        <v>-0.0092547070193915</v>
+      </c>
+      <c r="G202">
+        <v>-0.93</v>
+      </c>
+      <c r="H202" t="s">
+        <v>14</v>
+      </c>
+      <c r="I202">
+        <v>276</v>
+      </c>
+      <c r="J202">
+        <v>1801.2864</v>
+      </c>
+      <c r="K202">
+        <v>1784.616022109985</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11">
+      <c r="A203" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B203" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" t="s">
+        <v>26</v>
+      </c>
+      <c r="D203">
+        <v>197.58</v>
+      </c>
+      <c r="E203">
+        <v>187.2799987792969</v>
+      </c>
+      <c r="F203">
+        <v>-0.0521307886461338</v>
+      </c>
+      <c r="G203">
+        <v>-5.21</v>
+      </c>
+      <c r="H203" t="s">
+        <v>15</v>
+      </c>
+      <c r="I203">
+        <v>4</v>
+      </c>
+      <c r="J203">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K203">
+        <v>749.1199951171875</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11">
+      <c r="A204" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B204" t="s">
+        <v>16</v>
+      </c>
+      <c r="C204" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204">
+        <v>79.86</v>
+      </c>
+      <c r="E204">
+        <v>102.5800018310547</v>
+      </c>
+      <c r="F204">
+        <v>0.2844978942030389</v>
+      </c>
+      <c r="G204">
+        <v>28.45</v>
+      </c>
+      <c r="H204" t="s">
+        <v>16</v>
+      </c>
+      <c r="I204">
+        <v>12</v>
+      </c>
+      <c r="J204">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K204">
+        <v>1230.960021972656</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11">
+      <c r="A205" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B205" t="s">
+        <v>17</v>
+      </c>
+      <c r="C205" t="s">
+        <v>28</v>
+      </c>
+      <c r="D205">
+        <v>19.7444</v>
+      </c>
+      <c r="E205">
+        <v>19.77249908447266</v>
+      </c>
+      <c r="F205">
+        <v>0.0014231419781132</v>
+      </c>
+      <c r="G205">
+        <v>0.14</v>
+      </c>
+      <c r="H205" t="s">
+        <v>17</v>
+      </c>
+      <c r="I205">
+        <v>61</v>
+      </c>
+      <c r="J205">
+        <v>1204.4084</v>
+      </c>
+      <c r="K205">
+        <v>1206.122444152832</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11">
+      <c r="A206" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B206" t="s">
+        <v>18</v>
+      </c>
+      <c r="C206" t="s">
+        <v>29</v>
+      </c>
+      <c r="D206">
+        <v>129.871</v>
+      </c>
+      <c r="E206">
+        <v>137.1000061035156</v>
+      </c>
+      <c r="F206">
+        <v>0.0556629740551439</v>
+      </c>
+      <c r="G206">
+        <v>5.57</v>
+      </c>
+      <c r="H206" t="s">
+        <v>18</v>
+      </c>
+      <c r="I206">
+        <v>51</v>
+      </c>
+      <c r="J206">
+        <v>6623.421</v>
+      </c>
+      <c r="K206">
+        <v>6992.100311279297</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11">
+      <c r="A207" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B207" t="s">
+        <v>19</v>
+      </c>
+      <c r="C207" t="s">
+        <v>30</v>
+      </c>
+      <c r="D207">
+        <v>34.0694</v>
+      </c>
+      <c r="E207">
+        <v>31.875</v>
+      </c>
+      <c r="F207">
+        <v>-0.064409704896476</v>
+      </c>
+      <c r="G207">
+        <v>-6.44</v>
+      </c>
+      <c r="H207" t="s">
+        <v>19</v>
+      </c>
+      <c r="I207">
+        <v>34</v>
+      </c>
+      <c r="J207">
+        <v>1158.3596</v>
+      </c>
+      <c r="K207">
+        <v>1083.75</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11">
+      <c r="A208" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B208" t="s">
+        <v>20</v>
+      </c>
+      <c r="C208" t="s">
+        <v>31</v>
+      </c>
+      <c r="D208">
+        <v>69.4158</v>
+      </c>
+      <c r="E208">
+        <v>67.68000030517578</v>
+      </c>
+      <c r="F208">
+        <v>-0.0250058300102313</v>
+      </c>
+      <c r="G208">
+        <v>-2.5</v>
+      </c>
+      <c r="H208" t="s">
+        <v>20</v>
+      </c>
+      <c r="I208">
+        <v>62</v>
+      </c>
+      <c r="J208">
+        <v>4303.7796</v>
+      </c>
+      <c r="K208">
+        <v>4196.160018920898</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11">
+      <c r="A209" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B209" t="s">
+        <v>21</v>
+      </c>
+      <c r="C209" t="s">
+        <v>32</v>
+      </c>
+      <c r="D209">
+        <v>8.1868</v>
+      </c>
+      <c r="E209">
+        <v>7.892000198364258</v>
+      </c>
+      <c r="F209">
+        <v>-0.0360091612883839</v>
+      </c>
+      <c r="G209">
+        <v>-3.6</v>
+      </c>
+      <c r="H209" t="s">
+        <v>21</v>
+      </c>
+      <c r="I209">
+        <v>431</v>
+      </c>
+      <c r="J209">
+        <v>3528.5108</v>
+      </c>
+      <c r="K209">
+        <v>3401.452085494995</v>
       </c>
     </row>
   </sheetData>
@@ -9305,7 +9762,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -10086,6 +10543,47 @@
       </c>
       <c r="M19" s="2">
         <v>0.009025881265433133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.0319552260624189</v>
+      </c>
+      <c r="C20" s="2">
+        <v>-0.0076351756160042</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.0485198721844442</v>
+      </c>
+      <c r="E20" s="2">
+        <v>-0.0092547070193915</v>
+      </c>
+      <c r="F20" s="2">
+        <v>-0.0521307886461338</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.2844978942030389</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.0014231419781132</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.0556629740551439</v>
+      </c>
+      <c r="J20" s="2">
+        <v>-0.064409704896476</v>
+      </c>
+      <c r="K20" s="2">
+        <v>-0.0250058300102313</v>
+      </c>
+      <c r="L20" s="2">
+        <v>-0.0360091612883839</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0.01627949441484677</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -281,16 +281,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$20</c:f>
+              <c:f>grafico_dati!$B$2:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -347,6 +350,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0.0319552260624189</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.0215698327517257</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -374,10 +380,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -434,16 +440,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$20</c:f>
+              <c:f>grafico_dati!$C$2:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -500,6 +509,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-0.0076351756160042</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.0008253978393907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -527,10 +539,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -587,16 +599,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$20</c:f>
+              <c:f>grafico_dati!$D$2:$D$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -653,6 +668,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0.0485198721844442</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.0446006203390465</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -680,10 +698,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -740,16 +758,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$20</c:f>
+              <c:f>grafico_dati!$E$2:$E$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -806,6 +827,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-0.0092547070193915</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.0113998312785303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -833,10 +857,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -893,16 +917,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$20</c:f>
+              <c:f>grafico_dati!$F$2:$F$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -956,6 +983,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-0.0521307886461338</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.0529406057435596</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -983,10 +1013,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1043,16 +1073,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$20</c:f>
+              <c:f>grafico_dati!$G$2:$G$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1109,6 +1142,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0.2844978942030389</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.287002238658864</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1136,10 +1172,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1196,16 +1232,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$20</c:f>
+              <c:f>grafico_dati!$H$2:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1262,6 +1301,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0.0014231419781132</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.0067664886954992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1289,10 +1331,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1349,16 +1391,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$20</c:f>
+              <c:f>grafico_dati!$I$2:$I$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1415,6 +1460,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0.0556629740551439</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.0560478774821504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1442,10 +1490,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1502,16 +1550,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$20</c:f>
+              <c:f>grafico_dati!$J$2:$J$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1568,6 +1619,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-0.064409704896476</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.0622082935731345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1595,10 +1649,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1655,16 +1709,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$20</c:f>
+              <c:f>grafico_dati!$K$2:$K$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1721,6 +1778,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-0.0250058300102313</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.0237093479716952</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1748,10 +1808,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1808,16 +1868,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$20</c:f>
+              <c:f>grafico_dati!$L$2:$L$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1874,6 +1937,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-0.0360091612883839</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.0299018038474174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1905,10 +1971,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$20</c:f>
+              <c:f>grafico_dati!$A$2:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1965,16 +2031,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$20</c:f>
+              <c:f>grafico_dati!$M$2:$M$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2031,6 +2100,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0.01627949441484677</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.01727757383861817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2437,7 +2509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K209"/>
+  <dimension ref="A1:K220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -9753,6 +9825,391 @@
       </c>
       <c r="K209">
         <v>3401.452085494995</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B210" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" t="s">
+        <v>22</v>
+      </c>
+      <c r="D210">
+        <v>50.07</v>
+      </c>
+      <c r="E210">
+        <v>51.15000152587891</v>
+      </c>
+      <c r="F210">
+        <v>0.0215698327517257</v>
+      </c>
+      <c r="G210">
+        <v>2.16</v>
+      </c>
+      <c r="H210" t="s">
+        <v>11</v>
+      </c>
+      <c r="I210">
+        <v>23</v>
+      </c>
+      <c r="J210">
+        <v>1151.61</v>
+      </c>
+      <c r="K210">
+        <v>1176.450035095215</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11">
+      <c r="A211" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B211" t="s">
+        <v>12</v>
+      </c>
+      <c r="C211" t="s">
+        <v>23</v>
+      </c>
+      <c r="D211">
+        <v>242.3</v>
+      </c>
+      <c r="E211">
+        <v>242.1000061035156</v>
+      </c>
+      <c r="F211">
+        <v>-0.0008253978393907</v>
+      </c>
+      <c r="G211">
+        <v>-0.08</v>
+      </c>
+      <c r="H211" t="s">
+        <v>12</v>
+      </c>
+      <c r="I211">
+        <v>5</v>
+      </c>
+      <c r="J211">
+        <v>1211.5</v>
+      </c>
+      <c r="K211">
+        <v>1210.500030517578</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11">
+      <c r="A212" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B212" t="s">
+        <v>13</v>
+      </c>
+      <c r="C212" t="s">
+        <v>24</v>
+      </c>
+      <c r="D212">
+        <v>38.273</v>
+      </c>
+      <c r="E212">
+        <v>39.97999954223633</v>
+      </c>
+      <c r="F212">
+        <v>0.0446006203390465</v>
+      </c>
+      <c r="G212">
+        <v>4.46</v>
+      </c>
+      <c r="H212" t="s">
+        <v>13</v>
+      </c>
+      <c r="I212">
+        <v>54</v>
+      </c>
+      <c r="J212">
+        <v>2066.742</v>
+      </c>
+      <c r="K212">
+        <v>2158.919975280762</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11">
+      <c r="A213" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213" t="s">
+        <v>25</v>
+      </c>
+      <c r="D213">
+        <v>6.5264</v>
+      </c>
+      <c r="E213">
+        <v>6.452000141143799</v>
+      </c>
+      <c r="F213">
+        <v>-0.0113998312785303</v>
+      </c>
+      <c r="G213">
+        <v>-1.14</v>
+      </c>
+      <c r="H213" t="s">
+        <v>14</v>
+      </c>
+      <c r="I213">
+        <v>276</v>
+      </c>
+      <c r="J213">
+        <v>1801.2864</v>
+      </c>
+      <c r="K213">
+        <v>1780.752038955688</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11">
+      <c r="A214" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B214" t="s">
+        <v>15</v>
+      </c>
+      <c r="C214" t="s">
+        <v>26</v>
+      </c>
+      <c r="D214">
+        <v>197.58</v>
+      </c>
+      <c r="E214">
+        <v>187.1199951171875</v>
+      </c>
+      <c r="F214">
+        <v>-0.0529406057435596</v>
+      </c>
+      <c r="G214">
+        <v>-5.29</v>
+      </c>
+      <c r="H214" t="s">
+        <v>15</v>
+      </c>
+      <c r="I214">
+        <v>4</v>
+      </c>
+      <c r="J214">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K214">
+        <v>748.47998046875</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11">
+      <c r="A215" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B215" t="s">
+        <v>16</v>
+      </c>
+      <c r="C215" t="s">
+        <v>27</v>
+      </c>
+      <c r="D215">
+        <v>79.86</v>
+      </c>
+      <c r="E215">
+        <v>102.7799987792969</v>
+      </c>
+      <c r="F215">
+        <v>0.287002238658864</v>
+      </c>
+      <c r="G215">
+        <v>28.7</v>
+      </c>
+      <c r="H215" t="s">
+        <v>16</v>
+      </c>
+      <c r="I215">
+        <v>12</v>
+      </c>
+      <c r="J215">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K215">
+        <v>1233.359985351562</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11">
+      <c r="A216" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B216" t="s">
+        <v>17</v>
+      </c>
+      <c r="C216" t="s">
+        <v>28</v>
+      </c>
+      <c r="D216">
+        <v>19.7444</v>
+      </c>
+      <c r="E216">
+        <v>19.87800025939941</v>
+      </c>
+      <c r="F216">
+        <v>0.0067664886954992</v>
+      </c>
+      <c r="G216">
+        <v>0.68</v>
+      </c>
+      <c r="H216" t="s">
+        <v>17</v>
+      </c>
+      <c r="I216">
+        <v>61</v>
+      </c>
+      <c r="J216">
+        <v>1204.4084</v>
+      </c>
+      <c r="K216">
+        <v>1212.558015823364</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11">
+      <c r="A217" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B217" t="s">
+        <v>18</v>
+      </c>
+      <c r="C217" t="s">
+        <v>29</v>
+      </c>
+      <c r="D217">
+        <v>129.871</v>
+      </c>
+      <c r="E217">
+        <v>137.1499938964844</v>
+      </c>
+      <c r="F217">
+        <v>0.0560478774821504</v>
+      </c>
+      <c r="G217">
+        <v>5.6</v>
+      </c>
+      <c r="H217" t="s">
+        <v>18</v>
+      </c>
+      <c r="I217">
+        <v>51</v>
+      </c>
+      <c r="J217">
+        <v>6623.421</v>
+      </c>
+      <c r="K217">
+        <v>6994.649688720703</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11">
+      <c r="A218" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B218" t="s">
+        <v>19</v>
+      </c>
+      <c r="C218" t="s">
+        <v>30</v>
+      </c>
+      <c r="D218">
+        <v>34.0694</v>
+      </c>
+      <c r="E218">
+        <v>31.95000076293945</v>
+      </c>
+      <c r="F218">
+        <v>-0.0622082935731345</v>
+      </c>
+      <c r="G218">
+        <v>-6.22</v>
+      </c>
+      <c r="H218" t="s">
+        <v>19</v>
+      </c>
+      <c r="I218">
+        <v>34</v>
+      </c>
+      <c r="J218">
+        <v>1158.3596</v>
+      </c>
+      <c r="K218">
+        <v>1086.300025939941</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11">
+      <c r="A219" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B219" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" t="s">
+        <v>31</v>
+      </c>
+      <c r="D219">
+        <v>69.4158</v>
+      </c>
+      <c r="E219">
+        <v>67.76999664306641</v>
+      </c>
+      <c r="F219">
+        <v>-0.0237093479716952</v>
+      </c>
+      <c r="G219">
+        <v>-2.37</v>
+      </c>
+      <c r="H219" t="s">
+        <v>20</v>
+      </c>
+      <c r="I219">
+        <v>62</v>
+      </c>
+      <c r="J219">
+        <v>4303.7796</v>
+      </c>
+      <c r="K219">
+        <v>4201.739791870117</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11">
+      <c r="A220" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B220" t="s">
+        <v>21</v>
+      </c>
+      <c r="C220" t="s">
+        <v>32</v>
+      </c>
+      <c r="D220">
+        <v>8.1868</v>
+      </c>
+      <c r="E220">
+        <v>7.941999912261963</v>
+      </c>
+      <c r="F220">
+        <v>-0.0299018038474174</v>
+      </c>
+      <c r="G220">
+        <v>-2.99</v>
+      </c>
+      <c r="H220" t="s">
+        <v>21</v>
+      </c>
+      <c r="I220">
+        <v>431</v>
+      </c>
+      <c r="J220">
+        <v>3528.5108</v>
+      </c>
+      <c r="K220">
+        <v>3423.001962184906</v>
       </c>
     </row>
   </sheetData>
@@ -9762,7 +10219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -10584,6 +11041,47 @@
       </c>
       <c r="M20" s="2">
         <v>0.01627949441484677</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.0215698327517257</v>
+      </c>
+      <c r="C21" s="2">
+        <v>-0.0008253978393907</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.0446006203390465</v>
+      </c>
+      <c r="E21" s="2">
+        <v>-0.0113998312785303</v>
+      </c>
+      <c r="F21" s="2">
+        <v>-0.0529406057435596</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.287002238658864</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0.0067664886954992</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.0560478774821504</v>
+      </c>
+      <c r="J21" s="2">
+        <v>-0.0622082935731345</v>
+      </c>
+      <c r="K21" s="2">
+        <v>-0.0237093479716952</v>
+      </c>
+      <c r="L21" s="2">
+        <v>-0.0299018038474174</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0.01727757383861817</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -284,16 +284,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$21</c:f>
+              <c:f>grafico_dati!$B$2:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -353,6 +356,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.0215698327517257</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.0293589158283871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -380,10 +386,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -443,16 +449,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$21</c:f>
+              <c:f>grafico_dati!$C$2:$C$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -512,6 +521,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-0.0008253978393907</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.0034255257235347</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -539,10 +551,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -602,16 +614,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$21</c:f>
+              <c:f>grafico_dati!$D$2:$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -671,6 +686,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.0446006203390465</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.0631515331097374</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -698,10 +716,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -761,16 +779,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$21</c:f>
+              <c:f>grafico_dati!$E$2:$E$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -830,6 +851,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-0.0113998312785303</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.0042289624935449</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -857,10 +881,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -920,16 +944,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$21</c:f>
+              <c:f>grafico_dati!$F$2:$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -986,6 +1013,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-0.0529406057435596</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.0376556362503875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1013,10 +1043,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1076,16 +1106,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$21</c:f>
+              <c:f>grafico_dati!$G$2:$G$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1145,6 +1178,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.287002238658864</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.3035311604573139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1172,10 +1208,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1235,16 +1271,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$21</c:f>
+              <c:f>grafico_dati!$H$2:$H$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1304,6 +1343,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.0067664886954992</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.025860454648741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1331,10 +1373,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1394,16 +1436,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$21</c:f>
+              <c:f>grafico_dati!$I$2:$I$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1463,6 +1508,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.0560478774821504</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.0646718995962218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1490,10 +1538,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1553,16 +1601,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$21</c:f>
+              <c:f>grafico_dati!$J$2:$J$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1622,6 +1673,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-0.0622082935731345</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.0438633858260065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1649,10 +1703,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1712,16 +1766,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$21</c:f>
+              <c:f>grafico_dati!$K$2:$K$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1781,6 +1838,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-0.0237093479716952</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.0173706982492076</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1808,10 +1868,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1871,16 +1931,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$21</c:f>
+              <c:f>grafico_dati!$L$2:$L$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -1940,6 +2003,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-0.0299018038474174</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.020007846351594</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1971,10 +2037,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$21</c:f>
+              <c:f>grafico_dati!$A$2:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2034,16 +2100,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$21</c:f>
+              <c:f>grafico_dati!$M$2:$M$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2103,6 +2172,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.01727757383861817</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.02824973281511878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2509,7 +2581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K220"/>
+  <dimension ref="A1:K231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -10210,6 +10282,391 @@
       </c>
       <c r="K220">
         <v>3423.001962184906</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11">
+      <c r="A221" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" t="s">
+        <v>22</v>
+      </c>
+      <c r="D221">
+        <v>50.07</v>
+      </c>
+      <c r="E221">
+        <v>51.54000091552734</v>
+      </c>
+      <c r="F221">
+        <v>0.0293589158283871</v>
+      </c>
+      <c r="G221">
+        <v>2.94</v>
+      </c>
+      <c r="H221" t="s">
+        <v>11</v>
+      </c>
+      <c r="I221">
+        <v>23</v>
+      </c>
+      <c r="J221">
+        <v>1151.61</v>
+      </c>
+      <c r="K221">
+        <v>1185.420021057129</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11">
+      <c r="A222" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B222" t="s">
+        <v>12</v>
+      </c>
+      <c r="C222" t="s">
+        <v>23</v>
+      </c>
+      <c r="D222">
+        <v>242.3</v>
+      </c>
+      <c r="E222">
+        <v>243.1300048828125</v>
+      </c>
+      <c r="F222">
+        <v>0.0034255257235347</v>
+      </c>
+      <c r="G222">
+        <v>0.34</v>
+      </c>
+      <c r="H222" t="s">
+        <v>12</v>
+      </c>
+      <c r="I222">
+        <v>5</v>
+      </c>
+      <c r="J222">
+        <v>1211.5</v>
+      </c>
+      <c r="K222">
+        <v>1215.650024414062</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11">
+      <c r="A223" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B223" t="s">
+        <v>13</v>
+      </c>
+      <c r="C223" t="s">
+        <v>24</v>
+      </c>
+      <c r="D223">
+        <v>38.273</v>
+      </c>
+      <c r="E223">
+        <v>40.68999862670898</v>
+      </c>
+      <c r="F223">
+        <v>0.0631515331097374</v>
+      </c>
+      <c r="G223">
+        <v>6.32</v>
+      </c>
+      <c r="H223" t="s">
+        <v>13</v>
+      </c>
+      <c r="I223">
+        <v>54</v>
+      </c>
+      <c r="J223">
+        <v>2066.742</v>
+      </c>
+      <c r="K223">
+        <v>2197.259925842285</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="A224" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B224" t="s">
+        <v>14</v>
+      </c>
+      <c r="C224" t="s">
+        <v>25</v>
+      </c>
+      <c r="D224">
+        <v>6.5264</v>
+      </c>
+      <c r="E224">
+        <v>6.553999900817871</v>
+      </c>
+      <c r="F224">
+        <v>0.0042289624935449</v>
+      </c>
+      <c r="G224">
+        <v>0.42</v>
+      </c>
+      <c r="H224" t="s">
+        <v>14</v>
+      </c>
+      <c r="I224">
+        <v>276</v>
+      </c>
+      <c r="J224">
+        <v>1801.2864</v>
+      </c>
+      <c r="K224">
+        <v>1808.903972625732</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11">
+      <c r="A225" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B225" t="s">
+        <v>15</v>
+      </c>
+      <c r="C225" t="s">
+        <v>26</v>
+      </c>
+      <c r="D225">
+        <v>197.58</v>
+      </c>
+      <c r="E225">
+        <v>190.1399993896484</v>
+      </c>
+      <c r="F225">
+        <v>-0.0376556362503875</v>
+      </c>
+      <c r="G225">
+        <v>-3.77</v>
+      </c>
+      <c r="H225" t="s">
+        <v>15</v>
+      </c>
+      <c r="I225">
+        <v>4</v>
+      </c>
+      <c r="J225">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K225">
+        <v>760.5599975585938</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11">
+      <c r="A226" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B226" t="s">
+        <v>16</v>
+      </c>
+      <c r="C226" t="s">
+        <v>27</v>
+      </c>
+      <c r="D226">
+        <v>79.86</v>
+      </c>
+      <c r="E226">
+        <v>104.0999984741211</v>
+      </c>
+      <c r="F226">
+        <v>0.3035311604573139</v>
+      </c>
+      <c r="G226">
+        <v>30.35</v>
+      </c>
+      <c r="H226" t="s">
+        <v>16</v>
+      </c>
+      <c r="I226">
+        <v>12</v>
+      </c>
+      <c r="J226">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K226">
+        <v>1249.199981689453</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11">
+      <c r="A227" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B227" t="s">
+        <v>17</v>
+      </c>
+      <c r="C227" t="s">
+        <v>28</v>
+      </c>
+      <c r="D227">
+        <v>19.7444</v>
+      </c>
+      <c r="E227">
+        <v>20.2549991607666</v>
+      </c>
+      <c r="F227">
+        <v>0.025860454648741</v>
+      </c>
+      <c r="G227">
+        <v>2.59</v>
+      </c>
+      <c r="H227" t="s">
+        <v>17</v>
+      </c>
+      <c r="I227">
+        <v>61</v>
+      </c>
+      <c r="J227">
+        <v>1204.4084</v>
+      </c>
+      <c r="K227">
+        <v>1235.554948806763</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11">
+      <c r="A228" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B228" t="s">
+        <v>18</v>
+      </c>
+      <c r="C228" t="s">
+        <v>29</v>
+      </c>
+      <c r="D228">
+        <v>129.871</v>
+      </c>
+      <c r="E228">
+        <v>138.2700042724609</v>
+      </c>
+      <c r="F228">
+        <v>0.0646718995962218</v>
+      </c>
+      <c r="G228">
+        <v>6.47</v>
+      </c>
+      <c r="H228" t="s">
+        <v>18</v>
+      </c>
+      <c r="I228">
+        <v>51</v>
+      </c>
+      <c r="J228">
+        <v>6623.421</v>
+      </c>
+      <c r="K228">
+        <v>7051.770217895508</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11">
+      <c r="A229" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B229" t="s">
+        <v>19</v>
+      </c>
+      <c r="C229" t="s">
+        <v>30</v>
+      </c>
+      <c r="D229">
+        <v>34.0694</v>
+      </c>
+      <c r="E229">
+        <v>32.57500076293945</v>
+      </c>
+      <c r="F229">
+        <v>-0.0438633858260065</v>
+      </c>
+      <c r="G229">
+        <v>-4.39</v>
+      </c>
+      <c r="H229" t="s">
+        <v>19</v>
+      </c>
+      <c r="I229">
+        <v>34</v>
+      </c>
+      <c r="J229">
+        <v>1158.3596</v>
+      </c>
+      <c r="K229">
+        <v>1107.550025939941</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11">
+      <c r="A230" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B230" t="s">
+        <v>20</v>
+      </c>
+      <c r="C230" t="s">
+        <v>31</v>
+      </c>
+      <c r="D230">
+        <v>69.4158</v>
+      </c>
+      <c r="E230">
+        <v>68.20999908447266</v>
+      </c>
+      <c r="F230">
+        <v>-0.0173706982492076</v>
+      </c>
+      <c r="G230">
+        <v>-1.74</v>
+      </c>
+      <c r="H230" t="s">
+        <v>20</v>
+      </c>
+      <c r="I230">
+        <v>62</v>
+      </c>
+      <c r="J230">
+        <v>4303.7796</v>
+      </c>
+      <c r="K230">
+        <v>4229.019943237305</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11">
+      <c r="A231" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B231" t="s">
+        <v>21</v>
+      </c>
+      <c r="C231" t="s">
+        <v>32</v>
+      </c>
+      <c r="D231">
+        <v>8.1868</v>
+      </c>
+      <c r="E231">
+        <v>8.02299976348877</v>
+      </c>
+      <c r="F231">
+        <v>-0.020007846351594</v>
+      </c>
+      <c r="G231">
+        <v>-2</v>
+      </c>
+      <c r="H231" t="s">
+        <v>21</v>
+      </c>
+      <c r="I231">
+        <v>431</v>
+      </c>
+      <c r="J231">
+        <v>3528.5108</v>
+      </c>
+      <c r="K231">
+        <v>3457.91289806366</v>
       </c>
     </row>
   </sheetData>
@@ -10219,7 +10676,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -11082,6 +11539,47 @@
       </c>
       <c r="M21" s="2">
         <v>0.01727757383861817</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.0293589158283871</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.0034255257235347</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.0631515331097374</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.0042289624935449</v>
+      </c>
+      <c r="F22" s="2">
+        <v>-0.0376556362503875</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.3035311604573139</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0.025860454648741</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.0646718995962218</v>
+      </c>
+      <c r="J22" s="2">
+        <v>-0.0438633858260065</v>
+      </c>
+      <c r="K22" s="2">
+        <v>-0.0173706982492076</v>
+      </c>
+      <c r="L22" s="2">
+        <v>-0.020007846351594</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0.02824973281511878</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -287,16 +287,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$22</c:f>
+              <c:f>grafico_dati!$B$2:$B$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -359,6 +362,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.0293589158283871</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.0157779231146706</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -386,10 +392,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -452,16 +458,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$22</c:f>
+              <c:f>grafico_dati!$C$2:$C$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -524,6 +533,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.0034255257235347</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-4.129886036818853e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -551,10 +563,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -617,16 +629,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$22</c:f>
+              <c:f>grafico_dati!$D$2:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -689,6 +704,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.0631515331097374</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.0381992686842307</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -716,10 +734,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -782,16 +800,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$22</c:f>
+              <c:f>grafico_dati!$E$2:$E$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -854,6 +875,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.0042289624935449</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.0212061762312926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -881,10 +905,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -947,16 +971,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$22</c:f>
+              <c:f>grafico_dati!$F$2:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1016,6 +1043,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>-0.0376556362503875</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.0535479299524244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1043,10 +1073,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1109,16 +1139,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$22</c:f>
+              <c:f>grafico_dati!$G$2:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1181,6 +1214,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.3035311604573139</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.294765859327309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1208,10 +1244,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1274,16 +1310,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$22</c:f>
+              <c:f>grafico_dati!$H$2:$H$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1346,6 +1385,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.025860454648741</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.0106156921974058</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1373,10 +1415,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1439,16 +1481,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$22</c:f>
+              <c:f>grafico_dati!$I$2:$I$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1511,6 +1556,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.0646718995962218</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.0534299232206862</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1538,10 +1586,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1604,16 +1652,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$22</c:f>
+              <c:f>grafico_dati!$J$2:$J$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1676,6 +1727,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>-0.0438633858260065</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.0512013489248577</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1703,10 +1757,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1769,16 +1823,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$22</c:f>
+              <c:f>grafico_dati!$K$2:$K$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1841,6 +1898,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>-0.0173706982492076</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.0284632253549445</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1868,10 +1928,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1934,16 +1994,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$22</c:f>
+              <c:f>grafico_dati!$L$2:$L$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2006,6 +2069,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>-0.020007846351594</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.0263594817817022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2037,10 +2103,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$22</c:f>
+              <c:f>grafico_dati!$A$2:$A$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2103,16 +2169,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$22</c:f>
+              <c:f>grafico_dati!$M$2:$M$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2175,6 +2244,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.02824973281511878</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.01576261540427626</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2581,7 +2653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K231"/>
+  <dimension ref="A1:K242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -10667,6 +10739,391 @@
       </c>
       <c r="K231">
         <v>3457.91289806366</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11">
+      <c r="A232" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B232" t="s">
+        <v>11</v>
+      </c>
+      <c r="C232" t="s">
+        <v>22</v>
+      </c>
+      <c r="D232">
+        <v>50.07</v>
+      </c>
+      <c r="E232">
+        <v>50.86000061035156</v>
+      </c>
+      <c r="F232">
+        <v>0.0157779231146706</v>
+      </c>
+      <c r="G232">
+        <v>1.58</v>
+      </c>
+      <c r="H232" t="s">
+        <v>11</v>
+      </c>
+      <c r="I232">
+        <v>23</v>
+      </c>
+      <c r="J232">
+        <v>1151.61</v>
+      </c>
+      <c r="K232">
+        <v>1169.780014038086</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="A233" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B233" t="s">
+        <v>12</v>
+      </c>
+      <c r="C233" t="s">
+        <v>23</v>
+      </c>
+      <c r="D233">
+        <v>242.3</v>
+      </c>
+      <c r="E233">
+        <v>242.2899932861328</v>
+      </c>
+      <c r="F233">
+        <v>-4.129886036818853E-05</v>
+      </c>
+      <c r="G233">
+        <v>-0</v>
+      </c>
+      <c r="H233" t="s">
+        <v>12</v>
+      </c>
+      <c r="I233">
+        <v>5</v>
+      </c>
+      <c r="J233">
+        <v>1211.5</v>
+      </c>
+      <c r="K233">
+        <v>1211.449966430664</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11">
+      <c r="A234" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B234" t="s">
+        <v>13</v>
+      </c>
+      <c r="C234" t="s">
+        <v>24</v>
+      </c>
+      <c r="D234">
+        <v>38.273</v>
+      </c>
+      <c r="E234">
+        <v>39.73500061035156</v>
+      </c>
+      <c r="F234">
+        <v>0.0381992686842307</v>
+      </c>
+      <c r="G234">
+        <v>3.82</v>
+      </c>
+      <c r="H234" t="s">
+        <v>13</v>
+      </c>
+      <c r="I234">
+        <v>54</v>
+      </c>
+      <c r="J234">
+        <v>2066.742</v>
+      </c>
+      <c r="K234">
+        <v>2145.690032958984</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="A235" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B235" t="s">
+        <v>14</v>
+      </c>
+      <c r="C235" t="s">
+        <v>25</v>
+      </c>
+      <c r="D235">
+        <v>6.5264</v>
+      </c>
+      <c r="E235">
+        <v>6.388000011444092</v>
+      </c>
+      <c r="F235">
+        <v>-0.0212061762312926</v>
+      </c>
+      <c r="G235">
+        <v>-2.12</v>
+      </c>
+      <c r="H235" t="s">
+        <v>14</v>
+      </c>
+      <c r="I235">
+        <v>276</v>
+      </c>
+      <c r="J235">
+        <v>1801.2864</v>
+      </c>
+      <c r="K235">
+        <v>1763.088003158569</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11">
+      <c r="A236" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B236" t="s">
+        <v>15</v>
+      </c>
+      <c r="C236" t="s">
+        <v>26</v>
+      </c>
+      <c r="D236">
+        <v>197.58</v>
+      </c>
+      <c r="E236">
+        <v>187</v>
+      </c>
+      <c r="F236">
+        <v>-0.0535479299524244</v>
+      </c>
+      <c r="G236">
+        <v>-5.35</v>
+      </c>
+      <c r="H236" t="s">
+        <v>15</v>
+      </c>
+      <c r="I236">
+        <v>4</v>
+      </c>
+      <c r="J236">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K236">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="A237" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B237" t="s">
+        <v>16</v>
+      </c>
+      <c r="C237" t="s">
+        <v>27</v>
+      </c>
+      <c r="D237">
+        <v>79.86</v>
+      </c>
+      <c r="E237">
+        <v>103.4000015258789</v>
+      </c>
+      <c r="F237">
+        <v>0.294765859327309</v>
+      </c>
+      <c r="G237">
+        <v>29.48</v>
+      </c>
+      <c r="H237" t="s">
+        <v>16</v>
+      </c>
+      <c r="I237">
+        <v>12</v>
+      </c>
+      <c r="J237">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K237">
+        <v>1240.800018310547</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11">
+      <c r="A238" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B238" t="s">
+        <v>17</v>
+      </c>
+      <c r="C238" t="s">
+        <v>28</v>
+      </c>
+      <c r="D238">
+        <v>19.7444</v>
+      </c>
+      <c r="E238">
+        <v>19.95400047302246</v>
+      </c>
+      <c r="F238">
+        <v>0.0106156921974058</v>
+      </c>
+      <c r="G238">
+        <v>1.06</v>
+      </c>
+      <c r="H238" t="s">
+        <v>17</v>
+      </c>
+      <c r="I238">
+        <v>61</v>
+      </c>
+      <c r="J238">
+        <v>1204.4084</v>
+      </c>
+      <c r="K238">
+        <v>1217.19402885437</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11">
+      <c r="A239" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B239" t="s">
+        <v>18</v>
+      </c>
+      <c r="C239" t="s">
+        <v>29</v>
+      </c>
+      <c r="D239">
+        <v>129.871</v>
+      </c>
+      <c r="E239">
+        <v>136.8099975585938</v>
+      </c>
+      <c r="F239">
+        <v>0.0534299232206862</v>
+      </c>
+      <c r="G239">
+        <v>5.34</v>
+      </c>
+      <c r="H239" t="s">
+        <v>18</v>
+      </c>
+      <c r="I239">
+        <v>51</v>
+      </c>
+      <c r="J239">
+        <v>6623.421</v>
+      </c>
+      <c r="K239">
+        <v>6977.309875488281</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11">
+      <c r="A240" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B240" t="s">
+        <v>19</v>
+      </c>
+      <c r="C240" t="s">
+        <v>30</v>
+      </c>
+      <c r="D240">
+        <v>34.0694</v>
+      </c>
+      <c r="E240">
+        <v>32.32500076293945</v>
+      </c>
+      <c r="F240">
+        <v>-0.0512013489248577</v>
+      </c>
+      <c r="G240">
+        <v>-5.12</v>
+      </c>
+      <c r="H240" t="s">
+        <v>19</v>
+      </c>
+      <c r="I240">
+        <v>34</v>
+      </c>
+      <c r="J240">
+        <v>1158.3596</v>
+      </c>
+      <c r="K240">
+        <v>1099.050025939941</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11">
+      <c r="A241" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B241" t="s">
+        <v>20</v>
+      </c>
+      <c r="C241" t="s">
+        <v>31</v>
+      </c>
+      <c r="D241">
+        <v>69.4158</v>
+      </c>
+      <c r="E241">
+        <v>67.44000244140625</v>
+      </c>
+      <c r="F241">
+        <v>-0.0284632253549445</v>
+      </c>
+      <c r="G241">
+        <v>-2.85</v>
+      </c>
+      <c r="H241" t="s">
+        <v>20</v>
+      </c>
+      <c r="I241">
+        <v>62</v>
+      </c>
+      <c r="J241">
+        <v>4303.7796</v>
+      </c>
+      <c r="K241">
+        <v>4181.280151367188</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11">
+      <c r="A242" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B242" t="s">
+        <v>21</v>
+      </c>
+      <c r="C242" t="s">
+        <v>32</v>
+      </c>
+      <c r="D242">
+        <v>8.1868</v>
+      </c>
+      <c r="E242">
+        <v>7.97100019454956</v>
+      </c>
+      <c r="F242">
+        <v>-0.0263594817817022</v>
+      </c>
+      <c r="G242">
+        <v>-2.64</v>
+      </c>
+      <c r="H242" t="s">
+        <v>21</v>
+      </c>
+      <c r="I242">
+        <v>431</v>
+      </c>
+      <c r="J242">
+        <v>3528.5108</v>
+      </c>
+      <c r="K242">
+        <v>3435.50108385086</v>
       </c>
     </row>
   </sheetData>
@@ -10676,7 +11133,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -11580,6 +12037,47 @@
       </c>
       <c r="M22" s="2">
         <v>0.02824973281511878</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.0157779231146706</v>
+      </c>
+      <c r="C23" s="2">
+        <v>-4.129886036818853E-05</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.0381992686842307</v>
+      </c>
+      <c r="E23" s="2">
+        <v>-0.0212061762312926</v>
+      </c>
+      <c r="F23" s="2">
+        <v>-0.0535479299524244</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.294765859327309</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.0106156921974058</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.0534299232206862</v>
+      </c>
+      <c r="J23" s="2">
+        <v>-0.0512013489248577</v>
+      </c>
+      <c r="K23" s="2">
+        <v>-0.0284632253549445</v>
+      </c>
+      <c r="L23" s="2">
+        <v>-0.0263594817817022</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0.01576261540427626</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -290,16 +290,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$23</c:f>
+              <c:f>grafico_dati!$B$2:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -365,6 +368,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0.0157779231146706</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.0125823998989305</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -392,10 +398,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -461,16 +467,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$23</c:f>
+              <c:f>grafico_dati!$C$2:$C$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -536,6 +545,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>-4.129886036818853e-05</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.0064382769576391</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -563,10 +575,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -632,16 +644,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$23</c:f>
+              <c:f>grafico_dati!$D$2:$D$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -707,6 +722,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0.0381992686842307</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.0281399021273767</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -734,10 +752,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -803,16 +821,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$23</c:f>
+              <c:f>grafico_dati!$E$2:$E$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -878,6 +899,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>-0.0212061762312926</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.0330044327193715</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -905,10 +929,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -974,16 +998,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$23</c:f>
+              <c:f>grafico_dati!$F$2:$F$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1046,6 +1073,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>-0.0535479299524244</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.06640344815331931</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1073,10 +1103,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1142,16 +1172,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$23</c:f>
+              <c:f>grafico_dati!$G$2:$G$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1217,6 +1250,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0.294765859327309</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.282744833977038</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1244,10 +1280,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1313,16 +1349,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$23</c:f>
+              <c:f>grafico_dati!$H$2:$H$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1388,6 +1427,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0.0106156921974058</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.008098531273127501</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1415,10 +1457,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1484,16 +1526,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$23</c:f>
+              <c:f>grafico_dati!$I$2:$I$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1559,6 +1604,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0.0534299232206862</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.0385690791848256</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1586,10 +1634,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1655,16 +1703,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$23</c:f>
+              <c:f>grafico_dati!$J$2:$J$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1730,6 +1781,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>-0.0512013489248577</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.0585393120237088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1757,10 +1811,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1826,16 +1880,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$23</c:f>
+              <c:f>grafico_dati!$K$2:$K$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1901,6 +1958,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>-0.0284632253549445</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.0408523444078339</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1928,10 +1988,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1997,16 +2057,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$23</c:f>
+              <c:f>grafico_dati!$L$2:$L$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2072,6 +2135,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>-0.0263594817817022</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.0395514833540991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2103,10 +2169,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$23</c:f>
+              <c:f>grafico_dati!$A$2:$A$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2172,16 +2238,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$23</c:f>
+              <c:f>grafico_dati!$M$2:$M$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2247,6 +2316,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0.01576261540427626</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.003483954271819245</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2653,7 +2725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K242"/>
+  <dimension ref="A1:K253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -11124,6 +11196,391 @@
       </c>
       <c r="K242">
         <v>3435.50108385086</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11">
+      <c r="A243" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B243" t="s">
+        <v>11</v>
+      </c>
+      <c r="C243" t="s">
+        <v>22</v>
+      </c>
+      <c r="D243">
+        <v>50.07</v>
+      </c>
+      <c r="E243">
+        <v>50.70000076293945</v>
+      </c>
+      <c r="F243">
+        <v>0.0125823998989305</v>
+      </c>
+      <c r="G243">
+        <v>1.26</v>
+      </c>
+      <c r="H243" t="s">
+        <v>11</v>
+      </c>
+      <c r="I243">
+        <v>23</v>
+      </c>
+      <c r="J243">
+        <v>1151.61</v>
+      </c>
+      <c r="K243">
+        <v>1166.100017547607</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11">
+      <c r="A244" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B244" t="s">
+        <v>12</v>
+      </c>
+      <c r="C244" t="s">
+        <v>23</v>
+      </c>
+      <c r="D244">
+        <v>242.3</v>
+      </c>
+      <c r="E244">
+        <v>240.7400054931641</v>
+      </c>
+      <c r="F244">
+        <v>-0.0064382769576391</v>
+      </c>
+      <c r="G244">
+        <v>-0.64</v>
+      </c>
+      <c r="H244" t="s">
+        <v>12</v>
+      </c>
+      <c r="I244">
+        <v>5</v>
+      </c>
+      <c r="J244">
+        <v>1211.5</v>
+      </c>
+      <c r="K244">
+        <v>1203.700027465821</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11">
+      <c r="A245" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B245" t="s">
+        <v>13</v>
+      </c>
+      <c r="C245" t="s">
+        <v>24</v>
+      </c>
+      <c r="D245">
+        <v>38.273</v>
+      </c>
+      <c r="E245">
+        <v>39.34999847412109</v>
+      </c>
+      <c r="F245">
+        <v>0.0281399021273767</v>
+      </c>
+      <c r="G245">
+        <v>2.81</v>
+      </c>
+      <c r="H245" t="s">
+        <v>13</v>
+      </c>
+      <c r="I245">
+        <v>54</v>
+      </c>
+      <c r="J245">
+        <v>2066.742</v>
+      </c>
+      <c r="K245">
+        <v>2124.899917602539</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11">
+      <c r="A246" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B246" t="s">
+        <v>14</v>
+      </c>
+      <c r="C246" t="s">
+        <v>25</v>
+      </c>
+      <c r="D246">
+        <v>6.5264</v>
+      </c>
+      <c r="E246">
+        <v>6.310999870300293</v>
+      </c>
+      <c r="F246">
+        <v>-0.0330044327193715</v>
+      </c>
+      <c r="G246">
+        <v>-3.3</v>
+      </c>
+      <c r="H246" t="s">
+        <v>14</v>
+      </c>
+      <c r="I246">
+        <v>276</v>
+      </c>
+      <c r="J246">
+        <v>1801.2864</v>
+      </c>
+      <c r="K246">
+        <v>1741.835964202881</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11">
+      <c r="A247" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B247" t="s">
+        <v>15</v>
+      </c>
+      <c r="C247" t="s">
+        <v>26</v>
+      </c>
+      <c r="D247">
+        <v>197.58</v>
+      </c>
+      <c r="E247">
+        <v>184.4600067138672</v>
+      </c>
+      <c r="F247">
+        <v>-0.06640344815331931</v>
+      </c>
+      <c r="G247">
+        <v>-6.64</v>
+      </c>
+      <c r="H247" t="s">
+        <v>15</v>
+      </c>
+      <c r="I247">
+        <v>4</v>
+      </c>
+      <c r="J247">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K247">
+        <v>737.8400268554688</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11">
+      <c r="A248" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B248" t="s">
+        <v>16</v>
+      </c>
+      <c r="C248" t="s">
+        <v>27</v>
+      </c>
+      <c r="D248">
+        <v>79.86</v>
+      </c>
+      <c r="E248">
+        <v>102.4400024414062</v>
+      </c>
+      <c r="F248">
+        <v>0.282744833977038</v>
+      </c>
+      <c r="G248">
+        <v>28.27</v>
+      </c>
+      <c r="H248" t="s">
+        <v>16</v>
+      </c>
+      <c r="I248">
+        <v>12</v>
+      </c>
+      <c r="J248">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K248">
+        <v>1229.280029296875</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11">
+      <c r="A249" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B249" t="s">
+        <v>17</v>
+      </c>
+      <c r="C249" t="s">
+        <v>28</v>
+      </c>
+      <c r="D249">
+        <v>19.7444</v>
+      </c>
+      <c r="E249">
+        <v>19.58449935913086</v>
+      </c>
+      <c r="F249">
+        <v>-0.008098531273127501</v>
+      </c>
+      <c r="G249">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="H249" t="s">
+        <v>17</v>
+      </c>
+      <c r="I249">
+        <v>61</v>
+      </c>
+      <c r="J249">
+        <v>1204.4084</v>
+      </c>
+      <c r="K249">
+        <v>1194.654460906982</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11">
+      <c r="A250" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B250" t="s">
+        <v>18</v>
+      </c>
+      <c r="C250" t="s">
+        <v>29</v>
+      </c>
+      <c r="D250">
+        <v>129.871</v>
+      </c>
+      <c r="E250">
+        <v>134.8800048828125</v>
+      </c>
+      <c r="F250">
+        <v>0.0385690791848256</v>
+      </c>
+      <c r="G250">
+        <v>3.86</v>
+      </c>
+      <c r="H250" t="s">
+        <v>18</v>
+      </c>
+      <c r="I250">
+        <v>51</v>
+      </c>
+      <c r="J250">
+        <v>6623.421</v>
+      </c>
+      <c r="K250">
+        <v>6878.880249023438</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11">
+      <c r="A251" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B251" t="s">
+        <v>19</v>
+      </c>
+      <c r="C251" t="s">
+        <v>30</v>
+      </c>
+      <c r="D251">
+        <v>34.0694</v>
+      </c>
+      <c r="E251">
+        <v>32.07500076293945</v>
+      </c>
+      <c r="F251">
+        <v>-0.0585393120237088</v>
+      </c>
+      <c r="G251">
+        <v>-5.85</v>
+      </c>
+      <c r="H251" t="s">
+        <v>19</v>
+      </c>
+      <c r="I251">
+        <v>34</v>
+      </c>
+      <c r="J251">
+        <v>1158.3596</v>
+      </c>
+      <c r="K251">
+        <v>1090.550025939941</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11">
+      <c r="A252" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B252" t="s">
+        <v>20</v>
+      </c>
+      <c r="C252" t="s">
+        <v>31</v>
+      </c>
+      <c r="D252">
+        <v>69.4158</v>
+      </c>
+      <c r="E252">
+        <v>66.58000183105469</v>
+      </c>
+      <c r="F252">
+        <v>-0.0408523444078339</v>
+      </c>
+      <c r="G252">
+        <v>-4.09</v>
+      </c>
+      <c r="H252" t="s">
+        <v>20</v>
+      </c>
+      <c r="I252">
+        <v>62</v>
+      </c>
+      <c r="J252">
+        <v>4303.7796</v>
+      </c>
+      <c r="K252">
+        <v>4127.960113525391</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11">
+      <c r="A253" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B253" t="s">
+        <v>21</v>
+      </c>
+      <c r="C253" t="s">
+        <v>32</v>
+      </c>
+      <c r="D253">
+        <v>8.1868</v>
+      </c>
+      <c r="E253">
+        <v>7.86299991607666</v>
+      </c>
+      <c r="F253">
+        <v>-0.0395514833540991</v>
+      </c>
+      <c r="G253">
+        <v>-3.96</v>
+      </c>
+      <c r="H253" t="s">
+        <v>21</v>
+      </c>
+      <c r="I253">
+        <v>431</v>
+      </c>
+      <c r="J253">
+        <v>3528.5108</v>
+      </c>
+      <c r="K253">
+        <v>3388.952963829041</v>
       </c>
     </row>
   </sheetData>
@@ -11133,7 +11590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -12078,6 +12535,47 @@
       </c>
       <c r="M23" s="2">
         <v>0.01576261540427626</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.0125823998989305</v>
+      </c>
+      <c r="C24" s="2">
+        <v>-0.0064382769576391</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.0281399021273767</v>
+      </c>
+      <c r="E24" s="2">
+        <v>-0.0330044327193715</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-0.06640344815331931</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.282744833977038</v>
+      </c>
+      <c r="H24" s="2">
+        <v>-0.008098531273127501</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0.0385690791848256</v>
+      </c>
+      <c r="J24" s="2">
+        <v>-0.0585393120237088</v>
+      </c>
+      <c r="K24" s="2">
+        <v>-0.0408523444078339</v>
+      </c>
+      <c r="L24" s="2">
+        <v>-0.0395514833540991</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0.003483954271819245</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -293,16 +293,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$24</c:f>
+              <c:f>grafico_dati!$B$2:$B$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -371,6 +374,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.0125823998989305</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.0227681063405762</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -398,10 +404,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -470,16 +476,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$24</c:f>
+              <c:f>grafico_dati!$C$2:$C$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -548,6 +557,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>-0.0064382769576391</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.0064383021475507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -575,10 +587,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -647,16 +659,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$24</c:f>
+              <c:f>grafico_dati!$D$2:$D$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -725,6 +740,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.0281399021273767</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.0325817275302084</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -752,10 +770,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -824,16 +842,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$24</c:f>
+              <c:f>grafico_dati!$E$2:$E$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -902,6 +923,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>-0.0330044327193715</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.034689845744229</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -929,10 +953,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1001,16 +1025,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$24</c:f>
+              <c:f>grafico_dati!$F$2:$F$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1076,6 +1103,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>-0.06640344815331931</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.0555723954675796</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1103,10 +1133,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1175,16 +1205,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$24</c:f>
+              <c:f>grafico_dati!$G$2:$G$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1253,6 +1286,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.282744833977038</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.2980215835475754</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1280,10 +1316,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1352,16 +1388,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$24</c:f>
+              <c:f>grafico_dati!$H$2:$H$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1430,6 +1469,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>-0.008098531273127501</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.0066145337412126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1457,10 +1499,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1529,16 +1571,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$24</c:f>
+              <c:f>grafico_dati!$I$2:$I$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1634,10 +1679,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1706,16 +1751,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$24</c:f>
+              <c:f>grafico_dati!$J$2:$J$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1784,6 +1832,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>-0.0585393120237088</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.0479726272464142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1811,10 +1862,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1883,16 +1934,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$24</c:f>
+              <c:f>grafico_dati!$K$2:$K$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -1961,6 +2015,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>-0.0408523444078339</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.0355222161490297</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1988,10 +2045,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2060,16 +2117,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$24</c:f>
+              <c:f>grafico_dati!$L$2:$L$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2138,6 +2198,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>-0.0395514833540991</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.0353984663155301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2169,10 +2232,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$24</c:f>
+              <c:f>grafico_dati!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2241,16 +2304,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$24</c:f>
+              <c:f>grafico_dati!$M$2:$M$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2319,6 +2385,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.003483954271819245</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.002466865919742989</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2725,7 +2794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K253"/>
+  <dimension ref="A1:K263"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -11581,6 +11650,356 @@
       </c>
       <c r="K253">
         <v>3388.952963829041</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11">
+      <c r="A254" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B254" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254" t="s">
+        <v>22</v>
+      </c>
+      <c r="D254">
+        <v>50.07</v>
+      </c>
+      <c r="E254">
+        <v>51.20999908447266</v>
+      </c>
+      <c r="F254">
+        <v>0.0227681063405762</v>
+      </c>
+      <c r="G254">
+        <v>2.28</v>
+      </c>
+      <c r="H254" t="s">
+        <v>11</v>
+      </c>
+      <c r="I254">
+        <v>23</v>
+      </c>
+      <c r="J254">
+        <v>1151.61</v>
+      </c>
+      <c r="K254">
+        <v>1177.829978942871</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11">
+      <c r="A255" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B255" t="s">
+        <v>12</v>
+      </c>
+      <c r="C255" t="s">
+        <v>23</v>
+      </c>
+      <c r="D255">
+        <v>242.3</v>
+      </c>
+      <c r="E255">
+        <v>243.8600006103516</v>
+      </c>
+      <c r="F255">
+        <v>0.0064383021475507</v>
+      </c>
+      <c r="G255">
+        <v>0.64</v>
+      </c>
+      <c r="H255" t="s">
+        <v>12</v>
+      </c>
+      <c r="I255">
+        <v>5</v>
+      </c>
+      <c r="J255">
+        <v>1211.5</v>
+      </c>
+      <c r="K255">
+        <v>1219.300003051758</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11">
+      <c r="A256" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B256" t="s">
+        <v>13</v>
+      </c>
+      <c r="C256" t="s">
+        <v>24</v>
+      </c>
+      <c r="D256">
+        <v>38.273</v>
+      </c>
+      <c r="E256">
+        <v>39.52000045776367</v>
+      </c>
+      <c r="F256">
+        <v>0.0325817275302084</v>
+      </c>
+      <c r="G256">
+        <v>3.26</v>
+      </c>
+      <c r="H256" t="s">
+        <v>13</v>
+      </c>
+      <c r="I256">
+        <v>54</v>
+      </c>
+      <c r="J256">
+        <v>2066.742</v>
+      </c>
+      <c r="K256">
+        <v>2134.080024719238</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11">
+      <c r="A257" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B257" t="s">
+        <v>14</v>
+      </c>
+      <c r="C257" t="s">
+        <v>25</v>
+      </c>
+      <c r="D257">
+        <v>6.5264</v>
+      </c>
+      <c r="E257">
+        <v>6.300000190734863</v>
+      </c>
+      <c r="F257">
+        <v>-0.034689845744229</v>
+      </c>
+      <c r="G257">
+        <v>-3.47</v>
+      </c>
+      <c r="H257" t="s">
+        <v>14</v>
+      </c>
+      <c r="I257">
+        <v>276</v>
+      </c>
+      <c r="J257">
+        <v>1801.2864</v>
+      </c>
+      <c r="K257">
+        <v>1738.800052642822</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11">
+      <c r="A258" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B258" t="s">
+        <v>15</v>
+      </c>
+      <c r="C258" t="s">
+        <v>26</v>
+      </c>
+      <c r="D258">
+        <v>197.58</v>
+      </c>
+      <c r="E258">
+        <v>186.6000061035156</v>
+      </c>
+      <c r="F258">
+        <v>-0.0555723954675796</v>
+      </c>
+      <c r="G258">
+        <v>-5.56</v>
+      </c>
+      <c r="H258" t="s">
+        <v>15</v>
+      </c>
+      <c r="I258">
+        <v>4</v>
+      </c>
+      <c r="J258">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K258">
+        <v>746.4000244140624</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11">
+      <c r="A259" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B259" t="s">
+        <v>16</v>
+      </c>
+      <c r="C259" t="s">
+        <v>27</v>
+      </c>
+      <c r="D259">
+        <v>79.86</v>
+      </c>
+      <c r="E259">
+        <v>103.6600036621094</v>
+      </c>
+      <c r="F259">
+        <v>0.2980215835475754</v>
+      </c>
+      <c r="G259">
+        <v>29.8</v>
+      </c>
+      <c r="H259" t="s">
+        <v>16</v>
+      </c>
+      <c r="I259">
+        <v>12</v>
+      </c>
+      <c r="J259">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K259">
+        <v>1243.920043945312</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11">
+      <c r="A260" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B260" t="s">
+        <v>17</v>
+      </c>
+      <c r="C260" t="s">
+        <v>28</v>
+      </c>
+      <c r="D260">
+        <v>19.7444</v>
+      </c>
+      <c r="E260">
+        <v>19.875</v>
+      </c>
+      <c r="F260">
+        <v>0.0066145337412126</v>
+      </c>
+      <c r="G260">
+        <v>0.66</v>
+      </c>
+      <c r="H260" t="s">
+        <v>17</v>
+      </c>
+      <c r="I260">
+        <v>61</v>
+      </c>
+      <c r="J260">
+        <v>1204.4084</v>
+      </c>
+      <c r="K260">
+        <v>1212.375</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11">
+      <c r="A261" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B261" t="s">
+        <v>19</v>
+      </c>
+      <c r="C261" t="s">
+        <v>30</v>
+      </c>
+      <c r="D261">
+        <v>34.0694</v>
+      </c>
+      <c r="E261">
+        <v>32.43500137329102</v>
+      </c>
+      <c r="F261">
+        <v>-0.0479726272464142</v>
+      </c>
+      <c r="G261">
+        <v>-4.8</v>
+      </c>
+      <c r="H261" t="s">
+        <v>19</v>
+      </c>
+      <c r="I261">
+        <v>34</v>
+      </c>
+      <c r="J261">
+        <v>1158.3596</v>
+      </c>
+      <c r="K261">
+        <v>1102.790046691895</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11">
+      <c r="A262" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B262" t="s">
+        <v>20</v>
+      </c>
+      <c r="C262" t="s">
+        <v>31</v>
+      </c>
+      <c r="D262">
+        <v>69.4158</v>
+      </c>
+      <c r="E262">
+        <v>66.94999694824219</v>
+      </c>
+      <c r="F262">
+        <v>-0.0355222161490297</v>
+      </c>
+      <c r="G262">
+        <v>-3.55</v>
+      </c>
+      <c r="H262" t="s">
+        <v>20</v>
+      </c>
+      <c r="I262">
+        <v>62</v>
+      </c>
+      <c r="J262">
+        <v>4303.7796</v>
+      </c>
+      <c r="K262">
+        <v>4150.899810791016</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11">
+      <c r="A263" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B263" t="s">
+        <v>21</v>
+      </c>
+      <c r="C263" t="s">
+        <v>32</v>
+      </c>
+      <c r="D263">
+        <v>8.1868</v>
+      </c>
+      <c r="E263">
+        <v>7.896999835968018</v>
+      </c>
+      <c r="F263">
+        <v>-0.0353984663155301</v>
+      </c>
+      <c r="G263">
+        <v>-3.54</v>
+      </c>
+      <c r="H263" t="s">
+        <v>21</v>
+      </c>
+      <c r="I263">
+        <v>431</v>
+      </c>
+      <c r="J263">
+        <v>3528.5108</v>
+      </c>
+      <c r="K263">
+        <v>3403.606929302216</v>
       </c>
     </row>
   </sheetData>
@@ -11590,7 +12009,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -12576,6 +12995,44 @@
       </c>
       <c r="M24" s="2">
         <v>0.003483954271819245</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.0227681063405762</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.0064383021475507</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.0325817275302084</v>
+      </c>
+      <c r="E25" s="2">
+        <v>-0.034689845744229</v>
+      </c>
+      <c r="F25" s="2">
+        <v>-0.0555723954675796</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0.2980215835475754</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0.0066145337412126</v>
+      </c>
+      <c r="J25" s="2">
+        <v>-0.0479726272464142</v>
+      </c>
+      <c r="K25" s="2">
+        <v>-0.0355222161490297</v>
+      </c>
+      <c r="L25" s="2">
+        <v>-0.0353984663155301</v>
+      </c>
+      <c r="M25" s="2">
+        <v>-0.002466865919742989</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -296,16 +296,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$25</c:f>
+              <c:f>grafico_dati!$B$2:$B$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -377,6 +380,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.0227681063405762</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.0185739964050328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -404,10 +410,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -479,16 +485,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$25</c:f>
+              <c:f>grafico_dati!$C$2:$C$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -560,6 +569,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.0064383021475507</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.0009492314457155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -587,10 +599,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -662,16 +674,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$25</c:f>
+              <c:f>grafico_dati!$D$2:$D$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -743,6 +758,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.0325817275302084</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.0270948546832234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -770,10 +788,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -845,16 +863,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$25</c:f>
+              <c:f>grafico_dati!$E$2:$E$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -926,6 +947,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>-0.034689845744229</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.0368350430661832</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -953,10 +977,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1028,16 +1052,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$25</c:f>
+              <c:f>grafico_dati!$F$2:$F$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1106,6 +1133,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>-0.0555723954675796</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.0501063231309786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1133,10 +1163,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1208,16 +1238,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$25</c:f>
+              <c:f>grafico_dati!$G$2:$G$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1289,6 +1322,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.2980215835475754</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.3070372809093158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1316,10 +1352,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1391,16 +1427,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$25</c:f>
+              <c:f>grafico_dati!$H$2:$H$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1472,6 +1511,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.0066145337412126</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.0008407284883527</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1499,10 +1541,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1574,16 +1616,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$25</c:f>
+              <c:f>grafico_dati!$I$2:$I$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1652,6 +1697,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.0385690791848256</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.0445750295455442</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1679,10 +1727,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1754,16 +1802,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$25</c:f>
+              <c:f>grafico_dati!$J$2:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1835,6 +1886,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>-0.0479726272464142</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.0506142984407379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1862,10 +1916,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1937,16 +1991,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$25</c:f>
+              <c:f>grafico_dati!$K$2:$K$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2018,6 +2075,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>-0.0355222161490297</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.0358102866324989</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2045,10 +2105,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2120,16 +2180,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$25</c:f>
+              <c:f>grafico_dati!$L$2:$L$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2201,6 +2264,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>-0.0353984663155301</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.0356427443046717</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2232,10 +2298,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$25</c:f>
+              <c:f>grafico_dati!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2307,16 +2373,19 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$25</c:f>
+              <c:f>grafico_dati!$M$2:$M$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2388,6 +2457,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>-0.002466865919742989</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.009055650800799953</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2794,7 +2866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K263"/>
+  <dimension ref="A1:K274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -12000,6 +12072,391 @@
       </c>
       <c r="K263">
         <v>3403.606929302216</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11">
+      <c r="A264" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B264" t="s">
+        <v>11</v>
+      </c>
+      <c r="C264" t="s">
+        <v>22</v>
+      </c>
+      <c r="D264">
+        <v>50.07</v>
+      </c>
+      <c r="E264">
+        <v>51</v>
+      </c>
+      <c r="F264">
+        <v>0.0185739964050328</v>
+      </c>
+      <c r="G264">
+        <v>1.86</v>
+      </c>
+      <c r="H264" t="s">
+        <v>11</v>
+      </c>
+      <c r="I264">
+        <v>23</v>
+      </c>
+      <c r="J264">
+        <v>1151.61</v>
+      </c>
+      <c r="K264">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11">
+      <c r="A265" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B265" t="s">
+        <v>12</v>
+      </c>
+      <c r="C265" t="s">
+        <v>23</v>
+      </c>
+      <c r="D265">
+        <v>242.3</v>
+      </c>
+      <c r="E265">
+        <v>242.5299987792969</v>
+      </c>
+      <c r="F265">
+        <v>0.0009492314457155</v>
+      </c>
+      <c r="G265">
+        <v>0.09</v>
+      </c>
+      <c r="H265" t="s">
+        <v>12</v>
+      </c>
+      <c r="I265">
+        <v>5</v>
+      </c>
+      <c r="J265">
+        <v>1211.5</v>
+      </c>
+      <c r="K265">
+        <v>1212.649993896484</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11">
+      <c r="A266" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B266" t="s">
+        <v>13</v>
+      </c>
+      <c r="C266" t="s">
+        <v>24</v>
+      </c>
+      <c r="D266">
+        <v>38.273</v>
+      </c>
+      <c r="E266">
+        <v>39.31000137329102</v>
+      </c>
+      <c r="F266">
+        <v>0.0270948546832234</v>
+      </c>
+      <c r="G266">
+        <v>2.71</v>
+      </c>
+      <c r="H266" t="s">
+        <v>13</v>
+      </c>
+      <c r="I266">
+        <v>54</v>
+      </c>
+      <c r="J266">
+        <v>2066.742</v>
+      </c>
+      <c r="K266">
+        <v>2122.740074157715</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11">
+      <c r="A267" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B267" t="s">
+        <v>14</v>
+      </c>
+      <c r="C267" t="s">
+        <v>25</v>
+      </c>
+      <c r="D267">
+        <v>6.5264</v>
+      </c>
+      <c r="E267">
+        <v>6.285999774932861</v>
+      </c>
+      <c r="F267">
+        <v>-0.0368350430661832</v>
+      </c>
+      <c r="G267">
+        <v>-3.68</v>
+      </c>
+      <c r="H267" t="s">
+        <v>14</v>
+      </c>
+      <c r="I267">
+        <v>276</v>
+      </c>
+      <c r="J267">
+        <v>1801.2864</v>
+      </c>
+      <c r="K267">
+        <v>1734.93593788147</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11">
+      <c r="A268" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B268" t="s">
+        <v>15</v>
+      </c>
+      <c r="C268" t="s">
+        <v>26</v>
+      </c>
+      <c r="D268">
+        <v>197.58</v>
+      </c>
+      <c r="E268">
+        <v>187.6799926757812</v>
+      </c>
+      <c r="F268">
+        <v>-0.0501063231309786</v>
+      </c>
+      <c r="G268">
+        <v>-5.01</v>
+      </c>
+      <c r="H268" t="s">
+        <v>15</v>
+      </c>
+      <c r="I268">
+        <v>4</v>
+      </c>
+      <c r="J268">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K268">
+        <v>750.719970703125</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11">
+      <c r="A269" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B269" t="s">
+        <v>16</v>
+      </c>
+      <c r="C269" t="s">
+        <v>27</v>
+      </c>
+      <c r="D269">
+        <v>79.86</v>
+      </c>
+      <c r="E269">
+        <v>104.379997253418</v>
+      </c>
+      <c r="F269">
+        <v>0.3070372809093158</v>
+      </c>
+      <c r="G269">
+        <v>30.7</v>
+      </c>
+      <c r="H269" t="s">
+        <v>16</v>
+      </c>
+      <c r="I269">
+        <v>12</v>
+      </c>
+      <c r="J269">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K269">
+        <v>1252.559967041015</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11">
+      <c r="A270" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B270" t="s">
+        <v>17</v>
+      </c>
+      <c r="C270" t="s">
+        <v>28</v>
+      </c>
+      <c r="D270">
+        <v>19.7444</v>
+      </c>
+      <c r="E270">
+        <v>19.76099967956543</v>
+      </c>
+      <c r="F270">
+        <v>0.0008407284883527</v>
+      </c>
+      <c r="G270">
+        <v>0.08</v>
+      </c>
+      <c r="H270" t="s">
+        <v>17</v>
+      </c>
+      <c r="I270">
+        <v>61</v>
+      </c>
+      <c r="J270">
+        <v>1204.4084</v>
+      </c>
+      <c r="K270">
+        <v>1205.420980453491</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11">
+      <c r="A271" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B271" t="s">
+        <v>18</v>
+      </c>
+      <c r="C271" t="s">
+        <v>29</v>
+      </c>
+      <c r="D271">
+        <v>129.871</v>
+      </c>
+      <c r="E271">
+        <v>135.6600036621094</v>
+      </c>
+      <c r="F271">
+        <v>0.0445750295455442</v>
+      </c>
+      <c r="G271">
+        <v>4.46</v>
+      </c>
+      <c r="H271" t="s">
+        <v>18</v>
+      </c>
+      <c r="I271">
+        <v>51</v>
+      </c>
+      <c r="J271">
+        <v>6623.421</v>
+      </c>
+      <c r="K271">
+        <v>6918.660186767578</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11">
+      <c r="A272" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B272" t="s">
+        <v>19</v>
+      </c>
+      <c r="C272" t="s">
+        <v>30</v>
+      </c>
+      <c r="D272">
+        <v>34.0694</v>
+      </c>
+      <c r="E272">
+        <v>32.34500122070312</v>
+      </c>
+      <c r="F272">
+        <v>-0.0506142984407379</v>
+      </c>
+      <c r="G272">
+        <v>-5.06</v>
+      </c>
+      <c r="H272" t="s">
+        <v>19</v>
+      </c>
+      <c r="I272">
+        <v>34</v>
+      </c>
+      <c r="J272">
+        <v>1158.3596</v>
+      </c>
+      <c r="K272">
+        <v>1099.730041503906</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11">
+      <c r="A273" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B273" t="s">
+        <v>20</v>
+      </c>
+      <c r="C273" t="s">
+        <v>31</v>
+      </c>
+      <c r="D273">
+        <v>69.4158</v>
+      </c>
+      <c r="E273">
+        <v>66.93000030517578</v>
+      </c>
+      <c r="F273">
+        <v>-0.0358102866324989</v>
+      </c>
+      <c r="G273">
+        <v>-3.58</v>
+      </c>
+      <c r="H273" t="s">
+        <v>20</v>
+      </c>
+      <c r="I273">
+        <v>62</v>
+      </c>
+      <c r="J273">
+        <v>4303.7796</v>
+      </c>
+      <c r="K273">
+        <v>4149.660018920898</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11">
+      <c r="A274" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B274" t="s">
+        <v>21</v>
+      </c>
+      <c r="C274" t="s">
+        <v>32</v>
+      </c>
+      <c r="D274">
+        <v>8.1868</v>
+      </c>
+      <c r="E274">
+        <v>7.894999980926514</v>
+      </c>
+      <c r="F274">
+        <v>-0.0356427443046717</v>
+      </c>
+      <c r="G274">
+        <v>-3.56</v>
+      </c>
+      <c r="H274" t="s">
+        <v>21</v>
+      </c>
+      <c r="I274">
+        <v>431</v>
+      </c>
+      <c r="J274">
+        <v>3528.5108</v>
+      </c>
+      <c r="K274">
+        <v>3402.744991779327</v>
       </c>
     </row>
   </sheetData>
@@ -12009,7 +12466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -13033,6 +13490,47 @@
       </c>
       <c r="M25" s="2">
         <v>-0.002466865919742989</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.0185739964050328</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.0009492314457155</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.0270948546832234</v>
+      </c>
+      <c r="E26" s="2">
+        <v>-0.0368350430661832</v>
+      </c>
+      <c r="F26" s="2">
+        <v>-0.0501063231309786</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.3070372809093158</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0.0008407284883527</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0.0445750295455442</v>
+      </c>
+      <c r="J26" s="2">
+        <v>-0.0506142984407379</v>
+      </c>
+      <c r="K26" s="2">
+        <v>-0.0358102866324989</v>
+      </c>
+      <c r="L26" s="2">
+        <v>-0.0356427443046717</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0.009055650800799953</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -299,16 +299,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$26</c:f>
+              <c:f>grafico_dati!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -383,6 +386,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.0185739964050328</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.0405432089898361</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -410,10 +416,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -488,16 +494,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$26</c:f>
+              <c:f>grafico_dati!$C$2:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -572,6 +581,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.0009492314457155</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.0165910331168746</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -599,10 +611,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -677,16 +689,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$26</c:f>
+              <c:f>grafico_dati!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -761,6 +776,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.0270948546832234</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.0617144807444725</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -788,10 +806,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -866,16 +884,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$26</c:f>
+              <c:f>grafico_dati!$E$2:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -950,6 +971,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>-0.0368350430661832</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.001777412786762</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -977,10 +1001,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1055,16 +1079,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$26</c:f>
+              <c:f>grafico_dati!$F$2:$F$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1136,6 +1163,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>-0.0501063231309786</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.0242939630564993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1163,10 +1193,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1241,16 +1271,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$26</c:f>
+              <c:f>grafico_dati!$G$2:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1325,6 +1358,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.3070372809093158</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.3608815465211092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1352,10 +1388,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1430,16 +1466,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$26</c:f>
+              <c:f>grafico_dati!$H$2:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1514,6 +1553,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.0008407284883527</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.048601146300848</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1541,10 +1583,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1619,16 +1661,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$26</c:f>
+              <c:f>grafico_dati!$I$2:$I$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1700,6 +1745,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.0445750295455442</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.06628882296693669</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1727,10 +1775,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1805,16 +1853,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$26</c:f>
+              <c:f>grafico_dati!$J$2:$J$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1889,6 +1940,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>-0.0506142984407379</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.0288939903704599</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1916,10 +1970,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1994,16 +2048,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$26</c:f>
+              <c:f>grafico_dati!$K$2:$K$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2078,6 +2135,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>-0.0358102866324989</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.0176587687326769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2105,10 +2165,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2183,16 +2243,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$26</c:f>
+              <c:f>grafico_dati!$L$2:$L$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2267,6 +2330,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>-0.0356427443046717</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.0102360278503415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2298,10 +2364,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$26</c:f>
+              <c:f>grafico_dati!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2376,16 +2442,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$26</c:f>
+              <c:f>grafico_dati!$M$2:$M$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2460,6 +2529,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.009055650800799953</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.03533260048320974</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2866,7 +2938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K274"/>
+  <dimension ref="A1:K285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -12457,6 +12529,391 @@
       </c>
       <c r="K274">
         <v>3402.744991779327</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11">
+      <c r="A275" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B275" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275" t="s">
+        <v>22</v>
+      </c>
+      <c r="D275">
+        <v>50.07</v>
+      </c>
+      <c r="E275">
+        <v>52.09999847412109</v>
+      </c>
+      <c r="F275">
+        <v>0.0405432089898361</v>
+      </c>
+      <c r="G275">
+        <v>4.05</v>
+      </c>
+      <c r="H275" t="s">
+        <v>11</v>
+      </c>
+      <c r="I275">
+        <v>23</v>
+      </c>
+      <c r="J275">
+        <v>1151.61</v>
+      </c>
+      <c r="K275">
+        <v>1198.299964904785</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11">
+      <c r="A276" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B276" t="s">
+        <v>12</v>
+      </c>
+      <c r="C276" t="s">
+        <v>23</v>
+      </c>
+      <c r="D276">
+        <v>242.3</v>
+      </c>
+      <c r="E276">
+        <v>246.3200073242188</v>
+      </c>
+      <c r="F276">
+        <v>0.0165910331168746</v>
+      </c>
+      <c r="G276">
+        <v>1.66</v>
+      </c>
+      <c r="H276" t="s">
+        <v>12</v>
+      </c>
+      <c r="I276">
+        <v>5</v>
+      </c>
+      <c r="J276">
+        <v>1211.5</v>
+      </c>
+      <c r="K276">
+        <v>1231.600036621094</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11">
+      <c r="A277" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B277" t="s">
+        <v>13</v>
+      </c>
+      <c r="C277" t="s">
+        <v>24</v>
+      </c>
+      <c r="D277">
+        <v>38.273</v>
+      </c>
+      <c r="E277">
+        <v>40.6349983215332</v>
+      </c>
+      <c r="F277">
+        <v>0.0617144807444725</v>
+      </c>
+      <c r="G277">
+        <v>6.17</v>
+      </c>
+      <c r="H277" t="s">
+        <v>13</v>
+      </c>
+      <c r="I277">
+        <v>54</v>
+      </c>
+      <c r="J277">
+        <v>2066.742</v>
+      </c>
+      <c r="K277">
+        <v>2194.289909362793</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11">
+      <c r="A278" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B278" t="s">
+        <v>14</v>
+      </c>
+      <c r="C278" t="s">
+        <v>25</v>
+      </c>
+      <c r="D278">
+        <v>6.5264</v>
+      </c>
+      <c r="E278">
+        <v>6.538000106811523</v>
+      </c>
+      <c r="F278">
+        <v>0.001777412786762</v>
+      </c>
+      <c r="G278">
+        <v>0.18</v>
+      </c>
+      <c r="H278" t="s">
+        <v>14</v>
+      </c>
+      <c r="I278">
+        <v>276</v>
+      </c>
+      <c r="J278">
+        <v>1801.2864</v>
+      </c>
+      <c r="K278">
+        <v>1804.48802947998</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11">
+      <c r="A279" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B279" t="s">
+        <v>15</v>
+      </c>
+      <c r="C279" t="s">
+        <v>26</v>
+      </c>
+      <c r="D279">
+        <v>197.58</v>
+      </c>
+      <c r="E279">
+        <v>192.7799987792969</v>
+      </c>
+      <c r="F279">
+        <v>-0.0242939630564993</v>
+      </c>
+      <c r="G279">
+        <v>-2.43</v>
+      </c>
+      <c r="H279" t="s">
+        <v>15</v>
+      </c>
+      <c r="I279">
+        <v>4</v>
+      </c>
+      <c r="J279">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K279">
+        <v>771.1199951171875</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11">
+      <c r="A280" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B280" t="s">
+        <v>16</v>
+      </c>
+      <c r="C280" t="s">
+        <v>27</v>
+      </c>
+      <c r="D280">
+        <v>79.86</v>
+      </c>
+      <c r="E280">
+        <v>108.6800003051758</v>
+      </c>
+      <c r="F280">
+        <v>0.3608815465211092</v>
+      </c>
+      <c r="G280">
+        <v>36.09</v>
+      </c>
+      <c r="H280" t="s">
+        <v>16</v>
+      </c>
+      <c r="I280">
+        <v>12</v>
+      </c>
+      <c r="J280">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K280">
+        <v>1304.160003662109</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11">
+      <c r="A281" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B281" t="s">
+        <v>17</v>
+      </c>
+      <c r="C281" t="s">
+        <v>28</v>
+      </c>
+      <c r="D281">
+        <v>19.7444</v>
+      </c>
+      <c r="E281">
+        <v>20.70400047302246</v>
+      </c>
+      <c r="F281">
+        <v>0.048601146300848</v>
+      </c>
+      <c r="G281">
+        <v>4.86</v>
+      </c>
+      <c r="H281" t="s">
+        <v>17</v>
+      </c>
+      <c r="I281">
+        <v>61</v>
+      </c>
+      <c r="J281">
+        <v>1204.4084</v>
+      </c>
+      <c r="K281">
+        <v>1262.94402885437</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11">
+      <c r="A282" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B282" t="s">
+        <v>18</v>
+      </c>
+      <c r="C282" t="s">
+        <v>29</v>
+      </c>
+      <c r="D282">
+        <v>129.871</v>
+      </c>
+      <c r="E282">
+        <v>138.4799957275391</v>
+      </c>
+      <c r="F282">
+        <v>0.06628882296693669</v>
+      </c>
+      <c r="G282">
+        <v>6.63</v>
+      </c>
+      <c r="H282" t="s">
+        <v>18</v>
+      </c>
+      <c r="I282">
+        <v>51</v>
+      </c>
+      <c r="J282">
+        <v>6623.421</v>
+      </c>
+      <c r="K282">
+        <v>7062.479782104492</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11">
+      <c r="A283" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B283" t="s">
+        <v>19</v>
+      </c>
+      <c r="C283" t="s">
+        <v>30</v>
+      </c>
+      <c r="D283">
+        <v>34.0694</v>
+      </c>
+      <c r="E283">
+        <v>33.08499908447266</v>
+      </c>
+      <c r="F283">
+        <v>-0.0288939903704599</v>
+      </c>
+      <c r="G283">
+        <v>-2.89</v>
+      </c>
+      <c r="H283" t="s">
+        <v>19</v>
+      </c>
+      <c r="I283">
+        <v>34</v>
+      </c>
+      <c r="J283">
+        <v>1158.3596</v>
+      </c>
+      <c r="K283">
+        <v>1124.88996887207</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11">
+      <c r="A284" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B284" t="s">
+        <v>20</v>
+      </c>
+      <c r="C284" t="s">
+        <v>31</v>
+      </c>
+      <c r="D284">
+        <v>69.4158</v>
+      </c>
+      <c r="E284">
+        <v>68.19000244140625</v>
+      </c>
+      <c r="F284">
+        <v>-0.0176587687326769</v>
+      </c>
+      <c r="G284">
+        <v>-1.77</v>
+      </c>
+      <c r="H284" t="s">
+        <v>20</v>
+      </c>
+      <c r="I284">
+        <v>62</v>
+      </c>
+      <c r="J284">
+        <v>4303.7796</v>
+      </c>
+      <c r="K284">
+        <v>4227.780151367188</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11">
+      <c r="A285" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B285" t="s">
+        <v>21</v>
+      </c>
+      <c r="C285" t="s">
+        <v>32</v>
+      </c>
+      <c r="D285">
+        <v>8.1868</v>
+      </c>
+      <c r="E285">
+        <v>8.102999687194824</v>
+      </c>
+      <c r="F285">
+        <v>-0.0102360278503415</v>
+      </c>
+      <c r="G285">
+        <v>-1.02</v>
+      </c>
+      <c r="H285" t="s">
+        <v>21</v>
+      </c>
+      <c r="I285">
+        <v>431</v>
+      </c>
+      <c r="J285">
+        <v>3528.5108</v>
+      </c>
+      <c r="K285">
+        <v>3492.392865180969</v>
       </c>
     </row>
   </sheetData>
@@ -12466,7 +12923,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -13531,6 +13988,47 @@
       </c>
       <c r="M26" s="2">
         <v>0.009055650800799953</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.0405432089898361</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.0165910331168746</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.0617144807444725</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.001777412786762</v>
+      </c>
+      <c r="F27" s="2">
+        <v>-0.0242939630564993</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.3608815465211092</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.048601146300848</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.06628882296693669</v>
+      </c>
+      <c r="J27" s="2">
+        <v>-0.0288939903704599</v>
+      </c>
+      <c r="K27" s="2">
+        <v>-0.0176587687326769</v>
+      </c>
+      <c r="L27" s="2">
+        <v>-0.0102360278503415</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0.03533260048320974</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -302,16 +302,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$27</c:f>
+              <c:f>grafico_dati!$B$2:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -389,6 +392,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.0405432089898361</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.0421410086913476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -416,10 +422,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -497,16 +503,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$27</c:f>
+              <c:f>grafico_dati!$C$2:$C$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -584,6 +593,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.0165910331168746</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.0195212496050221</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -611,10 +623,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -692,16 +704,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$27</c:f>
+              <c:f>grafico_dati!$D$2:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -779,6 +794,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.0617144807444725</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.0473440567625389</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -806,10 +824,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -887,16 +905,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$27</c:f>
+              <c:f>grafico_dati!$E$2:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -974,6 +995,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.001777412786762</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.0143110922195947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1001,10 +1025,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1082,16 +1106,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$27</c:f>
+              <c:f>grafico_dati!$F$2:$F$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1166,6 +1193,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>-0.0242939630564993</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.0313796695879518</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1193,10 +1223,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1274,16 +1304,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$27</c:f>
+              <c:f>grafico_dati!$G$2:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1361,6 +1394,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.3608815465211092</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.3548709860786649</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1388,10 +1424,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1469,16 +1505,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$27</c:f>
+              <c:f>grafico_dati!$H$2:$H$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1556,6 +1595,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.048601146300848</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.0306720073271271</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1583,10 +1625,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1664,16 +1706,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$27</c:f>
+              <c:f>grafico_dati!$I$2:$I$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1748,6 +1793,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.06628882296693669</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.0665968866988082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1775,10 +1823,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1856,16 +1904,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$27</c:f>
+              <c:f>grafico_dati!$J$2:$J$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1943,6 +1994,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>-0.0288939903704599</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.0319759214357656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1970,10 +2024,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2051,16 +2105,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$27</c:f>
+              <c:f>grafico_dati!$K$2:$K$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2138,6 +2195,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>-0.0176587687326769</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.0172266080531647</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2165,10 +2225,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2246,16 +2306,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$27</c:f>
+              <c:f>grafico_dati!$L$2:$L$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2333,6 +2396,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>-0.0102360278503415</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.0123124490026771</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2364,10 +2430,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$27</c:f>
+              <c:f>grafico_dati!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2445,16 +2511,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$27</c:f>
+              <c:f>grafico_dati!$M$2:$M$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2532,6 +2601,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.03533260048320974</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.03157264743845434</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2938,7 +3010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K285"/>
+  <dimension ref="A1:K296"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -12914,6 +12986,391 @@
       </c>
       <c r="K285">
         <v>3492.392865180969</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11">
+      <c r="A286" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B286" t="s">
+        <v>11</v>
+      </c>
+      <c r="C286" t="s">
+        <v>22</v>
+      </c>
+      <c r="D286">
+        <v>50.07</v>
+      </c>
+      <c r="E286">
+        <v>52.18000030517578</v>
+      </c>
+      <c r="F286">
+        <v>0.0421410086913476</v>
+      </c>
+      <c r="G286">
+        <v>4.21</v>
+      </c>
+      <c r="H286" t="s">
+        <v>11</v>
+      </c>
+      <c r="I286">
+        <v>23</v>
+      </c>
+      <c r="J286">
+        <v>1151.61</v>
+      </c>
+      <c r="K286">
+        <v>1200.140007019043</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11">
+      <c r="A287" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B287" t="s">
+        <v>12</v>
+      </c>
+      <c r="C287" t="s">
+        <v>23</v>
+      </c>
+      <c r="D287">
+        <v>242.3</v>
+      </c>
+      <c r="E287">
+        <v>247.0299987792969</v>
+      </c>
+      <c r="F287">
+        <v>0.0195212496050221</v>
+      </c>
+      <c r="G287">
+        <v>1.95</v>
+      </c>
+      <c r="H287" t="s">
+        <v>12</v>
+      </c>
+      <c r="I287">
+        <v>5</v>
+      </c>
+      <c r="J287">
+        <v>1211.5</v>
+      </c>
+      <c r="K287">
+        <v>1235.149993896484</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11">
+      <c r="A288" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B288" t="s">
+        <v>13</v>
+      </c>
+      <c r="C288" t="s">
+        <v>24</v>
+      </c>
+      <c r="D288">
+        <v>38.273</v>
+      </c>
+      <c r="E288">
+        <v>40.08499908447266</v>
+      </c>
+      <c r="F288">
+        <v>0.0473440567625389</v>
+      </c>
+      <c r="G288">
+        <v>4.73</v>
+      </c>
+      <c r="H288" t="s">
+        <v>13</v>
+      </c>
+      <c r="I288">
+        <v>54</v>
+      </c>
+      <c r="J288">
+        <v>2066.742</v>
+      </c>
+      <c r="K288">
+        <v>2164.589950561523</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11">
+      <c r="A289" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B289" t="s">
+        <v>14</v>
+      </c>
+      <c r="C289" t="s">
+        <v>25</v>
+      </c>
+      <c r="D289">
+        <v>6.5264</v>
+      </c>
+      <c r="E289">
+        <v>6.433000087738037</v>
+      </c>
+      <c r="F289">
+        <v>-0.0143110922195947</v>
+      </c>
+      <c r="G289">
+        <v>-1.43</v>
+      </c>
+      <c r="H289" t="s">
+        <v>14</v>
+      </c>
+      <c r="I289">
+        <v>276</v>
+      </c>
+      <c r="J289">
+        <v>1801.2864</v>
+      </c>
+      <c r="K289">
+        <v>1775.508024215698</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11">
+      <c r="A290" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B290" t="s">
+        <v>15</v>
+      </c>
+      <c r="C290" t="s">
+        <v>26</v>
+      </c>
+      <c r="D290">
+        <v>197.58</v>
+      </c>
+      <c r="E290">
+        <v>191.3800048828125</v>
+      </c>
+      <c r="F290">
+        <v>-0.0313796695879518</v>
+      </c>
+      <c r="G290">
+        <v>-3.14</v>
+      </c>
+      <c r="H290" t="s">
+        <v>15</v>
+      </c>
+      <c r="I290">
+        <v>4</v>
+      </c>
+      <c r="J290">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K290">
+        <v>765.52001953125</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11">
+      <c r="A291" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B291" t="s">
+        <v>16</v>
+      </c>
+      <c r="C291" t="s">
+        <v>27</v>
+      </c>
+      <c r="D291">
+        <v>79.86</v>
+      </c>
+      <c r="E291">
+        <v>108.1999969482422</v>
+      </c>
+      <c r="F291">
+        <v>0.3548709860786649</v>
+      </c>
+      <c r="G291">
+        <v>35.49</v>
+      </c>
+      <c r="H291" t="s">
+        <v>16</v>
+      </c>
+      <c r="I291">
+        <v>12</v>
+      </c>
+      <c r="J291">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K291">
+        <v>1298.399963378906</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11">
+      <c r="A292" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B292" t="s">
+        <v>17</v>
+      </c>
+      <c r="C292" t="s">
+        <v>28</v>
+      </c>
+      <c r="D292">
+        <v>19.7444</v>
+      </c>
+      <c r="E292">
+        <v>20.35000038146973</v>
+      </c>
+      <c r="F292">
+        <v>0.0306720073271271</v>
+      </c>
+      <c r="G292">
+        <v>3.07</v>
+      </c>
+      <c r="H292" t="s">
+        <v>17</v>
+      </c>
+      <c r="I292">
+        <v>61</v>
+      </c>
+      <c r="J292">
+        <v>1204.4084</v>
+      </c>
+      <c r="K292">
+        <v>1241.350023269653</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11">
+      <c r="A293" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B293" t="s">
+        <v>18</v>
+      </c>
+      <c r="C293" t="s">
+        <v>29</v>
+      </c>
+      <c r="D293">
+        <v>129.871</v>
+      </c>
+      <c r="E293">
+        <v>138.5200042724609</v>
+      </c>
+      <c r="F293">
+        <v>0.0665968866988082</v>
+      </c>
+      <c r="G293">
+        <v>6.66</v>
+      </c>
+      <c r="H293" t="s">
+        <v>18</v>
+      </c>
+      <c r="I293">
+        <v>51</v>
+      </c>
+      <c r="J293">
+        <v>6623.421</v>
+      </c>
+      <c r="K293">
+        <v>7064.520217895508</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11">
+      <c r="A294" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B294" t="s">
+        <v>19</v>
+      </c>
+      <c r="C294" t="s">
+        <v>30</v>
+      </c>
+      <c r="D294">
+        <v>34.0694</v>
+      </c>
+      <c r="E294">
+        <v>32.97999954223633</v>
+      </c>
+      <c r="F294">
+        <v>-0.0319759214357656</v>
+      </c>
+      <c r="G294">
+        <v>-3.2</v>
+      </c>
+      <c r="H294" t="s">
+        <v>19</v>
+      </c>
+      <c r="I294">
+        <v>34</v>
+      </c>
+      <c r="J294">
+        <v>1158.3596</v>
+      </c>
+      <c r="K294">
+        <v>1121.319984436035</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11">
+      <c r="A295" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B295" t="s">
+        <v>20</v>
+      </c>
+      <c r="C295" t="s">
+        <v>31</v>
+      </c>
+      <c r="D295">
+        <v>69.4158</v>
+      </c>
+      <c r="E295">
+        <v>68.22000122070312</v>
+      </c>
+      <c r="F295">
+        <v>-0.0172266080531647</v>
+      </c>
+      <c r="G295">
+        <v>-1.72</v>
+      </c>
+      <c r="H295" t="s">
+        <v>20</v>
+      </c>
+      <c r="I295">
+        <v>62</v>
+      </c>
+      <c r="J295">
+        <v>4303.7796</v>
+      </c>
+      <c r="K295">
+        <v>4229.640075683594</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11">
+      <c r="A296" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B296" t="s">
+        <v>21</v>
+      </c>
+      <c r="C296" t="s">
+        <v>32</v>
+      </c>
+      <c r="D296">
+        <v>8.1868</v>
+      </c>
+      <c r="E296">
+        <v>8.086000442504883</v>
+      </c>
+      <c r="F296">
+        <v>-0.0123124490026771</v>
+      </c>
+      <c r="G296">
+        <v>-1.23</v>
+      </c>
+      <c r="H296" t="s">
+        <v>21</v>
+      </c>
+      <c r="I296">
+        <v>431</v>
+      </c>
+      <c r="J296">
+        <v>3528.5108</v>
+      </c>
+      <c r="K296">
+        <v>3485.066190719604</v>
       </c>
     </row>
   </sheetData>
@@ -12923,7 +13380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -14029,6 +14486,47 @@
       </c>
       <c r="M27" s="2">
         <v>0.03533260048320974</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.0421410086913476</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.0195212496050221</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.0473440567625389</v>
+      </c>
+      <c r="E28" s="2">
+        <v>-0.0143110922195947</v>
+      </c>
+      <c r="F28" s="2">
+        <v>-0.0313796695879518</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.3548709860786649</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0.0306720073271271</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0.0665968866988082</v>
+      </c>
+      <c r="J28" s="2">
+        <v>-0.0319759214357656</v>
+      </c>
+      <c r="K28" s="2">
+        <v>-0.0172266080531647</v>
+      </c>
+      <c r="L28" s="2">
+        <v>-0.0123124490026771</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0.03157264743845434</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -305,16 +305,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$28</c:f>
+              <c:f>grafico_dati!$B$2:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -395,6 +398,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.0421410086913476</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.0457359818324658</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -422,10 +428,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -506,16 +512,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$28</c:f>
+              <c:f>grafico_dati!$C$2:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -596,6 +605,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.0195212496050221</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.0200990432065426</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -623,10 +635,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -707,16 +719,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$28</c:f>
+              <c:f>grafico_dati!$D$2:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -797,6 +812,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.0473440567625389</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.0439474781452899</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -824,10 +842,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -908,16 +926,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$28</c:f>
+              <c:f>grafico_dati!$E$2:$E$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -998,6 +1019,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>-0.0143110922195947</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.0115530440023524</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1025,10 +1049,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1109,16 +1133,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$28</c:f>
+              <c:f>grafico_dati!$F$2:$F$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1196,6 +1223,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>-0.0313796695879518</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.0404899188629684</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1223,10 +1253,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1307,16 +1337,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$28</c:f>
+              <c:f>grafico_dati!$G$2:$G$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1397,6 +1430,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.3548709860786649</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.3418482802668341</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1424,10 +1460,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1508,16 +1544,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$28</c:f>
+              <c:f>grafico_dati!$H$2:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1598,6 +1637,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.0306720073271271</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.0164907363517867</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1625,10 +1667,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1709,16 +1751,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$28</c:f>
+              <c:f>grafico_dati!$I$2:$I$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1796,6 +1841,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.0665968866988082</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.0604369044721539</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1823,10 +1871,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1907,16 +1955,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$28</c:f>
+              <c:f>grafico_dati!$J$2:$J$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -1997,6 +2048,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>-0.0319759214357656</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.0492935188277916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2024,10 +2078,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2108,16 +2162,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$28</c:f>
+              <c:f>grafico_dati!$K$2:$K$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2198,6 +2255,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>-0.0172266080531647</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.0251499202062742</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2225,10 +2285,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2309,16 +2369,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$28</c:f>
+              <c:f>grafico_dati!$L$2:$L$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2399,6 +2462,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>-0.0123124490026771</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.0146332646334195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2430,10 +2496,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$28</c:f>
+              <c:f>grafico_dati!$A$2:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2514,16 +2580,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$28</c:f>
+              <c:f>grafico_dati!$M$2:$M$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2604,6 +2673,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.03157264743845434</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.0260431799791101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3010,7 +3082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K296"/>
+  <dimension ref="A1:K307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -13371,6 +13443,391 @@
       </c>
       <c r="K296">
         <v>3485.066190719604</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11">
+      <c r="A297" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B297" t="s">
+        <v>11</v>
+      </c>
+      <c r="C297" t="s">
+        <v>22</v>
+      </c>
+      <c r="D297">
+        <v>50.07</v>
+      </c>
+      <c r="E297">
+        <v>52.36000061035156</v>
+      </c>
+      <c r="F297">
+        <v>0.0457359818324658</v>
+      </c>
+      <c r="G297">
+        <v>4.57</v>
+      </c>
+      <c r="H297" t="s">
+        <v>11</v>
+      </c>
+      <c r="I297">
+        <v>23</v>
+      </c>
+      <c r="J297">
+        <v>1151.61</v>
+      </c>
+      <c r="K297">
+        <v>1204.280014038086</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11">
+      <c r="A298" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B298" t="s">
+        <v>12</v>
+      </c>
+      <c r="C298" t="s">
+        <v>23</v>
+      </c>
+      <c r="D298">
+        <v>242.3</v>
+      </c>
+      <c r="E298">
+        <v>247.1699981689453</v>
+      </c>
+      <c r="F298">
+        <v>0.0200990432065426</v>
+      </c>
+      <c r="G298">
+        <v>2.01</v>
+      </c>
+      <c r="H298" t="s">
+        <v>12</v>
+      </c>
+      <c r="I298">
+        <v>5</v>
+      </c>
+      <c r="J298">
+        <v>1211.5</v>
+      </c>
+      <c r="K298">
+        <v>1235.849990844727</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11">
+      <c r="A299" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B299" t="s">
+        <v>13</v>
+      </c>
+      <c r="C299" t="s">
+        <v>24</v>
+      </c>
+      <c r="D299">
+        <v>38.273</v>
+      </c>
+      <c r="E299">
+        <v>39.95500183105469</v>
+      </c>
+      <c r="F299">
+        <v>0.0439474781452899</v>
+      </c>
+      <c r="G299">
+        <v>4.39</v>
+      </c>
+      <c r="H299" t="s">
+        <v>13</v>
+      </c>
+      <c r="I299">
+        <v>54</v>
+      </c>
+      <c r="J299">
+        <v>2066.742</v>
+      </c>
+      <c r="K299">
+        <v>2157.570098876953</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11">
+      <c r="A300" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B300" t="s">
+        <v>14</v>
+      </c>
+      <c r="C300" t="s">
+        <v>25</v>
+      </c>
+      <c r="D300">
+        <v>6.5264</v>
+      </c>
+      <c r="E300">
+        <v>6.451000213623047</v>
+      </c>
+      <c r="F300">
+        <v>-0.0115530440023524</v>
+      </c>
+      <c r="G300">
+        <v>-1.16</v>
+      </c>
+      <c r="H300" t="s">
+        <v>14</v>
+      </c>
+      <c r="I300">
+        <v>276</v>
+      </c>
+      <c r="J300">
+        <v>1801.2864</v>
+      </c>
+      <c r="K300">
+        <v>1780.476058959961</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11">
+      <c r="A301" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B301" t="s">
+        <v>15</v>
+      </c>
+      <c r="C301" t="s">
+        <v>26</v>
+      </c>
+      <c r="D301">
+        <v>197.58</v>
+      </c>
+      <c r="E301">
+        <v>189.5800018310547</v>
+      </c>
+      <c r="F301">
+        <v>-0.0404899188629684</v>
+      </c>
+      <c r="G301">
+        <v>-4.05</v>
+      </c>
+      <c r="H301" t="s">
+        <v>15</v>
+      </c>
+      <c r="I301">
+        <v>4</v>
+      </c>
+      <c r="J301">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K301">
+        <v>758.3200073242188</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11">
+      <c r="A302" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B302" t="s">
+        <v>16</v>
+      </c>
+      <c r="C302" t="s">
+        <v>27</v>
+      </c>
+      <c r="D302">
+        <v>79.86</v>
+      </c>
+      <c r="E302">
+        <v>107.1600036621094</v>
+      </c>
+      <c r="F302">
+        <v>0.3418482802668341</v>
+      </c>
+      <c r="G302">
+        <v>34.18</v>
+      </c>
+      <c r="H302" t="s">
+        <v>16</v>
+      </c>
+      <c r="I302">
+        <v>12</v>
+      </c>
+      <c r="J302">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K302">
+        <v>1285.920043945312</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11">
+      <c r="A303" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B303" t="s">
+        <v>17</v>
+      </c>
+      <c r="C303" t="s">
+        <v>28</v>
+      </c>
+      <c r="D303">
+        <v>19.7444</v>
+      </c>
+      <c r="E303">
+        <v>20.06999969482422</v>
+      </c>
+      <c r="F303">
+        <v>0.0164907363517867</v>
+      </c>
+      <c r="G303">
+        <v>1.65</v>
+      </c>
+      <c r="H303" t="s">
+        <v>17</v>
+      </c>
+      <c r="I303">
+        <v>61</v>
+      </c>
+      <c r="J303">
+        <v>1204.4084</v>
+      </c>
+      <c r="K303">
+        <v>1224.269981384277</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11">
+      <c r="A304" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B304" t="s">
+        <v>18</v>
+      </c>
+      <c r="C304" t="s">
+        <v>29</v>
+      </c>
+      <c r="D304">
+        <v>129.871</v>
+      </c>
+      <c r="E304">
+        <v>137.7200012207031</v>
+      </c>
+      <c r="F304">
+        <v>0.0604369044721539</v>
+      </c>
+      <c r="G304">
+        <v>6.04</v>
+      </c>
+      <c r="H304" t="s">
+        <v>18</v>
+      </c>
+      <c r="I304">
+        <v>51</v>
+      </c>
+      <c r="J304">
+        <v>6623.421</v>
+      </c>
+      <c r="K304">
+        <v>7023.720062255859</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11">
+      <c r="A305" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B305" t="s">
+        <v>19</v>
+      </c>
+      <c r="C305" t="s">
+        <v>30</v>
+      </c>
+      <c r="D305">
+        <v>34.0694</v>
+      </c>
+      <c r="E305">
+        <v>32.38999938964844</v>
+      </c>
+      <c r="F305">
+        <v>-0.0492935188277916</v>
+      </c>
+      <c r="G305">
+        <v>-4.93</v>
+      </c>
+      <c r="H305" t="s">
+        <v>19</v>
+      </c>
+      <c r="I305">
+        <v>34</v>
+      </c>
+      <c r="J305">
+        <v>1158.3596</v>
+      </c>
+      <c r="K305">
+        <v>1101.259979248047</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11">
+      <c r="A306" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B306" t="s">
+        <v>20</v>
+      </c>
+      <c r="C306" t="s">
+        <v>31</v>
+      </c>
+      <c r="D306">
+        <v>69.4158</v>
+      </c>
+      <c r="E306">
+        <v>67.66999816894531</v>
+      </c>
+      <c r="F306">
+        <v>-0.0251499202062742</v>
+      </c>
+      <c r="G306">
+        <v>-2.51</v>
+      </c>
+      <c r="H306" t="s">
+        <v>20</v>
+      </c>
+      <c r="I306">
+        <v>62</v>
+      </c>
+      <c r="J306">
+        <v>4303.7796</v>
+      </c>
+      <c r="K306">
+        <v>4195.539886474609</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11">
+      <c r="A307" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B307" t="s">
+        <v>21</v>
+      </c>
+      <c r="C307" t="s">
+        <v>32</v>
+      </c>
+      <c r="D307">
+        <v>8.1868</v>
+      </c>
+      <c r="E307">
+        <v>8.067000389099121</v>
+      </c>
+      <c r="F307">
+        <v>-0.0146332646334195</v>
+      </c>
+      <c r="G307">
+        <v>-1.46</v>
+      </c>
+      <c r="H307" t="s">
+        <v>21</v>
+      </c>
+      <c r="I307">
+        <v>431</v>
+      </c>
+      <c r="J307">
+        <v>3528.5108</v>
+      </c>
+      <c r="K307">
+        <v>3476.877167701721</v>
       </c>
     </row>
   </sheetData>
@@ -13380,7 +13837,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -14527,6 +14984,47 @@
       </c>
       <c r="M28" s="2">
         <v>0.03157264743845434</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.0457359818324658</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.0200990432065426</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.0439474781452899</v>
+      </c>
+      <c r="E29" s="2">
+        <v>-0.0115530440023524</v>
+      </c>
+      <c r="F29" s="2">
+        <v>-0.0404899188629684</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.3418482802668341</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0.0164907363517867</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0.0604369044721539</v>
+      </c>
+      <c r="J29" s="2">
+        <v>-0.0492935188277916</v>
+      </c>
+      <c r="K29" s="2">
+        <v>-0.0251499202062742</v>
+      </c>
+      <c r="L29" s="2">
+        <v>-0.0146332646334195</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0.0260431799791101</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -308,16 +308,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$29</c:f>
+              <c:f>grafico_dati!$B$2:$B$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -401,6 +404,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.0457359818324658</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.0788895637660009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -428,10 +434,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -515,16 +521,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$29</c:f>
+              <c:f>grafico_dati!$C$2:$C$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -608,6 +617,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.0200990432065426</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.0317787866281469</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -635,10 +647,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -722,16 +734,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$29</c:f>
+              <c:f>grafico_dati!$D$2:$D$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -815,6 +830,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.0439474781452899</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.1018210793234215</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -842,10 +860,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -929,16 +947,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$29</c:f>
+              <c:f>grafico_dati!$E$2:$E$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1022,6 +1043,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>-0.0115530440023524</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.0498897150820101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1049,10 +1073,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1136,16 +1160,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$29</c:f>
+              <c:f>grafico_dati!$F$2:$F$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1226,6 +1253,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>-0.0404899188629684</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.0084016878892805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1253,10 +1283,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1340,16 +1370,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$29</c:f>
+              <c:f>grafico_dati!$G$2:$G$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1433,6 +1466,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.3418482802668341</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.4032055792461027</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1460,10 +1496,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1547,16 +1583,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$29</c:f>
+              <c:f>grafico_dati!$H$2:$H$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1640,6 +1679,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.0164907363517867</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.0679990221626627</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1667,10 +1709,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1754,16 +1796,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$29</c:f>
+              <c:f>grafico_dati!$I$2:$I$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1844,6 +1889,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.0604369044721539</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.088002733880218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1871,10 +1919,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1958,16 +2006,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$29</c:f>
+              <c:f>grafico_dati!$J$2:$J$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2051,6 +2102,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>-0.0492935188277916</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.0203819263033691</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2078,10 +2132,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2165,16 +2219,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$29</c:f>
+              <c:f>grafico_dati!$K$2:$K$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2258,6 +2315,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>-0.0251499202062742</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.0003486589711023</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2285,10 +2345,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2372,16 +2432,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$29</c:f>
+              <c:f>grafico_dati!$L$2:$L$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2465,6 +2528,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>-0.0146332646334195</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.0133384871961619</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2496,10 +2562,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$29</c:f>
+              <c:f>grafico_dati!$A$2:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2583,16 +2649,19 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$29</c:f>
+              <c:f>grafico_dati!$M$2:$M$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2676,6 +2745,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.0260431799791101</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.06098925490738094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3082,7 +3154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K307"/>
+  <dimension ref="A1:K318"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -13828,6 +13900,391 @@
       </c>
       <c r="K307">
         <v>3476.877167701721</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11">
+      <c r="A308" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B308" t="s">
+        <v>11</v>
+      </c>
+      <c r="C308" t="s">
+        <v>22</v>
+      </c>
+      <c r="D308">
+        <v>50.07</v>
+      </c>
+      <c r="E308">
+        <v>54.02000045776367</v>
+      </c>
+      <c r="F308">
+        <v>0.0788895637660009</v>
+      </c>
+      <c r="G308">
+        <v>7.89</v>
+      </c>
+      <c r="H308" t="s">
+        <v>11</v>
+      </c>
+      <c r="I308">
+        <v>23</v>
+      </c>
+      <c r="J308">
+        <v>1151.61</v>
+      </c>
+      <c r="K308">
+        <v>1242.460010528564</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11">
+      <c r="A309" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B309" t="s">
+        <v>12</v>
+      </c>
+      <c r="C309" t="s">
+        <v>23</v>
+      </c>
+      <c r="D309">
+        <v>242.3</v>
+      </c>
+      <c r="E309">
+        <v>250</v>
+      </c>
+      <c r="F309">
+        <v>0.0317787866281469</v>
+      </c>
+      <c r="G309">
+        <v>3.18</v>
+      </c>
+      <c r="H309" t="s">
+        <v>12</v>
+      </c>
+      <c r="I309">
+        <v>5</v>
+      </c>
+      <c r="J309">
+        <v>1211.5</v>
+      </c>
+      <c r="K309">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11">
+      <c r="A310" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B310" t="s">
+        <v>13</v>
+      </c>
+      <c r="C310" t="s">
+        <v>24</v>
+      </c>
+      <c r="D310">
+        <v>38.273</v>
+      </c>
+      <c r="E310">
+        <v>42.16999816894531</v>
+      </c>
+      <c r="F310">
+        <v>0.1018210793234215</v>
+      </c>
+      <c r="G310">
+        <v>10.18</v>
+      </c>
+      <c r="H310" t="s">
+        <v>13</v>
+      </c>
+      <c r="I310">
+        <v>54</v>
+      </c>
+      <c r="J310">
+        <v>2066.742</v>
+      </c>
+      <c r="K310">
+        <v>2277.179901123047</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11">
+      <c r="A311" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B311" t="s">
+        <v>14</v>
+      </c>
+      <c r="C311" t="s">
+        <v>25</v>
+      </c>
+      <c r="D311">
+        <v>6.5264</v>
+      </c>
+      <c r="E311">
+        <v>6.852000236511231</v>
+      </c>
+      <c r="F311">
+        <v>0.0498897150820101</v>
+      </c>
+      <c r="G311">
+        <v>4.99</v>
+      </c>
+      <c r="H311" t="s">
+        <v>14</v>
+      </c>
+      <c r="I311">
+        <v>276</v>
+      </c>
+      <c r="J311">
+        <v>1801.2864</v>
+      </c>
+      <c r="K311">
+        <v>1891.1520652771</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11">
+      <c r="A312" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B312" t="s">
+        <v>15</v>
+      </c>
+      <c r="C312" t="s">
+        <v>26</v>
+      </c>
+      <c r="D312">
+        <v>197.58</v>
+      </c>
+      <c r="E312">
+        <v>199.2400054931641</v>
+      </c>
+      <c r="F312">
+        <v>0.0084016878892805</v>
+      </c>
+      <c r="G312">
+        <v>0.84</v>
+      </c>
+      <c r="H312" t="s">
+        <v>15</v>
+      </c>
+      <c r="I312">
+        <v>4</v>
+      </c>
+      <c r="J312">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K312">
+        <v>796.9600219726564</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11">
+      <c r="A313" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B313" t="s">
+        <v>16</v>
+      </c>
+      <c r="C313" t="s">
+        <v>27</v>
+      </c>
+      <c r="D313">
+        <v>79.86</v>
+      </c>
+      <c r="E313">
+        <v>112.0599975585938</v>
+      </c>
+      <c r="F313">
+        <v>0.4032055792461027</v>
+      </c>
+      <c r="G313">
+        <v>40.32</v>
+      </c>
+      <c r="H313" t="s">
+        <v>16</v>
+      </c>
+      <c r="I313">
+        <v>12</v>
+      </c>
+      <c r="J313">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K313">
+        <v>1344.719970703125</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11">
+      <c r="A314" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B314" t="s">
+        <v>17</v>
+      </c>
+      <c r="C314" t="s">
+        <v>28</v>
+      </c>
+      <c r="D314">
+        <v>19.7444</v>
+      </c>
+      <c r="E314">
+        <v>21.08699989318848</v>
+      </c>
+      <c r="F314">
+        <v>0.0679990221626627</v>
+      </c>
+      <c r="G314">
+        <v>6.8</v>
+      </c>
+      <c r="H314" t="s">
+        <v>17</v>
+      </c>
+      <c r="I314">
+        <v>61</v>
+      </c>
+      <c r="J314">
+        <v>1204.4084</v>
+      </c>
+      <c r="K314">
+        <v>1286.306993484497</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11">
+      <c r="A315" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B315" t="s">
+        <v>18</v>
+      </c>
+      <c r="C315" t="s">
+        <v>29</v>
+      </c>
+      <c r="D315">
+        <v>129.871</v>
+      </c>
+      <c r="E315">
+        <v>141.3000030517578</v>
+      </c>
+      <c r="F315">
+        <v>0.088002733880218</v>
+      </c>
+      <c r="G315">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H315" t="s">
+        <v>18</v>
+      </c>
+      <c r="I315">
+        <v>51</v>
+      </c>
+      <c r="J315">
+        <v>6623.421</v>
+      </c>
+      <c r="K315">
+        <v>7206.300155639648</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11">
+      <c r="A316" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B316" t="s">
+        <v>19</v>
+      </c>
+      <c r="C316" t="s">
+        <v>30</v>
+      </c>
+      <c r="D316">
+        <v>34.0694</v>
+      </c>
+      <c r="E316">
+        <v>33.375</v>
+      </c>
+      <c r="F316">
+        <v>-0.0203819263033691</v>
+      </c>
+      <c r="G316">
+        <v>-2.04</v>
+      </c>
+      <c r="H316" t="s">
+        <v>19</v>
+      </c>
+      <c r="I316">
+        <v>34</v>
+      </c>
+      <c r="J316">
+        <v>1158.3596</v>
+      </c>
+      <c r="K316">
+        <v>1134.75</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11">
+      <c r="A317" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B317" t="s">
+        <v>20</v>
+      </c>
+      <c r="C317" t="s">
+        <v>31</v>
+      </c>
+      <c r="D317">
+        <v>69.4158</v>
+      </c>
+      <c r="E317">
+        <v>69.44000244140625</v>
+      </c>
+      <c r="F317">
+        <v>0.0003486589711023</v>
+      </c>
+      <c r="G317">
+        <v>0.03</v>
+      </c>
+      <c r="H317" t="s">
+        <v>20</v>
+      </c>
+      <c r="I317">
+        <v>62</v>
+      </c>
+      <c r="J317">
+        <v>4303.7796</v>
+      </c>
+      <c r="K317">
+        <v>4305.280151367188</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11">
+      <c r="A318" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B318" t="s">
+        <v>21</v>
+      </c>
+      <c r="C318" t="s">
+        <v>32</v>
+      </c>
+      <c r="D318">
+        <v>8.1868</v>
+      </c>
+      <c r="E318">
+        <v>8.295999526977539</v>
+      </c>
+      <c r="F318">
+        <v>0.0133384871961619</v>
+      </c>
+      <c r="G318">
+        <v>1.33</v>
+      </c>
+      <c r="H318" t="s">
+        <v>21</v>
+      </c>
+      <c r="I318">
+        <v>431</v>
+      </c>
+      <c r="J318">
+        <v>3528.5108</v>
+      </c>
+      <c r="K318">
+        <v>3575.575796127319</v>
       </c>
     </row>
   </sheetData>
@@ -13837,7 +14294,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -15025,6 +15482,47 @@
       </c>
       <c r="M29" s="2">
         <v>0.0260431799791101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.0788895637660009</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.0317787866281469</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.1018210793234215</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.0498897150820101</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.0084016878892805</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.4032055792461027</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0.0679990221626627</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.088002733880218</v>
+      </c>
+      <c r="J30" s="2">
+        <v>-0.0203819263033691</v>
+      </c>
+      <c r="K30" s="2">
+        <v>0.0003486589711023</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0.0133384871961619</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0.06098925490738094</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -311,16 +311,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$30</c:f>
+              <c:f>grafico_dati!$B$2:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -407,6 +410,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.0788895637660009</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0854802970665287</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -434,10 +440,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -524,16 +530,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$30</c:f>
+              <c:f>grafico_dati!$C$2:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -620,6 +629,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.0317787866281469</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0311184330907579</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -647,10 +659,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -737,16 +749,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$30</c:f>
+              <c:f>grafico_dati!$D$2:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -833,6 +848,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.1018210793234215</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0979019271487384</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -860,10 +878,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -950,16 +968,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$30</c:f>
+              <c:f>grafico_dati!$E$2:$E$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1046,6 +1067,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.0498897150820101</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0440671931998815</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1073,10 +1097,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1163,16 +1187,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$30</c:f>
+              <c:f>grafico_dati!$F$2:$F$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1256,6 +1283,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.0084016878892805</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.00263185768502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1283,10 +1313,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1373,16 +1403,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$30</c:f>
+              <c:f>grafico_dati!$G$2:$G$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1469,6 +1502,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.4032055792461027</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.4064613034663689</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1496,10 +1532,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1586,16 +1622,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$30</c:f>
+              <c:f>grafico_dati!$H$2:$H$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1682,6 +1721,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.0679990221626627</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0489556756601812</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1709,10 +1751,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1799,16 +1841,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$30</c:f>
+              <c:f>grafico_dati!$I$2:$I$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1892,6 +1937,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.088002733880218</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0894657428768859</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1919,10 +1967,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2009,16 +2057,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$30</c:f>
+              <c:f>grafico_dati!$J$2:$J$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2105,6 +2156,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>-0.0203819263033691</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.0190611466904228</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2132,10 +2186,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2222,16 +2276,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$30</c:f>
+              <c:f>grafico_dati!$K$2:$K$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2318,6 +2375,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.0003486589711023</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0036619641197725</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2345,10 +2405,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2435,16 +2495,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$30</c:f>
+              <c:f>grafico_dati!$L$2:$L$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2531,6 +2594,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.0133384871961619</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0124834559895341</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2562,10 +2628,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$30</c:f>
+              <c:f>grafico_dati!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2652,16 +2718,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46121</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$30</c:f>
+              <c:f>grafico_dati!$M$2:$M$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2748,6 +2817,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.06098925490738094</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.06026859412382479</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3154,7 +3226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K318"/>
+  <dimension ref="A1:K329"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -14285,6 +14357,391 @@
       </c>
       <c r="K318">
         <v>3575.575796127319</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11">
+      <c r="A319" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B319" t="s">
+        <v>11</v>
+      </c>
+      <c r="C319" t="s">
+        <v>22</v>
+      </c>
+      <c r="D319">
+        <v>50.07</v>
+      </c>
+      <c r="E319">
+        <v>54.34999847412109</v>
+      </c>
+      <c r="F319">
+        <v>0.0854802970665287</v>
+      </c>
+      <c r="G319">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H319" t="s">
+        <v>11</v>
+      </c>
+      <c r="I319">
+        <v>23</v>
+      </c>
+      <c r="J319">
+        <v>1151.61</v>
+      </c>
+      <c r="K319">
+        <v>1250.049964904785</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11">
+      <c r="A320" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B320" t="s">
+        <v>12</v>
+      </c>
+      <c r="C320" t="s">
+        <v>23</v>
+      </c>
+      <c r="D320">
+        <v>242.3</v>
+      </c>
+      <c r="E320">
+        <v>249.8399963378907</v>
+      </c>
+      <c r="F320">
+        <v>0.0311184330907579</v>
+      </c>
+      <c r="G320">
+        <v>3.11</v>
+      </c>
+      <c r="H320" t="s">
+        <v>12</v>
+      </c>
+      <c r="I320">
+        <v>5</v>
+      </c>
+      <c r="J320">
+        <v>1211.5</v>
+      </c>
+      <c r="K320">
+        <v>1249.199981689453</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11">
+      <c r="A321" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B321" t="s">
+        <v>13</v>
+      </c>
+      <c r="C321" t="s">
+        <v>24</v>
+      </c>
+      <c r="D321">
+        <v>38.273</v>
+      </c>
+      <c r="E321">
+        <v>42.02000045776367</v>
+      </c>
+      <c r="F321">
+        <v>0.0979019271487384</v>
+      </c>
+      <c r="G321">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="H321" t="s">
+        <v>13</v>
+      </c>
+      <c r="I321">
+        <v>54</v>
+      </c>
+      <c r="J321">
+        <v>2066.742</v>
+      </c>
+      <c r="K321">
+        <v>2269.080024719238</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11">
+      <c r="A322" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B322" t="s">
+        <v>14</v>
+      </c>
+      <c r="C322" t="s">
+        <v>25</v>
+      </c>
+      <c r="D322">
+        <v>6.5264</v>
+      </c>
+      <c r="E322">
+        <v>6.814000129699707</v>
+      </c>
+      <c r="F322">
+        <v>0.0440671931998815</v>
+      </c>
+      <c r="G322">
+        <v>4.41</v>
+      </c>
+      <c r="H322" t="s">
+        <v>14</v>
+      </c>
+      <c r="I322">
+        <v>276</v>
+      </c>
+      <c r="J322">
+        <v>1801.2864</v>
+      </c>
+      <c r="K322">
+        <v>1880.664035797119</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11">
+      <c r="A323" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B323" t="s">
+        <v>15</v>
+      </c>
+      <c r="C323" t="s">
+        <v>26</v>
+      </c>
+      <c r="D323">
+        <v>197.58</v>
+      </c>
+      <c r="E323">
+        <v>197.0599975585937</v>
+      </c>
+      <c r="F323">
+        <v>-0.00263185768502</v>
+      </c>
+      <c r="G323">
+        <v>-0.26</v>
+      </c>
+      <c r="H323" t="s">
+        <v>15</v>
+      </c>
+      <c r="I323">
+        <v>4</v>
+      </c>
+      <c r="J323">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K323">
+        <v>788.2399902343749</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11">
+      <c r="A324" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B324" t="s">
+        <v>16</v>
+      </c>
+      <c r="C324" t="s">
+        <v>27</v>
+      </c>
+      <c r="D324">
+        <v>79.86</v>
+      </c>
+      <c r="E324">
+        <v>112.3199996948242</v>
+      </c>
+      <c r="F324">
+        <v>0.4064613034663689</v>
+      </c>
+      <c r="G324">
+        <v>40.65</v>
+      </c>
+      <c r="H324" t="s">
+        <v>16</v>
+      </c>
+      <c r="I324">
+        <v>12</v>
+      </c>
+      <c r="J324">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K324">
+        <v>1347.839996337891</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11">
+      <c r="A325" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B325" t="s">
+        <v>17</v>
+      </c>
+      <c r="C325" t="s">
+        <v>28</v>
+      </c>
+      <c r="D325">
+        <v>19.7444</v>
+      </c>
+      <c r="E325">
+        <v>20.71100044250488</v>
+      </c>
+      <c r="F325">
+        <v>0.0489556756601812</v>
+      </c>
+      <c r="G325">
+        <v>4.9</v>
+      </c>
+      <c r="H325" t="s">
+        <v>17</v>
+      </c>
+      <c r="I325">
+        <v>61</v>
+      </c>
+      <c r="J325">
+        <v>1204.4084</v>
+      </c>
+      <c r="K325">
+        <v>1263.371026992798</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11">
+      <c r="A326" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B326" t="s">
+        <v>18</v>
+      </c>
+      <c r="C326" t="s">
+        <v>29</v>
+      </c>
+      <c r="D326">
+        <v>129.871</v>
+      </c>
+      <c r="E326">
+        <v>141.4900054931641</v>
+      </c>
+      <c r="F326">
+        <v>0.0894657428768859</v>
+      </c>
+      <c r="G326">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H326" t="s">
+        <v>18</v>
+      </c>
+      <c r="I326">
+        <v>51</v>
+      </c>
+      <c r="J326">
+        <v>6623.421</v>
+      </c>
+      <c r="K326">
+        <v>7215.990280151367</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11">
+      <c r="A327" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B327" t="s">
+        <v>19</v>
+      </c>
+      <c r="C327" t="s">
+        <v>30</v>
+      </c>
+      <c r="D327">
+        <v>34.0694</v>
+      </c>
+      <c r="E327">
+        <v>33.41999816894531</v>
+      </c>
+      <c r="F327">
+        <v>-0.0190611466904228</v>
+      </c>
+      <c r="G327">
+        <v>-1.91</v>
+      </c>
+      <c r="H327" t="s">
+        <v>19</v>
+      </c>
+      <c r="I327">
+        <v>34</v>
+      </c>
+      <c r="J327">
+        <v>1158.3596</v>
+      </c>
+      <c r="K327">
+        <v>1136.279937744141</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11">
+      <c r="A328" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B328" t="s">
+        <v>20</v>
+      </c>
+      <c r="C328" t="s">
+        <v>31</v>
+      </c>
+      <c r="D328">
+        <v>69.4158</v>
+      </c>
+      <c r="E328">
+        <v>69.66999816894531</v>
+      </c>
+      <c r="F328">
+        <v>0.0036619641197725</v>
+      </c>
+      <c r="G328">
+        <v>0.37</v>
+      </c>
+      <c r="H328" t="s">
+        <v>20</v>
+      </c>
+      <c r="I328">
+        <v>62</v>
+      </c>
+      <c r="J328">
+        <v>4303.7796</v>
+      </c>
+      <c r="K328">
+        <v>4319.539886474609</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11">
+      <c r="A329" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B329" t="s">
+        <v>21</v>
+      </c>
+      <c r="C329" t="s">
+        <v>32</v>
+      </c>
+      <c r="D329">
+        <v>8.1868</v>
+      </c>
+      <c r="E329">
+        <v>8.288999557495117</v>
+      </c>
+      <c r="F329">
+        <v>0.0124834559895341</v>
+      </c>
+      <c r="G329">
+        <v>1.25</v>
+      </c>
+      <c r="H329" t="s">
+        <v>21</v>
+      </c>
+      <c r="I329">
+        <v>431</v>
+      </c>
+      <c r="J329">
+        <v>3528.5108</v>
+      </c>
+      <c r="K329">
+        <v>3572.558809280396</v>
       </c>
     </row>
   </sheetData>
@@ -14294,7 +14751,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -15523,6 +15980,47 @@
       </c>
       <c r="M30" s="2">
         <v>0.06098925490738094</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.0854802970665287</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.0311184330907579</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.0979019271487384</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.0440671931998815</v>
+      </c>
+      <c r="F31" s="2">
+        <v>-0.00263185768502</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.4064613034663689</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0.0489556756601812</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.0894657428768859</v>
+      </c>
+      <c r="J31" s="2">
+        <v>-0.0190611466904228</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0.0036619641197725</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0.0124834559895341</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0.06026859412382479</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -314,16 +314,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$31</c:f>
+              <c:f>grafico_dati!$B$2:$B$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -413,6 +416,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.0854802970665287</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.0922707934233868</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -440,10 +446,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -533,16 +539,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$31</c:f>
+              <c:f>grafico_dati!$C$2:$C$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -632,6 +641,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.0311184330907579</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.0321915233327099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -659,10 +671,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -752,16 +764,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$31</c:f>
+              <c:f>grafico_dati!$D$2:$D$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -851,6 +866,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.0979019271487384</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.1078306253985552</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -878,10 +896,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -971,16 +989,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$31</c:f>
+              <c:f>grafico_dati!$E$2:$E$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1070,6 +1091,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.0440671931998815</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.0570912245413519</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1097,10 +1121,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1190,16 +1214,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$31</c:f>
+              <c:f>grafico_dati!$F$2:$F$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1286,6 +1313,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>-0.00263185768502</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.0037453368868781</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1313,10 +1343,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1406,16 +1436,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$31</c:f>
+              <c:f>grafico_dati!$G$2:$G$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1505,6 +1538,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.4064613034663689</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.4207362770407294</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1532,10 +1568,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1625,16 +1661,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$31</c:f>
+              <c:f>grafico_dati!$H$2:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1724,6 +1763,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.0489556756601812</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.0483478558430354</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1751,10 +1793,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1844,16 +1886,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$31</c:f>
+              <c:f>grafico_dati!$I$2:$I$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1940,6 +1985,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.0894657428768859</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.0919296652724144</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1967,10 +2015,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2060,16 +2108,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$31</c:f>
+              <c:f>grafico_dati!$J$2:$J$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2159,6 +2210,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>-0.0190611466904228</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.0170064140117878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2186,10 +2240,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2279,16 +2333,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$31</c:f>
+              <c:f>grafico_dati!$K$2:$K$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2378,6 +2435,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.0036619641197725</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.00553480694248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2405,10 +2465,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2498,16 +2558,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$31</c:f>
+              <c:f>grafico_dati!$L$2:$L$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2597,6 +2660,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.0124834559895341</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.0105291155871365</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2628,10 +2694,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$31</c:f>
+              <c:f>grafico_dati!$A$2:$A$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2721,16 +2787,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$31</c:f>
+              <c:f>grafico_dati!$M$2:$M$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2820,6 +2889,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.06026859412382479</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.06369755078311989</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3226,7 +3298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K329"/>
+  <dimension ref="A1:K340"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -14531,7 +14603,7 @@
         <v>790.3200000000001</v>
       </c>
       <c r="K323">
-        <v>788.2399902343749</v>
+        <v>788.2399902343748</v>
       </c>
     </row>
     <row r="324" spans="1:11">
@@ -14742,6 +14814,391 @@
       </c>
       <c r="K329">
         <v>3572.558809280396</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11">
+      <c r="A330" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B330" t="s">
+        <v>11</v>
+      </c>
+      <c r="C330" t="s">
+        <v>22</v>
+      </c>
+      <c r="D330">
+        <v>50.07</v>
+      </c>
+      <c r="E330">
+        <v>54.68999862670898</v>
+      </c>
+      <c r="F330">
+        <v>0.0922707934233868</v>
+      </c>
+      <c r="G330">
+        <v>9.23</v>
+      </c>
+      <c r="H330" t="s">
+        <v>11</v>
+      </c>
+      <c r="I330">
+        <v>23</v>
+      </c>
+      <c r="J330">
+        <v>1151.61</v>
+      </c>
+      <c r="K330">
+        <v>1257.869968414306</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11">
+      <c r="A331" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B331" t="s">
+        <v>12</v>
+      </c>
+      <c r="C331" t="s">
+        <v>23</v>
+      </c>
+      <c r="D331">
+        <v>242.3</v>
+      </c>
+      <c r="E331">
+        <v>250.1000061035156</v>
+      </c>
+      <c r="F331">
+        <v>0.0321915233327099</v>
+      </c>
+      <c r="G331">
+        <v>3.22</v>
+      </c>
+      <c r="H331" t="s">
+        <v>12</v>
+      </c>
+      <c r="I331">
+        <v>5</v>
+      </c>
+      <c r="J331">
+        <v>1211.5</v>
+      </c>
+      <c r="K331">
+        <v>1250.500030517578</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11">
+      <c r="A332" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B332" t="s">
+        <v>13</v>
+      </c>
+      <c r="C332" t="s">
+        <v>24</v>
+      </c>
+      <c r="D332">
+        <v>38.273</v>
+      </c>
+      <c r="E332">
+        <v>42.40000152587891</v>
+      </c>
+      <c r="F332">
+        <v>0.1078306253985552</v>
+      </c>
+      <c r="G332">
+        <v>10.78</v>
+      </c>
+      <c r="H332" t="s">
+        <v>13</v>
+      </c>
+      <c r="I332">
+        <v>54</v>
+      </c>
+      <c r="J332">
+        <v>2066.742</v>
+      </c>
+      <c r="K332">
+        <v>2289.600082397461</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11">
+      <c r="A333" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B333" t="s">
+        <v>14</v>
+      </c>
+      <c r="C333" t="s">
+        <v>25</v>
+      </c>
+      <c r="D333">
+        <v>6.5264</v>
+      </c>
+      <c r="E333">
+        <v>6.89900016784668</v>
+      </c>
+      <c r="F333">
+        <v>0.0570912245413519</v>
+      </c>
+      <c r="G333">
+        <v>5.71</v>
+      </c>
+      <c r="H333" t="s">
+        <v>14</v>
+      </c>
+      <c r="I333">
+        <v>276</v>
+      </c>
+      <c r="J333">
+        <v>1801.2864</v>
+      </c>
+      <c r="K333">
+        <v>1904.124046325684</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11">
+      <c r="A334" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B334" t="s">
+        <v>15</v>
+      </c>
+      <c r="C334" t="s">
+        <v>26</v>
+      </c>
+      <c r="D334">
+        <v>197.58</v>
+      </c>
+      <c r="E334">
+        <v>196.8399963378907</v>
+      </c>
+      <c r="F334">
+        <v>-0.0037453368868781</v>
+      </c>
+      <c r="G334">
+        <v>-0.37</v>
+      </c>
+      <c r="H334" t="s">
+        <v>15</v>
+      </c>
+      <c r="I334">
+        <v>4</v>
+      </c>
+      <c r="J334">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K334">
+        <v>787.3599853515626</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11">
+      <c r="A335" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B335" t="s">
+        <v>16</v>
+      </c>
+      <c r="C335" t="s">
+        <v>27</v>
+      </c>
+      <c r="D335">
+        <v>79.86</v>
+      </c>
+      <c r="E335">
+        <v>113.4599990844727</v>
+      </c>
+      <c r="F335">
+        <v>0.4207362770407294</v>
+      </c>
+      <c r="G335">
+        <v>42.07</v>
+      </c>
+      <c r="H335" t="s">
+        <v>16</v>
+      </c>
+      <c r="I335">
+        <v>12</v>
+      </c>
+      <c r="J335">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K335">
+        <v>1361.519989013672</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11">
+      <c r="A336" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B336" t="s">
+        <v>17</v>
+      </c>
+      <c r="C336" t="s">
+        <v>28</v>
+      </c>
+      <c r="D336">
+        <v>19.7444</v>
+      </c>
+      <c r="E336">
+        <v>20.69899940490723</v>
+      </c>
+      <c r="F336">
+        <v>0.0483478558430354</v>
+      </c>
+      <c r="G336">
+        <v>4.83</v>
+      </c>
+      <c r="H336" t="s">
+        <v>17</v>
+      </c>
+      <c r="I336">
+        <v>61</v>
+      </c>
+      <c r="J336">
+        <v>1204.4084</v>
+      </c>
+      <c r="K336">
+        <v>1262.638963699341</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11">
+      <c r="A337" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B337" t="s">
+        <v>18</v>
+      </c>
+      <c r="C337" t="s">
+        <v>29</v>
+      </c>
+      <c r="D337">
+        <v>129.871</v>
+      </c>
+      <c r="E337">
+        <v>141.8099975585938</v>
+      </c>
+      <c r="F337">
+        <v>0.0919296652724144</v>
+      </c>
+      <c r="G337">
+        <v>9.19</v>
+      </c>
+      <c r="H337" t="s">
+        <v>18</v>
+      </c>
+      <c r="I337">
+        <v>51</v>
+      </c>
+      <c r="J337">
+        <v>6623.421</v>
+      </c>
+      <c r="K337">
+        <v>7232.309875488281</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11">
+      <c r="A338" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B338" t="s">
+        <v>19</v>
+      </c>
+      <c r="C338" t="s">
+        <v>30</v>
+      </c>
+      <c r="D338">
+        <v>34.0694</v>
+      </c>
+      <c r="E338">
+        <v>33.4900016784668</v>
+      </c>
+      <c r="F338">
+        <v>-0.0170064140117878</v>
+      </c>
+      <c r="G338">
+        <v>-1.7</v>
+      </c>
+      <c r="H338" t="s">
+        <v>19</v>
+      </c>
+      <c r="I338">
+        <v>34</v>
+      </c>
+      <c r="J338">
+        <v>1158.3596</v>
+      </c>
+      <c r="K338">
+        <v>1138.660057067871</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11">
+      <c r="A339" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B339" t="s">
+        <v>20</v>
+      </c>
+      <c r="C339" t="s">
+        <v>31</v>
+      </c>
+      <c r="D339">
+        <v>69.4158</v>
+      </c>
+      <c r="E339">
+        <v>69.80000305175781</v>
+      </c>
+      <c r="F339">
+        <v>0.00553480694248</v>
+      </c>
+      <c r="G339">
+        <v>0.55</v>
+      </c>
+      <c r="H339" t="s">
+        <v>20</v>
+      </c>
+      <c r="I339">
+        <v>62</v>
+      </c>
+      <c r="J339">
+        <v>4303.7796</v>
+      </c>
+      <c r="K339">
+        <v>4327.600189208984</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11">
+      <c r="A340" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B340" t="s">
+        <v>21</v>
+      </c>
+      <c r="C340" t="s">
+        <v>32</v>
+      </c>
+      <c r="D340">
+        <v>8.1868</v>
+      </c>
+      <c r="E340">
+        <v>8.27299976348877</v>
+      </c>
+      <c r="F340">
+        <v>0.0105291155871365</v>
+      </c>
+      <c r="G340">
+        <v>1.05</v>
+      </c>
+      <c r="H340" t="s">
+        <v>21</v>
+      </c>
+      <c r="I340">
+        <v>431</v>
+      </c>
+      <c r="J340">
+        <v>3528.5108</v>
+      </c>
+      <c r="K340">
+        <v>3565.66289806366</v>
       </c>
     </row>
   </sheetData>
@@ -14751,7 +15208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -16021,6 +16478,47 @@
       </c>
       <c r="M31" s="2">
         <v>0.06026859412382479</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.0922707934233868</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.0321915233327099</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0.1078306253985552</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.0570912245413519</v>
+      </c>
+      <c r="F32" s="2">
+        <v>-0.0037453368868781</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.4207362770407294</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0.0483478558430354</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0.0919296652724144</v>
+      </c>
+      <c r="J32" s="2">
+        <v>-0.0170064140117878</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0.00553480694248</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0.0105291155871365</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0.06369755078311989</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -317,16 +317,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$32</c:f>
+              <c:f>grafico_dati!$B$2:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -419,6 +422,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.0922707934233868</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.09167165662896171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -446,10 +452,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -542,16 +548,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$32</c:f>
+              <c:f>grafico_dati!$C$2:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -644,6 +653,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.0321915233327099</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.0356995334223779</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -671,10 +683,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -767,16 +779,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$32</c:f>
+              <c:f>grafico_dati!$D$2:$D$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -869,6 +884,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.1078306253985552</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.1040420418601946</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -896,10 +914,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -992,16 +1010,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$32</c:f>
+              <c:f>grafico_dati!$E$2:$E$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1094,6 +1115,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.0570912245413519</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.0523412647887928</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1121,10 +1145,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1217,16 +1241,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$32</c:f>
+              <c:f>grafico_dati!$F$2:$F$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1316,6 +1343,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>-0.0037453368868781</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.0065796194994591</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1343,10 +1373,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1439,16 +1469,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$32</c:f>
+              <c:f>grafico_dati!$G$2:$G$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1541,6 +1574,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.4207362770407294</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.4159779843608151</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1568,10 +1604,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1664,16 +1700,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$32</c:f>
+              <c:f>grafico_dati!$H$2:$H$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1766,6 +1805,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.0483478558430354</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.0409533587477948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1793,10 +1835,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1889,16 +1931,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$32</c:f>
+              <c:f>grafico_dati!$I$2:$I$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -1987,6 +2032,9 @@
                   <c:v>0.0894657428768859</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>0.0919296652724144</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>0.0919296652724144</c:v>
                 </c:pt>
               </c:numCache>
@@ -2015,10 +2063,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2111,16 +2159,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$32</c:f>
+              <c:f>grafico_dati!$J$2:$J$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2213,6 +2264,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>-0.0170064140117878</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.0150985839147217</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2240,10 +2294,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2336,16 +2390,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$32</c:f>
+              <c:f>grafico_dati!$K$2:$K$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2438,6 +2495,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.00553480694248</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.0040941247992847</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2465,10 +2525,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2561,16 +2621,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$32</c:f>
+              <c:f>grafico_dati!$L$2:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2662,6 +2725,9 @@
                   <c:v>0.0124834559895341</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>0.0105291155871365</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>0.0105291155871365</c:v>
                 </c:pt>
               </c:numCache>
@@ -2694,10 +2760,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$32</c:f>
+              <c:f>grafico_dati!$A$2:$A$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2790,16 +2856,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$32</c:f>
+              <c:f>grafico_dati!$M$2:$M$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2892,6 +2961,9 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0.06369755078311989</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.06238606925142931</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3298,7 +3370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K340"/>
+  <dimension ref="A1:K351"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -15198,6 +15270,391 @@
         <v>3528.5108</v>
       </c>
       <c r="K340">
+        <v>3565.66289806366</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11">
+      <c r="A341" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B341" t="s">
+        <v>11</v>
+      </c>
+      <c r="C341" t="s">
+        <v>22</v>
+      </c>
+      <c r="D341">
+        <v>50.07</v>
+      </c>
+      <c r="E341">
+        <v>54.65999984741211</v>
+      </c>
+      <c r="F341">
+        <v>0.09167165662896171</v>
+      </c>
+      <c r="G341">
+        <v>9.17</v>
+      </c>
+      <c r="H341" t="s">
+        <v>11</v>
+      </c>
+      <c r="I341">
+        <v>23</v>
+      </c>
+      <c r="J341">
+        <v>1151.61</v>
+      </c>
+      <c r="K341">
+        <v>1257.179996490479</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11">
+      <c r="A342" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B342" t="s">
+        <v>12</v>
+      </c>
+      <c r="C342" t="s">
+        <v>23</v>
+      </c>
+      <c r="D342">
+        <v>242.3</v>
+      </c>
+      <c r="E342">
+        <v>250.9499969482422</v>
+      </c>
+      <c r="F342">
+        <v>0.0356995334223779</v>
+      </c>
+      <c r="G342">
+        <v>3.57</v>
+      </c>
+      <c r="H342" t="s">
+        <v>12</v>
+      </c>
+      <c r="I342">
+        <v>5</v>
+      </c>
+      <c r="J342">
+        <v>1211.5</v>
+      </c>
+      <c r="K342">
+        <v>1254.749984741211</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11">
+      <c r="A343" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B343" t="s">
+        <v>13</v>
+      </c>
+      <c r="C343" t="s">
+        <v>24</v>
+      </c>
+      <c r="D343">
+        <v>38.273</v>
+      </c>
+      <c r="E343">
+        <v>42.25500106811523</v>
+      </c>
+      <c r="F343">
+        <v>0.1040420418601946</v>
+      </c>
+      <c r="G343">
+        <v>10.4</v>
+      </c>
+      <c r="H343" t="s">
+        <v>13</v>
+      </c>
+      <c r="I343">
+        <v>54</v>
+      </c>
+      <c r="J343">
+        <v>2066.742</v>
+      </c>
+      <c r="K343">
+        <v>2281.770057678223</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11">
+      <c r="A344" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B344" t="s">
+        <v>14</v>
+      </c>
+      <c r="C344" t="s">
+        <v>25</v>
+      </c>
+      <c r="D344">
+        <v>6.5264</v>
+      </c>
+      <c r="E344">
+        <v>6.868000030517578</v>
+      </c>
+      <c r="F344">
+        <v>0.0523412647887928</v>
+      </c>
+      <c r="G344">
+        <v>5.23</v>
+      </c>
+      <c r="H344" t="s">
+        <v>14</v>
+      </c>
+      <c r="I344">
+        <v>276</v>
+      </c>
+      <c r="J344">
+        <v>1801.2864</v>
+      </c>
+      <c r="K344">
+        <v>1895.568008422852</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11">
+      <c r="A345" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B345" t="s">
+        <v>15</v>
+      </c>
+      <c r="C345" t="s">
+        <v>26</v>
+      </c>
+      <c r="D345">
+        <v>197.58</v>
+      </c>
+      <c r="E345">
+        <v>196.2799987792969</v>
+      </c>
+      <c r="F345">
+        <v>-0.0065796194994591</v>
+      </c>
+      <c r="G345">
+        <v>-0.66</v>
+      </c>
+      <c r="H345" t="s">
+        <v>15</v>
+      </c>
+      <c r="I345">
+        <v>4</v>
+      </c>
+      <c r="J345">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K345">
+        <v>785.1199951171875</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11">
+      <c r="A346" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B346" t="s">
+        <v>16</v>
+      </c>
+      <c r="C346" t="s">
+        <v>27</v>
+      </c>
+      <c r="D346">
+        <v>79.86</v>
+      </c>
+      <c r="E346">
+        <v>113.0800018310547</v>
+      </c>
+      <c r="F346">
+        <v>0.4159779843608151</v>
+      </c>
+      <c r="G346">
+        <v>41.6</v>
+      </c>
+      <c r="H346" t="s">
+        <v>16</v>
+      </c>
+      <c r="I346">
+        <v>12</v>
+      </c>
+      <c r="J346">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K346">
+        <v>1356.960021972656</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11">
+      <c r="A347" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B347" t="s">
+        <v>17</v>
+      </c>
+      <c r="C347" t="s">
+        <v>28</v>
+      </c>
+      <c r="D347">
+        <v>19.7444</v>
+      </c>
+      <c r="E347">
+        <v>20.55299949645996</v>
+      </c>
+      <c r="F347">
+        <v>0.0409533587477948</v>
+      </c>
+      <c r="G347">
+        <v>4.1</v>
+      </c>
+      <c r="H347" t="s">
+        <v>17</v>
+      </c>
+      <c r="I347">
+        <v>61</v>
+      </c>
+      <c r="J347">
+        <v>1204.4084</v>
+      </c>
+      <c r="K347">
+        <v>1253.732969284058</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11">
+      <c r="A348" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B348" t="s">
+        <v>18</v>
+      </c>
+      <c r="C348" t="s">
+        <v>29</v>
+      </c>
+      <c r="D348">
+        <v>129.871</v>
+      </c>
+      <c r="E348">
+        <v>141.8099975585938</v>
+      </c>
+      <c r="F348">
+        <v>0.0919296652724144</v>
+      </c>
+      <c r="G348">
+        <v>9.19</v>
+      </c>
+      <c r="H348" t="s">
+        <v>18</v>
+      </c>
+      <c r="I348">
+        <v>51</v>
+      </c>
+      <c r="J348">
+        <v>6623.421</v>
+      </c>
+      <c r="K348">
+        <v>7232.309875488281</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11">
+      <c r="A349" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B349" t="s">
+        <v>19</v>
+      </c>
+      <c r="C349" t="s">
+        <v>30</v>
+      </c>
+      <c r="D349">
+        <v>34.0694</v>
+      </c>
+      <c r="E349">
+        <v>33.55500030517578</v>
+      </c>
+      <c r="F349">
+        <v>-0.0150985839147217</v>
+      </c>
+      <c r="G349">
+        <v>-1.51</v>
+      </c>
+      <c r="H349" t="s">
+        <v>19</v>
+      </c>
+      <c r="I349">
+        <v>34</v>
+      </c>
+      <c r="J349">
+        <v>1158.3596</v>
+      </c>
+      <c r="K349">
+        <v>1140.870010375977</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11">
+      <c r="A350" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B350" t="s">
+        <v>20</v>
+      </c>
+      <c r="C350" t="s">
+        <v>31</v>
+      </c>
+      <c r="D350">
+        <v>69.4158</v>
+      </c>
+      <c r="E350">
+        <v>69.69999694824219</v>
+      </c>
+      <c r="F350">
+        <v>0.0040941247992847</v>
+      </c>
+      <c r="G350">
+        <v>0.41</v>
+      </c>
+      <c r="H350" t="s">
+        <v>20</v>
+      </c>
+      <c r="I350">
+        <v>62</v>
+      </c>
+      <c r="J350">
+        <v>4303.7796</v>
+      </c>
+      <c r="K350">
+        <v>4321.399810791016</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11">
+      <c r="A351" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B351" t="s">
+        <v>21</v>
+      </c>
+      <c r="C351" t="s">
+        <v>32</v>
+      </c>
+      <c r="D351">
+        <v>8.1868</v>
+      </c>
+      <c r="E351">
+        <v>8.27299976348877</v>
+      </c>
+      <c r="F351">
+        <v>0.0105291155871365</v>
+      </c>
+      <c r="G351">
+        <v>1.05</v>
+      </c>
+      <c r="H351" t="s">
+        <v>21</v>
+      </c>
+      <c r="I351">
+        <v>431</v>
+      </c>
+      <c r="J351">
+        <v>3528.5108</v>
+      </c>
+      <c r="K351">
         <v>3565.66289806366</v>
       </c>
     </row>
@@ -15208,7 +15665,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -16519,6 +16976,47 @@
       </c>
       <c r="M32" s="2">
         <v>0.06369755078311989</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.09167165662896171</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.0356995334223779</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.1040420418601946</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.0523412647887928</v>
+      </c>
+      <c r="F33" s="2">
+        <v>-0.0065796194994591</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.4159779843608151</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0.0409533587477948</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0.0919296652724144</v>
+      </c>
+      <c r="J33" s="2">
+        <v>-0.0150985839147217</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0.0040941247992847</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0.0105291155871365</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0.06238606925142931</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -320,16 +320,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$33</c:f>
+              <c:f>grafico_dati!$B$2:$B$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -425,6 +428,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.09167165662896171</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.0946674929756543</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -452,10 +458,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -551,16 +557,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$33</c:f>
+              <c:f>grafico_dati!$C$2:$C$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -656,6 +665,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.0356995334223779</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.0403219452093219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -683,10 +695,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -782,16 +794,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$33</c:f>
+              <c:f>grafico_dati!$D$2:$D$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -887,6 +902,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.1040420418601946</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.1240300069961504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -914,10 +932,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1013,16 +1031,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$33</c:f>
+              <c:f>grafico_dati!$E$2:$E$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1118,6 +1139,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.0523412647887928</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.0748651425725661</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1145,10 +1169,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1244,16 +1268,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$33</c:f>
+              <c:f>grafico_dati!$F$2:$F$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1346,6 +1373,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>-0.0065796194994591</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.0065796380342773</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1373,10 +1403,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1472,16 +1502,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$33</c:f>
+              <c:f>grafico_dati!$G$2:$G$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1577,6 +1610,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.4159779843608151</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.4375156906055324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1604,10 +1640,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1703,16 +1739,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$33</c:f>
+              <c:f>grafico_dati!$H$2:$H$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1808,6 +1847,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.0409533587477948</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.0574137608334219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1835,10 +1877,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1934,16 +1976,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$33</c:f>
+              <c:f>grafico_dati!$I$2:$I$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2036,6 +2081,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.0919296652724144</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.1037876516198044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2063,10 +2111,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2162,16 +2210,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$33</c:f>
+              <c:f>grafico_dati!$J$2:$J$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2267,6 +2318,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>-0.0150985839147217</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.0127504939466734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2294,10 +2348,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2393,16 +2447,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$33</c:f>
+              <c:f>grafico_dati!$K$2:$K$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2498,6 +2555,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.0040941247992847</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.0137461895790587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2525,10 +2585,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2624,16 +2684,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$33</c:f>
+              <c:f>grafico_dati!$L$2:$L$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2729,6 +2792,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.0105291155871365</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.0238432561541044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2760,10 +2826,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$33</c:f>
+              <c:f>grafico_dati!$A$2:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2859,16 +2925,19 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$33</c:f>
+              <c:f>grafico_dati!$M$2:$M$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -2964,6 +3033,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0.06238606925142931</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.07495053702515309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3370,7 +3442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K351"/>
+  <dimension ref="A1:K362"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -15656,6 +15728,391 @@
       </c>
       <c r="K351">
         <v>3565.66289806366</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11">
+      <c r="A352" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B352" t="s">
+        <v>11</v>
+      </c>
+      <c r="C352" t="s">
+        <v>22</v>
+      </c>
+      <c r="D352">
+        <v>50.07</v>
+      </c>
+      <c r="E352">
+        <v>54.81000137329102</v>
+      </c>
+      <c r="F352">
+        <v>0.0946674929756543</v>
+      </c>
+      <c r="G352">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="H352" t="s">
+        <v>11</v>
+      </c>
+      <c r="I352">
+        <v>23</v>
+      </c>
+      <c r="J352">
+        <v>1151.61</v>
+      </c>
+      <c r="K352">
+        <v>1260.630031585693</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11">
+      <c r="A353" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B353" t="s">
+        <v>12</v>
+      </c>
+      <c r="C353" t="s">
+        <v>23</v>
+      </c>
+      <c r="D353">
+        <v>242.3</v>
+      </c>
+      <c r="E353">
+        <v>252.0700073242188</v>
+      </c>
+      <c r="F353">
+        <v>0.0403219452093219</v>
+      </c>
+      <c r="G353">
+        <v>4.03</v>
+      </c>
+      <c r="H353" t="s">
+        <v>12</v>
+      </c>
+      <c r="I353">
+        <v>5</v>
+      </c>
+      <c r="J353">
+        <v>1211.5</v>
+      </c>
+      <c r="K353">
+        <v>1260.350036621094</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11">
+      <c r="A354" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B354" t="s">
+        <v>13</v>
+      </c>
+      <c r="C354" t="s">
+        <v>24</v>
+      </c>
+      <c r="D354">
+        <v>38.273</v>
+      </c>
+      <c r="E354">
+        <v>43.02000045776367</v>
+      </c>
+      <c r="F354">
+        <v>0.1240300069961504</v>
+      </c>
+      <c r="G354">
+        <v>12.4</v>
+      </c>
+      <c r="H354" t="s">
+        <v>13</v>
+      </c>
+      <c r="I354">
+        <v>54</v>
+      </c>
+      <c r="J354">
+        <v>2066.742</v>
+      </c>
+      <c r="K354">
+        <v>2323.080024719238</v>
+      </c>
+    </row>
+    <row r="355" spans="1:11">
+      <c r="A355" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B355" t="s">
+        <v>14</v>
+      </c>
+      <c r="C355" t="s">
+        <v>25</v>
+      </c>
+      <c r="D355">
+        <v>6.5264</v>
+      </c>
+      <c r="E355">
+        <v>7.014999866485596</v>
+      </c>
+      <c r="F355">
+        <v>0.0748651425725661</v>
+      </c>
+      <c r="G355">
+        <v>7.49</v>
+      </c>
+      <c r="H355" t="s">
+        <v>14</v>
+      </c>
+      <c r="I355">
+        <v>276</v>
+      </c>
+      <c r="J355">
+        <v>1801.2864</v>
+      </c>
+      <c r="K355">
+        <v>1936.139963150024</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11">
+      <c r="A356" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B356" t="s">
+        <v>15</v>
+      </c>
+      <c r="C356" t="s">
+        <v>26</v>
+      </c>
+      <c r="D356">
+        <v>197.58</v>
+      </c>
+      <c r="E356">
+        <v>198.8800048828125</v>
+      </c>
+      <c r="F356">
+        <v>0.0065796380342773</v>
+      </c>
+      <c r="G356">
+        <v>0.66</v>
+      </c>
+      <c r="H356" t="s">
+        <v>15</v>
+      </c>
+      <c r="I356">
+        <v>4</v>
+      </c>
+      <c r="J356">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K356">
+        <v>795.52001953125</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11">
+      <c r="A357" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B357" t="s">
+        <v>16</v>
+      </c>
+      <c r="C357" t="s">
+        <v>27</v>
+      </c>
+      <c r="D357">
+        <v>79.86</v>
+      </c>
+      <c r="E357">
+        <v>114.8000030517578</v>
+      </c>
+      <c r="F357">
+        <v>0.4375156906055324</v>
+      </c>
+      <c r="G357">
+        <v>43.75</v>
+      </c>
+      <c r="H357" t="s">
+        <v>16</v>
+      </c>
+      <c r="I357">
+        <v>12</v>
+      </c>
+      <c r="J357">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K357">
+        <v>1377.600036621094</v>
+      </c>
+    </row>
+    <row r="358" spans="1:11">
+      <c r="A358" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B358" t="s">
+        <v>17</v>
+      </c>
+      <c r="C358" t="s">
+        <v>28</v>
+      </c>
+      <c r="D358">
+        <v>19.7444</v>
+      </c>
+      <c r="E358">
+        <v>20.87800025939941</v>
+      </c>
+      <c r="F358">
+        <v>0.0574137608334219</v>
+      </c>
+      <c r="G358">
+        <v>5.74</v>
+      </c>
+      <c r="H358" t="s">
+        <v>17</v>
+      </c>
+      <c r="I358">
+        <v>61</v>
+      </c>
+      <c r="J358">
+        <v>1204.4084</v>
+      </c>
+      <c r="K358">
+        <v>1273.558015823364</v>
+      </c>
+    </row>
+    <row r="359" spans="1:11">
+      <c r="A359" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B359" t="s">
+        <v>18</v>
+      </c>
+      <c r="C359" t="s">
+        <v>29</v>
+      </c>
+      <c r="D359">
+        <v>129.871</v>
+      </c>
+      <c r="E359">
+        <v>143.3500061035156</v>
+      </c>
+      <c r="F359">
+        <v>0.1037876516198044</v>
+      </c>
+      <c r="G359">
+        <v>10.38</v>
+      </c>
+      <c r="H359" t="s">
+        <v>18</v>
+      </c>
+      <c r="I359">
+        <v>51</v>
+      </c>
+      <c r="J359">
+        <v>6623.421</v>
+      </c>
+      <c r="K359">
+        <v>7310.850311279297</v>
+      </c>
+    </row>
+    <row r="360" spans="1:11">
+      <c r="A360" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B360" t="s">
+        <v>19</v>
+      </c>
+      <c r="C360" t="s">
+        <v>30</v>
+      </c>
+      <c r="D360">
+        <v>34.0694</v>
+      </c>
+      <c r="E360">
+        <v>33.6349983215332</v>
+      </c>
+      <c r="F360">
+        <v>-0.0127504939466734</v>
+      </c>
+      <c r="G360">
+        <v>-1.28</v>
+      </c>
+      <c r="H360" t="s">
+        <v>19</v>
+      </c>
+      <c r="I360">
+        <v>34</v>
+      </c>
+      <c r="J360">
+        <v>1158.3596</v>
+      </c>
+      <c r="K360">
+        <v>1143.589942932129</v>
+      </c>
+    </row>
+    <row r="361" spans="1:11">
+      <c r="A361" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B361" t="s">
+        <v>20</v>
+      </c>
+      <c r="C361" t="s">
+        <v>31</v>
+      </c>
+      <c r="D361">
+        <v>69.4158</v>
+      </c>
+      <c r="E361">
+        <v>70.37000274658203</v>
+      </c>
+      <c r="F361">
+        <v>0.0137461895790587</v>
+      </c>
+      <c r="G361">
+        <v>1.37</v>
+      </c>
+      <c r="H361" t="s">
+        <v>20</v>
+      </c>
+      <c r="I361">
+        <v>62</v>
+      </c>
+      <c r="J361">
+        <v>4303.7796</v>
+      </c>
+      <c r="K361">
+        <v>4362.940170288086</v>
+      </c>
+    </row>
+    <row r="362" spans="1:11">
+      <c r="A362" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B362" t="s">
+        <v>21</v>
+      </c>
+      <c r="C362" t="s">
+        <v>32</v>
+      </c>
+      <c r="D362">
+        <v>8.1868</v>
+      </c>
+      <c r="E362">
+        <v>8.381999969482422</v>
+      </c>
+      <c r="F362">
+        <v>0.0238432561541044</v>
+      </c>
+      <c r="G362">
+        <v>2.38</v>
+      </c>
+      <c r="H362" t="s">
+        <v>21</v>
+      </c>
+      <c r="I362">
+        <v>431</v>
+      </c>
+      <c r="J362">
+        <v>3528.5108</v>
+      </c>
+      <c r="K362">
+        <v>3612.641986846924</v>
       </c>
     </row>
   </sheetData>
@@ -15665,7 +16122,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -17017,6 +17474,47 @@
       </c>
       <c r="M33" s="2">
         <v>0.06238606925142931</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.0946674929756543</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.0403219452093219</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0.1240300069961504</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.0748651425725661</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.0065796380342773</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0.4375156906055324</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0.0574137608334219</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0.1037876516198044</v>
+      </c>
+      <c r="J34" s="2">
+        <v>-0.0127504939466734</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0.0137461895790587</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0.0238432561541044</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0.07495053702515309</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -323,16 +323,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$34</c:f>
+              <c:f>grafico_dati!$B$2:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -430,6 +433,9 @@
                   <c:v>0.09167165662896171</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>0.0946674929756543</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>0.0946674929756543</c:v>
                 </c:pt>
               </c:numCache>
@@ -458,10 +464,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -560,16 +566,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$34</c:f>
+              <c:f>grafico_dati!$C$2:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -668,6 +677,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.0403219452093219</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.047379276843982</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -695,10 +707,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -797,16 +809,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$34</c:f>
+              <c:f>grafico_dati!$D$2:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -905,6 +920,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.1240300069961504</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.1266427751126058</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -932,10 +950,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1034,16 +1052,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$34</c:f>
+              <c:f>grafico_dati!$E$2:$E$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1142,6 +1163,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.0748651425725661</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.08084087717851671</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1169,10 +1193,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1271,16 +1295,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$34</c:f>
+              <c:f>grafico_dati!$F$2:$F$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1376,6 +1403,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.0065796380342773</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.0080979485564391</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1403,10 +1433,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1505,16 +1535,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$34</c:f>
+              <c:f>grafico_dati!$G$2:$G$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1613,6 +1646,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.4375156906055324</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.4412722072892698</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1640,10 +1676,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1742,16 +1778,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$34</c:f>
+              <c:f>grafico_dati!$H$2:$H$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1850,6 +1889,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.0574137608334219</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.052399633749989</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1877,10 +1919,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1979,16 +2021,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$34</c:f>
+              <c:f>grafico_dati!$I$2:$I$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2084,6 +2129,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.1037876516198044</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.1083305929838549</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2111,10 +2159,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2213,16 +2261,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$34</c:f>
+              <c:f>grafico_dati!$J$2:$J$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2321,6 +2372,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>-0.0127504939466734</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.0102555013970564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2348,10 +2402,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2450,16 +2504,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$34</c:f>
+              <c:f>grafico_dati!$K$2:$K$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2558,6 +2615,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.0137461895790587</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.0125936878279488</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2585,10 +2645,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2687,16 +2747,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$34</c:f>
+              <c:f>grafico_dati!$L$2:$L$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2795,6 +2858,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.0238432561541044</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.0207896065559374</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2826,10 +2892,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$34</c:f>
+              <c:f>grafico_dati!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2928,16 +2994,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$34</c:f>
+              <c:f>grafico_dati!$M$2:$M$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3036,6 +3105,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.07495053702515309</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.07659257522140828</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3442,7 +3514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K362"/>
+  <dimension ref="A1:K373"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -16113,6 +16185,391 @@
       </c>
       <c r="K362">
         <v>3612.641986846924</v>
+      </c>
+    </row>
+    <row r="363" spans="1:11">
+      <c r="A363" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B363" t="s">
+        <v>11</v>
+      </c>
+      <c r="C363" t="s">
+        <v>22</v>
+      </c>
+      <c r="D363">
+        <v>50.07</v>
+      </c>
+      <c r="E363">
+        <v>54.81000137329102</v>
+      </c>
+      <c r="F363">
+        <v>0.0946674929756543</v>
+      </c>
+      <c r="G363">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="H363" t="s">
+        <v>11</v>
+      </c>
+      <c r="I363">
+        <v>23</v>
+      </c>
+      <c r="J363">
+        <v>1151.61</v>
+      </c>
+      <c r="K363">
+        <v>1260.630031585693</v>
+      </c>
+    </row>
+    <row r="364" spans="1:11">
+      <c r="A364" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B364" t="s">
+        <v>12</v>
+      </c>
+      <c r="C364" t="s">
+        <v>23</v>
+      </c>
+      <c r="D364">
+        <v>242.3</v>
+      </c>
+      <c r="E364">
+        <v>253.7799987792969</v>
+      </c>
+      <c r="F364">
+        <v>0.047379276843982</v>
+      </c>
+      <c r="G364">
+        <v>4.74</v>
+      </c>
+      <c r="H364" t="s">
+        <v>12</v>
+      </c>
+      <c r="I364">
+        <v>5</v>
+      </c>
+      <c r="J364">
+        <v>1211.5</v>
+      </c>
+      <c r="K364">
+        <v>1268.899993896484</v>
+      </c>
+    </row>
+    <row r="365" spans="1:11">
+      <c r="A365" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B365" t="s">
+        <v>13</v>
+      </c>
+      <c r="C365" t="s">
+        <v>24</v>
+      </c>
+      <c r="D365">
+        <v>38.273</v>
+      </c>
+      <c r="E365">
+        <v>43.11999893188477</v>
+      </c>
+      <c r="F365">
+        <v>0.1266427751126058</v>
+      </c>
+      <c r="G365">
+        <v>12.66</v>
+      </c>
+      <c r="H365" t="s">
+        <v>13</v>
+      </c>
+      <c r="I365">
+        <v>54</v>
+      </c>
+      <c r="J365">
+        <v>2066.742</v>
+      </c>
+      <c r="K365">
+        <v>2328.479942321777</v>
+      </c>
+    </row>
+    <row r="366" spans="1:11">
+      <c r="A366" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B366" t="s">
+        <v>14</v>
+      </c>
+      <c r="C366" t="s">
+        <v>25</v>
+      </c>
+      <c r="D366">
+        <v>6.5264</v>
+      </c>
+      <c r="E366">
+        <v>7.053999900817871</v>
+      </c>
+      <c r="F366">
+        <v>0.08084087717851671</v>
+      </c>
+      <c r="G366">
+        <v>8.08</v>
+      </c>
+      <c r="H366" t="s">
+        <v>14</v>
+      </c>
+      <c r="I366">
+        <v>276</v>
+      </c>
+      <c r="J366">
+        <v>1801.2864</v>
+      </c>
+      <c r="K366">
+        <v>1946.903972625732</v>
+      </c>
+    </row>
+    <row r="367" spans="1:11">
+      <c r="A367" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B367" t="s">
+        <v>15</v>
+      </c>
+      <c r="C367" t="s">
+        <v>26</v>
+      </c>
+      <c r="D367">
+        <v>197.58</v>
+      </c>
+      <c r="E367">
+        <v>199.1799926757812</v>
+      </c>
+      <c r="F367">
+        <v>0.0080979485564391</v>
+      </c>
+      <c r="G367">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H367" t="s">
+        <v>15</v>
+      </c>
+      <c r="I367">
+        <v>4</v>
+      </c>
+      <c r="J367">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K367">
+        <v>796.719970703125</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11">
+      <c r="A368" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B368" t="s">
+        <v>16</v>
+      </c>
+      <c r="C368" t="s">
+        <v>27</v>
+      </c>
+      <c r="D368">
+        <v>79.86</v>
+      </c>
+      <c r="E368">
+        <v>115.0999984741211</v>
+      </c>
+      <c r="F368">
+        <v>0.4412722072892698</v>
+      </c>
+      <c r="G368">
+        <v>44.13</v>
+      </c>
+      <c r="H368" t="s">
+        <v>16</v>
+      </c>
+      <c r="I368">
+        <v>12</v>
+      </c>
+      <c r="J368">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K368">
+        <v>1381.199981689453</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11">
+      <c r="A369" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B369" t="s">
+        <v>17</v>
+      </c>
+      <c r="C369" t="s">
+        <v>28</v>
+      </c>
+      <c r="D369">
+        <v>19.7444</v>
+      </c>
+      <c r="E369">
+        <v>20.77899932861328</v>
+      </c>
+      <c r="F369">
+        <v>0.052399633749989</v>
+      </c>
+      <c r="G369">
+        <v>5.24</v>
+      </c>
+      <c r="H369" t="s">
+        <v>17</v>
+      </c>
+      <c r="I369">
+        <v>61</v>
+      </c>
+      <c r="J369">
+        <v>1204.4084</v>
+      </c>
+      <c r="K369">
+        <v>1267.51895904541</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11">
+      <c r="A370" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B370" t="s">
+        <v>18</v>
+      </c>
+      <c r="C370" t="s">
+        <v>29</v>
+      </c>
+      <c r="D370">
+        <v>129.871</v>
+      </c>
+      <c r="E370">
+        <v>143.9400024414062</v>
+      </c>
+      <c r="F370">
+        <v>0.1083305929838549</v>
+      </c>
+      <c r="G370">
+        <v>10.83</v>
+      </c>
+      <c r="H370" t="s">
+        <v>18</v>
+      </c>
+      <c r="I370">
+        <v>51</v>
+      </c>
+      <c r="J370">
+        <v>6623.421</v>
+      </c>
+      <c r="K370">
+        <v>7340.940124511719</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11">
+      <c r="A371" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B371" t="s">
+        <v>19</v>
+      </c>
+      <c r="C371" t="s">
+        <v>30</v>
+      </c>
+      <c r="D371">
+        <v>34.0694</v>
+      </c>
+      <c r="E371">
+        <v>33.72000122070312</v>
+      </c>
+      <c r="F371">
+        <v>-0.0102555013970564</v>
+      </c>
+      <c r="G371">
+        <v>-1.03</v>
+      </c>
+      <c r="H371" t="s">
+        <v>19</v>
+      </c>
+      <c r="I371">
+        <v>34</v>
+      </c>
+      <c r="J371">
+        <v>1158.3596</v>
+      </c>
+      <c r="K371">
+        <v>1146.480041503906</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11">
+      <c r="A372" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B372" t="s">
+        <v>20</v>
+      </c>
+      <c r="C372" t="s">
+        <v>31</v>
+      </c>
+      <c r="D372">
+        <v>69.4158</v>
+      </c>
+      <c r="E372">
+        <v>70.29000091552734</v>
+      </c>
+      <c r="F372">
+        <v>0.0125936878279488</v>
+      </c>
+      <c r="G372">
+        <v>1.26</v>
+      </c>
+      <c r="H372" t="s">
+        <v>20</v>
+      </c>
+      <c r="I372">
+        <v>62</v>
+      </c>
+      <c r="J372">
+        <v>4303.7796</v>
+      </c>
+      <c r="K372">
+        <v>4357.980056762695</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11">
+      <c r="A373" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B373" t="s">
+        <v>21</v>
+      </c>
+      <c r="C373" t="s">
+        <v>32</v>
+      </c>
+      <c r="D373">
+        <v>8.1868</v>
+      </c>
+      <c r="E373">
+        <v>8.357000350952148</v>
+      </c>
+      <c r="F373">
+        <v>0.0207896065559374</v>
+      </c>
+      <c r="G373">
+        <v>2.08</v>
+      </c>
+      <c r="H373" t="s">
+        <v>21</v>
+      </c>
+      <c r="I373">
+        <v>431</v>
+      </c>
+      <c r="J373">
+        <v>3528.5108</v>
+      </c>
+      <c r="K373">
+        <v>3601.867151260376</v>
       </c>
     </row>
   </sheetData>
@@ -16122,7 +16579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -17515,6 +17972,47 @@
       </c>
       <c r="M34" s="2">
         <v>0.07495053702515309</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.0946674929756543</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.047379276843982</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.1266427751126058</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.08084087717851671</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.0080979485564391</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.4412722072892698</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0.052399633749989</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.1083305929838549</v>
+      </c>
+      <c r="J35" s="2">
+        <v>-0.0102555013970564</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0.0125936878279488</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0.0207896065559374</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0.07659257522140828</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -326,16 +326,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$35</c:f>
+              <c:f>grafico_dati!$B$2:$B$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -437,6 +440,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.0946674929756543</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.0876772335624656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -464,10 +470,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -569,16 +575,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$35</c:f>
+              <c:f>grafico_dati!$C$2:$C$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -680,6 +689,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.047379276843982</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.0515063919904947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -707,10 +719,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -812,16 +824,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$35</c:f>
+              <c:f>grafico_dati!$D$2:$D$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -923,6 +938,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.1266427751126058</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.1356569945545915</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -950,10 +968,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1055,16 +1073,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$35</c:f>
+              <c:f>grafico_dati!$E$2:$E$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1166,6 +1187,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.08084087717851671</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.0845182748015063</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1193,10 +1217,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1298,16 +1322,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$35</c:f>
+              <c:f>grafico_dati!$F$2:$F$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1406,6 +1433,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.0080979485564391</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.0108310619531486</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,10 +1463,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1538,16 +1568,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$35</c:f>
+              <c:f>grafico_dati!$G$2:$G$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1649,6 +1682,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.4412722072892698</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.438517371067092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1676,10 +1712,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1781,16 +1817,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$35</c:f>
+              <c:f>grafico_dati!$H$2:$H$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1892,6 +1931,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.052399633749989</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.0587812588199949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1919,10 +1961,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2024,16 +2066,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$35</c:f>
+              <c:f>grafico_dati!$I$2:$I$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2132,6 +2177,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.1083305929838549</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.1145675323975328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2159,10 +2207,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2264,16 +2312,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$35</c:f>
+              <c:f>grafico_dati!$J$2:$J$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2375,6 +2426,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>-0.0102555013970564</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.0155388437857038</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2402,10 +2456,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2507,16 +2561,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$35</c:f>
+              <c:f>grafico_dati!$K$2:$K$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2618,6 +2675,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.0125936878279488</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.0196525687134179</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2645,10 +2705,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2750,16 +2810,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$35</c:f>
+              <c:f>grafico_dati!$L$2:$L$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2861,6 +2924,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.0207896065559374</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.0259197937957051</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2892,10 +2958,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$35</c:f>
+              <c:f>grafico_dati!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2997,16 +3063,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$35</c:f>
+              <c:f>grafico_dati!$M$2:$M$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3108,6 +3177,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.07659257522140828</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.08115264620024942</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3514,7 +3586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K373"/>
+  <dimension ref="A1:K384"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -16570,6 +16642,391 @@
       </c>
       <c r="K373">
         <v>3601.867151260376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11">
+      <c r="A374" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B374" t="s">
+        <v>11</v>
+      </c>
+      <c r="C374" t="s">
+        <v>22</v>
+      </c>
+      <c r="D374">
+        <v>50.07</v>
+      </c>
+      <c r="E374">
+        <v>54.45999908447266</v>
+      </c>
+      <c r="F374">
+        <v>0.0876772335624656</v>
+      </c>
+      <c r="G374">
+        <v>8.77</v>
+      </c>
+      <c r="H374" t="s">
+        <v>11</v>
+      </c>
+      <c r="I374">
+        <v>23</v>
+      </c>
+      <c r="J374">
+        <v>1151.61</v>
+      </c>
+      <c r="K374">
+        <v>1252.579978942871</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11">
+      <c r="A375" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B375" t="s">
+        <v>12</v>
+      </c>
+      <c r="C375" t="s">
+        <v>23</v>
+      </c>
+      <c r="D375">
+        <v>242.3</v>
+      </c>
+      <c r="E375">
+        <v>254.7799987792969</v>
+      </c>
+      <c r="F375">
+        <v>0.0515063919904947</v>
+      </c>
+      <c r="G375">
+        <v>5.15</v>
+      </c>
+      <c r="H375" t="s">
+        <v>12</v>
+      </c>
+      <c r="I375">
+        <v>5</v>
+      </c>
+      <c r="J375">
+        <v>1211.5</v>
+      </c>
+      <c r="K375">
+        <v>1273.899993896484</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11">
+      <c r="A376" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B376" t="s">
+        <v>13</v>
+      </c>
+      <c r="C376" t="s">
+        <v>24</v>
+      </c>
+      <c r="D376">
+        <v>38.273</v>
+      </c>
+      <c r="E376">
+        <v>43.46500015258789</v>
+      </c>
+      <c r="F376">
+        <v>0.1356569945545915</v>
+      </c>
+      <c r="G376">
+        <v>13.57</v>
+      </c>
+      <c r="H376" t="s">
+        <v>13</v>
+      </c>
+      <c r="I376">
+        <v>54</v>
+      </c>
+      <c r="J376">
+        <v>2066.742</v>
+      </c>
+      <c r="K376">
+        <v>2347.110008239746</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11">
+      <c r="A377" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B377" t="s">
+        <v>14</v>
+      </c>
+      <c r="C377" t="s">
+        <v>25</v>
+      </c>
+      <c r="D377">
+        <v>6.5264</v>
+      </c>
+      <c r="E377">
+        <v>7.078000068664551</v>
+      </c>
+      <c r="F377">
+        <v>0.0845182748015063</v>
+      </c>
+      <c r="G377">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H377" t="s">
+        <v>14</v>
+      </c>
+      <c r="I377">
+        <v>276</v>
+      </c>
+      <c r="J377">
+        <v>1801.2864</v>
+      </c>
+      <c r="K377">
+        <v>1953.528018951416</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11">
+      <c r="A378" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B378" t="s">
+        <v>15</v>
+      </c>
+      <c r="C378" t="s">
+        <v>26</v>
+      </c>
+      <c r="D378">
+        <v>197.58</v>
+      </c>
+      <c r="E378">
+        <v>199.7200012207031</v>
+      </c>
+      <c r="F378">
+        <v>0.0108310619531486</v>
+      </c>
+      <c r="G378">
+        <v>1.08</v>
+      </c>
+      <c r="H378" t="s">
+        <v>15</v>
+      </c>
+      <c r="I378">
+        <v>4</v>
+      </c>
+      <c r="J378">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K378">
+        <v>798.8800048828125</v>
+      </c>
+    </row>
+    <row r="379" spans="1:11">
+      <c r="A379" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B379" t="s">
+        <v>16</v>
+      </c>
+      <c r="C379" t="s">
+        <v>27</v>
+      </c>
+      <c r="D379">
+        <v>79.86</v>
+      </c>
+      <c r="E379">
+        <v>114.879997253418</v>
+      </c>
+      <c r="F379">
+        <v>0.438517371067092</v>
+      </c>
+      <c r="G379">
+        <v>43.85</v>
+      </c>
+      <c r="H379" t="s">
+        <v>16</v>
+      </c>
+      <c r="I379">
+        <v>12</v>
+      </c>
+      <c r="J379">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K379">
+        <v>1378.559967041015</v>
+      </c>
+    </row>
+    <row r="380" spans="1:11">
+      <c r="A380" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B380" t="s">
+        <v>17</v>
+      </c>
+      <c r="C380" t="s">
+        <v>28</v>
+      </c>
+      <c r="D380">
+        <v>19.7444</v>
+      </c>
+      <c r="E380">
+        <v>20.90500068664551</v>
+      </c>
+      <c r="F380">
+        <v>0.0587812588199949</v>
+      </c>
+      <c r="G380">
+        <v>5.88</v>
+      </c>
+      <c r="H380" t="s">
+        <v>17</v>
+      </c>
+      <c r="I380">
+        <v>61</v>
+      </c>
+      <c r="J380">
+        <v>1204.4084</v>
+      </c>
+      <c r="K380">
+        <v>1275.205041885376</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11">
+      <c r="A381" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B381" t="s">
+        <v>18</v>
+      </c>
+      <c r="C381" t="s">
+        <v>29</v>
+      </c>
+      <c r="D381">
+        <v>129.871</v>
+      </c>
+      <c r="E381">
+        <v>144.75</v>
+      </c>
+      <c r="F381">
+        <v>0.1145675323975328</v>
+      </c>
+      <c r="G381">
+        <v>11.46</v>
+      </c>
+      <c r="H381" t="s">
+        <v>18</v>
+      </c>
+      <c r="I381">
+        <v>51</v>
+      </c>
+      <c r="J381">
+        <v>6623.421</v>
+      </c>
+      <c r="K381">
+        <v>7382.25</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11">
+      <c r="A382" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B382" t="s">
+        <v>19</v>
+      </c>
+      <c r="C382" t="s">
+        <v>30</v>
+      </c>
+      <c r="D382">
+        <v>34.0694</v>
+      </c>
+      <c r="E382">
+        <v>33.54000091552734</v>
+      </c>
+      <c r="F382">
+        <v>-0.0155388437857038</v>
+      </c>
+      <c r="G382">
+        <v>-1.55</v>
+      </c>
+      <c r="H382" t="s">
+        <v>19</v>
+      </c>
+      <c r="I382">
+        <v>34</v>
+      </c>
+      <c r="J382">
+        <v>1158.3596</v>
+      </c>
+      <c r="K382">
+        <v>1140.36003112793</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11">
+      <c r="A383" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B383" t="s">
+        <v>20</v>
+      </c>
+      <c r="C383" t="s">
+        <v>31</v>
+      </c>
+      <c r="D383">
+        <v>69.4158</v>
+      </c>
+      <c r="E383">
+        <v>70.77999877929688</v>
+      </c>
+      <c r="F383">
+        <v>0.0196525687134179</v>
+      </c>
+      <c r="G383">
+        <v>1.97</v>
+      </c>
+      <c r="H383" t="s">
+        <v>20</v>
+      </c>
+      <c r="I383">
+        <v>62</v>
+      </c>
+      <c r="J383">
+        <v>4303.7796</v>
+      </c>
+      <c r="K383">
+        <v>4388.359924316406</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11">
+      <c r="A384" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B384" t="s">
+        <v>21</v>
+      </c>
+      <c r="C384" t="s">
+        <v>32</v>
+      </c>
+      <c r="D384">
+        <v>8.1868</v>
+      </c>
+      <c r="E384">
+        <v>8.39900016784668</v>
+      </c>
+      <c r="F384">
+        <v>0.0259197937957051</v>
+      </c>
+      <c r="G384">
+        <v>2.59</v>
+      </c>
+      <c r="H384" t="s">
+        <v>21</v>
+      </c>
+      <c r="I384">
+        <v>431</v>
+      </c>
+      <c r="J384">
+        <v>3528.5108</v>
+      </c>
+      <c r="K384">
+        <v>3619.969072341919</v>
       </c>
     </row>
   </sheetData>
@@ -16579,7 +17036,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -18013,6 +18470,47 @@
       </c>
       <c r="M35" s="2">
         <v>0.07659257522140828</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.0876772335624656</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.0515063919904947</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.1356569945545915</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.0845182748015063</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.0108310619531486</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0.438517371067092</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0.0587812588199949</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0.1145675323975328</v>
+      </c>
+      <c r="J36" s="2">
+        <v>-0.0155388437857038</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0.0196525687134179</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0.0259197937957051</v>
+      </c>
+      <c r="M36" s="2">
+        <v>0.08115264620024942</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -329,16 +329,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$36</c:f>
+              <c:f>grafico_dati!$B$2:$B$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -443,6 +446,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.0876772335624656</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.09886160291119769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -470,10 +476,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -578,16 +584,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$36</c:f>
+              <c:f>grafico_dati!$C$2:$C$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -692,6 +701,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.0515063919904947</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.0553033303683128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -719,10 +731,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -827,16 +839,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$36</c:f>
+              <c:f>grafico_dati!$D$2:$D$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -941,6 +956,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.1356569945545915</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.159433543228908</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -968,10 +986,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1076,16 +1094,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$36</c:f>
+              <c:f>grafico_dati!$E$2:$E$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1190,6 +1211,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.0845182748015063</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.1078082892672049</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1217,10 +1241,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1325,16 +1349,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$36</c:f>
+              <c:f>grafico_dati!$F$2:$F$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1436,6 +1463,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.0108310619531486</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.0347707103362797</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1463,10 +1493,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1571,16 +1601,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$36</c:f>
+              <c:f>grafico_dati!$G$2:$G$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1685,6 +1718,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.438517371067092</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.4693212664399027</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1712,10 +1748,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1820,16 +1856,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$36</c:f>
+              <c:f>grafico_dati!$H$2:$H$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1934,6 +1973,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.0587812588199949</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.0715950318087621</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1961,10 +2003,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2069,16 +2111,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$36</c:f>
+              <c:f>grafico_dati!$I$2:$I$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2180,6 +2225,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.1145675323975328</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.1279654849286142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2207,10 +2255,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2315,16 +2363,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$36</c:f>
+              <c:f>grafico_dati!$J$2:$J$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2429,6 +2480,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>-0.0155388437857038</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.0079426157369337</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2456,10 +2510,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2564,16 +2618,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$36</c:f>
+              <c:f>grafico_dati!$K$2:$K$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2678,6 +2735,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.0196525687134179</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.0300248646561733</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2705,10 +2765,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2813,16 +2873,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$36</c:f>
+              <c:f>grafico_dati!$L$2:$L$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2927,6 +2990,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.0259197937957051</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.0454634307982104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2958,10 +3024,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$36</c:f>
+              <c:f>grafico_dati!$A$2:$A$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3066,16 +3132,19 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$36</c:f>
+              <c:f>grafico_dati!$M$2:$M$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3180,6 +3249,9 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>0.08115264620024942</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.09736286772558467</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3586,7 +3658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K384"/>
+  <dimension ref="A1:K395"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -17027,6 +17099,391 @@
       </c>
       <c r="K384">
         <v>3619.969072341919</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11">
+      <c r="A385" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B385" t="s">
+        <v>11</v>
+      </c>
+      <c r="C385" t="s">
+        <v>22</v>
+      </c>
+      <c r="D385">
+        <v>50.07</v>
+      </c>
+      <c r="E385">
+        <v>55.02000045776367</v>
+      </c>
+      <c r="F385">
+        <v>0.09886160291119769</v>
+      </c>
+      <c r="G385">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H385" t="s">
+        <v>11</v>
+      </c>
+      <c r="I385">
+        <v>23</v>
+      </c>
+      <c r="J385">
+        <v>1151.61</v>
+      </c>
+      <c r="K385">
+        <v>1265.460010528564</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11">
+      <c r="A386" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B386" t="s">
+        <v>12</v>
+      </c>
+      <c r="C386" t="s">
+        <v>23</v>
+      </c>
+      <c r="D386">
+        <v>242.3</v>
+      </c>
+      <c r="E386">
+        <v>255.6999969482422</v>
+      </c>
+      <c r="F386">
+        <v>0.0553033303683128</v>
+      </c>
+      <c r="G386">
+        <v>5.53</v>
+      </c>
+      <c r="H386" t="s">
+        <v>12</v>
+      </c>
+      <c r="I386">
+        <v>5</v>
+      </c>
+      <c r="J386">
+        <v>1211.5</v>
+      </c>
+      <c r="K386">
+        <v>1278.499984741211</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11">
+      <c r="A387" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B387" t="s">
+        <v>13</v>
+      </c>
+      <c r="C387" t="s">
+        <v>24</v>
+      </c>
+      <c r="D387">
+        <v>38.273</v>
+      </c>
+      <c r="E387">
+        <v>44.375</v>
+      </c>
+      <c r="F387">
+        <v>0.159433543228908</v>
+      </c>
+      <c r="G387">
+        <v>15.94</v>
+      </c>
+      <c r="H387" t="s">
+        <v>13</v>
+      </c>
+      <c r="I387">
+        <v>54</v>
+      </c>
+      <c r="J387">
+        <v>2066.742</v>
+      </c>
+      <c r="K387">
+        <v>2396.25</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11">
+      <c r="A388" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B388" t="s">
+        <v>14</v>
+      </c>
+      <c r="C388" t="s">
+        <v>25</v>
+      </c>
+      <c r="D388">
+        <v>6.5264</v>
+      </c>
+      <c r="E388">
+        <v>7.230000019073486</v>
+      </c>
+      <c r="F388">
+        <v>0.1078082892672049</v>
+      </c>
+      <c r="G388">
+        <v>10.78</v>
+      </c>
+      <c r="H388" t="s">
+        <v>14</v>
+      </c>
+      <c r="I388">
+        <v>276</v>
+      </c>
+      <c r="J388">
+        <v>1801.2864</v>
+      </c>
+      <c r="K388">
+        <v>1995.480005264282</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11">
+      <c r="A389" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B389" t="s">
+        <v>15</v>
+      </c>
+      <c r="C389" t="s">
+        <v>26</v>
+      </c>
+      <c r="D389">
+        <v>197.58</v>
+      </c>
+      <c r="E389">
+        <v>204.4499969482422</v>
+      </c>
+      <c r="F389">
+        <v>0.0347707103362797</v>
+      </c>
+      <c r="G389">
+        <v>3.48</v>
+      </c>
+      <c r="H389" t="s">
+        <v>15</v>
+      </c>
+      <c r="I389">
+        <v>4</v>
+      </c>
+      <c r="J389">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K389">
+        <v>817.7999877929688</v>
+      </c>
+    </row>
+    <row r="390" spans="1:11">
+      <c r="A390" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B390" t="s">
+        <v>16</v>
+      </c>
+      <c r="C390" t="s">
+        <v>27</v>
+      </c>
+      <c r="D390">
+        <v>79.86</v>
+      </c>
+      <c r="E390">
+        <v>117.3399963378906</v>
+      </c>
+      <c r="F390">
+        <v>0.4693212664399027</v>
+      </c>
+      <c r="G390">
+        <v>46.93</v>
+      </c>
+      <c r="H390" t="s">
+        <v>16</v>
+      </c>
+      <c r="I390">
+        <v>12</v>
+      </c>
+      <c r="J390">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K390">
+        <v>1408.079956054688</v>
+      </c>
+    </row>
+    <row r="391" spans="1:11">
+      <c r="A391" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B391" t="s">
+        <v>17</v>
+      </c>
+      <c r="C391" t="s">
+        <v>28</v>
+      </c>
+      <c r="D391">
+        <v>19.7444</v>
+      </c>
+      <c r="E391">
+        <v>21.15800094604492</v>
+      </c>
+      <c r="F391">
+        <v>0.0715950318087621</v>
+      </c>
+      <c r="G391">
+        <v>7.16</v>
+      </c>
+      <c r="H391" t="s">
+        <v>17</v>
+      </c>
+      <c r="I391">
+        <v>61</v>
+      </c>
+      <c r="J391">
+        <v>1204.4084</v>
+      </c>
+      <c r="K391">
+        <v>1290.63805770874</v>
+      </c>
+    </row>
+    <row r="392" spans="1:11">
+      <c r="A392" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B392" t="s">
+        <v>18</v>
+      </c>
+      <c r="C392" t="s">
+        <v>29</v>
+      </c>
+      <c r="D392">
+        <v>129.871</v>
+      </c>
+      <c r="E392">
+        <v>146.4900054931641</v>
+      </c>
+      <c r="F392">
+        <v>0.1279654849286142</v>
+      </c>
+      <c r="G392">
+        <v>12.8</v>
+      </c>
+      <c r="H392" t="s">
+        <v>18</v>
+      </c>
+      <c r="I392">
+        <v>51</v>
+      </c>
+      <c r="J392">
+        <v>6623.421</v>
+      </c>
+      <c r="K392">
+        <v>7470.990280151367</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11">
+      <c r="A393" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B393" t="s">
+        <v>19</v>
+      </c>
+      <c r="C393" t="s">
+        <v>30</v>
+      </c>
+      <c r="D393">
+        <v>34.0694</v>
+      </c>
+      <c r="E393">
+        <v>34.34000015258789</v>
+      </c>
+      <c r="F393">
+        <v>0.0079426157369337</v>
+      </c>
+      <c r="G393">
+        <v>0.79</v>
+      </c>
+      <c r="H393" t="s">
+        <v>19</v>
+      </c>
+      <c r="I393">
+        <v>34</v>
+      </c>
+      <c r="J393">
+        <v>1158.3596</v>
+      </c>
+      <c r="K393">
+        <v>1167.560005187988</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11">
+      <c r="A394" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B394" t="s">
+        <v>20</v>
+      </c>
+      <c r="C394" t="s">
+        <v>31</v>
+      </c>
+      <c r="D394">
+        <v>69.4158</v>
+      </c>
+      <c r="E394">
+        <v>71.5</v>
+      </c>
+      <c r="F394">
+        <v>0.0300248646561733</v>
+      </c>
+      <c r="G394">
+        <v>3</v>
+      </c>
+      <c r="H394" t="s">
+        <v>20</v>
+      </c>
+      <c r="I394">
+        <v>62</v>
+      </c>
+      <c r="J394">
+        <v>4303.7796</v>
+      </c>
+      <c r="K394">
+        <v>4433</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11">
+      <c r="A395" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B395" t="s">
+        <v>21</v>
+      </c>
+      <c r="C395" t="s">
+        <v>32</v>
+      </c>
+      <c r="D395">
+        <v>8.1868</v>
+      </c>
+      <c r="E395">
+        <v>8.559000015258789</v>
+      </c>
+      <c r="F395">
+        <v>0.0454634307982104</v>
+      </c>
+      <c r="G395">
+        <v>4.55</v>
+      </c>
+      <c r="H395" t="s">
+        <v>21</v>
+      </c>
+      <c r="I395">
+        <v>431</v>
+      </c>
+      <c r="J395">
+        <v>3528.5108</v>
+      </c>
+      <c r="K395">
+        <v>3688.929006576538</v>
       </c>
     </row>
   </sheetData>
@@ -17036,7 +17493,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -18511,6 +18968,47 @@
       </c>
       <c r="M36" s="2">
         <v>0.08115264620024942</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.09886160291119769</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.0553033303683128</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.159433543228908</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.1078082892672049</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.0347707103362797</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0.4693212664399027</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0.0715950318087621</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0.1279654849286142</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0.0079426157369337</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0.0300248646561733</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0.0454634307982104</v>
+      </c>
+      <c r="M37" s="2">
+        <v>0.09736286772558467</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -332,16 +332,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$37</c:f>
+              <c:f>grafico_dati!$B$2:$B$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -449,6 +452,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.09886160291119769</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.0904733068528278</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -476,10 +482,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -587,16 +593,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$37</c:f>
+              <c:f>grafico_dati!$C$2:$C$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -704,6 +713,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.0553033303683128</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.060709904109059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -731,10 +743,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -842,16 +854,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$37</c:f>
+              <c:f>grafico_dati!$D$2:$D$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -959,6 +974,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.159433543228908</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.145846929747768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -986,10 +1004,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1097,16 +1115,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$37</c:f>
+              <c:f>grafico_dati!$E$2:$E$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1214,6 +1235,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.1078082892672049</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.09555039460765991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1241,10 +1265,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1352,16 +1376,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$37</c:f>
+              <c:f>grafico_dati!$F$2:$F$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1466,6 +1493,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.0347707103362797</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.0223706852920335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1493,10 +1523,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1604,16 +1634,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$37</c:f>
+              <c:f>grafico_dati!$G$2:$G$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1721,6 +1754,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.4693212664399027</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.4615577413060747</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1748,10 +1784,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1859,16 +1895,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$37</c:f>
+              <c:f>grafico_dati!$H$2:$H$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -1976,6 +2015,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.0715950318087621</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.0582747745063751</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2003,10 +2045,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2114,16 +2156,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$37</c:f>
+              <c:f>grafico_dati!$I$2:$I$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2228,6 +2273,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.1279654849286142</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.123884521670482</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2255,10 +2303,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2366,16 +2414,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$37</c:f>
+              <c:f>grafico_dati!$J$2:$J$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2483,6 +2534,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.0079426157369337</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.0041268435743704</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2510,10 +2564,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2621,16 +2675,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$37</c:f>
+              <c:f>grafico_dati!$K$2:$K$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2738,6 +2795,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.0300248646561733</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.0291605432971491</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2765,10 +2825,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2876,16 +2936,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$37</c:f>
+              <c:f>grafico_dati!$L$2:$L$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -2993,6 +3056,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.0454634307982104</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.0425318619499817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3024,10 +3090,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$37</c:f>
+              <c:f>grafico_dati!$A$2:$A$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3135,16 +3201,19 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$37</c:f>
+              <c:f>grafico_dati!$M$2:$M$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3252,6 +3321,9 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.09736286772558467</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.09203721782375407</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3658,7 +3730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K395"/>
+  <dimension ref="A1:K406"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -17484,6 +17556,391 @@
       </c>
       <c r="K395">
         <v>3688.929006576538</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11">
+      <c r="A396" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B396" t="s">
+        <v>11</v>
+      </c>
+      <c r="C396" t="s">
+        <v>22</v>
+      </c>
+      <c r="D396">
+        <v>50.07</v>
+      </c>
+      <c r="E396">
+        <v>54.59999847412109</v>
+      </c>
+      <c r="F396">
+        <v>0.0904733068528278</v>
+      </c>
+      <c r="G396">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="H396" t="s">
+        <v>11</v>
+      </c>
+      <c r="I396">
+        <v>23</v>
+      </c>
+      <c r="J396">
+        <v>1151.61</v>
+      </c>
+      <c r="K396">
+        <v>1255.799964904785</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11">
+      <c r="A397" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B397" t="s">
+        <v>12</v>
+      </c>
+      <c r="C397" t="s">
+        <v>23</v>
+      </c>
+      <c r="D397">
+        <v>242.3</v>
+      </c>
+      <c r="E397">
+        <v>257.010009765625</v>
+      </c>
+      <c r="F397">
+        <v>0.060709904109059</v>
+      </c>
+      <c r="G397">
+        <v>6.07</v>
+      </c>
+      <c r="H397" t="s">
+        <v>12</v>
+      </c>
+      <c r="I397">
+        <v>5</v>
+      </c>
+      <c r="J397">
+        <v>1211.5</v>
+      </c>
+      <c r="K397">
+        <v>1285.050048828125</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11">
+      <c r="A398" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B398" t="s">
+        <v>13</v>
+      </c>
+      <c r="C398" t="s">
+        <v>24</v>
+      </c>
+      <c r="D398">
+        <v>38.273</v>
+      </c>
+      <c r="E398">
+        <v>43.85499954223633</v>
+      </c>
+      <c r="F398">
+        <v>0.145846929747768</v>
+      </c>
+      <c r="G398">
+        <v>14.58</v>
+      </c>
+      <c r="H398" t="s">
+        <v>13</v>
+      </c>
+      <c r="I398">
+        <v>54</v>
+      </c>
+      <c r="J398">
+        <v>2066.742</v>
+      </c>
+      <c r="K398">
+        <v>2368.169975280762</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11">
+      <c r="A399" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B399" t="s">
+        <v>14</v>
+      </c>
+      <c r="C399" t="s">
+        <v>25</v>
+      </c>
+      <c r="D399">
+        <v>6.5264</v>
+      </c>
+      <c r="E399">
+        <v>7.150000095367432</v>
+      </c>
+      <c r="F399">
+        <v>0.09555039460765991</v>
+      </c>
+      <c r="G399">
+        <v>9.56</v>
+      </c>
+      <c r="H399" t="s">
+        <v>14</v>
+      </c>
+      <c r="I399">
+        <v>276</v>
+      </c>
+      <c r="J399">
+        <v>1801.2864</v>
+      </c>
+      <c r="K399">
+        <v>1973.400026321411</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11">
+      <c r="A400" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B400" t="s">
+        <v>15</v>
+      </c>
+      <c r="C400" t="s">
+        <v>26</v>
+      </c>
+      <c r="D400">
+        <v>197.58</v>
+      </c>
+      <c r="E400">
+        <v>202</v>
+      </c>
+      <c r="F400">
+        <v>0.0223706852920335</v>
+      </c>
+      <c r="G400">
+        <v>2.24</v>
+      </c>
+      <c r="H400" t="s">
+        <v>15</v>
+      </c>
+      <c r="I400">
+        <v>4</v>
+      </c>
+      <c r="J400">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K400">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11">
+      <c r="A401" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B401" t="s">
+        <v>16</v>
+      </c>
+      <c r="C401" t="s">
+        <v>27</v>
+      </c>
+      <c r="D401">
+        <v>79.86</v>
+      </c>
+      <c r="E401">
+        <v>116.7200012207031</v>
+      </c>
+      <c r="F401">
+        <v>0.4615577413060747</v>
+      </c>
+      <c r="G401">
+        <v>46.16</v>
+      </c>
+      <c r="H401" t="s">
+        <v>16</v>
+      </c>
+      <c r="I401">
+        <v>12</v>
+      </c>
+      <c r="J401">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K401">
+        <v>1400.640014648438</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11">
+      <c r="A402" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B402" t="s">
+        <v>17</v>
+      </c>
+      <c r="C402" t="s">
+        <v>28</v>
+      </c>
+      <c r="D402">
+        <v>19.7444</v>
+      </c>
+      <c r="E402">
+        <v>20.89500045776367</v>
+      </c>
+      <c r="F402">
+        <v>0.0582747745063751</v>
+      </c>
+      <c r="G402">
+        <v>5.83</v>
+      </c>
+      <c r="H402" t="s">
+        <v>17</v>
+      </c>
+      <c r="I402">
+        <v>61</v>
+      </c>
+      <c r="J402">
+        <v>1204.4084</v>
+      </c>
+      <c r="K402">
+        <v>1274.595027923584</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11">
+      <c r="A403" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B403" t="s">
+        <v>18</v>
+      </c>
+      <c r="C403" t="s">
+        <v>29</v>
+      </c>
+      <c r="D403">
+        <v>129.871</v>
+      </c>
+      <c r="E403">
+        <v>145.9600067138672</v>
+      </c>
+      <c r="F403">
+        <v>0.123884521670482</v>
+      </c>
+      <c r="G403">
+        <v>12.39</v>
+      </c>
+      <c r="H403" t="s">
+        <v>18</v>
+      </c>
+      <c r="I403">
+        <v>51</v>
+      </c>
+      <c r="J403">
+        <v>6623.421</v>
+      </c>
+      <c r="K403">
+        <v>7443.960342407227</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11">
+      <c r="A404" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B404" t="s">
+        <v>19</v>
+      </c>
+      <c r="C404" t="s">
+        <v>30</v>
+      </c>
+      <c r="D404">
+        <v>34.0694</v>
+      </c>
+      <c r="E404">
+        <v>34.20999908447266</v>
+      </c>
+      <c r="F404">
+        <v>0.0041268435743704</v>
+      </c>
+      <c r="G404">
+        <v>0.41</v>
+      </c>
+      <c r="H404" t="s">
+        <v>19</v>
+      </c>
+      <c r="I404">
+        <v>34</v>
+      </c>
+      <c r="J404">
+        <v>1158.3596</v>
+      </c>
+      <c r="K404">
+        <v>1163.13996887207</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11">
+      <c r="A405" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B405" t="s">
+        <v>20</v>
+      </c>
+      <c r="C405" t="s">
+        <v>31</v>
+      </c>
+      <c r="D405">
+        <v>69.4158</v>
+      </c>
+      <c r="E405">
+        <v>71.44000244140625</v>
+      </c>
+      <c r="F405">
+        <v>0.0291605432971491</v>
+      </c>
+      <c r="G405">
+        <v>2.92</v>
+      </c>
+      <c r="H405" t="s">
+        <v>20</v>
+      </c>
+      <c r="I405">
+        <v>62</v>
+      </c>
+      <c r="J405">
+        <v>4303.7796</v>
+      </c>
+      <c r="K405">
+        <v>4429.280151367188</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11">
+      <c r="A406" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B406" t="s">
+        <v>21</v>
+      </c>
+      <c r="C406" t="s">
+        <v>32</v>
+      </c>
+      <c r="D406">
+        <v>8.1868</v>
+      </c>
+      <c r="E406">
+        <v>8.534999847412109</v>
+      </c>
+      <c r="F406">
+        <v>0.0425318619499817</v>
+      </c>
+      <c r="G406">
+        <v>4.25</v>
+      </c>
+      <c r="H406" t="s">
+        <v>21</v>
+      </c>
+      <c r="I406">
+        <v>431</v>
+      </c>
+      <c r="J406">
+        <v>3528.5108</v>
+      </c>
+      <c r="K406">
+        <v>3678.584934234619</v>
       </c>
     </row>
   </sheetData>
@@ -17493,7 +17950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -19009,6 +19466,47 @@
       </c>
       <c r="M37" s="2">
         <v>0.09736286772558467</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.0904733068528278</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.060709904109059</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.145846929747768</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.09555039460765991</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.0223706852920335</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0.4615577413060747</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.0582747745063751</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0.123884521670482</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0.0041268435743704</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0.0291605432971491</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0.0425318619499817</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0.09203721782375407</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -335,16 +335,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$38</c:f>
+              <c:f>grafico_dati!$B$2:$B$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -455,6 +458,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.0904733068528278</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.0804872872802295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -482,10 +488,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -596,16 +602,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$38</c:f>
+              <c:f>grafico_dati!$C$2:$C$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -716,6 +725,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.060709904109059</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.0570780226281983</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -743,10 +755,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -857,16 +869,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$38</c:f>
+              <c:f>grafico_dati!$D$2:$D$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -977,6 +992,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.145846929747768</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.143364730267635</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1004,10 +1022,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1118,16 +1136,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$38</c:f>
+              <c:f>grafico_dati!$E$2:$E$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1238,6 +1259,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.09555039460765991</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.0953971818838379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1265,10 +1289,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1379,16 +1403,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$38</c:f>
+              <c:f>grafico_dati!$F$2:$F$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1496,6 +1523,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.0223706852920335</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.0150319012640844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1523,10 +1553,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1637,16 +1667,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$38</c:f>
+              <c:f>grafico_dati!$G$2:$G$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1757,6 +1790,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.4615577413060747</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.4495367159558034</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1784,10 +1820,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1898,16 +1934,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$38</c:f>
+              <c:f>grafico_dati!$H$2:$H$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2018,6 +2057,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.0582747745063751</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.0429792960022743</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2045,10 +2087,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2159,16 +2201,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$38</c:f>
+              <c:f>grafico_dati!$I$2:$I$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2276,6 +2321,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.123884521670482</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.122729458913797</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2303,10 +2351,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2417,16 +2465,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$38</c:f>
+              <c:f>grafico_dati!$J$2:$J$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2537,6 +2588,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.0041268435743704</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.0052657402346846</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2564,10 +2618,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2678,16 +2732,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$38</c:f>
+              <c:f>grafico_dati!$K$2:$K$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2798,6 +2855,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.0291605432971491</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.0272877004744416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2825,10 +2885,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2939,16 +2999,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$38</c:f>
+              <c:f>grafico_dati!$L$2:$L$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3059,6 +3122,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.0425318619499817</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.040088965569301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3090,10 +3156,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$38</c:f>
+              <c:f>grafico_dati!$A$2:$A$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3204,16 +3270,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$38</c:f>
+              <c:f>grafico_dati!$M$2:$M$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3324,6 +3393,9 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0.09203721782375407</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.08831685181213</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3730,7 +3802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K406"/>
+  <dimension ref="A1:K417"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -17941,6 +18013,391 @@
       </c>
       <c r="K406">
         <v>3678.584934234619</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11">
+      <c r="A407" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B407" t="s">
+        <v>11</v>
+      </c>
+      <c r="C407" t="s">
+        <v>22</v>
+      </c>
+      <c r="D407">
+        <v>50.07</v>
+      </c>
+      <c r="E407">
+        <v>54.09999847412109</v>
+      </c>
+      <c r="F407">
+        <v>0.0804872872802295</v>
+      </c>
+      <c r="G407">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="H407" t="s">
+        <v>11</v>
+      </c>
+      <c r="I407">
+        <v>23</v>
+      </c>
+      <c r="J407">
+        <v>1151.61</v>
+      </c>
+      <c r="K407">
+        <v>1244.299964904785</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11">
+      <c r="A408" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B408" t="s">
+        <v>12</v>
+      </c>
+      <c r="C408" t="s">
+        <v>23</v>
+      </c>
+      <c r="D408">
+        <v>242.3</v>
+      </c>
+      <c r="E408">
+        <v>256.1300048828125</v>
+      </c>
+      <c r="F408">
+        <v>0.0570780226281983</v>
+      </c>
+      <c r="G408">
+        <v>5.71</v>
+      </c>
+      <c r="H408" t="s">
+        <v>12</v>
+      </c>
+      <c r="I408">
+        <v>5</v>
+      </c>
+      <c r="J408">
+        <v>1211.5</v>
+      </c>
+      <c r="K408">
+        <v>1280.650024414062</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11">
+      <c r="A409" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B409" t="s">
+        <v>13</v>
+      </c>
+      <c r="C409" t="s">
+        <v>24</v>
+      </c>
+      <c r="D409">
+        <v>38.273</v>
+      </c>
+      <c r="E409">
+        <v>43.7599983215332</v>
+      </c>
+      <c r="F409">
+        <v>0.143364730267635</v>
+      </c>
+      <c r="G409">
+        <v>14.34</v>
+      </c>
+      <c r="H409" t="s">
+        <v>13</v>
+      </c>
+      <c r="I409">
+        <v>54</v>
+      </c>
+      <c r="J409">
+        <v>2066.742</v>
+      </c>
+      <c r="K409">
+        <v>2363.039909362793</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11">
+      <c r="A410" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B410" t="s">
+        <v>14</v>
+      </c>
+      <c r="C410" t="s">
+        <v>25</v>
+      </c>
+      <c r="D410">
+        <v>6.5264</v>
+      </c>
+      <c r="E410">
+        <v>7.14900016784668</v>
+      </c>
+      <c r="F410">
+        <v>0.0953971818838379</v>
+      </c>
+      <c r="G410">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="H410" t="s">
+        <v>14</v>
+      </c>
+      <c r="I410">
+        <v>276</v>
+      </c>
+      <c r="J410">
+        <v>1801.2864</v>
+      </c>
+      <c r="K410">
+        <v>1973.124046325684</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11">
+      <c r="A411" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B411" t="s">
+        <v>15</v>
+      </c>
+      <c r="C411" t="s">
+        <v>26</v>
+      </c>
+      <c r="D411">
+        <v>197.58</v>
+      </c>
+      <c r="E411">
+        <v>200.5500030517578</v>
+      </c>
+      <c r="F411">
+        <v>0.0150319012640844</v>
+      </c>
+      <c r="G411">
+        <v>1.5</v>
+      </c>
+      <c r="H411" t="s">
+        <v>15</v>
+      </c>
+      <c r="I411">
+        <v>4</v>
+      </c>
+      <c r="J411">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K411">
+        <v>802.2000122070312</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11">
+      <c r="A412" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B412" t="s">
+        <v>16</v>
+      </c>
+      <c r="C412" t="s">
+        <v>27</v>
+      </c>
+      <c r="D412">
+        <v>79.86</v>
+      </c>
+      <c r="E412">
+        <v>115.7600021362305</v>
+      </c>
+      <c r="F412">
+        <v>0.4495367159558034</v>
+      </c>
+      <c r="G412">
+        <v>44.95</v>
+      </c>
+      <c r="H412" t="s">
+        <v>16</v>
+      </c>
+      <c r="I412">
+        <v>12</v>
+      </c>
+      <c r="J412">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K412">
+        <v>1389.120025634766</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11">
+      <c r="A413" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B413" t="s">
+        <v>17</v>
+      </c>
+      <c r="C413" t="s">
+        <v>28</v>
+      </c>
+      <c r="D413">
+        <v>19.7444</v>
+      </c>
+      <c r="E413">
+        <v>20.5930004119873</v>
+      </c>
+      <c r="F413">
+        <v>0.0429792960022743</v>
+      </c>
+      <c r="G413">
+        <v>4.3</v>
+      </c>
+      <c r="H413" t="s">
+        <v>17</v>
+      </c>
+      <c r="I413">
+        <v>61</v>
+      </c>
+      <c r="J413">
+        <v>1204.4084</v>
+      </c>
+      <c r="K413">
+        <v>1256.173025131226</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11">
+      <c r="A414" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B414" t="s">
+        <v>18</v>
+      </c>
+      <c r="C414" t="s">
+        <v>29</v>
+      </c>
+      <c r="D414">
+        <v>129.871</v>
+      </c>
+      <c r="E414">
+        <v>145.8099975585938</v>
+      </c>
+      <c r="F414">
+        <v>0.122729458913797</v>
+      </c>
+      <c r="G414">
+        <v>12.27</v>
+      </c>
+      <c r="H414" t="s">
+        <v>18</v>
+      </c>
+      <c r="I414">
+        <v>51</v>
+      </c>
+      <c r="J414">
+        <v>6623.421</v>
+      </c>
+      <c r="K414">
+        <v>7436.309875488281</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11">
+      <c r="A415" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B415" t="s">
+        <v>19</v>
+      </c>
+      <c r="C415" t="s">
+        <v>30</v>
+      </c>
+      <c r="D415">
+        <v>34.0694</v>
+      </c>
+      <c r="E415">
+        <v>33.88999938964844</v>
+      </c>
+      <c r="F415">
+        <v>-0.0052657402346846</v>
+      </c>
+      <c r="G415">
+        <v>-0.53</v>
+      </c>
+      <c r="H415" t="s">
+        <v>19</v>
+      </c>
+      <c r="I415">
+        <v>34</v>
+      </c>
+      <c r="J415">
+        <v>1158.3596</v>
+      </c>
+      <c r="K415">
+        <v>1152.259979248047</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11">
+      <c r="A416" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B416" t="s">
+        <v>20</v>
+      </c>
+      <c r="C416" t="s">
+        <v>31</v>
+      </c>
+      <c r="D416">
+        <v>69.4158</v>
+      </c>
+      <c r="E416">
+        <v>71.30999755859375</v>
+      </c>
+      <c r="F416">
+        <v>0.0272877004744416</v>
+      </c>
+      <c r="G416">
+        <v>2.73</v>
+      </c>
+      <c r="H416" t="s">
+        <v>20</v>
+      </c>
+      <c r="I416">
+        <v>62</v>
+      </c>
+      <c r="J416">
+        <v>4303.7796</v>
+      </c>
+      <c r="K416">
+        <v>4421.219848632812</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11">
+      <c r="A417" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B417" t="s">
+        <v>21</v>
+      </c>
+      <c r="C417" t="s">
+        <v>32</v>
+      </c>
+      <c r="D417">
+        <v>8.1868</v>
+      </c>
+      <c r="E417">
+        <v>8.515000343322754</v>
+      </c>
+      <c r="F417">
+        <v>0.040088965569301</v>
+      </c>
+      <c r="G417">
+        <v>4.01</v>
+      </c>
+      <c r="H417" t="s">
+        <v>21</v>
+      </c>
+      <c r="I417">
+        <v>431</v>
+      </c>
+      <c r="J417">
+        <v>3528.5108</v>
+      </c>
+      <c r="K417">
+        <v>3669.965147972107</v>
       </c>
     </row>
   </sheetData>
@@ -17950,7 +18407,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -19507,6 +19964,47 @@
       </c>
       <c r="M38" s="2">
         <v>0.09203721782375407</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.0804872872802295</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.0570780226281983</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.143364730267635</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.0953971818838379</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0.0150319012640844</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0.4495367159558034</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0.0429792960022743</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0.122729458913797</v>
+      </c>
+      <c r="J39" s="2">
+        <v>-0.0052657402346846</v>
+      </c>
+      <c r="K39" s="2">
+        <v>0.0272877004744416</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0.040088965569301</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0.08831685181213</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -338,16 +338,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$39</c:f>
+              <c:f>grafico_dati!$B$2:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -461,6 +464,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.0804872872802295</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.0740962408487493</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -488,10 +494,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -605,16 +611,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$39</c:f>
+              <c:f>grafico_dati!$C$2:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -728,6 +737,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.0570780226281983</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.0550144650549422</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -755,10 +767,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -872,16 +884,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$39</c:f>
+              <c:f>grafico_dati!$D$2:$D$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -995,6 +1010,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.143364730267635</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.1596947801722676</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1022,10 +1040,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1139,16 +1157,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$39</c:f>
+              <c:f>grafico_dati!$E$2:$E$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1262,6 +1283,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.0953971818838379</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.1088808513967745</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1289,10 +1313,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1406,16 +1430,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$39</c:f>
+              <c:f>grafico_dati!$F$2:$F$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1526,6 +1553,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.0150319012640844</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.012248203259439</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1553,10 +1583,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1670,16 +1700,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$39</c:f>
+              <c:f>grafico_dati!$G$2:$G$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1793,6 +1826,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.4495367159558034</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.4462809917355372</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1820,10 +1856,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1937,16 +1973,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$39</c:f>
+              <c:f>grafico_dati!$H$2:$H$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2060,6 +2099,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.0429792960022743</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.0432832059108472</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2087,10 +2129,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2204,16 +2246,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$39</c:f>
+              <c:f>grafico_dati!$I$2:$I$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2324,6 +2369,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.122729458913797</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.1272724002778478</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2351,10 +2399,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2468,16 +2516,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$39</c:f>
+              <c:f>grafico_dati!$J$2:$J$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2591,6 +2642,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>-0.0052657402346846</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.0133374324623622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2618,10 +2672,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2735,16 +2789,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$39</c:f>
+              <c:f>grafico_dati!$K$2:$K$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2858,6 +2915,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.0272877004744416</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.0314654368907523</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2885,10 +2945,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3002,16 +3062,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$39</c:f>
+              <c:f>grafico_dati!$L$2:$L$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3125,6 +3188,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.040088965569301</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.0408217995367257</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3156,10 +3222,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$39</c:f>
+              <c:f>grafico_dati!$A$2:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3273,16 +3339,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$39</c:f>
+              <c:f>grafico_dati!$M$2:$M$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3396,6 +3465,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0.08831685181213</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.09172554739087047</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3802,7 +3874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K417"/>
+  <dimension ref="A1:K428"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -18398,6 +18470,391 @@
       </c>
       <c r="K417">
         <v>3669.965147972107</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11">
+      <c r="A418" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B418" t="s">
+        <v>11</v>
+      </c>
+      <c r="C418" t="s">
+        <v>22</v>
+      </c>
+      <c r="D418">
+        <v>50.07</v>
+      </c>
+      <c r="E418">
+        <v>53.77999877929688</v>
+      </c>
+      <c r="F418">
+        <v>0.0740962408487493</v>
+      </c>
+      <c r="G418">
+        <v>7.41</v>
+      </c>
+      <c r="H418" t="s">
+        <v>11</v>
+      </c>
+      <c r="I418">
+        <v>23</v>
+      </c>
+      <c r="J418">
+        <v>1151.61</v>
+      </c>
+      <c r="K418">
+        <v>1236.939971923828</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11">
+      <c r="A419" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B419" t="s">
+        <v>12</v>
+      </c>
+      <c r="C419" t="s">
+        <v>23</v>
+      </c>
+      <c r="D419">
+        <v>242.3</v>
+      </c>
+      <c r="E419">
+        <v>255.6300048828125</v>
+      </c>
+      <c r="F419">
+        <v>0.0550144650549422</v>
+      </c>
+      <c r="G419">
+        <v>5.5</v>
+      </c>
+      <c r="H419" t="s">
+        <v>12</v>
+      </c>
+      <c r="I419">
+        <v>5</v>
+      </c>
+      <c r="J419">
+        <v>1211.5</v>
+      </c>
+      <c r="K419">
+        <v>1278.150024414062</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11">
+      <c r="A420" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B420" t="s">
+        <v>13</v>
+      </c>
+      <c r="C420" t="s">
+        <v>24</v>
+      </c>
+      <c r="D420">
+        <v>38.273</v>
+      </c>
+      <c r="E420">
+        <v>44.3849983215332</v>
+      </c>
+      <c r="F420">
+        <v>0.1596947801722676</v>
+      </c>
+      <c r="G420">
+        <v>15.97</v>
+      </c>
+      <c r="H420" t="s">
+        <v>13</v>
+      </c>
+      <c r="I420">
+        <v>54</v>
+      </c>
+      <c r="J420">
+        <v>2066.742</v>
+      </c>
+      <c r="K420">
+        <v>2396.789909362793</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11">
+      <c r="A421" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B421" t="s">
+        <v>14</v>
+      </c>
+      <c r="C421" t="s">
+        <v>25</v>
+      </c>
+      <c r="D421">
+        <v>6.5264</v>
+      </c>
+      <c r="E421">
+        <v>7.236999988555908</v>
+      </c>
+      <c r="F421">
+        <v>0.1088808513967745</v>
+      </c>
+      <c r="G421">
+        <v>10.89</v>
+      </c>
+      <c r="H421" t="s">
+        <v>14</v>
+      </c>
+      <c r="I421">
+        <v>276</v>
+      </c>
+      <c r="J421">
+        <v>1801.2864</v>
+      </c>
+      <c r="K421">
+        <v>1997.411996841431</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11">
+      <c r="A422" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B422" t="s">
+        <v>15</v>
+      </c>
+      <c r="C422" t="s">
+        <v>26</v>
+      </c>
+      <c r="D422">
+        <v>197.58</v>
+      </c>
+      <c r="E422">
+        <v>200</v>
+      </c>
+      <c r="F422">
+        <v>0.012248203259439</v>
+      </c>
+      <c r="G422">
+        <v>1.22</v>
+      </c>
+      <c r="H422" t="s">
+        <v>15</v>
+      </c>
+      <c r="I422">
+        <v>4</v>
+      </c>
+      <c r="J422">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K422">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11">
+      <c r="A423" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B423" t="s">
+        <v>16</v>
+      </c>
+      <c r="C423" t="s">
+        <v>27</v>
+      </c>
+      <c r="D423">
+        <v>79.86</v>
+      </c>
+      <c r="E423">
+        <v>115.5</v>
+      </c>
+      <c r="F423">
+        <v>0.4462809917355372</v>
+      </c>
+      <c r="G423">
+        <v>44.63</v>
+      </c>
+      <c r="H423" t="s">
+        <v>16</v>
+      </c>
+      <c r="I423">
+        <v>12</v>
+      </c>
+      <c r="J423">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K423">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11">
+      <c r="A424" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B424" t="s">
+        <v>17</v>
+      </c>
+      <c r="C424" t="s">
+        <v>28</v>
+      </c>
+      <c r="D424">
+        <v>19.7444</v>
+      </c>
+      <c r="E424">
+        <v>20.59900093078613</v>
+      </c>
+      <c r="F424">
+        <v>0.0432832059108472</v>
+      </c>
+      <c r="G424">
+        <v>4.33</v>
+      </c>
+      <c r="H424" t="s">
+        <v>17</v>
+      </c>
+      <c r="I424">
+        <v>61</v>
+      </c>
+      <c r="J424">
+        <v>1204.4084</v>
+      </c>
+      <c r="K424">
+        <v>1256.539056777954</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11">
+      <c r="A425" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B425" t="s">
+        <v>18</v>
+      </c>
+      <c r="C425" t="s">
+        <v>29</v>
+      </c>
+      <c r="D425">
+        <v>129.871</v>
+      </c>
+      <c r="E425">
+        <v>146.3999938964844</v>
+      </c>
+      <c r="F425">
+        <v>0.1272724002778478</v>
+      </c>
+      <c r="G425">
+        <v>12.73</v>
+      </c>
+      <c r="H425" t="s">
+        <v>18</v>
+      </c>
+      <c r="I425">
+        <v>51</v>
+      </c>
+      <c r="J425">
+        <v>6623.421</v>
+      </c>
+      <c r="K425">
+        <v>7466.399688720703</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11">
+      <c r="A426" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B426" t="s">
+        <v>19</v>
+      </c>
+      <c r="C426" t="s">
+        <v>30</v>
+      </c>
+      <c r="D426">
+        <v>34.0694</v>
+      </c>
+      <c r="E426">
+        <v>33.6150016784668</v>
+      </c>
+      <c r="F426">
+        <v>-0.0133374324623622</v>
+      </c>
+      <c r="G426">
+        <v>-1.33</v>
+      </c>
+      <c r="H426" t="s">
+        <v>19</v>
+      </c>
+      <c r="I426">
+        <v>34</v>
+      </c>
+      <c r="J426">
+        <v>1158.3596</v>
+      </c>
+      <c r="K426">
+        <v>1142.910057067871</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11">
+      <c r="A427" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B427" t="s">
+        <v>20</v>
+      </c>
+      <c r="C427" t="s">
+        <v>31</v>
+      </c>
+      <c r="D427">
+        <v>69.4158</v>
+      </c>
+      <c r="E427">
+        <v>71.59999847412109</v>
+      </c>
+      <c r="F427">
+        <v>0.0314654368907523</v>
+      </c>
+      <c r="G427">
+        <v>3.15</v>
+      </c>
+      <c r="H427" t="s">
+        <v>20</v>
+      </c>
+      <c r="I427">
+        <v>62</v>
+      </c>
+      <c r="J427">
+        <v>4303.7796</v>
+      </c>
+      <c r="K427">
+        <v>4439.199905395508</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11">
+      <c r="A428" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B428" t="s">
+        <v>21</v>
+      </c>
+      <c r="C428" t="s">
+        <v>32</v>
+      </c>
+      <c r="D428">
+        <v>8.1868</v>
+      </c>
+      <c r="E428">
+        <v>8.520999908447266</v>
+      </c>
+      <c r="F428">
+        <v>0.0408217995367257</v>
+      </c>
+      <c r="G428">
+        <v>4.08</v>
+      </c>
+      <c r="H428" t="s">
+        <v>21</v>
+      </c>
+      <c r="I428">
+        <v>431</v>
+      </c>
+      <c r="J428">
+        <v>3528.5108</v>
+      </c>
+      <c r="K428">
+        <v>3672.550960540771</v>
       </c>
     </row>
   </sheetData>
@@ -18407,7 +18864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -20005,6 +20462,47 @@
       </c>
       <c r="M39" s="2">
         <v>0.08831685181213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.0740962408487493</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.0550144650549422</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.1596947801722676</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.1088808513967745</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.012248203259439</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.4462809917355372</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0.0432832059108472</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0.1272724002778478</v>
+      </c>
+      <c r="J40" s="2">
+        <v>-0.0133374324623622</v>
+      </c>
+      <c r="K40" s="2">
+        <v>0.0314654368907523</v>
+      </c>
+      <c r="L40" s="2">
+        <v>0.0408217995367257</v>
+      </c>
+      <c r="M40" s="2">
+        <v>0.09172554739087047</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -341,16 +341,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$40</c:f>
+              <c:f>grafico_dati!$B$2:$B$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -467,6 +470,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.0740962408487493</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.07769121398986729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -494,10 +500,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -614,16 +620,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$40</c:f>
+              <c:f>grafico_dati!$C$2:$C$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -740,6 +749,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.0550144650549422</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.0563764206102648</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -767,10 +779,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -887,16 +899,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$40</c:f>
+              <c:f>grafico_dati!$D$2:$D$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1013,6 +1028,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.1596947801722676</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.1512032339584306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1040,10 +1058,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1160,16 +1178,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$40</c:f>
+              <c:f>grafico_dati!$E$2:$E$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1286,6 +1307,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.1088808513967745</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.1094937753548777</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1313,10 +1337,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1433,16 +1457,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$40</c:f>
+              <c:f>grafico_dati!$F$2:$F$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1556,6 +1583,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.012248203259439</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.0104261534044358</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1583,10 +1613,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1703,16 +1733,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$40</c:f>
+              <c:f>grafico_dati!$G$2:$G$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1829,6 +1862,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.4462809917355372</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.4535437244058939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1856,10 +1892,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1976,16 +2012,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$40</c:f>
+              <c:f>grafico_dati!$H$2:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2102,6 +2141,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.0432832059108472</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.0456129564718945</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2129,10 +2171,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2249,16 +2291,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$40</c:f>
+              <c:f>grafico_dati!$I$2:$I$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2372,6 +2417,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.1272724002778478</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.1311223744830205</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2399,10 +2447,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2519,16 +2567,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$40</c:f>
+              <c:f>grafico_dati!$J$2:$J$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2645,6 +2696,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>-0.0133374324623622</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.0007162389432948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2672,10 +2726,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2792,16 +2846,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$40</c:f>
+              <c:f>grafico_dati!$K$2:$K$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2918,6 +2975,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.0314654368907523</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.0349228322354653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2945,10 +3005,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3065,16 +3125,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$40</c:f>
+              <c:f>grafico_dati!$L$2:$L$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3191,6 +3254,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.0408217995367257</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.040943996775929</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3222,10 +3288,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$40</c:f>
+              <c:f>grafico_dati!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3342,16 +3408,19 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$40</c:f>
+              <c:f>grafico_dati!$M$2:$M$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3468,6 +3537,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.09172554739087047</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.09386687305062402</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3874,7 +3946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K428"/>
+  <dimension ref="A1:K439"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -18855,6 +18927,391 @@
       </c>
       <c r="K428">
         <v>3672.550960540771</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11">
+      <c r="A429" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B429" t="s">
+        <v>11</v>
+      </c>
+      <c r="C429" t="s">
+        <v>22</v>
+      </c>
+      <c r="D429">
+        <v>50.07</v>
+      </c>
+      <c r="E429">
+        <v>53.95999908447266</v>
+      </c>
+      <c r="F429">
+        <v>0.07769121398986729</v>
+      </c>
+      <c r="G429">
+        <v>7.77</v>
+      </c>
+      <c r="H429" t="s">
+        <v>11</v>
+      </c>
+      <c r="I429">
+        <v>23</v>
+      </c>
+      <c r="J429">
+        <v>1151.61</v>
+      </c>
+      <c r="K429">
+        <v>1241.079978942871</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11">
+      <c r="A430" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B430" t="s">
+        <v>12</v>
+      </c>
+      <c r="C430" t="s">
+        <v>23</v>
+      </c>
+      <c r="D430">
+        <v>242.3</v>
+      </c>
+      <c r="E430">
+        <v>255.9600067138672</v>
+      </c>
+      <c r="F430">
+        <v>0.0563764206102648</v>
+      </c>
+      <c r="G430">
+        <v>5.64</v>
+      </c>
+      <c r="H430" t="s">
+        <v>12</v>
+      </c>
+      <c r="I430">
+        <v>5</v>
+      </c>
+      <c r="J430">
+        <v>1211.5</v>
+      </c>
+      <c r="K430">
+        <v>1279.800033569336</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11">
+      <c r="A431" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B431" t="s">
+        <v>13</v>
+      </c>
+      <c r="C431" t="s">
+        <v>24</v>
+      </c>
+      <c r="D431">
+        <v>38.273</v>
+      </c>
+      <c r="E431">
+        <v>44.06000137329102</v>
+      </c>
+      <c r="F431">
+        <v>0.1512032339584306</v>
+      </c>
+      <c r="G431">
+        <v>15.12</v>
+      </c>
+      <c r="H431" t="s">
+        <v>13</v>
+      </c>
+      <c r="I431">
+        <v>54</v>
+      </c>
+      <c r="J431">
+        <v>2066.742</v>
+      </c>
+      <c r="K431">
+        <v>2379.240074157715</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11">
+      <c r="A432" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B432" t="s">
+        <v>14</v>
+      </c>
+      <c r="C432" t="s">
+        <v>25</v>
+      </c>
+      <c r="D432">
+        <v>6.5264</v>
+      </c>
+      <c r="E432">
+        <v>7.241000175476074</v>
+      </c>
+      <c r="F432">
+        <v>0.1094937753548777</v>
+      </c>
+      <c r="G432">
+        <v>10.95</v>
+      </c>
+      <c r="H432" t="s">
+        <v>14</v>
+      </c>
+      <c r="I432">
+        <v>276</v>
+      </c>
+      <c r="J432">
+        <v>1801.2864</v>
+      </c>
+      <c r="K432">
+        <v>1998.516048431396</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11">
+      <c r="A433" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B433" t="s">
+        <v>15</v>
+      </c>
+      <c r="C433" t="s">
+        <v>26</v>
+      </c>
+      <c r="D433">
+        <v>197.58</v>
+      </c>
+      <c r="E433">
+        <v>199.6399993896484</v>
+      </c>
+      <c r="F433">
+        <v>0.0104261534044358</v>
+      </c>
+      <c r="G433">
+        <v>1.04</v>
+      </c>
+      <c r="H433" t="s">
+        <v>15</v>
+      </c>
+      <c r="I433">
+        <v>4</v>
+      </c>
+      <c r="J433">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K433">
+        <v>798.5599975585938</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11">
+      <c r="A434" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B434" t="s">
+        <v>16</v>
+      </c>
+      <c r="C434" t="s">
+        <v>27</v>
+      </c>
+      <c r="D434">
+        <v>79.86</v>
+      </c>
+      <c r="E434">
+        <v>116.0800018310547</v>
+      </c>
+      <c r="F434">
+        <v>0.4535437244058939</v>
+      </c>
+      <c r="G434">
+        <v>45.35</v>
+      </c>
+      <c r="H434" t="s">
+        <v>16</v>
+      </c>
+      <c r="I434">
+        <v>12</v>
+      </c>
+      <c r="J434">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K434">
+        <v>1392.960021972656</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11">
+      <c r="A435" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B435" t="s">
+        <v>17</v>
+      </c>
+      <c r="C435" t="s">
+        <v>28</v>
+      </c>
+      <c r="D435">
+        <v>19.7444</v>
+      </c>
+      <c r="E435">
+        <v>20.64500045776367</v>
+      </c>
+      <c r="F435">
+        <v>0.0456129564718945</v>
+      </c>
+      <c r="G435">
+        <v>4.56</v>
+      </c>
+      <c r="H435" t="s">
+        <v>17</v>
+      </c>
+      <c r="I435">
+        <v>61</v>
+      </c>
+      <c r="J435">
+        <v>1204.4084</v>
+      </c>
+      <c r="K435">
+        <v>1259.345027923584</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11">
+      <c r="A436" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B436" t="s">
+        <v>18</v>
+      </c>
+      <c r="C436" t="s">
+        <v>29</v>
+      </c>
+      <c r="D436">
+        <v>129.871</v>
+      </c>
+      <c r="E436">
+        <v>146.8999938964844</v>
+      </c>
+      <c r="F436">
+        <v>0.1311223744830205</v>
+      </c>
+      <c r="G436">
+        <v>13.11</v>
+      </c>
+      <c r="H436" t="s">
+        <v>18</v>
+      </c>
+      <c r="I436">
+        <v>51</v>
+      </c>
+      <c r="J436">
+        <v>6623.421</v>
+      </c>
+      <c r="K436">
+        <v>7491.899688720703</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11">
+      <c r="A437" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B437" t="s">
+        <v>19</v>
+      </c>
+      <c r="C437" t="s">
+        <v>30</v>
+      </c>
+      <c r="D437">
+        <v>34.0694</v>
+      </c>
+      <c r="E437">
+        <v>34.04499816894531</v>
+      </c>
+      <c r="F437">
+        <v>-0.0007162389432948</v>
+      </c>
+      <c r="G437">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H437" t="s">
+        <v>19</v>
+      </c>
+      <c r="I437">
+        <v>34</v>
+      </c>
+      <c r="J437">
+        <v>1158.3596</v>
+      </c>
+      <c r="K437">
+        <v>1157.529937744141</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11">
+      <c r="A438" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B438" t="s">
+        <v>20</v>
+      </c>
+      <c r="C438" t="s">
+        <v>31</v>
+      </c>
+      <c r="D438">
+        <v>69.4158</v>
+      </c>
+      <c r="E438">
+        <v>71.83999633789062</v>
+      </c>
+      <c r="F438">
+        <v>0.0349228322354653</v>
+      </c>
+      <c r="G438">
+        <v>3.49</v>
+      </c>
+      <c r="H438" t="s">
+        <v>20</v>
+      </c>
+      <c r="I438">
+        <v>62</v>
+      </c>
+      <c r="J438">
+        <v>4303.7796</v>
+      </c>
+      <c r="K438">
+        <v>4454.079772949219</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11">
+      <c r="A439" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B439" t="s">
+        <v>21</v>
+      </c>
+      <c r="C439" t="s">
+        <v>32</v>
+      </c>
+      <c r="D439">
+        <v>8.1868</v>
+      </c>
+      <c r="E439">
+        <v>8.522000312805176</v>
+      </c>
+      <c r="F439">
+        <v>0.040943996775929</v>
+      </c>
+      <c r="G439">
+        <v>4.09</v>
+      </c>
+      <c r="H439" t="s">
+        <v>21</v>
+      </c>
+      <c r="I439">
+        <v>431</v>
+      </c>
+      <c r="J439">
+        <v>3528.5108</v>
+      </c>
+      <c r="K439">
+        <v>3672.982134819031</v>
       </c>
     </row>
   </sheetData>
@@ -18864,7 +19321,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -20503,6 +20960,47 @@
       </c>
       <c r="M40" s="2">
         <v>0.09172554739087047</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.07769121398986729</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.0563764206102648</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.1512032339584306</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.1094937753548777</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.0104261534044358</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.4535437244058939</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0.0456129564718945</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0.1311223744830205</v>
+      </c>
+      <c r="J41" s="2">
+        <v>-0.0007162389432948</v>
+      </c>
+      <c r="K41" s="2">
+        <v>0.0349228322354653</v>
+      </c>
+      <c r="L41" s="2">
+        <v>0.040943996775929</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0.09386687305062402</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -344,16 +344,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$41</c:f>
+              <c:f>grafico_dati!$B$2:$B$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -473,6 +476,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.07769121398986729</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.0651088841832372</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -500,10 +506,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -623,16 +629,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$41</c:f>
+              <c:f>grafico_dati!$C$2:$C$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -752,6 +761,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.0563764206102648</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.0507635414920166</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -779,10 +791,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -902,16 +914,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$41</c:f>
+              <c:f>grafico_dati!$D$2:$D$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1031,6 +1046,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.1512032339584306</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.1598254484793049</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1058,10 +1076,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1181,16 +1199,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$41</c:f>
+              <c:f>grafico_dati!$E$2:$E$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1310,6 +1331,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.1094937753548777</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.1206791078848534</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1337,10 +1361,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1460,16 +1484,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$41</c:f>
+              <c:f>grafico_dati!$F$2:$F$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1586,6 +1613,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.0104261534044358</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.00961633630701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1613,10 +1643,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1736,16 +1766,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$41</c:f>
+              <c:f>grafico_dati!$G$2:$G$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1865,6 +1898,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.4535437244058939</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.4445279315095363</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1892,10 +1928,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2015,16 +2051,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$41</c:f>
+              <c:f>grafico_dati!$H$2:$H$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2144,6 +2183,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.0456129564718945</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.039180711951128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2171,10 +2213,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2294,16 +2336,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$41</c:f>
+              <c:f>grafico_dati!$I$2:$I$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2420,6 +2465,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.1311223744830205</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.1285814949004684</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2447,10 +2495,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2570,16 +2618,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$41</c:f>
+              <c:f>grafico_dati!$J$2:$J$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2699,6 +2750,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>-0.0007162389432948</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.007907411429008301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2726,10 +2780,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2849,16 +2903,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$41</c:f>
+              <c:f>grafico_dati!$K$2:$K$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -2978,6 +3035,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.0349228322354653</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.0339144206803985</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3005,10 +3065,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3128,16 +3188,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$41</c:f>
+              <c:f>grafico_dati!$L$2:$L$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3257,6 +3320,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.040943996775929</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.0344701058619849</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3288,10 +3354,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$41</c:f>
+              <c:f>grafico_dati!$A$2:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3411,16 +3477,19 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$41</c:f>
+              <c:f>grafico_dati!$M$2:$M$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3540,6 +3609,9 @@
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.09386687305062402</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.09174206280623287</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3946,7 +4018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K439"/>
+  <dimension ref="A1:K450"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -19312,6 +19384,391 @@
       </c>
       <c r="K439">
         <v>3672.982134819031</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11">
+      <c r="A440" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B440" t="s">
+        <v>11</v>
+      </c>
+      <c r="C440" t="s">
+        <v>22</v>
+      </c>
+      <c r="D440">
+        <v>50.07</v>
+      </c>
+      <c r="E440">
+        <v>53.33000183105469</v>
+      </c>
+      <c r="F440">
+        <v>0.0651088841832372</v>
+      </c>
+      <c r="G440">
+        <v>6.51</v>
+      </c>
+      <c r="H440" t="s">
+        <v>11</v>
+      </c>
+      <c r="I440">
+        <v>23</v>
+      </c>
+      <c r="J440">
+        <v>1151.61</v>
+      </c>
+      <c r="K440">
+        <v>1226.590042114258</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11">
+      <c r="A441" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B441" t="s">
+        <v>12</v>
+      </c>
+      <c r="C441" t="s">
+        <v>23</v>
+      </c>
+      <c r="D441">
+        <v>242.3</v>
+      </c>
+      <c r="E441">
+        <v>254.6000061035156</v>
+      </c>
+      <c r="F441">
+        <v>0.0507635414920166</v>
+      </c>
+      <c r="G441">
+        <v>5.08</v>
+      </c>
+      <c r="H441" t="s">
+        <v>12</v>
+      </c>
+      <c r="I441">
+        <v>5</v>
+      </c>
+      <c r="J441">
+        <v>1211.5</v>
+      </c>
+      <c r="K441">
+        <v>1273.000030517578</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11">
+      <c r="A442" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B442" t="s">
+        <v>13</v>
+      </c>
+      <c r="C442" t="s">
+        <v>24</v>
+      </c>
+      <c r="D442">
+        <v>38.273</v>
+      </c>
+      <c r="E442">
+        <v>44.38999938964844</v>
+      </c>
+      <c r="F442">
+        <v>0.1598254484793049</v>
+      </c>
+      <c r="G442">
+        <v>15.98</v>
+      </c>
+      <c r="H442" t="s">
+        <v>13</v>
+      </c>
+      <c r="I442">
+        <v>54</v>
+      </c>
+      <c r="J442">
+        <v>2066.742</v>
+      </c>
+      <c r="K442">
+        <v>2397.059967041016</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11">
+      <c r="A443" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B443" t="s">
+        <v>14</v>
+      </c>
+      <c r="C443" t="s">
+        <v>25</v>
+      </c>
+      <c r="D443">
+        <v>6.5264</v>
+      </c>
+      <c r="E443">
+        <v>7.314000129699707</v>
+      </c>
+      <c r="F443">
+        <v>0.1206791078848534</v>
+      </c>
+      <c r="G443">
+        <v>12.07</v>
+      </c>
+      <c r="H443" t="s">
+        <v>14</v>
+      </c>
+      <c r="I443">
+        <v>276</v>
+      </c>
+      <c r="J443">
+        <v>1801.2864</v>
+      </c>
+      <c r="K443">
+        <v>2018.664035797119</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11">
+      <c r="A444" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B444" t="s">
+        <v>15</v>
+      </c>
+      <c r="C444" t="s">
+        <v>26</v>
+      </c>
+      <c r="D444">
+        <v>197.58</v>
+      </c>
+      <c r="E444">
+        <v>199.479995727539</v>
+      </c>
+      <c r="F444">
+        <v>0.00961633630701</v>
+      </c>
+      <c r="G444">
+        <v>0.96</v>
+      </c>
+      <c r="H444" t="s">
+        <v>15</v>
+      </c>
+      <c r="I444">
+        <v>4</v>
+      </c>
+      <c r="J444">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K444">
+        <v>797.9199829101561</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11">
+      <c r="A445" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B445" t="s">
+        <v>16</v>
+      </c>
+      <c r="C445" t="s">
+        <v>27</v>
+      </c>
+      <c r="D445">
+        <v>79.86</v>
+      </c>
+      <c r="E445">
+        <v>115.3600006103516</v>
+      </c>
+      <c r="F445">
+        <v>0.4445279315095363</v>
+      </c>
+      <c r="G445">
+        <v>44.45</v>
+      </c>
+      <c r="H445" t="s">
+        <v>16</v>
+      </c>
+      <c r="I445">
+        <v>12</v>
+      </c>
+      <c r="J445">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K445">
+        <v>1384.320007324219</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11">
+      <c r="A446" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B446" t="s">
+        <v>17</v>
+      </c>
+      <c r="C446" t="s">
+        <v>28</v>
+      </c>
+      <c r="D446">
+        <v>19.7444</v>
+      </c>
+      <c r="E446">
+        <v>20.51799964904785</v>
+      </c>
+      <c r="F446">
+        <v>0.039180711951128</v>
+      </c>
+      <c r="G446">
+        <v>3.92</v>
+      </c>
+      <c r="H446" t="s">
+        <v>17</v>
+      </c>
+      <c r="I446">
+        <v>61</v>
+      </c>
+      <c r="J446">
+        <v>1204.4084</v>
+      </c>
+      <c r="K446">
+        <v>1251.597978591919</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11">
+      <c r="A447" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B447" t="s">
+        <v>18</v>
+      </c>
+      <c r="C447" t="s">
+        <v>29</v>
+      </c>
+      <c r="D447">
+        <v>129.871</v>
+      </c>
+      <c r="E447">
+        <v>146.5700073242188</v>
+      </c>
+      <c r="F447">
+        <v>0.1285814949004684</v>
+      </c>
+      <c r="G447">
+        <v>12.86</v>
+      </c>
+      <c r="H447" t="s">
+        <v>18</v>
+      </c>
+      <c r="I447">
+        <v>51</v>
+      </c>
+      <c r="J447">
+        <v>6623.421</v>
+      </c>
+      <c r="K447">
+        <v>7475.070373535156</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11">
+      <c r="A448" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B448" t="s">
+        <v>19</v>
+      </c>
+      <c r="C448" t="s">
+        <v>30</v>
+      </c>
+      <c r="D448">
+        <v>34.0694</v>
+      </c>
+      <c r="E448">
+        <v>33.79999923706055</v>
+      </c>
+      <c r="F448">
+        <v>-0.007907411429008301</v>
+      </c>
+      <c r="G448">
+        <v>-0.79</v>
+      </c>
+      <c r="H448" t="s">
+        <v>19</v>
+      </c>
+      <c r="I448">
+        <v>34</v>
+      </c>
+      <c r="J448">
+        <v>1158.3596</v>
+      </c>
+      <c r="K448">
+        <v>1149.199974060059</v>
+      </c>
+    </row>
+    <row r="449" spans="1:11">
+      <c r="A449" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B449" t="s">
+        <v>20</v>
+      </c>
+      <c r="C449" t="s">
+        <v>31</v>
+      </c>
+      <c r="D449">
+        <v>69.4158</v>
+      </c>
+      <c r="E449">
+        <v>71.76999664306641</v>
+      </c>
+      <c r="F449">
+        <v>0.0339144206803985</v>
+      </c>
+      <c r="G449">
+        <v>3.39</v>
+      </c>
+      <c r="H449" t="s">
+        <v>20</v>
+      </c>
+      <c r="I449">
+        <v>62</v>
+      </c>
+      <c r="J449">
+        <v>4303.7796</v>
+      </c>
+      <c r="K449">
+        <v>4449.739791870117</v>
+      </c>
+    </row>
+    <row r="450" spans="1:11">
+      <c r="A450" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B450" t="s">
+        <v>21</v>
+      </c>
+      <c r="C450" t="s">
+        <v>32</v>
+      </c>
+      <c r="D450">
+        <v>8.1868</v>
+      </c>
+      <c r="E450">
+        <v>8.468999862670898</v>
+      </c>
+      <c r="F450">
+        <v>0.0344701058619849</v>
+      </c>
+      <c r="G450">
+        <v>3.45</v>
+      </c>
+      <c r="H450" t="s">
+        <v>21</v>
+      </c>
+      <c r="I450">
+        <v>431</v>
+      </c>
+      <c r="J450">
+        <v>3528.5108</v>
+      </c>
+      <c r="K450">
+        <v>3650.138940811157</v>
       </c>
     </row>
   </sheetData>
@@ -19321,7 +19778,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -21001,6 +21458,47 @@
       </c>
       <c r="M41" s="2">
         <v>0.09386687305062402</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.0651088841832372</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.0507635414920166</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.1598254484793049</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.1206791078848534</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.00961633630701</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0.4445279315095363</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0.039180711951128</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0.1285814949004684</v>
+      </c>
+      <c r="J42" s="2">
+        <v>-0.007907411429008301</v>
+      </c>
+      <c r="K42" s="2">
+        <v>0.0339144206803985</v>
+      </c>
+      <c r="L42" s="2">
+        <v>0.0344701058619849</v>
+      </c>
+      <c r="M42" s="2">
+        <v>0.09174206280623287</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -347,16 +347,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$42</c:f>
+              <c:f>grafico_dati!$B$2:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -479,6 +482,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.0651088841832372</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.0649091211269066</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -506,10 +512,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -632,16 +638,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$42</c:f>
+              <c:f>grafico_dati!$C$2:$C$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -764,6 +773,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.0507635414920166</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.0531985243145118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -791,10 +803,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -917,16 +929,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$42</c:f>
+              <c:f>grafico_dati!$D$2:$D$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1049,6 +1064,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.1598254484793049</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.1595642115359452</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1076,10 +1094,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1202,16 +1220,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$42</c:f>
+              <c:f>grafico_dati!$E$2:$E$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1334,6 +1355,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.1206791078848534</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.1242032197212057</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1361,10 +1385,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1487,16 +1511,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$42</c:f>
+              <c:f>grafico_dati!$F$2:$F$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1616,6 +1643,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.00961633630701</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.0077942864520066</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1643,10 +1673,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1769,16 +1799,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$42</c:f>
+              <c:f>grafico_dati!$G$2:$G$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1901,6 +1934,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.4445279315095363</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.4477836557298025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1928,10 +1964,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2054,16 +2090,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$42</c:f>
+              <c:f>grafico_dati!$H$2:$H$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2186,6 +2225,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.039180711951128</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.0442454584853213</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2213,10 +2255,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2339,16 +2381,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$42</c:f>
+              <c:f>grafico_dati!$I$2:$I$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2468,6 +2513,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.1285814949004684</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.1270414112248885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2495,10 +2543,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2621,16 +2669,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$42</c:f>
+              <c:f>grafico_dati!$J$2:$J$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2753,6 +2804,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>-0.007907411429008301</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.009962032139212</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2780,10 +2834,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2906,16 +2960,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$42</c:f>
+              <c:f>grafico_dati!$K$2:$K$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3065,10 +3122,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3191,16 +3248,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$42</c:f>
+              <c:f>grafico_dati!$L$2:$L$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3323,6 +3383,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.0344701058619849</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.0363023655144443</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3354,10 +3417,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$42</c:f>
+              <c:f>grafico_dati!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3480,16 +3543,19 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$42</c:f>
+              <c:f>grafico_dati!$M$2:$M$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3612,6 +3678,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.09174206280623287</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.1043830270766006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4018,7 +4087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K450"/>
+  <dimension ref="A1:K460"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -19769,6 +19838,356 @@
       </c>
       <c r="K450">
         <v>3650.138940811157</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11">
+      <c r="A451" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B451" t="s">
+        <v>11</v>
+      </c>
+      <c r="C451" t="s">
+        <v>22</v>
+      </c>
+      <c r="D451">
+        <v>50.07</v>
+      </c>
+      <c r="E451">
+        <v>53.31999969482422</v>
+      </c>
+      <c r="F451">
+        <v>0.0649091211269066</v>
+      </c>
+      <c r="G451">
+        <v>6.49</v>
+      </c>
+      <c r="H451" t="s">
+        <v>11</v>
+      </c>
+      <c r="I451">
+        <v>23</v>
+      </c>
+      <c r="J451">
+        <v>1151.61</v>
+      </c>
+      <c r="K451">
+        <v>1226.359992980957</v>
+      </c>
+    </row>
+    <row r="452" spans="1:11">
+      <c r="A452" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B452" t="s">
+        <v>12</v>
+      </c>
+      <c r="C452" t="s">
+        <v>23</v>
+      </c>
+      <c r="D452">
+        <v>242.3</v>
+      </c>
+      <c r="E452">
+        <v>255.1900024414062</v>
+      </c>
+      <c r="F452">
+        <v>0.0531985243145118</v>
+      </c>
+      <c r="G452">
+        <v>5.32</v>
+      </c>
+      <c r="H452" t="s">
+        <v>12</v>
+      </c>
+      <c r="I452">
+        <v>5</v>
+      </c>
+      <c r="J452">
+        <v>1211.5</v>
+      </c>
+      <c r="K452">
+        <v>1275.950012207031</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11">
+      <c r="A453" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B453" t="s">
+        <v>13</v>
+      </c>
+      <c r="C453" t="s">
+        <v>24</v>
+      </c>
+      <c r="D453">
+        <v>38.273</v>
+      </c>
+      <c r="E453">
+        <v>44.38000106811523</v>
+      </c>
+      <c r="F453">
+        <v>0.1595642115359452</v>
+      </c>
+      <c r="G453">
+        <v>15.96</v>
+      </c>
+      <c r="H453" t="s">
+        <v>13</v>
+      </c>
+      <c r="I453">
+        <v>54</v>
+      </c>
+      <c r="J453">
+        <v>2066.742</v>
+      </c>
+      <c r="K453">
+        <v>2396.520057678223</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11">
+      <c r="A454" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B454" t="s">
+        <v>14</v>
+      </c>
+      <c r="C454" t="s">
+        <v>25</v>
+      </c>
+      <c r="D454">
+        <v>6.5264</v>
+      </c>
+      <c r="E454">
+        <v>7.336999893188477</v>
+      </c>
+      <c r="F454">
+        <v>0.1242032197212057</v>
+      </c>
+      <c r="G454">
+        <v>12.42</v>
+      </c>
+      <c r="H454" t="s">
+        <v>14</v>
+      </c>
+      <c r="I454">
+        <v>276</v>
+      </c>
+      <c r="J454">
+        <v>1801.2864</v>
+      </c>
+      <c r="K454">
+        <v>2025.01197052002</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11">
+      <c r="A455" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B455" t="s">
+        <v>15</v>
+      </c>
+      <c r="C455" t="s">
+        <v>26</v>
+      </c>
+      <c r="D455">
+        <v>197.58</v>
+      </c>
+      <c r="E455">
+        <v>199.1199951171875</v>
+      </c>
+      <c r="F455">
+        <v>0.0077942864520066</v>
+      </c>
+      <c r="G455">
+        <v>0.78</v>
+      </c>
+      <c r="H455" t="s">
+        <v>15</v>
+      </c>
+      <c r="I455">
+        <v>4</v>
+      </c>
+      <c r="J455">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K455">
+        <v>796.47998046875</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11">
+      <c r="A456" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B456" t="s">
+        <v>16</v>
+      </c>
+      <c r="C456" t="s">
+        <v>27</v>
+      </c>
+      <c r="D456">
+        <v>79.86</v>
+      </c>
+      <c r="E456">
+        <v>115.620002746582</v>
+      </c>
+      <c r="F456">
+        <v>0.4477836557298025</v>
+      </c>
+      <c r="G456">
+        <v>44.78</v>
+      </c>
+      <c r="H456" t="s">
+        <v>16</v>
+      </c>
+      <c r="I456">
+        <v>12</v>
+      </c>
+      <c r="J456">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K456">
+        <v>1387.440032958985</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11">
+      <c r="A457" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B457" t="s">
+        <v>17</v>
+      </c>
+      <c r="C457" t="s">
+        <v>28</v>
+      </c>
+      <c r="D457">
+        <v>19.7444</v>
+      </c>
+      <c r="E457">
+        <v>20.61800003051757</v>
+      </c>
+      <c r="F457">
+        <v>0.0442454584853213</v>
+      </c>
+      <c r="G457">
+        <v>4.42</v>
+      </c>
+      <c r="H457" t="s">
+        <v>17</v>
+      </c>
+      <c r="I457">
+        <v>61</v>
+      </c>
+      <c r="J457">
+        <v>1204.4084</v>
+      </c>
+      <c r="K457">
+        <v>1257.698001861572</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11">
+      <c r="A458" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B458" t="s">
+        <v>18</v>
+      </c>
+      <c r="C458" t="s">
+        <v>29</v>
+      </c>
+      <c r="D458">
+        <v>129.871</v>
+      </c>
+      <c r="E458">
+        <v>146.3699951171875</v>
+      </c>
+      <c r="F458">
+        <v>0.1270414112248885</v>
+      </c>
+      <c r="G458">
+        <v>12.7</v>
+      </c>
+      <c r="H458" t="s">
+        <v>18</v>
+      </c>
+      <c r="I458">
+        <v>51</v>
+      </c>
+      <c r="J458">
+        <v>6623.421</v>
+      </c>
+      <c r="K458">
+        <v>7464.869750976562</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11">
+      <c r="A459" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B459" t="s">
+        <v>19</v>
+      </c>
+      <c r="C459" t="s">
+        <v>30</v>
+      </c>
+      <c r="D459">
+        <v>34.0694</v>
+      </c>
+      <c r="E459">
+        <v>33.72999954223633</v>
+      </c>
+      <c r="F459">
+        <v>-0.009962032139212</v>
+      </c>
+      <c r="G459">
+        <v>-1</v>
+      </c>
+      <c r="H459" t="s">
+        <v>19</v>
+      </c>
+      <c r="I459">
+        <v>34</v>
+      </c>
+      <c r="J459">
+        <v>1158.3596</v>
+      </c>
+      <c r="K459">
+        <v>1146.819984436035</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11">
+      <c r="A460" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B460" t="s">
+        <v>21</v>
+      </c>
+      <c r="C460" t="s">
+        <v>32</v>
+      </c>
+      <c r="D460">
+        <v>8.1868</v>
+      </c>
+      <c r="E460">
+        <v>8.484000205993652</v>
+      </c>
+      <c r="F460">
+        <v>0.0363023655144443</v>
+      </c>
+      <c r="G460">
+        <v>3.63</v>
+      </c>
+      <c r="H460" t="s">
+        <v>21</v>
+      </c>
+      <c r="I460">
+        <v>431</v>
+      </c>
+      <c r="J460">
+        <v>3528.5108</v>
+      </c>
+      <c r="K460">
+        <v>3656.604088783264</v>
       </c>
     </row>
   </sheetData>
@@ -19778,7 +20197,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -21499,6 +21918,44 @@
       </c>
       <c r="M42" s="2">
         <v>0.09174206280623287</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.0649091211269066</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.0531985243145118</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.1595642115359452</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.1242032197212057</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0.0077942864520066</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.4477836557298025</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0.0442454584853213</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0.1270414112248885</v>
+      </c>
+      <c r="J43" s="2">
+        <v>-0.009962032139212</v>
+      </c>
+      <c r="L43" s="2">
+        <v>0.0363023655144443</v>
+      </c>
+      <c r="M43" s="2">
+        <v>0.1043830270766006</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -350,16 +350,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$43</c:f>
+              <c:f>grafico_dati!$B$2:$B$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -485,6 +488,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.0649091211269066</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.0621130478365443</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -512,10 +518,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -641,16 +647,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$43</c:f>
+              <c:f>grafico_dati!$C$2:$C$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -776,6 +785,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.0531985243145118</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.047626893676808</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -803,10 +815,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -932,16 +944,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$43</c:f>
+              <c:f>grafico_dati!$D$2:$D$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1067,6 +1082,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.1595642115359452</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.1450631192469744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1094,10 +1112,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1223,16 +1241,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$43</c:f>
+              <c:f>grafico_dati!$E$2:$E$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1358,6 +1379,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.1242032197212057</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.107655076543383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1385,10 +1409,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1514,16 +1538,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$43</c:f>
+              <c:f>grafico_dati!$F$2:$F$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1646,6 +1673,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.0077942864520066</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.0042514331862804</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1673,10 +1703,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1802,16 +1832,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$43</c:f>
+              <c:f>grafico_dati!$G$2:$G$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1937,6 +1970,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.4477836557298025</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.4505383964173632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1964,10 +2000,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2093,16 +2129,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$43</c:f>
+              <c:f>grafico_dati!$H$2:$H$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2228,6 +2267,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.0442454584853213</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.0439415485767484</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2255,10 +2297,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2384,16 +2426,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$43</c:f>
+              <c:f>grafico_dati!$I$2:$I$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2516,6 +2561,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.1270414112248885</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.1237304898045463</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2543,10 +2591,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2672,16 +2720,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$43</c:f>
+              <c:f>grafico_dati!$J$2:$J$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2807,6 +2858,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>-0.009962032139212</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.0161258942698236</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2834,10 +2888,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2963,16 +3017,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$43</c:f>
+              <c:f>grafico_dati!$K$2:$K$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3095,6 +3152,9 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>0.0339144206803985</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.0265674693114603</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3122,10 +3182,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3251,16 +3311,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$43</c:f>
+              <c:f>grafico_dati!$L$2:$L$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3386,6 +3449,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.0363023655144443</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.0301949498288451</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3417,10 +3483,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$43</c:f>
+              <c:f>grafico_dati!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3546,16 +3612,19 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$43</c:f>
+              <c:f>grafico_dati!$M$2:$M$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="42"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3681,6 +3750,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0.1043830270766006</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.08600291481845979</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4087,7 +4159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K460"/>
+  <dimension ref="A1:K471"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -20188,6 +20260,391 @@
       </c>
       <c r="K460">
         <v>3656.604088783264</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11">
+      <c r="A461" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B461" t="s">
+        <v>11</v>
+      </c>
+      <c r="C461" t="s">
+        <v>22</v>
+      </c>
+      <c r="D461">
+        <v>50.07</v>
+      </c>
+      <c r="E461">
+        <v>53.18000030517578</v>
+      </c>
+      <c r="F461">
+        <v>0.0621130478365443</v>
+      </c>
+      <c r="G461">
+        <v>6.21</v>
+      </c>
+      <c r="H461" t="s">
+        <v>11</v>
+      </c>
+      <c r="I461">
+        <v>23</v>
+      </c>
+      <c r="J461">
+        <v>1151.61</v>
+      </c>
+      <c r="K461">
+        <v>1223.140007019043</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11">
+      <c r="A462" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B462" t="s">
+        <v>12</v>
+      </c>
+      <c r="C462" t="s">
+        <v>23</v>
+      </c>
+      <c r="D462">
+        <v>242.3</v>
+      </c>
+      <c r="E462">
+        <v>253.8399963378907</v>
+      </c>
+      <c r="F462">
+        <v>0.047626893676808</v>
+      </c>
+      <c r="G462">
+        <v>4.76</v>
+      </c>
+      <c r="H462" t="s">
+        <v>12</v>
+      </c>
+      <c r="I462">
+        <v>5</v>
+      </c>
+      <c r="J462">
+        <v>1211.5</v>
+      </c>
+      <c r="K462">
+        <v>1269.199981689453</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11">
+      <c r="A463" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B463" t="s">
+        <v>13</v>
+      </c>
+      <c r="C463" t="s">
+        <v>24</v>
+      </c>
+      <c r="D463">
+        <v>38.273</v>
+      </c>
+      <c r="E463">
+        <v>43.82500076293945</v>
+      </c>
+      <c r="F463">
+        <v>0.1450631192469744</v>
+      </c>
+      <c r="G463">
+        <v>14.51</v>
+      </c>
+      <c r="H463" t="s">
+        <v>13</v>
+      </c>
+      <c r="I463">
+        <v>54</v>
+      </c>
+      <c r="J463">
+        <v>2066.742</v>
+      </c>
+      <c r="K463">
+        <v>2366.55004119873</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11">
+      <c r="A464" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B464" t="s">
+        <v>14</v>
+      </c>
+      <c r="C464" t="s">
+        <v>25</v>
+      </c>
+      <c r="D464">
+        <v>6.5264</v>
+      </c>
+      <c r="E464">
+        <v>7.229000091552734</v>
+      </c>
+      <c r="F464">
+        <v>0.107655076543383</v>
+      </c>
+      <c r="G464">
+        <v>10.77</v>
+      </c>
+      <c r="H464" t="s">
+        <v>14</v>
+      </c>
+      <c r="I464">
+        <v>276</v>
+      </c>
+      <c r="J464">
+        <v>1801.2864</v>
+      </c>
+      <c r="K464">
+        <v>1995.204025268555</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11">
+      <c r="A465" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B465" t="s">
+        <v>15</v>
+      </c>
+      <c r="C465" t="s">
+        <v>26</v>
+      </c>
+      <c r="D465">
+        <v>197.58</v>
+      </c>
+      <c r="E465">
+        <v>198.4199981689453</v>
+      </c>
+      <c r="F465">
+        <v>0.0042514331862804</v>
+      </c>
+      <c r="G465">
+        <v>0.43</v>
+      </c>
+      <c r="H465" t="s">
+        <v>15</v>
+      </c>
+      <c r="I465">
+        <v>4</v>
+      </c>
+      <c r="J465">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K465">
+        <v>793.6799926757812</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11">
+      <c r="A466" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B466" t="s">
+        <v>16</v>
+      </c>
+      <c r="C466" t="s">
+        <v>27</v>
+      </c>
+      <c r="D466">
+        <v>79.86</v>
+      </c>
+      <c r="E466">
+        <v>115.8399963378906</v>
+      </c>
+      <c r="F466">
+        <v>0.4505383964173632</v>
+      </c>
+      <c r="G466">
+        <v>45.05</v>
+      </c>
+      <c r="H466" t="s">
+        <v>16</v>
+      </c>
+      <c r="I466">
+        <v>12</v>
+      </c>
+      <c r="J466">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K466">
+        <v>1390.079956054688</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11">
+      <c r="A467" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B467" t="s">
+        <v>17</v>
+      </c>
+      <c r="C467" t="s">
+        <v>28</v>
+      </c>
+      <c r="D467">
+        <v>19.7444</v>
+      </c>
+      <c r="E467">
+        <v>20.61199951171875</v>
+      </c>
+      <c r="F467">
+        <v>0.0439415485767484</v>
+      </c>
+      <c r="G467">
+        <v>4.39</v>
+      </c>
+      <c r="H467" t="s">
+        <v>17</v>
+      </c>
+      <c r="I467">
+        <v>61</v>
+      </c>
+      <c r="J467">
+        <v>1204.4084</v>
+      </c>
+      <c r="K467">
+        <v>1257.331970214844</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11">
+      <c r="A468" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B468" t="s">
+        <v>18</v>
+      </c>
+      <c r="C468" t="s">
+        <v>29</v>
+      </c>
+      <c r="D468">
+        <v>129.871</v>
+      </c>
+      <c r="E468">
+        <v>145.9400024414062</v>
+      </c>
+      <c r="F468">
+        <v>0.1237304898045463</v>
+      </c>
+      <c r="G468">
+        <v>12.37</v>
+      </c>
+      <c r="H468" t="s">
+        <v>18</v>
+      </c>
+      <c r="I468">
+        <v>51</v>
+      </c>
+      <c r="J468">
+        <v>6623.421</v>
+      </c>
+      <c r="K468">
+        <v>7442.940124511719</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11">
+      <c r="A469" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B469" t="s">
+        <v>19</v>
+      </c>
+      <c r="C469" t="s">
+        <v>30</v>
+      </c>
+      <c r="D469">
+        <v>34.0694</v>
+      </c>
+      <c r="E469">
+        <v>33.52000045776367</v>
+      </c>
+      <c r="F469">
+        <v>-0.0161258942698236</v>
+      </c>
+      <c r="G469">
+        <v>-1.61</v>
+      </c>
+      <c r="H469" t="s">
+        <v>19</v>
+      </c>
+      <c r="I469">
+        <v>34</v>
+      </c>
+      <c r="J469">
+        <v>1158.3596</v>
+      </c>
+      <c r="K469">
+        <v>1139.680015563965</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11">
+      <c r="A470" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B470" t="s">
+        <v>20</v>
+      </c>
+      <c r="C470" t="s">
+        <v>31</v>
+      </c>
+      <c r="D470">
+        <v>69.4158</v>
+      </c>
+      <c r="E470">
+        <v>71.26000213623047</v>
+      </c>
+      <c r="F470">
+        <v>0.0265674693114603</v>
+      </c>
+      <c r="G470">
+        <v>2.66</v>
+      </c>
+      <c r="H470" t="s">
+        <v>20</v>
+      </c>
+      <c r="I470">
+        <v>62</v>
+      </c>
+      <c r="J470">
+        <v>4303.7796</v>
+      </c>
+      <c r="K470">
+        <v>4418.120132446289</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11">
+      <c r="A471" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B471" t="s">
+        <v>21</v>
+      </c>
+      <c r="C471" t="s">
+        <v>32</v>
+      </c>
+      <c r="D471">
+        <v>8.1868</v>
+      </c>
+      <c r="E471">
+        <v>8.434000015258789</v>
+      </c>
+      <c r="F471">
+        <v>0.0301949498288451</v>
+      </c>
+      <c r="G471">
+        <v>3.02</v>
+      </c>
+      <c r="H471" t="s">
+        <v>21</v>
+      </c>
+      <c r="I471">
+        <v>431</v>
+      </c>
+      <c r="J471">
+        <v>3528.5108</v>
+      </c>
+      <c r="K471">
+        <v>3635.054006576538</v>
       </c>
     </row>
   </sheetData>
@@ -20197,7 +20654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -21956,6 +22413,47 @@
       </c>
       <c r="M43" s="2">
         <v>0.1043830270766006</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.0621130478365443</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.047626893676808</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.1450631192469744</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.107655076543383</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0.0042514331862804</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0.4505383964173632</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0.0439415485767484</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0.1237304898045463</v>
+      </c>
+      <c r="J44" s="2">
+        <v>-0.0161258942698236</v>
+      </c>
+      <c r="K44" s="2">
+        <v>0.0265674693114603</v>
+      </c>
+      <c r="L44" s="2">
+        <v>0.0301949498288451</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0.08600291481845979</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -353,16 +353,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$44</c:f>
+              <c:f>grafico_dati!$B$2:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -491,6 +494,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.0621130478365443</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.0511284415441428</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -518,10 +524,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -650,16 +656,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$44</c:f>
+              <c:f>grafico_dati!$C$2:$C$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -788,6 +797,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.047626893676808</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.0411473556436687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -815,10 +827,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -947,16 +959,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$44</c:f>
+              <c:f>grafico_dati!$D$2:$D$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1085,6 +1100,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.1450631192469744</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.1501580868435625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1112,10 +1130,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1244,16 +1262,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$44</c:f>
+              <c:f>grafico_dati!$E$2:$E$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1382,6 +1403,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.107655076543383</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.1119453250616606</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1409,10 +1433,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1541,16 +1565,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$44</c:f>
+              <c:f>grafico_dati!$F$2:$F$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1676,6 +1703,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.0042514331862804</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.0017208126781318</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1703,10 +1733,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1835,16 +1865,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$44</c:f>
+              <c:f>grafico_dati!$G$2:$G$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -1973,6 +2006,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.4505383964173632</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.4450288195076246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2000,10 +2036,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2132,16 +2168,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$44</c:f>
+              <c:f>grafico_dati!$H$2:$H$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2270,6 +2309,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.0439415485767484</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.039180711951128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2297,10 +2339,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2429,16 +2471,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$44</c:f>
+              <c:f>grafico_dati!$I$2:$I$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2564,6 +2609,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.1237304898045463</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.1242694250974885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2591,10 +2639,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2723,16 +2771,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$44</c:f>
+              <c:f>grafico_dati!$J$2:$J$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2861,6 +2912,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>-0.0161258942698236</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-0.0224365470135728</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2888,10 +2942,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3020,16 +3074,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$44</c:f>
+              <c:f>grafico_dati!$K$2:$K$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3155,6 +3212,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.0265674693114603</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.0261353086319482</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3182,10 +3242,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3314,16 +3374,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$44</c:f>
+              <c:f>grafico_dati!$L$2:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3452,6 +3515,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.0301949498288451</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.0261640717848468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3483,10 +3549,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$44</c:f>
+              <c:f>grafico_dati!$A$2:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3615,16 +3681,19 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$44</c:f>
+              <c:f>grafico_dati!$M$2:$M$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3753,6 +3822,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>0.08600291481845979</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.08458832942783934</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4159,7 +4231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K471"/>
+  <dimension ref="A1:K482"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -20645,6 +20717,391 @@
       </c>
       <c r="K471">
         <v>3635.054006576538</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11">
+      <c r="A472" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B472" t="s">
+        <v>11</v>
+      </c>
+      <c r="C472" t="s">
+        <v>22</v>
+      </c>
+      <c r="D472">
+        <v>50.07</v>
+      </c>
+      <c r="E472">
+        <v>52.63000106811523</v>
+      </c>
+      <c r="F472">
+        <v>0.0511284415441428</v>
+      </c>
+      <c r="G472">
+        <v>5.11</v>
+      </c>
+      <c r="H472" t="s">
+        <v>11</v>
+      </c>
+      <c r="I472">
+        <v>23</v>
+      </c>
+      <c r="J472">
+        <v>1151.61</v>
+      </c>
+      <c r="K472">
+        <v>1210.49002456665</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11">
+      <c r="A473" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B473" t="s">
+        <v>12</v>
+      </c>
+      <c r="C473" t="s">
+        <v>23</v>
+      </c>
+      <c r="D473">
+        <v>242.3</v>
+      </c>
+      <c r="E473">
+        <v>252.2700042724609</v>
+      </c>
+      <c r="F473">
+        <v>0.0411473556436687</v>
+      </c>
+      <c r="G473">
+        <v>4.11</v>
+      </c>
+      <c r="H473" t="s">
+        <v>12</v>
+      </c>
+      <c r="I473">
+        <v>5</v>
+      </c>
+      <c r="J473">
+        <v>1211.5</v>
+      </c>
+      <c r="K473">
+        <v>1261.350021362304</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11">
+      <c r="A474" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B474" t="s">
+        <v>13</v>
+      </c>
+      <c r="C474" t="s">
+        <v>24</v>
+      </c>
+      <c r="D474">
+        <v>38.273</v>
+      </c>
+      <c r="E474">
+        <v>44.02000045776367</v>
+      </c>
+      <c r="F474">
+        <v>0.1501580868435625</v>
+      </c>
+      <c r="G474">
+        <v>15.02</v>
+      </c>
+      <c r="H474" t="s">
+        <v>13</v>
+      </c>
+      <c r="I474">
+        <v>54</v>
+      </c>
+      <c r="J474">
+        <v>2066.742</v>
+      </c>
+      <c r="K474">
+        <v>2377.080024719238</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11">
+      <c r="A475" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B475" t="s">
+        <v>14</v>
+      </c>
+      <c r="C475" t="s">
+        <v>25</v>
+      </c>
+      <c r="D475">
+        <v>6.5264</v>
+      </c>
+      <c r="E475">
+        <v>7.256999969482422</v>
+      </c>
+      <c r="F475">
+        <v>0.1119453250616606</v>
+      </c>
+      <c r="G475">
+        <v>11.19</v>
+      </c>
+      <c r="H475" t="s">
+        <v>14</v>
+      </c>
+      <c r="I475">
+        <v>276</v>
+      </c>
+      <c r="J475">
+        <v>1801.2864</v>
+      </c>
+      <c r="K475">
+        <v>2002.931991577148</v>
+      </c>
+    </row>
+    <row r="476" spans="1:11">
+      <c r="A476" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B476" t="s">
+        <v>15</v>
+      </c>
+      <c r="C476" t="s">
+        <v>26</v>
+      </c>
+      <c r="D476">
+        <v>197.58</v>
+      </c>
+      <c r="E476">
+        <v>197.9199981689453</v>
+      </c>
+      <c r="F476">
+        <v>0.0017208126781318</v>
+      </c>
+      <c r="G476">
+        <v>0.17</v>
+      </c>
+      <c r="H476" t="s">
+        <v>15</v>
+      </c>
+      <c r="I476">
+        <v>4</v>
+      </c>
+      <c r="J476">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K476">
+        <v>791.6799926757812</v>
+      </c>
+    </row>
+    <row r="477" spans="1:11">
+      <c r="A477" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B477" t="s">
+        <v>16</v>
+      </c>
+      <c r="C477" t="s">
+        <v>27</v>
+      </c>
+      <c r="D477">
+        <v>79.86</v>
+      </c>
+      <c r="E477">
+        <v>115.4000015258789</v>
+      </c>
+      <c r="F477">
+        <v>0.4450288195076246</v>
+      </c>
+      <c r="G477">
+        <v>44.5</v>
+      </c>
+      <c r="H477" t="s">
+        <v>16</v>
+      </c>
+      <c r="I477">
+        <v>12</v>
+      </c>
+      <c r="J477">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K477">
+        <v>1384.800018310547</v>
+      </c>
+    </row>
+    <row r="478" spans="1:11">
+      <c r="A478" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B478" t="s">
+        <v>17</v>
+      </c>
+      <c r="C478" t="s">
+        <v>28</v>
+      </c>
+      <c r="D478">
+        <v>19.7444</v>
+      </c>
+      <c r="E478">
+        <v>20.51799964904785</v>
+      </c>
+      <c r="F478">
+        <v>0.039180711951128</v>
+      </c>
+      <c r="G478">
+        <v>3.92</v>
+      </c>
+      <c r="H478" t="s">
+        <v>17</v>
+      </c>
+      <c r="I478">
+        <v>61</v>
+      </c>
+      <c r="J478">
+        <v>1204.4084</v>
+      </c>
+      <c r="K478">
+        <v>1251.597978591919</v>
+      </c>
+    </row>
+    <row r="479" spans="1:11">
+      <c r="A479" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B479" t="s">
+        <v>18</v>
+      </c>
+      <c r="C479" t="s">
+        <v>29</v>
+      </c>
+      <c r="D479">
+        <v>129.871</v>
+      </c>
+      <c r="E479">
+        <v>146.0099945068359</v>
+      </c>
+      <c r="F479">
+        <v>0.1242694250974885</v>
+      </c>
+      <c r="G479">
+        <v>12.43</v>
+      </c>
+      <c r="H479" t="s">
+        <v>18</v>
+      </c>
+      <c r="I479">
+        <v>51</v>
+      </c>
+      <c r="J479">
+        <v>6623.421</v>
+      </c>
+      <c r="K479">
+        <v>7446.509719848633</v>
+      </c>
+    </row>
+    <row r="480" spans="1:11">
+      <c r="A480" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B480" t="s">
+        <v>19</v>
+      </c>
+      <c r="C480" t="s">
+        <v>30</v>
+      </c>
+      <c r="D480">
+        <v>34.0694</v>
+      </c>
+      <c r="E480">
+        <v>33.30500030517578</v>
+      </c>
+      <c r="F480">
+        <v>-0.0224365470135728</v>
+      </c>
+      <c r="G480">
+        <v>-2.24</v>
+      </c>
+      <c r="H480" t="s">
+        <v>19</v>
+      </c>
+      <c r="I480">
+        <v>34</v>
+      </c>
+      <c r="J480">
+        <v>1158.3596</v>
+      </c>
+      <c r="K480">
+        <v>1132.370010375977</v>
+      </c>
+    </row>
+    <row r="481" spans="1:11">
+      <c r="A481" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B481" t="s">
+        <v>20</v>
+      </c>
+      <c r="C481" t="s">
+        <v>31</v>
+      </c>
+      <c r="D481">
+        <v>69.4158</v>
+      </c>
+      <c r="E481">
+        <v>71.23000335693359</v>
+      </c>
+      <c r="F481">
+        <v>0.0261353086319482</v>
+      </c>
+      <c r="G481">
+        <v>2.61</v>
+      </c>
+      <c r="H481" t="s">
+        <v>20</v>
+      </c>
+      <c r="I481">
+        <v>62</v>
+      </c>
+      <c r="J481">
+        <v>4303.7796</v>
+      </c>
+      <c r="K481">
+        <v>4416.260208129883</v>
+      </c>
+    </row>
+    <row r="482" spans="1:11">
+      <c r="A482" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B482" t="s">
+        <v>21</v>
+      </c>
+      <c r="C482" t="s">
+        <v>32</v>
+      </c>
+      <c r="D482">
+        <v>8.1868</v>
+      </c>
+      <c r="E482">
+        <v>8.401000022888184</v>
+      </c>
+      <c r="F482">
+        <v>0.0261640717848468</v>
+      </c>
+      <c r="G482">
+        <v>2.62</v>
+      </c>
+      <c r="H482" t="s">
+        <v>21</v>
+      </c>
+      <c r="I482">
+        <v>431</v>
+      </c>
+      <c r="J482">
+        <v>3528.5108</v>
+      </c>
+      <c r="K482">
+        <v>3620.831009864807</v>
       </c>
     </row>
   </sheetData>
@@ -20654,7 +21111,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -22454,6 +22911,47 @@
       </c>
       <c r="M44" s="2">
         <v>0.08600291481845979</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.0511284415441428</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.0411473556436687</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.1501580868435625</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.1119453250616606</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.0017208126781318</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.4450288195076246</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0.039180711951128</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0.1242694250974885</v>
+      </c>
+      <c r="J45" s="2">
+        <v>-0.0224365470135728</v>
+      </c>
+      <c r="K45" s="2">
+        <v>0.0261353086319482</v>
+      </c>
+      <c r="L45" s="2">
+        <v>0.0261640717848468</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0.08458832942783934</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -356,16 +356,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$45</c:f>
+              <c:f>grafico_dati!$B$2:$B$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -497,6 +500,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.0511284415441428</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.0738965539797018</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -524,10 +530,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -659,16 +665,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$45</c:f>
+              <c:f>grafico_dati!$C$2:$C$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -800,6 +809,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.0411473556436687</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.0541477431652714</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -827,10 +839,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -962,16 +974,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$45</c:f>
+              <c:f>grafico_dati!$D$2:$D$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1103,6 +1118,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.1501580868435625</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.1573432489991719</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1130,10 +1148,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1265,16 +1283,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$45</c:f>
+              <c:f>grafico_dati!$E$2:$E$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1406,6 +1427,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.1119453250616606</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.1180742723914332</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,10 +1457,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1568,16 +1592,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$45</c:f>
+              <c:f>grafico_dati!$F$2:$F$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1706,6 +1733,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.0017208126781318</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.0152849787605811</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1733,10 +1763,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1868,16 +1898,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$45</c:f>
+              <c:f>grafico_dati!$G$2:$G$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2009,6 +2042,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.4450288195076246</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.4593037930819852</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2036,10 +2072,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2171,16 +2207,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$45</c:f>
+              <c:f>grafico_dati!$H$2:$H$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2312,6 +2351,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.039180711951128</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.056805941016276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2339,10 +2381,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2474,16 +2516,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$45</c:f>
+              <c:f>grafico_dati!$I$2:$I$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2612,6 +2657,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.1242694250974885</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.1315844700808277</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2639,10 +2687,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2774,16 +2822,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$45</c:f>
+              <c:f>grafico_dati!$J$2:$J$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2915,6 +2966,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>-0.0224365470135728</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-0.0067333104607686</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2942,10 +2996,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3077,16 +3131,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$45</c:f>
+              <c:f>grafico_dati!$K$2:$K$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3215,6 +3272,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.0261353086319482</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.030745205727771</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3242,10 +3302,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3377,16 +3437,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$45</c:f>
+              <c:f>grafico_dati!$L$2:$L$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3518,6 +3581,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.0261640717848468</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.0367909214927273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3549,10 +3615,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$45</c:f>
+              <c:f>grafico_dati!$A$2:$A$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3684,16 +3750,19 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$45</c:f>
+              <c:f>grafico_dati!$M$2:$M$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3825,6 +3894,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>0.08458832942783934</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.09416421875041814</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4231,7 +4303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K482"/>
+  <dimension ref="A1:K493"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -21102,6 +21174,391 @@
       </c>
       <c r="K482">
         <v>3620.831009864807</v>
+      </c>
+    </row>
+    <row r="483" spans="1:11">
+      <c r="A483" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B483" t="s">
+        <v>11</v>
+      </c>
+      <c r="C483" t="s">
+        <v>22</v>
+      </c>
+      <c r="D483">
+        <v>50.07</v>
+      </c>
+      <c r="E483">
+        <v>53.77000045776367</v>
+      </c>
+      <c r="F483">
+        <v>0.0738965539797018</v>
+      </c>
+      <c r="G483">
+        <v>7.39</v>
+      </c>
+      <c r="H483" t="s">
+        <v>11</v>
+      </c>
+      <c r="I483">
+        <v>23</v>
+      </c>
+      <c r="J483">
+        <v>1151.61</v>
+      </c>
+      <c r="K483">
+        <v>1236.710010528564</v>
+      </c>
+    </row>
+    <row r="484" spans="1:11">
+      <c r="A484" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B484" t="s">
+        <v>12</v>
+      </c>
+      <c r="C484" t="s">
+        <v>23</v>
+      </c>
+      <c r="D484">
+        <v>242.3</v>
+      </c>
+      <c r="E484">
+        <v>255.4199981689453</v>
+      </c>
+      <c r="F484">
+        <v>0.0541477431652714</v>
+      </c>
+      <c r="G484">
+        <v>5.41</v>
+      </c>
+      <c r="H484" t="s">
+        <v>12</v>
+      </c>
+      <c r="I484">
+        <v>5</v>
+      </c>
+      <c r="J484">
+        <v>1211.5</v>
+      </c>
+      <c r="K484">
+        <v>1277.099990844727</v>
+      </c>
+    </row>
+    <row r="485" spans="1:11">
+      <c r="A485" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B485" t="s">
+        <v>13</v>
+      </c>
+      <c r="C485" t="s">
+        <v>24</v>
+      </c>
+      <c r="D485">
+        <v>38.273</v>
+      </c>
+      <c r="E485">
+        <v>44.29499816894531</v>
+      </c>
+      <c r="F485">
+        <v>0.1573432489991719</v>
+      </c>
+      <c r="G485">
+        <v>15.73</v>
+      </c>
+      <c r="H485" t="s">
+        <v>13</v>
+      </c>
+      <c r="I485">
+        <v>54</v>
+      </c>
+      <c r="J485">
+        <v>2066.742</v>
+      </c>
+      <c r="K485">
+        <v>2391.929901123047</v>
+      </c>
+    </row>
+    <row r="486" spans="1:11">
+      <c r="A486" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B486" t="s">
+        <v>14</v>
+      </c>
+      <c r="C486" t="s">
+        <v>25</v>
+      </c>
+      <c r="D486">
+        <v>6.5264</v>
+      </c>
+      <c r="E486">
+        <v>7.296999931335449</v>
+      </c>
+      <c r="F486">
+        <v>0.1180742723914332</v>
+      </c>
+      <c r="G486">
+        <v>11.81</v>
+      </c>
+      <c r="H486" t="s">
+        <v>14</v>
+      </c>
+      <c r="I486">
+        <v>276</v>
+      </c>
+      <c r="J486">
+        <v>1801.2864</v>
+      </c>
+      <c r="K486">
+        <v>2013.971981048584</v>
+      </c>
+    </row>
+    <row r="487" spans="1:11">
+      <c r="A487" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B487" t="s">
+        <v>15</v>
+      </c>
+      <c r="C487" t="s">
+        <v>26</v>
+      </c>
+      <c r="D487">
+        <v>197.58</v>
+      </c>
+      <c r="E487">
+        <v>200.6000061035156</v>
+      </c>
+      <c r="F487">
+        <v>0.0152849787605811</v>
+      </c>
+      <c r="G487">
+        <v>1.53</v>
+      </c>
+      <c r="H487" t="s">
+        <v>15</v>
+      </c>
+      <c r="I487">
+        <v>4</v>
+      </c>
+      <c r="J487">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K487">
+        <v>802.4000244140624</v>
+      </c>
+    </row>
+    <row r="488" spans="1:11">
+      <c r="A488" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B488" t="s">
+        <v>16</v>
+      </c>
+      <c r="C488" t="s">
+        <v>27</v>
+      </c>
+      <c r="D488">
+        <v>79.86</v>
+      </c>
+      <c r="E488">
+        <v>116.5400009155273</v>
+      </c>
+      <c r="F488">
+        <v>0.4593037930819852</v>
+      </c>
+      <c r="G488">
+        <v>45.93</v>
+      </c>
+      <c r="H488" t="s">
+        <v>16</v>
+      </c>
+      <c r="I488">
+        <v>12</v>
+      </c>
+      <c r="J488">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K488">
+        <v>1398.480010986328</v>
+      </c>
+    </row>
+    <row r="489" spans="1:11">
+      <c r="A489" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B489" t="s">
+        <v>17</v>
+      </c>
+      <c r="C489" t="s">
+        <v>28</v>
+      </c>
+      <c r="D489">
+        <v>19.7444</v>
+      </c>
+      <c r="E489">
+        <v>20.86599922180176</v>
+      </c>
+      <c r="F489">
+        <v>0.056805941016276</v>
+      </c>
+      <c r="G489">
+        <v>5.68</v>
+      </c>
+      <c r="H489" t="s">
+        <v>17</v>
+      </c>
+      <c r="I489">
+        <v>61</v>
+      </c>
+      <c r="J489">
+        <v>1204.4084</v>
+      </c>
+      <c r="K489">
+        <v>1272.825952529907</v>
+      </c>
+    </row>
+    <row r="490" spans="1:11">
+      <c r="A490" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B490" t="s">
+        <v>18</v>
+      </c>
+      <c r="C490" t="s">
+        <v>29</v>
+      </c>
+      <c r="D490">
+        <v>129.871</v>
+      </c>
+      <c r="E490">
+        <v>146.9600067138672</v>
+      </c>
+      <c r="F490">
+        <v>0.1315844700808277</v>
+      </c>
+      <c r="G490">
+        <v>13.16</v>
+      </c>
+      <c r="H490" t="s">
+        <v>18</v>
+      </c>
+      <c r="I490">
+        <v>51</v>
+      </c>
+      <c r="J490">
+        <v>6623.421</v>
+      </c>
+      <c r="K490">
+        <v>7494.960342407227</v>
+      </c>
+    </row>
+    <row r="491" spans="1:11">
+      <c r="A491" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B491" t="s">
+        <v>19</v>
+      </c>
+      <c r="C491" t="s">
+        <v>30</v>
+      </c>
+      <c r="D491">
+        <v>34.0694</v>
+      </c>
+      <c r="E491">
+        <v>33.84000015258789</v>
+      </c>
+      <c r="F491">
+        <v>-0.0067333104607686</v>
+      </c>
+      <c r="G491">
+        <v>-0.67</v>
+      </c>
+      <c r="H491" t="s">
+        <v>19</v>
+      </c>
+      <c r="I491">
+        <v>34</v>
+      </c>
+      <c r="J491">
+        <v>1158.3596</v>
+      </c>
+      <c r="K491">
+        <v>1150.560005187988</v>
+      </c>
+    </row>
+    <row r="492" spans="1:11">
+      <c r="A492" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B492" t="s">
+        <v>20</v>
+      </c>
+      <c r="C492" t="s">
+        <v>31</v>
+      </c>
+      <c r="D492">
+        <v>69.4158</v>
+      </c>
+      <c r="E492">
+        <v>71.55000305175781</v>
+      </c>
+      <c r="F492">
+        <v>0.030745205727771</v>
+      </c>
+      <c r="G492">
+        <v>3.07</v>
+      </c>
+      <c r="H492" t="s">
+        <v>20</v>
+      </c>
+      <c r="I492">
+        <v>62</v>
+      </c>
+      <c r="J492">
+        <v>4303.7796</v>
+      </c>
+      <c r="K492">
+        <v>4436.100189208984</v>
+      </c>
+    </row>
+    <row r="493" spans="1:11">
+      <c r="A493" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B493" t="s">
+        <v>21</v>
+      </c>
+      <c r="C493" t="s">
+        <v>32</v>
+      </c>
+      <c r="D493">
+        <v>8.1868</v>
+      </c>
+      <c r="E493">
+        <v>8.48799991607666</v>
+      </c>
+      <c r="F493">
+        <v>0.0367909214927273</v>
+      </c>
+      <c r="G493">
+        <v>3.68</v>
+      </c>
+      <c r="H493" t="s">
+        <v>21</v>
+      </c>
+      <c r="I493">
+        <v>431</v>
+      </c>
+      <c r="J493">
+        <v>3528.5108</v>
+      </c>
+      <c r="K493">
+        <v>3658.327963829041</v>
       </c>
     </row>
   </sheetData>
@@ -21111,7 +21568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -22952,6 +23409,47 @@
       </c>
       <c r="M45" s="2">
         <v>0.08458832942783934</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.0738965539797018</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.0541477431652714</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0.1573432489991719</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.1180742723914332</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.0152849787605811</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.4593037930819852</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0.056805941016276</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0.1315844700808277</v>
+      </c>
+      <c r="J46" s="2">
+        <v>-0.0067333104607686</v>
+      </c>
+      <c r="K46" s="2">
+        <v>0.030745205727771</v>
+      </c>
+      <c r="L46" s="2">
+        <v>0.0367909214927273</v>
+      </c>
+      <c r="M46" s="2">
+        <v>0.09416421875041814</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -359,16 +359,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$46</c:f>
+              <c:f>grafico_dati!$B$2:$B$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -503,6 +506,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.0738965539797018</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.0583183878263791</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -530,10 +536,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -668,16 +674,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$46</c:f>
+              <c:f>grafico_dati!$C$2:$C$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -812,6 +821,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.0541477431652714</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.0589764603297178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -839,10 +851,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -977,16 +989,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$46</c:f>
+              <c:f>grafico_dati!$D$2:$D$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1121,6 +1136,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.1573432489991719</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.1741958724612384</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1148,10 +1166,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1286,16 +1304,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$46</c:f>
+              <c:f>grafico_dati!$E$2:$E$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1430,6 +1451,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.1180742723914332</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.1402917247275623</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1457,10 +1481,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1595,16 +1619,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$46</c:f>
+              <c:f>grafico_dati!$F$2:$F$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1736,6 +1763,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.0152849787605811</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.0027330454357095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1763,10 +1793,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1901,16 +1931,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$46</c:f>
+              <c:f>grafico_dati!$G$2:$G$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2045,6 +2078,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.4593037930819852</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.4382669748353565</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2072,10 +2108,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2210,16 +2246,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$46</c:f>
+              <c:f>grafico_dati!$H$2:$H$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2354,6 +2393,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.056805941016276</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.0527035436585618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2381,10 +2423,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2519,16 +2561,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$46</c:f>
+              <c:f>grafico_dati!$I$2:$I$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2660,6 +2705,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.1315844700808277</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.1346644024482106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2687,10 +2735,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2825,16 +2873,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$46</c:f>
+              <c:f>grafico_dati!$J$2:$J$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -2969,6 +3020,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>-0.0067333104607686</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-0.0158324250119792</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2996,10 +3050,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3134,16 +3188,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$46</c:f>
+              <c:f>grafico_dati!$K$2:$K$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3275,6 +3332,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.030745205727771</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.0282961120295086</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3302,10 +3362,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3440,16 +3500,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$46</c:f>
+              <c:f>grafico_dati!$L$2:$L$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3584,6 +3647,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.0367909214927273</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.0403332435584427</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3615,10 +3681,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$46</c:f>
+              <c:f>grafico_dati!$A$2:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3753,16 +3819,19 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46146</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$46</c:f>
+              <c:f>grafico_dati!$M$2:$M$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
+                <c:ptCount val="46"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3897,6 +3966,9 @@
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>0.09416421875041814</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.0957593885985335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4303,7 +4375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K493"/>
+  <dimension ref="A1:K504"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -21559,6 +21631,391 @@
       </c>
       <c r="K493">
         <v>3658.327963829041</v>
+      </c>
+    </row>
+    <row r="494" spans="1:11">
+      <c r="A494" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B494" t="s">
+        <v>11</v>
+      </c>
+      <c r="C494" t="s">
+        <v>22</v>
+      </c>
+      <c r="D494">
+        <v>50.07</v>
+      </c>
+      <c r="E494">
+        <v>52.9900016784668</v>
+      </c>
+      <c r="F494">
+        <v>0.0583183878263791</v>
+      </c>
+      <c r="G494">
+        <v>5.83</v>
+      </c>
+      <c r="H494" t="s">
+        <v>11</v>
+      </c>
+      <c r="I494">
+        <v>23</v>
+      </c>
+      <c r="J494">
+        <v>1151.61</v>
+      </c>
+      <c r="K494">
+        <v>1218.770038604736</v>
+      </c>
+    </row>
+    <row r="495" spans="1:11">
+      <c r="A495" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B495" t="s">
+        <v>12</v>
+      </c>
+      <c r="C495" t="s">
+        <v>23</v>
+      </c>
+      <c r="D495">
+        <v>242.3</v>
+      </c>
+      <c r="E495">
+        <v>256.5899963378906</v>
+      </c>
+      <c r="F495">
+        <v>0.0589764603297178</v>
+      </c>
+      <c r="G495">
+        <v>5.9</v>
+      </c>
+      <c r="H495" t="s">
+        <v>12</v>
+      </c>
+      <c r="I495">
+        <v>5</v>
+      </c>
+      <c r="J495">
+        <v>1211.5</v>
+      </c>
+      <c r="K495">
+        <v>1282.949981689453</v>
+      </c>
+    </row>
+    <row r="496" spans="1:11">
+      <c r="A496" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B496" t="s">
+        <v>13</v>
+      </c>
+      <c r="C496" t="s">
+        <v>24</v>
+      </c>
+      <c r="D496">
+        <v>38.273</v>
+      </c>
+      <c r="E496">
+        <v>44.93999862670898</v>
+      </c>
+      <c r="F496">
+        <v>0.1741958724612384</v>
+      </c>
+      <c r="G496">
+        <v>17.42</v>
+      </c>
+      <c r="H496" t="s">
+        <v>13</v>
+      </c>
+      <c r="I496">
+        <v>54</v>
+      </c>
+      <c r="J496">
+        <v>2066.742</v>
+      </c>
+      <c r="K496">
+        <v>2426.759925842285</v>
+      </c>
+    </row>
+    <row r="497" spans="1:11">
+      <c r="A497" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B497" t="s">
+        <v>14</v>
+      </c>
+      <c r="C497" t="s">
+        <v>25</v>
+      </c>
+      <c r="D497">
+        <v>6.5264</v>
+      </c>
+      <c r="E497">
+        <v>7.441999912261963</v>
+      </c>
+      <c r="F497">
+        <v>0.1402917247275623</v>
+      </c>
+      <c r="G497">
+        <v>14.03</v>
+      </c>
+      <c r="H497" t="s">
+        <v>14</v>
+      </c>
+      <c r="I497">
+        <v>276</v>
+      </c>
+      <c r="J497">
+        <v>1801.2864</v>
+      </c>
+      <c r="K497">
+        <v>2053.991975784302</v>
+      </c>
+    </row>
+    <row r="498" spans="1:11">
+      <c r="A498" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B498" t="s">
+        <v>15</v>
+      </c>
+      <c r="C498" t="s">
+        <v>26</v>
+      </c>
+      <c r="D498">
+        <v>197.58</v>
+      </c>
+      <c r="E498">
+        <v>198.1199951171875</v>
+      </c>
+      <c r="F498">
+        <v>0.0027330454357095</v>
+      </c>
+      <c r="G498">
+        <v>0.27</v>
+      </c>
+      <c r="H498" t="s">
+        <v>15</v>
+      </c>
+      <c r="I498">
+        <v>4</v>
+      </c>
+      <c r="J498">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K498">
+        <v>792.47998046875</v>
+      </c>
+    </row>
+    <row r="499" spans="1:11">
+      <c r="A499" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B499" t="s">
+        <v>16</v>
+      </c>
+      <c r="C499" t="s">
+        <v>27</v>
+      </c>
+      <c r="D499">
+        <v>79.86</v>
+      </c>
+      <c r="E499">
+        <v>114.8600006103516</v>
+      </c>
+      <c r="F499">
+        <v>0.4382669748353565</v>
+      </c>
+      <c r="G499">
+        <v>43.83</v>
+      </c>
+      <c r="H499" t="s">
+        <v>16</v>
+      </c>
+      <c r="I499">
+        <v>12</v>
+      </c>
+      <c r="J499">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K499">
+        <v>1378.320007324219</v>
+      </c>
+    </row>
+    <row r="500" spans="1:11">
+      <c r="A500" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B500" t="s">
+        <v>17</v>
+      </c>
+      <c r="C500" t="s">
+        <v>28</v>
+      </c>
+      <c r="D500">
+        <v>19.7444</v>
+      </c>
+      <c r="E500">
+        <v>20.78499984741211</v>
+      </c>
+      <c r="F500">
+        <v>0.0527035436585618</v>
+      </c>
+      <c r="G500">
+        <v>5.27</v>
+      </c>
+      <c r="H500" t="s">
+        <v>17</v>
+      </c>
+      <c r="I500">
+        <v>61</v>
+      </c>
+      <c r="J500">
+        <v>1204.4084</v>
+      </c>
+      <c r="K500">
+        <v>1267.884990692139</v>
+      </c>
+    </row>
+    <row r="501" spans="1:11">
+      <c r="A501" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B501" t="s">
+        <v>18</v>
+      </c>
+      <c r="C501" t="s">
+        <v>29</v>
+      </c>
+      <c r="D501">
+        <v>129.871</v>
+      </c>
+      <c r="E501">
+        <v>147.3600006103516</v>
+      </c>
+      <c r="F501">
+        <v>0.1346644024482106</v>
+      </c>
+      <c r="G501">
+        <v>13.47</v>
+      </c>
+      <c r="H501" t="s">
+        <v>18</v>
+      </c>
+      <c r="I501">
+        <v>51</v>
+      </c>
+      <c r="J501">
+        <v>6623.421</v>
+      </c>
+      <c r="K501">
+        <v>7515.36003112793</v>
+      </c>
+    </row>
+    <row r="502" spans="1:11">
+      <c r="A502" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B502" t="s">
+        <v>19</v>
+      </c>
+      <c r="C502" t="s">
+        <v>30</v>
+      </c>
+      <c r="D502">
+        <v>34.0694</v>
+      </c>
+      <c r="E502">
+        <v>33.52999877929688</v>
+      </c>
+      <c r="F502">
+        <v>-0.0158324250119792</v>
+      </c>
+      <c r="G502">
+        <v>-1.58</v>
+      </c>
+      <c r="H502" t="s">
+        <v>19</v>
+      </c>
+      <c r="I502">
+        <v>34</v>
+      </c>
+      <c r="J502">
+        <v>1158.3596</v>
+      </c>
+      <c r="K502">
+        <v>1140.019958496094</v>
+      </c>
+    </row>
+    <row r="503" spans="1:11">
+      <c r="A503" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B503" t="s">
+        <v>20</v>
+      </c>
+      <c r="C503" t="s">
+        <v>31</v>
+      </c>
+      <c r="D503">
+        <v>69.4158</v>
+      </c>
+      <c r="E503">
+        <v>71.37999725341797</v>
+      </c>
+      <c r="F503">
+        <v>0.0282961120295086</v>
+      </c>
+      <c r="G503">
+        <v>2.83</v>
+      </c>
+      <c r="H503" t="s">
+        <v>20</v>
+      </c>
+      <c r="I503">
+        <v>62</v>
+      </c>
+      <c r="J503">
+        <v>4303.7796</v>
+      </c>
+      <c r="K503">
+        <v>4425.559829711914</v>
+      </c>
+    </row>
+    <row r="504" spans="1:11">
+      <c r="A504" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B504" t="s">
+        <v>21</v>
+      </c>
+      <c r="C504" t="s">
+        <v>32</v>
+      </c>
+      <c r="D504">
+        <v>8.1868</v>
+      </c>
+      <c r="E504">
+        <v>8.517000198364258</v>
+      </c>
+      <c r="F504">
+        <v>0.0403332435584427</v>
+      </c>
+      <c r="G504">
+        <v>4.03</v>
+      </c>
+      <c r="H504" t="s">
+        <v>21</v>
+      </c>
+      <c r="I504">
+        <v>431</v>
+      </c>
+      <c r="J504">
+        <v>3528.5108</v>
+      </c>
+      <c r="K504">
+        <v>3670.827085494995</v>
       </c>
     </row>
   </sheetData>
@@ -21568,7 +22025,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -23450,6 +23907,47 @@
       </c>
       <c r="M46" s="2">
         <v>0.09416421875041814</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.0583183878263791</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.0589764603297178</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0.1741958724612384</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.1402917247275623</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0.0027330454357095</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0.4382669748353565</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0.0527035436585618</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0.1346644024482106</v>
+      </c>
+      <c r="J47" s="2">
+        <v>-0.0158324250119792</v>
+      </c>
+      <c r="K47" s="2">
+        <v>0.0282961120295086</v>
+      </c>
+      <c r="L47" s="2">
+        <v>0.0403332435584427</v>
+      </c>
+      <c r="M47" s="2">
+        <v>0.0957593885985335</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -362,16 +362,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$47</c:f>
+              <c:f>grafico_dati!$B$2:$B$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -509,6 +512,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.0583183878263791</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.0677051944172688</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -536,10 +542,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -677,16 +683,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$47</c:f>
+              <c:f>grafico_dati!$C$2:$C$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -824,6 +833,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.0589764603297178</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.0557160670728758</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -851,10 +863,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -992,16 +1004,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$47</c:f>
+              <c:f>grafico_dati!$D$2:$D$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1139,6 +1154,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.1741958724612384</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.1970579423277239</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1166,10 +1184,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1307,16 +1325,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$47</c:f>
+              <c:f>grafico_dati!$E$2:$E$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1454,6 +1475,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.1402917247275623</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.1661865746866813</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1481,10 +1505,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1622,16 +1646,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$47</c:f>
+              <c:f>grafico_dati!$F$2:$F$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1766,6 +1793,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.0027330454357095</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.0205992200449658</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1793,10 +1823,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1934,16 +1964,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$47</c:f>
+              <c:f>grafico_dati!$G$2:$G$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2081,6 +2114,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.4382669748353565</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.4708239304341679</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2108,10 +2144,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2249,16 +2285,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$47</c:f>
+              <c:f>grafico_dati!$H$2:$H$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2396,6 +2435,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.0527035436585618</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.0632381855370423</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2423,10 +2465,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2564,16 +2606,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$47</c:f>
+              <c:f>grafico_dati!$I$2:$I$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2708,6 +2753,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.1346644024482106</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.1430573180174341</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2735,10 +2783,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2876,16 +2924,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$47</c:f>
+              <c:f>grafico_dati!$J$2:$J$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3023,6 +3074,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>-0.0158324250119792</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-0.008494461913128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3050,10 +3104,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3191,16 +3245,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$47</c:f>
+              <c:f>grafico_dati!$K$2:$K$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3335,6 +3392,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.0282961120295086</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.0337704403929719</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3362,10 +3422,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3503,16 +3563,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$47</c:f>
+              <c:f>grafico_dati!$L$2:$L$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3650,6 +3713,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.0403332435584427</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.0497385868313502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3681,10 +3747,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$47</c:f>
+              <c:f>grafico_dati!$A$2:$A$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3822,16 +3888,19 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$47</c:f>
+              <c:f>grafico_dati!$M$2:$M$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -3969,6 +4038,9 @@
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>0.0957593885985335</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.1070343328499763</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4375,7 +4447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K504"/>
+  <dimension ref="A1:K515"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -22016,6 +22088,391 @@
       </c>
       <c r="K504">
         <v>3670.827085494995</v>
+      </c>
+    </row>
+    <row r="505" spans="1:11">
+      <c r="A505" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B505" t="s">
+        <v>11</v>
+      </c>
+      <c r="C505" t="s">
+        <v>22</v>
+      </c>
+      <c r="D505">
+        <v>50.07</v>
+      </c>
+      <c r="E505">
+        <v>53.45999908447266</v>
+      </c>
+      <c r="F505">
+        <v>0.0677051944172688</v>
+      </c>
+      <c r="G505">
+        <v>6.77</v>
+      </c>
+      <c r="H505" t="s">
+        <v>11</v>
+      </c>
+      <c r="I505">
+        <v>23</v>
+      </c>
+      <c r="J505">
+        <v>1151.61</v>
+      </c>
+      <c r="K505">
+        <v>1229.579978942871</v>
+      </c>
+    </row>
+    <row r="506" spans="1:11">
+      <c r="A506" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B506" t="s">
+        <v>12</v>
+      </c>
+      <c r="C506" t="s">
+        <v>23</v>
+      </c>
+      <c r="D506">
+        <v>242.3</v>
+      </c>
+      <c r="E506">
+        <v>255.8000030517578</v>
+      </c>
+      <c r="F506">
+        <v>0.0557160670728758</v>
+      </c>
+      <c r="G506">
+        <v>5.57</v>
+      </c>
+      <c r="H506" t="s">
+        <v>12</v>
+      </c>
+      <c r="I506">
+        <v>5</v>
+      </c>
+      <c r="J506">
+        <v>1211.5</v>
+      </c>
+      <c r="K506">
+        <v>1279.000015258789</v>
+      </c>
+    </row>
+    <row r="507" spans="1:11">
+      <c r="A507" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B507" t="s">
+        <v>13</v>
+      </c>
+      <c r="C507" t="s">
+        <v>24</v>
+      </c>
+      <c r="D507">
+        <v>38.273</v>
+      </c>
+      <c r="E507">
+        <v>45.81499862670898</v>
+      </c>
+      <c r="F507">
+        <v>0.1970579423277239</v>
+      </c>
+      <c r="G507">
+        <v>19.71</v>
+      </c>
+      <c r="H507" t="s">
+        <v>13</v>
+      </c>
+      <c r="I507">
+        <v>54</v>
+      </c>
+      <c r="J507">
+        <v>2066.742</v>
+      </c>
+      <c r="K507">
+        <v>2474.009925842285</v>
+      </c>
+    </row>
+    <row r="508" spans="1:11">
+      <c r="A508" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B508" t="s">
+        <v>14</v>
+      </c>
+      <c r="C508" t="s">
+        <v>25</v>
+      </c>
+      <c r="D508">
+        <v>6.5264</v>
+      </c>
+      <c r="E508">
+        <v>7.611000061035156</v>
+      </c>
+      <c r="F508">
+        <v>0.1661865746866813</v>
+      </c>
+      <c r="G508">
+        <v>16.62</v>
+      </c>
+      <c r="H508" t="s">
+        <v>14</v>
+      </c>
+      <c r="I508">
+        <v>276</v>
+      </c>
+      <c r="J508">
+        <v>1801.2864</v>
+      </c>
+      <c r="K508">
+        <v>2100.636016845703</v>
+      </c>
+    </row>
+    <row r="509" spans="1:11">
+      <c r="A509" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B509" t="s">
+        <v>15</v>
+      </c>
+      <c r="C509" t="s">
+        <v>26</v>
+      </c>
+      <c r="D509">
+        <v>197.58</v>
+      </c>
+      <c r="E509">
+        <v>201.6499938964844</v>
+      </c>
+      <c r="F509">
+        <v>0.0205992200449658</v>
+      </c>
+      <c r="G509">
+        <v>2.06</v>
+      </c>
+      <c r="H509" t="s">
+        <v>15</v>
+      </c>
+      <c r="I509">
+        <v>4</v>
+      </c>
+      <c r="J509">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K509">
+        <v>806.5999755859376</v>
+      </c>
+    </row>
+    <row r="510" spans="1:11">
+      <c r="A510" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B510" t="s">
+        <v>16</v>
+      </c>
+      <c r="C510" t="s">
+        <v>27</v>
+      </c>
+      <c r="D510">
+        <v>79.86</v>
+      </c>
+      <c r="E510">
+        <v>117.4599990844727</v>
+      </c>
+      <c r="F510">
+        <v>0.4708239304341679</v>
+      </c>
+      <c r="G510">
+        <v>47.08</v>
+      </c>
+      <c r="H510" t="s">
+        <v>16</v>
+      </c>
+      <c r="I510">
+        <v>12</v>
+      </c>
+      <c r="J510">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K510">
+        <v>1409.519989013672</v>
+      </c>
+    </row>
+    <row r="511" spans="1:11">
+      <c r="A511" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B511" t="s">
+        <v>17</v>
+      </c>
+      <c r="C511" t="s">
+        <v>28</v>
+      </c>
+      <c r="D511">
+        <v>19.7444</v>
+      </c>
+      <c r="E511">
+        <v>20.99300003051757</v>
+      </c>
+      <c r="F511">
+        <v>0.0632381855370423</v>
+      </c>
+      <c r="G511">
+        <v>6.32</v>
+      </c>
+      <c r="H511" t="s">
+        <v>17</v>
+      </c>
+      <c r="I511">
+        <v>61</v>
+      </c>
+      <c r="J511">
+        <v>1204.4084</v>
+      </c>
+      <c r="K511">
+        <v>1280.573001861572</v>
+      </c>
+    </row>
+    <row r="512" spans="1:11">
+      <c r="A512" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B512" t="s">
+        <v>18</v>
+      </c>
+      <c r="C512" t="s">
+        <v>29</v>
+      </c>
+      <c r="D512">
+        <v>129.871</v>
+      </c>
+      <c r="E512">
+        <v>148.4499969482422</v>
+      </c>
+      <c r="F512">
+        <v>0.1430573180174341</v>
+      </c>
+      <c r="G512">
+        <v>14.31</v>
+      </c>
+      <c r="H512" t="s">
+        <v>18</v>
+      </c>
+      <c r="I512">
+        <v>51</v>
+      </c>
+      <c r="J512">
+        <v>6623.421</v>
+      </c>
+      <c r="K512">
+        <v>7570.949844360352</v>
+      </c>
+    </row>
+    <row r="513" spans="1:11">
+      <c r="A513" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B513" t="s">
+        <v>19</v>
+      </c>
+      <c r="C513" t="s">
+        <v>30</v>
+      </c>
+      <c r="D513">
+        <v>34.0694</v>
+      </c>
+      <c r="E513">
+        <v>33.77999877929688</v>
+      </c>
+      <c r="F513">
+        <v>-0.008494461913128</v>
+      </c>
+      <c r="G513">
+        <v>-0.85</v>
+      </c>
+      <c r="H513" t="s">
+        <v>19</v>
+      </c>
+      <c r="I513">
+        <v>34</v>
+      </c>
+      <c r="J513">
+        <v>1158.3596</v>
+      </c>
+      <c r="K513">
+        <v>1148.519958496094</v>
+      </c>
+    </row>
+    <row r="514" spans="1:11">
+      <c r="A514" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B514" t="s">
+        <v>20</v>
+      </c>
+      <c r="C514" t="s">
+        <v>31</v>
+      </c>
+      <c r="D514">
+        <v>69.4158</v>
+      </c>
+      <c r="E514">
+        <v>71.76000213623047</v>
+      </c>
+      <c r="F514">
+        <v>0.0337704403929719</v>
+      </c>
+      <c r="G514">
+        <v>3.38</v>
+      </c>
+      <c r="H514" t="s">
+        <v>20</v>
+      </c>
+      <c r="I514">
+        <v>62</v>
+      </c>
+      <c r="J514">
+        <v>4303.7796</v>
+      </c>
+      <c r="K514">
+        <v>4449.120132446289</v>
+      </c>
+    </row>
+    <row r="515" spans="1:11">
+      <c r="A515" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B515" t="s">
+        <v>21</v>
+      </c>
+      <c r="C515" t="s">
+        <v>32</v>
+      </c>
+      <c r="D515">
+        <v>8.1868</v>
+      </c>
+      <c r="E515">
+        <v>8.593999862670898</v>
+      </c>
+      <c r="F515">
+        <v>0.0497385868313502</v>
+      </c>
+      <c r="G515">
+        <v>4.97</v>
+      </c>
+      <c r="H515" t="s">
+        <v>21</v>
+      </c>
+      <c r="I515">
+        <v>431</v>
+      </c>
+      <c r="J515">
+        <v>3528.5108</v>
+      </c>
+      <c r="K515">
+        <v>3704.013940811157</v>
       </c>
     </row>
   </sheetData>
@@ -22025,7 +22482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -23948,6 +24405,47 @@
       </c>
       <c r="M47" s="2">
         <v>0.0957593885985335</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.0677051944172688</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0.0557160670728758</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0.1970579423277239</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.1661865746866813</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.0205992200449658</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0.4708239304341679</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0.0632381855370423</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0.1430573180174341</v>
+      </c>
+      <c r="J48" s="2">
+        <v>-0.008494461913128</v>
+      </c>
+      <c r="K48" s="2">
+        <v>0.0337704403929719</v>
+      </c>
+      <c r="L48" s="2">
+        <v>0.0497385868313502</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0.1070343328499763</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -365,16 +365,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$48</c:f>
+              <c:f>grafico_dati!$B$2:$B$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -515,6 +518,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.0677051944172688</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.09506694290103219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +548,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -686,16 +692,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$48</c:f>
+              <c:f>grafico_dati!$C$2:$C$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -836,6 +845,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.0557160670728758</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.0569953997175505</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -863,10 +875,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1007,16 +1019,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$48</c:f>
+              <c:f>grafico_dati!$D$2:$D$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1157,6 +1172,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.1970579423277239</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.2226634486177019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1184,10 +1202,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1328,16 +1346,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$48</c:f>
+              <c:f>grafico_dati!$E$2:$E$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1478,6 +1499,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.1661865746866813</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.1962184604402557</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1505,10 +1529,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1649,16 +1673,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$48</c:f>
+              <c:f>grafico_dati!$F$2:$F$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1796,6 +1823,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.0205992200449658</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.041350339103148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1823,10 +1853,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1967,16 +1997,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$48</c:f>
+              <c:f>grafico_dati!$G$2:$G$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2117,6 +2150,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.4708239304341679</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.5113949029331604</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2144,10 +2180,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2288,16 +2324,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$48</c:f>
+              <c:f>grafico_dati!$H$2:$H$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2438,6 +2477,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.0632381855370423</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.0893214997754308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2465,10 +2507,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2609,16 +2651,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$48</c:f>
+              <c:f>grafico_dati!$I$2:$I$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2756,6 +2801,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.1430573180174341</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.1563781958696031</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2783,10 +2831,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2927,16 +2975,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$48</c:f>
+              <c:f>grafico_dati!$J$2:$J$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3077,6 +3128,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>-0.008494461913128</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.0089699260920357</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3104,10 +3158,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3248,16 +3302,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$48</c:f>
+              <c:f>grafico_dati!$K$2:$K$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3395,6 +3452,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.0337704403929719</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.0455833085703065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3422,10 +3482,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3566,16 +3626,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$48</c:f>
+              <c:f>grafico_dati!$L$2:$L$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3716,6 +3779,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.0497385868313502</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.06415203659408771</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3747,10 +3813,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$48</c:f>
+              <c:f>grafico_dati!$A$2:$A$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3891,16 +3957,19 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$48</c:f>
+              <c:f>grafico_dati!$M$2:$M$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="47"/>
+                <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4041,6 +4110,9 @@
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>0.1070343328499763</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.1246536656368895</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4447,7 +4519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K515"/>
+  <dimension ref="A1:K526"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -22473,6 +22545,391 @@
       </c>
       <c r="K515">
         <v>3704.013940811157</v>
+      </c>
+    </row>
+    <row r="516" spans="1:11">
+      <c r="A516" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B516" t="s">
+        <v>11</v>
+      </c>
+      <c r="C516" t="s">
+        <v>22</v>
+      </c>
+      <c r="D516">
+        <v>50.07</v>
+      </c>
+      <c r="E516">
+        <v>54.83000183105469</v>
+      </c>
+      <c r="F516">
+        <v>0.09506694290103219</v>
+      </c>
+      <c r="G516">
+        <v>9.51</v>
+      </c>
+      <c r="H516" t="s">
+        <v>11</v>
+      </c>
+      <c r="I516">
+        <v>23</v>
+      </c>
+      <c r="J516">
+        <v>1151.61</v>
+      </c>
+      <c r="K516">
+        <v>1261.090042114258</v>
+      </c>
+    </row>
+    <row r="517" spans="1:11">
+      <c r="A517" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B517" t="s">
+        <v>12</v>
+      </c>
+      <c r="C517" t="s">
+        <v>23</v>
+      </c>
+      <c r="D517">
+        <v>242.3</v>
+      </c>
+      <c r="E517">
+        <v>256.1099853515625</v>
+      </c>
+      <c r="F517">
+        <v>0.0569953997175505</v>
+      </c>
+      <c r="G517">
+        <v>5.7</v>
+      </c>
+      <c r="H517" t="s">
+        <v>12</v>
+      </c>
+      <c r="I517">
+        <v>5</v>
+      </c>
+      <c r="J517">
+        <v>1211.5</v>
+      </c>
+      <c r="K517">
+        <v>1280.549926757812</v>
+      </c>
+    </row>
+    <row r="518" spans="1:11">
+      <c r="A518" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B518" t="s">
+        <v>13</v>
+      </c>
+      <c r="C518" t="s">
+        <v>24</v>
+      </c>
+      <c r="D518">
+        <v>38.273</v>
+      </c>
+      <c r="E518">
+        <v>46.79499816894531</v>
+      </c>
+      <c r="F518">
+        <v>0.2226634486177019</v>
+      </c>
+      <c r="G518">
+        <v>22.27</v>
+      </c>
+      <c r="H518" t="s">
+        <v>13</v>
+      </c>
+      <c r="I518">
+        <v>54</v>
+      </c>
+      <c r="J518">
+        <v>2066.742</v>
+      </c>
+      <c r="K518">
+        <v>2526.929901123047</v>
+      </c>
+    </row>
+    <row r="519" spans="1:11">
+      <c r="A519" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B519" t="s">
+        <v>14</v>
+      </c>
+      <c r="C519" t="s">
+        <v>25</v>
+      </c>
+      <c r="D519">
+        <v>6.5264</v>
+      </c>
+      <c r="E519">
+        <v>7.807000160217285</v>
+      </c>
+      <c r="F519">
+        <v>0.1962184604402557</v>
+      </c>
+      <c r="G519">
+        <v>19.62</v>
+      </c>
+      <c r="H519" t="s">
+        <v>14</v>
+      </c>
+      <c r="I519">
+        <v>276</v>
+      </c>
+      <c r="J519">
+        <v>1801.2864</v>
+      </c>
+      <c r="K519">
+        <v>2154.732044219971</v>
+      </c>
+    </row>
+    <row r="520" spans="1:11">
+      <c r="A520" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B520" t="s">
+        <v>15</v>
+      </c>
+      <c r="C520" t="s">
+        <v>26</v>
+      </c>
+      <c r="D520">
+        <v>197.58</v>
+      </c>
+      <c r="E520">
+        <v>205.75</v>
+      </c>
+      <c r="F520">
+        <v>0.041350339103148</v>
+      </c>
+      <c r="G520">
+        <v>4.14</v>
+      </c>
+      <c r="H520" t="s">
+        <v>15</v>
+      </c>
+      <c r="I520">
+        <v>4</v>
+      </c>
+      <c r="J520">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K520">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="521" spans="1:11">
+      <c r="A521" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B521" t="s">
+        <v>16</v>
+      </c>
+      <c r="C521" t="s">
+        <v>27</v>
+      </c>
+      <c r="D521">
+        <v>79.86</v>
+      </c>
+      <c r="E521">
+        <v>120.6999969482422</v>
+      </c>
+      <c r="F521">
+        <v>0.5113949029331604</v>
+      </c>
+      <c r="G521">
+        <v>51.14</v>
+      </c>
+      <c r="H521" t="s">
+        <v>16</v>
+      </c>
+      <c r="I521">
+        <v>12</v>
+      </c>
+      <c r="J521">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K521">
+        <v>1448.399963378906</v>
+      </c>
+    </row>
+    <row r="522" spans="1:11">
+      <c r="A522" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B522" t="s">
+        <v>17</v>
+      </c>
+      <c r="C522" t="s">
+        <v>28</v>
+      </c>
+      <c r="D522">
+        <v>19.7444</v>
+      </c>
+      <c r="E522">
+        <v>21.50799942016602</v>
+      </c>
+      <c r="F522">
+        <v>0.0893214997754308</v>
+      </c>
+      <c r="G522">
+        <v>8.93</v>
+      </c>
+      <c r="H522" t="s">
+        <v>17</v>
+      </c>
+      <c r="I522">
+        <v>61</v>
+      </c>
+      <c r="J522">
+        <v>1204.4084</v>
+      </c>
+      <c r="K522">
+        <v>1311.987964630127</v>
+      </c>
+    </row>
+    <row r="523" spans="1:11">
+      <c r="A523" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B523" t="s">
+        <v>18</v>
+      </c>
+      <c r="C523" t="s">
+        <v>29</v>
+      </c>
+      <c r="D523">
+        <v>129.871</v>
+      </c>
+      <c r="E523">
+        <v>150.1799926757812</v>
+      </c>
+      <c r="F523">
+        <v>0.1563781958696031</v>
+      </c>
+      <c r="G523">
+        <v>15.64</v>
+      </c>
+      <c r="H523" t="s">
+        <v>18</v>
+      </c>
+      <c r="I523">
+        <v>51</v>
+      </c>
+      <c r="J523">
+        <v>6623.421</v>
+      </c>
+      <c r="K523">
+        <v>7659.179626464844</v>
+      </c>
+    </row>
+    <row r="524" spans="1:11">
+      <c r="A524" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B524" t="s">
+        <v>19</v>
+      </c>
+      <c r="C524" t="s">
+        <v>30</v>
+      </c>
+      <c r="D524">
+        <v>34.0694</v>
+      </c>
+      <c r="E524">
+        <v>34.375</v>
+      </c>
+      <c r="F524">
+        <v>0.0089699260920357</v>
+      </c>
+      <c r="G524">
+        <v>0.9</v>
+      </c>
+      <c r="H524" t="s">
+        <v>19</v>
+      </c>
+      <c r="I524">
+        <v>34</v>
+      </c>
+      <c r="J524">
+        <v>1158.3596</v>
+      </c>
+      <c r="K524">
+        <v>1168.75</v>
+      </c>
+    </row>
+    <row r="525" spans="1:11">
+      <c r="A525" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B525" t="s">
+        <v>20</v>
+      </c>
+      <c r="C525" t="s">
+        <v>31</v>
+      </c>
+      <c r="D525">
+        <v>69.4158</v>
+      </c>
+      <c r="E525">
+        <v>72.58000183105469</v>
+      </c>
+      <c r="F525">
+        <v>0.0455833085703065</v>
+      </c>
+      <c r="G525">
+        <v>4.56</v>
+      </c>
+      <c r="H525" t="s">
+        <v>20</v>
+      </c>
+      <c r="I525">
+        <v>62</v>
+      </c>
+      <c r="J525">
+        <v>4303.7796</v>
+      </c>
+      <c r="K525">
+        <v>4499.960113525391</v>
+      </c>
+    </row>
+    <row r="526" spans="1:11">
+      <c r="A526" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B526" t="s">
+        <v>21</v>
+      </c>
+      <c r="C526" t="s">
+        <v>32</v>
+      </c>
+      <c r="D526">
+        <v>8.1868</v>
+      </c>
+      <c r="E526">
+        <v>8.711999893188477</v>
+      </c>
+      <c r="F526">
+        <v>0.06415203659408771</v>
+      </c>
+      <c r="G526">
+        <v>6.42</v>
+      </c>
+      <c r="H526" t="s">
+        <v>21</v>
+      </c>
+      <c r="I526">
+        <v>431</v>
+      </c>
+      <c r="J526">
+        <v>3528.5108</v>
+      </c>
+      <c r="K526">
+        <v>3754.871953964233</v>
       </c>
     </row>
   </sheetData>
@@ -22482,7 +22939,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -24446,6 +24903,47 @@
       </c>
       <c r="M48" s="2">
         <v>0.1070343328499763</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.09506694290103219</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.0569953997175505</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0.2226634486177019</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.1962184604402557</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0.041350339103148</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0.5113949029331604</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0.0893214997754308</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0.1563781958696031</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0.0089699260920357</v>
+      </c>
+      <c r="K49" s="2">
+        <v>0.0455833085703065</v>
+      </c>
+      <c r="L49" s="2">
+        <v>0.06415203659408771</v>
+      </c>
+      <c r="M49" s="2">
+        <v>0.1246536656368895</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -368,16 +368,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$49</c:f>
+              <c:f>grafico_dati!$B$2:$B$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -521,6 +524,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.09506694290103219</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.08587974699190649</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -548,10 +554,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -695,16 +701,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$49</c:f>
+              <c:f>grafico_dati!$C$2:$C$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -848,6 +857,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.0569953997175505</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.0553446418236367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -875,10 +887,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1022,16 +1034,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$49</c:f>
+              <c:f>grafico_dati!$D$2:$D$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1175,6 +1190,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.2226634486177019</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.2214877328665114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1202,10 +1220,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1349,16 +1367,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$49</c:f>
+              <c:f>grafico_dati!$E$2:$E$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1502,6 +1523,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.1962184604402557</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.194226548904939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1529,10 +1553,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1676,16 +1700,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$49</c:f>
+              <c:f>grafico_dati!$F$2:$F$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1826,6 +1853,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.041350339103148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.0307217020775603</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1853,10 +1883,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2000,16 +2030,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$49</c:f>
+              <c:f>grafico_dati!$G$2:$G$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2153,6 +2186,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.5113949029331604</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.4981217053549767</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2180,10 +2216,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2327,16 +2363,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$49</c:f>
+              <c:f>grafico_dati!$H$2:$H$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2480,6 +2519,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.0893214997754308</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.0866372198550502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2507,10 +2549,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2654,16 +2696,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$49</c:f>
+              <c:f>grafico_dati!$I$2:$I$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2804,6 +2849,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.1563781958696031</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.1569172486544339</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2831,10 +2879,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2978,16 +3026,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$49</c:f>
+              <c:f>grafico_dati!$J$2:$J$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3131,6 +3182,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.0089699260920357</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-0.0007162389432948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3158,10 +3212,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3305,16 +3359,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$49</c:f>
+              <c:f>grafico_dati!$K$2:$K$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3455,6 +3512,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.0455833085703065</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.0447188773026658</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3482,10 +3542,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3629,16 +3689,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$49</c:f>
+              <c:f>grafico_dati!$L$2:$L$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3782,6 +3845,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.06415203659408771</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.0613426649850621</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3813,10 +3879,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$49</c:f>
+              <c:f>grafico_dati!$A$2:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3960,16 +4026,19 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$49</c:f>
+              <c:f>grafico_dati!$M$2:$M$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="49"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4113,6 +4182,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>0.1246536656368895</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.1220634136316909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4519,7 +4591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K526"/>
+  <dimension ref="A1:K537"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -22930,6 +23002,391 @@
       </c>
       <c r="K526">
         <v>3754.871953964233</v>
+      </c>
+    </row>
+    <row r="527" spans="1:11">
+      <c r="A527" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B527" t="s">
+        <v>11</v>
+      </c>
+      <c r="C527" t="s">
+        <v>22</v>
+      </c>
+      <c r="D527">
+        <v>50.07</v>
+      </c>
+      <c r="E527">
+        <v>54.36999893188477</v>
+      </c>
+      <c r="F527">
+        <v>0.08587974699190649</v>
+      </c>
+      <c r="G527">
+        <v>8.59</v>
+      </c>
+      <c r="H527" t="s">
+        <v>11</v>
+      </c>
+      <c r="I527">
+        <v>23</v>
+      </c>
+      <c r="J527">
+        <v>1151.61</v>
+      </c>
+      <c r="K527">
+        <v>1250.50997543335</v>
+      </c>
+    </row>
+    <row r="528" spans="1:11">
+      <c r="A528" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B528" t="s">
+        <v>12</v>
+      </c>
+      <c r="C528" t="s">
+        <v>23</v>
+      </c>
+      <c r="D528">
+        <v>242.3</v>
+      </c>
+      <c r="E528">
+        <v>255.7100067138672</v>
+      </c>
+      <c r="F528">
+        <v>0.0553446418236367</v>
+      </c>
+      <c r="G528">
+        <v>5.53</v>
+      </c>
+      <c r="H528" t="s">
+        <v>12</v>
+      </c>
+      <c r="I528">
+        <v>5</v>
+      </c>
+      <c r="J528">
+        <v>1211.5</v>
+      </c>
+      <c r="K528">
+        <v>1278.550033569336</v>
+      </c>
+    </row>
+    <row r="529" spans="1:11">
+      <c r="A529" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B529" t="s">
+        <v>13</v>
+      </c>
+      <c r="C529" t="s">
+        <v>24</v>
+      </c>
+      <c r="D529">
+        <v>38.273</v>
+      </c>
+      <c r="E529">
+        <v>46.75</v>
+      </c>
+      <c r="F529">
+        <v>0.2214877328665114</v>
+      </c>
+      <c r="G529">
+        <v>22.15</v>
+      </c>
+      <c r="H529" t="s">
+        <v>13</v>
+      </c>
+      <c r="I529">
+        <v>54</v>
+      </c>
+      <c r="J529">
+        <v>2066.742</v>
+      </c>
+      <c r="K529">
+        <v>2524.5</v>
+      </c>
+    </row>
+    <row r="530" spans="1:11">
+      <c r="A530" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B530" t="s">
+        <v>14</v>
+      </c>
+      <c r="C530" t="s">
+        <v>25</v>
+      </c>
+      <c r="D530">
+        <v>6.5264</v>
+      </c>
+      <c r="E530">
+        <v>7.794000148773193</v>
+      </c>
+      <c r="F530">
+        <v>0.194226548904939</v>
+      </c>
+      <c r="G530">
+        <v>19.42</v>
+      </c>
+      <c r="H530" t="s">
+        <v>14</v>
+      </c>
+      <c r="I530">
+        <v>276</v>
+      </c>
+      <c r="J530">
+        <v>1801.2864</v>
+      </c>
+      <c r="K530">
+        <v>2151.144041061401</v>
+      </c>
+    </row>
+    <row r="531" spans="1:11">
+      <c r="A531" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B531" t="s">
+        <v>15</v>
+      </c>
+      <c r="C531" t="s">
+        <v>26</v>
+      </c>
+      <c r="D531">
+        <v>197.58</v>
+      </c>
+      <c r="E531">
+        <v>203.6499938964844</v>
+      </c>
+      <c r="F531">
+        <v>0.0307217020775603</v>
+      </c>
+      <c r="G531">
+        <v>3.07</v>
+      </c>
+      <c r="H531" t="s">
+        <v>15</v>
+      </c>
+      <c r="I531">
+        <v>4</v>
+      </c>
+      <c r="J531">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K531">
+        <v>814.5999755859376</v>
+      </c>
+    </row>
+    <row r="532" spans="1:11">
+      <c r="A532" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B532" t="s">
+        <v>16</v>
+      </c>
+      <c r="C532" t="s">
+        <v>27</v>
+      </c>
+      <c r="D532">
+        <v>79.86</v>
+      </c>
+      <c r="E532">
+        <v>119.6399993896484</v>
+      </c>
+      <c r="F532">
+        <v>0.4981217053549767</v>
+      </c>
+      <c r="G532">
+        <v>49.81</v>
+      </c>
+      <c r="H532" t="s">
+        <v>16</v>
+      </c>
+      <c r="I532">
+        <v>12</v>
+      </c>
+      <c r="J532">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K532">
+        <v>1435.679992675781</v>
+      </c>
+    </row>
+    <row r="533" spans="1:11">
+      <c r="A533" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B533" t="s">
+        <v>17</v>
+      </c>
+      <c r="C533" t="s">
+        <v>28</v>
+      </c>
+      <c r="D533">
+        <v>19.7444</v>
+      </c>
+      <c r="E533">
+        <v>21.45499992370605</v>
+      </c>
+      <c r="F533">
+        <v>0.0866372198550502</v>
+      </c>
+      <c r="G533">
+        <v>8.66</v>
+      </c>
+      <c r="H533" t="s">
+        <v>17</v>
+      </c>
+      <c r="I533">
+        <v>61</v>
+      </c>
+      <c r="J533">
+        <v>1204.4084</v>
+      </c>
+      <c r="K533">
+        <v>1308.754995346069</v>
+      </c>
+    </row>
+    <row r="534" spans="1:11">
+      <c r="A534" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B534" t="s">
+        <v>18</v>
+      </c>
+      <c r="C534" t="s">
+        <v>29</v>
+      </c>
+      <c r="D534">
+        <v>129.871</v>
+      </c>
+      <c r="E534">
+        <v>150.25</v>
+      </c>
+      <c r="F534">
+        <v>0.1569172486544339</v>
+      </c>
+      <c r="G534">
+        <v>15.69</v>
+      </c>
+      <c r="H534" t="s">
+        <v>18</v>
+      </c>
+      <c r="I534">
+        <v>51</v>
+      </c>
+      <c r="J534">
+        <v>6623.421</v>
+      </c>
+      <c r="K534">
+        <v>7662.75</v>
+      </c>
+    </row>
+    <row r="535" spans="1:11">
+      <c r="A535" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B535" t="s">
+        <v>19</v>
+      </c>
+      <c r="C535" t="s">
+        <v>30</v>
+      </c>
+      <c r="D535">
+        <v>34.0694</v>
+      </c>
+      <c r="E535">
+        <v>34.04499816894531</v>
+      </c>
+      <c r="F535">
+        <v>-0.0007162389432948</v>
+      </c>
+      <c r="G535">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H535" t="s">
+        <v>19</v>
+      </c>
+      <c r="I535">
+        <v>34</v>
+      </c>
+      <c r="J535">
+        <v>1158.3596</v>
+      </c>
+      <c r="K535">
+        <v>1157.529937744141</v>
+      </c>
+    </row>
+    <row r="536" spans="1:11">
+      <c r="A536" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B536" t="s">
+        <v>20</v>
+      </c>
+      <c r="C536" t="s">
+        <v>31</v>
+      </c>
+      <c r="D536">
+        <v>69.4158</v>
+      </c>
+      <c r="E536">
+        <v>72.51999664306641</v>
+      </c>
+      <c r="F536">
+        <v>0.0447188773026658</v>
+      </c>
+      <c r="G536">
+        <v>4.47</v>
+      </c>
+      <c r="H536" t="s">
+        <v>20</v>
+      </c>
+      <c r="I536">
+        <v>62</v>
+      </c>
+      <c r="J536">
+        <v>4303.7796</v>
+      </c>
+      <c r="K536">
+        <v>4496.239791870117</v>
+      </c>
+    </row>
+    <row r="537" spans="1:11">
+      <c r="A537" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B537" t="s">
+        <v>21</v>
+      </c>
+      <c r="C537" t="s">
+        <v>32</v>
+      </c>
+      <c r="D537">
+        <v>8.1868</v>
+      </c>
+      <c r="E537">
+        <v>8.689000129699707</v>
+      </c>
+      <c r="F537">
+        <v>0.0613426649850621</v>
+      </c>
+      <c r="G537">
+        <v>6.13</v>
+      </c>
+      <c r="H537" t="s">
+        <v>21</v>
+      </c>
+      <c r="I537">
+        <v>431</v>
+      </c>
+      <c r="J537">
+        <v>3528.5108</v>
+      </c>
+      <c r="K537">
+        <v>3744.959055900574</v>
       </c>
     </row>
   </sheetData>
@@ -22939,7 +23396,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -24944,6 +25401,47 @@
       </c>
       <c r="M49" s="2">
         <v>0.1246536656368895</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.08587974699190649</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0.0553446418236367</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0.2214877328665114</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0.194226548904939</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0.0307217020775603</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0.4981217053549767</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0.0866372198550502</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0.1569172486544339</v>
+      </c>
+      <c r="J50" s="2">
+        <v>-0.0007162389432948</v>
+      </c>
+      <c r="K50" s="2">
+        <v>0.0447188773026658</v>
+      </c>
+      <c r="L50" s="2">
+        <v>0.0613426649850621</v>
+      </c>
+      <c r="M50" s="2">
+        <v>0.1220634136316909</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -371,16 +371,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$50</c:f>
+              <c:f>grafico_dati!$B$2:$B$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -527,6 +530,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.08587974699190649</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.0742960039050797</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -554,10 +560,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -704,16 +710,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$50</c:f>
+              <c:f>grafico_dati!$C$2:$C$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -860,6 +869,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.0553446418236367</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.0524556108412543</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -887,10 +899,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1037,16 +1049,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$50</c:f>
+              <c:f>grafico_dati!$D$2:$D$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1193,6 +1208,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.2214877328665114</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.2293261368865922</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1220,10 +1238,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1370,16 +1388,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$50</c:f>
+              <c:f>grafico_dati!$E$2:$E$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1526,6 +1547,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.194226548904939</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.20617801811684</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1553,10 +1577,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1703,16 +1727,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$50</c:f>
+              <c:f>grafico_dati!$F$2:$F$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1856,6 +1883,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.0307217020775603</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.0165502890146553</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1883,10 +1913,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2033,16 +2063,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$50</c:f>
+              <c:f>grafico_dati!$G$2:$G$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2189,6 +2222,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.4981217053549767</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.5013774295752431</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2216,10 +2252,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2366,16 +2402,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$50</c:f>
+              <c:f>grafico_dati!$H$2:$H$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2522,6 +2561,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.0866372198550502</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.091955160245051</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2549,10 +2591,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2699,16 +2741,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$50</c:f>
+              <c:f>grafico_dati!$I$2:$I$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2852,6 +2897,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.1569172486544339</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.1557623033896376</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2879,10 +2927,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3029,16 +3077,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$50</c:f>
+              <c:f>grafico_dati!$J$2:$J$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3185,6 +3236,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>-0.0007162389432948</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-0.0026240690403609</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3212,10 +3266,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3362,16 +3416,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$50</c:f>
+              <c:f>grafico_dati!$K$2:$K$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3515,6 +3572,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.0447188773026658</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.0432783050680869</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3542,10 +3602,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3692,16 +3752,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$50</c:f>
+              <c:f>grafico_dati!$L$2:$L$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3848,6 +3911,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.0613426649850621</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.0608541090067791</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3879,10 +3945,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$50</c:f>
+              <c:f>grafico_dati!$A$2:$A$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4029,16 +4095,19 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$50</c:f>
+              <c:f>grafico_dati!$M$2:$M$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4185,6 +4254,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>0.1220634136316909</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.122121062294837</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4591,7 +4663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K537"/>
+  <dimension ref="A1:K548"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -23387,6 +23459,391 @@
       </c>
       <c r="K537">
         <v>3744.959055900574</v>
+      </c>
+    </row>
+    <row r="538" spans="1:11">
+      <c r="A538" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B538" t="s">
+        <v>11</v>
+      </c>
+      <c r="C538" t="s">
+        <v>22</v>
+      </c>
+      <c r="D538">
+        <v>50.07</v>
+      </c>
+      <c r="E538">
+        <v>53.79000091552734</v>
+      </c>
+      <c r="F538">
+        <v>0.0742960039050797</v>
+      </c>
+      <c r="G538">
+        <v>7.43</v>
+      </c>
+      <c r="H538" t="s">
+        <v>11</v>
+      </c>
+      <c r="I538">
+        <v>23</v>
+      </c>
+      <c r="J538">
+        <v>1151.61</v>
+      </c>
+      <c r="K538">
+        <v>1237.170021057129</v>
+      </c>
+    </row>
+    <row r="539" spans="1:11">
+      <c r="A539" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B539" t="s">
+        <v>12</v>
+      </c>
+      <c r="C539" t="s">
+        <v>23</v>
+      </c>
+      <c r="D539">
+        <v>242.3</v>
+      </c>
+      <c r="E539">
+        <v>255.009994506836</v>
+      </c>
+      <c r="F539">
+        <v>0.0524556108412543</v>
+      </c>
+      <c r="G539">
+        <v>5.25</v>
+      </c>
+      <c r="H539" t="s">
+        <v>12</v>
+      </c>
+      <c r="I539">
+        <v>5</v>
+      </c>
+      <c r="J539">
+        <v>1211.5</v>
+      </c>
+      <c r="K539">
+        <v>1275.04997253418</v>
+      </c>
+    </row>
+    <row r="540" spans="1:11">
+      <c r="A540" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B540" t="s">
+        <v>13</v>
+      </c>
+      <c r="C540" t="s">
+        <v>24</v>
+      </c>
+      <c r="D540">
+        <v>38.273</v>
+      </c>
+      <c r="E540">
+        <v>47.04999923706055</v>
+      </c>
+      <c r="F540">
+        <v>0.2293261368865922</v>
+      </c>
+      <c r="G540">
+        <v>22.93</v>
+      </c>
+      <c r="H540" t="s">
+        <v>13</v>
+      </c>
+      <c r="I540">
+        <v>54</v>
+      </c>
+      <c r="J540">
+        <v>2066.742</v>
+      </c>
+      <c r="K540">
+        <v>2540.69995880127</v>
+      </c>
+    </row>
+    <row r="541" spans="1:11">
+      <c r="A541" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B541" t="s">
+        <v>14</v>
+      </c>
+      <c r="C541" t="s">
+        <v>25</v>
+      </c>
+      <c r="D541">
+        <v>6.5264</v>
+      </c>
+      <c r="E541">
+        <v>7.872000217437744</v>
+      </c>
+      <c r="F541">
+        <v>0.20617801811684</v>
+      </c>
+      <c r="G541">
+        <v>20.62</v>
+      </c>
+      <c r="H541" t="s">
+        <v>14</v>
+      </c>
+      <c r="I541">
+        <v>276</v>
+      </c>
+      <c r="J541">
+        <v>1801.2864</v>
+      </c>
+      <c r="K541">
+        <v>2172.672060012817</v>
+      </c>
+    </row>
+    <row r="542" spans="1:11">
+      <c r="A542" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B542" t="s">
+        <v>15</v>
+      </c>
+      <c r="C542" t="s">
+        <v>26</v>
+      </c>
+      <c r="D542">
+        <v>197.58</v>
+      </c>
+      <c r="E542">
+        <v>200.8500061035156</v>
+      </c>
+      <c r="F542">
+        <v>0.0165502890146553</v>
+      </c>
+      <c r="G542">
+        <v>1.66</v>
+      </c>
+      <c r="H542" t="s">
+        <v>15</v>
+      </c>
+      <c r="I542">
+        <v>4</v>
+      </c>
+      <c r="J542">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K542">
+        <v>803.4000244140624</v>
+      </c>
+    </row>
+    <row r="543" spans="1:11">
+      <c r="A543" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B543" t="s">
+        <v>16</v>
+      </c>
+      <c r="C543" t="s">
+        <v>27</v>
+      </c>
+      <c r="D543">
+        <v>79.86</v>
+      </c>
+      <c r="E543">
+        <v>119.9000015258789</v>
+      </c>
+      <c r="F543">
+        <v>0.5013774295752431</v>
+      </c>
+      <c r="G543">
+        <v>50.14</v>
+      </c>
+      <c r="H543" t="s">
+        <v>16</v>
+      </c>
+      <c r="I543">
+        <v>12</v>
+      </c>
+      <c r="J543">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K543">
+        <v>1438.800018310547</v>
+      </c>
+    </row>
+    <row r="544" spans="1:11">
+      <c r="A544" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B544" t="s">
+        <v>17</v>
+      </c>
+      <c r="C544" t="s">
+        <v>28</v>
+      </c>
+      <c r="D544">
+        <v>19.7444</v>
+      </c>
+      <c r="E544">
+        <v>21.55999946594238</v>
+      </c>
+      <c r="F544">
+        <v>0.091955160245051</v>
+      </c>
+      <c r="G544">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H544" t="s">
+        <v>17</v>
+      </c>
+      <c r="I544">
+        <v>61</v>
+      </c>
+      <c r="J544">
+        <v>1204.4084</v>
+      </c>
+      <c r="K544">
+        <v>1315.159967422485</v>
+      </c>
+    </row>
+    <row r="545" spans="1:11">
+      <c r="A545" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B545" t="s">
+        <v>18</v>
+      </c>
+      <c r="C545" t="s">
+        <v>29</v>
+      </c>
+      <c r="D545">
+        <v>129.871</v>
+      </c>
+      <c r="E545">
+        <v>150.1000061035156</v>
+      </c>
+      <c r="F545">
+        <v>0.1557623033896376</v>
+      </c>
+      <c r="G545">
+        <v>15.58</v>
+      </c>
+      <c r="H545" t="s">
+        <v>18</v>
+      </c>
+      <c r="I545">
+        <v>51</v>
+      </c>
+      <c r="J545">
+        <v>6623.421</v>
+      </c>
+      <c r="K545">
+        <v>7655.100311279297</v>
+      </c>
+    </row>
+    <row r="546" spans="1:11">
+      <c r="A546" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B546" t="s">
+        <v>19</v>
+      </c>
+      <c r="C546" t="s">
+        <v>30</v>
+      </c>
+      <c r="D546">
+        <v>34.0694</v>
+      </c>
+      <c r="E546">
+        <v>33.97999954223633</v>
+      </c>
+      <c r="F546">
+        <v>-0.0026240690403609</v>
+      </c>
+      <c r="G546">
+        <v>-0.26</v>
+      </c>
+      <c r="H546" t="s">
+        <v>19</v>
+      </c>
+      <c r="I546">
+        <v>34</v>
+      </c>
+      <c r="J546">
+        <v>1158.3596</v>
+      </c>
+      <c r="K546">
+        <v>1155.319984436035</v>
+      </c>
+    </row>
+    <row r="547" spans="1:11">
+      <c r="A547" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B547" t="s">
+        <v>20</v>
+      </c>
+      <c r="C547" t="s">
+        <v>31</v>
+      </c>
+      <c r="D547">
+        <v>69.4158</v>
+      </c>
+      <c r="E547">
+        <v>72.41999816894531</v>
+      </c>
+      <c r="F547">
+        <v>0.0432783050680869</v>
+      </c>
+      <c r="G547">
+        <v>4.33</v>
+      </c>
+      <c r="H547" t="s">
+        <v>20</v>
+      </c>
+      <c r="I547">
+        <v>62</v>
+      </c>
+      <c r="J547">
+        <v>4303.7796</v>
+      </c>
+      <c r="K547">
+        <v>4490.039886474609</v>
+      </c>
+    </row>
+    <row r="548" spans="1:11">
+      <c r="A548" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B548" t="s">
+        <v>21</v>
+      </c>
+      <c r="C548" t="s">
+        <v>32</v>
+      </c>
+      <c r="D548">
+        <v>8.1868</v>
+      </c>
+      <c r="E548">
+        <v>8.685000419616699</v>
+      </c>
+      <c r="F548">
+        <v>0.0608541090067791</v>
+      </c>
+      <c r="G548">
+        <v>6.09</v>
+      </c>
+      <c r="H548" t="s">
+        <v>21</v>
+      </c>
+      <c r="I548">
+        <v>431</v>
+      </c>
+      <c r="J548">
+        <v>3528.5108</v>
+      </c>
+      <c r="K548">
+        <v>3743.235180854797</v>
       </c>
     </row>
   </sheetData>
@@ -23396,7 +23853,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -25442,6 +25899,47 @@
       </c>
       <c r="M50" s="2">
         <v>0.1220634136316909</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.0742960039050797</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.0524556108412543</v>
+      </c>
+      <c r="D51" s="2">
+        <v>0.2293261368865922</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0.20617801811684</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0.0165502890146553</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0.5013774295752431</v>
+      </c>
+      <c r="H51" s="2">
+        <v>0.091955160245051</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0.1557623033896376</v>
+      </c>
+      <c r="J51" s="2">
+        <v>-0.0026240690403609</v>
+      </c>
+      <c r="K51" s="2">
+        <v>0.0432783050680869</v>
+      </c>
+      <c r="L51" s="2">
+        <v>0.0608541090067791</v>
+      </c>
+      <c r="M51" s="2">
+        <v>0.122121062294837</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -374,16 +374,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$51</c:f>
+              <c:f>grafico_dati!$B$2:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -533,6 +536,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.0742960039050797</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.0780906639152452</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -560,10 +566,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -713,16 +719,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$51</c:f>
+              <c:f>grafico_dati!$C$2:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -872,6 +881,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.0524556108412543</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.0550557135354867</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -899,10 +911,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1052,16 +1064,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$51</c:f>
+              <c:f>grafico_dati!$D$2:$D$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1211,6 +1226,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.2293261368865922</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.2335066256753495</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1238,10 +1256,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1391,16 +1409,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$51</c:f>
+              <c:f>grafico_dati!$E$2:$E$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1550,6 +1571,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.20617801811684</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.2087827805474449</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1577,10 +1601,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1730,16 +1754,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$51</c:f>
+              <c:f>grafico_dati!$F$2:$F$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1885,6 +1912,9 @@
                   <c:v>0.0307217020775603</c:v>
                 </c:pt>
                 <c:pt idx="49">
+                  <c:v>0.0165502890146553</c:v>
+                </c:pt>
+                <c:pt idx="50">
                   <c:v>0.0165502890146553</c:v>
                 </c:pt>
               </c:numCache>
@@ -1913,10 +1943,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2066,16 +2096,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$51</c:f>
+              <c:f>grafico_dati!$G$2:$G$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2225,6 +2258,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.5013774295752431</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.5096418427071594</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2252,10 +2288,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2405,16 +2441,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$51</c:f>
+              <c:f>grafico_dati!$H$2:$H$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2564,6 +2603,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.091955160245051</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.0965640419163849</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2591,10 +2633,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2744,16 +2786,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$51</c:f>
+              <c:f>grafico_dati!$I$2:$I$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2900,6 +2945,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.1557623033896376</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.1599202238347932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2927,10 +2975,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3080,16 +3128,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$51</c:f>
+              <c:f>grafico_dati!$J$2:$J$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3239,6 +3290,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>-0.0026240690403609</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-0.0040916392664449</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3266,10 +3320,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3419,16 +3473,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$51</c:f>
+              <c:f>grafico_dati!$K$2:$K$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3575,6 +3632,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.0432783050680869</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.0431343247806603</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3602,10 +3662,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3755,16 +3815,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$51</c:f>
+              <c:f>grafico_dati!$L$2:$L$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3914,6 +3977,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.0608541090067791</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.0647627898115741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3945,10 +4011,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$51</c:f>
+              <c:f>grafico_dati!$A$2:$A$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4098,16 +4164,19 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$51</c:f>
+              <c:f>grafico_dati!$M$2:$M$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4257,6 +4326,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0.122121062294837</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.1250783136895137</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4663,7 +4735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K548"/>
+  <dimension ref="A1:K559"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -23844,6 +23916,391 @@
       </c>
       <c r="K548">
         <v>3743.235180854797</v>
+      </c>
+    </row>
+    <row r="549" spans="1:11">
+      <c r="A549" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B549" t="s">
+        <v>11</v>
+      </c>
+      <c r="C549" t="s">
+        <v>22</v>
+      </c>
+      <c r="D549">
+        <v>50.07</v>
+      </c>
+      <c r="E549">
+        <v>53.97999954223633</v>
+      </c>
+      <c r="F549">
+        <v>0.0780906639152452</v>
+      </c>
+      <c r="G549">
+        <v>7.81</v>
+      </c>
+      <c r="H549" t="s">
+        <v>11</v>
+      </c>
+      <c r="I549">
+        <v>23</v>
+      </c>
+      <c r="J549">
+        <v>1151.61</v>
+      </c>
+      <c r="K549">
+        <v>1241.539989471436</v>
+      </c>
+    </row>
+    <row r="550" spans="1:11">
+      <c r="A550" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B550" t="s">
+        <v>12</v>
+      </c>
+      <c r="C550" t="s">
+        <v>23</v>
+      </c>
+      <c r="D550">
+        <v>242.3</v>
+      </c>
+      <c r="E550">
+        <v>255.6399993896484</v>
+      </c>
+      <c r="F550">
+        <v>0.0550557135354867</v>
+      </c>
+      <c r="G550">
+        <v>5.51</v>
+      </c>
+      <c r="H550" t="s">
+        <v>12</v>
+      </c>
+      <c r="I550">
+        <v>5</v>
+      </c>
+      <c r="J550">
+        <v>1211.5</v>
+      </c>
+      <c r="K550">
+        <v>1278.199996948242</v>
+      </c>
+    </row>
+    <row r="551" spans="1:11">
+      <c r="A551" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B551" t="s">
+        <v>13</v>
+      </c>
+      <c r="C551" t="s">
+        <v>24</v>
+      </c>
+      <c r="D551">
+        <v>38.273</v>
+      </c>
+      <c r="E551">
+        <v>47.20999908447266</v>
+      </c>
+      <c r="F551">
+        <v>0.2335066256753495</v>
+      </c>
+      <c r="G551">
+        <v>23.35</v>
+      </c>
+      <c r="H551" t="s">
+        <v>13</v>
+      </c>
+      <c r="I551">
+        <v>54</v>
+      </c>
+      <c r="J551">
+        <v>2066.742</v>
+      </c>
+      <c r="K551">
+        <v>2549.339950561523</v>
+      </c>
+    </row>
+    <row r="552" spans="1:11">
+      <c r="A552" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B552" t="s">
+        <v>14</v>
+      </c>
+      <c r="C552" t="s">
+        <v>25</v>
+      </c>
+      <c r="D552">
+        <v>6.5264</v>
+      </c>
+      <c r="E552">
+        <v>7.888999938964844</v>
+      </c>
+      <c r="F552">
+        <v>0.2087827805474449</v>
+      </c>
+      <c r="G552">
+        <v>20.88</v>
+      </c>
+      <c r="H552" t="s">
+        <v>14</v>
+      </c>
+      <c r="I552">
+        <v>276</v>
+      </c>
+      <c r="J552">
+        <v>1801.2864</v>
+      </c>
+      <c r="K552">
+        <v>2177.363983154297</v>
+      </c>
+    </row>
+    <row r="553" spans="1:11">
+      <c r="A553" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B553" t="s">
+        <v>15</v>
+      </c>
+      <c r="C553" t="s">
+        <v>26</v>
+      </c>
+      <c r="D553">
+        <v>197.58</v>
+      </c>
+      <c r="E553">
+        <v>200.8500061035156</v>
+      </c>
+      <c r="F553">
+        <v>0.0165502890146553</v>
+      </c>
+      <c r="G553">
+        <v>1.66</v>
+      </c>
+      <c r="H553" t="s">
+        <v>15</v>
+      </c>
+      <c r="I553">
+        <v>4</v>
+      </c>
+      <c r="J553">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K553">
+        <v>803.4000244140624</v>
+      </c>
+    </row>
+    <row r="554" spans="1:11">
+      <c r="A554" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B554" t="s">
+        <v>16</v>
+      </c>
+      <c r="C554" t="s">
+        <v>27</v>
+      </c>
+      <c r="D554">
+        <v>79.86</v>
+      </c>
+      <c r="E554">
+        <v>120.5599975585938</v>
+      </c>
+      <c r="F554">
+        <v>0.5096418427071594</v>
+      </c>
+      <c r="G554">
+        <v>50.96</v>
+      </c>
+      <c r="H554" t="s">
+        <v>16</v>
+      </c>
+      <c r="I554">
+        <v>12</v>
+      </c>
+      <c r="J554">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K554">
+        <v>1446.719970703125</v>
+      </c>
+    </row>
+    <row r="555" spans="1:11">
+      <c r="A555" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B555" t="s">
+        <v>17</v>
+      </c>
+      <c r="C555" t="s">
+        <v>28</v>
+      </c>
+      <c r="D555">
+        <v>19.7444</v>
+      </c>
+      <c r="E555">
+        <v>21.65099906921387</v>
+      </c>
+      <c r="F555">
+        <v>0.0965640419163849</v>
+      </c>
+      <c r="G555">
+        <v>9.66</v>
+      </c>
+      <c r="H555" t="s">
+        <v>17</v>
+      </c>
+      <c r="I555">
+        <v>61</v>
+      </c>
+      <c r="J555">
+        <v>1204.4084</v>
+      </c>
+      <c r="K555">
+        <v>1320.710943222046</v>
+      </c>
+    </row>
+    <row r="556" spans="1:11">
+      <c r="A556" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B556" t="s">
+        <v>18</v>
+      </c>
+      <c r="C556" t="s">
+        <v>29</v>
+      </c>
+      <c r="D556">
+        <v>129.871</v>
+      </c>
+      <c r="E556">
+        <v>150.6399993896484</v>
+      </c>
+      <c r="F556">
+        <v>0.1599202238347932</v>
+      </c>
+      <c r="G556">
+        <v>15.99</v>
+      </c>
+      <c r="H556" t="s">
+        <v>18</v>
+      </c>
+      <c r="I556">
+        <v>51</v>
+      </c>
+      <c r="J556">
+        <v>6623.421</v>
+      </c>
+      <c r="K556">
+        <v>7682.63996887207</v>
+      </c>
+    </row>
+    <row r="557" spans="1:11">
+      <c r="A557" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B557" t="s">
+        <v>19</v>
+      </c>
+      <c r="C557" t="s">
+        <v>30</v>
+      </c>
+      <c r="D557">
+        <v>34.0694</v>
+      </c>
+      <c r="E557">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="F557">
+        <v>-0.0040916392664449</v>
+      </c>
+      <c r="G557">
+        <v>-0.41</v>
+      </c>
+      <c r="H557" t="s">
+        <v>19</v>
+      </c>
+      <c r="I557">
+        <v>34</v>
+      </c>
+      <c r="J557">
+        <v>1158.3596</v>
+      </c>
+      <c r="K557">
+        <v>1153.620010375977</v>
+      </c>
+    </row>
+    <row r="558" spans="1:11">
+      <c r="A558" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B558" t="s">
+        <v>20</v>
+      </c>
+      <c r="C558" t="s">
+        <v>31</v>
+      </c>
+      <c r="D558">
+        <v>69.4158</v>
+      </c>
+      <c r="E558">
+        <v>72.41000366210938</v>
+      </c>
+      <c r="F558">
+        <v>0.0431343247806603</v>
+      </c>
+      <c r="G558">
+        <v>4.31</v>
+      </c>
+      <c r="H558" t="s">
+        <v>20</v>
+      </c>
+      <c r="I558">
+        <v>62</v>
+      </c>
+      <c r="J558">
+        <v>4303.7796</v>
+      </c>
+      <c r="K558">
+        <v>4489.420227050781</v>
+      </c>
+    </row>
+    <row r="559" spans="1:11">
+      <c r="A559" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B559" t="s">
+        <v>21</v>
+      </c>
+      <c r="C559" t="s">
+        <v>32</v>
+      </c>
+      <c r="D559">
+        <v>8.1868</v>
+      </c>
+      <c r="E559">
+        <v>8.717000007629395</v>
+      </c>
+      <c r="F559">
+        <v>0.0647627898115741</v>
+      </c>
+      <c r="G559">
+        <v>6.48</v>
+      </c>
+      <c r="H559" t="s">
+        <v>21</v>
+      </c>
+      <c r="I559">
+        <v>431</v>
+      </c>
+      <c r="J559">
+        <v>3528.5108</v>
+      </c>
+      <c r="K559">
+        <v>3757.027003288269</v>
       </c>
     </row>
   </sheetData>
@@ -23853,7 +24310,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -25940,6 +26397,47 @@
       </c>
       <c r="M51" s="2">
         <v>0.122121062294837</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0.0780906639152452</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0.0550557135354867</v>
+      </c>
+      <c r="D52" s="2">
+        <v>0.2335066256753495</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0.2087827805474449</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0.0165502890146553</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0.5096418427071594</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0.0965640419163849</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0.1599202238347932</v>
+      </c>
+      <c r="J52" s="2">
+        <v>-0.0040916392664449</v>
+      </c>
+      <c r="K52" s="2">
+        <v>0.0431343247806603</v>
+      </c>
+      <c r="L52" s="2">
+        <v>0.0647627898115741</v>
+      </c>
+      <c r="M52" s="2">
+        <v>0.1250783136895137</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -377,16 +377,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$52</c:f>
+              <c:f>grafico_dati!$B$2:$B$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -539,6 +542,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.0780906639152452</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.0627121846309697</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -566,10 +572,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -722,16 +728,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$52</c:f>
+              <c:f>grafico_dati!$C$2:$C$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -884,6 +893,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.0550557135354867</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.0482459987336527</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -911,10 +923,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1067,16 +1079,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$52</c:f>
+              <c:f>grafico_dati!$D$2:$D$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1229,6 +1244,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.2335066256753495</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.1898727801721145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1256,10 +1274,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1412,16 +1430,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$52</c:f>
+              <c:f>grafico_dati!$E$2:$E$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1574,6 +1595,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.2087827805474449</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.1582189285454138</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1601,10 +1625,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1757,16 +1781,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$52</c:f>
+              <c:f>grafico_dati!$F$2:$F$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1916,6 +1943,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.0165502890146553</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.0001012557116895</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1943,10 +1973,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2099,16 +2129,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$52</c:f>
+              <c:f>grafico_dati!$G$2:$G$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2261,6 +2294,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.5096418427071594</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.4808414993267025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2288,10 +2324,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2444,16 +2480,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$52</c:f>
+              <c:f>grafico_dati!$H$2:$H$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2606,6 +2645,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.0965640419163849</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.08947345472971729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2633,10 +2675,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2789,16 +2831,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$52</c:f>
+              <c:f>grafico_dati!$I$2:$I$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2948,6 +2993,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.1599202238347932</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.1525282216644303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2975,10 +3023,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3131,16 +3179,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$52</c:f>
+              <c:f>grafico_dati!$J$2:$J$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3293,6 +3344,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>-0.0040916392664449</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-0.0051189496215469</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3320,10 +3374,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3476,16 +3530,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$52</c:f>
+              <c:f>grafico_dati!$K$2:$K$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3635,6 +3692,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.0431343247806603</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.0388124981683069</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3662,10 +3722,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3818,16 +3878,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$52</c:f>
+              <c:f>grafico_dati!$L$2:$L$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -3980,6 +4043,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.0647627898115741</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.0487614748747842</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4011,10 +4077,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$52</c:f>
+              <c:f>grafico_dati!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4167,16 +4233,19 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$52</c:f>
+              <c:f>grafico_dati!$M$2:$M$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="51"/>
+                <c:ptCount val="52"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4329,6 +4398,9 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0.1250783136895137</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.1096913010216034</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4735,7 +4807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K559"/>
+  <dimension ref="A1:K570"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -24301,6 +24373,391 @@
       </c>
       <c r="K559">
         <v>3757.027003288269</v>
+      </c>
+    </row>
+    <row r="560" spans="1:11">
+      <c r="A560" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B560" t="s">
+        <v>11</v>
+      </c>
+      <c r="C560" t="s">
+        <v>22</v>
+      </c>
+      <c r="D560">
+        <v>50.07</v>
+      </c>
+      <c r="E560">
+        <v>53.20999908447266</v>
+      </c>
+      <c r="F560">
+        <v>0.0627121846309697</v>
+      </c>
+      <c r="G560">
+        <v>6.27</v>
+      </c>
+      <c r="H560" t="s">
+        <v>11</v>
+      </c>
+      <c r="I560">
+        <v>23</v>
+      </c>
+      <c r="J560">
+        <v>1151.61</v>
+      </c>
+      <c r="K560">
+        <v>1223.829978942871</v>
+      </c>
+    </row>
+    <row r="561" spans="1:11">
+      <c r="A561" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B561" t="s">
+        <v>12</v>
+      </c>
+      <c r="C561" t="s">
+        <v>23</v>
+      </c>
+      <c r="D561">
+        <v>242.3</v>
+      </c>
+      <c r="E561">
+        <v>253.9900054931641</v>
+      </c>
+      <c r="F561">
+        <v>0.0482459987336527</v>
+      </c>
+      <c r="G561">
+        <v>4.82</v>
+      </c>
+      <c r="H561" t="s">
+        <v>12</v>
+      </c>
+      <c r="I561">
+        <v>5</v>
+      </c>
+      <c r="J561">
+        <v>1211.5</v>
+      </c>
+      <c r="K561">
+        <v>1269.950027465821</v>
+      </c>
+    </row>
+    <row r="562" spans="1:11">
+      <c r="A562" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B562" t="s">
+        <v>13</v>
+      </c>
+      <c r="C562" t="s">
+        <v>24</v>
+      </c>
+      <c r="D562">
+        <v>38.273</v>
+      </c>
+      <c r="E562">
+        <v>45.54000091552734</v>
+      </c>
+      <c r="F562">
+        <v>0.1898727801721145</v>
+      </c>
+      <c r="G562">
+        <v>18.99</v>
+      </c>
+      <c r="H562" t="s">
+        <v>13</v>
+      </c>
+      <c r="I562">
+        <v>54</v>
+      </c>
+      <c r="J562">
+        <v>2066.742</v>
+      </c>
+      <c r="K562">
+        <v>2459.160049438477</v>
+      </c>
+    </row>
+    <row r="563" spans="1:11">
+      <c r="A563" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B563" t="s">
+        <v>14</v>
+      </c>
+      <c r="C563" t="s">
+        <v>25</v>
+      </c>
+      <c r="D563">
+        <v>6.5264</v>
+      </c>
+      <c r="E563">
+        <v>7.559000015258789</v>
+      </c>
+      <c r="F563">
+        <v>0.1582189285454138</v>
+      </c>
+      <c r="G563">
+        <v>15.82</v>
+      </c>
+      <c r="H563" t="s">
+        <v>14</v>
+      </c>
+      <c r="I563">
+        <v>276</v>
+      </c>
+      <c r="J563">
+        <v>1801.2864</v>
+      </c>
+      <c r="K563">
+        <v>2086.284004211426</v>
+      </c>
+    </row>
+    <row r="564" spans="1:11">
+      <c r="A564" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B564" t="s">
+        <v>15</v>
+      </c>
+      <c r="C564" t="s">
+        <v>26</v>
+      </c>
+      <c r="D564">
+        <v>197.58</v>
+      </c>
+      <c r="E564">
+        <v>197.6000061035156</v>
+      </c>
+      <c r="F564">
+        <v>0.0001012557116895</v>
+      </c>
+      <c r="G564">
+        <v>0.01</v>
+      </c>
+      <c r="H564" t="s">
+        <v>15</v>
+      </c>
+      <c r="I564">
+        <v>4</v>
+      </c>
+      <c r="J564">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K564">
+        <v>790.4000244140624</v>
+      </c>
+    </row>
+    <row r="565" spans="1:11">
+      <c r="A565" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B565" t="s">
+        <v>16</v>
+      </c>
+      <c r="C565" t="s">
+        <v>27</v>
+      </c>
+      <c r="D565">
+        <v>79.86</v>
+      </c>
+      <c r="E565">
+        <v>118.2600021362305</v>
+      </c>
+      <c r="F565">
+        <v>0.4808414993267025</v>
+      </c>
+      <c r="G565">
+        <v>48.08</v>
+      </c>
+      <c r="H565" t="s">
+        <v>16</v>
+      </c>
+      <c r="I565">
+        <v>12</v>
+      </c>
+      <c r="J565">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K565">
+        <v>1419.120025634766</v>
+      </c>
+    </row>
+    <row r="566" spans="1:11">
+      <c r="A566" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B566" t="s">
+        <v>17</v>
+      </c>
+      <c r="C566" t="s">
+        <v>28</v>
+      </c>
+      <c r="D566">
+        <v>19.7444</v>
+      </c>
+      <c r="E566">
+        <v>21.51099967956543</v>
+      </c>
+      <c r="F566">
+        <v>0.08947345472971729</v>
+      </c>
+      <c r="G566">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H566" t="s">
+        <v>17</v>
+      </c>
+      <c r="I566">
+        <v>61</v>
+      </c>
+      <c r="J566">
+        <v>1204.4084</v>
+      </c>
+      <c r="K566">
+        <v>1312.170980453491</v>
+      </c>
+    </row>
+    <row r="567" spans="1:11">
+      <c r="A567" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B567" t="s">
+        <v>18</v>
+      </c>
+      <c r="C567" t="s">
+        <v>29</v>
+      </c>
+      <c r="D567">
+        <v>129.871</v>
+      </c>
+      <c r="E567">
+        <v>149.6799926757812</v>
+      </c>
+      <c r="F567">
+        <v>0.1525282216644303</v>
+      </c>
+      <c r="G567">
+        <v>15.25</v>
+      </c>
+      <c r="H567" t="s">
+        <v>18</v>
+      </c>
+      <c r="I567">
+        <v>51</v>
+      </c>
+      <c r="J567">
+        <v>6623.421</v>
+      </c>
+      <c r="K567">
+        <v>7633.679626464844</v>
+      </c>
+    </row>
+    <row r="568" spans="1:11">
+      <c r="A568" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B568" t="s">
+        <v>19</v>
+      </c>
+      <c r="C568" t="s">
+        <v>30</v>
+      </c>
+      <c r="D568">
+        <v>34.0694</v>
+      </c>
+      <c r="E568">
+        <v>33.89500045776367</v>
+      </c>
+      <c r="F568">
+        <v>-0.0051189496215469</v>
+      </c>
+      <c r="G568">
+        <v>-0.51</v>
+      </c>
+      <c r="H568" t="s">
+        <v>19</v>
+      </c>
+      <c r="I568">
+        <v>34</v>
+      </c>
+      <c r="J568">
+        <v>1158.3596</v>
+      </c>
+      <c r="K568">
+        <v>1152.430015563965</v>
+      </c>
+    </row>
+    <row r="569" spans="1:11">
+      <c r="A569" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B569" t="s">
+        <v>20</v>
+      </c>
+      <c r="C569" t="s">
+        <v>31</v>
+      </c>
+      <c r="D569">
+        <v>69.4158</v>
+      </c>
+      <c r="E569">
+        <v>72.11000061035156</v>
+      </c>
+      <c r="F569">
+        <v>0.0388124981683069</v>
+      </c>
+      <c r="G569">
+        <v>3.88</v>
+      </c>
+      <c r="H569" t="s">
+        <v>20</v>
+      </c>
+      <c r="I569">
+        <v>62</v>
+      </c>
+      <c r="J569">
+        <v>4303.7796</v>
+      </c>
+      <c r="K569">
+        <v>4470.820037841797</v>
+      </c>
+    </row>
+    <row r="570" spans="1:11">
+      <c r="A570" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B570" t="s">
+        <v>21</v>
+      </c>
+      <c r="C570" t="s">
+        <v>32</v>
+      </c>
+      <c r="D570">
+        <v>8.1868</v>
+      </c>
+      <c r="E570">
+        <v>8.586000442504883</v>
+      </c>
+      <c r="F570">
+        <v>0.0487614748747842</v>
+      </c>
+      <c r="G570">
+        <v>4.88</v>
+      </c>
+      <c r="H570" t="s">
+        <v>21</v>
+      </c>
+      <c r="I570">
+        <v>431</v>
+      </c>
+      <c r="J570">
+        <v>3528.5108</v>
+      </c>
+      <c r="K570">
+        <v>3700.566190719604</v>
       </c>
     </row>
   </sheetData>
@@ -24310,7 +24767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -26438,6 +26895,47 @@
       </c>
       <c r="M52" s="2">
         <v>0.1250783136895137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.0627121846309697</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0.0482459987336527</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0.1898727801721145</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0.1582189285454138</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0.0001012557116895</v>
+      </c>
+      <c r="G53" s="2">
+        <v>0.4808414993267025</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0.08947345472971729</v>
+      </c>
+      <c r="I53" s="2">
+        <v>0.1525282216644303</v>
+      </c>
+      <c r="J53" s="2">
+        <v>-0.0051189496215469</v>
+      </c>
+      <c r="K53" s="2">
+        <v>0.0388124981683069</v>
+      </c>
+      <c r="L53" s="2">
+        <v>0.0487614748747842</v>
+      </c>
+      <c r="M53" s="2">
+        <v>0.1096913010216034</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -380,16 +380,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$53</c:f>
+              <c:f>grafico_dati!$B$2:$B$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -545,6 +548,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.0627121846309697</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.0645096712015287</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -572,10 +578,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -731,16 +737,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$53</c:f>
+              <c:f>grafico_dati!$C$2:$C$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -896,6 +905,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.0482459987336527</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.0532397727950564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -923,10 +935,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1082,16 +1094,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$53</c:f>
+              <c:f>grafico_dati!$D$2:$D$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1247,6 +1262,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.1898727801721145</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.2225328799813795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1274,10 +1292,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1433,16 +1451,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$53</c:f>
+              <c:f>grafico_dati!$E$2:$E$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1598,6 +1619,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.1582189285454138</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1888636651942765</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1625,10 +1649,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1784,16 +1808,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$53</c:f>
+              <c:f>grafico_dati!$F$2:$F$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1946,6 +1973,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.0001012557116895</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.008199195000719601</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1973,10 +2003,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2132,16 +2162,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$53</c:f>
+              <c:f>grafico_dati!$G$2:$G$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2297,6 +2330,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.4808414993267025</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.5033808860329796</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2324,10 +2360,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2483,16 +2519,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$53</c:f>
+              <c:f>grafico_dati!$H$2:$H$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2648,6 +2687,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.08947345472971729</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1115049910611523</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2675,10 +2717,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2834,16 +2876,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$53</c:f>
+              <c:f>grafico_dati!$I$2:$I$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -2996,6 +3041,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.1525282216644303</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1650791751706981</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3023,10 +3071,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3182,16 +3230,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$53</c:f>
+              <c:f>grafico_dati!$J$2:$J$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3347,6 +3398,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>-0.0051189496215469</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.0033931144455439</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3374,10 +3428,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3533,16 +3587,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$53</c:f>
+              <c:f>grafico_dati!$K$2:$K$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3695,6 +3752,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.0388124981683069</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.0458713790537756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3722,10 +3782,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3881,16 +3941,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$53</c:f>
+              <c:f>grafico_dati!$L$2:$L$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4046,6 +4109,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.0487614748747842</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.0567010337235773</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4077,10 +4143,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$53</c:f>
+              <c:f>grafico_dati!$A$2:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4236,16 +4302,19 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$53</c:f>
+              <c:f>grafico_dati!$M$2:$M$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="53"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4401,6 +4470,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0.1096913010216034</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1232704707188441</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4807,7 +4879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K570"/>
+  <dimension ref="A1:K581"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -24758,6 +24830,391 @@
       </c>
       <c r="K570">
         <v>3700.566190719604</v>
+      </c>
+    </row>
+    <row r="571" spans="1:11">
+      <c r="A571" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B571" t="s">
+        <v>11</v>
+      </c>
+      <c r="C571" t="s">
+        <v>22</v>
+      </c>
+      <c r="D571">
+        <v>50.07</v>
+      </c>
+      <c r="E571">
+        <v>53.29999923706055</v>
+      </c>
+      <c r="F571">
+        <v>0.0645096712015287</v>
+      </c>
+      <c r="G571">
+        <v>6.45</v>
+      </c>
+      <c r="H571" t="s">
+        <v>11</v>
+      </c>
+      <c r="I571">
+        <v>23</v>
+      </c>
+      <c r="J571">
+        <v>1151.61</v>
+      </c>
+      <c r="K571">
+        <v>1225.899982452393</v>
+      </c>
+    </row>
+    <row r="572" spans="1:11">
+      <c r="A572" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B572" t="s">
+        <v>12</v>
+      </c>
+      <c r="C572" t="s">
+        <v>23</v>
+      </c>
+      <c r="D572">
+        <v>242.3</v>
+      </c>
+      <c r="E572">
+        <v>255.1999969482422</v>
+      </c>
+      <c r="F572">
+        <v>0.0532397727950564</v>
+      </c>
+      <c r="G572">
+        <v>5.32</v>
+      </c>
+      <c r="H572" t="s">
+        <v>12</v>
+      </c>
+      <c r="I572">
+        <v>5</v>
+      </c>
+      <c r="J572">
+        <v>1211.5</v>
+      </c>
+      <c r="K572">
+        <v>1275.999984741211</v>
+      </c>
+    </row>
+    <row r="573" spans="1:11">
+      <c r="A573" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B573" t="s">
+        <v>13</v>
+      </c>
+      <c r="C573" t="s">
+        <v>24</v>
+      </c>
+      <c r="D573">
+        <v>38.273</v>
+      </c>
+      <c r="E573">
+        <v>46.79000091552734</v>
+      </c>
+      <c r="F573">
+        <v>0.2225328799813795</v>
+      </c>
+      <c r="G573">
+        <v>22.25</v>
+      </c>
+      <c r="H573" t="s">
+        <v>13</v>
+      </c>
+      <c r="I573">
+        <v>54</v>
+      </c>
+      <c r="J573">
+        <v>2066.742</v>
+      </c>
+      <c r="K573">
+        <v>2526.660049438477</v>
+      </c>
+    </row>
+    <row r="574" spans="1:11">
+      <c r="A574" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B574" t="s">
+        <v>14</v>
+      </c>
+      <c r="C574" t="s">
+        <v>25</v>
+      </c>
+      <c r="D574">
+        <v>6.5264</v>
+      </c>
+      <c r="E574">
+        <v>7.758999824523926</v>
+      </c>
+      <c r="F574">
+        <v>0.1888636651942765</v>
+      </c>
+      <c r="G574">
+        <v>18.89</v>
+      </c>
+      <c r="H574" t="s">
+        <v>14</v>
+      </c>
+      <c r="I574">
+        <v>276</v>
+      </c>
+      <c r="J574">
+        <v>1801.2864</v>
+      </c>
+      <c r="K574">
+        <v>2141.483951568604</v>
+      </c>
+    </row>
+    <row r="575" spans="1:11">
+      <c r="A575" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B575" t="s">
+        <v>15</v>
+      </c>
+      <c r="C575" t="s">
+        <v>26</v>
+      </c>
+      <c r="D575">
+        <v>197.58</v>
+      </c>
+      <c r="E575">
+        <v>199.1999969482422</v>
+      </c>
+      <c r="F575">
+        <v>0.008199195000719601</v>
+      </c>
+      <c r="G575">
+        <v>0.82</v>
+      </c>
+      <c r="H575" t="s">
+        <v>15</v>
+      </c>
+      <c r="I575">
+        <v>4</v>
+      </c>
+      <c r="J575">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K575">
+        <v>796.7999877929688</v>
+      </c>
+    </row>
+    <row r="576" spans="1:11">
+      <c r="A576" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B576" t="s">
+        <v>16</v>
+      </c>
+      <c r="C576" t="s">
+        <v>27</v>
+      </c>
+      <c r="D576">
+        <v>79.86</v>
+      </c>
+      <c r="E576">
+        <v>120.0599975585938</v>
+      </c>
+      <c r="F576">
+        <v>0.5033808860329796</v>
+      </c>
+      <c r="G576">
+        <v>50.34</v>
+      </c>
+      <c r="H576" t="s">
+        <v>16</v>
+      </c>
+      <c r="I576">
+        <v>12</v>
+      </c>
+      <c r="J576">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K576">
+        <v>1440.719970703125</v>
+      </c>
+    </row>
+    <row r="577" spans="1:11">
+      <c r="A577" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B577" t="s">
+        <v>17</v>
+      </c>
+      <c r="C577" t="s">
+        <v>28</v>
+      </c>
+      <c r="D577">
+        <v>19.7444</v>
+      </c>
+      <c r="E577">
+        <v>21.94599914550781</v>
+      </c>
+      <c r="F577">
+        <v>0.1115049910611523</v>
+      </c>
+      <c r="G577">
+        <v>11.15</v>
+      </c>
+      <c r="H577" t="s">
+        <v>17</v>
+      </c>
+      <c r="I577">
+        <v>61</v>
+      </c>
+      <c r="J577">
+        <v>1204.4084</v>
+      </c>
+      <c r="K577">
+        <v>1338.705947875976</v>
+      </c>
+    </row>
+    <row r="578" spans="1:11">
+      <c r="A578" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B578" t="s">
+        <v>18</v>
+      </c>
+      <c r="C578" t="s">
+        <v>29</v>
+      </c>
+      <c r="D578">
+        <v>129.871</v>
+      </c>
+      <c r="E578">
+        <v>151.3099975585938</v>
+      </c>
+      <c r="F578">
+        <v>0.1650791751706981</v>
+      </c>
+      <c r="G578">
+        <v>16.51</v>
+      </c>
+      <c r="H578" t="s">
+        <v>18</v>
+      </c>
+      <c r="I578">
+        <v>51</v>
+      </c>
+      <c r="J578">
+        <v>6623.421</v>
+      </c>
+      <c r="K578">
+        <v>7716.809875488281</v>
+      </c>
+    </row>
+    <row r="579" spans="1:11">
+      <c r="A579" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B579" t="s">
+        <v>19</v>
+      </c>
+      <c r="C579" t="s">
+        <v>30</v>
+      </c>
+      <c r="D579">
+        <v>34.0694</v>
+      </c>
+      <c r="E579">
+        <v>34.18500137329102</v>
+      </c>
+      <c r="F579">
+        <v>0.0033931144455439</v>
+      </c>
+      <c r="G579">
+        <v>0.34</v>
+      </c>
+      <c r="H579" t="s">
+        <v>19</v>
+      </c>
+      <c r="I579">
+        <v>34</v>
+      </c>
+      <c r="J579">
+        <v>1158.3596</v>
+      </c>
+      <c r="K579">
+        <v>1162.290046691895</v>
+      </c>
+    </row>
+    <row r="580" spans="1:11">
+      <c r="A580" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B580" t="s">
+        <v>20</v>
+      </c>
+      <c r="C580" t="s">
+        <v>31</v>
+      </c>
+      <c r="D580">
+        <v>69.4158</v>
+      </c>
+      <c r="E580">
+        <v>72.59999847412109</v>
+      </c>
+      <c r="F580">
+        <v>0.0458713790537756</v>
+      </c>
+      <c r="G580">
+        <v>4.59</v>
+      </c>
+      <c r="H580" t="s">
+        <v>20</v>
+      </c>
+      <c r="I580">
+        <v>62</v>
+      </c>
+      <c r="J580">
+        <v>4303.7796</v>
+      </c>
+      <c r="K580">
+        <v>4501.199905395508</v>
+      </c>
+    </row>
+    <row r="581" spans="1:11">
+      <c r="A581" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B581" t="s">
+        <v>21</v>
+      </c>
+      <c r="C581" t="s">
+        <v>32</v>
+      </c>
+      <c r="D581">
+        <v>8.1868</v>
+      </c>
+      <c r="E581">
+        <v>8.651000022888184</v>
+      </c>
+      <c r="F581">
+        <v>0.0567010337235773</v>
+      </c>
+      <c r="G581">
+        <v>5.67</v>
+      </c>
+      <c r="H581" t="s">
+        <v>21</v>
+      </c>
+      <c r="I581">
+        <v>431</v>
+      </c>
+      <c r="J581">
+        <v>3528.5108</v>
+      </c>
+      <c r="K581">
+        <v>3728.581009864807</v>
       </c>
     </row>
   </sheetData>
@@ -24767,7 +25224,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -26936,6 +27393,47 @@
       </c>
       <c r="M53" s="2">
         <v>0.1096913010216034</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.0645096712015287</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0.0532397727950564</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0.2225328799813795</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0.1888636651942765</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0.008199195000719601</v>
+      </c>
+      <c r="G54" s="2">
+        <v>0.5033808860329796</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0.1115049910611523</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0.1650791751706981</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.0033931144455439</v>
+      </c>
+      <c r="K54" s="2">
+        <v>0.0458713790537756</v>
+      </c>
+      <c r="L54" s="2">
+        <v>0.0567010337235773</v>
+      </c>
+      <c r="M54" s="2">
+        <v>0.1232704707188441</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -383,16 +383,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$54</c:f>
+              <c:f>grafico_dati!$B$2:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -551,6 +554,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.0645096712015287</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.0758937274193083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -578,10 +584,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -740,16 +746,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$54</c:f>
+              <c:f>grafico_dati!$C$2:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -908,6 +917,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.0532397727950564</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.0610400179029739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -935,10 +947,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1097,16 +1109,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$54</c:f>
+              <c:f>grafico_dati!$D$2:$D$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1265,6 +1280,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.2225328799813795</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.232330909924159</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1292,10 +1310,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1454,16 +1472,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$54</c:f>
+              <c:f>grafico_dati!$E$2:$E$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1622,6 +1643,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.1888636651942765</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.2103150539112956</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1649,10 +1673,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1811,16 +1835,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$54</c:f>
+              <c:f>grafico_dati!$F$2:$F$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -1976,6 +2003,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.008199195000719601</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.0208522975414626</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2003,10 +2033,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2165,16 +2195,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$54</c:f>
+              <c:f>grafico_dati!$G$2:$G$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2333,6 +2366,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.5033808860329796</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.5211620755939594</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2360,10 +2396,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2522,16 +2558,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$54</c:f>
+              <c:f>grafico_dati!$H$2:$H$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2690,6 +2729,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.1115049910611523</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.1035533902015315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2717,10 +2759,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2879,16 +2921,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$54</c:f>
+              <c:f>grafico_dati!$I$2:$I$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3044,6 +3089,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.1650791751706981</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.1797861048325115</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3071,10 +3119,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3233,16 +3281,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$54</c:f>
+              <c:f>grafico_dati!$J$2:$J$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3401,6 +3452,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.0033931144455439</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.0117583878994969</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3428,10 +3482,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3590,16 +3644,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$54</c:f>
+              <c:f>grafico_dati!$K$2:$K$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3755,6 +3812,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.0458713790537756</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.0599892507333299</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3782,10 +3842,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3944,16 +4004,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$54</c:f>
+              <c:f>grafico_dati!$L$2:$L$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4112,6 +4175,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.0567010337235773</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.0665950494640335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4143,10 +4209,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$54</c:f>
+              <c:f>grafico_dati!$A$2:$A$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4305,16 +4371,19 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$54</c:f>
+              <c:f>grafico_dati!$M$2:$M$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="53"/>
+                <c:ptCount val="54"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4473,6 +4542,9 @@
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0.1232704707188441</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.1354360314181373</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4879,7 +4951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K581"/>
+  <dimension ref="A1:K592"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -25215,6 +25287,391 @@
       </c>
       <c r="K581">
         <v>3728.581009864807</v>
+      </c>
+    </row>
+    <row r="582" spans="1:11">
+      <c r="A582" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B582" t="s">
+        <v>11</v>
+      </c>
+      <c r="C582" t="s">
+        <v>22</v>
+      </c>
+      <c r="D582">
+        <v>50.07</v>
+      </c>
+      <c r="E582">
+        <v>53.86999893188477</v>
+      </c>
+      <c r="F582">
+        <v>0.0758937274193083</v>
+      </c>
+      <c r="G582">
+        <v>7.59</v>
+      </c>
+      <c r="H582" t="s">
+        <v>11</v>
+      </c>
+      <c r="I582">
+        <v>23</v>
+      </c>
+      <c r="J582">
+        <v>1151.61</v>
+      </c>
+      <c r="K582">
+        <v>1239.00997543335</v>
+      </c>
+    </row>
+    <row r="583" spans="1:11">
+      <c r="A583" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B583" t="s">
+        <v>12</v>
+      </c>
+      <c r="C583" t="s">
+        <v>23</v>
+      </c>
+      <c r="D583">
+        <v>242.3</v>
+      </c>
+      <c r="E583">
+        <v>257.0899963378906</v>
+      </c>
+      <c r="F583">
+        <v>0.0610400179029739</v>
+      </c>
+      <c r="G583">
+        <v>6.1</v>
+      </c>
+      <c r="H583" t="s">
+        <v>12</v>
+      </c>
+      <c r="I583">
+        <v>5</v>
+      </c>
+      <c r="J583">
+        <v>1211.5</v>
+      </c>
+      <c r="K583">
+        <v>1285.449981689453</v>
+      </c>
+    </row>
+    <row r="584" spans="1:11">
+      <c r="A584" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B584" t="s">
+        <v>13</v>
+      </c>
+      <c r="C584" t="s">
+        <v>24</v>
+      </c>
+      <c r="D584">
+        <v>38.273</v>
+      </c>
+      <c r="E584">
+        <v>47.16500091552734</v>
+      </c>
+      <c r="F584">
+        <v>0.232330909924159</v>
+      </c>
+      <c r="G584">
+        <v>23.23</v>
+      </c>
+      <c r="H584" t="s">
+        <v>13</v>
+      </c>
+      <c r="I584">
+        <v>54</v>
+      </c>
+      <c r="J584">
+        <v>2066.742</v>
+      </c>
+      <c r="K584">
+        <v>2546.910049438477</v>
+      </c>
+    </row>
+    <row r="585" spans="1:11">
+      <c r="A585" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B585" t="s">
+        <v>14</v>
+      </c>
+      <c r="C585" t="s">
+        <v>25</v>
+      </c>
+      <c r="D585">
+        <v>6.5264</v>
+      </c>
+      <c r="E585">
+        <v>7.89900016784668</v>
+      </c>
+      <c r="F585">
+        <v>0.2103150539112956</v>
+      </c>
+      <c r="G585">
+        <v>21.03</v>
+      </c>
+      <c r="H585" t="s">
+        <v>14</v>
+      </c>
+      <c r="I585">
+        <v>276</v>
+      </c>
+      <c r="J585">
+        <v>1801.2864</v>
+      </c>
+      <c r="K585">
+        <v>2180.124046325684</v>
+      </c>
+    </row>
+    <row r="586" spans="1:11">
+      <c r="A586" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B586" t="s">
+        <v>15</v>
+      </c>
+      <c r="C586" t="s">
+        <v>26</v>
+      </c>
+      <c r="D586">
+        <v>197.58</v>
+      </c>
+      <c r="E586">
+        <v>201.6999969482422</v>
+      </c>
+      <c r="F586">
+        <v>0.0208522975414626</v>
+      </c>
+      <c r="G586">
+        <v>2.09</v>
+      </c>
+      <c r="H586" t="s">
+        <v>15</v>
+      </c>
+      <c r="I586">
+        <v>4</v>
+      </c>
+      <c r="J586">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K586">
+        <v>806.7999877929688</v>
+      </c>
+    </row>
+    <row r="587" spans="1:11">
+      <c r="A587" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B587" t="s">
+        <v>16</v>
+      </c>
+      <c r="C587" t="s">
+        <v>27</v>
+      </c>
+      <c r="D587">
+        <v>79.86</v>
+      </c>
+      <c r="E587">
+        <v>121.4800033569336</v>
+      </c>
+      <c r="F587">
+        <v>0.5211620755939594</v>
+      </c>
+      <c r="G587">
+        <v>52.12</v>
+      </c>
+      <c r="H587" t="s">
+        <v>16</v>
+      </c>
+      <c r="I587">
+        <v>12</v>
+      </c>
+      <c r="J587">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K587">
+        <v>1457.760040283203</v>
+      </c>
+    </row>
+    <row r="588" spans="1:11">
+      <c r="A588" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B588" t="s">
+        <v>17</v>
+      </c>
+      <c r="C588" t="s">
+        <v>28</v>
+      </c>
+      <c r="D588">
+        <v>19.7444</v>
+      </c>
+      <c r="E588">
+        <v>21.78899955749512</v>
+      </c>
+      <c r="F588">
+        <v>0.1035533902015315</v>
+      </c>
+      <c r="G588">
+        <v>10.36</v>
+      </c>
+      <c r="H588" t="s">
+        <v>17</v>
+      </c>
+      <c r="I588">
+        <v>61</v>
+      </c>
+      <c r="J588">
+        <v>1204.4084</v>
+      </c>
+      <c r="K588">
+        <v>1329.128973007202</v>
+      </c>
+    </row>
+    <row r="589" spans="1:11">
+      <c r="A589" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B589" t="s">
+        <v>18</v>
+      </c>
+      <c r="C589" t="s">
+        <v>29</v>
+      </c>
+      <c r="D589">
+        <v>129.871</v>
+      </c>
+      <c r="E589">
+        <v>153.2200012207031</v>
+      </c>
+      <c r="F589">
+        <v>0.1797861048325115</v>
+      </c>
+      <c r="G589">
+        <v>17.98</v>
+      </c>
+      <c r="H589" t="s">
+        <v>18</v>
+      </c>
+      <c r="I589">
+        <v>51</v>
+      </c>
+      <c r="J589">
+        <v>6623.421</v>
+      </c>
+      <c r="K589">
+        <v>7814.220062255859</v>
+      </c>
+    </row>
+    <row r="590" spans="1:11">
+      <c r="A590" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B590" t="s">
+        <v>19</v>
+      </c>
+      <c r="C590" t="s">
+        <v>30</v>
+      </c>
+      <c r="D590">
+        <v>34.0694</v>
+      </c>
+      <c r="E590">
+        <v>34.47000122070312</v>
+      </c>
+      <c r="F590">
+        <v>0.0117583878994969</v>
+      </c>
+      <c r="G590">
+        <v>1.18</v>
+      </c>
+      <c r="H590" t="s">
+        <v>19</v>
+      </c>
+      <c r="I590">
+        <v>34</v>
+      </c>
+      <c r="J590">
+        <v>1158.3596</v>
+      </c>
+      <c r="K590">
+        <v>1171.980041503906</v>
+      </c>
+    </row>
+    <row r="591" spans="1:11">
+      <c r="A591" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B591" t="s">
+        <v>20</v>
+      </c>
+      <c r="C591" t="s">
+        <v>31</v>
+      </c>
+      <c r="D591">
+        <v>69.4158</v>
+      </c>
+      <c r="E591">
+        <v>73.58000183105469</v>
+      </c>
+      <c r="F591">
+        <v>0.0599892507333299</v>
+      </c>
+      <c r="G591">
+        <v>6</v>
+      </c>
+      <c r="H591" t="s">
+        <v>20</v>
+      </c>
+      <c r="I591">
+        <v>62</v>
+      </c>
+      <c r="J591">
+        <v>4303.7796</v>
+      </c>
+      <c r="K591">
+        <v>4561.960113525391</v>
+      </c>
+    </row>
+    <row r="592" spans="1:11">
+      <c r="A592" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B592" t="s">
+        <v>21</v>
+      </c>
+      <c r="C592" t="s">
+        <v>32</v>
+      </c>
+      <c r="D592">
+        <v>8.1868</v>
+      </c>
+      <c r="E592">
+        <v>8.732000350952148</v>
+      </c>
+      <c r="F592">
+        <v>0.0665950494640335</v>
+      </c>
+      <c r="G592">
+        <v>6.66</v>
+      </c>
+      <c r="H592" t="s">
+        <v>21</v>
+      </c>
+      <c r="I592">
+        <v>431</v>
+      </c>
+      <c r="J592">
+        <v>3528.5108</v>
+      </c>
+      <c r="K592">
+        <v>3763.492151260376</v>
       </c>
     </row>
   </sheetData>
@@ -25224,7 +25681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -27434,6 +27891,47 @@
       </c>
       <c r="M54" s="2">
         <v>0.1232704707188441</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.0758937274193083</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0.0610400179029739</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0.232330909924159</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0.2103150539112956</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0.0208522975414626</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0.5211620755939594</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0.1035533902015315</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0.1797861048325115</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0.0117583878994969</v>
+      </c>
+      <c r="K55" s="2">
+        <v>0.0599892507333299</v>
+      </c>
+      <c r="L55" s="2">
+        <v>0.0665950494640335</v>
+      </c>
+      <c r="M55" s="2">
+        <v>0.1354360314181373</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -386,16 +386,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$55</c:f>
+              <c:f>grafico_dati!$B$2:$B$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -557,6 +560,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.0758937274193083</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.0587177615644738</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -584,10 +590,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -749,16 +755,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$55</c:f>
+              <c:f>grafico_dati!$C$2:$C$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -920,6 +929,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.0610400179029739</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.0524556108412543</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -947,10 +959,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1112,16 +1124,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$55</c:f>
+              <c:f>grafico_dati!$D$2:$D$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1283,6 +1298,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.232330909924159</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.1987563313070632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1310,10 +1328,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1475,16 +1493,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$55</c:f>
+              <c:f>grafico_dati!$E$2:$E$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1646,6 +1667,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.2103150539112956</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.1735412968698451</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1673,10 +1697,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1838,16 +1862,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$55</c:f>
+              <c:f>grafico_dati!$F$2:$F$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2006,6 +2033,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.0208522975414626</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.0001012557116895</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2033,10 +2063,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2198,16 +2228,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$55</c:f>
+              <c:f>grafico_dati!$G$2:$G$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2369,6 +2402,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.5211620755939594</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.4896068004567073</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2396,10 +2432,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2561,16 +2597,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$55</c:f>
+              <c:f>grafico_dati!$H$2:$H$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2732,6 +2771,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.1035533902015315</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.09747577164210371</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2759,10 +2801,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2924,16 +2966,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$55</c:f>
+              <c:f>grafico_dati!$I$2:$I$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3092,6 +3137,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.1797861048325115</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.1705461902384746</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3119,10 +3167,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3284,16 +3332,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$55</c:f>
+              <c:f>grafico_dati!$J$2:$J$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3455,6 +3506,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.0117583878994969</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.0045671034453524</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3482,10 +3536,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3647,16 +3701,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$55</c:f>
+              <c:f>grafico_dati!$K$2:$K$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3815,6 +3872,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.0599892507333299</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.0556674241209762</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3842,10 +3902,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4007,16 +4067,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$55</c:f>
+              <c:f>grafico_dati!$L$2:$L$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4178,6 +4241,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.0665950494640335</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.0526701556795792</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4209,10 +4275,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$55</c:f>
+              <c:f>grafico_dati!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4374,16 +4440,19 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$55</c:f>
+              <c:f>grafico_dati!$M$2:$M$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4545,6 +4614,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0.1354360314181373</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.1210384757179497</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4951,7 +5023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K592"/>
+  <dimension ref="A1:K603"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -25672,6 +25744,391 @@
       </c>
       <c r="K592">
         <v>3763.492151260376</v>
+      </c>
+    </row>
+    <row r="593" spans="1:11">
+      <c r="A593" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B593" t="s">
+        <v>11</v>
+      </c>
+      <c r="C593" t="s">
+        <v>22</v>
+      </c>
+      <c r="D593">
+        <v>50.07</v>
+      </c>
+      <c r="E593">
+        <v>53.0099983215332</v>
+      </c>
+      <c r="F593">
+        <v>0.0587177615644738</v>
+      </c>
+      <c r="G593">
+        <v>5.87</v>
+      </c>
+      <c r="H593" t="s">
+        <v>11</v>
+      </c>
+      <c r="I593">
+        <v>23</v>
+      </c>
+      <c r="J593">
+        <v>1151.61</v>
+      </c>
+      <c r="K593">
+        <v>1219.229961395264</v>
+      </c>
+    </row>
+    <row r="594" spans="1:11">
+      <c r="A594" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B594" t="s">
+        <v>12</v>
+      </c>
+      <c r="C594" t="s">
+        <v>23</v>
+      </c>
+      <c r="D594">
+        <v>242.3</v>
+      </c>
+      <c r="E594">
+        <v>255.009994506836</v>
+      </c>
+      <c r="F594">
+        <v>0.0524556108412543</v>
+      </c>
+      <c r="G594">
+        <v>5.25</v>
+      </c>
+      <c r="H594" t="s">
+        <v>12</v>
+      </c>
+      <c r="I594">
+        <v>5</v>
+      </c>
+      <c r="J594">
+        <v>1211.5</v>
+      </c>
+      <c r="K594">
+        <v>1275.04997253418</v>
+      </c>
+    </row>
+    <row r="595" spans="1:11">
+      <c r="A595" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B595" t="s">
+        <v>13</v>
+      </c>
+      <c r="C595" t="s">
+        <v>24</v>
+      </c>
+      <c r="D595">
+        <v>38.273</v>
+      </c>
+      <c r="E595">
+        <v>45.88000106811523</v>
+      </c>
+      <c r="F595">
+        <v>0.1987563313070632</v>
+      </c>
+      <c r="G595">
+        <v>19.88</v>
+      </c>
+      <c r="H595" t="s">
+        <v>13</v>
+      </c>
+      <c r="I595">
+        <v>54</v>
+      </c>
+      <c r="J595">
+        <v>2066.742</v>
+      </c>
+      <c r="K595">
+        <v>2477.520057678223</v>
+      </c>
+    </row>
+    <row r="596" spans="1:11">
+      <c r="A596" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B596" t="s">
+        <v>14</v>
+      </c>
+      <c r="C596" t="s">
+        <v>25</v>
+      </c>
+      <c r="D596">
+        <v>6.5264</v>
+      </c>
+      <c r="E596">
+        <v>7.658999919891357</v>
+      </c>
+      <c r="F596">
+        <v>0.1735412968698451</v>
+      </c>
+      <c r="G596">
+        <v>17.35</v>
+      </c>
+      <c r="H596" t="s">
+        <v>14</v>
+      </c>
+      <c r="I596">
+        <v>276</v>
+      </c>
+      <c r="J596">
+        <v>1801.2864</v>
+      </c>
+      <c r="K596">
+        <v>2113.883977890015</v>
+      </c>
+    </row>
+    <row r="597" spans="1:11">
+      <c r="A597" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B597" t="s">
+        <v>15</v>
+      </c>
+      <c r="C597" t="s">
+        <v>26</v>
+      </c>
+      <c r="D597">
+        <v>197.58</v>
+      </c>
+      <c r="E597">
+        <v>197.6000061035156</v>
+      </c>
+      <c r="F597">
+        <v>0.0001012557116895</v>
+      </c>
+      <c r="G597">
+        <v>0.01</v>
+      </c>
+      <c r="H597" t="s">
+        <v>15</v>
+      </c>
+      <c r="I597">
+        <v>4</v>
+      </c>
+      <c r="J597">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K597">
+        <v>790.4000244140624</v>
+      </c>
+    </row>
+    <row r="598" spans="1:11">
+      <c r="A598" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B598" t="s">
+        <v>16</v>
+      </c>
+      <c r="C598" t="s">
+        <v>27</v>
+      </c>
+      <c r="D598">
+        <v>79.86</v>
+      </c>
+      <c r="E598">
+        <v>118.9599990844727</v>
+      </c>
+      <c r="F598">
+        <v>0.4896068004567073</v>
+      </c>
+      <c r="G598">
+        <v>48.96</v>
+      </c>
+      <c r="H598" t="s">
+        <v>16</v>
+      </c>
+      <c r="I598">
+        <v>12</v>
+      </c>
+      <c r="J598">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K598">
+        <v>1427.519989013672</v>
+      </c>
+    </row>
+    <row r="599" spans="1:11">
+      <c r="A599" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B599" t="s">
+        <v>17</v>
+      </c>
+      <c r="C599" t="s">
+        <v>28</v>
+      </c>
+      <c r="D599">
+        <v>19.7444</v>
+      </c>
+      <c r="E599">
+        <v>21.66900062561035</v>
+      </c>
+      <c r="F599">
+        <v>0.09747577164210371</v>
+      </c>
+      <c r="G599">
+        <v>9.75</v>
+      </c>
+      <c r="H599" t="s">
+        <v>17</v>
+      </c>
+      <c r="I599">
+        <v>61</v>
+      </c>
+      <c r="J599">
+        <v>1204.4084</v>
+      </c>
+      <c r="K599">
+        <v>1321.809038162231</v>
+      </c>
+    </row>
+    <row r="600" spans="1:11">
+      <c r="A600" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B600" t="s">
+        <v>18</v>
+      </c>
+      <c r="C600" t="s">
+        <v>29</v>
+      </c>
+      <c r="D600">
+        <v>129.871</v>
+      </c>
+      <c r="E600">
+        <v>152.0200042724609</v>
+      </c>
+      <c r="F600">
+        <v>0.1705461902384746</v>
+      </c>
+      <c r="G600">
+        <v>17.05</v>
+      </c>
+      <c r="H600" t="s">
+        <v>18</v>
+      </c>
+      <c r="I600">
+        <v>51</v>
+      </c>
+      <c r="J600">
+        <v>6623.421</v>
+      </c>
+      <c r="K600">
+        <v>7753.020217895508</v>
+      </c>
+    </row>
+    <row r="601" spans="1:11">
+      <c r="A601" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B601" t="s">
+        <v>19</v>
+      </c>
+      <c r="C601" t="s">
+        <v>30</v>
+      </c>
+      <c r="D601">
+        <v>34.0694</v>
+      </c>
+      <c r="E601">
+        <v>34.22499847412109</v>
+      </c>
+      <c r="F601">
+        <v>0.0045671034453524</v>
+      </c>
+      <c r="G601">
+        <v>0.46</v>
+      </c>
+      <c r="H601" t="s">
+        <v>19</v>
+      </c>
+      <c r="I601">
+        <v>34</v>
+      </c>
+      <c r="J601">
+        <v>1158.3596</v>
+      </c>
+      <c r="K601">
+        <v>1163.649948120117</v>
+      </c>
+    </row>
+    <row r="602" spans="1:11">
+      <c r="A602" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B602" t="s">
+        <v>20</v>
+      </c>
+      <c r="C602" t="s">
+        <v>31</v>
+      </c>
+      <c r="D602">
+        <v>69.4158</v>
+      </c>
+      <c r="E602">
+        <v>73.27999877929688</v>
+      </c>
+      <c r="F602">
+        <v>0.0556674241209762</v>
+      </c>
+      <c r="G602">
+        <v>5.57</v>
+      </c>
+      <c r="H602" t="s">
+        <v>20</v>
+      </c>
+      <c r="I602">
+        <v>62</v>
+      </c>
+      <c r="J602">
+        <v>4303.7796</v>
+      </c>
+      <c r="K602">
+        <v>4543.359924316406</v>
+      </c>
+    </row>
+    <row r="603" spans="1:11">
+      <c r="A603" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B603" t="s">
+        <v>21</v>
+      </c>
+      <c r="C603" t="s">
+        <v>32</v>
+      </c>
+      <c r="D603">
+        <v>8.1868</v>
+      </c>
+      <c r="E603">
+        <v>8.618000030517578</v>
+      </c>
+      <c r="F603">
+        <v>0.0526701556795792</v>
+      </c>
+      <c r="G603">
+        <v>5.27</v>
+      </c>
+      <c r="H603" t="s">
+        <v>21</v>
+      </c>
+      <c r="I603">
+        <v>431</v>
+      </c>
+      <c r="J603">
+        <v>3528.5108</v>
+      </c>
+      <c r="K603">
+        <v>3714.358013153076</v>
       </c>
     </row>
   </sheetData>
@@ -25681,7 +26138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -27932,6 +28389,47 @@
       </c>
       <c r="M55" s="2">
         <v>0.1354360314181373</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.0587177615644738</v>
+      </c>
+      <c r="C56" s="2">
+        <v>0.0524556108412543</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0.1987563313070632</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0.1735412968698451</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0.0001012557116895</v>
+      </c>
+      <c r="G56" s="2">
+        <v>0.4896068004567073</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0.09747577164210371</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0.1705461902384746</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0.0045671034453524</v>
+      </c>
+      <c r="K56" s="2">
+        <v>0.0556674241209762</v>
+      </c>
+      <c r="L56" s="2">
+        <v>0.0526701556795792</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0.1210384757179497</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -389,16 +389,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$56</c:f>
+              <c:f>grafico_dati!$B$2:$B$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -563,6 +566,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.0587177615644738</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.0545236516289304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -590,10 +596,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -758,16 +764,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$56</c:f>
+              <c:f>grafico_dati!$C$2:$C$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -932,6 +941,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.0524556108412543</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.0497730111859329</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -959,10 +971,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1127,16 +1139,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$56</c:f>
+              <c:f>grafico_dati!$D$2:$D$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1301,6 +1316,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.1987563313070632</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.1900033488084369</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1328,10 +1346,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1496,16 +1514,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$56</c:f>
+              <c:f>grafico_dati!$E$2:$E$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1670,6 +1691,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.1735412968698451</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.1626623897875136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1697,10 +1721,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1865,16 +1889,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$56</c:f>
+              <c:f>grafico_dati!$F$2:$F$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2036,6 +2063,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.0001012557116895</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.0150319012640844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2063,10 +2093,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2231,16 +2261,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$56</c:f>
+              <c:f>grafico_dati!$G$2:$G$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2405,6 +2438,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.4896068004567073</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.4926120329106209</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2432,10 +2468,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2600,16 +2636,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$56</c:f>
+              <c:f>grafico_dati!$H$2:$H$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2774,6 +2813,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.09747577164210371</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.08739689802447741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2801,10 +2843,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2969,16 +3011,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$56</c:f>
+              <c:f>grafico_dati!$I$2:$I$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3140,6 +3185,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.1705461902384746</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.1641552189588611</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3167,10 +3215,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3335,16 +3383,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$56</c:f>
+              <c:f>grafico_dati!$J$2:$J$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3509,6 +3560,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.0045671034453524</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.007208774639676</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3536,10 +3590,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3704,16 +3758,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$56</c:f>
+              <c:f>grafico_dati!$K$2:$K$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3875,6 +3932,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.0556674241209762</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.0507694565416843</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3902,10 +3962,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4070,16 +4130,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$56</c:f>
+              <c:f>grafico_dati!$L$2:$L$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4244,6 +4307,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.0526701556795792</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.0474177712006078</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4275,10 +4341,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$56</c:f>
+              <c:f>grafico_dati!$A$2:$A$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4443,16 +4509,19 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$56</c:f>
+              <c:f>grafico_dati!$M$2:$M$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4617,6 +4686,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>0.1210384757179497</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.1161144117883874</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5023,7 +5095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K603"/>
+  <dimension ref="A1:K614"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -26129,6 +26201,391 @@
       </c>
       <c r="K603">
         <v>3714.358013153076</v>
+      </c>
+    </row>
+    <row r="604" spans="1:11">
+      <c r="A604" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B604" t="s">
+        <v>11</v>
+      </c>
+      <c r="C604" t="s">
+        <v>22</v>
+      </c>
+      <c r="D604">
+        <v>50.07</v>
+      </c>
+      <c r="E604">
+        <v>52.79999923706055</v>
+      </c>
+      <c r="F604">
+        <v>0.0545236516289304</v>
+      </c>
+      <c r="G604">
+        <v>5.45</v>
+      </c>
+      <c r="H604" t="s">
+        <v>11</v>
+      </c>
+      <c r="I604">
+        <v>23</v>
+      </c>
+      <c r="J604">
+        <v>1151.61</v>
+      </c>
+      <c r="K604">
+        <v>1214.399982452393</v>
+      </c>
+    </row>
+    <row r="605" spans="1:11">
+      <c r="A605" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B605" t="s">
+        <v>12</v>
+      </c>
+      <c r="C605" t="s">
+        <v>23</v>
+      </c>
+      <c r="D605">
+        <v>242.3</v>
+      </c>
+      <c r="E605">
+        <v>254.3600006103516</v>
+      </c>
+      <c r="F605">
+        <v>0.0497730111859329</v>
+      </c>
+      <c r="G605">
+        <v>4.98</v>
+      </c>
+      <c r="H605" t="s">
+        <v>12</v>
+      </c>
+      <c r="I605">
+        <v>5</v>
+      </c>
+      <c r="J605">
+        <v>1211.5</v>
+      </c>
+      <c r="K605">
+        <v>1271.800003051758</v>
+      </c>
+    </row>
+    <row r="606" spans="1:11">
+      <c r="A606" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B606" t="s">
+        <v>13</v>
+      </c>
+      <c r="C606" t="s">
+        <v>24</v>
+      </c>
+      <c r="D606">
+        <v>38.273</v>
+      </c>
+      <c r="E606">
+        <v>45.54499816894531</v>
+      </c>
+      <c r="F606">
+        <v>0.1900033488084369</v>
+      </c>
+      <c r="G606">
+        <v>19</v>
+      </c>
+      <c r="H606" t="s">
+        <v>13</v>
+      </c>
+      <c r="I606">
+        <v>54</v>
+      </c>
+      <c r="J606">
+        <v>2066.742</v>
+      </c>
+      <c r="K606">
+        <v>2459.429901123047</v>
+      </c>
+    </row>
+    <row r="607" spans="1:11">
+      <c r="A607" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B607" t="s">
+        <v>14</v>
+      </c>
+      <c r="C607" t="s">
+        <v>25</v>
+      </c>
+      <c r="D607">
+        <v>6.5264</v>
+      </c>
+      <c r="E607">
+        <v>7.587999820709229</v>
+      </c>
+      <c r="F607">
+        <v>0.1626623897875136</v>
+      </c>
+      <c r="G607">
+        <v>16.27</v>
+      </c>
+      <c r="H607" t="s">
+        <v>14</v>
+      </c>
+      <c r="I607">
+        <v>276</v>
+      </c>
+      <c r="J607">
+        <v>1801.2864</v>
+      </c>
+      <c r="K607">
+        <v>2094.287950515747</v>
+      </c>
+    </row>
+    <row r="608" spans="1:11">
+      <c r="A608" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B608" t="s">
+        <v>15</v>
+      </c>
+      <c r="C608" t="s">
+        <v>26</v>
+      </c>
+      <c r="D608">
+        <v>197.58</v>
+      </c>
+      <c r="E608">
+        <v>200.5500030517578</v>
+      </c>
+      <c r="F608">
+        <v>0.0150319012640844</v>
+      </c>
+      <c r="G608">
+        <v>1.5</v>
+      </c>
+      <c r="H608" t="s">
+        <v>15</v>
+      </c>
+      <c r="I608">
+        <v>4</v>
+      </c>
+      <c r="J608">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K608">
+        <v>802.2000122070312</v>
+      </c>
+    </row>
+    <row r="609" spans="1:11">
+      <c r="A609" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B609" t="s">
+        <v>16</v>
+      </c>
+      <c r="C609" t="s">
+        <v>27</v>
+      </c>
+      <c r="D609">
+        <v>79.86</v>
+      </c>
+      <c r="E609">
+        <v>119.1999969482422</v>
+      </c>
+      <c r="F609">
+        <v>0.4926120329106209</v>
+      </c>
+      <c r="G609">
+        <v>49.26</v>
+      </c>
+      <c r="H609" t="s">
+        <v>16</v>
+      </c>
+      <c r="I609">
+        <v>12</v>
+      </c>
+      <c r="J609">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K609">
+        <v>1430.399963378906</v>
+      </c>
+    </row>
+    <row r="610" spans="1:11">
+      <c r="A610" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B610" t="s">
+        <v>17</v>
+      </c>
+      <c r="C610" t="s">
+        <v>28</v>
+      </c>
+      <c r="D610">
+        <v>19.7444</v>
+      </c>
+      <c r="E610">
+        <v>21.46999931335449</v>
+      </c>
+      <c r="F610">
+        <v>0.08739689802447741</v>
+      </c>
+      <c r="G610">
+        <v>8.74</v>
+      </c>
+      <c r="H610" t="s">
+        <v>17</v>
+      </c>
+      <c r="I610">
+        <v>61</v>
+      </c>
+      <c r="J610">
+        <v>1204.4084</v>
+      </c>
+      <c r="K610">
+        <v>1309.669958114624</v>
+      </c>
+    </row>
+    <row r="611" spans="1:11">
+      <c r="A611" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B611" t="s">
+        <v>18</v>
+      </c>
+      <c r="C611" t="s">
+        <v>29</v>
+      </c>
+      <c r="D611">
+        <v>129.871</v>
+      </c>
+      <c r="E611">
+        <v>151.1900024414062</v>
+      </c>
+      <c r="F611">
+        <v>0.1641552189588611</v>
+      </c>
+      <c r="G611">
+        <v>16.42</v>
+      </c>
+      <c r="H611" t="s">
+        <v>18</v>
+      </c>
+      <c r="I611">
+        <v>51</v>
+      </c>
+      <c r="J611">
+        <v>6623.421</v>
+      </c>
+      <c r="K611">
+        <v>7710.690124511719</v>
+      </c>
+    </row>
+    <row r="612" spans="1:11">
+      <c r="A612" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B612" t="s">
+        <v>19</v>
+      </c>
+      <c r="C612" t="s">
+        <v>30</v>
+      </c>
+      <c r="D612">
+        <v>34.0694</v>
+      </c>
+      <c r="E612">
+        <v>34.31499862670898</v>
+      </c>
+      <c r="F612">
+        <v>0.007208774639676</v>
+      </c>
+      <c r="G612">
+        <v>0.72</v>
+      </c>
+      <c r="H612" t="s">
+        <v>19</v>
+      </c>
+      <c r="I612">
+        <v>34</v>
+      </c>
+      <c r="J612">
+        <v>1158.3596</v>
+      </c>
+      <c r="K612">
+        <v>1166.709953308105</v>
+      </c>
+    </row>
+    <row r="613" spans="1:11">
+      <c r="A613" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B613" t="s">
+        <v>20</v>
+      </c>
+      <c r="C613" t="s">
+        <v>31</v>
+      </c>
+      <c r="D613">
+        <v>69.4158</v>
+      </c>
+      <c r="E613">
+        <v>72.94000244140625</v>
+      </c>
+      <c r="F613">
+        <v>0.0507694565416843</v>
+      </c>
+      <c r="G613">
+        <v>5.08</v>
+      </c>
+      <c r="H613" t="s">
+        <v>20</v>
+      </c>
+      <c r="I613">
+        <v>62</v>
+      </c>
+      <c r="J613">
+        <v>4303.7796</v>
+      </c>
+      <c r="K613">
+        <v>4522.280151367188</v>
+      </c>
+    </row>
+    <row r="614" spans="1:11">
+      <c r="A614" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B614" t="s">
+        <v>21</v>
+      </c>
+      <c r="C614" t="s">
+        <v>32</v>
+      </c>
+      <c r="D614">
+        <v>8.1868</v>
+      </c>
+      <c r="E614">
+        <v>8.574999809265137</v>
+      </c>
+      <c r="F614">
+        <v>0.0474177712006078</v>
+      </c>
+      <c r="G614">
+        <v>4.74</v>
+      </c>
+      <c r="H614" t="s">
+        <v>21</v>
+      </c>
+      <c r="I614">
+        <v>431</v>
+      </c>
+      <c r="J614">
+        <v>3528.5108</v>
+      </c>
+      <c r="K614">
+        <v>3695.824917793274</v>
       </c>
     </row>
   </sheetData>
@@ -26138,7 +26595,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -28430,6 +28887,47 @@
       </c>
       <c r="M56" s="2">
         <v>0.1210384757179497</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0.0545236516289304</v>
+      </c>
+      <c r="C57" s="2">
+        <v>0.0497730111859329</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0.1900033488084369</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0.1626623897875136</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0.0150319012640844</v>
+      </c>
+      <c r="G57" s="2">
+        <v>0.4926120329106209</v>
+      </c>
+      <c r="H57" s="2">
+        <v>0.08739689802447741</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0.1641552189588611</v>
+      </c>
+      <c r="J57" s="2">
+        <v>0.007208774639676</v>
+      </c>
+      <c r="K57" s="2">
+        <v>0.0507694565416843</v>
+      </c>
+      <c r="L57" s="2">
+        <v>0.0474177712006078</v>
+      </c>
+      <c r="M57" s="2">
+        <v>0.1161144117883874</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -392,16 +392,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$57</c:f>
+              <c:f>grafico_dati!$B$2:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -569,6 +572,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.0545236516289304</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.0503295416933871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -596,10 +602,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -767,16 +773,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$57</c:f>
+              <c:f>grafico_dati!$C$2:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -944,6 +953,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.0497730111859329</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.0563351091549408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -971,10 +983,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1142,16 +1154,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$57</c:f>
+              <c:f>grafico_dati!$D$2:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1319,6 +1334,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.1900033488084369</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.1753716878831437</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1346,10 +1364,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1517,16 +1535,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$57</c:f>
+              <c:f>grafico_dati!$E$2:$E$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1694,6 +1715,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.1626623897875136</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.1467271705677943</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1721,10 +1745,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1892,16 +1916,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$57</c:f>
+              <c:f>grafico_dati!$F$2:$F$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2066,6 +2093,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.0150319012640844</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.0180685995368172</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2093,10 +2123,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2264,16 +2294,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$57</c:f>
+              <c:f>grafico_dati!$G$2:$G$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2441,6 +2474,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.4926120329106209</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.4876033439989709</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2468,10 +2504,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2639,16 +2675,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$57</c:f>
+              <c:f>grafico_dati!$H$2:$H$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2816,6 +2855,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.08739689802447741</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.08511776691419071</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2843,10 +2885,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3014,16 +3056,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$57</c:f>
+              <c:f>grafico_dati!$I$2:$I$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3188,6 +3233,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.1641552189588611</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.1627691671492166</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3215,10 +3263,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3386,16 +3434,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$57</c:f>
+              <c:f>grafico_dati!$J$2:$J$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3563,6 +3614,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.007208774639676</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.0136662179965632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3590,10 +3644,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3761,16 +3815,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$57</c:f>
+              <c:f>grafico_dati!$K$2:$K$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3935,6 +3992,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.0507694565416843</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.0532184403313302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3962,10 +4022,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4133,16 +4193,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$57</c:f>
+              <c:f>grafico_dati!$L$2:$L$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4310,6 +4373,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.0474177712006078</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.0404553243083807</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4341,10 +4407,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$57</c:f>
+              <c:f>grafico_dati!$A$2:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4512,16 +4578,19 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$57</c:f>
+              <c:f>grafico_dati!$M$2:$M$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0.08659212287311968</c:v>
                 </c:pt>
@@ -4689,6 +4758,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>0.1161144117883874</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.1130216028713822</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5095,7 +5167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K614"/>
+  <dimension ref="A1:K625"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -26586,6 +26658,391 @@
       </c>
       <c r="K614">
         <v>3695.824917793274</v>
+      </c>
+    </row>
+    <row r="615" spans="1:11">
+      <c r="A615" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B615" t="s">
+        <v>11</v>
+      </c>
+      <c r="C615" t="s">
+        <v>22</v>
+      </c>
+      <c r="D615">
+        <v>50.07</v>
+      </c>
+      <c r="E615">
+        <v>52.59000015258789</v>
+      </c>
+      <c r="F615">
+        <v>0.0503295416933871</v>
+      </c>
+      <c r="G615">
+        <v>5.03</v>
+      </c>
+      <c r="H615" t="s">
+        <v>11</v>
+      </c>
+      <c r="I615">
+        <v>23</v>
+      </c>
+      <c r="J615">
+        <v>1151.61</v>
+      </c>
+      <c r="K615">
+        <v>1209.570003509521</v>
+      </c>
+    </row>
+    <row r="616" spans="1:11">
+      <c r="A616" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B616" t="s">
+        <v>12</v>
+      </c>
+      <c r="C616" t="s">
+        <v>23</v>
+      </c>
+      <c r="D616">
+        <v>242.3</v>
+      </c>
+      <c r="E616">
+        <v>255.9499969482422</v>
+      </c>
+      <c r="F616">
+        <v>0.0563351091549408</v>
+      </c>
+      <c r="G616">
+        <v>5.63</v>
+      </c>
+      <c r="H616" t="s">
+        <v>12</v>
+      </c>
+      <c r="I616">
+        <v>5</v>
+      </c>
+      <c r="J616">
+        <v>1211.5</v>
+      </c>
+      <c r="K616">
+        <v>1279.749984741211</v>
+      </c>
+    </row>
+    <row r="617" spans="1:11">
+      <c r="A617" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B617" t="s">
+        <v>13</v>
+      </c>
+      <c r="C617" t="s">
+        <v>24</v>
+      </c>
+      <c r="D617">
+        <v>38.273</v>
+      </c>
+      <c r="E617">
+        <v>44.98500061035156</v>
+      </c>
+      <c r="F617">
+        <v>0.1753716878831437</v>
+      </c>
+      <c r="G617">
+        <v>17.54</v>
+      </c>
+      <c r="H617" t="s">
+        <v>13</v>
+      </c>
+      <c r="I617">
+        <v>54</v>
+      </c>
+      <c r="J617">
+        <v>2066.742</v>
+      </c>
+      <c r="K617">
+        <v>2429.190032958984</v>
+      </c>
+    </row>
+    <row r="618" spans="1:11">
+      <c r="A618" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B618" t="s">
+        <v>14</v>
+      </c>
+      <c r="C618" t="s">
+        <v>25</v>
+      </c>
+      <c r="D618">
+        <v>6.5264</v>
+      </c>
+      <c r="E618">
+        <v>7.484000205993652</v>
+      </c>
+      <c r="F618">
+        <v>0.1467271705677943</v>
+      </c>
+      <c r="G618">
+        <v>14.67</v>
+      </c>
+      <c r="H618" t="s">
+        <v>14</v>
+      </c>
+      <c r="I618">
+        <v>276</v>
+      </c>
+      <c r="J618">
+        <v>1801.2864</v>
+      </c>
+      <c r="K618">
+        <v>2065.584056854248</v>
+      </c>
+    </row>
+    <row r="619" spans="1:11">
+      <c r="A619" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B619" t="s">
+        <v>15</v>
+      </c>
+      <c r="C619" t="s">
+        <v>26</v>
+      </c>
+      <c r="D619">
+        <v>197.58</v>
+      </c>
+      <c r="E619">
+        <v>201.1499938964844</v>
+      </c>
+      <c r="F619">
+        <v>0.0180685995368172</v>
+      </c>
+      <c r="G619">
+        <v>1.81</v>
+      </c>
+      <c r="H619" t="s">
+        <v>15</v>
+      </c>
+      <c r="I619">
+        <v>4</v>
+      </c>
+      <c r="J619">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K619">
+        <v>804.5999755859376</v>
+      </c>
+    </row>
+    <row r="620" spans="1:11">
+      <c r="A620" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B620" t="s">
+        <v>16</v>
+      </c>
+      <c r="C620" t="s">
+        <v>27</v>
+      </c>
+      <c r="D620">
+        <v>79.86</v>
+      </c>
+      <c r="E620">
+        <v>118.8000030517578</v>
+      </c>
+      <c r="F620">
+        <v>0.4876033439989709</v>
+      </c>
+      <c r="G620">
+        <v>48.76</v>
+      </c>
+      <c r="H620" t="s">
+        <v>16</v>
+      </c>
+      <c r="I620">
+        <v>12</v>
+      </c>
+      <c r="J620">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K620">
+        <v>1425.600036621094</v>
+      </c>
+    </row>
+    <row r="621" spans="1:11">
+      <c r="A621" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B621" t="s">
+        <v>17</v>
+      </c>
+      <c r="C621" t="s">
+        <v>28</v>
+      </c>
+      <c r="D621">
+        <v>19.7444</v>
+      </c>
+      <c r="E621">
+        <v>21.42499923706055</v>
+      </c>
+      <c r="F621">
+        <v>0.08511776691419071</v>
+      </c>
+      <c r="G621">
+        <v>8.51</v>
+      </c>
+      <c r="H621" t="s">
+        <v>17</v>
+      </c>
+      <c r="I621">
+        <v>61</v>
+      </c>
+      <c r="J621">
+        <v>1204.4084</v>
+      </c>
+      <c r="K621">
+        <v>1306.924953460693</v>
+      </c>
+    </row>
+    <row r="622" spans="1:11">
+      <c r="A622" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B622" t="s">
+        <v>18</v>
+      </c>
+      <c r="C622" t="s">
+        <v>29</v>
+      </c>
+      <c r="D622">
+        <v>129.871</v>
+      </c>
+      <c r="E622">
+        <v>151.0099945068359</v>
+      </c>
+      <c r="F622">
+        <v>0.1627691671492166</v>
+      </c>
+      <c r="G622">
+        <v>16.28</v>
+      </c>
+      <c r="H622" t="s">
+        <v>18</v>
+      </c>
+      <c r="I622">
+        <v>51</v>
+      </c>
+      <c r="J622">
+        <v>6623.421</v>
+      </c>
+      <c r="K622">
+        <v>7701.509719848633</v>
+      </c>
+    </row>
+    <row r="623" spans="1:11">
+      <c r="A623" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B623" t="s">
+        <v>19</v>
+      </c>
+      <c r="C623" t="s">
+        <v>30</v>
+      </c>
+      <c r="D623">
+        <v>34.0694</v>
+      </c>
+      <c r="E623">
+        <v>34.53499984741211</v>
+      </c>
+      <c r="F623">
+        <v>0.0136662179965632</v>
+      </c>
+      <c r="G623">
+        <v>1.37</v>
+      </c>
+      <c r="H623" t="s">
+        <v>19</v>
+      </c>
+      <c r="I623">
+        <v>34</v>
+      </c>
+      <c r="J623">
+        <v>1158.3596</v>
+      </c>
+      <c r="K623">
+        <v>1174.189994812012</v>
+      </c>
+    </row>
+    <row r="624" spans="1:11">
+      <c r="A624" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B624" t="s">
+        <v>20</v>
+      </c>
+      <c r="C624" t="s">
+        <v>31</v>
+      </c>
+      <c r="D624">
+        <v>69.4158</v>
+      </c>
+      <c r="E624">
+        <v>73.11000061035156</v>
+      </c>
+      <c r="F624">
+        <v>0.0532184403313302</v>
+      </c>
+      <c r="G624">
+        <v>5.32</v>
+      </c>
+      <c r="H624" t="s">
+        <v>20</v>
+      </c>
+      <c r="I624">
+        <v>62</v>
+      </c>
+      <c r="J624">
+        <v>4303.7796</v>
+      </c>
+      <c r="K624">
+        <v>4532.820037841797</v>
+      </c>
+    </row>
+    <row r="625" spans="1:11">
+      <c r="A625" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B625" t="s">
+        <v>21</v>
+      </c>
+      <c r="C625" t="s">
+        <v>32</v>
+      </c>
+      <c r="D625">
+        <v>8.1868</v>
+      </c>
+      <c r="E625">
+        <v>8.517999649047852</v>
+      </c>
+      <c r="F625">
+        <v>0.0404553243083807</v>
+      </c>
+      <c r="G625">
+        <v>4.05</v>
+      </c>
+      <c r="H625" t="s">
+        <v>21</v>
+      </c>
+      <c r="I625">
+        <v>431</v>
+      </c>
+      <c r="J625">
+        <v>3528.5108</v>
+      </c>
+      <c r="K625">
+        <v>3671.257848739624</v>
       </c>
     </row>
   </sheetData>
@@ -26595,7 +27052,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -28928,6 +29385,47 @@
       </c>
       <c r="M57" s="2">
         <v>0.1161144117883874</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0.0503295416933871</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0.0563351091549408</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0.1753716878831437</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0.1467271705677943</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0.0180685995368172</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0.4876033439989709</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0.08511776691419071</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0.1627691671492166</v>
+      </c>
+      <c r="J58" s="2">
+        <v>0.0136662179965632</v>
+      </c>
+      <c r="K58" s="2">
+        <v>0.0532184403313302</v>
+      </c>
+      <c r="L58" s="2">
+        <v>0.0404553243083807</v>
+      </c>
+      <c r="M58" s="2">
+        <v>0.1130216028713822</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -395,16 +395,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$58</c:f>
+              <c:f>grafico_dati!$B$2:$B$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -575,6 +578,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.0503295416933871</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.0603155612659853</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -602,10 +608,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -776,16 +782,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$58</c:f>
+              <c:f>grafico_dati!$C$2:$C$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -956,6 +965,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.0563351091549408</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.06624022329143869</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -983,10 +995,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1157,16 +1169,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$58</c:f>
+              <c:f>grafico_dati!$D$2:$D$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1337,6 +1352,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.1753716878831437</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.1978418524992324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1364,10 +1382,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1538,16 +1556,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$58</c:f>
+              <c:f>grafico_dati!$E$2:$E$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1718,6 +1739,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.1467271705677943</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.1740010081041265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1745,10 +1769,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1919,16 +1943,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$58</c:f>
+              <c:f>grafico_dati!$F$2:$F$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2096,6 +2123,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.0180685995368172</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.0329993223176212</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2123,10 +2153,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2297,16 +2327,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$58</c:f>
+              <c:f>grafico_dati!$G$2:$G$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2477,6 +2510,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.4876033439989709</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.5126471706956901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2504,10 +2540,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2678,16 +2714,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$58</c:f>
+              <c:f>grafico_dati!$H$2:$H$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2858,6 +2897,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.08511776691419071</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.0921577346500979</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2885,10 +2927,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3059,16 +3101,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$58</c:f>
+              <c:f>grafico_dati!$I$2:$I$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3236,6 +3281,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.1627691671492166</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.1732411016869623</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3263,10 +3311,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3437,16 +3485,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$58</c:f>
+              <c:f>grafico_dati!$J$2:$J$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3617,6 +3668,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.0136662179965632</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.0202703399981567</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3644,10 +3698,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3818,16 +3872,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$58</c:f>
+              <c:f>grafico_dati!$K$2:$K$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -3995,6 +4052,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.0532184403313302</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.0601332310207562</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4022,10 +4082,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4196,16 +4256,19 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$58</c:f>
+              <c:f>grafico_dati!$L$2:$L$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4376,6 +4439,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>0.0404553243083807</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.0537694648753486</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4407,10 +4473,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$58</c:f>
+              <c:f>grafico_dati!$A$2:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4581,186 +4647,192 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$58</c:f>
+              <c:f>grafico_dati!$M$2:$M$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
-                  <c:v>0.08659212287311968</c:v>
+                  <c:v>0.08578526067735348</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.08575413785832886</c:v>
+                  <c:v>0.0848854524083833</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.08313910176808248</c:v>
+                  <c:v>0.08250566795836645</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.08013679690745534</c:v>
+                  <c:v>0.07924391397719122</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.05511860933311308</c:v>
+                  <c:v>0.05421593878442521</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.067733222569895</c:v>
+                  <c:v>0.06671973433862921</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.05588978697012448</c:v>
+                  <c:v>0.05487546664171727</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.04393944472218569</c:v>
+                  <c:v>0.04296791492621166</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.03947997164330386</c:v>
+                  <c:v>0.03841243925054116</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.05996044742932116</c:v>
+                  <c:v>0.05862776438148121</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.05126016601743588</c:v>
+                  <c:v>0.04996167796802142</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.04322778601843358</c:v>
+                  <c:v>0.04194797007897466</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.04040918396084137</c:v>
+                  <c:v>0.03919927747478447</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04595019140029666</c:v>
+                  <c:v>0.04464666041586129</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.05050291159109199</c:v>
+                  <c:v>0.04922982946951349</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04322410959754541</c:v>
+                  <c:v>0.04175021033129345</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.02330435739138426</c:v>
+                  <c:v>0.02168548538232229</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.009025881265433133</c:v>
+                  <c:v>0.007532059620589004</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.01627949441484677</c:v>
+                  <c:v>0.01475679976827537</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.01727757383861817</c:v>
+                  <c:v>0.01577758739905799</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.02824973281511878</c:v>
+                  <c:v>0.0268888783186112</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.01576261540427626</c:v>
+                  <c:v>0.0144989311582131</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.003483954271819245</c:v>
+                  <c:v>0.002313506475123628</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-0.002466865919742989</c:v>
+                  <c:v>-0.00363055768215681</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.009055650800799953</c:v>
+                  <c:v>0.007929612705902978</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.03533260048320974</c:v>
+                  <c:v>0.03412057350940034</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.03157264743845434</c:v>
+                  <c:v>0.03037341549108197</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.0260431799791101</c:v>
+                  <c:v>0.02462149295107285</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.06098925490738094</c:v>
+                  <c:v>0.05945369050629257</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.06026859412382479</c:v>
+                  <c:v>0.05877155396624834</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.06369755078311989</c:v>
+                  <c:v>0.06217457749550381</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.06238606925142931</c:v>
+                  <c:v>0.06092384794331718</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.07495053702515309</c:v>
+                  <c:v>0.07329552134152562</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.07659257522140828</c:v>
+                  <c:v>0.07495365573205115</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.08115264620024942</c:v>
+                  <c:v>0.07932797058781027</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.09736286772558467</c:v>
+                  <c:v>0.09567540843536637</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.09203721782375407</c:v>
+                  <c:v>0.09037825160039192</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.08831685181213</c:v>
+                  <c:v>0.08655084455046214</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.09172554739087047</c:v>
+                  <c:v>0.08974289248363676</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.09386687305062402</c:v>
+                  <c:v>0.0920819848683343</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.09174206280623287</c:v>
+                  <c:v>0.08986156675165935</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1043830270766006</c:v>
+                  <c:v>0.101782379702843</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.08600291481845979</c:v>
+                  <c:v>0.0840756309665105</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.08458832942783934</c:v>
+                  <c:v>0.0825686513569428</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.09416421875041814</c:v>
+                  <c:v>0.09226017051480007</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.0957593885985335</c:v>
+                  <c:v>0.0936535273601502</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.1070343328499763</c:v>
+                  <c:v>0.1048541764125344</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1246536656368895</c:v>
+                  <c:v>0.1224705852196375</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1220634136316909</c:v>
+                  <c:v>0.1197464254687215</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.122121062294837</c:v>
+                  <c:v>0.119766983368647</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1250783136895137</c:v>
+                  <c:v>0.1226407334737896</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1096913010216034</c:v>
+                  <c:v>0.1075247043083143</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1232704707188441</c:v>
+                  <c:v>0.1210082521046998</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1354360314181373</c:v>
+                  <c:v>0.1331020971705092</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1210384757179497</c:v>
+                  <c:v>0.1188405317979211</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1161144117883874</c:v>
+                  <c:v>0.1140592416778508</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1130216028713822</c:v>
+                  <c:v>0.11114665660908</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.1238170024713718</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5167,7 +5239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K625"/>
+  <dimension ref="A1:K636"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5511,13 +5583,13 @@
         <v>19</v>
       </c>
       <c r="I10">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J10">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K10">
-        <v>1209.209953308105</v>
+        <v>1707.119934082031</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -5896,13 +5968,13 @@
         <v>19</v>
       </c>
       <c r="I21">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J21">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K21">
-        <v>1204.449974060059</v>
+        <v>1700.399963378906</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -6281,13 +6353,13 @@
         <v>19</v>
       </c>
       <c r="I32">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J32">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K32">
-        <v>1215.839942932129</v>
+        <v>1716.479919433594</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -6666,13 +6738,13 @@
         <v>19</v>
       </c>
       <c r="I43">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J43">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K43">
-        <v>1196.459953308105</v>
+        <v>1689.119934082031</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -7051,13 +7123,13 @@
         <v>19</v>
       </c>
       <c r="I54">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J54">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K54">
-        <v>1166.879989624023</v>
+        <v>1647.359985351562</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -7436,13 +7508,13 @@
         <v>19</v>
       </c>
       <c r="I65">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J65">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K65">
-        <v>1174.699974060059</v>
+        <v>1658.399963378906</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -7821,13 +7893,13 @@
         <v>19</v>
       </c>
       <c r="I76">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J76">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K76">
-        <v>1160.930015563965</v>
+        <v>1638.960021972656</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -8206,13 +8278,13 @@
         <v>19</v>
       </c>
       <c r="I87">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J87">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K87">
-        <v>1149.709953308105</v>
+        <v>1623.119934082031</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -8591,13 +8663,13 @@
         <v>19</v>
       </c>
       <c r="I98">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J98">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K98">
-        <v>1138.660057067871</v>
+        <v>1607.520080566406</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -8941,13 +9013,13 @@
         <v>19</v>
       </c>
       <c r="I108">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J108">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K108">
-        <v>1148.689994812012</v>
+        <v>1621.679992675781</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -9326,13 +9398,13 @@
         <v>19</v>
       </c>
       <c r="I119">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J119">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K119">
-        <v>1138.149948120117</v>
+        <v>1606.799926757812</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -9711,13 +9783,13 @@
         <v>19</v>
       </c>
       <c r="I130">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J130">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K130">
-        <v>1129.990020751953</v>
+        <v>1595.280029296875</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -10096,13 +10168,13 @@
         <v>19</v>
       </c>
       <c r="I141">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J141">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K141">
-        <v>1131.009979248047</v>
+        <v>1596.719970703125</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -10481,13 +10553,13 @@
         <v>19</v>
       </c>
       <c r="I152">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J152">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K152">
-        <v>1131.689994812012</v>
+        <v>1597.679992675781</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -10866,13 +10938,13 @@
         <v>19</v>
       </c>
       <c r="I163">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J163">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K163">
-        <v>1138.829963684082</v>
+        <v>1607.759948730469</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -11251,13 +11323,13 @@
         <v>19</v>
       </c>
       <c r="I174">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J174">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K174">
-        <v>1118.089942932129</v>
+        <v>1578.479919433594</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -11636,13 +11708,13 @@
         <v>19</v>
       </c>
       <c r="I185">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J185">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K185">
-        <v>1086.129989624023</v>
+        <v>1533.359985351562</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -12021,13 +12093,13 @@
         <v>19</v>
       </c>
       <c r="I196">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J196">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K196">
-        <v>1077.120010375977</v>
+        <v>1520.640014648438</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -12406,13 +12478,13 @@
         <v>19</v>
       </c>
       <c r="I207">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J207">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K207">
-        <v>1083.75</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -12791,13 +12863,13 @@
         <v>19</v>
       </c>
       <c r="I218">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J218">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K218">
-        <v>1086.300025939941</v>
+        <v>1533.600036621094</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -13176,13 +13248,13 @@
         <v>19</v>
       </c>
       <c r="I229">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J229">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K229">
-        <v>1107.550025939941</v>
+        <v>1563.600036621094</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -13561,13 +13633,13 @@
         <v>19</v>
       </c>
       <c r="I240">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J240">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K240">
-        <v>1099.050025939941</v>
+        <v>1551.600036621094</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -13946,13 +14018,13 @@
         <v>19</v>
       </c>
       <c r="I251">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J251">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K251">
-        <v>1090.550025939941</v>
+        <v>1539.600036621094</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -14296,13 +14368,13 @@
         <v>19</v>
       </c>
       <c r="I261">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J261">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K261">
-        <v>1102.790046691895</v>
+        <v>1556.880065917969</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -14681,13 +14753,13 @@
         <v>19</v>
       </c>
       <c r="I272">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J272">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K272">
-        <v>1099.730041503906</v>
+        <v>1552.56005859375</v>
       </c>
     </row>
     <row r="273" spans="1:11">
@@ -15066,13 +15138,13 @@
         <v>19</v>
       </c>
       <c r="I283">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J283">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K283">
-        <v>1124.88996887207</v>
+        <v>1588.079956054688</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -15451,13 +15523,13 @@
         <v>19</v>
       </c>
       <c r="I294">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J294">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K294">
-        <v>1121.319984436035</v>
+        <v>1583.039978027344</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -15836,13 +15908,13 @@
         <v>19</v>
       </c>
       <c r="I305">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J305">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K305">
-        <v>1101.259979248047</v>
+        <v>1554.719970703125</v>
       </c>
     </row>
     <row r="306" spans="1:11">
@@ -16221,13 +16293,13 @@
         <v>19</v>
       </c>
       <c r="I316">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J316">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K316">
-        <v>1134.75</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="317" spans="1:11">
@@ -16606,13 +16678,13 @@
         <v>19</v>
       </c>
       <c r="I327">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J327">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K327">
-        <v>1136.279937744141</v>
+        <v>1604.159912109375</v>
       </c>
     </row>
     <row r="328" spans="1:11">
@@ -16991,13 +17063,13 @@
         <v>19</v>
       </c>
       <c r="I338">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J338">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K338">
-        <v>1138.660057067871</v>
+        <v>1607.520080566406</v>
       </c>
     </row>
     <row r="339" spans="1:11">
@@ -17376,13 +17448,13 @@
         <v>19</v>
       </c>
       <c r="I349">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J349">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K349">
-        <v>1140.870010375977</v>
+        <v>1610.640014648438</v>
       </c>
     </row>
     <row r="350" spans="1:11">
@@ -17761,13 +17833,13 @@
         <v>19</v>
       </c>
       <c r="I360">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J360">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K360">
-        <v>1143.589942932129</v>
+        <v>1614.479919433594</v>
       </c>
     </row>
     <row r="361" spans="1:11">
@@ -18146,13 +18218,13 @@
         <v>19</v>
       </c>
       <c r="I371">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J371">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K371">
-        <v>1146.480041503906</v>
+        <v>1618.56005859375</v>
       </c>
     </row>
     <row r="372" spans="1:11">
@@ -18531,13 +18603,13 @@
         <v>19</v>
       </c>
       <c r="I382">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J382">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K382">
-        <v>1140.36003112793</v>
+        <v>1609.920043945312</v>
       </c>
     </row>
     <row r="383" spans="1:11">
@@ -18916,13 +18988,13 @@
         <v>19</v>
       </c>
       <c r="I393">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J393">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K393">
-        <v>1167.560005187988</v>
+        <v>1648.320007324219</v>
       </c>
     </row>
     <row r="394" spans="1:11">
@@ -19301,13 +19373,13 @@
         <v>19</v>
       </c>
       <c r="I404">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J404">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K404">
-        <v>1163.13996887207</v>
+        <v>1642.079956054688</v>
       </c>
     </row>
     <row r="405" spans="1:11">
@@ -19686,13 +19758,13 @@
         <v>19</v>
       </c>
       <c r="I415">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J415">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K415">
-        <v>1152.259979248047</v>
+        <v>1626.719970703125</v>
       </c>
     </row>
     <row r="416" spans="1:11">
@@ -20071,13 +20143,13 @@
         <v>19</v>
       </c>
       <c r="I426">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J426">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K426">
-        <v>1142.910057067871</v>
+        <v>1613.520080566406</v>
       </c>
     </row>
     <row r="427" spans="1:11">
@@ -20456,13 +20528,13 @@
         <v>19</v>
       </c>
       <c r="I437">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J437">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K437">
-        <v>1157.529937744141</v>
+        <v>1634.159912109375</v>
       </c>
     </row>
     <row r="438" spans="1:11">
@@ -20841,13 +20913,13 @@
         <v>19</v>
       </c>
       <c r="I448">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J448">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K448">
-        <v>1149.199974060059</v>
+        <v>1622.399963378906</v>
       </c>
     </row>
     <row r="449" spans="1:11">
@@ -21226,13 +21298,13 @@
         <v>19</v>
       </c>
       <c r="I459">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J459">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K459">
-        <v>1146.819984436035</v>
+        <v>1619.039978027344</v>
       </c>
     </row>
     <row r="460" spans="1:11">
@@ -21576,13 +21648,13 @@
         <v>19</v>
       </c>
       <c r="I469">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J469">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K469">
-        <v>1139.680015563965</v>
+        <v>1608.960021972656</v>
       </c>
     </row>
     <row r="470" spans="1:11">
@@ -21961,13 +22033,13 @@
         <v>19</v>
       </c>
       <c r="I480">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J480">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K480">
-        <v>1132.370010375977</v>
+        <v>1598.640014648438</v>
       </c>
     </row>
     <row r="481" spans="1:11">
@@ -22346,13 +22418,13 @@
         <v>19</v>
       </c>
       <c r="I491">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J491">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K491">
-        <v>1150.560005187988</v>
+        <v>1624.320007324219</v>
       </c>
     </row>
     <row r="492" spans="1:11">
@@ -22731,13 +22803,13 @@
         <v>19</v>
       </c>
       <c r="I502">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J502">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K502">
-        <v>1140.019958496094</v>
+        <v>1609.43994140625</v>
       </c>
     </row>
     <row r="503" spans="1:11">
@@ -23116,13 +23188,13 @@
         <v>19</v>
       </c>
       <c r="I513">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J513">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K513">
-        <v>1148.519958496094</v>
+        <v>1621.43994140625</v>
       </c>
     </row>
     <row r="514" spans="1:11">
@@ -23501,13 +23573,13 @@
         <v>19</v>
       </c>
       <c r="I524">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J524">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K524">
-        <v>1168.75</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="525" spans="1:11">
@@ -23886,13 +23958,13 @@
         <v>19</v>
       </c>
       <c r="I535">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J535">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K535">
-        <v>1157.529937744141</v>
+        <v>1634.159912109375</v>
       </c>
     </row>
     <row r="536" spans="1:11">
@@ -24271,13 +24343,13 @@
         <v>19</v>
       </c>
       <c r="I546">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J546">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K546">
-        <v>1155.319984436035</v>
+        <v>1631.039978027344</v>
       </c>
     </row>
     <row r="547" spans="1:11">
@@ -24656,13 +24728,13 @@
         <v>19</v>
       </c>
       <c r="I557">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J557">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K557">
-        <v>1153.620010375977</v>
+        <v>1628.640014648438</v>
       </c>
     </row>
     <row r="558" spans="1:11">
@@ -25041,13 +25113,13 @@
         <v>19</v>
       </c>
       <c r="I568">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J568">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K568">
-        <v>1152.430015563965</v>
+        <v>1626.960021972656</v>
       </c>
     </row>
     <row r="569" spans="1:11">
@@ -25426,13 +25498,13 @@
         <v>19</v>
       </c>
       <c r="I579">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J579">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K579">
-        <v>1162.290046691895</v>
+        <v>1640.880065917969</v>
       </c>
     </row>
     <row r="580" spans="1:11">
@@ -25811,13 +25883,13 @@
         <v>19</v>
       </c>
       <c r="I590">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J590">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K590">
-        <v>1171.980041503906</v>
+        <v>1654.56005859375</v>
       </c>
     </row>
     <row r="591" spans="1:11">
@@ -26196,13 +26268,13 @@
         <v>19</v>
       </c>
       <c r="I601">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J601">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K601">
-        <v>1163.649948120117</v>
+        <v>1642.799926757812</v>
       </c>
     </row>
     <row r="602" spans="1:11">
@@ -26581,13 +26653,13 @@
         <v>19</v>
       </c>
       <c r="I612">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J612">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K612">
-        <v>1166.709953308105</v>
+        <v>1647.119934082031</v>
       </c>
     </row>
     <row r="613" spans="1:11">
@@ -26966,13 +27038,13 @@
         <v>19</v>
       </c>
       <c r="I623">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J623">
-        <v>1158.3596</v>
+        <v>1635.3312</v>
       </c>
       <c r="K623">
-        <v>1174.189994812012</v>
+        <v>1657.679992675781</v>
       </c>
     </row>
     <row r="624" spans="1:11">
@@ -27043,6 +27115,391 @@
       </c>
       <c r="K625">
         <v>3671.257848739624</v>
+      </c>
+    </row>
+    <row r="626" spans="1:11">
+      <c r="A626" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B626" t="s">
+        <v>11</v>
+      </c>
+      <c r="C626" t="s">
+        <v>22</v>
+      </c>
+      <c r="D626">
+        <v>50.07</v>
+      </c>
+      <c r="E626">
+        <v>53.09000015258789</v>
+      </c>
+      <c r="F626">
+        <v>0.0603155612659853</v>
+      </c>
+      <c r="G626">
+        <v>6.03</v>
+      </c>
+      <c r="H626" t="s">
+        <v>11</v>
+      </c>
+      <c r="I626">
+        <v>23</v>
+      </c>
+      <c r="J626">
+        <v>1151.61</v>
+      </c>
+      <c r="K626">
+        <v>1221.070003509521</v>
+      </c>
+    </row>
+    <row r="627" spans="1:11">
+      <c r="A627" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B627" t="s">
+        <v>12</v>
+      </c>
+      <c r="C627" t="s">
+        <v>23</v>
+      </c>
+      <c r="D627">
+        <v>242.3</v>
+      </c>
+      <c r="E627">
+        <v>258.3500061035156</v>
+      </c>
+      <c r="F627">
+        <v>0.06624022329143869</v>
+      </c>
+      <c r="G627">
+        <v>6.62</v>
+      </c>
+      <c r="H627" t="s">
+        <v>12</v>
+      </c>
+      <c r="I627">
+        <v>5</v>
+      </c>
+      <c r="J627">
+        <v>1211.5</v>
+      </c>
+      <c r="K627">
+        <v>1291.750030517578</v>
+      </c>
+    </row>
+    <row r="628" spans="1:11">
+      <c r="A628" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B628" t="s">
+        <v>13</v>
+      </c>
+      <c r="C628" t="s">
+        <v>24</v>
+      </c>
+      <c r="D628">
+        <v>38.273</v>
+      </c>
+      <c r="E628">
+        <v>45.84500122070312</v>
+      </c>
+      <c r="F628">
+        <v>0.1978418524992324</v>
+      </c>
+      <c r="G628">
+        <v>19.78</v>
+      </c>
+      <c r="H628" t="s">
+        <v>13</v>
+      </c>
+      <c r="I628">
+        <v>54</v>
+      </c>
+      <c r="J628">
+        <v>2066.742</v>
+      </c>
+      <c r="K628">
+        <v>2475.630065917969</v>
+      </c>
+    </row>
+    <row r="629" spans="1:11">
+      <c r="A629" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B629" t="s">
+        <v>14</v>
+      </c>
+      <c r="C629" t="s">
+        <v>25</v>
+      </c>
+      <c r="D629">
+        <v>6.5264</v>
+      </c>
+      <c r="E629">
+        <v>7.662000179290771</v>
+      </c>
+      <c r="F629">
+        <v>0.1740010081041265</v>
+      </c>
+      <c r="G629">
+        <v>17.4</v>
+      </c>
+      <c r="H629" t="s">
+        <v>14</v>
+      </c>
+      <c r="I629">
+        <v>276</v>
+      </c>
+      <c r="J629">
+        <v>1801.2864</v>
+      </c>
+      <c r="K629">
+        <v>2114.712049484253</v>
+      </c>
+    </row>
+    <row r="630" spans="1:11">
+      <c r="A630" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B630" t="s">
+        <v>15</v>
+      </c>
+      <c r="C630" t="s">
+        <v>26</v>
+      </c>
+      <c r="D630">
+        <v>197.58</v>
+      </c>
+      <c r="E630">
+        <v>204.1000061035156</v>
+      </c>
+      <c r="F630">
+        <v>0.0329993223176212</v>
+      </c>
+      <c r="G630">
+        <v>3.3</v>
+      </c>
+      <c r="H630" t="s">
+        <v>15</v>
+      </c>
+      <c r="I630">
+        <v>4</v>
+      </c>
+      <c r="J630">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K630">
+        <v>816.4000244140624</v>
+      </c>
+    </row>
+    <row r="631" spans="1:11">
+      <c r="A631" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B631" t="s">
+        <v>16</v>
+      </c>
+      <c r="C631" t="s">
+        <v>27</v>
+      </c>
+      <c r="D631">
+        <v>79.86</v>
+      </c>
+      <c r="E631">
+        <v>120.8000030517578</v>
+      </c>
+      <c r="F631">
+        <v>0.5126471706956901</v>
+      </c>
+      <c r="G631">
+        <v>51.26</v>
+      </c>
+      <c r="H631" t="s">
+        <v>16</v>
+      </c>
+      <c r="I631">
+        <v>12</v>
+      </c>
+      <c r="J631">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K631">
+        <v>1449.600036621094</v>
+      </c>
+    </row>
+    <row r="632" spans="1:11">
+      <c r="A632" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B632" t="s">
+        <v>17</v>
+      </c>
+      <c r="C632" t="s">
+        <v>28</v>
+      </c>
+      <c r="D632">
+        <v>19.7444</v>
+      </c>
+      <c r="E632">
+        <v>21.56399917602539</v>
+      </c>
+      <c r="F632">
+        <v>0.0921577346500979</v>
+      </c>
+      <c r="G632">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="H632" t="s">
+        <v>17</v>
+      </c>
+      <c r="I632">
+        <v>61</v>
+      </c>
+      <c r="J632">
+        <v>1204.4084</v>
+      </c>
+      <c r="K632">
+        <v>1315.403949737549</v>
+      </c>
+    </row>
+    <row r="633" spans="1:11">
+      <c r="A633" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B633" t="s">
+        <v>18</v>
+      </c>
+      <c r="C633" t="s">
+        <v>29</v>
+      </c>
+      <c r="D633">
+        <v>129.871</v>
+      </c>
+      <c r="E633">
+        <v>152.3699951171875</v>
+      </c>
+      <c r="F633">
+        <v>0.1732411016869623</v>
+      </c>
+      <c r="G633">
+        <v>17.32</v>
+      </c>
+      <c r="H633" t="s">
+        <v>18</v>
+      </c>
+      <c r="I633">
+        <v>51</v>
+      </c>
+      <c r="J633">
+        <v>6623.421</v>
+      </c>
+      <c r="K633">
+        <v>7770.869750976562</v>
+      </c>
+    </row>
+    <row r="634" spans="1:11">
+      <c r="A634" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B634" t="s">
+        <v>19</v>
+      </c>
+      <c r="C634" t="s">
+        <v>30</v>
+      </c>
+      <c r="D634">
+        <v>34.0694</v>
+      </c>
+      <c r="E634">
+        <v>34.7599983215332</v>
+      </c>
+      <c r="F634">
+        <v>0.0202703399981567</v>
+      </c>
+      <c r="G634">
+        <v>2.03</v>
+      </c>
+      <c r="H634" t="s">
+        <v>19</v>
+      </c>
+      <c r="I634">
+        <v>48</v>
+      </c>
+      <c r="J634">
+        <v>1635.3312</v>
+      </c>
+      <c r="K634">
+        <v>1668.479919433594</v>
+      </c>
+    </row>
+    <row r="635" spans="1:11">
+      <c r="A635" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B635" t="s">
+        <v>20</v>
+      </c>
+      <c r="C635" t="s">
+        <v>31</v>
+      </c>
+      <c r="D635">
+        <v>69.4158</v>
+      </c>
+      <c r="E635">
+        <v>73.58999633789062</v>
+      </c>
+      <c r="F635">
+        <v>0.0601332310207562</v>
+      </c>
+      <c r="G635">
+        <v>6.01</v>
+      </c>
+      <c r="H635" t="s">
+        <v>20</v>
+      </c>
+      <c r="I635">
+        <v>62</v>
+      </c>
+      <c r="J635">
+        <v>4303.7796</v>
+      </c>
+      <c r="K635">
+        <v>4562.579772949219</v>
+      </c>
+    </row>
+    <row r="636" spans="1:11">
+      <c r="A636" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B636" t="s">
+        <v>21</v>
+      </c>
+      <c r="C636" t="s">
+        <v>32</v>
+      </c>
+      <c r="D636">
+        <v>8.1868</v>
+      </c>
+      <c r="E636">
+        <v>8.626999855041504</v>
+      </c>
+      <c r="F636">
+        <v>0.0537694648753486</v>
+      </c>
+      <c r="G636">
+        <v>5.38</v>
+      </c>
+      <c r="H636" t="s">
+        <v>21</v>
+      </c>
+      <c r="I636">
+        <v>431</v>
+      </c>
+      <c r="J636">
+        <v>3528.5108</v>
+      </c>
+      <c r="K636">
+        <v>3718.236937522888</v>
       </c>
     </row>
   </sheetData>
@@ -27052,7 +27509,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -27138,7 +27595,7 @@
         <v>0.0259197937957051</v>
       </c>
       <c r="M2" s="2">
-        <v>0.08659212287311968</v>
+        <v>0.08578526067735348</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -27179,7 +27636,7 @@
         <v>0.0298284746005002</v>
       </c>
       <c r="M3" s="2">
-        <v>0.08575413785832886</v>
+        <v>0.0848854524083833</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27220,7 +27677,7 @@
         <v>0.0267748250023331</v>
       </c>
       <c r="M4" s="2">
-        <v>0.08313910176808248</v>
+        <v>0.08250566795836645</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -27261,7 +27718,7 @@
         <v>0.0272633809806162</v>
       </c>
       <c r="M5" s="2">
-        <v>0.08013679690745534</v>
+        <v>0.07924391397719122</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27302,7 +27759,7 @@
         <v>0.0102848375979951</v>
       </c>
       <c r="M6" s="2">
-        <v>0.05511860933311308</v>
+        <v>0.05421593878442521</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -27343,7 +27800,7 @@
         <v>0.019812378110106</v>
       </c>
       <c r="M7" s="2">
-        <v>0.067733222569895</v>
+        <v>0.06671973433862921</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -27384,7 +27841,7 @@
         <v>0.0115063440329679</v>
       </c>
       <c r="M8" s="2">
-        <v>0.05588978697012448</v>
+        <v>0.05487546664171727</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -27425,7 +27882,7 @@
         <v>-0.0070601810129711</v>
       </c>
       <c r="M9" s="2">
-        <v>0.04393944472218569</v>
+        <v>0.04296791492621166</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -27466,7 +27923,7 @@
         <v>-0.0187863399166211</v>
       </c>
       <c r="M10" s="2">
-        <v>0.03947997164330386</v>
+        <v>0.03841243925054116</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27504,7 +27961,7 @@
         <v>0.0019788035208567</v>
       </c>
       <c r="M11" s="2">
-        <v>0.05996044742932116</v>
+        <v>0.05862776438148121</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -27545,7 +28002,7 @@
         <v>-0.0076709342304576</v>
       </c>
       <c r="M12" s="2">
-        <v>0.05126016601743588</v>
+        <v>0.04996167796802142</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -27586,7 +28043,7 @@
         <v>-0.0151219371009677</v>
       </c>
       <c r="M13" s="2">
-        <v>0.04322778601843358</v>
+        <v>0.04194797007897466</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -27627,7 +28084,7 @@
         <v>-0.0195191738840457</v>
       </c>
       <c r="M14" s="2">
-        <v>0.04040918396084137</v>
+        <v>0.03919927747478447</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -27668,7 +28125,7 @@
         <v>-0.0154882958400475</v>
       </c>
       <c r="M15" s="2">
-        <v>0.04595019140029666</v>
+        <v>0.04464666041586129</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -27709,7 +28166,7 @@
         <v>-0.0124346462418805</v>
       </c>
       <c r="M16" s="2">
-        <v>0.05050291159109199</v>
+        <v>0.04922982946951349</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -27750,7 +28207,7 @@
         <v>-0.0147554618726228</v>
       </c>
       <c r="M17" s="2">
-        <v>0.04322410959754541</v>
+        <v>0.04175021033129345</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -27791,7 +28248,7 @@
         <v>-0.0331997896793585</v>
       </c>
       <c r="M18" s="2">
-        <v>0.02330435739138426</v>
+        <v>0.02168548538232229</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -27832,7 +28289,7 @@
         <v>-0.0434602224035267</v>
       </c>
       <c r="M19" s="2">
-        <v>0.009025881265433133</v>
+        <v>0.007532059620589004</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -27873,7 +28330,7 @@
         <v>-0.0360091612883839</v>
       </c>
       <c r="M20" s="2">
-        <v>0.01627949441484677</v>
+        <v>0.01475679976827537</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -27914,7 +28371,7 @@
         <v>-0.0299018038474174</v>
       </c>
       <c r="M21" s="2">
-        <v>0.01727757383861817</v>
+        <v>0.01577758739905799</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -27955,7 +28412,7 @@
         <v>-0.020007846351594</v>
       </c>
       <c r="M22" s="2">
-        <v>0.02824973281511878</v>
+        <v>0.0268888783186112</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -27996,7 +28453,7 @@
         <v>-0.0263594817817022</v>
       </c>
       <c r="M23" s="2">
-        <v>0.01576261540427626</v>
+        <v>0.0144989311582131</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -28037,7 +28494,7 @@
         <v>-0.0395514833540991</v>
       </c>
       <c r="M24" s="2">
-        <v>0.003483954271819245</v>
+        <v>0.002313506475123628</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -28075,7 +28532,7 @@
         <v>-0.0353984663155301</v>
       </c>
       <c r="M25" s="2">
-        <v>-0.002466865919742989</v>
+        <v>-0.00363055768215681</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -28116,7 +28573,7 @@
         <v>-0.0356427443046717</v>
       </c>
       <c r="M26" s="2">
-        <v>0.009055650800799953</v>
+        <v>0.007929612705902978</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -28157,7 +28614,7 @@
         <v>-0.0102360278503415</v>
       </c>
       <c r="M27" s="2">
-        <v>0.03533260048320974</v>
+        <v>0.03412057350940034</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -28198,7 +28655,7 @@
         <v>-0.0123124490026771</v>
       </c>
       <c r="M28" s="2">
-        <v>0.03157264743845434</v>
+        <v>0.03037341549108197</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -28239,7 +28696,7 @@
         <v>-0.0146332646334195</v>
       </c>
       <c r="M29" s="2">
-        <v>0.0260431799791101</v>
+        <v>0.02462149295107285</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -28280,7 +28737,7 @@
         <v>0.0133384871961619</v>
       </c>
       <c r="M30" s="2">
-        <v>0.06098925490738094</v>
+        <v>0.05945369050629257</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -28321,7 +28778,7 @@
         <v>0.0124834559895341</v>
       </c>
       <c r="M31" s="2">
-        <v>0.06026859412382479</v>
+        <v>0.05877155396624834</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -28362,7 +28819,7 @@
         <v>0.0105291155871365</v>
       </c>
       <c r="M32" s="2">
-        <v>0.06369755078311989</v>
+        <v>0.06217457749550381</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -28403,7 +28860,7 @@
         <v>0.0105291155871365</v>
       </c>
       <c r="M33" s="2">
-        <v>0.06238606925142931</v>
+        <v>0.06092384794331718</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -28444,7 +28901,7 @@
         <v>0.0238432561541044</v>
       </c>
       <c r="M34" s="2">
-        <v>0.07495053702515309</v>
+        <v>0.07329552134152562</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -28485,7 +28942,7 @@
         <v>0.0207896065559374</v>
       </c>
       <c r="M35" s="2">
-        <v>0.07659257522140828</v>
+        <v>0.07495365573205115</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -28526,7 +28983,7 @@
         <v>0.0259197937957051</v>
       </c>
       <c r="M36" s="2">
-        <v>0.08115264620024942</v>
+        <v>0.07932797058781027</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -28567,7 +29024,7 @@
         <v>0.0454634307982104</v>
       </c>
       <c r="M37" s="2">
-        <v>0.09736286772558467</v>
+        <v>0.09567540843536637</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -28608,7 +29065,7 @@
         <v>0.0425318619499817</v>
       </c>
       <c r="M38" s="2">
-        <v>0.09203721782375407</v>
+        <v>0.09037825160039192</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -28649,7 +29106,7 @@
         <v>0.040088965569301</v>
       </c>
       <c r="M39" s="2">
-        <v>0.08831685181213</v>
+        <v>0.08655084455046214</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -28690,7 +29147,7 @@
         <v>0.0408217995367257</v>
       </c>
       <c r="M40" s="2">
-        <v>0.09172554739087047</v>
+        <v>0.08974289248363676</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -28731,7 +29188,7 @@
         <v>0.040943996775929</v>
       </c>
       <c r="M41" s="2">
-        <v>0.09386687305062402</v>
+        <v>0.0920819848683343</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -28772,7 +29229,7 @@
         <v>0.0344701058619849</v>
       </c>
       <c r="M42" s="2">
-        <v>0.09174206280623287</v>
+        <v>0.08986156675165935</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -28810,7 +29267,7 @@
         <v>0.0363023655144443</v>
       </c>
       <c r="M43" s="2">
-        <v>0.1043830270766006</v>
+        <v>0.101782379702843</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -28851,7 +29308,7 @@
         <v>0.0301949498288451</v>
       </c>
       <c r="M44" s="2">
-        <v>0.08600291481845979</v>
+        <v>0.0840756309665105</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -28892,7 +29349,7 @@
         <v>0.0261640717848468</v>
       </c>
       <c r="M45" s="2">
-        <v>0.08458832942783934</v>
+        <v>0.0825686513569428</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -28933,7 +29390,7 @@
         <v>0.0367909214927273</v>
       </c>
       <c r="M46" s="2">
-        <v>0.09416421875041814</v>
+        <v>0.09226017051480007</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -28974,7 +29431,7 @@
         <v>0.0403332435584427</v>
       </c>
       <c r="M47" s="2">
-        <v>0.0957593885985335</v>
+        <v>0.0936535273601502</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -29015,7 +29472,7 @@
         <v>0.0497385868313502</v>
       </c>
       <c r="M48" s="2">
-        <v>0.1070343328499763</v>
+        <v>0.1048541764125344</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -29056,7 +29513,7 @@
         <v>0.06415203659408771</v>
       </c>
       <c r="M49" s="2">
-        <v>0.1246536656368895</v>
+        <v>0.1224705852196375</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -29097,7 +29554,7 @@
         <v>0.0613426649850621</v>
       </c>
       <c r="M50" s="2">
-        <v>0.1220634136316909</v>
+        <v>0.1197464254687215</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -29138,7 +29595,7 @@
         <v>0.0608541090067791</v>
       </c>
       <c r="M51" s="2">
-        <v>0.122121062294837</v>
+        <v>0.119766983368647</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -29179,7 +29636,7 @@
         <v>0.0647627898115741</v>
       </c>
       <c r="M52" s="2">
-        <v>0.1250783136895137</v>
+        <v>0.1226407334737896</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -29220,7 +29677,7 @@
         <v>0.0487614748747842</v>
       </c>
       <c r="M53" s="2">
-        <v>0.1096913010216034</v>
+        <v>0.1075247043083143</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -29261,7 +29718,7 @@
         <v>0.0567010337235773</v>
       </c>
       <c r="M54" s="2">
-        <v>0.1232704707188441</v>
+        <v>0.1210082521046998</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -29302,7 +29759,7 @@
         <v>0.0665950494640335</v>
       </c>
       <c r="M55" s="2">
-        <v>0.1354360314181373</v>
+        <v>0.1331020971705092</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -29343,7 +29800,7 @@
         <v>0.0526701556795792</v>
       </c>
       <c r="M56" s="2">
-        <v>0.1210384757179497</v>
+        <v>0.1188405317979211</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -29384,7 +29841,7 @@
         <v>0.0474177712006078</v>
       </c>
       <c r="M57" s="2">
-        <v>0.1161144117883874</v>
+        <v>0.1140592416778508</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -29425,7 +29882,48 @@
         <v>0.0404553243083807</v>
       </c>
       <c r="M58" s="2">
-        <v>0.1130216028713822</v>
+        <v>0.11114665660908</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0.0603155612659853</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0.06624022329143869</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0.1978418524992324</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0.1740010081041265</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0.0329993223176212</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0.5126471706956901</v>
+      </c>
+      <c r="H59" s="2">
+        <v>0.0921577346500979</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0.1732411016869623</v>
+      </c>
+      <c r="J59" s="2">
+        <v>0.0202703399981567</v>
+      </c>
+      <c r="K59" s="2">
+        <v>0.0601332310207562</v>
+      </c>
+      <c r="L59" s="2">
+        <v>0.0537694648753486</v>
+      </c>
+      <c r="M59" s="2">
+        <v>0.1238170024713718</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="35">
   <si>
     <t>data</t>
   </si>
@@ -221,10 +221,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -398,16 +398,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$59</c:f>
+              <c:f>grafico_dati!$B$2:$B$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -581,6 +584,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.0603155612659853</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.06331139761267821</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -608,10 +614,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -785,16 +791,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$59</c:f>
+              <c:f>grafico_dati!$C$2:$C$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -968,6 +977,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.06624022329143869</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.07296744113218361</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -995,10 +1007,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1172,16 +1184,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$59</c:f>
+              <c:f>grafico_dati!$D$2:$D$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1355,6 +1370,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.1978418524992324</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.2004546206156876</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1382,10 +1400,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1559,16 +1577,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$59</c:f>
+              <c:f>grafico_dati!$E$2:$E$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1742,6 +1763,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.1740010081041265</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.1851863406341021</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1769,10 +1793,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1946,16 +1970,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$59</c:f>
+              <c:f>grafico_dati!$F$2:$F$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2126,6 +2153,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.0329993223176212</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.0274319263083306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2153,10 +2183,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2330,16 +2360,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$59</c:f>
+              <c:f>grafico_dati!$G$2:$G$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2513,6 +2546,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.5126471706956901</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.516153291147692</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2540,10 +2576,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2717,16 +2753,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$59</c:f>
+              <c:f>grafico_dati!$H$2:$H$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -2900,6 +2939,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.0921577346500979</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.0905370428077174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2927,10 +2969,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3104,16 +3146,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$59</c:f>
+              <c:f>grafico_dati!$I$2:$I$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3284,6 +3329,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.1732411016869623</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.1755511097084436</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3311,10 +3359,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3488,16 +3536,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$59</c:f>
+              <c:f>grafico_dati!$J$2:$J$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3671,6 +3722,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.0202703399981567</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.0233523830318935</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3698,10 +3752,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3875,16 +3929,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$59</c:f>
+              <c:f>grafico_dati!$K$2:$K$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4055,6 +4112,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.0601332310207562</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.0622941443269331</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4082,10 +4142,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4259,16 +4319,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$59</c:f>
+              <c:f>grafico_dati!$L$2:$L$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4442,6 +4505,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.0537694648753486</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.0575560649302053</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4473,10 +4539,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$59</c:f>
+              <c:f>grafico_dati!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4650,16 +4716,19 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$59</c:f>
+              <c:f>grafico_dati!$M$2:$M$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0.08578526067735348</c:v>
                 </c:pt>
@@ -4833,6 +4902,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0.1238170024713718</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.126869691722614</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5239,7 +5311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K636"/>
+  <dimension ref="A1:K647"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -27500,6 +27572,391 @@
       </c>
       <c r="K636">
         <v>3718.236937522888</v>
+      </c>
+    </row>
+    <row r="637" spans="1:11">
+      <c r="A637" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B637" t="s">
+        <v>11</v>
+      </c>
+      <c r="C637" t="s">
+        <v>22</v>
+      </c>
+      <c r="D637">
+        <v>50.07</v>
+      </c>
+      <c r="E637">
+        <v>53.2400016784668</v>
+      </c>
+      <c r="F637">
+        <v>0.06331139761267821</v>
+      </c>
+      <c r="G637">
+        <v>6.33</v>
+      </c>
+      <c r="H637" t="s">
+        <v>11</v>
+      </c>
+      <c r="I637">
+        <v>23</v>
+      </c>
+      <c r="J637">
+        <v>1151.61</v>
+      </c>
+      <c r="K637">
+        <v>1224.520038604736</v>
+      </c>
+    </row>
+    <row r="638" spans="1:11">
+      <c r="A638" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B638" t="s">
+        <v>12</v>
+      </c>
+      <c r="C638" t="s">
+        <v>23</v>
+      </c>
+      <c r="D638">
+        <v>242.3</v>
+      </c>
+      <c r="E638">
+        <v>259.9800109863281</v>
+      </c>
+      <c r="F638">
+        <v>0.07296744113218361</v>
+      </c>
+      <c r="G638">
+        <v>7.3</v>
+      </c>
+      <c r="H638" t="s">
+        <v>12</v>
+      </c>
+      <c r="I638">
+        <v>5</v>
+      </c>
+      <c r="J638">
+        <v>1211.5</v>
+      </c>
+      <c r="K638">
+        <v>1299.900054931641</v>
+      </c>
+    </row>
+    <row r="639" spans="1:11">
+      <c r="A639" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B639" t="s">
+        <v>13</v>
+      </c>
+      <c r="C639" t="s">
+        <v>24</v>
+      </c>
+      <c r="D639">
+        <v>38.273</v>
+      </c>
+      <c r="E639">
+        <v>45.94499969482422</v>
+      </c>
+      <c r="F639">
+        <v>0.2004546206156876</v>
+      </c>
+      <c r="G639">
+        <v>20.05</v>
+      </c>
+      <c r="H639" t="s">
+        <v>13</v>
+      </c>
+      <c r="I639">
+        <v>54</v>
+      </c>
+      <c r="J639">
+        <v>2066.742</v>
+      </c>
+      <c r="K639">
+        <v>2481.029983520508</v>
+      </c>
+    </row>
+    <row r="640" spans="1:11">
+      <c r="A640" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B640" t="s">
+        <v>14</v>
+      </c>
+      <c r="C640" t="s">
+        <v>25</v>
+      </c>
+      <c r="D640">
+        <v>6.5264</v>
+      </c>
+      <c r="E640">
+        <v>7.735000133514404</v>
+      </c>
+      <c r="F640">
+        <v>0.1851863406341021</v>
+      </c>
+      <c r="G640">
+        <v>18.52</v>
+      </c>
+      <c r="H640" t="s">
+        <v>14</v>
+      </c>
+      <c r="I640">
+        <v>276</v>
+      </c>
+      <c r="J640">
+        <v>1801.2864</v>
+      </c>
+      <c r="K640">
+        <v>2134.860036849976</v>
+      </c>
+    </row>
+    <row r="641" spans="1:11">
+      <c r="A641" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B641" t="s">
+        <v>15</v>
+      </c>
+      <c r="C641" t="s">
+        <v>26</v>
+      </c>
+      <c r="D641">
+        <v>197.58</v>
+      </c>
+      <c r="E641">
+        <v>203</v>
+      </c>
+      <c r="F641">
+        <v>0.0274319263083306</v>
+      </c>
+      <c r="G641">
+        <v>2.74</v>
+      </c>
+      <c r="H641" t="s">
+        <v>15</v>
+      </c>
+      <c r="I641">
+        <v>4</v>
+      </c>
+      <c r="J641">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K641">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="642" spans="1:11">
+      <c r="A642" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B642" t="s">
+        <v>16</v>
+      </c>
+      <c r="C642" t="s">
+        <v>27</v>
+      </c>
+      <c r="D642">
+        <v>79.86</v>
+      </c>
+      <c r="E642">
+        <v>121.0800018310547</v>
+      </c>
+      <c r="F642">
+        <v>0.516153291147692</v>
+      </c>
+      <c r="G642">
+        <v>51.62</v>
+      </c>
+      <c r="H642" t="s">
+        <v>16</v>
+      </c>
+      <c r="I642">
+        <v>12</v>
+      </c>
+      <c r="J642">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="K642">
+        <v>1452.960021972656</v>
+      </c>
+    </row>
+    <row r="643" spans="1:11">
+      <c r="A643" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B643" t="s">
+        <v>17</v>
+      </c>
+      <c r="C643" t="s">
+        <v>28</v>
+      </c>
+      <c r="D643">
+        <v>19.7444</v>
+      </c>
+      <c r="E643">
+        <v>21.53199958801269</v>
+      </c>
+      <c r="F643">
+        <v>0.0905370428077174</v>
+      </c>
+      <c r="G643">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="H643" t="s">
+        <v>17</v>
+      </c>
+      <c r="I643">
+        <v>61</v>
+      </c>
+      <c r="J643">
+        <v>1204.4084</v>
+      </c>
+      <c r="K643">
+        <v>1313.451974868774</v>
+      </c>
+    </row>
+    <row r="644" spans="1:11">
+      <c r="A644" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B644" t="s">
+        <v>18</v>
+      </c>
+      <c r="C644" t="s">
+        <v>29</v>
+      </c>
+      <c r="D644">
+        <v>129.871</v>
+      </c>
+      <c r="E644">
+        <v>152.6699981689453</v>
+      </c>
+      <c r="F644">
+        <v>0.1755511097084436</v>
+      </c>
+      <c r="G644">
+        <v>17.56</v>
+      </c>
+      <c r="H644" t="s">
+        <v>18</v>
+      </c>
+      <c r="I644">
+        <v>51</v>
+      </c>
+      <c r="J644">
+        <v>6623.421</v>
+      </c>
+      <c r="K644">
+        <v>7786.169906616211</v>
+      </c>
+    </row>
+    <row r="645" spans="1:11">
+      <c r="A645" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B645" t="s">
+        <v>19</v>
+      </c>
+      <c r="C645" t="s">
+        <v>30</v>
+      </c>
+      <c r="D645">
+        <v>34.0694</v>
+      </c>
+      <c r="E645">
+        <v>34.8650016784668</v>
+      </c>
+      <c r="F645">
+        <v>0.0233523830318935</v>
+      </c>
+      <c r="G645">
+        <v>2.34</v>
+      </c>
+      <c r="H645" t="s">
+        <v>19</v>
+      </c>
+      <c r="I645">
+        <v>48</v>
+      </c>
+      <c r="J645">
+        <v>1635.3312</v>
+      </c>
+      <c r="K645">
+        <v>1673.520080566406</v>
+      </c>
+    </row>
+    <row r="646" spans="1:11">
+      <c r="A646" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B646" t="s">
+        <v>20</v>
+      </c>
+      <c r="C646" t="s">
+        <v>31</v>
+      </c>
+      <c r="D646">
+        <v>69.4158</v>
+      </c>
+      <c r="E646">
+        <v>73.73999786376953</v>
+      </c>
+      <c r="F646">
+        <v>0.0622941443269331</v>
+      </c>
+      <c r="G646">
+        <v>6.23</v>
+      </c>
+      <c r="H646" t="s">
+        <v>20</v>
+      </c>
+      <c r="I646">
+        <v>62</v>
+      </c>
+      <c r="J646">
+        <v>4303.7796</v>
+      </c>
+      <c r="K646">
+        <v>4571.879867553711</v>
+      </c>
+    </row>
+    <row r="647" spans="1:11">
+      <c r="A647" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B647" t="s">
+        <v>21</v>
+      </c>
+      <c r="C647" t="s">
+        <v>32</v>
+      </c>
+      <c r="D647">
+        <v>8.1868</v>
+      </c>
+      <c r="E647">
+        <v>8.657999992370605</v>
+      </c>
+      <c r="F647">
+        <v>0.0575560649302053</v>
+      </c>
+      <c r="G647">
+        <v>5.76</v>
+      </c>
+      <c r="H647" t="s">
+        <v>21</v>
+      </c>
+      <c r="I647">
+        <v>431</v>
+      </c>
+      <c r="J647">
+        <v>3528.5108</v>
+      </c>
+      <c r="K647">
+        <v>3731.597996711731</v>
       </c>
     </row>
   </sheetData>
@@ -27509,7 +27966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -29924,6 +30381,47 @@
       </c>
       <c r="M59" s="2">
         <v>0.1238170024713718</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.06331139761267821</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0.07296744113218361</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0.2004546206156876</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0.1851863406341021</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0.0274319263083306</v>
+      </c>
+      <c r="G60" s="2">
+        <v>0.516153291147692</v>
+      </c>
+      <c r="H60" s="2">
+        <v>0.0905370428077174</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0.1755511097084436</v>
+      </c>
+      <c r="J60" s="2">
+        <v>0.0233523830318935</v>
+      </c>
+      <c r="K60" s="2">
+        <v>0.0622941443269331</v>
+      </c>
+      <c r="L60" s="2">
+        <v>0.0575560649302053</v>
+      </c>
+      <c r="M60" s="2">
+        <v>0.126869691722614</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -616,7 +616,7 @@
                   <c:v>0.06331139761267821</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.06490899999999999</c:v>
+                  <c:v>0.063711</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -838,7 +838,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="59">
-                  <c:v>-0.09325600000000001</c:v>
+                  <c:v>-0.102091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1237,7 +1237,7 @@
                   <c:v>0.07296744113218361</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.075031</c:v>
+                  <c:v>0.075279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1636,7 +1636,7 @@
                   <c:v>0.2004546206156876</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.209599</c:v>
+                  <c:v>0.217177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2035,7 +2035,7 @@
                   <c:v>0.1851863406341021</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.201888</c:v>
+                  <c:v>0.20342</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2431,7 +2431,7 @@
                   <c:v>0.0274319263083306</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.031987</c:v>
+                  <c:v>0.039073</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2830,7 +2830,7 @@
                   <c:v>0.516153291147692</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.523917</c:v>
+                  <c:v>0.53143</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3229,7 +3229,7 @@
                   <c:v>0.0905370428077174</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.097982</c:v>
+                  <c:v>0.105174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3625,7 +3625,7 @@
                   <c:v>0.1755511097084436</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.160437</c:v>
+                  <c:v>0.165347</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4024,7 +4024,7 @@
                   <c:v>0.0233523830318935</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.025113</c:v>
+                  <c:v>0.028195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4420,7 +4420,7 @@
                   <c:v>0.0622941443269331</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.06848899999999999</c:v>
+                  <c:v>0.073243</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4819,7 +4819,7 @@
                   <c:v>0.0575560649302053</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.065618</c:v>
+                  <c:v>0.070259</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5222,7 +5222,7 @@
                   <c:v>0.128325635668824</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1209634082681328</c:v>
+                  <c:v>0.1249612591513305</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -28306,13 +28306,13 @@
         <v>50.07</v>
       </c>
       <c r="E648">
-        <v>53.32</v>
+        <v>53.26</v>
       </c>
       <c r="F648">
-        <v>0.06490899999999999</v>
+        <v>0.063711</v>
       </c>
       <c r="G648">
-        <v>6.49</v>
+        <v>6.37</v>
       </c>
       <c r="H648" t="s">
         <v>28</v>
@@ -28324,10 +28324,10 @@
         <v>1151.61</v>
       </c>
       <c r="K648">
-        <v>1226.36</v>
+        <v>1224.98</v>
       </c>
       <c r="L648">
-        <v>74.75</v>
+        <v>73.37</v>
       </c>
       <c r="M648" t="s">
         <v>16</v>
@@ -28339,7 +28339,7 @@
         <v>1151.61</v>
       </c>
       <c r="P648">
-        <v>1226.36</v>
+        <v>1224.98</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -28356,13 +28356,13 @@
         <v>16.0729</v>
       </c>
       <c r="E649">
-        <v>14.574</v>
+        <v>14.432</v>
       </c>
       <c r="F649">
-        <v>-0.09325600000000001</v>
+        <v>-0.102091</v>
       </c>
       <c r="G649">
-        <v>-9.33</v>
+        <v>-10.21</v>
       </c>
       <c r="H649" t="s">
         <v>40</v>
@@ -28374,10 +28374,10 @@
         <v>1012.59</v>
       </c>
       <c r="K649">
-        <v>918.16</v>
+        <v>909.22</v>
       </c>
       <c r="L649">
-        <v>-94.43000000000001</v>
+        <v>-103.38</v>
       </c>
       <c r="M649" t="s">
         <v>27</v>
@@ -28389,7 +28389,7 @@
         <v>1012.5927</v>
       </c>
       <c r="P649">
-        <v>918.162</v>
+        <v>909.216</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -28406,13 +28406,13 @@
         <v>242.3</v>
       </c>
       <c r="E650">
-        <v>260.48</v>
+        <v>260.54</v>
       </c>
       <c r="F650">
-        <v>0.075031</v>
+        <v>0.075279</v>
       </c>
       <c r="G650">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="H650" t="s">
         <v>29</v>
@@ -28424,10 +28424,10 @@
         <v>1211.5</v>
       </c>
       <c r="K650">
-        <v>1302.4</v>
+        <v>1302.7</v>
       </c>
       <c r="L650">
-        <v>90.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="M650" t="s">
         <v>17</v>
@@ -28439,7 +28439,7 @@
         <v>1211.5</v>
       </c>
       <c r="P650">
-        <v>1302.4</v>
+        <v>1302.7</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -28456,13 +28456,13 @@
         <v>38.273</v>
       </c>
       <c r="E651">
-        <v>46.295</v>
+        <v>46.585</v>
       </c>
       <c r="F651">
-        <v>0.209599</v>
+        <v>0.217177</v>
       </c>
       <c r="G651">
-        <v>20.96</v>
+        <v>21.72</v>
       </c>
       <c r="H651" t="s">
         <v>30</v>
@@ -28474,10 +28474,10 @@
         <v>2066.74</v>
       </c>
       <c r="K651">
-        <v>2499.93</v>
+        <v>2515.59</v>
       </c>
       <c r="L651">
-        <v>433.19</v>
+        <v>448.85</v>
       </c>
       <c r="M651" t="s">
         <v>18</v>
@@ -28489,7 +28489,7 @@
         <v>2066.742</v>
       </c>
       <c r="P651">
-        <v>2499.93</v>
+        <v>2515.59</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -28506,13 +28506,13 @@
         <v>6.5264</v>
       </c>
       <c r="E652">
-        <v>7.844</v>
+        <v>7.854</v>
       </c>
       <c r="F652">
-        <v>0.201888</v>
+        <v>0.20342</v>
       </c>
       <c r="G652">
-        <v>20.19</v>
+        <v>20.34</v>
       </c>
       <c r="H652" t="s">
         <v>31</v>
@@ -28524,10 +28524,10 @@
         <v>1801.29</v>
       </c>
       <c r="K652">
-        <v>2164.94</v>
+        <v>2167.7</v>
       </c>
       <c r="L652">
-        <v>363.66</v>
+        <v>366.42</v>
       </c>
       <c r="M652" t="s">
         <v>19</v>
@@ -28539,7 +28539,7 @@
         <v>1801.2864</v>
       </c>
       <c r="P652">
-        <v>2164.944</v>
+        <v>2167.704</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -28556,13 +28556,13 @@
         <v>197.58</v>
       </c>
       <c r="E653">
-        <v>203.9</v>
+        <v>205.3</v>
       </c>
       <c r="F653">
-        <v>0.031987</v>
+        <v>0.039073</v>
       </c>
       <c r="G653">
-        <v>3.2</v>
+        <v>3.91</v>
       </c>
       <c r="H653" t="s">
         <v>32</v>
@@ -28574,10 +28574,10 @@
         <v>790.3200000000001</v>
       </c>
       <c r="K653">
-        <v>815.6</v>
+        <v>821.2</v>
       </c>
       <c r="L653">
-        <v>25.28</v>
+        <v>30.88</v>
       </c>
       <c r="M653" t="s">
         <v>20</v>
@@ -28589,7 +28589,7 @@
         <v>790.3200000000001</v>
       </c>
       <c r="P653">
-        <v>815.6</v>
+        <v>821.2</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -28606,13 +28606,13 @@
         <v>79.86</v>
       </c>
       <c r="E654">
-        <v>121.7</v>
+        <v>122.3</v>
       </c>
       <c r="F654">
-        <v>0.523917</v>
+        <v>0.53143</v>
       </c>
       <c r="G654">
-        <v>52.39</v>
+        <v>53.14</v>
       </c>
       <c r="H654" t="s">
         <v>33</v>
@@ -28624,10 +28624,10 @@
         <v>958.3200000000001</v>
       </c>
       <c r="K654">
-        <v>1460.4</v>
+        <v>1467.6</v>
       </c>
       <c r="L654">
-        <v>502.08</v>
+        <v>509.28</v>
       </c>
       <c r="M654" t="s">
         <v>21</v>
@@ -28639,7 +28639,7 @@
         <v>958.3199999999999</v>
       </c>
       <c r="P654">
-        <v>1460.4</v>
+        <v>1467.6</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -28656,13 +28656,13 @@
         <v>19.7444</v>
       </c>
       <c r="E655">
-        <v>21.679</v>
+        <v>21.821</v>
       </c>
       <c r="F655">
-        <v>0.097982</v>
+        <v>0.105174</v>
       </c>
       <c r="G655">
-        <v>9.800000000000001</v>
+        <v>10.52</v>
       </c>
       <c r="H655" t="s">
         <v>34</v>
@@ -28674,10 +28674,10 @@
         <v>1204.41</v>
       </c>
       <c r="K655">
-        <v>1322.42</v>
+        <v>1331.08</v>
       </c>
       <c r="L655">
-        <v>118.01</v>
+        <v>126.67</v>
       </c>
       <c r="M655" t="s">
         <v>22</v>
@@ -28689,7 +28689,7 @@
         <v>1204.4084</v>
       </c>
       <c r="P655">
-        <v>1322.419</v>
+        <v>1331.081</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -28706,13 +28706,13 @@
         <v>132.3898</v>
       </c>
       <c r="E656">
-        <v>153.63</v>
+        <v>154.28</v>
       </c>
       <c r="F656">
-        <v>0.160437</v>
+        <v>0.165347</v>
       </c>
       <c r="G656">
-        <v>16.04</v>
+        <v>16.53</v>
       </c>
       <c r="H656" t="s">
         <v>35</v>
@@ -28724,10 +28724,10 @@
         <v>7546.22</v>
       </c>
       <c r="K656">
-        <v>8756.91</v>
+        <v>8793.959999999999</v>
       </c>
       <c r="L656">
-        <v>1210.69</v>
+        <v>1247.74</v>
       </c>
       <c r="M656" t="s">
         <v>23</v>
@@ -28739,7 +28739,7 @@
         <v>7546.2186</v>
       </c>
       <c r="P656">
-        <v>8756.91</v>
+        <v>8793.960000000001</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -28756,13 +28756,13 @@
         <v>34.0694</v>
       </c>
       <c r="E657">
-        <v>34.925</v>
+        <v>35.03</v>
       </c>
       <c r="F657">
-        <v>0.025113</v>
+        <v>0.028195</v>
       </c>
       <c r="G657">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="H657" t="s">
         <v>36</v>
@@ -28774,10 +28774,10 @@
         <v>1635.33</v>
       </c>
       <c r="K657">
-        <v>1676.4</v>
+        <v>1681.44</v>
       </c>
       <c r="L657">
-        <v>41.07</v>
+        <v>46.11</v>
       </c>
       <c r="M657" t="s">
         <v>24</v>
@@ -28789,7 +28789,7 @@
         <v>1635.3312</v>
       </c>
       <c r="P657">
-        <v>1676.4</v>
+        <v>1681.44</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -28806,13 +28806,13 @@
         <v>69.4158</v>
       </c>
       <c r="E658">
-        <v>74.17</v>
+        <v>74.5</v>
       </c>
       <c r="F658">
-        <v>0.06848899999999999</v>
+        <v>0.073243</v>
       </c>
       <c r="G658">
-        <v>6.85</v>
+        <v>7.32</v>
       </c>
       <c r="H658" t="s">
         <v>37</v>
@@ -28824,10 +28824,10 @@
         <v>4303.78</v>
       </c>
       <c r="K658">
-        <v>4598.54</v>
+        <v>4619</v>
       </c>
       <c r="L658">
-        <v>294.76</v>
+        <v>315.22</v>
       </c>
       <c r="M658" t="s">
         <v>25</v>
@@ -28839,7 +28839,7 @@
         <v>4303.7796</v>
       </c>
       <c r="P658">
-        <v>4598.54</v>
+        <v>4619</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -28856,13 +28856,13 @@
         <v>8.1868</v>
       </c>
       <c r="E659">
-        <v>8.724</v>
+        <v>8.762</v>
       </c>
       <c r="F659">
-        <v>0.065618</v>
+        <v>0.070259</v>
       </c>
       <c r="G659">
-        <v>6.56</v>
+        <v>7.03</v>
       </c>
       <c r="H659" t="s">
         <v>38</v>
@@ -28874,10 +28874,10 @@
         <v>3528.51</v>
       </c>
       <c r="K659">
-        <v>3760.04</v>
+        <v>3776.42</v>
       </c>
       <c r="L659">
-        <v>231.53</v>
+        <v>247.91</v>
       </c>
       <c r="M659" t="s">
         <v>26</v>
@@ -28889,7 +28889,7 @@
         <v>3528.5108</v>
       </c>
       <c r="P659">
-        <v>3760.044</v>
+        <v>3776.422</v>
       </c>
     </row>
   </sheetData>
@@ -31365,43 +31365,43 @@
         <v>46164</v>
       </c>
       <c r="B61" s="2">
-        <v>0.06490899999999999</v>
+        <v>0.063711</v>
       </c>
       <c r="C61" s="2">
-        <v>-0.09325600000000001</v>
+        <v>-0.102091</v>
       </c>
       <c r="D61" s="2">
-        <v>0.075031</v>
+        <v>0.075279</v>
       </c>
       <c r="E61" s="2">
-        <v>0.209599</v>
+        <v>0.217177</v>
       </c>
       <c r="F61" s="2">
-        <v>0.201888</v>
+        <v>0.20342</v>
       </c>
       <c r="G61" s="2">
-        <v>0.031987</v>
+        <v>0.039073</v>
       </c>
       <c r="H61" s="2">
-        <v>0.523917</v>
+        <v>0.53143</v>
       </c>
       <c r="I61" s="2">
-        <v>0.097982</v>
+        <v>0.105174</v>
       </c>
       <c r="J61" s="2">
-        <v>0.160437</v>
+        <v>0.165347</v>
       </c>
       <c r="K61" s="2">
-        <v>0.025113</v>
+        <v>0.028195</v>
       </c>
       <c r="L61" s="2">
-        <v>0.06848899999999999</v>
+        <v>0.073243</v>
       </c>
       <c r="M61" s="2">
-        <v>0.065618</v>
+        <v>0.070259</v>
       </c>
       <c r="N61" s="2">
-        <v>0.1209634082681328</v>
+        <v>0.1249612591513305</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="43">
   <si>
     <t>data</t>
   </si>
@@ -245,10 +245,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -428,16 +428,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$61</c:f>
+              <c:f>grafico_dati!$B$2:$B$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -617,6 +620,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.063711</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.072299</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -644,10 +650,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -827,17 +833,23 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$61</c:f>
+              <c:f>grafico_dati!$C$2:$C$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="59">
+                  <c:v>-0.102091</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>-0.102091</c:v>
                 </c:pt>
               </c:numCache>
@@ -866,10 +878,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1049,16 +1061,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$61</c:f>
+              <c:f>grafico_dati!$D$2:$D$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1238,6 +1253,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.075279</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.08212999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1265,10 +1283,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1448,16 +1466,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$61</c:f>
+              <c:f>grafico_dati!$E$2:$E$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1637,6 +1658,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.217177</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.23834</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1664,10 +1688,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1847,16 +1871,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$61</c:f>
+              <c:f>grafico_dati!$F$2:$F$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2036,6 +2063,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.20342</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.229774</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2063,10 +2093,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2246,16 +2276,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$61</c:f>
+              <c:f>grafico_dati!$G$2:$G$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2432,6 +2465,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.039073</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.06033</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2459,10 +2495,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2642,16 +2678,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$61</c:f>
+              <c:f>grafico_dati!$H$2:$H$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2831,6 +2870,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.53143</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.5559730000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2858,10 +2900,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3041,16 +3083,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$61</c:f>
+              <c:f>grafico_dati!$I$2:$I$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3230,6 +3275,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.105174</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.116367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3257,10 +3305,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3440,16 +3488,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$61</c:f>
+              <c:f>grafico_dati!$J$2:$J$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3626,6 +3677,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.165347</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.172145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3653,10 +3707,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3836,16 +3890,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$61</c:f>
+              <c:f>grafico_dati!$K$2:$K$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4025,6 +4082,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.028195</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.046687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4052,10 +4112,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4235,16 +4295,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$61</c:f>
+              <c:f>grafico_dati!$L$2:$L$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4421,6 +4484,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.073243</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.079869</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4448,10 +4514,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4631,16 +4697,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$61</c:f>
+              <c:f>grafico_dati!$M$2:$M$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4820,6 +4889,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.070259</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.08369600000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4851,10 +4923,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$61</c:f>
+              <c:f>grafico_dati!$A$2:$A$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5034,16 +5106,19 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$N$2:$N$61</c:f>
+              <c:f>grafico_dati!$N$2:$N$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5223,6 +5298,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>0.1249612591513305</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.1367461065210505</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5629,7 +5707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P659"/>
+  <dimension ref="A1:P671"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28890,6 +28968,606 @@
       </c>
       <c r="P659">
         <v>3776.422</v>
+      </c>
+    </row>
+    <row r="660" spans="1:16">
+      <c r="A660" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B660" t="s">
+        <v>16</v>
+      </c>
+      <c r="C660" t="s">
+        <v>28</v>
+      </c>
+      <c r="D660">
+        <v>50.07</v>
+      </c>
+      <c r="E660">
+        <v>53.69</v>
+      </c>
+      <c r="F660">
+        <v>0.072299</v>
+      </c>
+      <c r="G660">
+        <v>7.23</v>
+      </c>
+      <c r="H660" t="s">
+        <v>28</v>
+      </c>
+      <c r="I660">
+        <v>23</v>
+      </c>
+      <c r="J660">
+        <v>1151.61</v>
+      </c>
+      <c r="K660">
+        <v>1234.87</v>
+      </c>
+      <c r="L660">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="M660" t="s">
+        <v>16</v>
+      </c>
+      <c r="N660">
+        <v>23</v>
+      </c>
+      <c r="O660">
+        <v>1151.61</v>
+      </c>
+      <c r="P660">
+        <v>1234.87</v>
+      </c>
+    </row>
+    <row r="661" spans="1:16">
+      <c r="A661" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B661" t="s">
+        <v>27</v>
+      </c>
+      <c r="C661" t="s">
+        <v>39</v>
+      </c>
+      <c r="D661">
+        <v>16.0729</v>
+      </c>
+      <c r="E661">
+        <v>14.432</v>
+      </c>
+      <c r="F661">
+        <v>-0.102091</v>
+      </c>
+      <c r="G661">
+        <v>-10.21</v>
+      </c>
+      <c r="H661" t="s">
+        <v>40</v>
+      </c>
+      <c r="I661">
+        <v>63</v>
+      </c>
+      <c r="J661">
+        <v>1012.59</v>
+      </c>
+      <c r="K661">
+        <v>909.22</v>
+      </c>
+      <c r="L661">
+        <v>-103.38</v>
+      </c>
+      <c r="M661" t="s">
+        <v>27</v>
+      </c>
+      <c r="N661">
+        <v>63</v>
+      </c>
+      <c r="O661">
+        <v>1012.5927</v>
+      </c>
+      <c r="P661">
+        <v>909.216</v>
+      </c>
+    </row>
+    <row r="662" spans="1:16">
+      <c r="A662" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B662" t="s">
+        <v>17</v>
+      </c>
+      <c r="C662" t="s">
+        <v>29</v>
+      </c>
+      <c r="D662">
+        <v>242.3</v>
+      </c>
+      <c r="E662">
+        <v>262.2</v>
+      </c>
+      <c r="F662">
+        <v>0.08212999999999999</v>
+      </c>
+      <c r="G662">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="H662" t="s">
+        <v>29</v>
+      </c>
+      <c r="I662">
+        <v>5</v>
+      </c>
+      <c r="J662">
+        <v>1211.5</v>
+      </c>
+      <c r="K662">
+        <v>1311</v>
+      </c>
+      <c r="L662">
+        <v>99.5</v>
+      </c>
+      <c r="M662" t="s">
+        <v>17</v>
+      </c>
+      <c r="N662">
+        <v>5</v>
+      </c>
+      <c r="O662">
+        <v>1211.5</v>
+      </c>
+      <c r="P662">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="663" spans="1:16">
+      <c r="A663" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B663" t="s">
+        <v>18</v>
+      </c>
+      <c r="C663" t="s">
+        <v>30</v>
+      </c>
+      <c r="D663">
+        <v>38.273</v>
+      </c>
+      <c r="E663">
+        <v>47.395</v>
+      </c>
+      <c r="F663">
+        <v>0.23834</v>
+      </c>
+      <c r="G663">
+        <v>23.83</v>
+      </c>
+      <c r="H663" t="s">
+        <v>30</v>
+      </c>
+      <c r="I663">
+        <v>54</v>
+      </c>
+      <c r="J663">
+        <v>2066.74</v>
+      </c>
+      <c r="K663">
+        <v>2559.33</v>
+      </c>
+      <c r="L663">
+        <v>492.59</v>
+      </c>
+      <c r="M663" t="s">
+        <v>18</v>
+      </c>
+      <c r="N663">
+        <v>54</v>
+      </c>
+      <c r="O663">
+        <v>2066.742</v>
+      </c>
+      <c r="P663">
+        <v>2559.33</v>
+      </c>
+    </row>
+    <row r="664" spans="1:16">
+      <c r="A664" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B664" t="s">
+        <v>19</v>
+      </c>
+      <c r="C664" t="s">
+        <v>31</v>
+      </c>
+      <c r="D664">
+        <v>6.5264</v>
+      </c>
+      <c r="E664">
+        <v>8.026</v>
+      </c>
+      <c r="F664">
+        <v>0.229774</v>
+      </c>
+      <c r="G664">
+        <v>22.98</v>
+      </c>
+      <c r="H664" t="s">
+        <v>31</v>
+      </c>
+      <c r="I664">
+        <v>276</v>
+      </c>
+      <c r="J664">
+        <v>1801.29</v>
+      </c>
+      <c r="K664">
+        <v>2215.18</v>
+      </c>
+      <c r="L664">
+        <v>413.89</v>
+      </c>
+      <c r="M664" t="s">
+        <v>19</v>
+      </c>
+      <c r="N664">
+        <v>276</v>
+      </c>
+      <c r="O664">
+        <v>1801.2864</v>
+      </c>
+      <c r="P664">
+        <v>2215.176</v>
+      </c>
+    </row>
+    <row r="665" spans="1:16">
+      <c r="A665" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B665" t="s">
+        <v>20</v>
+      </c>
+      <c r="C665" t="s">
+        <v>32</v>
+      </c>
+      <c r="D665">
+        <v>197.58</v>
+      </c>
+      <c r="E665">
+        <v>209.5</v>
+      </c>
+      <c r="F665">
+        <v>0.06033</v>
+      </c>
+      <c r="G665">
+        <v>6.03</v>
+      </c>
+      <c r="H665" t="s">
+        <v>32</v>
+      </c>
+      <c r="I665">
+        <v>4</v>
+      </c>
+      <c r="J665">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K665">
+        <v>838</v>
+      </c>
+      <c r="L665">
+        <v>47.68</v>
+      </c>
+      <c r="M665" t="s">
+        <v>20</v>
+      </c>
+      <c r="N665">
+        <v>4</v>
+      </c>
+      <c r="O665">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P665">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="666" spans="1:16">
+      <c r="A666" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B666" t="s">
+        <v>21</v>
+      </c>
+      <c r="C666" t="s">
+        <v>33</v>
+      </c>
+      <c r="D666">
+        <v>79.86</v>
+      </c>
+      <c r="E666">
+        <v>124.26</v>
+      </c>
+      <c r="F666">
+        <v>0.5559730000000001</v>
+      </c>
+      <c r="G666">
+        <v>55.6</v>
+      </c>
+      <c r="H666" t="s">
+        <v>33</v>
+      </c>
+      <c r="I666">
+        <v>12</v>
+      </c>
+      <c r="J666">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K666">
+        <v>1491.12</v>
+      </c>
+      <c r="L666">
+        <v>532.8</v>
+      </c>
+      <c r="M666" t="s">
+        <v>21</v>
+      </c>
+      <c r="N666">
+        <v>12</v>
+      </c>
+      <c r="O666">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P666">
+        <v>1491.12</v>
+      </c>
+    </row>
+    <row r="667" spans="1:16">
+      <c r="A667" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B667" t="s">
+        <v>22</v>
+      </c>
+      <c r="C667" t="s">
+        <v>34</v>
+      </c>
+      <c r="D667">
+        <v>19.7444</v>
+      </c>
+      <c r="E667">
+        <v>22.042</v>
+      </c>
+      <c r="F667">
+        <v>0.116367</v>
+      </c>
+      <c r="G667">
+        <v>11.64</v>
+      </c>
+      <c r="H667" t="s">
+        <v>34</v>
+      </c>
+      <c r="I667">
+        <v>61</v>
+      </c>
+      <c r="J667">
+        <v>1204.41</v>
+      </c>
+      <c r="K667">
+        <v>1344.56</v>
+      </c>
+      <c r="L667">
+        <v>140.15</v>
+      </c>
+      <c r="M667" t="s">
+        <v>22</v>
+      </c>
+      <c r="N667">
+        <v>61</v>
+      </c>
+      <c r="O667">
+        <v>1204.4084</v>
+      </c>
+      <c r="P667">
+        <v>1344.562</v>
+      </c>
+    </row>
+    <row r="668" spans="1:16">
+      <c r="A668" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B668" t="s">
+        <v>23</v>
+      </c>
+      <c r="C668" t="s">
+        <v>35</v>
+      </c>
+      <c r="D668">
+        <v>132.3898</v>
+      </c>
+      <c r="E668">
+        <v>155.18</v>
+      </c>
+      <c r="F668">
+        <v>0.172145</v>
+      </c>
+      <c r="G668">
+        <v>17.21</v>
+      </c>
+      <c r="H668" t="s">
+        <v>35</v>
+      </c>
+      <c r="I668">
+        <v>57</v>
+      </c>
+      <c r="J668">
+        <v>7546.22</v>
+      </c>
+      <c r="K668">
+        <v>8845.26</v>
+      </c>
+      <c r="L668">
+        <v>1299.04</v>
+      </c>
+      <c r="M668" t="s">
+        <v>23</v>
+      </c>
+      <c r="N668">
+        <v>57</v>
+      </c>
+      <c r="O668">
+        <v>7546.2186</v>
+      </c>
+      <c r="P668">
+        <v>8845.26</v>
+      </c>
+    </row>
+    <row r="669" spans="1:16">
+      <c r="A669" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B669" t="s">
+        <v>24</v>
+      </c>
+      <c r="C669" t="s">
+        <v>36</v>
+      </c>
+      <c r="D669">
+        <v>34.0694</v>
+      </c>
+      <c r="E669">
+        <v>35.66</v>
+      </c>
+      <c r="F669">
+        <v>0.046687</v>
+      </c>
+      <c r="G669">
+        <v>4.67</v>
+      </c>
+      <c r="H669" t="s">
+        <v>36</v>
+      </c>
+      <c r="I669">
+        <v>48</v>
+      </c>
+      <c r="J669">
+        <v>1635.33</v>
+      </c>
+      <c r="K669">
+        <v>1711.68</v>
+      </c>
+      <c r="L669">
+        <v>76.34999999999999</v>
+      </c>
+      <c r="M669" t="s">
+        <v>24</v>
+      </c>
+      <c r="N669">
+        <v>48</v>
+      </c>
+      <c r="O669">
+        <v>1635.3312</v>
+      </c>
+      <c r="P669">
+        <v>1711.68</v>
+      </c>
+    </row>
+    <row r="670" spans="1:16">
+      <c r="A670" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B670" t="s">
+        <v>25</v>
+      </c>
+      <c r="C670" t="s">
+        <v>37</v>
+      </c>
+      <c r="D670">
+        <v>69.4158</v>
+      </c>
+      <c r="E670">
+        <v>74.95999999999999</v>
+      </c>
+      <c r="F670">
+        <v>0.079869</v>
+      </c>
+      <c r="G670">
+        <v>7.99</v>
+      </c>
+      <c r="H670" t="s">
+        <v>37</v>
+      </c>
+      <c r="I670">
+        <v>62</v>
+      </c>
+      <c r="J670">
+        <v>4303.78</v>
+      </c>
+      <c r="K670">
+        <v>4647.52</v>
+      </c>
+      <c r="L670">
+        <v>343.74</v>
+      </c>
+      <c r="M670" t="s">
+        <v>25</v>
+      </c>
+      <c r="N670">
+        <v>62</v>
+      </c>
+      <c r="O670">
+        <v>4303.7796</v>
+      </c>
+      <c r="P670">
+        <v>4647.52</v>
+      </c>
+    </row>
+    <row r="671" spans="1:16">
+      <c r="A671" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B671" t="s">
+        <v>26</v>
+      </c>
+      <c r="C671" t="s">
+        <v>38</v>
+      </c>
+      <c r="D671">
+        <v>8.1868</v>
+      </c>
+      <c r="E671">
+        <v>8.872</v>
+      </c>
+      <c r="F671">
+        <v>0.08369600000000001</v>
+      </c>
+      <c r="G671">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H671" t="s">
+        <v>38</v>
+      </c>
+      <c r="I671">
+        <v>431</v>
+      </c>
+      <c r="J671">
+        <v>3528.51</v>
+      </c>
+      <c r="K671">
+        <v>3823.83</v>
+      </c>
+      <c r="L671">
+        <v>295.32</v>
+      </c>
+      <c r="M671" t="s">
+        <v>26</v>
+      </c>
+      <c r="N671">
+        <v>431</v>
+      </c>
+      <c r="O671">
+        <v>3528.5108</v>
+      </c>
+      <c r="P671">
+        <v>3823.832</v>
       </c>
     </row>
   </sheetData>
@@ -28899,7 +29577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -31402,6 +32080,50 @@
       </c>
       <c r="N61" s="2">
         <v>0.1249612591513305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B62" s="2">
+        <v>0.072299</v>
+      </c>
+      <c r="C62" s="2">
+        <v>-0.102091</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0.08212999999999999</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0.23834</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0.229774</v>
+      </c>
+      <c r="G62" s="2">
+        <v>0.06033</v>
+      </c>
+      <c r="H62" s="2">
+        <v>0.5559730000000001</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0.116367</v>
+      </c>
+      <c r="J62" s="2">
+        <v>0.172145</v>
+      </c>
+      <c r="K62" s="2">
+        <v>0.046687</v>
+      </c>
+      <c r="L62" s="2">
+        <v>0.079869</v>
+      </c>
+      <c r="M62" s="2">
+        <v>0.08369600000000001</v>
+      </c>
+      <c r="N62" s="2">
+        <v>0.1367461065210505</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="43">
   <si>
     <t>data</t>
   </si>
@@ -245,10 +245,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -431,16 +431,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$62</c:f>
+              <c:f>grafico_dati!$B$2:$B$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -623,6 +626,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.072299</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.063511</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -650,10 +656,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -836,21 +842,27 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$62</c:f>
+              <c:f>grafico_dati!$C$2:$C$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="59">
                   <c:v>-0.102091</c:v>
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-0.102091</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-0.098109</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -878,10 +890,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1064,16 +1076,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$62</c:f>
+              <c:f>grafico_dati!$D$2:$D$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1256,6 +1271,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.08212999999999999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.07532</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1283,10 +1301,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1469,16 +1487,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$62</c:f>
+              <c:f>grafico_dati!$E$2:$E$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1661,6 +1682,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.23834</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.248922</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1688,10 +1712,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1874,16 +1898,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$62</c:f>
+              <c:f>grafico_dati!$F$2:$F$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2066,6 +2093,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.229774</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.243565</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2093,10 +2123,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2279,16 +2309,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$62</c:f>
+              <c:f>grafico_dati!$G$2:$G$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2468,6 +2501,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.06033</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.051726</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2495,10 +2531,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2681,16 +2717,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$62</c:f>
+              <c:f>grafico_dati!$H$2:$H$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2873,6 +2912,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.5559730000000001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.539194</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2900,10 +2942,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3086,16 +3128,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$62</c:f>
+              <c:f>grafico_dati!$I$2:$I$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3278,6 +3323,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.116367</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.116468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3305,10 +3353,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3491,16 +3539,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$62</c:f>
+              <c:f>grafico_dati!$J$2:$J$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3680,6 +3731,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.172145</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.168066</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3707,10 +3761,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3893,16 +3947,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$62</c:f>
+              <c:f>grafico_dati!$K$2:$K$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4085,6 +4142,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.046687</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.029369</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4112,10 +4172,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4298,16 +4358,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$62</c:f>
+              <c:f>grafico_dati!$L$2:$L$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4487,6 +4550,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.079869</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.073675</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4514,10 +4580,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4700,16 +4766,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$62</c:f>
+              <c:f>grafico_dati!$M$2:$M$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4892,6 +4961,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.08369600000000001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.083574</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4923,10 +4995,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$62</c:f>
+              <c:f>grafico_dati!$A$2:$A$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5109,16 +5181,19 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$N$2:$N$62</c:f>
+              <c:f>grafico_dati!$N$2:$N$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5301,6 +5376,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0.1367461065210505</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.1339318743997584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5707,7 +5785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P671"/>
+  <dimension ref="A1:P683"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -29568,6 +29646,606 @@
       </c>
       <c r="P671">
         <v>3823.832</v>
+      </c>
+    </row>
+    <row r="672" spans="1:16">
+      <c r="A672" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B672" t="s">
+        <v>16</v>
+      </c>
+      <c r="C672" t="s">
+        <v>28</v>
+      </c>
+      <c r="D672">
+        <v>50.07</v>
+      </c>
+      <c r="E672">
+        <v>53.25</v>
+      </c>
+      <c r="F672">
+        <v>0.063511</v>
+      </c>
+      <c r="G672">
+        <v>6.35</v>
+      </c>
+      <c r="H672" t="s">
+        <v>28</v>
+      </c>
+      <c r="I672">
+        <v>23</v>
+      </c>
+      <c r="J672">
+        <v>1151.61</v>
+      </c>
+      <c r="K672">
+        <v>1224.75</v>
+      </c>
+      <c r="L672">
+        <v>73.14</v>
+      </c>
+      <c r="M672" t="s">
+        <v>16</v>
+      </c>
+      <c r="N672">
+        <v>23</v>
+      </c>
+      <c r="O672">
+        <v>1151.61</v>
+      </c>
+      <c r="P672">
+        <v>1224.75</v>
+      </c>
+    </row>
+    <row r="673" spans="1:16">
+      <c r="A673" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B673" t="s">
+        <v>27</v>
+      </c>
+      <c r="C673" t="s">
+        <v>39</v>
+      </c>
+      <c r="D673">
+        <v>16.0729</v>
+      </c>
+      <c r="E673">
+        <v>14.496</v>
+      </c>
+      <c r="F673">
+        <v>-0.098109</v>
+      </c>
+      <c r="G673">
+        <v>-9.81</v>
+      </c>
+      <c r="H673" t="s">
+        <v>40</v>
+      </c>
+      <c r="I673">
+        <v>63</v>
+      </c>
+      <c r="J673">
+        <v>1012.59</v>
+      </c>
+      <c r="K673">
+        <v>913.25</v>
+      </c>
+      <c r="L673">
+        <v>-99.34</v>
+      </c>
+      <c r="M673" t="s">
+        <v>27</v>
+      </c>
+      <c r="N673">
+        <v>63</v>
+      </c>
+      <c r="O673">
+        <v>1012.5927</v>
+      </c>
+      <c r="P673">
+        <v>913.248</v>
+      </c>
+    </row>
+    <row r="674" spans="1:16">
+      <c r="A674" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B674" t="s">
+        <v>17</v>
+      </c>
+      <c r="C674" t="s">
+        <v>29</v>
+      </c>
+      <c r="D674">
+        <v>242.3</v>
+      </c>
+      <c r="E674">
+        <v>260.55</v>
+      </c>
+      <c r="F674">
+        <v>0.07532</v>
+      </c>
+      <c r="G674">
+        <v>7.53</v>
+      </c>
+      <c r="H674" t="s">
+        <v>29</v>
+      </c>
+      <c r="I674">
+        <v>5</v>
+      </c>
+      <c r="J674">
+        <v>1211.5</v>
+      </c>
+      <c r="K674">
+        <v>1302.75</v>
+      </c>
+      <c r="L674">
+        <v>91.25</v>
+      </c>
+      <c r="M674" t="s">
+        <v>17</v>
+      </c>
+      <c r="N674">
+        <v>5</v>
+      </c>
+      <c r="O674">
+        <v>1211.5</v>
+      </c>
+      <c r="P674">
+        <v>1302.75</v>
+      </c>
+    </row>
+    <row r="675" spans="1:16">
+      <c r="A675" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B675" t="s">
+        <v>18</v>
+      </c>
+      <c r="C675" t="s">
+        <v>30</v>
+      </c>
+      <c r="D675">
+        <v>38.273</v>
+      </c>
+      <c r="E675">
+        <v>47.8</v>
+      </c>
+      <c r="F675">
+        <v>0.248922</v>
+      </c>
+      <c r="G675">
+        <v>24.89</v>
+      </c>
+      <c r="H675" t="s">
+        <v>30</v>
+      </c>
+      <c r="I675">
+        <v>54</v>
+      </c>
+      <c r="J675">
+        <v>2066.74</v>
+      </c>
+      <c r="K675">
+        <v>2581.2</v>
+      </c>
+      <c r="L675">
+        <v>514.46</v>
+      </c>
+      <c r="M675" t="s">
+        <v>18</v>
+      </c>
+      <c r="N675">
+        <v>54</v>
+      </c>
+      <c r="O675">
+        <v>2066.742</v>
+      </c>
+      <c r="P675">
+        <v>2581.2</v>
+      </c>
+    </row>
+    <row r="676" spans="1:16">
+      <c r="A676" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B676" t="s">
+        <v>19</v>
+      </c>
+      <c r="C676" t="s">
+        <v>31</v>
+      </c>
+      <c r="D676">
+        <v>6.5264</v>
+      </c>
+      <c r="E676">
+        <v>8.116</v>
+      </c>
+      <c r="F676">
+        <v>0.243565</v>
+      </c>
+      <c r="G676">
+        <v>24.36</v>
+      </c>
+      <c r="H676" t="s">
+        <v>31</v>
+      </c>
+      <c r="I676">
+        <v>276</v>
+      </c>
+      <c r="J676">
+        <v>1801.29</v>
+      </c>
+      <c r="K676">
+        <v>2240.02</v>
+      </c>
+      <c r="L676">
+        <v>438.73</v>
+      </c>
+      <c r="M676" t="s">
+        <v>19</v>
+      </c>
+      <c r="N676">
+        <v>276</v>
+      </c>
+      <c r="O676">
+        <v>1801.2864</v>
+      </c>
+      <c r="P676">
+        <v>2240.016</v>
+      </c>
+    </row>
+    <row r="677" spans="1:16">
+      <c r="A677" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B677" t="s">
+        <v>20</v>
+      </c>
+      <c r="C677" t="s">
+        <v>32</v>
+      </c>
+      <c r="D677">
+        <v>197.58</v>
+      </c>
+      <c r="E677">
+        <v>207.8</v>
+      </c>
+      <c r="F677">
+        <v>0.051726</v>
+      </c>
+      <c r="G677">
+        <v>5.17</v>
+      </c>
+      <c r="H677" t="s">
+        <v>32</v>
+      </c>
+      <c r="I677">
+        <v>4</v>
+      </c>
+      <c r="J677">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K677">
+        <v>831.2</v>
+      </c>
+      <c r="L677">
+        <v>40.88</v>
+      </c>
+      <c r="M677" t="s">
+        <v>20</v>
+      </c>
+      <c r="N677">
+        <v>4</v>
+      </c>
+      <c r="O677">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P677">
+        <v>831.2</v>
+      </c>
+    </row>
+    <row r="678" spans="1:16">
+      <c r="A678" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B678" t="s">
+        <v>21</v>
+      </c>
+      <c r="C678" t="s">
+        <v>33</v>
+      </c>
+      <c r="D678">
+        <v>79.86</v>
+      </c>
+      <c r="E678">
+        <v>122.92</v>
+      </c>
+      <c r="F678">
+        <v>0.539194</v>
+      </c>
+      <c r="G678">
+        <v>53.92</v>
+      </c>
+      <c r="H678" t="s">
+        <v>33</v>
+      </c>
+      <c r="I678">
+        <v>12</v>
+      </c>
+      <c r="J678">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K678">
+        <v>1475.04</v>
+      </c>
+      <c r="L678">
+        <v>516.72</v>
+      </c>
+      <c r="M678" t="s">
+        <v>21</v>
+      </c>
+      <c r="N678">
+        <v>12</v>
+      </c>
+      <c r="O678">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P678">
+        <v>1475.04</v>
+      </c>
+    </row>
+    <row r="679" spans="1:16">
+      <c r="A679" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B679" t="s">
+        <v>22</v>
+      </c>
+      <c r="C679" t="s">
+        <v>34</v>
+      </c>
+      <c r="D679">
+        <v>19.7444</v>
+      </c>
+      <c r="E679">
+        <v>22.044</v>
+      </c>
+      <c r="F679">
+        <v>0.116468</v>
+      </c>
+      <c r="G679">
+        <v>11.65</v>
+      </c>
+      <c r="H679" t="s">
+        <v>34</v>
+      </c>
+      <c r="I679">
+        <v>61</v>
+      </c>
+      <c r="J679">
+        <v>1204.41</v>
+      </c>
+      <c r="K679">
+        <v>1344.68</v>
+      </c>
+      <c r="L679">
+        <v>140.28</v>
+      </c>
+      <c r="M679" t="s">
+        <v>22</v>
+      </c>
+      <c r="N679">
+        <v>61</v>
+      </c>
+      <c r="O679">
+        <v>1204.4084</v>
+      </c>
+      <c r="P679">
+        <v>1344.684</v>
+      </c>
+    </row>
+    <row r="680" spans="1:16">
+      <c r="A680" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B680" t="s">
+        <v>23</v>
+      </c>
+      <c r="C680" t="s">
+        <v>35</v>
+      </c>
+      <c r="D680">
+        <v>132.3898</v>
+      </c>
+      <c r="E680">
+        <v>154.64</v>
+      </c>
+      <c r="F680">
+        <v>0.168066</v>
+      </c>
+      <c r="G680">
+        <v>16.81</v>
+      </c>
+      <c r="H680" t="s">
+        <v>35</v>
+      </c>
+      <c r="I680">
+        <v>57</v>
+      </c>
+      <c r="J680">
+        <v>7546.22</v>
+      </c>
+      <c r="K680">
+        <v>8814.48</v>
+      </c>
+      <c r="L680">
+        <v>1268.26</v>
+      </c>
+      <c r="M680" t="s">
+        <v>23</v>
+      </c>
+      <c r="N680">
+        <v>57</v>
+      </c>
+      <c r="O680">
+        <v>7546.2186</v>
+      </c>
+      <c r="P680">
+        <v>8814.48</v>
+      </c>
+    </row>
+    <row r="681" spans="1:16">
+      <c r="A681" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B681" t="s">
+        <v>24</v>
+      </c>
+      <c r="C681" t="s">
+        <v>36</v>
+      </c>
+      <c r="D681">
+        <v>34.0694</v>
+      </c>
+      <c r="E681">
+        <v>35.07</v>
+      </c>
+      <c r="F681">
+        <v>0.029369</v>
+      </c>
+      <c r="G681">
+        <v>2.94</v>
+      </c>
+      <c r="H681" t="s">
+        <v>36</v>
+      </c>
+      <c r="I681">
+        <v>48</v>
+      </c>
+      <c r="J681">
+        <v>1635.33</v>
+      </c>
+      <c r="K681">
+        <v>1683.36</v>
+      </c>
+      <c r="L681">
+        <v>48.03</v>
+      </c>
+      <c r="M681" t="s">
+        <v>24</v>
+      </c>
+      <c r="N681">
+        <v>48</v>
+      </c>
+      <c r="O681">
+        <v>1635.3312</v>
+      </c>
+      <c r="P681">
+        <v>1683.36</v>
+      </c>
+    </row>
+    <row r="682" spans="1:16">
+      <c r="A682" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B682" t="s">
+        <v>25</v>
+      </c>
+      <c r="C682" t="s">
+        <v>37</v>
+      </c>
+      <c r="D682">
+        <v>69.4158</v>
+      </c>
+      <c r="E682">
+        <v>74.53</v>
+      </c>
+      <c r="F682">
+        <v>0.073675</v>
+      </c>
+      <c r="G682">
+        <v>7.37</v>
+      </c>
+      <c r="H682" t="s">
+        <v>37</v>
+      </c>
+      <c r="I682">
+        <v>62</v>
+      </c>
+      <c r="J682">
+        <v>4303.78</v>
+      </c>
+      <c r="K682">
+        <v>4620.86</v>
+      </c>
+      <c r="L682">
+        <v>317.08</v>
+      </c>
+      <c r="M682" t="s">
+        <v>25</v>
+      </c>
+      <c r="N682">
+        <v>62</v>
+      </c>
+      <c r="O682">
+        <v>4303.7796</v>
+      </c>
+      <c r="P682">
+        <v>4620.86</v>
+      </c>
+    </row>
+    <row r="683" spans="1:16">
+      <c r="A683" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B683" t="s">
+        <v>26</v>
+      </c>
+      <c r="C683" t="s">
+        <v>38</v>
+      </c>
+      <c r="D683">
+        <v>8.1868</v>
+      </c>
+      <c r="E683">
+        <v>8.871</v>
+      </c>
+      <c r="F683">
+        <v>0.083574</v>
+      </c>
+      <c r="G683">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H683" t="s">
+        <v>38</v>
+      </c>
+      <c r="I683">
+        <v>431</v>
+      </c>
+      <c r="J683">
+        <v>3528.51</v>
+      </c>
+      <c r="K683">
+        <v>3823.4</v>
+      </c>
+      <c r="L683">
+        <v>294.89</v>
+      </c>
+      <c r="M683" t="s">
+        <v>26</v>
+      </c>
+      <c r="N683">
+        <v>431</v>
+      </c>
+      <c r="O683">
+        <v>3528.5108</v>
+      </c>
+      <c r="P683">
+        <v>3823.401</v>
       </c>
     </row>
   </sheetData>
@@ -29577,7 +30255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -32124,6 +32802,50 @@
       </c>
       <c r="N62" s="2">
         <v>0.1367461065210505</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B63" s="2">
+        <v>0.063511</v>
+      </c>
+      <c r="C63" s="2">
+        <v>-0.098109</v>
+      </c>
+      <c r="D63" s="2">
+        <v>0.07532</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0.248922</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0.243565</v>
+      </c>
+      <c r="G63" s="2">
+        <v>0.051726</v>
+      </c>
+      <c r="H63" s="2">
+        <v>0.539194</v>
+      </c>
+      <c r="I63" s="2">
+        <v>0.116468</v>
+      </c>
+      <c r="J63" s="2">
+        <v>0.168066</v>
+      </c>
+      <c r="K63" s="2">
+        <v>0.029369</v>
+      </c>
+      <c r="L63" s="2">
+        <v>0.073675</v>
+      </c>
+      <c r="M63" s="2">
+        <v>0.083574</v>
+      </c>
+      <c r="N63" s="2">
+        <v>0.1339318743997584</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="43">
   <si>
     <t>data</t>
   </si>
@@ -245,10 +245,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -434,16 +434,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$63</c:f>
+              <c:f>grafico_dati!$B$2:$B$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -629,6 +632,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.063511</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.06590799999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -656,10 +662,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -845,16 +851,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$63</c:f>
+              <c:f>grafico_dati!$C$2:$C$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="59">
                   <c:v>-0.102091</c:v>
                 </c:pt>
@@ -863,6 +872,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-0.098109</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-0.123369</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -890,10 +902,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1079,16 +1091,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$63</c:f>
+              <c:f>grafico_dati!$D$2:$D$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1274,6 +1289,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.07532</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.071564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1301,10 +1319,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1490,16 +1508,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$63</c:f>
+              <c:f>grafico_dati!$E$2:$E$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1685,6 +1706,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.248922</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.249967</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1712,10 +1736,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1901,16 +1925,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$63</c:f>
+              <c:f>grafico_dati!$F$2:$F$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2096,6 +2123,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.243565</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.247855</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2123,10 +2153,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2312,16 +2342,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$63</c:f>
+              <c:f>grafico_dati!$G$2:$G$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2504,6 +2537,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.051726</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.050714</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2531,10 +2567,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2720,16 +2756,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$63</c:f>
+              <c:f>grafico_dati!$H$2:$H$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2915,6 +2954,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.539194</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.530679</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2942,10 +2984,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3131,16 +3173,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$63</c:f>
+              <c:f>grafico_dati!$I$2:$I$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3326,6 +3371,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.116468</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.105529</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3353,10 +3401,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3542,16 +3590,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$63</c:f>
+              <c:f>grafico_dati!$J$2:$J$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3734,6 +3785,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.168066</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.166253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3761,10 +3815,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3950,16 +4004,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$63</c:f>
+              <c:f>grafico_dati!$K$2:$K$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4145,6 +4202,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.029369</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.033185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4172,10 +4232,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4361,16 +4421,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$63</c:f>
+              <c:f>grafico_dati!$L$2:$L$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4553,6 +4616,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.073675</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.07137</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4580,10 +4646,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4769,16 +4835,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$63</c:f>
+              <c:f>grafico_dati!$M$2:$M$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4964,6 +5033,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.083574</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.087604</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4995,10 +5067,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$63</c:f>
+              <c:f>grafico_dati!$A$2:$A$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5184,16 +5256,19 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$N$2:$N$63</c:f>
+              <c:f>grafico_dati!$N$2:$N$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5379,6 +5454,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.1339318743997584</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.1323606863683446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5785,7 +5863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P683"/>
+  <dimension ref="A1:P695"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -30246,6 +30324,606 @@
       </c>
       <c r="P683">
         <v>3823.401</v>
+      </c>
+    </row>
+    <row r="684" spans="1:16">
+      <c r="A684" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B684" t="s">
+        <v>16</v>
+      </c>
+      <c r="C684" t="s">
+        <v>28</v>
+      </c>
+      <c r="D684">
+        <v>50.07</v>
+      </c>
+      <c r="E684">
+        <v>53.37</v>
+      </c>
+      <c r="F684">
+        <v>0.06590799999999999</v>
+      </c>
+      <c r="G684">
+        <v>6.59</v>
+      </c>
+      <c r="H684" t="s">
+        <v>28</v>
+      </c>
+      <c r="I684">
+        <v>23</v>
+      </c>
+      <c r="J684">
+        <v>1151.61</v>
+      </c>
+      <c r="K684">
+        <v>1227.51</v>
+      </c>
+      <c r="L684">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M684" t="s">
+        <v>16</v>
+      </c>
+      <c r="N684">
+        <v>23</v>
+      </c>
+      <c r="O684">
+        <v>1151.61</v>
+      </c>
+      <c r="P684">
+        <v>1227.51</v>
+      </c>
+    </row>
+    <row r="685" spans="1:16">
+      <c r="A685" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B685" t="s">
+        <v>27</v>
+      </c>
+      <c r="C685" t="s">
+        <v>39</v>
+      </c>
+      <c r="D685">
+        <v>16.0729</v>
+      </c>
+      <c r="E685">
+        <v>14.09</v>
+      </c>
+      <c r="F685">
+        <v>-0.123369</v>
+      </c>
+      <c r="G685">
+        <v>-12.34</v>
+      </c>
+      <c r="H685" t="s">
+        <v>40</v>
+      </c>
+      <c r="I685">
+        <v>63</v>
+      </c>
+      <c r="J685">
+        <v>1012.59</v>
+      </c>
+      <c r="K685">
+        <v>887.67</v>
+      </c>
+      <c r="L685">
+        <v>-124.92</v>
+      </c>
+      <c r="M685" t="s">
+        <v>27</v>
+      </c>
+      <c r="N685">
+        <v>63</v>
+      </c>
+      <c r="O685">
+        <v>1012.5927</v>
+      </c>
+      <c r="P685">
+        <v>887.67</v>
+      </c>
+    </row>
+    <row r="686" spans="1:16">
+      <c r="A686" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B686" t="s">
+        <v>17</v>
+      </c>
+      <c r="C686" t="s">
+        <v>29</v>
+      </c>
+      <c r="D686">
+        <v>242.3</v>
+      </c>
+      <c r="E686">
+        <v>259.64</v>
+      </c>
+      <c r="F686">
+        <v>0.071564</v>
+      </c>
+      <c r="G686">
+        <v>7.16</v>
+      </c>
+      <c r="H686" t="s">
+        <v>29</v>
+      </c>
+      <c r="I686">
+        <v>5</v>
+      </c>
+      <c r="J686">
+        <v>1211.5</v>
+      </c>
+      <c r="K686">
+        <v>1298.2</v>
+      </c>
+      <c r="L686">
+        <v>86.7</v>
+      </c>
+      <c r="M686" t="s">
+        <v>17</v>
+      </c>
+      <c r="N686">
+        <v>5</v>
+      </c>
+      <c r="O686">
+        <v>1211.5</v>
+      </c>
+      <c r="P686">
+        <v>1298.2</v>
+      </c>
+    </row>
+    <row r="687" spans="1:16">
+      <c r="A687" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B687" t="s">
+        <v>18</v>
+      </c>
+      <c r="C687" t="s">
+        <v>30</v>
+      </c>
+      <c r="D687">
+        <v>38.273</v>
+      </c>
+      <c r="E687">
+        <v>47.84</v>
+      </c>
+      <c r="F687">
+        <v>0.249967</v>
+      </c>
+      <c r="G687">
+        <v>25</v>
+      </c>
+      <c r="H687" t="s">
+        <v>30</v>
+      </c>
+      <c r="I687">
+        <v>54</v>
+      </c>
+      <c r="J687">
+        <v>2066.74</v>
+      </c>
+      <c r="K687">
+        <v>2583.36</v>
+      </c>
+      <c r="L687">
+        <v>516.62</v>
+      </c>
+      <c r="M687" t="s">
+        <v>18</v>
+      </c>
+      <c r="N687">
+        <v>54</v>
+      </c>
+      <c r="O687">
+        <v>2066.742</v>
+      </c>
+      <c r="P687">
+        <v>2583.36</v>
+      </c>
+    </row>
+    <row r="688" spans="1:16">
+      <c r="A688" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B688" t="s">
+        <v>19</v>
+      </c>
+      <c r="C688" t="s">
+        <v>31</v>
+      </c>
+      <c r="D688">
+        <v>6.5264</v>
+      </c>
+      <c r="E688">
+        <v>8.144</v>
+      </c>
+      <c r="F688">
+        <v>0.247855</v>
+      </c>
+      <c r="G688">
+        <v>24.79</v>
+      </c>
+      <c r="H688" t="s">
+        <v>31</v>
+      </c>
+      <c r="I688">
+        <v>276</v>
+      </c>
+      <c r="J688">
+        <v>1801.29</v>
+      </c>
+      <c r="K688">
+        <v>2247.74</v>
+      </c>
+      <c r="L688">
+        <v>446.46</v>
+      </c>
+      <c r="M688" t="s">
+        <v>19</v>
+      </c>
+      <c r="N688">
+        <v>276</v>
+      </c>
+      <c r="O688">
+        <v>1801.2864</v>
+      </c>
+      <c r="P688">
+        <v>2247.744</v>
+      </c>
+    </row>
+    <row r="689" spans="1:16">
+      <c r="A689" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B689" t="s">
+        <v>20</v>
+      </c>
+      <c r="C689" t="s">
+        <v>32</v>
+      </c>
+      <c r="D689">
+        <v>197.58</v>
+      </c>
+      <c r="E689">
+        <v>207.6</v>
+      </c>
+      <c r="F689">
+        <v>0.050714</v>
+      </c>
+      <c r="G689">
+        <v>5.07</v>
+      </c>
+      <c r="H689" t="s">
+        <v>32</v>
+      </c>
+      <c r="I689">
+        <v>4</v>
+      </c>
+      <c r="J689">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K689">
+        <v>830.4</v>
+      </c>
+      <c r="L689">
+        <v>40.08</v>
+      </c>
+      <c r="M689" t="s">
+        <v>20</v>
+      </c>
+      <c r="N689">
+        <v>4</v>
+      </c>
+      <c r="O689">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P689">
+        <v>830.4</v>
+      </c>
+    </row>
+    <row r="690" spans="1:16">
+      <c r="A690" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B690" t="s">
+        <v>21</v>
+      </c>
+      <c r="C690" t="s">
+        <v>33</v>
+      </c>
+      <c r="D690">
+        <v>79.86</v>
+      </c>
+      <c r="E690">
+        <v>122.24</v>
+      </c>
+      <c r="F690">
+        <v>0.530679</v>
+      </c>
+      <c r="G690">
+        <v>53.07</v>
+      </c>
+      <c r="H690" t="s">
+        <v>33</v>
+      </c>
+      <c r="I690">
+        <v>12</v>
+      </c>
+      <c r="J690">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K690">
+        <v>1466.88</v>
+      </c>
+      <c r="L690">
+        <v>508.56</v>
+      </c>
+      <c r="M690" t="s">
+        <v>21</v>
+      </c>
+      <c r="N690">
+        <v>12</v>
+      </c>
+      <c r="O690">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P690">
+        <v>1466.88</v>
+      </c>
+    </row>
+    <row r="691" spans="1:16">
+      <c r="A691" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B691" t="s">
+        <v>22</v>
+      </c>
+      <c r="C691" t="s">
+        <v>34</v>
+      </c>
+      <c r="D691">
+        <v>19.7444</v>
+      </c>
+      <c r="E691">
+        <v>21.828</v>
+      </c>
+      <c r="F691">
+        <v>0.105529</v>
+      </c>
+      <c r="G691">
+        <v>10.55</v>
+      </c>
+      <c r="H691" t="s">
+        <v>34</v>
+      </c>
+      <c r="I691">
+        <v>61</v>
+      </c>
+      <c r="J691">
+        <v>1204.41</v>
+      </c>
+      <c r="K691">
+        <v>1331.51</v>
+      </c>
+      <c r="L691">
+        <v>127.1</v>
+      </c>
+      <c r="M691" t="s">
+        <v>22</v>
+      </c>
+      <c r="N691">
+        <v>61</v>
+      </c>
+      <c r="O691">
+        <v>1204.4084</v>
+      </c>
+      <c r="P691">
+        <v>1331.508</v>
+      </c>
+    </row>
+    <row r="692" spans="1:16">
+      <c r="A692" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B692" t="s">
+        <v>23</v>
+      </c>
+      <c r="C692" t="s">
+        <v>35</v>
+      </c>
+      <c r="D692">
+        <v>132.3898</v>
+      </c>
+      <c r="E692">
+        <v>154.4</v>
+      </c>
+      <c r="F692">
+        <v>0.166253</v>
+      </c>
+      <c r="G692">
+        <v>16.63</v>
+      </c>
+      <c r="H692" t="s">
+        <v>35</v>
+      </c>
+      <c r="I692">
+        <v>57</v>
+      </c>
+      <c r="J692">
+        <v>7546.22</v>
+      </c>
+      <c r="K692">
+        <v>8800.799999999999</v>
+      </c>
+      <c r="L692">
+        <v>1254.58</v>
+      </c>
+      <c r="M692" t="s">
+        <v>23</v>
+      </c>
+      <c r="N692">
+        <v>57</v>
+      </c>
+      <c r="O692">
+        <v>7546.2186</v>
+      </c>
+      <c r="P692">
+        <v>8800.800000000001</v>
+      </c>
+    </row>
+    <row r="693" spans="1:16">
+      <c r="A693" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B693" t="s">
+        <v>24</v>
+      </c>
+      <c r="C693" t="s">
+        <v>36</v>
+      </c>
+      <c r="D693">
+        <v>34.0694</v>
+      </c>
+      <c r="E693">
+        <v>35.2</v>
+      </c>
+      <c r="F693">
+        <v>0.033185</v>
+      </c>
+      <c r="G693">
+        <v>3.32</v>
+      </c>
+      <c r="H693" t="s">
+        <v>36</v>
+      </c>
+      <c r="I693">
+        <v>48</v>
+      </c>
+      <c r="J693">
+        <v>1635.33</v>
+      </c>
+      <c r="K693">
+        <v>1689.6</v>
+      </c>
+      <c r="L693">
+        <v>54.27</v>
+      </c>
+      <c r="M693" t="s">
+        <v>24</v>
+      </c>
+      <c r="N693">
+        <v>48</v>
+      </c>
+      <c r="O693">
+        <v>1635.3312</v>
+      </c>
+      <c r="P693">
+        <v>1689.6</v>
+      </c>
+    </row>
+    <row r="694" spans="1:16">
+      <c r="A694" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B694" t="s">
+        <v>25</v>
+      </c>
+      <c r="C694" t="s">
+        <v>37</v>
+      </c>
+      <c r="D694">
+        <v>69.4158</v>
+      </c>
+      <c r="E694">
+        <v>74.37</v>
+      </c>
+      <c r="F694">
+        <v>0.07137</v>
+      </c>
+      <c r="G694">
+        <v>7.14</v>
+      </c>
+      <c r="H694" t="s">
+        <v>37</v>
+      </c>
+      <c r="I694">
+        <v>62</v>
+      </c>
+      <c r="J694">
+        <v>4303.78</v>
+      </c>
+      <c r="K694">
+        <v>4610.94</v>
+      </c>
+      <c r="L694">
+        <v>307.16</v>
+      </c>
+      <c r="M694" t="s">
+        <v>25</v>
+      </c>
+      <c r="N694">
+        <v>62</v>
+      </c>
+      <c r="O694">
+        <v>4303.7796</v>
+      </c>
+      <c r="P694">
+        <v>4610.940000000001</v>
+      </c>
+    </row>
+    <row r="695" spans="1:16">
+      <c r="A695" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B695" t="s">
+        <v>26</v>
+      </c>
+      <c r="C695" t="s">
+        <v>38</v>
+      </c>
+      <c r="D695">
+        <v>8.1868</v>
+      </c>
+      <c r="E695">
+        <v>8.904</v>
+      </c>
+      <c r="F695">
+        <v>0.087604</v>
+      </c>
+      <c r="G695">
+        <v>8.76</v>
+      </c>
+      <c r="H695" t="s">
+        <v>38</v>
+      </c>
+      <c r="I695">
+        <v>431</v>
+      </c>
+      <c r="J695">
+        <v>3528.51</v>
+      </c>
+      <c r="K695">
+        <v>3837.62</v>
+      </c>
+      <c r="L695">
+        <v>309.11</v>
+      </c>
+      <c r="M695" t="s">
+        <v>26</v>
+      </c>
+      <c r="N695">
+        <v>431</v>
+      </c>
+      <c r="O695">
+        <v>3528.5108</v>
+      </c>
+      <c r="P695">
+        <v>3837.624</v>
       </c>
     </row>
   </sheetData>
@@ -30255,7 +30933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -32846,6 +33524,50 @@
       </c>
       <c r="N63" s="2">
         <v>0.1339318743997584</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0.06590799999999999</v>
+      </c>
+      <c r="C64" s="2">
+        <v>-0.123369</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0.071564</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0.249967</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0.247855</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0.050714</v>
+      </c>
+      <c r="H64" s="2">
+        <v>0.530679</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0.105529</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0.166253</v>
+      </c>
+      <c r="K64" s="2">
+        <v>0.033185</v>
+      </c>
+      <c r="L64" s="2">
+        <v>0.07137</v>
+      </c>
+      <c r="M64" s="2">
+        <v>0.087604</v>
+      </c>
+      <c r="N64" s="2">
+        <v>0.1323606863683446</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -428,16 +428,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$64</c:f>
+              <c:f>grafico_dati!$B$2:$B$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -626,6 +629,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.06590799999999999</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.074296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -653,10 +659,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -845,16 +851,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$64</c:f>
+              <c:f>grafico_dati!$C$2:$C$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1043,6 +1052,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.071564</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.073834</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1070,10 +1082,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1262,16 +1274,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$64</c:f>
+              <c:f>grafico_dati!$D$2:$D$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1460,6 +1475,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.249967</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.260419</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1487,10 +1505,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1679,16 +1697,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$64</c:f>
+              <c:f>grafico_dati!$E$2:$E$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1877,6 +1898,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.247855</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.267314</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1904,10 +1928,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2096,16 +2120,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$64</c:f>
+              <c:f>grafico_dati!$F$2:$F$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2291,6 +2318,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.050714</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.049195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2318,10 +2348,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2510,16 +2540,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$64</c:f>
+              <c:f>grafico_dati!$G$2:$G$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2708,6 +2741,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.530679</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.552717</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2735,10 +2771,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2927,16 +2963,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$64</c:f>
+              <c:f>grafico_dati!$H$2:$H$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3125,6 +3164,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.105529</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.116823</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3152,10 +3194,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3344,16 +3386,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$64</c:f>
+              <c:f>grafico_dati!$I$2:$I$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3539,6 +3584,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.166253</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.173731</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3566,10 +3614,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3758,16 +3806,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$64</c:f>
+              <c:f>grafico_dati!$J$2:$J$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -3956,6 +4007,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.033185</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.037588</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3983,10 +4037,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4175,16 +4229,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$64</c:f>
+              <c:f>grafico_dati!$K$2:$K$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4370,6 +4427,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.07137</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.07338699999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4397,10 +4457,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4589,16 +4649,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$64</c:f>
+              <c:f>grafico_dati!$L$2:$L$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4787,6 +4850,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.087604</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.09017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4818,10 +4884,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$64</c:f>
+              <c:f>grafico_dati!$A$2:$A$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5010,16 +5076,19 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$64</c:f>
+              <c:f>grafico_dati!$M$2:$M$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5208,6 +5277,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>0.1422450247875535</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.1492663932287723</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5614,7 +5686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P691"/>
+  <dimension ref="A1:P702"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -30475,6 +30547,556 @@
       </c>
       <c r="P691">
         <v>3837.624</v>
+      </c>
+    </row>
+    <row r="692" spans="1:16">
+      <c r="A692" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B692" t="s">
+        <v>16</v>
+      </c>
+      <c r="C692" t="s">
+        <v>27</v>
+      </c>
+      <c r="D692">
+        <v>50.07</v>
+      </c>
+      <c r="E692">
+        <v>53.79</v>
+      </c>
+      <c r="F692">
+        <v>0.074296</v>
+      </c>
+      <c r="G692">
+        <v>7.43</v>
+      </c>
+      <c r="H692" t="s">
+        <v>27</v>
+      </c>
+      <c r="I692">
+        <v>23</v>
+      </c>
+      <c r="J692">
+        <v>1151.61</v>
+      </c>
+      <c r="K692">
+        <v>1237.17</v>
+      </c>
+      <c r="L692">
+        <v>85.56</v>
+      </c>
+      <c r="M692" t="s">
+        <v>16</v>
+      </c>
+      <c r="N692">
+        <v>23</v>
+      </c>
+      <c r="O692">
+        <v>1151.61</v>
+      </c>
+      <c r="P692">
+        <v>1237.17</v>
+      </c>
+    </row>
+    <row r="693" spans="1:16">
+      <c r="A693" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B693" t="s">
+        <v>17</v>
+      </c>
+      <c r="C693" t="s">
+        <v>28</v>
+      </c>
+      <c r="D693">
+        <v>242.3</v>
+      </c>
+      <c r="E693">
+        <v>260.19</v>
+      </c>
+      <c r="F693">
+        <v>0.073834</v>
+      </c>
+      <c r="G693">
+        <v>7.38</v>
+      </c>
+      <c r="H693" t="s">
+        <v>28</v>
+      </c>
+      <c r="I693">
+        <v>5</v>
+      </c>
+      <c r="J693">
+        <v>1211.5</v>
+      </c>
+      <c r="K693">
+        <v>1300.95</v>
+      </c>
+      <c r="L693">
+        <v>89.45</v>
+      </c>
+      <c r="M693" t="s">
+        <v>17</v>
+      </c>
+      <c r="N693">
+        <v>5</v>
+      </c>
+      <c r="O693">
+        <v>1211.5</v>
+      </c>
+      <c r="P693">
+        <v>1300.95</v>
+      </c>
+    </row>
+    <row r="694" spans="1:16">
+      <c r="A694" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B694" t="s">
+        <v>18</v>
+      </c>
+      <c r="C694" t="s">
+        <v>29</v>
+      </c>
+      <c r="D694">
+        <v>38.273</v>
+      </c>
+      <c r="E694">
+        <v>48.24</v>
+      </c>
+      <c r="F694">
+        <v>0.260419</v>
+      </c>
+      <c r="G694">
+        <v>26.04</v>
+      </c>
+      <c r="H694" t="s">
+        <v>29</v>
+      </c>
+      <c r="I694">
+        <v>54</v>
+      </c>
+      <c r="J694">
+        <v>2066.74</v>
+      </c>
+      <c r="K694">
+        <v>2604.96</v>
+      </c>
+      <c r="L694">
+        <v>538.22</v>
+      </c>
+      <c r="M694" t="s">
+        <v>18</v>
+      </c>
+      <c r="N694">
+        <v>54</v>
+      </c>
+      <c r="O694">
+        <v>2066.742</v>
+      </c>
+      <c r="P694">
+        <v>2604.96</v>
+      </c>
+    </row>
+    <row r="695" spans="1:16">
+      <c r="A695" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B695" t="s">
+        <v>19</v>
+      </c>
+      <c r="C695" t="s">
+        <v>30</v>
+      </c>
+      <c r="D695">
+        <v>6.5264</v>
+      </c>
+      <c r="E695">
+        <v>8.271000000000001</v>
+      </c>
+      <c r="F695">
+        <v>0.267314</v>
+      </c>
+      <c r="G695">
+        <v>26.73</v>
+      </c>
+      <c r="H695" t="s">
+        <v>30</v>
+      </c>
+      <c r="I695">
+        <v>276</v>
+      </c>
+      <c r="J695">
+        <v>1801.29</v>
+      </c>
+      <c r="K695">
+        <v>2282.8</v>
+      </c>
+      <c r="L695">
+        <v>481.51</v>
+      </c>
+      <c r="M695" t="s">
+        <v>19</v>
+      </c>
+      <c r="N695">
+        <v>276</v>
+      </c>
+      <c r="O695">
+        <v>1801.2864</v>
+      </c>
+      <c r="P695">
+        <v>2282.796</v>
+      </c>
+    </row>
+    <row r="696" spans="1:16">
+      <c r="A696" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B696" t="s">
+        <v>20</v>
+      </c>
+      <c r="C696" t="s">
+        <v>31</v>
+      </c>
+      <c r="D696">
+        <v>197.58</v>
+      </c>
+      <c r="E696">
+        <v>207.3</v>
+      </c>
+      <c r="F696">
+        <v>0.049195</v>
+      </c>
+      <c r="G696">
+        <v>4.92</v>
+      </c>
+      <c r="H696" t="s">
+        <v>31</v>
+      </c>
+      <c r="I696">
+        <v>4</v>
+      </c>
+      <c r="J696">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K696">
+        <v>829.2</v>
+      </c>
+      <c r="L696">
+        <v>38.88</v>
+      </c>
+      <c r="M696" t="s">
+        <v>20</v>
+      </c>
+      <c r="N696">
+        <v>4</v>
+      </c>
+      <c r="O696">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P696">
+        <v>829.2</v>
+      </c>
+    </row>
+    <row r="697" spans="1:16">
+      <c r="A697" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B697" t="s">
+        <v>21</v>
+      </c>
+      <c r="C697" t="s">
+        <v>32</v>
+      </c>
+      <c r="D697">
+        <v>79.86</v>
+      </c>
+      <c r="E697">
+        <v>124</v>
+      </c>
+      <c r="F697">
+        <v>0.552717</v>
+      </c>
+      <c r="G697">
+        <v>55.27</v>
+      </c>
+      <c r="H697" t="s">
+        <v>32</v>
+      </c>
+      <c r="I697">
+        <v>12</v>
+      </c>
+      <c r="J697">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K697">
+        <v>1488</v>
+      </c>
+      <c r="L697">
+        <v>529.6799999999999</v>
+      </c>
+      <c r="M697" t="s">
+        <v>21</v>
+      </c>
+      <c r="N697">
+        <v>12</v>
+      </c>
+      <c r="O697">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P697">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="698" spans="1:16">
+      <c r="A698" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B698" t="s">
+        <v>22</v>
+      </c>
+      <c r="C698" t="s">
+        <v>33</v>
+      </c>
+      <c r="D698">
+        <v>19.7444</v>
+      </c>
+      <c r="E698">
+        <v>22.051</v>
+      </c>
+      <c r="F698">
+        <v>0.116823</v>
+      </c>
+      <c r="G698">
+        <v>11.68</v>
+      </c>
+      <c r="H698" t="s">
+        <v>33</v>
+      </c>
+      <c r="I698">
+        <v>61</v>
+      </c>
+      <c r="J698">
+        <v>1204.41</v>
+      </c>
+      <c r="K698">
+        <v>1345.11</v>
+      </c>
+      <c r="L698">
+        <v>140.7</v>
+      </c>
+      <c r="M698" t="s">
+        <v>22</v>
+      </c>
+      <c r="N698">
+        <v>61</v>
+      </c>
+      <c r="O698">
+        <v>1204.4084</v>
+      </c>
+      <c r="P698">
+        <v>1345.111</v>
+      </c>
+    </row>
+    <row r="699" spans="1:16">
+      <c r="A699" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B699" t="s">
+        <v>23</v>
+      </c>
+      <c r="C699" t="s">
+        <v>34</v>
+      </c>
+      <c r="D699">
+        <v>132.3898</v>
+      </c>
+      <c r="E699">
+        <v>155.39</v>
+      </c>
+      <c r="F699">
+        <v>0.173731</v>
+      </c>
+      <c r="G699">
+        <v>17.37</v>
+      </c>
+      <c r="H699" t="s">
+        <v>34</v>
+      </c>
+      <c r="I699">
+        <v>57</v>
+      </c>
+      <c r="J699">
+        <v>7546.22</v>
+      </c>
+      <c r="K699">
+        <v>8857.23</v>
+      </c>
+      <c r="L699">
+        <v>1311.01</v>
+      </c>
+      <c r="M699" t="s">
+        <v>23</v>
+      </c>
+      <c r="N699">
+        <v>57</v>
+      </c>
+      <c r="O699">
+        <v>7546.2186</v>
+      </c>
+      <c r="P699">
+        <v>8857.23</v>
+      </c>
+    </row>
+    <row r="700" spans="1:16">
+      <c r="A700" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B700" t="s">
+        <v>24</v>
+      </c>
+      <c r="C700" t="s">
+        <v>35</v>
+      </c>
+      <c r="D700">
+        <v>34.0694</v>
+      </c>
+      <c r="E700">
+        <v>35.35</v>
+      </c>
+      <c r="F700">
+        <v>0.037588</v>
+      </c>
+      <c r="G700">
+        <v>3.76</v>
+      </c>
+      <c r="H700" t="s">
+        <v>35</v>
+      </c>
+      <c r="I700">
+        <v>48</v>
+      </c>
+      <c r="J700">
+        <v>1635.33</v>
+      </c>
+      <c r="K700">
+        <v>1696.8</v>
+      </c>
+      <c r="L700">
+        <v>61.47</v>
+      </c>
+      <c r="M700" t="s">
+        <v>24</v>
+      </c>
+      <c r="N700">
+        <v>48</v>
+      </c>
+      <c r="O700">
+        <v>1635.3312</v>
+      </c>
+      <c r="P700">
+        <v>1696.8</v>
+      </c>
+    </row>
+    <row r="701" spans="1:16">
+      <c r="A701" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B701" t="s">
+        <v>25</v>
+      </c>
+      <c r="C701" t="s">
+        <v>36</v>
+      </c>
+      <c r="D701">
+        <v>69.4158</v>
+      </c>
+      <c r="E701">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="F701">
+        <v>0.07338699999999999</v>
+      </c>
+      <c r="G701">
+        <v>7.34</v>
+      </c>
+      <c r="H701" t="s">
+        <v>36</v>
+      </c>
+      <c r="I701">
+        <v>62</v>
+      </c>
+      <c r="J701">
+        <v>4303.78</v>
+      </c>
+      <c r="K701">
+        <v>4619.62</v>
+      </c>
+      <c r="L701">
+        <v>315.84</v>
+      </c>
+      <c r="M701" t="s">
+        <v>25</v>
+      </c>
+      <c r="N701">
+        <v>62</v>
+      </c>
+      <c r="O701">
+        <v>4303.7796</v>
+      </c>
+      <c r="P701">
+        <v>4619.62</v>
+      </c>
+    </row>
+    <row r="702" spans="1:16">
+      <c r="A702" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B702" t="s">
+        <v>26</v>
+      </c>
+      <c r="C702" t="s">
+        <v>37</v>
+      </c>
+      <c r="D702">
+        <v>8.1868</v>
+      </c>
+      <c r="E702">
+        <v>8.925000000000001</v>
+      </c>
+      <c r="F702">
+        <v>0.09017</v>
+      </c>
+      <c r="G702">
+        <v>9.02</v>
+      </c>
+      <c r="H702" t="s">
+        <v>37</v>
+      </c>
+      <c r="I702">
+        <v>431</v>
+      </c>
+      <c r="J702">
+        <v>3528.51</v>
+      </c>
+      <c r="K702">
+        <v>3846.68</v>
+      </c>
+      <c r="L702">
+        <v>318.16</v>
+      </c>
+      <c r="M702" t="s">
+        <v>26</v>
+      </c>
+      <c r="N702">
+        <v>431</v>
+      </c>
+      <c r="O702">
+        <v>3528.5108</v>
+      </c>
+      <c r="P702">
+        <v>3846.675</v>
       </c>
     </row>
   </sheetData>
@@ -30484,7 +31106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -33104,6 +33726,47 @@
       </c>
       <c r="M64" s="2">
         <v>0.1422450247875535</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
+      <c r="A65" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0.074296</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0.073834</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.260419</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.267314</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0.049195</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0.552717</v>
+      </c>
+      <c r="H65" s="2">
+        <v>0.116823</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0.173731</v>
+      </c>
+      <c r="J65" s="2">
+        <v>0.037588</v>
+      </c>
+      <c r="K65" s="2">
+        <v>0.07338699999999999</v>
+      </c>
+      <c r="L65" s="2">
+        <v>0.09017</v>
+      </c>
+      <c r="M65" s="2">
+        <v>0.1492663932287723</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -631,7 +631,7 @@
                   <c:v>0.06590799999999999</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.074296</c:v>
+                  <c:v>0.076293</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1054,7 +1054,7 @@
                   <c:v>0.071564</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.073834</c:v>
+                  <c:v>0.072431</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1477,7 +1477,7 @@
                   <c:v>0.249967</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.260419</c:v>
+                  <c:v>0.253625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1900,7 +1900,7 @@
                   <c:v>0.247855</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.267314</c:v>
+                  <c:v>0.258427</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2320,7 +2320,7 @@
                   <c:v>0.050714</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.049195</c:v>
+                  <c:v>0.048436</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2743,7 +2743,7 @@
                   <c:v>0.530679</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.552717</c:v>
+                  <c:v>0.5464560000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3166,7 +3166,7 @@
                   <c:v>0.105529</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.116823</c:v>
+                  <c:v>0.112721</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3586,7 +3586,7 @@
                   <c:v>0.166253</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.173731</c:v>
+                  <c:v>0.171163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4009,7 +4009,7 @@
                   <c:v>0.033185</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.037588</c:v>
+                  <c:v>0.032598</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4429,7 +4429,7 @@
                   <c:v>0.07137</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.07338699999999999</c:v>
+                  <c:v>0.06920900000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4852,7 +4852,7 @@
                   <c:v>0.087604</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.09017</c:v>
+                  <c:v>0.084551</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5279,7 +5279,7 @@
                   <c:v>0.1422450247875535</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1492663932287723</c:v>
+                  <c:v>0.1452074997861479</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30563,13 +30563,13 @@
         <v>50.07</v>
       </c>
       <c r="E692">
-        <v>53.79</v>
+        <v>53.89</v>
       </c>
       <c r="F692">
-        <v>0.074296</v>
+        <v>0.076293</v>
       </c>
       <c r="G692">
-        <v>7.43</v>
+        <v>7.63</v>
       </c>
       <c r="H692" t="s">
         <v>27</v>
@@ -30581,10 +30581,10 @@
         <v>1151.61</v>
       </c>
       <c r="K692">
-        <v>1237.17</v>
+        <v>1239.47</v>
       </c>
       <c r="L692">
-        <v>85.56</v>
+        <v>87.86</v>
       </c>
       <c r="M692" t="s">
         <v>16</v>
@@ -30596,7 +30596,7 @@
         <v>1151.61</v>
       </c>
       <c r="P692">
-        <v>1237.17</v>
+        <v>1239.47</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -30613,13 +30613,13 @@
         <v>242.3</v>
       </c>
       <c r="E693">
-        <v>260.19</v>
+        <v>259.85</v>
       </c>
       <c r="F693">
-        <v>0.073834</v>
+        <v>0.072431</v>
       </c>
       <c r="G693">
-        <v>7.38</v>
+        <v>7.24</v>
       </c>
       <c r="H693" t="s">
         <v>28</v>
@@ -30631,10 +30631,10 @@
         <v>1211.5</v>
       </c>
       <c r="K693">
-        <v>1300.95</v>
+        <v>1299.25</v>
       </c>
       <c r="L693">
-        <v>89.45</v>
+        <v>87.75</v>
       </c>
       <c r="M693" t="s">
         <v>17</v>
@@ -30646,7 +30646,7 @@
         <v>1211.5</v>
       </c>
       <c r="P693">
-        <v>1300.95</v>
+        <v>1299.25</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -30663,13 +30663,13 @@
         <v>38.273</v>
       </c>
       <c r="E694">
-        <v>48.24</v>
+        <v>47.98</v>
       </c>
       <c r="F694">
-        <v>0.260419</v>
+        <v>0.253625</v>
       </c>
       <c r="G694">
-        <v>26.04</v>
+        <v>25.36</v>
       </c>
       <c r="H694" t="s">
         <v>29</v>
@@ -30681,10 +30681,10 @@
         <v>2066.74</v>
       </c>
       <c r="K694">
-        <v>2604.96</v>
+        <v>2590.92</v>
       </c>
       <c r="L694">
-        <v>538.22</v>
+        <v>524.1799999999999</v>
       </c>
       <c r="M694" t="s">
         <v>18</v>
@@ -30696,7 +30696,7 @@
         <v>2066.742</v>
       </c>
       <c r="P694">
-        <v>2604.96</v>
+        <v>2590.92</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -30713,13 +30713,13 @@
         <v>6.5264</v>
       </c>
       <c r="E695">
-        <v>8.271000000000001</v>
+        <v>8.212999999999999</v>
       </c>
       <c r="F695">
-        <v>0.267314</v>
+        <v>0.258427</v>
       </c>
       <c r="G695">
-        <v>26.73</v>
+        <v>25.84</v>
       </c>
       <c r="H695" t="s">
         <v>30</v>
@@ -30731,10 +30731,10 @@
         <v>1801.29</v>
       </c>
       <c r="K695">
-        <v>2282.8</v>
+        <v>2266.79</v>
       </c>
       <c r="L695">
-        <v>481.51</v>
+        <v>465.5</v>
       </c>
       <c r="M695" t="s">
         <v>19</v>
@@ -30746,7 +30746,7 @@
         <v>1801.2864</v>
       </c>
       <c r="P695">
-        <v>2282.796</v>
+        <v>2266.788</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -30763,13 +30763,13 @@
         <v>197.58</v>
       </c>
       <c r="E696">
-        <v>207.3</v>
+        <v>207.15</v>
       </c>
       <c r="F696">
-        <v>0.049195</v>
+        <v>0.048436</v>
       </c>
       <c r="G696">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="H696" t="s">
         <v>31</v>
@@ -30781,10 +30781,10 @@
         <v>790.3200000000001</v>
       </c>
       <c r="K696">
-        <v>829.2</v>
+        <v>828.6</v>
       </c>
       <c r="L696">
-        <v>38.88</v>
+        <v>38.28</v>
       </c>
       <c r="M696" t="s">
         <v>20</v>
@@ -30796,7 +30796,7 @@
         <v>790.3200000000001</v>
       </c>
       <c r="P696">
-        <v>829.2</v>
+        <v>828.6</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -30813,13 +30813,13 @@
         <v>79.86</v>
       </c>
       <c r="E697">
-        <v>124</v>
+        <v>123.5</v>
       </c>
       <c r="F697">
-        <v>0.552717</v>
+        <v>0.5464560000000001</v>
       </c>
       <c r="G697">
-        <v>55.27</v>
+        <v>54.65</v>
       </c>
       <c r="H697" t="s">
         <v>32</v>
@@ -30831,10 +30831,10 @@
         <v>958.3200000000001</v>
       </c>
       <c r="K697">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="L697">
-        <v>529.6799999999999</v>
+        <v>523.6799999999999</v>
       </c>
       <c r="M697" t="s">
         <v>21</v>
@@ -30846,7 +30846,7 @@
         <v>958.3199999999999</v>
       </c>
       <c r="P697">
-        <v>1488</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -30863,13 +30863,13 @@
         <v>19.7444</v>
       </c>
       <c r="E698">
-        <v>22.051</v>
+        <v>21.97</v>
       </c>
       <c r="F698">
-        <v>0.116823</v>
+        <v>0.112721</v>
       </c>
       <c r="G698">
-        <v>11.68</v>
+        <v>11.27</v>
       </c>
       <c r="H698" t="s">
         <v>33</v>
@@ -30881,10 +30881,10 @@
         <v>1204.41</v>
       </c>
       <c r="K698">
-        <v>1345.11</v>
+        <v>1340.17</v>
       </c>
       <c r="L698">
-        <v>140.7</v>
+        <v>135.76</v>
       </c>
       <c r="M698" t="s">
         <v>22</v>
@@ -30896,7 +30896,7 @@
         <v>1204.4084</v>
       </c>
       <c r="P698">
-        <v>1345.111</v>
+        <v>1340.17</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -30913,13 +30913,13 @@
         <v>132.3898</v>
       </c>
       <c r="E699">
-        <v>155.39</v>
+        <v>155.05</v>
       </c>
       <c r="F699">
-        <v>0.173731</v>
+        <v>0.171163</v>
       </c>
       <c r="G699">
-        <v>17.37</v>
+        <v>17.12</v>
       </c>
       <c r="H699" t="s">
         <v>34</v>
@@ -30931,10 +30931,10 @@
         <v>7546.22</v>
       </c>
       <c r="K699">
-        <v>8857.23</v>
+        <v>8837.85</v>
       </c>
       <c r="L699">
-        <v>1311.01</v>
+        <v>1291.63</v>
       </c>
       <c r="M699" t="s">
         <v>23</v>
@@ -30946,7 +30946,7 @@
         <v>7546.2186</v>
       </c>
       <c r="P699">
-        <v>8857.23</v>
+        <v>8837.85</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -30963,13 +30963,13 @@
         <v>34.0694</v>
       </c>
       <c r="E700">
-        <v>35.35</v>
+        <v>35.18</v>
       </c>
       <c r="F700">
-        <v>0.037588</v>
+        <v>0.032598</v>
       </c>
       <c r="G700">
-        <v>3.76</v>
+        <v>3.26</v>
       </c>
       <c r="H700" t="s">
         <v>35</v>
@@ -30981,10 +30981,10 @@
         <v>1635.33</v>
       </c>
       <c r="K700">
-        <v>1696.8</v>
+        <v>1688.64</v>
       </c>
       <c r="L700">
-        <v>61.47</v>
+        <v>53.31</v>
       </c>
       <c r="M700" t="s">
         <v>24</v>
@@ -30996,7 +30996,7 @@
         <v>1635.3312</v>
       </c>
       <c r="P700">
-        <v>1696.8</v>
+        <v>1688.64</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -31013,13 +31013,13 @@
         <v>69.4158</v>
       </c>
       <c r="E701">
-        <v>74.51000000000001</v>
+        <v>74.22</v>
       </c>
       <c r="F701">
-        <v>0.07338699999999999</v>
+        <v>0.06920900000000001</v>
       </c>
       <c r="G701">
-        <v>7.34</v>
+        <v>6.92</v>
       </c>
       <c r="H701" t="s">
         <v>36</v>
@@ -31031,10 +31031,10 @@
         <v>4303.78</v>
       </c>
       <c r="K701">
-        <v>4619.62</v>
+        <v>4601.64</v>
       </c>
       <c r="L701">
-        <v>315.84</v>
+        <v>297.86</v>
       </c>
       <c r="M701" t="s">
         <v>25</v>
@@ -31046,7 +31046,7 @@
         <v>4303.7796</v>
       </c>
       <c r="P701">
-        <v>4619.62</v>
+        <v>4601.64</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -31063,13 +31063,13 @@
         <v>8.1868</v>
       </c>
       <c r="E702">
-        <v>8.925000000000001</v>
+        <v>8.879</v>
       </c>
       <c r="F702">
-        <v>0.09017</v>
+        <v>0.084551</v>
       </c>
       <c r="G702">
-        <v>9.02</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="H702" t="s">
         <v>37</v>
@@ -31081,10 +31081,10 @@
         <v>3528.51</v>
       </c>
       <c r="K702">
-        <v>3846.68</v>
+        <v>3826.85</v>
       </c>
       <c r="L702">
-        <v>318.16</v>
+        <v>298.34</v>
       </c>
       <c r="M702" t="s">
         <v>26</v>
@@ -31096,7 +31096,7 @@
         <v>3528.5108</v>
       </c>
       <c r="P702">
-        <v>3846.675</v>
+        <v>3826.849</v>
       </c>
     </row>
   </sheetData>
@@ -33733,40 +33733,40 @@
         <v>46171</v>
       </c>
       <c r="B65" s="2">
-        <v>0.074296</v>
+        <v>0.076293</v>
       </c>
       <c r="C65" s="2">
-        <v>0.073834</v>
+        <v>0.072431</v>
       </c>
       <c r="D65" s="2">
-        <v>0.260419</v>
+        <v>0.253625</v>
       </c>
       <c r="E65" s="2">
-        <v>0.267314</v>
+        <v>0.258427</v>
       </c>
       <c r="F65" s="2">
-        <v>0.049195</v>
+        <v>0.048436</v>
       </c>
       <c r="G65" s="2">
-        <v>0.552717</v>
+        <v>0.5464560000000001</v>
       </c>
       <c r="H65" s="2">
-        <v>0.116823</v>
+        <v>0.112721</v>
       </c>
       <c r="I65" s="2">
-        <v>0.173731</v>
+        <v>0.171163</v>
       </c>
       <c r="J65" s="2">
-        <v>0.037588</v>
+        <v>0.032598</v>
       </c>
       <c r="K65" s="2">
-        <v>0.07338699999999999</v>
+        <v>0.06920900000000001</v>
       </c>
       <c r="L65" s="2">
-        <v>0.09017</v>
+        <v>0.084551</v>
       </c>
       <c r="M65" s="2">
-        <v>0.1492663932287723</v>
+        <v>0.1452074997861479</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -431,16 +431,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$65</c:f>
+              <c:f>grafico_dati!$B$2:$B$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -631,6 +634,9 @@
                   <c:v>0.06590799999999999</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.076293</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.076293</c:v>
                 </c:pt>
               </c:numCache>
@@ -659,10 +665,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -854,16 +860,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$65</c:f>
+              <c:f>grafico_dati!$C$2:$C$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1054,6 +1063,9 @@
                   <c:v>0.071564</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.072431</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.072431</c:v>
                 </c:pt>
               </c:numCache>
@@ -1082,10 +1094,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1277,16 +1289,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$65</c:f>
+              <c:f>grafico_dati!$D$2:$D$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1477,6 +1492,9 @@
                   <c:v>0.249967</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.253625</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.253625</c:v>
                 </c:pt>
               </c:numCache>
@@ -1505,10 +1523,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1700,16 +1718,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$65</c:f>
+              <c:f>grafico_dati!$E$2:$E$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1900,6 +1921,9 @@
                   <c:v>0.247855</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.258427</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.258427</c:v>
                 </c:pt>
               </c:numCache>
@@ -1928,10 +1952,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2123,16 +2147,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$65</c:f>
+              <c:f>grafico_dati!$F$2:$F$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2320,6 +2347,9 @@
                   <c:v>0.050714</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.048436</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.048436</c:v>
                 </c:pt>
               </c:numCache>
@@ -2348,10 +2378,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2543,16 +2573,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$65</c:f>
+              <c:f>grafico_dati!$G$2:$G$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2743,6 +2776,9 @@
                   <c:v>0.530679</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.5464560000000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.5464560000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -2771,10 +2807,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2966,16 +3002,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$65</c:f>
+              <c:f>grafico_dati!$H$2:$H$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3167,6 +3206,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>0.112721</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>206.782116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3194,10 +3236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3389,16 +3431,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$65</c:f>
+              <c:f>grafico_dati!$I$2:$I$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3586,6 +3631,9 @@
                   <c:v>0.166253</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.171163</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.171163</c:v>
                 </c:pt>
               </c:numCache>
@@ -3614,10 +3662,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3809,16 +3857,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$65</c:f>
+              <c:f>grafico_dati!$J$2:$J$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4009,6 +4060,9 @@
                   <c:v>0.033185</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.032598</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.032598</c:v>
                 </c:pt>
               </c:numCache>
@@ -4037,10 +4091,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4232,16 +4286,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$65</c:f>
+              <c:f>grafico_dati!$K$2:$K$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4429,6 +4486,9 @@
                   <c:v>0.07137</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.06920900000000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.06920900000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -4457,10 +4517,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4652,16 +4712,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$65</c:f>
+              <c:f>grafico_dati!$L$2:$L$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4852,6 +4915,9 @@
                   <c:v>0.087604</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>0.084551</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.084551</c:v>
                 </c:pt>
               </c:numCache>
@@ -4884,10 +4950,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$65</c:f>
+              <c:f>grafico_dati!$A$2:$A$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5079,16 +5145,19 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$65</c:f>
+              <c:f>grafico_dati!$M$2:$M$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5280,6 +5349,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>0.1452074997861479</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>9.646470904087549</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5686,7 +5758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P702"/>
+  <dimension ref="A1:P713"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -31096,6 +31168,556 @@
         <v>3528.5108</v>
       </c>
       <c r="P702">
+        <v>3826.849</v>
+      </c>
+    </row>
+    <row r="703" spans="1:16">
+      <c r="A703" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B703" t="s">
+        <v>16</v>
+      </c>
+      <c r="C703" t="s">
+        <v>27</v>
+      </c>
+      <c r="D703">
+        <v>50.07</v>
+      </c>
+      <c r="E703">
+        <v>53.89</v>
+      </c>
+      <c r="F703">
+        <v>0.076293</v>
+      </c>
+      <c r="G703">
+        <v>7.63</v>
+      </c>
+      <c r="H703" t="s">
+        <v>27</v>
+      </c>
+      <c r="I703">
+        <v>23</v>
+      </c>
+      <c r="J703">
+        <v>1151.61</v>
+      </c>
+      <c r="K703">
+        <v>1239.47</v>
+      </c>
+      <c r="L703">
+        <v>87.86</v>
+      </c>
+      <c r="M703" t="s">
+        <v>16</v>
+      </c>
+      <c r="N703">
+        <v>23</v>
+      </c>
+      <c r="O703">
+        <v>1151.61</v>
+      </c>
+      <c r="P703">
+        <v>1239.47</v>
+      </c>
+    </row>
+    <row r="704" spans="1:16">
+      <c r="A704" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B704" t="s">
+        <v>17</v>
+      </c>
+      <c r="C704" t="s">
+        <v>28</v>
+      </c>
+      <c r="D704">
+        <v>242.3</v>
+      </c>
+      <c r="E704">
+        <v>259.85</v>
+      </c>
+      <c r="F704">
+        <v>0.072431</v>
+      </c>
+      <c r="G704">
+        <v>7.24</v>
+      </c>
+      <c r="H704" t="s">
+        <v>28</v>
+      </c>
+      <c r="I704">
+        <v>5</v>
+      </c>
+      <c r="J704">
+        <v>1211.5</v>
+      </c>
+      <c r="K704">
+        <v>1299.25</v>
+      </c>
+      <c r="L704">
+        <v>87.75</v>
+      </c>
+      <c r="M704" t="s">
+        <v>17</v>
+      </c>
+      <c r="N704">
+        <v>5</v>
+      </c>
+      <c r="O704">
+        <v>1211.5</v>
+      </c>
+      <c r="P704">
+        <v>1299.25</v>
+      </c>
+    </row>
+    <row r="705" spans="1:16">
+      <c r="A705" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B705" t="s">
+        <v>18</v>
+      </c>
+      <c r="C705" t="s">
+        <v>29</v>
+      </c>
+      <c r="D705">
+        <v>38.273</v>
+      </c>
+      <c r="E705">
+        <v>47.98</v>
+      </c>
+      <c r="F705">
+        <v>0.253625</v>
+      </c>
+      <c r="G705">
+        <v>25.36</v>
+      </c>
+      <c r="H705" t="s">
+        <v>29</v>
+      </c>
+      <c r="I705">
+        <v>54</v>
+      </c>
+      <c r="J705">
+        <v>2066.74</v>
+      </c>
+      <c r="K705">
+        <v>2590.92</v>
+      </c>
+      <c r="L705">
+        <v>524.1799999999999</v>
+      </c>
+      <c r="M705" t="s">
+        <v>18</v>
+      </c>
+      <c r="N705">
+        <v>54</v>
+      </c>
+      <c r="O705">
+        <v>2066.742</v>
+      </c>
+      <c r="P705">
+        <v>2590.92</v>
+      </c>
+    </row>
+    <row r="706" spans="1:16">
+      <c r="A706" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B706" t="s">
+        <v>19</v>
+      </c>
+      <c r="C706" t="s">
+        <v>30</v>
+      </c>
+      <c r="D706">
+        <v>6.5264</v>
+      </c>
+      <c r="E706">
+        <v>8.212999999999999</v>
+      </c>
+      <c r="F706">
+        <v>0.258427</v>
+      </c>
+      <c r="G706">
+        <v>25.84</v>
+      </c>
+      <c r="H706" t="s">
+        <v>30</v>
+      </c>
+      <c r="I706">
+        <v>276</v>
+      </c>
+      <c r="J706">
+        <v>1801.29</v>
+      </c>
+      <c r="K706">
+        <v>2266.79</v>
+      </c>
+      <c r="L706">
+        <v>465.5</v>
+      </c>
+      <c r="M706" t="s">
+        <v>19</v>
+      </c>
+      <c r="N706">
+        <v>276</v>
+      </c>
+      <c r="O706">
+        <v>1801.2864</v>
+      </c>
+      <c r="P706">
+        <v>2266.788</v>
+      </c>
+    </row>
+    <row r="707" spans="1:16">
+      <c r="A707" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B707" t="s">
+        <v>20</v>
+      </c>
+      <c r="C707" t="s">
+        <v>31</v>
+      </c>
+      <c r="D707">
+        <v>197.58</v>
+      </c>
+      <c r="E707">
+        <v>207.15</v>
+      </c>
+      <c r="F707">
+        <v>0.048436</v>
+      </c>
+      <c r="G707">
+        <v>4.84</v>
+      </c>
+      <c r="H707" t="s">
+        <v>31</v>
+      </c>
+      <c r="I707">
+        <v>4</v>
+      </c>
+      <c r="J707">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K707">
+        <v>828.6</v>
+      </c>
+      <c r="L707">
+        <v>38.28</v>
+      </c>
+      <c r="M707" t="s">
+        <v>20</v>
+      </c>
+      <c r="N707">
+        <v>4</v>
+      </c>
+      <c r="O707">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P707">
+        <v>828.6</v>
+      </c>
+    </row>
+    <row r="708" spans="1:16">
+      <c r="A708" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B708" t="s">
+        <v>21</v>
+      </c>
+      <c r="C708" t="s">
+        <v>32</v>
+      </c>
+      <c r="D708">
+        <v>79.86</v>
+      </c>
+      <c r="E708">
+        <v>123.5</v>
+      </c>
+      <c r="F708">
+        <v>0.5464560000000001</v>
+      </c>
+      <c r="G708">
+        <v>54.65</v>
+      </c>
+      <c r="H708" t="s">
+        <v>32</v>
+      </c>
+      <c r="I708">
+        <v>12</v>
+      </c>
+      <c r="J708">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K708">
+        <v>1482</v>
+      </c>
+      <c r="L708">
+        <v>523.6799999999999</v>
+      </c>
+      <c r="M708" t="s">
+        <v>21</v>
+      </c>
+      <c r="N708">
+        <v>12</v>
+      </c>
+      <c r="O708">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P708">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="709" spans="1:16">
+      <c r="A709" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B709" t="s">
+        <v>22</v>
+      </c>
+      <c r="C709" t="s">
+        <v>33</v>
+      </c>
+      <c r="D709">
+        <v>19.7444</v>
+      </c>
+      <c r="E709">
+        <v>4102.5332</v>
+      </c>
+      <c r="F709">
+        <v>206.782116</v>
+      </c>
+      <c r="G709">
+        <v>20678.21</v>
+      </c>
+      <c r="H709" t="s">
+        <v>33</v>
+      </c>
+      <c r="I709">
+        <v>61</v>
+      </c>
+      <c r="J709">
+        <v>1204.41</v>
+      </c>
+      <c r="K709">
+        <v>250254.53</v>
+      </c>
+      <c r="L709">
+        <v>249050.12</v>
+      </c>
+      <c r="M709" t="s">
+        <v>22</v>
+      </c>
+      <c r="N709">
+        <v>61</v>
+      </c>
+      <c r="O709">
+        <v>1204.4084</v>
+      </c>
+      <c r="P709">
+        <v>250254.5252</v>
+      </c>
+    </row>
+    <row r="710" spans="1:16">
+      <c r="A710" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B710" t="s">
+        <v>23</v>
+      </c>
+      <c r="C710" t="s">
+        <v>34</v>
+      </c>
+      <c r="D710">
+        <v>132.3898</v>
+      </c>
+      <c r="E710">
+        <v>155.05</v>
+      </c>
+      <c r="F710">
+        <v>0.171163</v>
+      </c>
+      <c r="G710">
+        <v>17.12</v>
+      </c>
+      <c r="H710" t="s">
+        <v>34</v>
+      </c>
+      <c r="I710">
+        <v>57</v>
+      </c>
+      <c r="J710">
+        <v>7546.22</v>
+      </c>
+      <c r="K710">
+        <v>8837.85</v>
+      </c>
+      <c r="L710">
+        <v>1291.63</v>
+      </c>
+      <c r="M710" t="s">
+        <v>23</v>
+      </c>
+      <c r="N710">
+        <v>57</v>
+      </c>
+      <c r="O710">
+        <v>7546.2186</v>
+      </c>
+      <c r="P710">
+        <v>8837.85</v>
+      </c>
+    </row>
+    <row r="711" spans="1:16">
+      <c r="A711" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B711" t="s">
+        <v>24</v>
+      </c>
+      <c r="C711" t="s">
+        <v>35</v>
+      </c>
+      <c r="D711">
+        <v>34.0694</v>
+      </c>
+      <c r="E711">
+        <v>35.18</v>
+      </c>
+      <c r="F711">
+        <v>0.032598</v>
+      </c>
+      <c r="G711">
+        <v>3.26</v>
+      </c>
+      <c r="H711" t="s">
+        <v>35</v>
+      </c>
+      <c r="I711">
+        <v>48</v>
+      </c>
+      <c r="J711">
+        <v>1635.33</v>
+      </c>
+      <c r="K711">
+        <v>1688.64</v>
+      </c>
+      <c r="L711">
+        <v>53.31</v>
+      </c>
+      <c r="M711" t="s">
+        <v>24</v>
+      </c>
+      <c r="N711">
+        <v>48</v>
+      </c>
+      <c r="O711">
+        <v>1635.3312</v>
+      </c>
+      <c r="P711">
+        <v>1688.64</v>
+      </c>
+    </row>
+    <row r="712" spans="1:16">
+      <c r="A712" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B712" t="s">
+        <v>25</v>
+      </c>
+      <c r="C712" t="s">
+        <v>36</v>
+      </c>
+      <c r="D712">
+        <v>69.4158</v>
+      </c>
+      <c r="E712">
+        <v>74.22</v>
+      </c>
+      <c r="F712">
+        <v>0.06920900000000001</v>
+      </c>
+      <c r="G712">
+        <v>6.92</v>
+      </c>
+      <c r="H712" t="s">
+        <v>36</v>
+      </c>
+      <c r="I712">
+        <v>62</v>
+      </c>
+      <c r="J712">
+        <v>4303.78</v>
+      </c>
+      <c r="K712">
+        <v>4601.64</v>
+      </c>
+      <c r="L712">
+        <v>297.86</v>
+      </c>
+      <c r="M712" t="s">
+        <v>25</v>
+      </c>
+      <c r="N712">
+        <v>62</v>
+      </c>
+      <c r="O712">
+        <v>4303.7796</v>
+      </c>
+      <c r="P712">
+        <v>4601.64</v>
+      </c>
+    </row>
+    <row r="713" spans="1:16">
+      <c r="A713" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B713" t="s">
+        <v>26</v>
+      </c>
+      <c r="C713" t="s">
+        <v>37</v>
+      </c>
+      <c r="D713">
+        <v>8.1868</v>
+      </c>
+      <c r="E713">
+        <v>8.879</v>
+      </c>
+      <c r="F713">
+        <v>0.084551</v>
+      </c>
+      <c r="G713">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="H713" t="s">
+        <v>37</v>
+      </c>
+      <c r="I713">
+        <v>431</v>
+      </c>
+      <c r="J713">
+        <v>3528.51</v>
+      </c>
+      <c r="K713">
+        <v>3826.85</v>
+      </c>
+      <c r="L713">
+        <v>298.34</v>
+      </c>
+      <c r="M713" t="s">
+        <v>26</v>
+      </c>
+      <c r="N713">
+        <v>431</v>
+      </c>
+      <c r="O713">
+        <v>3528.5108</v>
+      </c>
+      <c r="P713">
         <v>3826.849</v>
       </c>
     </row>
@@ -31106,7 +31728,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -33767,6 +34389,47 @@
       </c>
       <c r="M65" s="2">
         <v>0.1452074997861479</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="A66" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.076293</v>
+      </c>
+      <c r="C66" s="2">
+        <v>0.072431</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.253625</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.258427</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.048436</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0.5464560000000001</v>
+      </c>
+      <c r="H66" s="2">
+        <v>206.782116</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0.171163</v>
+      </c>
+      <c r="J66" s="2">
+        <v>0.032598</v>
+      </c>
+      <c r="K66" s="2">
+        <v>0.06920900000000001</v>
+      </c>
+      <c r="L66" s="2">
+        <v>0.084551</v>
+      </c>
+      <c r="M66" s="2">
+        <v>9.646470904087549</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -434,16 +434,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$66</c:f>
+              <c:f>grafico_dati!$B$2:$B$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -638,6 +641,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.076293</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.084082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -665,10 +671,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -863,16 +869,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$66</c:f>
+              <c:f>grafico_dati!$C$2:$C$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1067,6 +1076,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.072431</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.086009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1094,10 +1106,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1292,16 +1304,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$66</c:f>
+              <c:f>grafico_dati!$D$2:$D$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1496,6 +1511,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.253625</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.292948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1523,10 +1541,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1721,16 +1739,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$66</c:f>
+              <c:f>grafico_dati!$E$2:$E$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1925,6 +1946,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.258427</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.297499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1952,10 +1976,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2150,16 +2174,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$66</c:f>
+              <c:f>grafico_dati!$F$2:$F$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2351,6 +2378,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.048436</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.048942</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2378,10 +2408,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2576,16 +2606,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$66</c:f>
+              <c:f>grafico_dati!$G$2:$G$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2780,6 +2813,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.5464560000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.566241</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2807,10 +2843,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3005,16 +3041,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$66</c:f>
+              <c:f>grafico_dati!$H$2:$H$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3209,6 +3248,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>206.782116</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.123053</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3236,10 +3278,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3434,16 +3476,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$66</c:f>
+              <c:f>grafico_dati!$I$2:$I$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3635,6 +3680,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.171163</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.179471</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3662,10 +3710,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3860,16 +3908,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$66</c:f>
+              <c:f>grafico_dati!$J$2:$J$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4064,6 +4115,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.032598</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.011905</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4091,10 +4145,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4289,16 +4343,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$66</c:f>
+              <c:f>grafico_dati!$K$2:$K$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4490,6 +4547,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.06920900000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.06992900000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4517,10 +4577,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4715,16 +4775,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$66</c:f>
+              <c:f>grafico_dati!$L$2:$L$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4919,6 +4982,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.084551</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.08919199999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4950,10 +5016,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$66</c:f>
+              <c:f>grafico_dati!$A$2:$A$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5148,16 +5214,19 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$66</c:f>
+              <c:f>grafico_dati!$M$2:$M$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5352,6 +5421,9 @@
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>9.646470904087549</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.155025491041749</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5758,7 +5830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P713"/>
+  <dimension ref="A1:P724"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -31719,6 +31791,556 @@
       </c>
       <c r="P713">
         <v>3826.849</v>
+      </c>
+    </row>
+    <row r="714" spans="1:16">
+      <c r="A714" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B714" t="s">
+        <v>16</v>
+      </c>
+      <c r="C714" t="s">
+        <v>27</v>
+      </c>
+      <c r="D714">
+        <v>50.07</v>
+      </c>
+      <c r="E714">
+        <v>54.28</v>
+      </c>
+      <c r="F714">
+        <v>0.084082</v>
+      </c>
+      <c r="G714">
+        <v>8.41</v>
+      </c>
+      <c r="H714" t="s">
+        <v>27</v>
+      </c>
+      <c r="I714">
+        <v>23</v>
+      </c>
+      <c r="J714">
+        <v>1151.61</v>
+      </c>
+      <c r="K714">
+        <v>1248.44</v>
+      </c>
+      <c r="L714">
+        <v>96.83</v>
+      </c>
+      <c r="M714" t="s">
+        <v>16</v>
+      </c>
+      <c r="N714">
+        <v>23</v>
+      </c>
+      <c r="O714">
+        <v>1151.61</v>
+      </c>
+      <c r="P714">
+        <v>1248.44</v>
+      </c>
+    </row>
+    <row r="715" spans="1:16">
+      <c r="A715" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B715" t="s">
+        <v>17</v>
+      </c>
+      <c r="C715" t="s">
+        <v>28</v>
+      </c>
+      <c r="D715">
+        <v>242.3</v>
+      </c>
+      <c r="E715">
+        <v>263.14</v>
+      </c>
+      <c r="F715">
+        <v>0.086009</v>
+      </c>
+      <c r="G715">
+        <v>8.6</v>
+      </c>
+      <c r="H715" t="s">
+        <v>28</v>
+      </c>
+      <c r="I715">
+        <v>5</v>
+      </c>
+      <c r="J715">
+        <v>1211.5</v>
+      </c>
+      <c r="K715">
+        <v>1315.7</v>
+      </c>
+      <c r="L715">
+        <v>104.2</v>
+      </c>
+      <c r="M715" t="s">
+        <v>17</v>
+      </c>
+      <c r="N715">
+        <v>5</v>
+      </c>
+      <c r="O715">
+        <v>1211.5</v>
+      </c>
+      <c r="P715">
+        <v>1315.7</v>
+      </c>
+    </row>
+    <row r="716" spans="1:16">
+      <c r="A716" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B716" t="s">
+        <v>18</v>
+      </c>
+      <c r="C716" t="s">
+        <v>29</v>
+      </c>
+      <c r="D716">
+        <v>38.273</v>
+      </c>
+      <c r="E716">
+        <v>49.485</v>
+      </c>
+      <c r="F716">
+        <v>0.292948</v>
+      </c>
+      <c r="G716">
+        <v>29.29</v>
+      </c>
+      <c r="H716" t="s">
+        <v>29</v>
+      </c>
+      <c r="I716">
+        <v>54</v>
+      </c>
+      <c r="J716">
+        <v>2066.74</v>
+      </c>
+      <c r="K716">
+        <v>2672.19</v>
+      </c>
+      <c r="L716">
+        <v>605.45</v>
+      </c>
+      <c r="M716" t="s">
+        <v>18</v>
+      </c>
+      <c r="N716">
+        <v>54</v>
+      </c>
+      <c r="O716">
+        <v>2066.742</v>
+      </c>
+      <c r="P716">
+        <v>2672.19</v>
+      </c>
+    </row>
+    <row r="717" spans="1:16">
+      <c r="A717" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B717" t="s">
+        <v>19</v>
+      </c>
+      <c r="C717" t="s">
+        <v>30</v>
+      </c>
+      <c r="D717">
+        <v>6.5264</v>
+      </c>
+      <c r="E717">
+        <v>8.468</v>
+      </c>
+      <c r="F717">
+        <v>0.297499</v>
+      </c>
+      <c r="G717">
+        <v>29.75</v>
+      </c>
+      <c r="H717" t="s">
+        <v>30</v>
+      </c>
+      <c r="I717">
+        <v>276</v>
+      </c>
+      <c r="J717">
+        <v>1801.29</v>
+      </c>
+      <c r="K717">
+        <v>2337.17</v>
+      </c>
+      <c r="L717">
+        <v>535.88</v>
+      </c>
+      <c r="M717" t="s">
+        <v>19</v>
+      </c>
+      <c r="N717">
+        <v>276</v>
+      </c>
+      <c r="O717">
+        <v>1801.2864</v>
+      </c>
+      <c r="P717">
+        <v>2337.168</v>
+      </c>
+    </row>
+    <row r="718" spans="1:16">
+      <c r="A718" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B718" t="s">
+        <v>20</v>
+      </c>
+      <c r="C718" t="s">
+        <v>31</v>
+      </c>
+      <c r="D718">
+        <v>197.58</v>
+      </c>
+      <c r="E718">
+        <v>207.25</v>
+      </c>
+      <c r="F718">
+        <v>0.048942</v>
+      </c>
+      <c r="G718">
+        <v>4.89</v>
+      </c>
+      <c r="H718" t="s">
+        <v>31</v>
+      </c>
+      <c r="I718">
+        <v>4</v>
+      </c>
+      <c r="J718">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K718">
+        <v>829</v>
+      </c>
+      <c r="L718">
+        <v>38.68</v>
+      </c>
+      <c r="M718" t="s">
+        <v>20</v>
+      </c>
+      <c r="N718">
+        <v>4</v>
+      </c>
+      <c r="O718">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P718">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="719" spans="1:16">
+      <c r="A719" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B719" t="s">
+        <v>21</v>
+      </c>
+      <c r="C719" t="s">
+        <v>32</v>
+      </c>
+      <c r="D719">
+        <v>79.86</v>
+      </c>
+      <c r="E719">
+        <v>125.08</v>
+      </c>
+      <c r="F719">
+        <v>0.566241</v>
+      </c>
+      <c r="G719">
+        <v>56.62</v>
+      </c>
+      <c r="H719" t="s">
+        <v>32</v>
+      </c>
+      <c r="I719">
+        <v>12</v>
+      </c>
+      <c r="J719">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K719">
+        <v>1500.96</v>
+      </c>
+      <c r="L719">
+        <v>542.64</v>
+      </c>
+      <c r="M719" t="s">
+        <v>21</v>
+      </c>
+      <c r="N719">
+        <v>12</v>
+      </c>
+      <c r="O719">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P719">
+        <v>1500.96</v>
+      </c>
+    </row>
+    <row r="720" spans="1:16">
+      <c r="A720" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B720" t="s">
+        <v>22</v>
+      </c>
+      <c r="C720" t="s">
+        <v>33</v>
+      </c>
+      <c r="D720">
+        <v>19.7444</v>
+      </c>
+      <c r="E720">
+        <v>22.174</v>
+      </c>
+      <c r="F720">
+        <v>0.123053</v>
+      </c>
+      <c r="G720">
+        <v>12.31</v>
+      </c>
+      <c r="H720" t="s">
+        <v>33</v>
+      </c>
+      <c r="I720">
+        <v>61</v>
+      </c>
+      <c r="J720">
+        <v>1204.41</v>
+      </c>
+      <c r="K720">
+        <v>1352.61</v>
+      </c>
+      <c r="L720">
+        <v>148.21</v>
+      </c>
+      <c r="M720" t="s">
+        <v>22</v>
+      </c>
+      <c r="N720">
+        <v>61</v>
+      </c>
+      <c r="O720">
+        <v>1204.4084</v>
+      </c>
+      <c r="P720">
+        <v>1352.614</v>
+      </c>
+    </row>
+    <row r="721" spans="1:16">
+      <c r="A721" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B721" t="s">
+        <v>23</v>
+      </c>
+      <c r="C721" t="s">
+        <v>34</v>
+      </c>
+      <c r="D721">
+        <v>132.3898</v>
+      </c>
+      <c r="E721">
+        <v>156.15</v>
+      </c>
+      <c r="F721">
+        <v>0.179471</v>
+      </c>
+      <c r="G721">
+        <v>17.95</v>
+      </c>
+      <c r="H721" t="s">
+        <v>34</v>
+      </c>
+      <c r="I721">
+        <v>57</v>
+      </c>
+      <c r="J721">
+        <v>7546.22</v>
+      </c>
+      <c r="K721">
+        <v>8900.549999999999</v>
+      </c>
+      <c r="L721">
+        <v>1354.33</v>
+      </c>
+      <c r="M721" t="s">
+        <v>23</v>
+      </c>
+      <c r="N721">
+        <v>57</v>
+      </c>
+      <c r="O721">
+        <v>7546.2186</v>
+      </c>
+      <c r="P721">
+        <v>8900.550000000001</v>
+      </c>
+    </row>
+    <row r="722" spans="1:16">
+      <c r="A722" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B722" t="s">
+        <v>24</v>
+      </c>
+      <c r="C722" t="s">
+        <v>35</v>
+      </c>
+      <c r="D722">
+        <v>34.0694</v>
+      </c>
+      <c r="E722">
+        <v>34.475</v>
+      </c>
+      <c r="F722">
+        <v>0.011905</v>
+      </c>
+      <c r="G722">
+        <v>1.19</v>
+      </c>
+      <c r="H722" t="s">
+        <v>35</v>
+      </c>
+      <c r="I722">
+        <v>48</v>
+      </c>
+      <c r="J722">
+        <v>1635.33</v>
+      </c>
+      <c r="K722">
+        <v>1654.8</v>
+      </c>
+      <c r="L722">
+        <v>19.47</v>
+      </c>
+      <c r="M722" t="s">
+        <v>24</v>
+      </c>
+      <c r="N722">
+        <v>48</v>
+      </c>
+      <c r="O722">
+        <v>1635.3312</v>
+      </c>
+      <c r="P722">
+        <v>1654.8</v>
+      </c>
+    </row>
+    <row r="723" spans="1:16">
+      <c r="A723" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B723" t="s">
+        <v>25</v>
+      </c>
+      <c r="C723" t="s">
+        <v>36</v>
+      </c>
+      <c r="D723">
+        <v>69.4158</v>
+      </c>
+      <c r="E723">
+        <v>74.27</v>
+      </c>
+      <c r="F723">
+        <v>0.06992900000000001</v>
+      </c>
+      <c r="G723">
+        <v>6.99</v>
+      </c>
+      <c r="H723" t="s">
+        <v>36</v>
+      </c>
+      <c r="I723">
+        <v>62</v>
+      </c>
+      <c r="J723">
+        <v>4303.78</v>
+      </c>
+      <c r="K723">
+        <v>4604.74</v>
+      </c>
+      <c r="L723">
+        <v>300.96</v>
+      </c>
+      <c r="M723" t="s">
+        <v>25</v>
+      </c>
+      <c r="N723">
+        <v>62</v>
+      </c>
+      <c r="O723">
+        <v>4303.7796</v>
+      </c>
+      <c r="P723">
+        <v>4604.74</v>
+      </c>
+    </row>
+    <row r="724" spans="1:16">
+      <c r="A724" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B724" t="s">
+        <v>26</v>
+      </c>
+      <c r="C724" t="s">
+        <v>37</v>
+      </c>
+      <c r="D724">
+        <v>8.1868</v>
+      </c>
+      <c r="E724">
+        <v>8.917</v>
+      </c>
+      <c r="F724">
+        <v>0.08919199999999999</v>
+      </c>
+      <c r="G724">
+        <v>8.92</v>
+      </c>
+      <c r="H724" t="s">
+        <v>37</v>
+      </c>
+      <c r="I724">
+        <v>431</v>
+      </c>
+      <c r="J724">
+        <v>3528.51</v>
+      </c>
+      <c r="K724">
+        <v>3843.23</v>
+      </c>
+      <c r="L724">
+        <v>314.72</v>
+      </c>
+      <c r="M724" t="s">
+        <v>26</v>
+      </c>
+      <c r="N724">
+        <v>431</v>
+      </c>
+      <c r="O724">
+        <v>3528.5108</v>
+      </c>
+      <c r="P724">
+        <v>3843.227</v>
       </c>
     </row>
   </sheetData>
@@ -31728,7 +32350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -34430,6 +35052,47 @@
       </c>
       <c r="M66" s="2">
         <v>9.646470904087549</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
+      <c r="A67" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.084082</v>
+      </c>
+      <c r="C67" s="2">
+        <v>0.086009</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.292948</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.297499</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0.048942</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0.566241</v>
+      </c>
+      <c r="H67" s="2">
+        <v>0.123053</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0.179471</v>
+      </c>
+      <c r="J67" s="2">
+        <v>0.011905</v>
+      </c>
+      <c r="K67" s="2">
+        <v>0.06992900000000001</v>
+      </c>
+      <c r="L67" s="2">
+        <v>0.08919199999999999</v>
+      </c>
+      <c r="M67" s="2">
+        <v>0.155025491041749</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -640,7 +640,7 @@
                   <c:v>0.076293</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.076293</c:v>
+                  <c:v>0.072898</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.084082</c:v>
@@ -1075,7 +1075,7 @@
                   <c:v>0.072431</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.072431</c:v>
+                  <c:v>0.076682</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.086009</c:v>
@@ -1510,7 +1510,7 @@
                   <c:v>0.253625</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.253625</c:v>
+                  <c:v>0.2791</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.292948</c:v>
@@ -1945,7 +1945,7 @@
                   <c:v>0.258427</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.258427</c:v>
+                  <c:v>0.290298</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.297499</c:v>
@@ -2377,7 +2377,7 @@
                   <c:v>0.048436</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.048436</c:v>
+                  <c:v>0.044134</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.048942</c:v>
@@ -2812,7 +2812,7 @@
                   <c:v>0.5464560000000001</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.5464560000000001</c:v>
+                  <c:v>0.538192</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.566241</c:v>
@@ -3247,7 +3247,7 @@
                   <c:v>0.112721</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>206.782116</c:v>
+                  <c:v>0.115962</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.123053</c:v>
@@ -3679,7 +3679,7 @@
                   <c:v>0.171163</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.171163</c:v>
+                  <c:v>0.174184</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.179471</c:v>
@@ -4114,7 +4114,7 @@
                   <c:v>0.032598</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.032598</c:v>
+                  <c:v>0.014253</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.011905</c:v>
@@ -4546,7 +4546,7 @@
                   <c:v>0.06920900000000001</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.06920900000000001</c:v>
+                  <c:v>0.067048</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.06992900000000001</c:v>
@@ -4981,7 +4981,7 @@
                   <c:v>0.084551</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.084551</c:v>
+                  <c:v>0.086383</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.08919199999999999</c:v>
@@ -5420,7 +5420,7 @@
                   <c:v>0.1452074997861479</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>9.646470904087549</c:v>
+                  <c:v>0.1487897161110643</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.155025491041749</c:v>
@@ -31257,13 +31257,13 @@
         <v>50.07</v>
       </c>
       <c r="E703">
-        <v>53.89</v>
+        <v>53.72</v>
       </c>
       <c r="F703">
-        <v>0.076293</v>
+        <v>0.072898</v>
       </c>
       <c r="G703">
-        <v>7.63</v>
+        <v>7.29</v>
       </c>
       <c r="H703" t="s">
         <v>27</v>
@@ -31275,10 +31275,10 @@
         <v>1151.61</v>
       </c>
       <c r="K703">
-        <v>1239.47</v>
+        <v>1235.56</v>
       </c>
       <c r="L703">
-        <v>87.86</v>
+        <v>83.95</v>
       </c>
       <c r="M703" t="s">
         <v>16</v>
@@ -31290,7 +31290,7 @@
         <v>1151.61</v>
       </c>
       <c r="P703">
-        <v>1239.47</v>
+        <v>1235.56</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -31307,13 +31307,13 @@
         <v>242.3</v>
       </c>
       <c r="E704">
-        <v>259.85</v>
+        <v>260.88</v>
       </c>
       <c r="F704">
-        <v>0.072431</v>
+        <v>0.076682</v>
       </c>
       <c r="G704">
-        <v>7.24</v>
+        <v>7.67</v>
       </c>
       <c r="H704" t="s">
         <v>28</v>
@@ -31325,10 +31325,10 @@
         <v>1211.5</v>
       </c>
       <c r="K704">
-        <v>1299.25</v>
+        <v>1304.4</v>
       </c>
       <c r="L704">
-        <v>87.75</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M704" t="s">
         <v>17</v>
@@ -31340,7 +31340,7 @@
         <v>1211.5</v>
       </c>
       <c r="P704">
-        <v>1299.25</v>
+        <v>1304.4</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -31357,13 +31357,13 @@
         <v>38.273</v>
       </c>
       <c r="E705">
-        <v>47.98</v>
+        <v>48.955</v>
       </c>
       <c r="F705">
-        <v>0.253625</v>
+        <v>0.2791</v>
       </c>
       <c r="G705">
-        <v>25.36</v>
+        <v>27.91</v>
       </c>
       <c r="H705" t="s">
         <v>29</v>
@@ -31375,10 +31375,10 @@
         <v>2066.74</v>
       </c>
       <c r="K705">
-        <v>2590.92</v>
+        <v>2643.57</v>
       </c>
       <c r="L705">
-        <v>524.1799999999999</v>
+        <v>576.83</v>
       </c>
       <c r="M705" t="s">
         <v>18</v>
@@ -31390,7 +31390,7 @@
         <v>2066.742</v>
       </c>
       <c r="P705">
-        <v>2590.92</v>
+        <v>2643.57</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -31407,13 +31407,13 @@
         <v>6.5264</v>
       </c>
       <c r="E706">
-        <v>8.212999999999999</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="F706">
-        <v>0.258427</v>
+        <v>0.290298</v>
       </c>
       <c r="G706">
-        <v>25.84</v>
+        <v>29.03</v>
       </c>
       <c r="H706" t="s">
         <v>30</v>
@@ -31425,10 +31425,10 @@
         <v>1801.29</v>
       </c>
       <c r="K706">
-        <v>2266.79</v>
+        <v>2324.2</v>
       </c>
       <c r="L706">
-        <v>465.5</v>
+        <v>522.91</v>
       </c>
       <c r="M706" t="s">
         <v>19</v>
@@ -31440,7 +31440,7 @@
         <v>1801.2864</v>
       </c>
       <c r="P706">
-        <v>2266.788</v>
+        <v>2324.196</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -31457,13 +31457,13 @@
         <v>197.58</v>
       </c>
       <c r="E707">
-        <v>207.15</v>
+        <v>206.3</v>
       </c>
       <c r="F707">
-        <v>0.048436</v>
+        <v>0.044134</v>
       </c>
       <c r="G707">
-        <v>4.84</v>
+        <v>4.41</v>
       </c>
       <c r="H707" t="s">
         <v>31</v>
@@ -31475,10 +31475,10 @@
         <v>790.3200000000001</v>
       </c>
       <c r="K707">
-        <v>828.6</v>
+        <v>825.2</v>
       </c>
       <c r="L707">
-        <v>38.28</v>
+        <v>34.88</v>
       </c>
       <c r="M707" t="s">
         <v>20</v>
@@ -31490,7 +31490,7 @@
         <v>790.3200000000001</v>
       </c>
       <c r="P707">
-        <v>828.6</v>
+        <v>825.2</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -31507,13 +31507,13 @@
         <v>79.86</v>
       </c>
       <c r="E708">
-        <v>123.5</v>
+        <v>122.84</v>
       </c>
       <c r="F708">
-        <v>0.5464560000000001</v>
+        <v>0.538192</v>
       </c>
       <c r="G708">
-        <v>54.65</v>
+        <v>53.82</v>
       </c>
       <c r="H708" t="s">
         <v>32</v>
@@ -31525,10 +31525,10 @@
         <v>958.3200000000001</v>
       </c>
       <c r="K708">
-        <v>1482</v>
+        <v>1474.08</v>
       </c>
       <c r="L708">
-        <v>523.6799999999999</v>
+        <v>515.76</v>
       </c>
       <c r="M708" t="s">
         <v>21</v>
@@ -31540,7 +31540,7 @@
         <v>958.3199999999999</v>
       </c>
       <c r="P708">
-        <v>1482</v>
+        <v>1474.08</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -31557,13 +31557,13 @@
         <v>19.7444</v>
       </c>
       <c r="E709">
-        <v>4102.5332</v>
+        <v>22.034</v>
       </c>
       <c r="F709">
-        <v>206.782116</v>
+        <v>0.115962</v>
       </c>
       <c r="G709">
-        <v>20678.21</v>
+        <v>11.6</v>
       </c>
       <c r="H709" t="s">
         <v>33</v>
@@ -31575,10 +31575,10 @@
         <v>1204.41</v>
       </c>
       <c r="K709">
-        <v>250254.53</v>
+        <v>1344.07</v>
       </c>
       <c r="L709">
-        <v>249050.12</v>
+        <v>139.67</v>
       </c>
       <c r="M709" t="s">
         <v>22</v>
@@ -31590,7 +31590,7 @@
         <v>1204.4084</v>
       </c>
       <c r="P709">
-        <v>250254.5252</v>
+        <v>1344.074</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -31607,13 +31607,13 @@
         <v>132.3898</v>
       </c>
       <c r="E710">
-        <v>155.05</v>
+        <v>155.45</v>
       </c>
       <c r="F710">
-        <v>0.171163</v>
+        <v>0.174184</v>
       </c>
       <c r="G710">
-        <v>17.12</v>
+        <v>17.42</v>
       </c>
       <c r="H710" t="s">
         <v>34</v>
@@ -31625,10 +31625,10 @@
         <v>7546.22</v>
       </c>
       <c r="K710">
-        <v>8837.85</v>
+        <v>8860.65</v>
       </c>
       <c r="L710">
-        <v>1291.63</v>
+        <v>1314.43</v>
       </c>
       <c r="M710" t="s">
         <v>23</v>
@@ -31640,7 +31640,7 @@
         <v>7546.2186</v>
       </c>
       <c r="P710">
-        <v>8837.85</v>
+        <v>8860.65</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -31657,13 +31657,13 @@
         <v>34.0694</v>
       </c>
       <c r="E711">
-        <v>35.18</v>
+        <v>34.555</v>
       </c>
       <c r="F711">
-        <v>0.032598</v>
+        <v>0.014253</v>
       </c>
       <c r="G711">
-        <v>3.26</v>
+        <v>1.43</v>
       </c>
       <c r="H711" t="s">
         <v>35</v>
@@ -31675,10 +31675,10 @@
         <v>1635.33</v>
       </c>
       <c r="K711">
-        <v>1688.64</v>
+        <v>1658.64</v>
       </c>
       <c r="L711">
-        <v>53.31</v>
+        <v>23.31</v>
       </c>
       <c r="M711" t="s">
         <v>24</v>
@@ -31690,7 +31690,7 @@
         <v>1635.3312</v>
       </c>
       <c r="P711">
-        <v>1688.64</v>
+        <v>1658.64</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -31707,13 +31707,13 @@
         <v>69.4158</v>
       </c>
       <c r="E712">
-        <v>74.22</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="F712">
-        <v>0.06920900000000001</v>
+        <v>0.067048</v>
       </c>
       <c r="G712">
-        <v>6.92</v>
+        <v>6.7</v>
       </c>
       <c r="H712" t="s">
         <v>36</v>
@@ -31725,10 +31725,10 @@
         <v>4303.78</v>
       </c>
       <c r="K712">
-        <v>4601.64</v>
+        <v>4592.34</v>
       </c>
       <c r="L712">
-        <v>297.86</v>
+        <v>288.56</v>
       </c>
       <c r="M712" t="s">
         <v>25</v>
@@ -31740,7 +31740,7 @@
         <v>4303.7796</v>
       </c>
       <c r="P712">
-        <v>4601.64</v>
+        <v>4592.339999999999</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -31757,13 +31757,13 @@
         <v>8.1868</v>
       </c>
       <c r="E713">
-        <v>8.879</v>
+        <v>8.894</v>
       </c>
       <c r="F713">
-        <v>0.084551</v>
+        <v>0.086383</v>
       </c>
       <c r="G713">
-        <v>8.460000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H713" t="s">
         <v>37</v>
@@ -31775,10 +31775,10 @@
         <v>3528.51</v>
       </c>
       <c r="K713">
-        <v>3826.85</v>
+        <v>3833.31</v>
       </c>
       <c r="L713">
-        <v>298.34</v>
+        <v>304.8</v>
       </c>
       <c r="M713" t="s">
         <v>26</v>
@@ -31790,7 +31790,7 @@
         <v>3528.5108</v>
       </c>
       <c r="P713">
-        <v>3826.849</v>
+        <v>3833.314</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -35018,40 +35018,40 @@
         <v>46174</v>
       </c>
       <c r="B66" s="2">
-        <v>0.076293</v>
+        <v>0.072898</v>
       </c>
       <c r="C66" s="2">
-        <v>0.072431</v>
+        <v>0.076682</v>
       </c>
       <c r="D66" s="2">
-        <v>0.253625</v>
+        <v>0.2791</v>
       </c>
       <c r="E66" s="2">
-        <v>0.258427</v>
+        <v>0.290298</v>
       </c>
       <c r="F66" s="2">
-        <v>0.048436</v>
+        <v>0.044134</v>
       </c>
       <c r="G66" s="2">
-        <v>0.5464560000000001</v>
+        <v>0.538192</v>
       </c>
       <c r="H66" s="2">
-        <v>206.782116</v>
+        <v>0.115962</v>
       </c>
       <c r="I66" s="2">
-        <v>0.171163</v>
+        <v>0.174184</v>
       </c>
       <c r="J66" s="2">
-        <v>0.032598</v>
+        <v>0.014253</v>
       </c>
       <c r="K66" s="2">
-        <v>0.06920900000000001</v>
+        <v>0.067048</v>
       </c>
       <c r="L66" s="2">
-        <v>0.084551</v>
+        <v>0.086383</v>
       </c>
       <c r="M66" s="2">
-        <v>9.646470904087549</v>
+        <v>0.1487897161110643</v>
       </c>
     </row>
     <row r="67" spans="1:13">

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2319" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -437,16 +437,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$67</c:f>
+              <c:f>grafico_dati!$B$2:$B$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -644,6 +647,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.084082</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.069103</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -671,10 +677,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -872,16 +878,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$67</c:f>
+              <c:f>grafico_dati!$C$2:$C$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1079,6 +1088,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.086009</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.08799</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1106,10 +1118,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1307,16 +1319,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$67</c:f>
+              <c:f>grafico_dati!$D$2:$D$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1514,6 +1529,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.292948</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.26068</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1541,10 +1559,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1742,16 +1760,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$67</c:f>
+              <c:f>grafico_dati!$E$2:$E$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1949,6 +1970,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.297499</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.265169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1976,10 +2000,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2177,16 +2201,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$67</c:f>
+              <c:f>grafico_dati!$F$2:$F$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2381,6 +2408,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.048942</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.04135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2408,10 +2438,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2609,16 +2639,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$67</c:f>
+              <c:f>grafico_dati!$G$2:$G$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2816,6 +2849,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.566241</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.549712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2843,10 +2879,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3044,16 +3080,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$67</c:f>
+              <c:f>grafico_dati!$H$2:$H$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3251,6 +3290,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.123053</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.126547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3278,10 +3320,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3479,16 +3521,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$67</c:f>
+              <c:f>grafico_dati!$I$2:$I$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3683,6 +3728,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.179471</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.175393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3710,10 +3758,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3911,16 +3959,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$67</c:f>
+              <c:f>grafico_dati!$J$2:$J$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4118,6 +4169,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.011905</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.013813</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4145,10 +4199,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4346,16 +4400,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$67</c:f>
+              <c:f>grafico_dati!$K$2:$K$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4550,6 +4607,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.06992900000000001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.077708</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4577,10 +4637,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4778,16 +4838,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$67</c:f>
+              <c:f>grafico_dati!$L$2:$L$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -4985,6 +5048,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.08919199999999999</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.09114700000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5016,10 +5082,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$67</c:f>
+              <c:f>grafico_dati!$A$2:$A$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5217,16 +5283,19 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$67</c:f>
+              <c:f>grafico_dati!$M$2:$M$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5424,6 +5493,9 @@
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>0.155025491041749</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.1495025178804494</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5830,7 +5902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P724"/>
+  <dimension ref="A1:P735"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -32341,6 +32413,556 @@
       </c>
       <c r="P724">
         <v>3843.227</v>
+      </c>
+    </row>
+    <row r="725" spans="1:16">
+      <c r="A725" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B725" t="s">
+        <v>16</v>
+      </c>
+      <c r="C725" t="s">
+        <v>27</v>
+      </c>
+      <c r="D725">
+        <v>50.07</v>
+      </c>
+      <c r="E725">
+        <v>53.53</v>
+      </c>
+      <c r="F725">
+        <v>0.069103</v>
+      </c>
+      <c r="G725">
+        <v>6.91</v>
+      </c>
+      <c r="H725" t="s">
+        <v>27</v>
+      </c>
+      <c r="I725">
+        <v>23</v>
+      </c>
+      <c r="J725">
+        <v>1151.61</v>
+      </c>
+      <c r="K725">
+        <v>1231.19</v>
+      </c>
+      <c r="L725">
+        <v>79.58</v>
+      </c>
+      <c r="M725" t="s">
+        <v>16</v>
+      </c>
+      <c r="N725">
+        <v>23</v>
+      </c>
+      <c r="O725">
+        <v>1151.61</v>
+      </c>
+      <c r="P725">
+        <v>1231.19</v>
+      </c>
+    </row>
+    <row r="726" spans="1:16">
+      <c r="A726" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B726" t="s">
+        <v>17</v>
+      </c>
+      <c r="C726" t="s">
+        <v>28</v>
+      </c>
+      <c r="D726">
+        <v>242.3</v>
+      </c>
+      <c r="E726">
+        <v>263.62</v>
+      </c>
+      <c r="F726">
+        <v>0.08799</v>
+      </c>
+      <c r="G726">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H726" t="s">
+        <v>28</v>
+      </c>
+      <c r="I726">
+        <v>5</v>
+      </c>
+      <c r="J726">
+        <v>1211.5</v>
+      </c>
+      <c r="K726">
+        <v>1318.1</v>
+      </c>
+      <c r="L726">
+        <v>106.6</v>
+      </c>
+      <c r="M726" t="s">
+        <v>17</v>
+      </c>
+      <c r="N726">
+        <v>5</v>
+      </c>
+      <c r="O726">
+        <v>1211.5</v>
+      </c>
+      <c r="P726">
+        <v>1318.1</v>
+      </c>
+    </row>
+    <row r="727" spans="1:16">
+      <c r="A727" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B727" t="s">
+        <v>18</v>
+      </c>
+      <c r="C727" t="s">
+        <v>29</v>
+      </c>
+      <c r="D727">
+        <v>38.273</v>
+      </c>
+      <c r="E727">
+        <v>48.25</v>
+      </c>
+      <c r="F727">
+        <v>0.26068</v>
+      </c>
+      <c r="G727">
+        <v>26.07</v>
+      </c>
+      <c r="H727" t="s">
+        <v>29</v>
+      </c>
+      <c r="I727">
+        <v>54</v>
+      </c>
+      <c r="J727">
+        <v>2066.74</v>
+      </c>
+      <c r="K727">
+        <v>2605.5</v>
+      </c>
+      <c r="L727">
+        <v>538.76</v>
+      </c>
+      <c r="M727" t="s">
+        <v>18</v>
+      </c>
+      <c r="N727">
+        <v>54</v>
+      </c>
+      <c r="O727">
+        <v>2066.742</v>
+      </c>
+      <c r="P727">
+        <v>2605.5</v>
+      </c>
+    </row>
+    <row r="728" spans="1:16">
+      <c r="A728" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B728" t="s">
+        <v>19</v>
+      </c>
+      <c r="C728" t="s">
+        <v>30</v>
+      </c>
+      <c r="D728">
+        <v>6.5264</v>
+      </c>
+      <c r="E728">
+        <v>8.257</v>
+      </c>
+      <c r="F728">
+        <v>0.265169</v>
+      </c>
+      <c r="G728">
+        <v>26.52</v>
+      </c>
+      <c r="H728" t="s">
+        <v>30</v>
+      </c>
+      <c r="I728">
+        <v>276</v>
+      </c>
+      <c r="J728">
+        <v>1801.29</v>
+      </c>
+      <c r="K728">
+        <v>2278.93</v>
+      </c>
+      <c r="L728">
+        <v>477.65</v>
+      </c>
+      <c r="M728" t="s">
+        <v>19</v>
+      </c>
+      <c r="N728">
+        <v>276</v>
+      </c>
+      <c r="O728">
+        <v>1801.2864</v>
+      </c>
+      <c r="P728">
+        <v>2278.932</v>
+      </c>
+    </row>
+    <row r="729" spans="1:16">
+      <c r="A729" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B729" t="s">
+        <v>20</v>
+      </c>
+      <c r="C729" t="s">
+        <v>31</v>
+      </c>
+      <c r="D729">
+        <v>197.58</v>
+      </c>
+      <c r="E729">
+        <v>205.75</v>
+      </c>
+      <c r="F729">
+        <v>0.04135</v>
+      </c>
+      <c r="G729">
+        <v>4.14</v>
+      </c>
+      <c r="H729" t="s">
+        <v>31</v>
+      </c>
+      <c r="I729">
+        <v>4</v>
+      </c>
+      <c r="J729">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K729">
+        <v>823</v>
+      </c>
+      <c r="L729">
+        <v>32.68</v>
+      </c>
+      <c r="M729" t="s">
+        <v>20</v>
+      </c>
+      <c r="N729">
+        <v>4</v>
+      </c>
+      <c r="O729">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P729">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="730" spans="1:16">
+      <c r="A730" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B730" t="s">
+        <v>21</v>
+      </c>
+      <c r="C730" t="s">
+        <v>32</v>
+      </c>
+      <c r="D730">
+        <v>79.86</v>
+      </c>
+      <c r="E730">
+        <v>123.76</v>
+      </c>
+      <c r="F730">
+        <v>0.549712</v>
+      </c>
+      <c r="G730">
+        <v>54.97</v>
+      </c>
+      <c r="H730" t="s">
+        <v>32</v>
+      </c>
+      <c r="I730">
+        <v>12</v>
+      </c>
+      <c r="J730">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K730">
+        <v>1485.12</v>
+      </c>
+      <c r="L730">
+        <v>526.8</v>
+      </c>
+      <c r="M730" t="s">
+        <v>21</v>
+      </c>
+      <c r="N730">
+        <v>12</v>
+      </c>
+      <c r="O730">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P730">
+        <v>1485.12</v>
+      </c>
+    </row>
+    <row r="731" spans="1:16">
+      <c r="A731" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B731" t="s">
+        <v>22</v>
+      </c>
+      <c r="C731" t="s">
+        <v>33</v>
+      </c>
+      <c r="D731">
+        <v>19.7444</v>
+      </c>
+      <c r="E731">
+        <v>22.243</v>
+      </c>
+      <c r="F731">
+        <v>0.126547</v>
+      </c>
+      <c r="G731">
+        <v>12.65</v>
+      </c>
+      <c r="H731" t="s">
+        <v>33</v>
+      </c>
+      <c r="I731">
+        <v>61</v>
+      </c>
+      <c r="J731">
+        <v>1204.41</v>
+      </c>
+      <c r="K731">
+        <v>1356.82</v>
+      </c>
+      <c r="L731">
+        <v>152.41</v>
+      </c>
+      <c r="M731" t="s">
+        <v>22</v>
+      </c>
+      <c r="N731">
+        <v>61</v>
+      </c>
+      <c r="O731">
+        <v>1204.4084</v>
+      </c>
+      <c r="P731">
+        <v>1356.823</v>
+      </c>
+    </row>
+    <row r="732" spans="1:16">
+      <c r="A732" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B732" t="s">
+        <v>23</v>
+      </c>
+      <c r="C732" t="s">
+        <v>34</v>
+      </c>
+      <c r="D732">
+        <v>132.3898</v>
+      </c>
+      <c r="E732">
+        <v>155.61</v>
+      </c>
+      <c r="F732">
+        <v>0.175393</v>
+      </c>
+      <c r="G732">
+        <v>17.54</v>
+      </c>
+      <c r="H732" t="s">
+        <v>34</v>
+      </c>
+      <c r="I732">
+        <v>57</v>
+      </c>
+      <c r="J732">
+        <v>7546.22</v>
+      </c>
+      <c r="K732">
+        <v>8869.77</v>
+      </c>
+      <c r="L732">
+        <v>1323.55</v>
+      </c>
+      <c r="M732" t="s">
+        <v>23</v>
+      </c>
+      <c r="N732">
+        <v>57</v>
+      </c>
+      <c r="O732">
+        <v>7546.2186</v>
+      </c>
+      <c r="P732">
+        <v>8869.77</v>
+      </c>
+    </row>
+    <row r="733" spans="1:16">
+      <c r="A733" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B733" t="s">
+        <v>24</v>
+      </c>
+      <c r="C733" t="s">
+        <v>35</v>
+      </c>
+      <c r="D733">
+        <v>34.0694</v>
+      </c>
+      <c r="E733">
+        <v>34.54</v>
+      </c>
+      <c r="F733">
+        <v>0.013813</v>
+      </c>
+      <c r="G733">
+        <v>1.38</v>
+      </c>
+      <c r="H733" t="s">
+        <v>35</v>
+      </c>
+      <c r="I733">
+        <v>48</v>
+      </c>
+      <c r="J733">
+        <v>1635.33</v>
+      </c>
+      <c r="K733">
+        <v>1657.92</v>
+      </c>
+      <c r="L733">
+        <v>22.59</v>
+      </c>
+      <c r="M733" t="s">
+        <v>24</v>
+      </c>
+      <c r="N733">
+        <v>48</v>
+      </c>
+      <c r="O733">
+        <v>1635.3312</v>
+      </c>
+      <c r="P733">
+        <v>1657.92</v>
+      </c>
+    </row>
+    <row r="734" spans="1:16">
+      <c r="A734" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B734" t="s">
+        <v>25</v>
+      </c>
+      <c r="C734" t="s">
+        <v>36</v>
+      </c>
+      <c r="D734">
+        <v>69.4158</v>
+      </c>
+      <c r="E734">
+        <v>74.81</v>
+      </c>
+      <c r="F734">
+        <v>0.077708</v>
+      </c>
+      <c r="G734">
+        <v>7.77</v>
+      </c>
+      <c r="H734" t="s">
+        <v>36</v>
+      </c>
+      <c r="I734">
+        <v>62</v>
+      </c>
+      <c r="J734">
+        <v>4303.78</v>
+      </c>
+      <c r="K734">
+        <v>4638.22</v>
+      </c>
+      <c r="L734">
+        <v>334.44</v>
+      </c>
+      <c r="M734" t="s">
+        <v>25</v>
+      </c>
+      <c r="N734">
+        <v>62</v>
+      </c>
+      <c r="O734">
+        <v>4303.7796</v>
+      </c>
+      <c r="P734">
+        <v>4638.22</v>
+      </c>
+    </row>
+    <row r="735" spans="1:16">
+      <c r="A735" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B735" t="s">
+        <v>26</v>
+      </c>
+      <c r="C735" t="s">
+        <v>37</v>
+      </c>
+      <c r="D735">
+        <v>8.1868</v>
+      </c>
+      <c r="E735">
+        <v>8.933</v>
+      </c>
+      <c r="F735">
+        <v>0.09114700000000001</v>
+      </c>
+      <c r="G735">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="H735" t="s">
+        <v>37</v>
+      </c>
+      <c r="I735">
+        <v>431</v>
+      </c>
+      <c r="J735">
+        <v>3528.51</v>
+      </c>
+      <c r="K735">
+        <v>3850.12</v>
+      </c>
+      <c r="L735">
+        <v>321.61</v>
+      </c>
+      <c r="M735" t="s">
+        <v>26</v>
+      </c>
+      <c r="N735">
+        <v>431</v>
+      </c>
+      <c r="O735">
+        <v>3528.5108</v>
+      </c>
+      <c r="P735">
+        <v>3850.123</v>
       </c>
     </row>
   </sheetData>
@@ -32350,7 +32972,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -35093,6 +35715,47 @@
       </c>
       <c r="M67" s="2">
         <v>0.155025491041749</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.069103</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0.08799</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.26068</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.265169</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0.04135</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.549712</v>
+      </c>
+      <c r="H68" s="2">
+        <v>0.126547</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0.175393</v>
+      </c>
+      <c r="J68" s="2">
+        <v>0.013813</v>
+      </c>
+      <c r="K68" s="2">
+        <v>0.077708</v>
+      </c>
+      <c r="L68" s="2">
+        <v>0.09114700000000001</v>
+      </c>
+      <c r="M68" s="2">
+        <v>0.1495025178804494</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2319" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -440,16 +440,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$68</c:f>
+              <c:f>grafico_dati!$B$2:$B$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -650,6 +653,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.069103</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.047334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -677,10 +683,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -881,16 +887,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$68</c:f>
+              <c:f>grafico_dati!$C$2:$C$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1091,6 +1100,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.08799</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.07858</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1118,10 +1130,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1322,16 +1334,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$68</c:f>
+              <c:f>grafico_dati!$D$2:$D$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1532,6 +1547,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.26068</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.216262</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1559,10 +1577,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1763,16 +1781,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$68</c:f>
+              <c:f>grafico_dati!$E$2:$E$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1973,6 +1994,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.265169</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.212307</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2000,10 +2024,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2204,16 +2228,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$68</c:f>
+              <c:f>grafico_dati!$F$2:$F$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2411,6 +2438,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.04135</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.033758</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2438,10 +2468,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2642,16 +2672,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$68</c:f>
+              <c:f>grafico_dati!$G$2:$G$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2852,6 +2885,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.549712</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.5427</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2879,10 +2915,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3083,16 +3119,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$68</c:f>
+              <c:f>grafico_dati!$H$2:$H$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3293,6 +3332,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.126547</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.118646</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3320,10 +3362,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3524,16 +3566,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$68</c:f>
+              <c:f>grafico_dati!$I$2:$I$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3731,6 +3776,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.175393</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.170181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3758,10 +3806,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3962,16 +4010,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$68</c:f>
+              <c:f>grafico_dati!$J$2:$J$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4172,6 +4223,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.013813</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.014253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4199,10 +4253,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4403,16 +4457,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$68</c:f>
+              <c:f>grafico_dati!$K$2:$K$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4610,6 +4667,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.077708</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.075692</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4637,10 +4697,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4841,16 +4901,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$68</c:f>
+              <c:f>grafico_dati!$L$2:$L$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5051,6 +5114,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.09114700000000001</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.080398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5082,10 +5148,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$68</c:f>
+              <c:f>grafico_dati!$A$2:$A$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5286,16 +5352,19 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$68</c:f>
+              <c:f>grafico_dati!$M$2:$M$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5496,6 +5565,9 @@
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0.1495025178804494</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.136870116211423</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5902,7 +5974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P735"/>
+  <dimension ref="A1:P746"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -32963,6 +33035,556 @@
       </c>
       <c r="P735">
         <v>3850.123</v>
+      </c>
+    </row>
+    <row r="736" spans="1:16">
+      <c r="A736" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B736" t="s">
+        <v>16</v>
+      </c>
+      <c r="C736" t="s">
+        <v>27</v>
+      </c>
+      <c r="D736">
+        <v>50.07</v>
+      </c>
+      <c r="E736">
+        <v>52.44</v>
+      </c>
+      <c r="F736">
+        <v>0.047334</v>
+      </c>
+      <c r="G736">
+        <v>4.73</v>
+      </c>
+      <c r="H736" t="s">
+        <v>27</v>
+      </c>
+      <c r="I736">
+        <v>23</v>
+      </c>
+      <c r="J736">
+        <v>1151.61</v>
+      </c>
+      <c r="K736">
+        <v>1206.12</v>
+      </c>
+      <c r="L736">
+        <v>54.51</v>
+      </c>
+      <c r="M736" t="s">
+        <v>16</v>
+      </c>
+      <c r="N736">
+        <v>23</v>
+      </c>
+      <c r="O736">
+        <v>1151.61</v>
+      </c>
+      <c r="P736">
+        <v>1206.12</v>
+      </c>
+    </row>
+    <row r="737" spans="1:16">
+      <c r="A737" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B737" t="s">
+        <v>17</v>
+      </c>
+      <c r="C737" t="s">
+        <v>28</v>
+      </c>
+      <c r="D737">
+        <v>242.3</v>
+      </c>
+      <c r="E737">
+        <v>261.34</v>
+      </c>
+      <c r="F737">
+        <v>0.07858</v>
+      </c>
+      <c r="G737">
+        <v>7.86</v>
+      </c>
+      <c r="H737" t="s">
+        <v>28</v>
+      </c>
+      <c r="I737">
+        <v>5</v>
+      </c>
+      <c r="J737">
+        <v>1211.5</v>
+      </c>
+      <c r="K737">
+        <v>1306.7</v>
+      </c>
+      <c r="L737">
+        <v>95.2</v>
+      </c>
+      <c r="M737" t="s">
+        <v>17</v>
+      </c>
+      <c r="N737">
+        <v>5</v>
+      </c>
+      <c r="O737">
+        <v>1211.5</v>
+      </c>
+      <c r="P737">
+        <v>1306.7</v>
+      </c>
+    </row>
+    <row r="738" spans="1:16">
+      <c r="A738" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B738" t="s">
+        <v>18</v>
+      </c>
+      <c r="C738" t="s">
+        <v>29</v>
+      </c>
+      <c r="D738">
+        <v>38.273</v>
+      </c>
+      <c r="E738">
+        <v>46.55</v>
+      </c>
+      <c r="F738">
+        <v>0.216262</v>
+      </c>
+      <c r="G738">
+        <v>21.63</v>
+      </c>
+      <c r="H738" t="s">
+        <v>29</v>
+      </c>
+      <c r="I738">
+        <v>54</v>
+      </c>
+      <c r="J738">
+        <v>2066.74</v>
+      </c>
+      <c r="K738">
+        <v>2513.7</v>
+      </c>
+      <c r="L738">
+        <v>446.96</v>
+      </c>
+      <c r="M738" t="s">
+        <v>18</v>
+      </c>
+      <c r="N738">
+        <v>54</v>
+      </c>
+      <c r="O738">
+        <v>2066.742</v>
+      </c>
+      <c r="P738">
+        <v>2513.7</v>
+      </c>
+    </row>
+    <row r="739" spans="1:16">
+      <c r="A739" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B739" t="s">
+        <v>19</v>
+      </c>
+      <c r="C739" t="s">
+        <v>30</v>
+      </c>
+      <c r="D739">
+        <v>6.5264</v>
+      </c>
+      <c r="E739">
+        <v>7.912</v>
+      </c>
+      <c r="F739">
+        <v>0.212307</v>
+      </c>
+      <c r="G739">
+        <v>21.23</v>
+      </c>
+      <c r="H739" t="s">
+        <v>30</v>
+      </c>
+      <c r="I739">
+        <v>276</v>
+      </c>
+      <c r="J739">
+        <v>1801.29</v>
+      </c>
+      <c r="K739">
+        <v>2183.71</v>
+      </c>
+      <c r="L739">
+        <v>382.43</v>
+      </c>
+      <c r="M739" t="s">
+        <v>19</v>
+      </c>
+      <c r="N739">
+        <v>276</v>
+      </c>
+      <c r="O739">
+        <v>1801.2864</v>
+      </c>
+      <c r="P739">
+        <v>2183.712</v>
+      </c>
+    </row>
+    <row r="740" spans="1:16">
+      <c r="A740" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B740" t="s">
+        <v>20</v>
+      </c>
+      <c r="C740" t="s">
+        <v>31</v>
+      </c>
+      <c r="D740">
+        <v>197.58</v>
+      </c>
+      <c r="E740">
+        <v>204.25</v>
+      </c>
+      <c r="F740">
+        <v>0.033758</v>
+      </c>
+      <c r="G740">
+        <v>3.38</v>
+      </c>
+      <c r="H740" t="s">
+        <v>31</v>
+      </c>
+      <c r="I740">
+        <v>4</v>
+      </c>
+      <c r="J740">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K740">
+        <v>817</v>
+      </c>
+      <c r="L740">
+        <v>26.68</v>
+      </c>
+      <c r="M740" t="s">
+        <v>20</v>
+      </c>
+      <c r="N740">
+        <v>4</v>
+      </c>
+      <c r="O740">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P740">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="741" spans="1:16">
+      <c r="A741" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B741" t="s">
+        <v>21</v>
+      </c>
+      <c r="C741" t="s">
+        <v>32</v>
+      </c>
+      <c r="D741">
+        <v>79.86</v>
+      </c>
+      <c r="E741">
+        <v>123.2</v>
+      </c>
+      <c r="F741">
+        <v>0.5427</v>
+      </c>
+      <c r="G741">
+        <v>54.27</v>
+      </c>
+      <c r="H741" t="s">
+        <v>32</v>
+      </c>
+      <c r="I741">
+        <v>12</v>
+      </c>
+      <c r="J741">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K741">
+        <v>1478.4</v>
+      </c>
+      <c r="L741">
+        <v>520.08</v>
+      </c>
+      <c r="M741" t="s">
+        <v>21</v>
+      </c>
+      <c r="N741">
+        <v>12</v>
+      </c>
+      <c r="O741">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P741">
+        <v>1478.4</v>
+      </c>
+    </row>
+    <row r="742" spans="1:16">
+      <c r="A742" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B742" t="s">
+        <v>22</v>
+      </c>
+      <c r="C742" t="s">
+        <v>33</v>
+      </c>
+      <c r="D742">
+        <v>19.7444</v>
+      </c>
+      <c r="E742">
+        <v>22.087</v>
+      </c>
+      <c r="F742">
+        <v>0.118646</v>
+      </c>
+      <c r="G742">
+        <v>11.86</v>
+      </c>
+      <c r="H742" t="s">
+        <v>33</v>
+      </c>
+      <c r="I742">
+        <v>61</v>
+      </c>
+      <c r="J742">
+        <v>1204.41</v>
+      </c>
+      <c r="K742">
+        <v>1347.31</v>
+      </c>
+      <c r="L742">
+        <v>142.9</v>
+      </c>
+      <c r="M742" t="s">
+        <v>22</v>
+      </c>
+      <c r="N742">
+        <v>61</v>
+      </c>
+      <c r="O742">
+        <v>1204.4084</v>
+      </c>
+      <c r="P742">
+        <v>1347.307</v>
+      </c>
+    </row>
+    <row r="743" spans="1:16">
+      <c r="A743" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B743" t="s">
+        <v>23</v>
+      </c>
+      <c r="C743" t="s">
+        <v>34</v>
+      </c>
+      <c r="D743">
+        <v>132.3898</v>
+      </c>
+      <c r="E743">
+        <v>154.92</v>
+      </c>
+      <c r="F743">
+        <v>0.170181</v>
+      </c>
+      <c r="G743">
+        <v>17.02</v>
+      </c>
+      <c r="H743" t="s">
+        <v>34</v>
+      </c>
+      <c r="I743">
+        <v>57</v>
+      </c>
+      <c r="J743">
+        <v>7546.22</v>
+      </c>
+      <c r="K743">
+        <v>8830.440000000001</v>
+      </c>
+      <c r="L743">
+        <v>1284.22</v>
+      </c>
+      <c r="M743" t="s">
+        <v>23</v>
+      </c>
+      <c r="N743">
+        <v>57</v>
+      </c>
+      <c r="O743">
+        <v>7546.2186</v>
+      </c>
+      <c r="P743">
+        <v>8830.439999999999</v>
+      </c>
+    </row>
+    <row r="744" spans="1:16">
+      <c r="A744" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B744" t="s">
+        <v>24</v>
+      </c>
+      <c r="C744" t="s">
+        <v>35</v>
+      </c>
+      <c r="D744">
+        <v>34.0694</v>
+      </c>
+      <c r="E744">
+        <v>34.555</v>
+      </c>
+      <c r="F744">
+        <v>0.014253</v>
+      </c>
+      <c r="G744">
+        <v>1.43</v>
+      </c>
+      <c r="H744" t="s">
+        <v>35</v>
+      </c>
+      <c r="I744">
+        <v>48</v>
+      </c>
+      <c r="J744">
+        <v>1635.33</v>
+      </c>
+      <c r="K744">
+        <v>1658.64</v>
+      </c>
+      <c r="L744">
+        <v>23.31</v>
+      </c>
+      <c r="M744" t="s">
+        <v>24</v>
+      </c>
+      <c r="N744">
+        <v>48</v>
+      </c>
+      <c r="O744">
+        <v>1635.3312</v>
+      </c>
+      <c r="P744">
+        <v>1658.64</v>
+      </c>
+    </row>
+    <row r="745" spans="1:16">
+      <c r="A745" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B745" t="s">
+        <v>25</v>
+      </c>
+      <c r="C745" t="s">
+        <v>36</v>
+      </c>
+      <c r="D745">
+        <v>69.4158</v>
+      </c>
+      <c r="E745">
+        <v>74.67</v>
+      </c>
+      <c r="F745">
+        <v>0.075692</v>
+      </c>
+      <c r="G745">
+        <v>7.57</v>
+      </c>
+      <c r="H745" t="s">
+        <v>36</v>
+      </c>
+      <c r="I745">
+        <v>62</v>
+      </c>
+      <c r="J745">
+        <v>4303.78</v>
+      </c>
+      <c r="K745">
+        <v>4629.54</v>
+      </c>
+      <c r="L745">
+        <v>325.76</v>
+      </c>
+      <c r="M745" t="s">
+        <v>25</v>
+      </c>
+      <c r="N745">
+        <v>62</v>
+      </c>
+      <c r="O745">
+        <v>4303.7796</v>
+      </c>
+      <c r="P745">
+        <v>4629.54</v>
+      </c>
+    </row>
+    <row r="746" spans="1:16">
+      <c r="A746" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B746" t="s">
+        <v>26</v>
+      </c>
+      <c r="C746" t="s">
+        <v>37</v>
+      </c>
+      <c r="D746">
+        <v>8.1868</v>
+      </c>
+      <c r="E746">
+        <v>8.845000000000001</v>
+      </c>
+      <c r="F746">
+        <v>0.080398</v>
+      </c>
+      <c r="G746">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="H746" t="s">
+        <v>37</v>
+      </c>
+      <c r="I746">
+        <v>431</v>
+      </c>
+      <c r="J746">
+        <v>3528.51</v>
+      </c>
+      <c r="K746">
+        <v>3812.2</v>
+      </c>
+      <c r="L746">
+        <v>283.68</v>
+      </c>
+      <c r="M746" t="s">
+        <v>26</v>
+      </c>
+      <c r="N746">
+        <v>431</v>
+      </c>
+      <c r="O746">
+        <v>3528.5108</v>
+      </c>
+      <c r="P746">
+        <v>3812.195</v>
       </c>
     </row>
   </sheetData>
@@ -32972,7 +33594,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -35756,6 +36378,47 @@
       </c>
       <c r="M68" s="2">
         <v>0.1495025178804494</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="A69" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.047334</v>
+      </c>
+      <c r="C69" s="2">
+        <v>0.07858</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0.216262</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.212307</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0.033758</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0.5427</v>
+      </c>
+      <c r="H69" s="2">
+        <v>0.118646</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0.170181</v>
+      </c>
+      <c r="J69" s="2">
+        <v>0.014253</v>
+      </c>
+      <c r="K69" s="2">
+        <v>0.075692</v>
+      </c>
+      <c r="L69" s="2">
+        <v>0.080398</v>
+      </c>
+      <c r="M69" s="2">
+        <v>0.136870116211423</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -443,16 +443,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$69</c:f>
+              <c:f>grafico_dati!$B$2:$B$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -656,6 +659,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.047334</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.044937</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -683,10 +689,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -890,16 +896,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$69</c:f>
+              <c:f>grafico_dati!$C$2:$C$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1103,6 +1112,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.07858</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.077755</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1130,10 +1142,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1337,16 +1349,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$69</c:f>
+              <c:f>grafico_dati!$D$2:$D$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1550,6 +1565,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.216262</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.213911</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1577,10 +1595,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1784,16 +1802,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$69</c:f>
+              <c:f>grafico_dati!$E$2:$E$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -1997,6 +2018,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.212307</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.21246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2024,10 +2048,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2231,16 +2255,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$69</c:f>
+              <c:f>grafico_dati!$F$2:$F$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2441,6 +2468,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.033758</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.027432</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2468,10 +2498,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2675,16 +2705,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$69</c:f>
+              <c:f>grafico_dati!$G$2:$G$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2888,6 +2921,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.5427</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.556474</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2915,10 +2951,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3122,16 +3158,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$69</c:f>
+              <c:f>grafico_dati!$H$2:$H$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3335,6 +3374,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.118646</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.114797</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3362,10 +3404,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3569,16 +3611,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$69</c:f>
+              <c:f>grafico_dati!$I$2:$I$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3779,6 +3824,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.170181</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.164214</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3806,10 +3854,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4013,16 +4061,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$69</c:f>
+              <c:f>grafico_dati!$J$2:$J$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4226,6 +4277,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.014253</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.008676</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4253,10 +4307,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4460,16 +4514,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$69</c:f>
+              <c:f>grafico_dati!$K$2:$K$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4670,6 +4727,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.075692</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.07266599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4697,10 +4757,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4904,16 +4964,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$69</c:f>
+              <c:f>grafico_dati!$L$2:$L$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5117,6 +5180,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.080398</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.079543</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5148,10 +5214,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$69</c:f>
+              <c:f>grafico_dati!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5355,16 +5421,19 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$69</c:f>
+              <c:f>grafico_dati!$M$2:$M$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="68"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5568,6 +5637,9 @@
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>0.136870116211423</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.1340085648434515</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5974,7 +6046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P746"/>
+  <dimension ref="A1:P757"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -33585,6 +33657,556 @@
       </c>
       <c r="P746">
         <v>3812.195</v>
+      </c>
+    </row>
+    <row r="747" spans="1:16">
+      <c r="A747" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B747" t="s">
+        <v>16</v>
+      </c>
+      <c r="C747" t="s">
+        <v>27</v>
+      </c>
+      <c r="D747">
+        <v>50.07</v>
+      </c>
+      <c r="E747">
+        <v>52.32</v>
+      </c>
+      <c r="F747">
+        <v>0.044937</v>
+      </c>
+      <c r="G747">
+        <v>4.49</v>
+      </c>
+      <c r="H747" t="s">
+        <v>27</v>
+      </c>
+      <c r="I747">
+        <v>23</v>
+      </c>
+      <c r="J747">
+        <v>1151.61</v>
+      </c>
+      <c r="K747">
+        <v>1203.36</v>
+      </c>
+      <c r="L747">
+        <v>51.75</v>
+      </c>
+      <c r="M747" t="s">
+        <v>16</v>
+      </c>
+      <c r="N747">
+        <v>23</v>
+      </c>
+      <c r="O747">
+        <v>1151.61</v>
+      </c>
+      <c r="P747">
+        <v>1203.36</v>
+      </c>
+    </row>
+    <row r="748" spans="1:16">
+      <c r="A748" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B748" t="s">
+        <v>17</v>
+      </c>
+      <c r="C748" t="s">
+        <v>28</v>
+      </c>
+      <c r="D748">
+        <v>242.3</v>
+      </c>
+      <c r="E748">
+        <v>261.14</v>
+      </c>
+      <c r="F748">
+        <v>0.077755</v>
+      </c>
+      <c r="G748">
+        <v>7.78</v>
+      </c>
+      <c r="H748" t="s">
+        <v>28</v>
+      </c>
+      <c r="I748">
+        <v>5</v>
+      </c>
+      <c r="J748">
+        <v>1211.5</v>
+      </c>
+      <c r="K748">
+        <v>1305.7</v>
+      </c>
+      <c r="L748">
+        <v>94.2</v>
+      </c>
+      <c r="M748" t="s">
+        <v>17</v>
+      </c>
+      <c r="N748">
+        <v>5</v>
+      </c>
+      <c r="O748">
+        <v>1211.5</v>
+      </c>
+      <c r="P748">
+        <v>1305.7</v>
+      </c>
+    </row>
+    <row r="749" spans="1:16">
+      <c r="A749" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B749" t="s">
+        <v>18</v>
+      </c>
+      <c r="C749" t="s">
+        <v>29</v>
+      </c>
+      <c r="D749">
+        <v>38.273</v>
+      </c>
+      <c r="E749">
+        <v>46.46</v>
+      </c>
+      <c r="F749">
+        <v>0.213911</v>
+      </c>
+      <c r="G749">
+        <v>21.39</v>
+      </c>
+      <c r="H749" t="s">
+        <v>29</v>
+      </c>
+      <c r="I749">
+        <v>54</v>
+      </c>
+      <c r="J749">
+        <v>2066.74</v>
+      </c>
+      <c r="K749">
+        <v>2508.84</v>
+      </c>
+      <c r="L749">
+        <v>442.1</v>
+      </c>
+      <c r="M749" t="s">
+        <v>18</v>
+      </c>
+      <c r="N749">
+        <v>54</v>
+      </c>
+      <c r="O749">
+        <v>2066.742</v>
+      </c>
+      <c r="P749">
+        <v>2508.84</v>
+      </c>
+    </row>
+    <row r="750" spans="1:16">
+      <c r="A750" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B750" t="s">
+        <v>19</v>
+      </c>
+      <c r="C750" t="s">
+        <v>30</v>
+      </c>
+      <c r="D750">
+        <v>6.5264</v>
+      </c>
+      <c r="E750">
+        <v>7.913</v>
+      </c>
+      <c r="F750">
+        <v>0.21246</v>
+      </c>
+      <c r="G750">
+        <v>21.25</v>
+      </c>
+      <c r="H750" t="s">
+        <v>30</v>
+      </c>
+      <c r="I750">
+        <v>276</v>
+      </c>
+      <c r="J750">
+        <v>1801.29</v>
+      </c>
+      <c r="K750">
+        <v>2183.99</v>
+      </c>
+      <c r="L750">
+        <v>382.7</v>
+      </c>
+      <c r="M750" t="s">
+        <v>19</v>
+      </c>
+      <c r="N750">
+        <v>276</v>
+      </c>
+      <c r="O750">
+        <v>1801.2864</v>
+      </c>
+      <c r="P750">
+        <v>2183.988</v>
+      </c>
+    </row>
+    <row r="751" spans="1:16">
+      <c r="A751" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B751" t="s">
+        <v>20</v>
+      </c>
+      <c r="C751" t="s">
+        <v>31</v>
+      </c>
+      <c r="D751">
+        <v>197.58</v>
+      </c>
+      <c r="E751">
+        <v>203</v>
+      </c>
+      <c r="F751">
+        <v>0.027432</v>
+      </c>
+      <c r="G751">
+        <v>2.74</v>
+      </c>
+      <c r="H751" t="s">
+        <v>31</v>
+      </c>
+      <c r="I751">
+        <v>4</v>
+      </c>
+      <c r="J751">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K751">
+        <v>812</v>
+      </c>
+      <c r="L751">
+        <v>21.68</v>
+      </c>
+      <c r="M751" t="s">
+        <v>20</v>
+      </c>
+      <c r="N751">
+        <v>4</v>
+      </c>
+      <c r="O751">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P751">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="752" spans="1:16">
+      <c r="A752" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B752" t="s">
+        <v>21</v>
+      </c>
+      <c r="C752" t="s">
+        <v>32</v>
+      </c>
+      <c r="D752">
+        <v>79.86</v>
+      </c>
+      <c r="E752">
+        <v>124.3</v>
+      </c>
+      <c r="F752">
+        <v>0.556474</v>
+      </c>
+      <c r="G752">
+        <v>55.65</v>
+      </c>
+      <c r="H752" t="s">
+        <v>32</v>
+      </c>
+      <c r="I752">
+        <v>12</v>
+      </c>
+      <c r="J752">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K752">
+        <v>1491.6</v>
+      </c>
+      <c r="L752">
+        <v>533.28</v>
+      </c>
+      <c r="M752" t="s">
+        <v>21</v>
+      </c>
+      <c r="N752">
+        <v>12</v>
+      </c>
+      <c r="O752">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P752">
+        <v>1491.6</v>
+      </c>
+    </row>
+    <row r="753" spans="1:16">
+      <c r="A753" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B753" t="s">
+        <v>22</v>
+      </c>
+      <c r="C753" t="s">
+        <v>33</v>
+      </c>
+      <c r="D753">
+        <v>19.7444</v>
+      </c>
+      <c r="E753">
+        <v>22.011</v>
+      </c>
+      <c r="F753">
+        <v>0.114797</v>
+      </c>
+      <c r="G753">
+        <v>11.48</v>
+      </c>
+      <c r="H753" t="s">
+        <v>33</v>
+      </c>
+      <c r="I753">
+        <v>61</v>
+      </c>
+      <c r="J753">
+        <v>1204.41</v>
+      </c>
+      <c r="K753">
+        <v>1342.67</v>
+      </c>
+      <c r="L753">
+        <v>138.26</v>
+      </c>
+      <c r="M753" t="s">
+        <v>22</v>
+      </c>
+      <c r="N753">
+        <v>61</v>
+      </c>
+      <c r="O753">
+        <v>1204.4084</v>
+      </c>
+      <c r="P753">
+        <v>1342.671</v>
+      </c>
+    </row>
+    <row r="754" spans="1:16">
+      <c r="A754" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B754" t="s">
+        <v>23</v>
+      </c>
+      <c r="C754" t="s">
+        <v>34</v>
+      </c>
+      <c r="D754">
+        <v>132.3898</v>
+      </c>
+      <c r="E754">
+        <v>154.13</v>
+      </c>
+      <c r="F754">
+        <v>0.164214</v>
+      </c>
+      <c r="G754">
+        <v>16.42</v>
+      </c>
+      <c r="H754" t="s">
+        <v>34</v>
+      </c>
+      <c r="I754">
+        <v>57</v>
+      </c>
+      <c r="J754">
+        <v>7546.22</v>
+      </c>
+      <c r="K754">
+        <v>8785.41</v>
+      </c>
+      <c r="L754">
+        <v>1239.19</v>
+      </c>
+      <c r="M754" t="s">
+        <v>23</v>
+      </c>
+      <c r="N754">
+        <v>57</v>
+      </c>
+      <c r="O754">
+        <v>7546.2186</v>
+      </c>
+      <c r="P754">
+        <v>8785.41</v>
+      </c>
+    </row>
+    <row r="755" spans="1:16">
+      <c r="A755" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B755" t="s">
+        <v>24</v>
+      </c>
+      <c r="C755" t="s">
+        <v>35</v>
+      </c>
+      <c r="D755">
+        <v>34.0694</v>
+      </c>
+      <c r="E755">
+        <v>34.365</v>
+      </c>
+      <c r="F755">
+        <v>0.008676</v>
+      </c>
+      <c r="G755">
+        <v>0.87</v>
+      </c>
+      <c r="H755" t="s">
+        <v>35</v>
+      </c>
+      <c r="I755">
+        <v>48</v>
+      </c>
+      <c r="J755">
+        <v>1635.33</v>
+      </c>
+      <c r="K755">
+        <v>1649.52</v>
+      </c>
+      <c r="L755">
+        <v>14.19</v>
+      </c>
+      <c r="M755" t="s">
+        <v>24</v>
+      </c>
+      <c r="N755">
+        <v>48</v>
+      </c>
+      <c r="O755">
+        <v>1635.3312</v>
+      </c>
+      <c r="P755">
+        <v>1649.52</v>
+      </c>
+    </row>
+    <row r="756" spans="1:16">
+      <c r="A756" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B756" t="s">
+        <v>25</v>
+      </c>
+      <c r="C756" t="s">
+        <v>36</v>
+      </c>
+      <c r="D756">
+        <v>69.4158</v>
+      </c>
+      <c r="E756">
+        <v>74.45999999999999</v>
+      </c>
+      <c r="F756">
+        <v>0.07266599999999999</v>
+      </c>
+      <c r="G756">
+        <v>7.27</v>
+      </c>
+      <c r="H756" t="s">
+        <v>36</v>
+      </c>
+      <c r="I756">
+        <v>62</v>
+      </c>
+      <c r="J756">
+        <v>4303.78</v>
+      </c>
+      <c r="K756">
+        <v>4616.52</v>
+      </c>
+      <c r="L756">
+        <v>312.74</v>
+      </c>
+      <c r="M756" t="s">
+        <v>25</v>
+      </c>
+      <c r="N756">
+        <v>62</v>
+      </c>
+      <c r="O756">
+        <v>4303.7796</v>
+      </c>
+      <c r="P756">
+        <v>4616.52</v>
+      </c>
+    </row>
+    <row r="757" spans="1:16">
+      <c r="A757" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B757" t="s">
+        <v>26</v>
+      </c>
+      <c r="C757" t="s">
+        <v>37</v>
+      </c>
+      <c r="D757">
+        <v>8.1868</v>
+      </c>
+      <c r="E757">
+        <v>8.837999999999999</v>
+      </c>
+      <c r="F757">
+        <v>0.079543</v>
+      </c>
+      <c r="G757">
+        <v>7.95</v>
+      </c>
+      <c r="H757" t="s">
+        <v>37</v>
+      </c>
+      <c r="I757">
+        <v>431</v>
+      </c>
+      <c r="J757">
+        <v>3528.51</v>
+      </c>
+      <c r="K757">
+        <v>3809.18</v>
+      </c>
+      <c r="L757">
+        <v>280.67</v>
+      </c>
+      <c r="M757" t="s">
+        <v>26</v>
+      </c>
+      <c r="N757">
+        <v>431</v>
+      </c>
+      <c r="O757">
+        <v>3528.5108</v>
+      </c>
+      <c r="P757">
+        <v>3809.177999999999</v>
       </c>
     </row>
   </sheetData>
@@ -33594,7 +34216,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -36419,6 +37041,47 @@
       </c>
       <c r="M69" s="2">
         <v>0.136870116211423</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="A70" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.044937</v>
+      </c>
+      <c r="C70" s="2">
+        <v>0.077755</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.213911</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.21246</v>
+      </c>
+      <c r="F70" s="2">
+        <v>0.027432</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0.556474</v>
+      </c>
+      <c r="H70" s="2">
+        <v>0.114797</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0.164214</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0.008676</v>
+      </c>
+      <c r="K70" s="2">
+        <v>0.07266599999999999</v>
+      </c>
+      <c r="L70" s="2">
+        <v>0.079543</v>
+      </c>
+      <c r="M70" s="2">
+        <v>0.1340085648434515</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2451" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -446,16 +446,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$70</c:f>
+              <c:f>grafico_dati!$B$2:$B$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -662,6 +665,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.044937</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.041142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -689,10 +695,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -899,16 +905,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$70</c:f>
+              <c:f>grafico_dati!$C$2:$C$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1115,6 +1124,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.077755</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.064053</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1142,10 +1154,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1352,16 +1364,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$70</c:f>
+              <c:f>grafico_dati!$D$2:$D$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1568,6 +1583,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.213911</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.204504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1595,10 +1613,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1805,16 +1823,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$70</c:f>
+              <c:f>grafico_dati!$E$2:$E$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2021,6 +2042,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.21246</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.200509</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2048,10 +2072,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2258,16 +2282,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$70</c:f>
+              <c:f>grafico_dati!$F$2:$F$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2471,6 +2498,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.027432</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.01984</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2498,10 +2528,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2708,16 +2738,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$70</c:f>
+              <c:f>grafico_dati!$G$2:$G$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2924,6 +2957,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.556474</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.561983</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2951,10 +2987,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3161,16 +3197,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$70</c:f>
+              <c:f>grafico_dati!$H$2:$H$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3377,6 +3416,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.114797</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.102237</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3404,10 +3446,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3614,16 +3656,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$70</c:f>
+              <c:f>grafico_dati!$I$2:$I$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3827,6 +3872,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.164214</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.146841</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3854,10 +3902,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4064,16 +4112,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$70</c:f>
+              <c:f>grafico_dati!$J$2:$J$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4280,6 +4331,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.008676</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.010291</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4307,10 +4361,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4517,16 +4571,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$70</c:f>
+              <c:f>grafico_dati!$K$2:$K$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4730,6 +4787,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.07266599999999999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.06315900000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4757,10 +4817,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4967,16 +5027,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$70</c:f>
+              <c:f>grafico_dati!$L$2:$L$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5183,6 +5246,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.079543</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.06952700000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5214,10 +5280,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$70</c:f>
+              <c:f>grafico_dati!$A$2:$A$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5424,16 +5490,19 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$70</c:f>
+              <c:f>grafico_dati!$M$2:$M$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5640,6 +5709,9 @@
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0.1340085648434515</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.1232250046921473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6046,7 +6118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P757"/>
+  <dimension ref="A1:P768"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -34207,6 +34279,556 @@
       </c>
       <c r="P757">
         <v>3809.177999999999</v>
+      </c>
+    </row>
+    <row r="758" spans="1:16">
+      <c r="A758" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B758" t="s">
+        <v>16</v>
+      </c>
+      <c r="C758" t="s">
+        <v>27</v>
+      </c>
+      <c r="D758">
+        <v>50.07</v>
+      </c>
+      <c r="E758">
+        <v>52.13</v>
+      </c>
+      <c r="F758">
+        <v>0.041142</v>
+      </c>
+      <c r="G758">
+        <v>4.11</v>
+      </c>
+      <c r="H758" t="s">
+        <v>27</v>
+      </c>
+      <c r="I758">
+        <v>23</v>
+      </c>
+      <c r="J758">
+        <v>1151.61</v>
+      </c>
+      <c r="K758">
+        <v>1198.99</v>
+      </c>
+      <c r="L758">
+        <v>47.38</v>
+      </c>
+      <c r="M758" t="s">
+        <v>16</v>
+      </c>
+      <c r="N758">
+        <v>23</v>
+      </c>
+      <c r="O758">
+        <v>1151.61</v>
+      </c>
+      <c r="P758">
+        <v>1198.99</v>
+      </c>
+    </row>
+    <row r="759" spans="1:16">
+      <c r="A759" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B759" t="s">
+        <v>17</v>
+      </c>
+      <c r="C759" t="s">
+        <v>28</v>
+      </c>
+      <c r="D759">
+        <v>242.3</v>
+      </c>
+      <c r="E759">
+        <v>257.82</v>
+      </c>
+      <c r="F759">
+        <v>0.064053</v>
+      </c>
+      <c r="G759">
+        <v>6.41</v>
+      </c>
+      <c r="H759" t="s">
+        <v>28</v>
+      </c>
+      <c r="I759">
+        <v>5</v>
+      </c>
+      <c r="J759">
+        <v>1211.5</v>
+      </c>
+      <c r="K759">
+        <v>1289.1</v>
+      </c>
+      <c r="L759">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="M759" t="s">
+        <v>17</v>
+      </c>
+      <c r="N759">
+        <v>5</v>
+      </c>
+      <c r="O759">
+        <v>1211.5</v>
+      </c>
+      <c r="P759">
+        <v>1289.1</v>
+      </c>
+    </row>
+    <row r="760" spans="1:16">
+      <c r="A760" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B760" t="s">
+        <v>18</v>
+      </c>
+      <c r="C760" t="s">
+        <v>29</v>
+      </c>
+      <c r="D760">
+        <v>38.273</v>
+      </c>
+      <c r="E760">
+        <v>46.1</v>
+      </c>
+      <c r="F760">
+        <v>0.204504</v>
+      </c>
+      <c r="G760">
+        <v>20.45</v>
+      </c>
+      <c r="H760" t="s">
+        <v>29</v>
+      </c>
+      <c r="I760">
+        <v>54</v>
+      </c>
+      <c r="J760">
+        <v>2066.74</v>
+      </c>
+      <c r="K760">
+        <v>2489.4</v>
+      </c>
+      <c r="L760">
+        <v>422.66</v>
+      </c>
+      <c r="M760" t="s">
+        <v>18</v>
+      </c>
+      <c r="N760">
+        <v>54</v>
+      </c>
+      <c r="O760">
+        <v>2066.742</v>
+      </c>
+      <c r="P760">
+        <v>2489.4</v>
+      </c>
+    </row>
+    <row r="761" spans="1:16">
+      <c r="A761" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B761" t="s">
+        <v>19</v>
+      </c>
+      <c r="C761" t="s">
+        <v>30</v>
+      </c>
+      <c r="D761">
+        <v>6.5264</v>
+      </c>
+      <c r="E761">
+        <v>7.835</v>
+      </c>
+      <c r="F761">
+        <v>0.200509</v>
+      </c>
+      <c r="G761">
+        <v>20.05</v>
+      </c>
+      <c r="H761" t="s">
+        <v>30</v>
+      </c>
+      <c r="I761">
+        <v>276</v>
+      </c>
+      <c r="J761">
+        <v>1801.29</v>
+      </c>
+      <c r="K761">
+        <v>2162.46</v>
+      </c>
+      <c r="L761">
+        <v>361.17</v>
+      </c>
+      <c r="M761" t="s">
+        <v>19</v>
+      </c>
+      <c r="N761">
+        <v>276</v>
+      </c>
+      <c r="O761">
+        <v>1801.2864</v>
+      </c>
+      <c r="P761">
+        <v>2162.46</v>
+      </c>
+    </row>
+    <row r="762" spans="1:16">
+      <c r="A762" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B762" t="s">
+        <v>20</v>
+      </c>
+      <c r="C762" t="s">
+        <v>31</v>
+      </c>
+      <c r="D762">
+        <v>197.58</v>
+      </c>
+      <c r="E762">
+        <v>201.5</v>
+      </c>
+      <c r="F762">
+        <v>0.01984</v>
+      </c>
+      <c r="G762">
+        <v>1.98</v>
+      </c>
+      <c r="H762" t="s">
+        <v>31</v>
+      </c>
+      <c r="I762">
+        <v>4</v>
+      </c>
+      <c r="J762">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K762">
+        <v>806</v>
+      </c>
+      <c r="L762">
+        <v>15.68</v>
+      </c>
+      <c r="M762" t="s">
+        <v>20</v>
+      </c>
+      <c r="N762">
+        <v>4</v>
+      </c>
+      <c r="O762">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P762">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="763" spans="1:16">
+      <c r="A763" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B763" t="s">
+        <v>21</v>
+      </c>
+      <c r="C763" t="s">
+        <v>32</v>
+      </c>
+      <c r="D763">
+        <v>79.86</v>
+      </c>
+      <c r="E763">
+        <v>124.74</v>
+      </c>
+      <c r="F763">
+        <v>0.561983</v>
+      </c>
+      <c r="G763">
+        <v>56.2</v>
+      </c>
+      <c r="H763" t="s">
+        <v>32</v>
+      </c>
+      <c r="I763">
+        <v>12</v>
+      </c>
+      <c r="J763">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K763">
+        <v>1496.88</v>
+      </c>
+      <c r="L763">
+        <v>538.5599999999999</v>
+      </c>
+      <c r="M763" t="s">
+        <v>21</v>
+      </c>
+      <c r="N763">
+        <v>12</v>
+      </c>
+      <c r="O763">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P763">
+        <v>1496.88</v>
+      </c>
+    </row>
+    <row r="764" spans="1:16">
+      <c r="A764" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B764" t="s">
+        <v>22</v>
+      </c>
+      <c r="C764" t="s">
+        <v>33</v>
+      </c>
+      <c r="D764">
+        <v>19.7444</v>
+      </c>
+      <c r="E764">
+        <v>21.763</v>
+      </c>
+      <c r="F764">
+        <v>0.102237</v>
+      </c>
+      <c r="G764">
+        <v>10.22</v>
+      </c>
+      <c r="H764" t="s">
+        <v>33</v>
+      </c>
+      <c r="I764">
+        <v>61</v>
+      </c>
+      <c r="J764">
+        <v>1204.41</v>
+      </c>
+      <c r="K764">
+        <v>1327.54</v>
+      </c>
+      <c r="L764">
+        <v>123.13</v>
+      </c>
+      <c r="M764" t="s">
+        <v>22</v>
+      </c>
+      <c r="N764">
+        <v>61</v>
+      </c>
+      <c r="O764">
+        <v>1204.4084</v>
+      </c>
+      <c r="P764">
+        <v>1327.543</v>
+      </c>
+    </row>
+    <row r="765" spans="1:16">
+      <c r="A765" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B765" t="s">
+        <v>23</v>
+      </c>
+      <c r="C765" t="s">
+        <v>34</v>
+      </c>
+      <c r="D765">
+        <v>132.3898</v>
+      </c>
+      <c r="E765">
+        <v>151.83</v>
+      </c>
+      <c r="F765">
+        <v>0.146841</v>
+      </c>
+      <c r="G765">
+        <v>14.68</v>
+      </c>
+      <c r="H765" t="s">
+        <v>34</v>
+      </c>
+      <c r="I765">
+        <v>57</v>
+      </c>
+      <c r="J765">
+        <v>7546.22</v>
+      </c>
+      <c r="K765">
+        <v>8654.309999999999</v>
+      </c>
+      <c r="L765">
+        <v>1108.09</v>
+      </c>
+      <c r="M765" t="s">
+        <v>23</v>
+      </c>
+      <c r="N765">
+        <v>57</v>
+      </c>
+      <c r="O765">
+        <v>7546.2186</v>
+      </c>
+      <c r="P765">
+        <v>8654.310000000001</v>
+      </c>
+    </row>
+    <row r="766" spans="1:16">
+      <c r="A766" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B766" t="s">
+        <v>24</v>
+      </c>
+      <c r="C766" t="s">
+        <v>35</v>
+      </c>
+      <c r="D766">
+        <v>34.0694</v>
+      </c>
+      <c r="E766">
+        <v>34.42</v>
+      </c>
+      <c r="F766">
+        <v>0.010291</v>
+      </c>
+      <c r="G766">
+        <v>1.03</v>
+      </c>
+      <c r="H766" t="s">
+        <v>35</v>
+      </c>
+      <c r="I766">
+        <v>48</v>
+      </c>
+      <c r="J766">
+        <v>1635.33</v>
+      </c>
+      <c r="K766">
+        <v>1652.16</v>
+      </c>
+      <c r="L766">
+        <v>16.83</v>
+      </c>
+      <c r="M766" t="s">
+        <v>24</v>
+      </c>
+      <c r="N766">
+        <v>48</v>
+      </c>
+      <c r="O766">
+        <v>1635.3312</v>
+      </c>
+      <c r="P766">
+        <v>1652.16</v>
+      </c>
+    </row>
+    <row r="767" spans="1:16">
+      <c r="A767" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B767" t="s">
+        <v>25</v>
+      </c>
+      <c r="C767" t="s">
+        <v>36</v>
+      </c>
+      <c r="D767">
+        <v>69.4158</v>
+      </c>
+      <c r="E767">
+        <v>73.8</v>
+      </c>
+      <c r="F767">
+        <v>0.06315900000000001</v>
+      </c>
+      <c r="G767">
+        <v>6.32</v>
+      </c>
+      <c r="H767" t="s">
+        <v>36</v>
+      </c>
+      <c r="I767">
+        <v>62</v>
+      </c>
+      <c r="J767">
+        <v>4303.78</v>
+      </c>
+      <c r="K767">
+        <v>4575.6</v>
+      </c>
+      <c r="L767">
+        <v>271.82</v>
+      </c>
+      <c r="M767" t="s">
+        <v>25</v>
+      </c>
+      <c r="N767">
+        <v>62</v>
+      </c>
+      <c r="O767">
+        <v>4303.7796</v>
+      </c>
+      <c r="P767">
+        <v>4575.599999999999</v>
+      </c>
+    </row>
+    <row r="768" spans="1:16">
+      <c r="A768" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B768" t="s">
+        <v>26</v>
+      </c>
+      <c r="C768" t="s">
+        <v>37</v>
+      </c>
+      <c r="D768">
+        <v>8.1868</v>
+      </c>
+      <c r="E768">
+        <v>8.756</v>
+      </c>
+      <c r="F768">
+        <v>0.06952700000000001</v>
+      </c>
+      <c r="G768">
+        <v>6.95</v>
+      </c>
+      <c r="H768" t="s">
+        <v>37</v>
+      </c>
+      <c r="I768">
+        <v>431</v>
+      </c>
+      <c r="J768">
+        <v>3528.51</v>
+      </c>
+      <c r="K768">
+        <v>3773.84</v>
+      </c>
+      <c r="L768">
+        <v>245.33</v>
+      </c>
+      <c r="M768" t="s">
+        <v>26</v>
+      </c>
+      <c r="N768">
+        <v>431</v>
+      </c>
+      <c r="O768">
+        <v>3528.5108</v>
+      </c>
+      <c r="P768">
+        <v>3773.836</v>
       </c>
     </row>
   </sheetData>
@@ -34216,7 +34838,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -37082,6 +37704,47 @@
       </c>
       <c r="M70" s="2">
         <v>0.1340085648434515</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.041142</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0.064053</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0.204504</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.200509</v>
+      </c>
+      <c r="F71" s="2">
+        <v>0.01984</v>
+      </c>
+      <c r="G71" s="2">
+        <v>0.561983</v>
+      </c>
+      <c r="H71" s="2">
+        <v>0.102237</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0.146841</v>
+      </c>
+      <c r="J71" s="2">
+        <v>0.010291</v>
+      </c>
+      <c r="K71" s="2">
+        <v>0.06315900000000001</v>
+      </c>
+      <c r="L71" s="2">
+        <v>0.06952700000000001</v>
+      </c>
+      <c r="M71" s="2">
+        <v>0.1232250046921473</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2451" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -449,16 +449,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$71</c:f>
+              <c:f>grafico_dati!$B$2:$B$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -668,6 +671,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.041142</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.054324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -695,10 +701,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -908,16 +914,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$71</c:f>
+              <c:f>grafico_dati!$C$2:$C$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1127,6 +1136,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.064053</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.06933599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1154,10 +1166,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1367,16 +1379,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$71</c:f>
+              <c:f>grafico_dati!$D$2:$D$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1586,6 +1601,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.204504</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.200455</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1613,10 +1631,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1826,16 +1844,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$71</c:f>
+              <c:f>grafico_dati!$E$2:$E$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2045,6 +2066,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.200509</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.191469</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2072,10 +2096,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2285,16 +2309,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$71</c:f>
+              <c:f>grafico_dati!$F$2:$F$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2501,6 +2528,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.01984</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.009819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2528,10 +2558,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2741,16 +2771,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$71</c:f>
+              <c:f>grafico_dati!$G$2:$G$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2960,6 +2993,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.561983</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.549462</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2987,10 +3023,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3200,16 +3236,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$71</c:f>
+              <c:f>grafico_dati!$H$2:$H$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3419,6 +3458,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.102237</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.082332</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3446,10 +3488,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3659,16 +3701,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$71</c:f>
+              <c:f>grafico_dati!$I$2:$I$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3875,6 +3920,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.146841</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.145934</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3902,10 +3950,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4115,16 +4163,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$71</c:f>
+              <c:f>grafico_dati!$J$2:$J$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4334,6 +4385,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.010291</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.014987</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4361,10 +4415,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4574,16 +4628,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$71</c:f>
+              <c:f>grafico_dati!$K$2:$K$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4790,6 +4847,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.06315900000000001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.06618400000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4817,10 +4877,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5030,16 +5090,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$71</c:f>
+              <c:f>grafico_dati!$L$2:$L$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5249,6 +5312,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.06952700000000001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.070992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5280,10 +5346,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$71</c:f>
+              <c:f>grafico_dati!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5493,16 +5559,19 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$71</c:f>
+              <c:f>grafico_dati!$M$2:$M$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5712,6 +5781,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.1232250046921473</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.1221587030198876</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6118,7 +6190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P768"/>
+  <dimension ref="A1:P779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -34829,6 +34901,556 @@
       </c>
       <c r="P768">
         <v>3773.836</v>
+      </c>
+    </row>
+    <row r="769" spans="1:16">
+      <c r="A769" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B769" t="s">
+        <v>16</v>
+      </c>
+      <c r="C769" t="s">
+        <v>27</v>
+      </c>
+      <c r="D769">
+        <v>50.07</v>
+      </c>
+      <c r="E769">
+        <v>52.79</v>
+      </c>
+      <c r="F769">
+        <v>0.054324</v>
+      </c>
+      <c r="G769">
+        <v>5.43</v>
+      </c>
+      <c r="H769" t="s">
+        <v>27</v>
+      </c>
+      <c r="I769">
+        <v>23</v>
+      </c>
+      <c r="J769">
+        <v>1151.61</v>
+      </c>
+      <c r="K769">
+        <v>1214.17</v>
+      </c>
+      <c r="L769">
+        <v>62.56</v>
+      </c>
+      <c r="M769" t="s">
+        <v>16</v>
+      </c>
+      <c r="N769">
+        <v>23</v>
+      </c>
+      <c r="O769">
+        <v>1151.61</v>
+      </c>
+      <c r="P769">
+        <v>1214.17</v>
+      </c>
+    </row>
+    <row r="770" spans="1:16">
+      <c r="A770" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B770" t="s">
+        <v>17</v>
+      </c>
+      <c r="C770" t="s">
+        <v>28</v>
+      </c>
+      <c r="D770">
+        <v>242.3</v>
+      </c>
+      <c r="E770">
+        <v>259.1</v>
+      </c>
+      <c r="F770">
+        <v>0.06933599999999999</v>
+      </c>
+      <c r="G770">
+        <v>6.93</v>
+      </c>
+      <c r="H770" t="s">
+        <v>28</v>
+      </c>
+      <c r="I770">
+        <v>5</v>
+      </c>
+      <c r="J770">
+        <v>1211.5</v>
+      </c>
+      <c r="K770">
+        <v>1295.5</v>
+      </c>
+      <c r="L770">
+        <v>84</v>
+      </c>
+      <c r="M770" t="s">
+        <v>17</v>
+      </c>
+      <c r="N770">
+        <v>5</v>
+      </c>
+      <c r="O770">
+        <v>1211.5</v>
+      </c>
+      <c r="P770">
+        <v>1295.5</v>
+      </c>
+    </row>
+    <row r="771" spans="1:16">
+      <c r="A771" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B771" t="s">
+        <v>18</v>
+      </c>
+      <c r="C771" t="s">
+        <v>29</v>
+      </c>
+      <c r="D771">
+        <v>38.273</v>
+      </c>
+      <c r="E771">
+        <v>45.945</v>
+      </c>
+      <c r="F771">
+        <v>0.200455</v>
+      </c>
+      <c r="G771">
+        <v>20.05</v>
+      </c>
+      <c r="H771" t="s">
+        <v>29</v>
+      </c>
+      <c r="I771">
+        <v>54</v>
+      </c>
+      <c r="J771">
+        <v>2066.74</v>
+      </c>
+      <c r="K771">
+        <v>2481.03</v>
+      </c>
+      <c r="L771">
+        <v>414.29</v>
+      </c>
+      <c r="M771" t="s">
+        <v>18</v>
+      </c>
+      <c r="N771">
+        <v>54</v>
+      </c>
+      <c r="O771">
+        <v>2066.742</v>
+      </c>
+      <c r="P771">
+        <v>2481.03</v>
+      </c>
+    </row>
+    <row r="772" spans="1:16">
+      <c r="A772" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B772" t="s">
+        <v>19</v>
+      </c>
+      <c r="C772" t="s">
+        <v>30</v>
+      </c>
+      <c r="D772">
+        <v>6.5264</v>
+      </c>
+      <c r="E772">
+        <v>7.776</v>
+      </c>
+      <c r="F772">
+        <v>0.191469</v>
+      </c>
+      <c r="G772">
+        <v>19.15</v>
+      </c>
+      <c r="H772" t="s">
+        <v>30</v>
+      </c>
+      <c r="I772">
+        <v>276</v>
+      </c>
+      <c r="J772">
+        <v>1801.29</v>
+      </c>
+      <c r="K772">
+        <v>2146.18</v>
+      </c>
+      <c r="L772">
+        <v>344.89</v>
+      </c>
+      <c r="M772" t="s">
+        <v>19</v>
+      </c>
+      <c r="N772">
+        <v>276</v>
+      </c>
+      <c r="O772">
+        <v>1801.2864</v>
+      </c>
+      <c r="P772">
+        <v>2146.176</v>
+      </c>
+    </row>
+    <row r="773" spans="1:16">
+      <c r="A773" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B773" t="s">
+        <v>20</v>
+      </c>
+      <c r="C773" t="s">
+        <v>31</v>
+      </c>
+      <c r="D773">
+        <v>197.58</v>
+      </c>
+      <c r="E773">
+        <v>199.52</v>
+      </c>
+      <c r="F773">
+        <v>0.009819</v>
+      </c>
+      <c r="G773">
+        <v>0.98</v>
+      </c>
+      <c r="H773" t="s">
+        <v>31</v>
+      </c>
+      <c r="I773">
+        <v>4</v>
+      </c>
+      <c r="J773">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K773">
+        <v>798.08</v>
+      </c>
+      <c r="L773">
+        <v>7.76</v>
+      </c>
+      <c r="M773" t="s">
+        <v>20</v>
+      </c>
+      <c r="N773">
+        <v>4</v>
+      </c>
+      <c r="O773">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P773">
+        <v>798.08</v>
+      </c>
+    </row>
+    <row r="774" spans="1:16">
+      <c r="A774" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B774" t="s">
+        <v>21</v>
+      </c>
+      <c r="C774" t="s">
+        <v>32</v>
+      </c>
+      <c r="D774">
+        <v>79.86</v>
+      </c>
+      <c r="E774">
+        <v>123.74</v>
+      </c>
+      <c r="F774">
+        <v>0.549462</v>
+      </c>
+      <c r="G774">
+        <v>54.95</v>
+      </c>
+      <c r="H774" t="s">
+        <v>32</v>
+      </c>
+      <c r="I774">
+        <v>12</v>
+      </c>
+      <c r="J774">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K774">
+        <v>1484.88</v>
+      </c>
+      <c r="L774">
+        <v>526.5599999999999</v>
+      </c>
+      <c r="M774" t="s">
+        <v>21</v>
+      </c>
+      <c r="N774">
+        <v>12</v>
+      </c>
+      <c r="O774">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P774">
+        <v>1484.88</v>
+      </c>
+    </row>
+    <row r="775" spans="1:16">
+      <c r="A775" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B775" t="s">
+        <v>22</v>
+      </c>
+      <c r="C775" t="s">
+        <v>33</v>
+      </c>
+      <c r="D775">
+        <v>19.7444</v>
+      </c>
+      <c r="E775">
+        <v>21.37</v>
+      </c>
+      <c r="F775">
+        <v>0.082332</v>
+      </c>
+      <c r="G775">
+        <v>8.23</v>
+      </c>
+      <c r="H775" t="s">
+        <v>33</v>
+      </c>
+      <c r="I775">
+        <v>61</v>
+      </c>
+      <c r="J775">
+        <v>1204.41</v>
+      </c>
+      <c r="K775">
+        <v>1303.57</v>
+      </c>
+      <c r="L775">
+        <v>99.16</v>
+      </c>
+      <c r="M775" t="s">
+        <v>22</v>
+      </c>
+      <c r="N775">
+        <v>61</v>
+      </c>
+      <c r="O775">
+        <v>1204.4084</v>
+      </c>
+      <c r="P775">
+        <v>1303.57</v>
+      </c>
+    </row>
+    <row r="776" spans="1:16">
+      <c r="A776" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B776" t="s">
+        <v>23</v>
+      </c>
+      <c r="C776" t="s">
+        <v>34</v>
+      </c>
+      <c r="D776">
+        <v>132.3898</v>
+      </c>
+      <c r="E776">
+        <v>151.71</v>
+      </c>
+      <c r="F776">
+        <v>0.145934</v>
+      </c>
+      <c r="G776">
+        <v>14.59</v>
+      </c>
+      <c r="H776" t="s">
+        <v>34</v>
+      </c>
+      <c r="I776">
+        <v>57</v>
+      </c>
+      <c r="J776">
+        <v>7546.22</v>
+      </c>
+      <c r="K776">
+        <v>8647.469999999999</v>
+      </c>
+      <c r="L776">
+        <v>1101.25</v>
+      </c>
+      <c r="M776" t="s">
+        <v>23</v>
+      </c>
+      <c r="N776">
+        <v>57</v>
+      </c>
+      <c r="O776">
+        <v>7546.2186</v>
+      </c>
+      <c r="P776">
+        <v>8647.470000000001</v>
+      </c>
+    </row>
+    <row r="777" spans="1:16">
+      <c r="A777" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B777" t="s">
+        <v>24</v>
+      </c>
+      <c r="C777" t="s">
+        <v>35</v>
+      </c>
+      <c r="D777">
+        <v>34.0694</v>
+      </c>
+      <c r="E777">
+        <v>34.58</v>
+      </c>
+      <c r="F777">
+        <v>0.014987</v>
+      </c>
+      <c r="G777">
+        <v>1.5</v>
+      </c>
+      <c r="H777" t="s">
+        <v>35</v>
+      </c>
+      <c r="I777">
+        <v>48</v>
+      </c>
+      <c r="J777">
+        <v>1635.33</v>
+      </c>
+      <c r="K777">
+        <v>1659.84</v>
+      </c>
+      <c r="L777">
+        <v>24.51</v>
+      </c>
+      <c r="M777" t="s">
+        <v>24</v>
+      </c>
+      <c r="N777">
+        <v>48</v>
+      </c>
+      <c r="O777">
+        <v>1635.3312</v>
+      </c>
+      <c r="P777">
+        <v>1659.84</v>
+      </c>
+    </row>
+    <row r="778" spans="1:16">
+      <c r="A778" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B778" t="s">
+        <v>25</v>
+      </c>
+      <c r="C778" t="s">
+        <v>36</v>
+      </c>
+      <c r="D778">
+        <v>69.4158</v>
+      </c>
+      <c r="E778">
+        <v>74.01000000000001</v>
+      </c>
+      <c r="F778">
+        <v>0.06618400000000001</v>
+      </c>
+      <c r="G778">
+        <v>6.62</v>
+      </c>
+      <c r="H778" t="s">
+        <v>36</v>
+      </c>
+      <c r="I778">
+        <v>62</v>
+      </c>
+      <c r="J778">
+        <v>4303.78</v>
+      </c>
+      <c r="K778">
+        <v>4588.62</v>
+      </c>
+      <c r="L778">
+        <v>284.84</v>
+      </c>
+      <c r="M778" t="s">
+        <v>25</v>
+      </c>
+      <c r="N778">
+        <v>62</v>
+      </c>
+      <c r="O778">
+        <v>4303.7796</v>
+      </c>
+      <c r="P778">
+        <v>4588.62</v>
+      </c>
+    </row>
+    <row r="779" spans="1:16">
+      <c r="A779" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B779" t="s">
+        <v>26</v>
+      </c>
+      <c r="C779" t="s">
+        <v>37</v>
+      </c>
+      <c r="D779">
+        <v>8.1868</v>
+      </c>
+      <c r="E779">
+        <v>8.768000000000001</v>
+      </c>
+      <c r="F779">
+        <v>0.070992</v>
+      </c>
+      <c r="G779">
+        <v>7.1</v>
+      </c>
+      <c r="H779" t="s">
+        <v>37</v>
+      </c>
+      <c r="I779">
+        <v>431</v>
+      </c>
+      <c r="J779">
+        <v>3528.51</v>
+      </c>
+      <c r="K779">
+        <v>3779.01</v>
+      </c>
+      <c r="L779">
+        <v>250.5</v>
+      </c>
+      <c r="M779" t="s">
+        <v>26</v>
+      </c>
+      <c r="N779">
+        <v>431</v>
+      </c>
+      <c r="O779">
+        <v>3528.5108</v>
+      </c>
+      <c r="P779">
+        <v>3779.008</v>
       </c>
     </row>
   </sheetData>
@@ -34838,7 +35460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -37745,6 +38367,47 @@
       </c>
       <c r="M71" s="2">
         <v>0.1232250046921473</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.054324</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0.06933599999999999</v>
+      </c>
+      <c r="D72" s="2">
+        <v>0.200455</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0.191469</v>
+      </c>
+      <c r="F72" s="2">
+        <v>0.009819</v>
+      </c>
+      <c r="G72" s="2">
+        <v>0.549462</v>
+      </c>
+      <c r="H72" s="2">
+        <v>0.082332</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0.145934</v>
+      </c>
+      <c r="J72" s="2">
+        <v>0.014987</v>
+      </c>
+      <c r="K72" s="2">
+        <v>0.06618400000000001</v>
+      </c>
+      <c r="L72" s="2">
+        <v>0.070992</v>
+      </c>
+      <c r="M72" s="2">
+        <v>0.1221587030198876</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -452,16 +452,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$72</c:f>
+              <c:f>grafico_dati!$B$2:$B$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -674,6 +677,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.054324</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.05692</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -701,10 +707,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -917,16 +923,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$72</c:f>
+              <c:f>grafico_dati!$C$2:$C$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1139,6 +1148,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.06933599999999999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.07106899999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1166,10 +1178,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1382,16 +1394,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$72</c:f>
+              <c:f>grafico_dati!$D$2:$D$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1604,6 +1619,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.200455</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.212996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1631,10 +1649,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1847,16 +1865,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$72</c:f>
+              <c:f>grafico_dati!$E$2:$E$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2069,6 +2090,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.191469</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.211081</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2096,10 +2120,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2312,16 +2336,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$72</c:f>
+              <c:f>grafico_dati!$F$2:$F$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2531,6 +2558,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.009819</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.011438</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2558,10 +2588,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2774,16 +2804,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$72</c:f>
+              <c:f>grafico_dati!$G$2:$G$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -2996,6 +3029,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.549462</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.572251</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3023,10 +3059,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3239,16 +3275,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$72</c:f>
+              <c:f>grafico_dati!$H$2:$H$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3461,6 +3500,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.082332</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.09393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3488,10 +3530,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3704,16 +3746,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$72</c:f>
+              <c:f>grafico_dati!$I$2:$I$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3923,6 +3968,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.145934</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.14669</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3950,10 +3998,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4166,16 +4214,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$72</c:f>
+              <c:f>grafico_dati!$J$2:$J$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4388,6 +4439,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.014987</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.022178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4415,10 +4469,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4631,16 +4685,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$72</c:f>
+              <c:f>grafico_dati!$K$2:$K$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4850,6 +4907,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.06618400000000001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.071226</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4877,10 +4937,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5093,16 +5153,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$72</c:f>
+              <c:f>grafico_dati!$L$2:$L$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5315,6 +5378,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.070992</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.076978</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5346,10 +5412,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$72</c:f>
+              <c:f>grafico_dati!$A$2:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5562,16 +5628,19 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$72</c:f>
+              <c:f>grafico_dati!$M$2:$M$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5784,6 +5853,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0.1221587030198876</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.1284074941979407</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6190,7 +6262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P779"/>
+  <dimension ref="A1:P790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -35451,6 +35523,556 @@
       </c>
       <c r="P779">
         <v>3779.008</v>
+      </c>
+    </row>
+    <row r="780" spans="1:16">
+      <c r="A780" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B780" t="s">
+        <v>16</v>
+      </c>
+      <c r="C780" t="s">
+        <v>27</v>
+      </c>
+      <c r="D780">
+        <v>50.07</v>
+      </c>
+      <c r="E780">
+        <v>52.92</v>
+      </c>
+      <c r="F780">
+        <v>0.05692</v>
+      </c>
+      <c r="G780">
+        <v>5.69</v>
+      </c>
+      <c r="H780" t="s">
+        <v>27</v>
+      </c>
+      <c r="I780">
+        <v>23</v>
+      </c>
+      <c r="J780">
+        <v>1151.61</v>
+      </c>
+      <c r="K780">
+        <v>1217.16</v>
+      </c>
+      <c r="L780">
+        <v>65.55</v>
+      </c>
+      <c r="M780" t="s">
+        <v>16</v>
+      </c>
+      <c r="N780">
+        <v>23</v>
+      </c>
+      <c r="O780">
+        <v>1151.61</v>
+      </c>
+      <c r="P780">
+        <v>1217.16</v>
+      </c>
+    </row>
+    <row r="781" spans="1:16">
+      <c r="A781" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B781" t="s">
+        <v>17</v>
+      </c>
+      <c r="C781" t="s">
+        <v>28</v>
+      </c>
+      <c r="D781">
+        <v>242.3</v>
+      </c>
+      <c r="E781">
+        <v>259.52</v>
+      </c>
+      <c r="F781">
+        <v>0.07106899999999999</v>
+      </c>
+      <c r="G781">
+        <v>7.11</v>
+      </c>
+      <c r="H781" t="s">
+        <v>28</v>
+      </c>
+      <c r="I781">
+        <v>5</v>
+      </c>
+      <c r="J781">
+        <v>1211.5</v>
+      </c>
+      <c r="K781">
+        <v>1297.6</v>
+      </c>
+      <c r="L781">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M781" t="s">
+        <v>17</v>
+      </c>
+      <c r="N781">
+        <v>5</v>
+      </c>
+      <c r="O781">
+        <v>1211.5</v>
+      </c>
+      <c r="P781">
+        <v>1297.6</v>
+      </c>
+    </row>
+    <row r="782" spans="1:16">
+      <c r="A782" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B782" t="s">
+        <v>18</v>
+      </c>
+      <c r="C782" t="s">
+        <v>29</v>
+      </c>
+      <c r="D782">
+        <v>38.273</v>
+      </c>
+      <c r="E782">
+        <v>46.425</v>
+      </c>
+      <c r="F782">
+        <v>0.212996</v>
+      </c>
+      <c r="G782">
+        <v>21.3</v>
+      </c>
+      <c r="H782" t="s">
+        <v>29</v>
+      </c>
+      <c r="I782">
+        <v>54</v>
+      </c>
+      <c r="J782">
+        <v>2066.74</v>
+      </c>
+      <c r="K782">
+        <v>2506.95</v>
+      </c>
+      <c r="L782">
+        <v>440.21</v>
+      </c>
+      <c r="M782" t="s">
+        <v>18</v>
+      </c>
+      <c r="N782">
+        <v>54</v>
+      </c>
+      <c r="O782">
+        <v>2066.742</v>
+      </c>
+      <c r="P782">
+        <v>2506.95</v>
+      </c>
+    </row>
+    <row r="783" spans="1:16">
+      <c r="A783" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B783" t="s">
+        <v>19</v>
+      </c>
+      <c r="C783" t="s">
+        <v>30</v>
+      </c>
+      <c r="D783">
+        <v>6.5264</v>
+      </c>
+      <c r="E783">
+        <v>7.904</v>
+      </c>
+      <c r="F783">
+        <v>0.211081</v>
+      </c>
+      <c r="G783">
+        <v>21.11</v>
+      </c>
+      <c r="H783" t="s">
+        <v>30</v>
+      </c>
+      <c r="I783">
+        <v>276</v>
+      </c>
+      <c r="J783">
+        <v>1801.29</v>
+      </c>
+      <c r="K783">
+        <v>2181.5</v>
+      </c>
+      <c r="L783">
+        <v>380.22</v>
+      </c>
+      <c r="M783" t="s">
+        <v>19</v>
+      </c>
+      <c r="N783">
+        <v>276</v>
+      </c>
+      <c r="O783">
+        <v>1801.2864</v>
+      </c>
+      <c r="P783">
+        <v>2181.504</v>
+      </c>
+    </row>
+    <row r="784" spans="1:16">
+      <c r="A784" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B784" t="s">
+        <v>20</v>
+      </c>
+      <c r="C784" t="s">
+        <v>31</v>
+      </c>
+      <c r="D784">
+        <v>197.58</v>
+      </c>
+      <c r="E784">
+        <v>199.84</v>
+      </c>
+      <c r="F784">
+        <v>0.011438</v>
+      </c>
+      <c r="G784">
+        <v>1.14</v>
+      </c>
+      <c r="H784" t="s">
+        <v>31</v>
+      </c>
+      <c r="I784">
+        <v>4</v>
+      </c>
+      <c r="J784">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K784">
+        <v>799.36</v>
+      </c>
+      <c r="L784">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="M784" t="s">
+        <v>20</v>
+      </c>
+      <c r="N784">
+        <v>4</v>
+      </c>
+      <c r="O784">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P784">
+        <v>799.36</v>
+      </c>
+    </row>
+    <row r="785" spans="1:16">
+      <c r="A785" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B785" t="s">
+        <v>21</v>
+      </c>
+      <c r="C785" t="s">
+        <v>32</v>
+      </c>
+      <c r="D785">
+        <v>79.86</v>
+      </c>
+      <c r="E785">
+        <v>125.56</v>
+      </c>
+      <c r="F785">
+        <v>0.572251</v>
+      </c>
+      <c r="G785">
+        <v>57.23</v>
+      </c>
+      <c r="H785" t="s">
+        <v>32</v>
+      </c>
+      <c r="I785">
+        <v>12</v>
+      </c>
+      <c r="J785">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K785">
+        <v>1506.72</v>
+      </c>
+      <c r="L785">
+        <v>548.4</v>
+      </c>
+      <c r="M785" t="s">
+        <v>21</v>
+      </c>
+      <c r="N785">
+        <v>12</v>
+      </c>
+      <c r="O785">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P785">
+        <v>1506.72</v>
+      </c>
+    </row>
+    <row r="786" spans="1:16">
+      <c r="A786" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B786" t="s">
+        <v>22</v>
+      </c>
+      <c r="C786" t="s">
+        <v>33</v>
+      </c>
+      <c r="D786">
+        <v>19.7444</v>
+      </c>
+      <c r="E786">
+        <v>21.599</v>
+      </c>
+      <c r="F786">
+        <v>0.09393</v>
+      </c>
+      <c r="G786">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="H786" t="s">
+        <v>33</v>
+      </c>
+      <c r="I786">
+        <v>61</v>
+      </c>
+      <c r="J786">
+        <v>1204.41</v>
+      </c>
+      <c r="K786">
+        <v>1317.54</v>
+      </c>
+      <c r="L786">
+        <v>113.13</v>
+      </c>
+      <c r="M786" t="s">
+        <v>22</v>
+      </c>
+      <c r="N786">
+        <v>61</v>
+      </c>
+      <c r="O786">
+        <v>1204.4084</v>
+      </c>
+      <c r="P786">
+        <v>1317.539</v>
+      </c>
+    </row>
+    <row r="787" spans="1:16">
+      <c r="A787" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B787" t="s">
+        <v>23</v>
+      </c>
+      <c r="C787" t="s">
+        <v>34</v>
+      </c>
+      <c r="D787">
+        <v>132.3898</v>
+      </c>
+      <c r="E787">
+        <v>151.81</v>
+      </c>
+      <c r="F787">
+        <v>0.14669</v>
+      </c>
+      <c r="G787">
+        <v>14.67</v>
+      </c>
+      <c r="H787" t="s">
+        <v>34</v>
+      </c>
+      <c r="I787">
+        <v>57</v>
+      </c>
+      <c r="J787">
+        <v>7546.22</v>
+      </c>
+      <c r="K787">
+        <v>8653.17</v>
+      </c>
+      <c r="L787">
+        <v>1106.95</v>
+      </c>
+      <c r="M787" t="s">
+        <v>23</v>
+      </c>
+      <c r="N787">
+        <v>57</v>
+      </c>
+      <c r="O787">
+        <v>7546.2186</v>
+      </c>
+      <c r="P787">
+        <v>8653.17</v>
+      </c>
+    </row>
+    <row r="788" spans="1:16">
+      <c r="A788" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B788" t="s">
+        <v>24</v>
+      </c>
+      <c r="C788" t="s">
+        <v>35</v>
+      </c>
+      <c r="D788">
+        <v>34.0694</v>
+      </c>
+      <c r="E788">
+        <v>34.825</v>
+      </c>
+      <c r="F788">
+        <v>0.022178</v>
+      </c>
+      <c r="G788">
+        <v>2.22</v>
+      </c>
+      <c r="H788" t="s">
+        <v>35</v>
+      </c>
+      <c r="I788">
+        <v>48</v>
+      </c>
+      <c r="J788">
+        <v>1635.33</v>
+      </c>
+      <c r="K788">
+        <v>1671.6</v>
+      </c>
+      <c r="L788">
+        <v>36.27</v>
+      </c>
+      <c r="M788" t="s">
+        <v>24</v>
+      </c>
+      <c r="N788">
+        <v>48</v>
+      </c>
+      <c r="O788">
+        <v>1635.3312</v>
+      </c>
+      <c r="P788">
+        <v>1671.6</v>
+      </c>
+    </row>
+    <row r="789" spans="1:16">
+      <c r="A789" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B789" t="s">
+        <v>25</v>
+      </c>
+      <c r="C789" t="s">
+        <v>36</v>
+      </c>
+      <c r="D789">
+        <v>69.4158</v>
+      </c>
+      <c r="E789">
+        <v>74.36</v>
+      </c>
+      <c r="F789">
+        <v>0.071226</v>
+      </c>
+      <c r="G789">
+        <v>7.12</v>
+      </c>
+      <c r="H789" t="s">
+        <v>36</v>
+      </c>
+      <c r="I789">
+        <v>62</v>
+      </c>
+      <c r="J789">
+        <v>4303.78</v>
+      </c>
+      <c r="K789">
+        <v>4610.32</v>
+      </c>
+      <c r="L789">
+        <v>306.54</v>
+      </c>
+      <c r="M789" t="s">
+        <v>25</v>
+      </c>
+      <c r="N789">
+        <v>62</v>
+      </c>
+      <c r="O789">
+        <v>4303.7796</v>
+      </c>
+      <c r="P789">
+        <v>4610.32</v>
+      </c>
+    </row>
+    <row r="790" spans="1:16">
+      <c r="A790" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B790" t="s">
+        <v>26</v>
+      </c>
+      <c r="C790" t="s">
+        <v>37</v>
+      </c>
+      <c r="D790">
+        <v>8.1868</v>
+      </c>
+      <c r="E790">
+        <v>8.817</v>
+      </c>
+      <c r="F790">
+        <v>0.076978</v>
+      </c>
+      <c r="G790">
+        <v>7.7</v>
+      </c>
+      <c r="H790" t="s">
+        <v>37</v>
+      </c>
+      <c r="I790">
+        <v>431</v>
+      </c>
+      <c r="J790">
+        <v>3528.51</v>
+      </c>
+      <c r="K790">
+        <v>3800.13</v>
+      </c>
+      <c r="L790">
+        <v>271.62</v>
+      </c>
+      <c r="M790" t="s">
+        <v>26</v>
+      </c>
+      <c r="N790">
+        <v>431</v>
+      </c>
+      <c r="O790">
+        <v>3528.5108</v>
+      </c>
+      <c r="P790">
+        <v>3800.127</v>
       </c>
     </row>
   </sheetData>
@@ -35460,7 +36082,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -38408,6 +39030,47 @@
       </c>
       <c r="M72" s="2">
         <v>0.1221587030198876</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.05692</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0.07106899999999999</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0.212996</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.211081</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0.011438</v>
+      </c>
+      <c r="G73" s="2">
+        <v>0.572251</v>
+      </c>
+      <c r="H73" s="2">
+        <v>0.09393</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0.14669</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0.022178</v>
+      </c>
+      <c r="K73" s="2">
+        <v>0.071226</v>
+      </c>
+      <c r="L73" s="2">
+        <v>0.076978</v>
+      </c>
+      <c r="M73" s="2">
+        <v>0.1284074941979407</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -455,16 +455,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$73</c:f>
+              <c:f>grafico_dati!$B$2:$B$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -680,6 +683,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.05692</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.082485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -707,10 +713,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -926,16 +932,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$73</c:f>
+              <c:f>grafico_dati!$C$2:$C$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1151,6 +1160,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.07106899999999999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.08695799999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1178,10 +1190,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1397,16 +1409,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$73</c:f>
+              <c:f>grafico_dati!$D$2:$D$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1622,6 +1637,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.212996</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.25049</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1649,10 +1667,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1868,16 +1886,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$73</c:f>
+              <c:f>grafico_dati!$E$2:$E$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2093,6 +2114,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.211081</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.255516</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2120,10 +2144,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2339,16 +2363,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$73</c:f>
+              <c:f>grafico_dati!$F$2:$F$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2561,6 +2588,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.011438</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.028444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2588,10 +2618,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2807,16 +2837,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$73</c:f>
+              <c:f>grafico_dati!$G$2:$G$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -3032,6 +3065,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.572251</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.603556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3059,10 +3095,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3278,16 +3314,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$73</c:f>
+              <c:f>grafico_dati!$H$2:$H$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3503,6 +3542,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.09393</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.121027</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3530,10 +3572,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3749,16 +3791,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$73</c:f>
+              <c:f>grafico_dati!$I$2:$I$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -3971,6 +4016,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.14669</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.164969</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3998,10 +4046,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4217,16 +4265,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$73</c:f>
+              <c:f>grafico_dati!$J$2:$J$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4442,6 +4493,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.022178</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.03524</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4469,10 +4523,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4688,16 +4742,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$73</c:f>
+              <c:f>grafico_dati!$K$2:$K$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4910,6 +4967,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.071226</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.08433499999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4937,10 +4997,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5156,16 +5216,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$73</c:f>
+              <c:f>grafico_dati!$L$2:$L$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5381,6 +5444,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.076978</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.102629</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5412,10 +5478,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$73</c:f>
+              <c:f>grafico_dati!$A$2:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5631,16 +5697,19 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$73</c:f>
+              <c:f>grafico_dati!$M$2:$M$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5856,6 +5925,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>0.1284074941979407</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.1508719721527119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6262,7 +6334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P790"/>
+  <dimension ref="A1:P801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -36073,6 +36145,556 @@
       </c>
       <c r="P790">
         <v>3800.127</v>
+      </c>
+    </row>
+    <row r="791" spans="1:16">
+      <c r="A791" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B791" t="s">
+        <v>16</v>
+      </c>
+      <c r="C791" t="s">
+        <v>27</v>
+      </c>
+      <c r="D791">
+        <v>50.07</v>
+      </c>
+      <c r="E791">
+        <v>54.2</v>
+      </c>
+      <c r="F791">
+        <v>0.082485</v>
+      </c>
+      <c r="G791">
+        <v>8.25</v>
+      </c>
+      <c r="H791" t="s">
+        <v>27</v>
+      </c>
+      <c r="I791">
+        <v>23</v>
+      </c>
+      <c r="J791">
+        <v>1151.61</v>
+      </c>
+      <c r="K791">
+        <v>1246.6</v>
+      </c>
+      <c r="L791">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="M791" t="s">
+        <v>16</v>
+      </c>
+      <c r="N791">
+        <v>23</v>
+      </c>
+      <c r="O791">
+        <v>1151.61</v>
+      </c>
+      <c r="P791">
+        <v>1246.6</v>
+      </c>
+    </row>
+    <row r="792" spans="1:16">
+      <c r="A792" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B792" t="s">
+        <v>17</v>
+      </c>
+      <c r="C792" t="s">
+        <v>28</v>
+      </c>
+      <c r="D792">
+        <v>242.3</v>
+      </c>
+      <c r="E792">
+        <v>263.37</v>
+      </c>
+      <c r="F792">
+        <v>0.08695799999999999</v>
+      </c>
+      <c r="G792">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H792" t="s">
+        <v>28</v>
+      </c>
+      <c r="I792">
+        <v>5</v>
+      </c>
+      <c r="J792">
+        <v>1211.5</v>
+      </c>
+      <c r="K792">
+        <v>1316.85</v>
+      </c>
+      <c r="L792">
+        <v>105.35</v>
+      </c>
+      <c r="M792" t="s">
+        <v>17</v>
+      </c>
+      <c r="N792">
+        <v>5</v>
+      </c>
+      <c r="O792">
+        <v>1211.5</v>
+      </c>
+      <c r="P792">
+        <v>1316.85</v>
+      </c>
+    </row>
+    <row r="793" spans="1:16">
+      <c r="A793" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B793" t="s">
+        <v>18</v>
+      </c>
+      <c r="C793" t="s">
+        <v>29</v>
+      </c>
+      <c r="D793">
+        <v>38.273</v>
+      </c>
+      <c r="E793">
+        <v>47.86</v>
+      </c>
+      <c r="F793">
+        <v>0.25049</v>
+      </c>
+      <c r="G793">
+        <v>25.05</v>
+      </c>
+      <c r="H793" t="s">
+        <v>29</v>
+      </c>
+      <c r="I793">
+        <v>54</v>
+      </c>
+      <c r="J793">
+        <v>2066.74</v>
+      </c>
+      <c r="K793">
+        <v>2584.44</v>
+      </c>
+      <c r="L793">
+        <v>517.7</v>
+      </c>
+      <c r="M793" t="s">
+        <v>18</v>
+      </c>
+      <c r="N793">
+        <v>54</v>
+      </c>
+      <c r="O793">
+        <v>2066.742</v>
+      </c>
+      <c r="P793">
+        <v>2584.44</v>
+      </c>
+    </row>
+    <row r="794" spans="1:16">
+      <c r="A794" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B794" t="s">
+        <v>19</v>
+      </c>
+      <c r="C794" t="s">
+        <v>30</v>
+      </c>
+      <c r="D794">
+        <v>6.5264</v>
+      </c>
+      <c r="E794">
+        <v>8.194000000000001</v>
+      </c>
+      <c r="F794">
+        <v>0.255516</v>
+      </c>
+      <c r="G794">
+        <v>25.55</v>
+      </c>
+      <c r="H794" t="s">
+        <v>30</v>
+      </c>
+      <c r="I794">
+        <v>276</v>
+      </c>
+      <c r="J794">
+        <v>1801.29</v>
+      </c>
+      <c r="K794">
+        <v>2261.54</v>
+      </c>
+      <c r="L794">
+        <v>460.26</v>
+      </c>
+      <c r="M794" t="s">
+        <v>19</v>
+      </c>
+      <c r="N794">
+        <v>276</v>
+      </c>
+      <c r="O794">
+        <v>1801.2864</v>
+      </c>
+      <c r="P794">
+        <v>2261.544</v>
+      </c>
+    </row>
+    <row r="795" spans="1:16">
+      <c r="A795" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B795" t="s">
+        <v>20</v>
+      </c>
+      <c r="C795" t="s">
+        <v>31</v>
+      </c>
+      <c r="D795">
+        <v>197.58</v>
+      </c>
+      <c r="E795">
+        <v>203.2</v>
+      </c>
+      <c r="F795">
+        <v>0.028444</v>
+      </c>
+      <c r="G795">
+        <v>2.84</v>
+      </c>
+      <c r="H795" t="s">
+        <v>31</v>
+      </c>
+      <c r="I795">
+        <v>4</v>
+      </c>
+      <c r="J795">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K795">
+        <v>812.8</v>
+      </c>
+      <c r="L795">
+        <v>22.48</v>
+      </c>
+      <c r="M795" t="s">
+        <v>20</v>
+      </c>
+      <c r="N795">
+        <v>4</v>
+      </c>
+      <c r="O795">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P795">
+        <v>812.8</v>
+      </c>
+    </row>
+    <row r="796" spans="1:16">
+      <c r="A796" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B796" t="s">
+        <v>21</v>
+      </c>
+      <c r="C796" t="s">
+        <v>32</v>
+      </c>
+      <c r="D796">
+        <v>79.86</v>
+      </c>
+      <c r="E796">
+        <v>128.06</v>
+      </c>
+      <c r="F796">
+        <v>0.603556</v>
+      </c>
+      <c r="G796">
+        <v>60.36</v>
+      </c>
+      <c r="H796" t="s">
+        <v>32</v>
+      </c>
+      <c r="I796">
+        <v>12</v>
+      </c>
+      <c r="J796">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K796">
+        <v>1536.72</v>
+      </c>
+      <c r="L796">
+        <v>578.4</v>
+      </c>
+      <c r="M796" t="s">
+        <v>21</v>
+      </c>
+      <c r="N796">
+        <v>12</v>
+      </c>
+      <c r="O796">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P796">
+        <v>1536.72</v>
+      </c>
+    </row>
+    <row r="797" spans="1:16">
+      <c r="A797" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B797" t="s">
+        <v>22</v>
+      </c>
+      <c r="C797" t="s">
+        <v>33</v>
+      </c>
+      <c r="D797">
+        <v>19.7444</v>
+      </c>
+      <c r="E797">
+        <v>22.134</v>
+      </c>
+      <c r="F797">
+        <v>0.121027</v>
+      </c>
+      <c r="G797">
+        <v>12.1</v>
+      </c>
+      <c r="H797" t="s">
+        <v>33</v>
+      </c>
+      <c r="I797">
+        <v>61</v>
+      </c>
+      <c r="J797">
+        <v>1204.41</v>
+      </c>
+      <c r="K797">
+        <v>1350.17</v>
+      </c>
+      <c r="L797">
+        <v>145.77</v>
+      </c>
+      <c r="M797" t="s">
+        <v>22</v>
+      </c>
+      <c r="N797">
+        <v>61</v>
+      </c>
+      <c r="O797">
+        <v>1204.4084</v>
+      </c>
+      <c r="P797">
+        <v>1350.174</v>
+      </c>
+    </row>
+    <row r="798" spans="1:16">
+      <c r="A798" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B798" t="s">
+        <v>23</v>
+      </c>
+      <c r="C798" t="s">
+        <v>34</v>
+      </c>
+      <c r="D798">
+        <v>132.3898</v>
+      </c>
+      <c r="E798">
+        <v>154.23</v>
+      </c>
+      <c r="F798">
+        <v>0.164969</v>
+      </c>
+      <c r="G798">
+        <v>16.5</v>
+      </c>
+      <c r="H798" t="s">
+        <v>34</v>
+      </c>
+      <c r="I798">
+        <v>57</v>
+      </c>
+      <c r="J798">
+        <v>7546.22</v>
+      </c>
+      <c r="K798">
+        <v>8791.110000000001</v>
+      </c>
+      <c r="L798">
+        <v>1244.89</v>
+      </c>
+      <c r="M798" t="s">
+        <v>23</v>
+      </c>
+      <c r="N798">
+        <v>57</v>
+      </c>
+      <c r="O798">
+        <v>7546.2186</v>
+      </c>
+      <c r="P798">
+        <v>8791.109999999999</v>
+      </c>
+    </row>
+    <row r="799" spans="1:16">
+      <c r="A799" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B799" t="s">
+        <v>24</v>
+      </c>
+      <c r="C799" t="s">
+        <v>35</v>
+      </c>
+      <c r="D799">
+        <v>34.0694</v>
+      </c>
+      <c r="E799">
+        <v>35.27</v>
+      </c>
+      <c r="F799">
+        <v>0.03524</v>
+      </c>
+      <c r="G799">
+        <v>3.52</v>
+      </c>
+      <c r="H799" t="s">
+        <v>35</v>
+      </c>
+      <c r="I799">
+        <v>48</v>
+      </c>
+      <c r="J799">
+        <v>1635.33</v>
+      </c>
+      <c r="K799">
+        <v>1692.96</v>
+      </c>
+      <c r="L799">
+        <v>57.63</v>
+      </c>
+      <c r="M799" t="s">
+        <v>24</v>
+      </c>
+      <c r="N799">
+        <v>48</v>
+      </c>
+      <c r="O799">
+        <v>1635.3312</v>
+      </c>
+      <c r="P799">
+        <v>1692.96</v>
+      </c>
+    </row>
+    <row r="800" spans="1:16">
+      <c r="A800" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B800" t="s">
+        <v>25</v>
+      </c>
+      <c r="C800" t="s">
+        <v>36</v>
+      </c>
+      <c r="D800">
+        <v>69.4158</v>
+      </c>
+      <c r="E800">
+        <v>75.27</v>
+      </c>
+      <c r="F800">
+        <v>0.08433499999999999</v>
+      </c>
+      <c r="G800">
+        <v>8.43</v>
+      </c>
+      <c r="H800" t="s">
+        <v>36</v>
+      </c>
+      <c r="I800">
+        <v>62</v>
+      </c>
+      <c r="J800">
+        <v>4303.78</v>
+      </c>
+      <c r="K800">
+        <v>4666.74</v>
+      </c>
+      <c r="L800">
+        <v>362.96</v>
+      </c>
+      <c r="M800" t="s">
+        <v>25</v>
+      </c>
+      <c r="N800">
+        <v>62</v>
+      </c>
+      <c r="O800">
+        <v>4303.7796</v>
+      </c>
+      <c r="P800">
+        <v>4666.74</v>
+      </c>
+    </row>
+    <row r="801" spans="1:16">
+      <c r="A801" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B801" t="s">
+        <v>26</v>
+      </c>
+      <c r="C801" t="s">
+        <v>37</v>
+      </c>
+      <c r="D801">
+        <v>8.1868</v>
+      </c>
+      <c r="E801">
+        <v>9.026999999999999</v>
+      </c>
+      <c r="F801">
+        <v>0.102629</v>
+      </c>
+      <c r="G801">
+        <v>10.26</v>
+      </c>
+      <c r="H801" t="s">
+        <v>37</v>
+      </c>
+      <c r="I801">
+        <v>431</v>
+      </c>
+      <c r="J801">
+        <v>3528.51</v>
+      </c>
+      <c r="K801">
+        <v>3890.64</v>
+      </c>
+      <c r="L801">
+        <v>362.13</v>
+      </c>
+      <c r="M801" t="s">
+        <v>26</v>
+      </c>
+      <c r="N801">
+        <v>431</v>
+      </c>
+      <c r="O801">
+        <v>3528.5108</v>
+      </c>
+      <c r="P801">
+        <v>3890.637</v>
       </c>
     </row>
   </sheetData>
@@ -36082,7 +36704,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -39071,6 +39693,47 @@
       </c>
       <c r="M73" s="2">
         <v>0.1284074941979407</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0.082485</v>
+      </c>
+      <c r="C74" s="2">
+        <v>0.08695799999999999</v>
+      </c>
+      <c r="D74" s="2">
+        <v>0.25049</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0.255516</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0.028444</v>
+      </c>
+      <c r="G74" s="2">
+        <v>0.603556</v>
+      </c>
+      <c r="H74" s="2">
+        <v>0.121027</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0.164969</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0.03524</v>
+      </c>
+      <c r="K74" s="2">
+        <v>0.08433499999999999</v>
+      </c>
+      <c r="L74" s="2">
+        <v>0.102629</v>
+      </c>
+      <c r="M74" s="2">
+        <v>0.1508719721527119</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2627" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -458,16 +458,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$74</c:f>
+              <c:f>grafico_dati!$B$2:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -686,6 +689,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.082485</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.079888</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -713,10 +719,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -935,16 +941,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$74</c:f>
+              <c:f>grafico_dati!$C$2:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1163,6 +1172,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.08695799999999999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.087619</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1190,10 +1202,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1412,16 +1424,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$74</c:f>
+              <c:f>grafico_dati!$D$2:$D$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1640,6 +1655,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.25049</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.283673</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1667,10 +1685,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1889,16 +1907,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$74</c:f>
+              <c:f>grafico_dati!$E$2:$E$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2117,6 +2138,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.255516</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.294435</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2144,10 +2168,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2366,16 +2390,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$74</c:f>
+              <c:f>grafico_dati!$F$2:$F$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2591,6 +2618,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.028444</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.039073</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2618,10 +2648,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2840,16 +2870,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$74</c:f>
+              <c:f>grafico_dati!$G$2:$G$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -3068,6 +3101,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.603556</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.62309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3095,10 +3131,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3317,16 +3353,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$74</c:f>
+              <c:f>grafico_dati!$H$2:$H$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3545,6 +3584,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.121027</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.137082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3572,10 +3614,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3794,16 +3836,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$74</c:f>
+              <c:f>grafico_dati!$I$2:$I$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -4019,6 +4064,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.164969</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.179094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4046,10 +4094,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4268,16 +4316,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$74</c:f>
+              <c:f>grafico_dati!$J$2:$J$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4496,6 +4547,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.03524</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.036854</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4523,10 +4577,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4745,16 +4799,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$74</c:f>
+              <c:f>grafico_dati!$K$2:$K$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -4970,6 +5027,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.08433499999999999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.093267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4997,10 +5057,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5219,16 +5279,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$74</c:f>
+              <c:f>grafico_dati!$L$2:$L$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5447,6 +5510,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.102629</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.110324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5478,10 +5544,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$74</c:f>
+              <c:f>grafico_dati!$A$2:$A$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5700,16 +5766,19 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$74</c:f>
+              <c:f>grafico_dati!$M$2:$M$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -5928,6 +5997,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0.1508719721527119</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.1645284967451937</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6334,7 +6406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P801"/>
+  <dimension ref="A1:P812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -36695,6 +36767,556 @@
       </c>
       <c r="P801">
         <v>3890.637</v>
+      </c>
+    </row>
+    <row r="802" spans="1:16">
+      <c r="A802" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B802" t="s">
+        <v>16</v>
+      </c>
+      <c r="C802" t="s">
+        <v>27</v>
+      </c>
+      <c r="D802">
+        <v>50.07</v>
+      </c>
+      <c r="E802">
+        <v>54.07</v>
+      </c>
+      <c r="F802">
+        <v>0.079888</v>
+      </c>
+      <c r="G802">
+        <v>7.99</v>
+      </c>
+      <c r="H802" t="s">
+        <v>27</v>
+      </c>
+      <c r="I802">
+        <v>23</v>
+      </c>
+      <c r="J802">
+        <v>1151.61</v>
+      </c>
+      <c r="K802">
+        <v>1243.61</v>
+      </c>
+      <c r="L802">
+        <v>92</v>
+      </c>
+      <c r="M802" t="s">
+        <v>16</v>
+      </c>
+      <c r="N802">
+        <v>23</v>
+      </c>
+      <c r="O802">
+        <v>1151.61</v>
+      </c>
+      <c r="P802">
+        <v>1243.61</v>
+      </c>
+    </row>
+    <row r="803" spans="1:16">
+      <c r="A803" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B803" t="s">
+        <v>17</v>
+      </c>
+      <c r="C803" t="s">
+        <v>28</v>
+      </c>
+      <c r="D803">
+        <v>242.3</v>
+      </c>
+      <c r="E803">
+        <v>263.53</v>
+      </c>
+      <c r="F803">
+        <v>0.087619</v>
+      </c>
+      <c r="G803">
+        <v>8.76</v>
+      </c>
+      <c r="H803" t="s">
+        <v>28</v>
+      </c>
+      <c r="I803">
+        <v>5</v>
+      </c>
+      <c r="J803">
+        <v>1211.5</v>
+      </c>
+      <c r="K803">
+        <v>1317.65</v>
+      </c>
+      <c r="L803">
+        <v>106.15</v>
+      </c>
+      <c r="M803" t="s">
+        <v>17</v>
+      </c>
+      <c r="N803">
+        <v>5</v>
+      </c>
+      <c r="O803">
+        <v>1211.5</v>
+      </c>
+      <c r="P803">
+        <v>1317.65</v>
+      </c>
+    </row>
+    <row r="804" spans="1:16">
+      <c r="A804" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B804" t="s">
+        <v>18</v>
+      </c>
+      <c r="C804" t="s">
+        <v>29</v>
+      </c>
+      <c r="D804">
+        <v>38.273</v>
+      </c>
+      <c r="E804">
+        <v>49.13</v>
+      </c>
+      <c r="F804">
+        <v>0.283673</v>
+      </c>
+      <c r="G804">
+        <v>28.37</v>
+      </c>
+      <c r="H804" t="s">
+        <v>29</v>
+      </c>
+      <c r="I804">
+        <v>54</v>
+      </c>
+      <c r="J804">
+        <v>2066.74</v>
+      </c>
+      <c r="K804">
+        <v>2653.02</v>
+      </c>
+      <c r="L804">
+        <v>586.28</v>
+      </c>
+      <c r="M804" t="s">
+        <v>18</v>
+      </c>
+      <c r="N804">
+        <v>54</v>
+      </c>
+      <c r="O804">
+        <v>2066.742</v>
+      </c>
+      <c r="P804">
+        <v>2653.02</v>
+      </c>
+    </row>
+    <row r="805" spans="1:16">
+      <c r="A805" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B805" t="s">
+        <v>19</v>
+      </c>
+      <c r="C805" t="s">
+        <v>30</v>
+      </c>
+      <c r="D805">
+        <v>6.5264</v>
+      </c>
+      <c r="E805">
+        <v>8.448</v>
+      </c>
+      <c r="F805">
+        <v>0.294435</v>
+      </c>
+      <c r="G805">
+        <v>29.44</v>
+      </c>
+      <c r="H805" t="s">
+        <v>30</v>
+      </c>
+      <c r="I805">
+        <v>276</v>
+      </c>
+      <c r="J805">
+        <v>1801.29</v>
+      </c>
+      <c r="K805">
+        <v>2331.65</v>
+      </c>
+      <c r="L805">
+        <v>530.36</v>
+      </c>
+      <c r="M805" t="s">
+        <v>19</v>
+      </c>
+      <c r="N805">
+        <v>276</v>
+      </c>
+      <c r="O805">
+        <v>1801.2864</v>
+      </c>
+      <c r="P805">
+        <v>2331.648</v>
+      </c>
+    </row>
+    <row r="806" spans="1:16">
+      <c r="A806" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B806" t="s">
+        <v>20</v>
+      </c>
+      <c r="C806" t="s">
+        <v>31</v>
+      </c>
+      <c r="D806">
+        <v>197.58</v>
+      </c>
+      <c r="E806">
+        <v>205.3</v>
+      </c>
+      <c r="F806">
+        <v>0.039073</v>
+      </c>
+      <c r="G806">
+        <v>3.91</v>
+      </c>
+      <c r="H806" t="s">
+        <v>31</v>
+      </c>
+      <c r="I806">
+        <v>4</v>
+      </c>
+      <c r="J806">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K806">
+        <v>821.2</v>
+      </c>
+      <c r="L806">
+        <v>30.88</v>
+      </c>
+      <c r="M806" t="s">
+        <v>20</v>
+      </c>
+      <c r="N806">
+        <v>4</v>
+      </c>
+      <c r="O806">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P806">
+        <v>821.2</v>
+      </c>
+    </row>
+    <row r="807" spans="1:16">
+      <c r="A807" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B807" t="s">
+        <v>21</v>
+      </c>
+      <c r="C807" t="s">
+        <v>32</v>
+      </c>
+      <c r="D807">
+        <v>79.86</v>
+      </c>
+      <c r="E807">
+        <v>129.62</v>
+      </c>
+      <c r="F807">
+        <v>0.62309</v>
+      </c>
+      <c r="G807">
+        <v>62.31</v>
+      </c>
+      <c r="H807" t="s">
+        <v>32</v>
+      </c>
+      <c r="I807">
+        <v>12</v>
+      </c>
+      <c r="J807">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K807">
+        <v>1555.44</v>
+      </c>
+      <c r="L807">
+        <v>597.12</v>
+      </c>
+      <c r="M807" t="s">
+        <v>21</v>
+      </c>
+      <c r="N807">
+        <v>12</v>
+      </c>
+      <c r="O807">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P807">
+        <v>1555.44</v>
+      </c>
+    </row>
+    <row r="808" spans="1:16">
+      <c r="A808" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B808" t="s">
+        <v>22</v>
+      </c>
+      <c r="C808" t="s">
+        <v>33</v>
+      </c>
+      <c r="D808">
+        <v>19.7444</v>
+      </c>
+      <c r="E808">
+        <v>22.451</v>
+      </c>
+      <c r="F808">
+        <v>0.137082</v>
+      </c>
+      <c r="G808">
+        <v>13.71</v>
+      </c>
+      <c r="H808" t="s">
+        <v>33</v>
+      </c>
+      <c r="I808">
+        <v>61</v>
+      </c>
+      <c r="J808">
+        <v>1204.41</v>
+      </c>
+      <c r="K808">
+        <v>1369.51</v>
+      </c>
+      <c r="L808">
+        <v>165.1</v>
+      </c>
+      <c r="M808" t="s">
+        <v>22</v>
+      </c>
+      <c r="N808">
+        <v>61</v>
+      </c>
+      <c r="O808">
+        <v>1204.4084</v>
+      </c>
+      <c r="P808">
+        <v>1369.511</v>
+      </c>
+    </row>
+    <row r="809" spans="1:16">
+      <c r="A809" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B809" t="s">
+        <v>23</v>
+      </c>
+      <c r="C809" t="s">
+        <v>34</v>
+      </c>
+      <c r="D809">
+        <v>132.3898</v>
+      </c>
+      <c r="E809">
+        <v>156.1</v>
+      </c>
+      <c r="F809">
+        <v>0.179094</v>
+      </c>
+      <c r="G809">
+        <v>17.91</v>
+      </c>
+      <c r="H809" t="s">
+        <v>34</v>
+      </c>
+      <c r="I809">
+        <v>57</v>
+      </c>
+      <c r="J809">
+        <v>7546.22</v>
+      </c>
+      <c r="K809">
+        <v>8897.700000000001</v>
+      </c>
+      <c r="L809">
+        <v>1351.48</v>
+      </c>
+      <c r="M809" t="s">
+        <v>23</v>
+      </c>
+      <c r="N809">
+        <v>57</v>
+      </c>
+      <c r="O809">
+        <v>7546.2186</v>
+      </c>
+      <c r="P809">
+        <v>8897.699999999999</v>
+      </c>
+    </row>
+    <row r="810" spans="1:16">
+      <c r="A810" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B810" t="s">
+        <v>24</v>
+      </c>
+      <c r="C810" t="s">
+        <v>35</v>
+      </c>
+      <c r="D810">
+        <v>34.0694</v>
+      </c>
+      <c r="E810">
+        <v>35.325</v>
+      </c>
+      <c r="F810">
+        <v>0.036854</v>
+      </c>
+      <c r="G810">
+        <v>3.69</v>
+      </c>
+      <c r="H810" t="s">
+        <v>35</v>
+      </c>
+      <c r="I810">
+        <v>48</v>
+      </c>
+      <c r="J810">
+        <v>1635.33</v>
+      </c>
+      <c r="K810">
+        <v>1695.6</v>
+      </c>
+      <c r="L810">
+        <v>60.27</v>
+      </c>
+      <c r="M810" t="s">
+        <v>24</v>
+      </c>
+      <c r="N810">
+        <v>48</v>
+      </c>
+      <c r="O810">
+        <v>1635.3312</v>
+      </c>
+      <c r="P810">
+        <v>1695.6</v>
+      </c>
+    </row>
+    <row r="811" spans="1:16">
+      <c r="A811" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B811" t="s">
+        <v>25</v>
+      </c>
+      <c r="C811" t="s">
+        <v>36</v>
+      </c>
+      <c r="D811">
+        <v>69.4158</v>
+      </c>
+      <c r="E811">
+        <v>75.89</v>
+      </c>
+      <c r="F811">
+        <v>0.093267</v>
+      </c>
+      <c r="G811">
+        <v>9.33</v>
+      </c>
+      <c r="H811" t="s">
+        <v>36</v>
+      </c>
+      <c r="I811">
+        <v>62</v>
+      </c>
+      <c r="J811">
+        <v>4303.78</v>
+      </c>
+      <c r="K811">
+        <v>4705.18</v>
+      </c>
+      <c r="L811">
+        <v>401.4</v>
+      </c>
+      <c r="M811" t="s">
+        <v>25</v>
+      </c>
+      <c r="N811">
+        <v>62</v>
+      </c>
+      <c r="O811">
+        <v>4303.7796</v>
+      </c>
+      <c r="P811">
+        <v>4705.18</v>
+      </c>
+    </row>
+    <row r="812" spans="1:16">
+      <c r="A812" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B812" t="s">
+        <v>26</v>
+      </c>
+      <c r="C812" t="s">
+        <v>37</v>
+      </c>
+      <c r="D812">
+        <v>8.1868</v>
+      </c>
+      <c r="E812">
+        <v>9.09</v>
+      </c>
+      <c r="F812">
+        <v>0.110324</v>
+      </c>
+      <c r="G812">
+        <v>11.03</v>
+      </c>
+      <c r="H812" t="s">
+        <v>37</v>
+      </c>
+      <c r="I812">
+        <v>431</v>
+      </c>
+      <c r="J812">
+        <v>3528.51</v>
+      </c>
+      <c r="K812">
+        <v>3917.79</v>
+      </c>
+      <c r="L812">
+        <v>389.28</v>
+      </c>
+      <c r="M812" t="s">
+        <v>26</v>
+      </c>
+      <c r="N812">
+        <v>431</v>
+      </c>
+      <c r="O812">
+        <v>3528.5108</v>
+      </c>
+      <c r="P812">
+        <v>3917.79</v>
       </c>
     </row>
   </sheetData>
@@ -36704,7 +37326,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -39734,6 +40356,47 @@
       </c>
       <c r="M74" s="2">
         <v>0.1508719721527119</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B75" s="2">
+        <v>0.079888</v>
+      </c>
+      <c r="C75" s="2">
+        <v>0.087619</v>
+      </c>
+      <c r="D75" s="2">
+        <v>0.283673</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0.294435</v>
+      </c>
+      <c r="F75" s="2">
+        <v>0.039073</v>
+      </c>
+      <c r="G75" s="2">
+        <v>0.62309</v>
+      </c>
+      <c r="H75" s="2">
+        <v>0.137082</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0.179094</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0.036854</v>
+      </c>
+      <c r="K75" s="2">
+        <v>0.093267</v>
+      </c>
+      <c r="L75" s="2">
+        <v>0.110324</v>
+      </c>
+      <c r="M75" s="2">
+        <v>0.1645284967451937</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2627" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -461,16 +461,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$75</c:f>
+              <c:f>grafico_dati!$B$2:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -692,6 +695,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.079888</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.08568000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -719,10 +725,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -944,16 +950,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$75</c:f>
+              <c:f>grafico_dati!$C$2:$C$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1175,6 +1184,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.087619</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.088403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1202,10 +1214,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1427,16 +1439,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$75</c:f>
+              <c:f>grafico_dati!$D$2:$D$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1658,6 +1673,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.283673</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.269171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1685,10 +1703,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1910,16 +1928,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$75</c:f>
+              <c:f>grafico_dati!$E$2:$E$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2141,6 +2162,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.294435</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.282637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2168,10 +2192,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2393,16 +2417,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$75</c:f>
+              <c:f>grafico_dati!$F$2:$F$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2648,10 +2675,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2873,16 +2900,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$75</c:f>
+              <c:f>grafico_dati!$G$2:$G$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -3104,6 +3134,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.62309</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.637866</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3131,10 +3164,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3356,16 +3389,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$75</c:f>
+              <c:f>grafico_dati!$H$2:$H$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3587,6 +3623,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.137082</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.14316</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3614,10 +3653,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3839,16 +3878,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$75</c:f>
+              <c:f>grafico_dati!$I$2:$I$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -4067,6 +4109,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.179094</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.177885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4094,10 +4139,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4319,16 +4364,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$75</c:f>
+              <c:f>grafico_dati!$J$2:$J$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4550,6 +4598,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.036854</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.040376</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4577,10 +4628,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4802,16 +4853,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$75</c:f>
+              <c:f>grafico_dati!$K$2:$K$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -5030,6 +5084,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.093267</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.09153799999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5057,10 +5114,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5282,16 +5339,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$75</c:f>
+              <c:f>grafico_dati!$L$2:$L$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5513,6 +5573,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.110324</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.104461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5544,10 +5607,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$75</c:f>
+              <c:f>grafico_dati!$A$2:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5769,16 +5832,19 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$75</c:f>
+              <c:f>grafico_dati!$M$2:$M$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -6000,6 +6066,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.1645284967451937</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.1663208726391563</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6406,7 +6475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P812"/>
+  <dimension ref="A1:P822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -37317,6 +37386,506 @@
       </c>
       <c r="P812">
         <v>3917.79</v>
+      </c>
+    </row>
+    <row r="813" spans="1:16">
+      <c r="A813" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B813" t="s">
+        <v>16</v>
+      </c>
+      <c r="C813" t="s">
+        <v>27</v>
+      </c>
+      <c r="D813">
+        <v>50.07</v>
+      </c>
+      <c r="E813">
+        <v>54.36</v>
+      </c>
+      <c r="F813">
+        <v>0.08568000000000001</v>
+      </c>
+      <c r="G813">
+        <v>8.57</v>
+      </c>
+      <c r="H813" t="s">
+        <v>27</v>
+      </c>
+      <c r="I813">
+        <v>23</v>
+      </c>
+      <c r="J813">
+        <v>1151.61</v>
+      </c>
+      <c r="K813">
+        <v>1250.28</v>
+      </c>
+      <c r="L813">
+        <v>98.67</v>
+      </c>
+      <c r="M813" t="s">
+        <v>16</v>
+      </c>
+      <c r="N813">
+        <v>23</v>
+      </c>
+      <c r="O813">
+        <v>1151.61</v>
+      </c>
+      <c r="P813">
+        <v>1250.28</v>
+      </c>
+    </row>
+    <row r="814" spans="1:16">
+      <c r="A814" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B814" t="s">
+        <v>17</v>
+      </c>
+      <c r="C814" t="s">
+        <v>28</v>
+      </c>
+      <c r="D814">
+        <v>242.3</v>
+      </c>
+      <c r="E814">
+        <v>263.72</v>
+      </c>
+      <c r="F814">
+        <v>0.088403</v>
+      </c>
+      <c r="G814">
+        <v>8.84</v>
+      </c>
+      <c r="H814" t="s">
+        <v>28</v>
+      </c>
+      <c r="I814">
+        <v>5</v>
+      </c>
+      <c r="J814">
+        <v>1211.5</v>
+      </c>
+      <c r="K814">
+        <v>1318.6</v>
+      </c>
+      <c r="L814">
+        <v>107.1</v>
+      </c>
+      <c r="M814" t="s">
+        <v>17</v>
+      </c>
+      <c r="N814">
+        <v>5</v>
+      </c>
+      <c r="O814">
+        <v>1211.5</v>
+      </c>
+      <c r="P814">
+        <v>1318.6</v>
+      </c>
+    </row>
+    <row r="815" spans="1:16">
+      <c r="A815" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B815" t="s">
+        <v>18</v>
+      </c>
+      <c r="C815" t="s">
+        <v>29</v>
+      </c>
+      <c r="D815">
+        <v>38.273</v>
+      </c>
+      <c r="E815">
+        <v>48.575</v>
+      </c>
+      <c r="F815">
+        <v>0.269171</v>
+      </c>
+      <c r="G815">
+        <v>26.92</v>
+      </c>
+      <c r="H815" t="s">
+        <v>29</v>
+      </c>
+      <c r="I815">
+        <v>54</v>
+      </c>
+      <c r="J815">
+        <v>2066.74</v>
+      </c>
+      <c r="K815">
+        <v>2623.05</v>
+      </c>
+      <c r="L815">
+        <v>556.3099999999999</v>
+      </c>
+      <c r="M815" t="s">
+        <v>18</v>
+      </c>
+      <c r="N815">
+        <v>54</v>
+      </c>
+      <c r="O815">
+        <v>2066.742</v>
+      </c>
+      <c r="P815">
+        <v>2623.05</v>
+      </c>
+    </row>
+    <row r="816" spans="1:16">
+      <c r="A816" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B816" t="s">
+        <v>19</v>
+      </c>
+      <c r="C816" t="s">
+        <v>30</v>
+      </c>
+      <c r="D816">
+        <v>6.5264</v>
+      </c>
+      <c r="E816">
+        <v>8.371</v>
+      </c>
+      <c r="F816">
+        <v>0.282637</v>
+      </c>
+      <c r="G816">
+        <v>28.26</v>
+      </c>
+      <c r="H816" t="s">
+        <v>30</v>
+      </c>
+      <c r="I816">
+        <v>276</v>
+      </c>
+      <c r="J816">
+        <v>1801.29</v>
+      </c>
+      <c r="K816">
+        <v>2310.4</v>
+      </c>
+      <c r="L816">
+        <v>509.11</v>
+      </c>
+      <c r="M816" t="s">
+        <v>19</v>
+      </c>
+      <c r="N816">
+        <v>276</v>
+      </c>
+      <c r="O816">
+        <v>1801.2864</v>
+      </c>
+      <c r="P816">
+        <v>2310.396</v>
+      </c>
+    </row>
+    <row r="817" spans="1:16">
+      <c r="A817" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B817" t="s">
+        <v>21</v>
+      </c>
+      <c r="C817" t="s">
+        <v>32</v>
+      </c>
+      <c r="D817">
+        <v>79.86</v>
+      </c>
+      <c r="E817">
+        <v>130.8</v>
+      </c>
+      <c r="F817">
+        <v>0.637866</v>
+      </c>
+      <c r="G817">
+        <v>63.79</v>
+      </c>
+      <c r="H817" t="s">
+        <v>32</v>
+      </c>
+      <c r="I817">
+        <v>12</v>
+      </c>
+      <c r="J817">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K817">
+        <v>1569.6</v>
+      </c>
+      <c r="L817">
+        <v>611.28</v>
+      </c>
+      <c r="M817" t="s">
+        <v>21</v>
+      </c>
+      <c r="N817">
+        <v>12</v>
+      </c>
+      <c r="O817">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P817">
+        <v>1569.6</v>
+      </c>
+    </row>
+    <row r="818" spans="1:16">
+      <c r="A818" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B818" t="s">
+        <v>22</v>
+      </c>
+      <c r="C818" t="s">
+        <v>33</v>
+      </c>
+      <c r="D818">
+        <v>19.7444</v>
+      </c>
+      <c r="E818">
+        <v>22.571</v>
+      </c>
+      <c r="F818">
+        <v>0.14316</v>
+      </c>
+      <c r="G818">
+        <v>14.32</v>
+      </c>
+      <c r="H818" t="s">
+        <v>33</v>
+      </c>
+      <c r="I818">
+        <v>61</v>
+      </c>
+      <c r="J818">
+        <v>1204.41</v>
+      </c>
+      <c r="K818">
+        <v>1376.83</v>
+      </c>
+      <c r="L818">
+        <v>172.42</v>
+      </c>
+      <c r="M818" t="s">
+        <v>22</v>
+      </c>
+      <c r="N818">
+        <v>61</v>
+      </c>
+      <c r="O818">
+        <v>1204.4084</v>
+      </c>
+      <c r="P818">
+        <v>1376.831</v>
+      </c>
+    </row>
+    <row r="819" spans="1:16">
+      <c r="A819" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B819" t="s">
+        <v>23</v>
+      </c>
+      <c r="C819" t="s">
+        <v>34</v>
+      </c>
+      <c r="D819">
+        <v>132.3898</v>
+      </c>
+      <c r="E819">
+        <v>155.94</v>
+      </c>
+      <c r="F819">
+        <v>0.177885</v>
+      </c>
+      <c r="G819">
+        <v>17.79</v>
+      </c>
+      <c r="H819" t="s">
+        <v>34</v>
+      </c>
+      <c r="I819">
+        <v>57</v>
+      </c>
+      <c r="J819">
+        <v>7546.22</v>
+      </c>
+      <c r="K819">
+        <v>8888.58</v>
+      </c>
+      <c r="L819">
+        <v>1342.36</v>
+      </c>
+      <c r="M819" t="s">
+        <v>23</v>
+      </c>
+      <c r="N819">
+        <v>57</v>
+      </c>
+      <c r="O819">
+        <v>7546.2186</v>
+      </c>
+      <c r="P819">
+        <v>8888.58</v>
+      </c>
+    </row>
+    <row r="820" spans="1:16">
+      <c r="A820" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B820" t="s">
+        <v>24</v>
+      </c>
+      <c r="C820" t="s">
+        <v>35</v>
+      </c>
+      <c r="D820">
+        <v>34.0694</v>
+      </c>
+      <c r="E820">
+        <v>35.445</v>
+      </c>
+      <c r="F820">
+        <v>0.040376</v>
+      </c>
+      <c r="G820">
+        <v>4.04</v>
+      </c>
+      <c r="H820" t="s">
+        <v>35</v>
+      </c>
+      <c r="I820">
+        <v>48</v>
+      </c>
+      <c r="J820">
+        <v>1635.33</v>
+      </c>
+      <c r="K820">
+        <v>1701.36</v>
+      </c>
+      <c r="L820">
+        <v>66.03</v>
+      </c>
+      <c r="M820" t="s">
+        <v>24</v>
+      </c>
+      <c r="N820">
+        <v>48</v>
+      </c>
+      <c r="O820">
+        <v>1635.3312</v>
+      </c>
+      <c r="P820">
+        <v>1701.36</v>
+      </c>
+    </row>
+    <row r="821" spans="1:16">
+      <c r="A821" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B821" t="s">
+        <v>25</v>
+      </c>
+      <c r="C821" t="s">
+        <v>36</v>
+      </c>
+      <c r="D821">
+        <v>69.4158</v>
+      </c>
+      <c r="E821">
+        <v>75.77</v>
+      </c>
+      <c r="F821">
+        <v>0.09153799999999999</v>
+      </c>
+      <c r="G821">
+        <v>9.15</v>
+      </c>
+      <c r="H821" t="s">
+        <v>36</v>
+      </c>
+      <c r="I821">
+        <v>62</v>
+      </c>
+      <c r="J821">
+        <v>4303.78</v>
+      </c>
+      <c r="K821">
+        <v>4697.74</v>
+      </c>
+      <c r="L821">
+        <v>393.96</v>
+      </c>
+      <c r="M821" t="s">
+        <v>25</v>
+      </c>
+      <c r="N821">
+        <v>62</v>
+      </c>
+      <c r="O821">
+        <v>4303.7796</v>
+      </c>
+      <c r="P821">
+        <v>4697.74</v>
+      </c>
+    </row>
+    <row r="822" spans="1:16">
+      <c r="A822" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B822" t="s">
+        <v>26</v>
+      </c>
+      <c r="C822" t="s">
+        <v>37</v>
+      </c>
+      <c r="D822">
+        <v>8.1868</v>
+      </c>
+      <c r="E822">
+        <v>9.042</v>
+      </c>
+      <c r="F822">
+        <v>0.104461</v>
+      </c>
+      <c r="G822">
+        <v>10.45</v>
+      </c>
+      <c r="H822" t="s">
+        <v>37</v>
+      </c>
+      <c r="I822">
+        <v>431</v>
+      </c>
+      <c r="J822">
+        <v>3528.51</v>
+      </c>
+      <c r="K822">
+        <v>3897.1</v>
+      </c>
+      <c r="L822">
+        <v>368.59</v>
+      </c>
+      <c r="M822" t="s">
+        <v>26</v>
+      </c>
+      <c r="N822">
+        <v>431</v>
+      </c>
+      <c r="O822">
+        <v>3528.5108</v>
+      </c>
+      <c r="P822">
+        <v>3897.102</v>
       </c>
     </row>
   </sheetData>
@@ -37326,7 +37895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -40397,6 +40966,44 @@
       </c>
       <c r="M75" s="2">
         <v>0.1645284967451937</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.08568000000000001</v>
+      </c>
+      <c r="C76" s="2">
+        <v>0.088403</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0.269171</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0.282637</v>
+      </c>
+      <c r="G76" s="2">
+        <v>0.637866</v>
+      </c>
+      <c r="H76" s="2">
+        <v>0.14316</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0.177885</v>
+      </c>
+      <c r="J76" s="2">
+        <v>0.040376</v>
+      </c>
+      <c r="K76" s="2">
+        <v>0.09153799999999999</v>
+      </c>
+      <c r="L76" s="2">
+        <v>0.104461</v>
+      </c>
+      <c r="M76" s="2">
+        <v>0.1663208726391563</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -464,16 +464,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$76</c:f>
+              <c:f>grafico_dati!$B$2:$B$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -698,6 +701,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.08568000000000001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.09307</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -725,10 +731,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -953,16 +959,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$76</c:f>
+              <c:f>grafico_dati!$C$2:$C$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1187,6 +1196,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.088403</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.09513000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1214,10 +1226,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1442,16 +1454,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$76</c:f>
+              <c:f>grafico_dati!$D$2:$D$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1676,6 +1691,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.269171</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.286155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1703,10 +1721,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1931,16 +1949,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$76</c:f>
+              <c:f>grafico_dati!$E$2:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2165,6 +2186,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.282637</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.305314</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2192,10 +2216,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2420,16 +2444,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$76</c:f>
+              <c:f>grafico_dati!$F$2:$F$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2648,6 +2675,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0.039073</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.040844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2675,10 +2705,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2903,16 +2933,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$76</c:f>
+              <c:f>grafico_dati!$G$2:$G$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -3137,6 +3170,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.637866</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.640871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3164,10 +3200,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3392,16 +3428,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$76</c:f>
+              <c:f>grafico_dati!$H$2:$H$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3626,6 +3665,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.14316</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.158252</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3653,10 +3695,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3881,16 +3923,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$76</c:f>
+              <c:f>grafico_dati!$I$2:$I$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -4112,6 +4157,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.177885</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.17849</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4139,10 +4187,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4367,16 +4415,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$76</c:f>
+              <c:f>grafico_dati!$J$2:$J$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4601,6 +4652,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.040376</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.045807</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4628,10 +4682,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4856,16 +4910,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$76</c:f>
+              <c:f>grafico_dati!$K$2:$K$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -5087,6 +5144,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.09153799999999999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.09225899999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5114,10 +5174,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5342,16 +5402,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$76</c:f>
+              <c:f>grafico_dati!$L$2:$L$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5576,6 +5639,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.104461</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.109347</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5607,10 +5673,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$76</c:f>
+              <c:f>grafico_dati!$A$2:$A$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5835,16 +5901,19 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$76</c:f>
+              <c:f>grafico_dati!$M$2:$M$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -6069,6 +6138,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>0.1663208726391563</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.1681637323299192</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6475,7 +6547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P822"/>
+  <dimension ref="A1:P833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -37886,6 +37958,556 @@
       </c>
       <c r="P822">
         <v>3897.102</v>
+      </c>
+    </row>
+    <row r="823" spans="1:16">
+      <c r="A823" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B823" t="s">
+        <v>16</v>
+      </c>
+      <c r="C823" t="s">
+        <v>27</v>
+      </c>
+      <c r="D823">
+        <v>50.07</v>
+      </c>
+      <c r="E823">
+        <v>54.73</v>
+      </c>
+      <c r="F823">
+        <v>0.09307</v>
+      </c>
+      <c r="G823">
+        <v>9.31</v>
+      </c>
+      <c r="H823" t="s">
+        <v>27</v>
+      </c>
+      <c r="I823">
+        <v>23</v>
+      </c>
+      <c r="J823">
+        <v>1151.61</v>
+      </c>
+      <c r="K823">
+        <v>1258.79</v>
+      </c>
+      <c r="L823">
+        <v>107.18</v>
+      </c>
+      <c r="M823" t="s">
+        <v>16</v>
+      </c>
+      <c r="N823">
+        <v>23</v>
+      </c>
+      <c r="O823">
+        <v>1151.61</v>
+      </c>
+      <c r="P823">
+        <v>1258.79</v>
+      </c>
+    </row>
+    <row r="824" spans="1:16">
+      <c r="A824" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B824" t="s">
+        <v>17</v>
+      </c>
+      <c r="C824" t="s">
+        <v>28</v>
+      </c>
+      <c r="D824">
+        <v>242.3</v>
+      </c>
+      <c r="E824">
+        <v>265.35</v>
+      </c>
+      <c r="F824">
+        <v>0.09513000000000001</v>
+      </c>
+      <c r="G824">
+        <v>9.51</v>
+      </c>
+      <c r="H824" t="s">
+        <v>28</v>
+      </c>
+      <c r="I824">
+        <v>5</v>
+      </c>
+      <c r="J824">
+        <v>1211.5</v>
+      </c>
+      <c r="K824">
+        <v>1326.75</v>
+      </c>
+      <c r="L824">
+        <v>115.25</v>
+      </c>
+      <c r="M824" t="s">
+        <v>17</v>
+      </c>
+      <c r="N824">
+        <v>5</v>
+      </c>
+      <c r="O824">
+        <v>1211.5</v>
+      </c>
+      <c r="P824">
+        <v>1326.75</v>
+      </c>
+    </row>
+    <row r="825" spans="1:16">
+      <c r="A825" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B825" t="s">
+        <v>18</v>
+      </c>
+      <c r="C825" t="s">
+        <v>29</v>
+      </c>
+      <c r="D825">
+        <v>38.273</v>
+      </c>
+      <c r="E825">
+        <v>49.225</v>
+      </c>
+      <c r="F825">
+        <v>0.286155</v>
+      </c>
+      <c r="G825">
+        <v>28.62</v>
+      </c>
+      <c r="H825" t="s">
+        <v>29</v>
+      </c>
+      <c r="I825">
+        <v>54</v>
+      </c>
+      <c r="J825">
+        <v>2066.74</v>
+      </c>
+      <c r="K825">
+        <v>2658.15</v>
+      </c>
+      <c r="L825">
+        <v>591.41</v>
+      </c>
+      <c r="M825" t="s">
+        <v>18</v>
+      </c>
+      <c r="N825">
+        <v>54</v>
+      </c>
+      <c r="O825">
+        <v>2066.742</v>
+      </c>
+      <c r="P825">
+        <v>2658.15</v>
+      </c>
+    </row>
+    <row r="826" spans="1:16">
+      <c r="A826" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B826" t="s">
+        <v>19</v>
+      </c>
+      <c r="C826" t="s">
+        <v>30</v>
+      </c>
+      <c r="D826">
+        <v>6.5264</v>
+      </c>
+      <c r="E826">
+        <v>8.519</v>
+      </c>
+      <c r="F826">
+        <v>0.305314</v>
+      </c>
+      <c r="G826">
+        <v>30.53</v>
+      </c>
+      <c r="H826" t="s">
+        <v>30</v>
+      </c>
+      <c r="I826">
+        <v>276</v>
+      </c>
+      <c r="J826">
+        <v>1801.29</v>
+      </c>
+      <c r="K826">
+        <v>2351.24</v>
+      </c>
+      <c r="L826">
+        <v>549.96</v>
+      </c>
+      <c r="M826" t="s">
+        <v>19</v>
+      </c>
+      <c r="N826">
+        <v>276</v>
+      </c>
+      <c r="O826">
+        <v>1801.2864</v>
+      </c>
+      <c r="P826">
+        <v>2351.244</v>
+      </c>
+    </row>
+    <row r="827" spans="1:16">
+      <c r="A827" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B827" t="s">
+        <v>20</v>
+      </c>
+      <c r="C827" t="s">
+        <v>31</v>
+      </c>
+      <c r="D827">
+        <v>197.58</v>
+      </c>
+      <c r="E827">
+        <v>205.65</v>
+      </c>
+      <c r="F827">
+        <v>0.040844</v>
+      </c>
+      <c r="G827">
+        <v>4.08</v>
+      </c>
+      <c r="H827" t="s">
+        <v>31</v>
+      </c>
+      <c r="I827">
+        <v>4</v>
+      </c>
+      <c r="J827">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K827">
+        <v>822.6</v>
+      </c>
+      <c r="L827">
+        <v>32.28</v>
+      </c>
+      <c r="M827" t="s">
+        <v>20</v>
+      </c>
+      <c r="N827">
+        <v>4</v>
+      </c>
+      <c r="O827">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="P827">
+        <v>822.6</v>
+      </c>
+    </row>
+    <row r="828" spans="1:16">
+      <c r="A828" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B828" t="s">
+        <v>21</v>
+      </c>
+      <c r="C828" t="s">
+        <v>32</v>
+      </c>
+      <c r="D828">
+        <v>79.86</v>
+      </c>
+      <c r="E828">
+        <v>131.04</v>
+      </c>
+      <c r="F828">
+        <v>0.640871</v>
+      </c>
+      <c r="G828">
+        <v>64.09</v>
+      </c>
+      <c r="H828" t="s">
+        <v>32</v>
+      </c>
+      <c r="I828">
+        <v>12</v>
+      </c>
+      <c r="J828">
+        <v>958.3200000000001</v>
+      </c>
+      <c r="K828">
+        <v>1572.48</v>
+      </c>
+      <c r="L828">
+        <v>614.16</v>
+      </c>
+      <c r="M828" t="s">
+        <v>21</v>
+      </c>
+      <c r="N828">
+        <v>12</v>
+      </c>
+      <c r="O828">
+        <v>958.3199999999999</v>
+      </c>
+      <c r="P828">
+        <v>1572.48</v>
+      </c>
+    </row>
+    <row r="829" spans="1:16">
+      <c r="A829" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B829" t="s">
+        <v>22</v>
+      </c>
+      <c r="C829" t="s">
+        <v>33</v>
+      </c>
+      <c r="D829">
+        <v>19.7444</v>
+      </c>
+      <c r="E829">
+        <v>22.869</v>
+      </c>
+      <c r="F829">
+        <v>0.158252</v>
+      </c>
+      <c r="G829">
+        <v>15.83</v>
+      </c>
+      <c r="H829" t="s">
+        <v>33</v>
+      </c>
+      <c r="I829">
+        <v>61</v>
+      </c>
+      <c r="J829">
+        <v>1204.41</v>
+      </c>
+      <c r="K829">
+        <v>1395.01</v>
+      </c>
+      <c r="L829">
+        <v>190.6</v>
+      </c>
+      <c r="M829" t="s">
+        <v>22</v>
+      </c>
+      <c r="N829">
+        <v>61</v>
+      </c>
+      <c r="O829">
+        <v>1204.4084</v>
+      </c>
+      <c r="P829">
+        <v>1395.009</v>
+      </c>
+    </row>
+    <row r="830" spans="1:16">
+      <c r="A830" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B830" t="s">
+        <v>23</v>
+      </c>
+      <c r="C830" t="s">
+        <v>34</v>
+      </c>
+      <c r="D830">
+        <v>132.3898</v>
+      </c>
+      <c r="E830">
+        <v>156.02</v>
+      </c>
+      <c r="F830">
+        <v>0.17849</v>
+      </c>
+      <c r="G830">
+        <v>17.85</v>
+      </c>
+      <c r="H830" t="s">
+        <v>34</v>
+      </c>
+      <c r="I830">
+        <v>57</v>
+      </c>
+      <c r="J830">
+        <v>7546.22</v>
+      </c>
+      <c r="K830">
+        <v>8893.139999999999</v>
+      </c>
+      <c r="L830">
+        <v>1346.92</v>
+      </c>
+      <c r="M830" t="s">
+        <v>23</v>
+      </c>
+      <c r="N830">
+        <v>57</v>
+      </c>
+      <c r="O830">
+        <v>7546.2186</v>
+      </c>
+      <c r="P830">
+        <v>8893.140000000001</v>
+      </c>
+    </row>
+    <row r="831" spans="1:16">
+      <c r="A831" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B831" t="s">
+        <v>24</v>
+      </c>
+      <c r="C831" t="s">
+        <v>35</v>
+      </c>
+      <c r="D831">
+        <v>34.0694</v>
+      </c>
+      <c r="E831">
+        <v>35.63</v>
+      </c>
+      <c r="F831">
+        <v>0.045807</v>
+      </c>
+      <c r="G831">
+        <v>4.58</v>
+      </c>
+      <c r="H831" t="s">
+        <v>35</v>
+      </c>
+      <c r="I831">
+        <v>48</v>
+      </c>
+      <c r="J831">
+        <v>1635.33</v>
+      </c>
+      <c r="K831">
+        <v>1710.24</v>
+      </c>
+      <c r="L831">
+        <v>74.91</v>
+      </c>
+      <c r="M831" t="s">
+        <v>24</v>
+      </c>
+      <c r="N831">
+        <v>48</v>
+      </c>
+      <c r="O831">
+        <v>1635.3312</v>
+      </c>
+      <c r="P831">
+        <v>1710.24</v>
+      </c>
+    </row>
+    <row r="832" spans="1:16">
+      <c r="A832" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B832" t="s">
+        <v>25</v>
+      </c>
+      <c r="C832" t="s">
+        <v>36</v>
+      </c>
+      <c r="D832">
+        <v>69.4158</v>
+      </c>
+      <c r="E832">
+        <v>75.81999999999999</v>
+      </c>
+      <c r="F832">
+        <v>0.09225899999999999</v>
+      </c>
+      <c r="G832">
+        <v>9.23</v>
+      </c>
+      <c r="H832" t="s">
+        <v>36</v>
+      </c>
+      <c r="I832">
+        <v>62</v>
+      </c>
+      <c r="J832">
+        <v>4303.78</v>
+      </c>
+      <c r="K832">
+        <v>4700.84</v>
+      </c>
+      <c r="L832">
+        <v>397.06</v>
+      </c>
+      <c r="M832" t="s">
+        <v>25</v>
+      </c>
+      <c r="N832">
+        <v>62</v>
+      </c>
+      <c r="O832">
+        <v>4303.7796</v>
+      </c>
+      <c r="P832">
+        <v>4700.839999999999</v>
+      </c>
+    </row>
+    <row r="833" spans="1:16">
+      <c r="A833" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B833" t="s">
+        <v>26</v>
+      </c>
+      <c r="C833" t="s">
+        <v>37</v>
+      </c>
+      <c r="D833">
+        <v>8.1868</v>
+      </c>
+      <c r="E833">
+        <v>9.082000000000001</v>
+      </c>
+      <c r="F833">
+        <v>0.109347</v>
+      </c>
+      <c r="G833">
+        <v>10.93</v>
+      </c>
+      <c r="H833" t="s">
+        <v>37</v>
+      </c>
+      <c r="I833">
+        <v>431</v>
+      </c>
+      <c r="J833">
+        <v>3528.51</v>
+      </c>
+      <c r="K833">
+        <v>3914.34</v>
+      </c>
+      <c r="L833">
+        <v>385.83</v>
+      </c>
+      <c r="M833" t="s">
+        <v>26</v>
+      </c>
+      <c r="N833">
+        <v>431</v>
+      </c>
+      <c r="O833">
+        <v>3528.5108</v>
+      </c>
+      <c r="P833">
+        <v>3914.342</v>
       </c>
     </row>
   </sheetData>
@@ -37895,7 +38517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" style="1" customWidth="1"/>
@@ -41004,6 +41626,47 @@
       </c>
       <c r="M76" s="2">
         <v>0.1663208726391563</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B77" s="2">
+        <v>0.09307</v>
+      </c>
+      <c r="C77" s="2">
+        <v>0.09513000000000001</v>
+      </c>
+      <c r="D77" s="2">
+        <v>0.286155</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0.305314</v>
+      </c>
+      <c r="F77" s="2">
+        <v>0.040844</v>
+      </c>
+      <c r="G77" s="2">
+        <v>0.640871</v>
+      </c>
+      <c r="H77" s="2">
+        <v>0.158252</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0.17849</v>
+      </c>
+      <c r="J77" s="2">
+        <v>0.045807</v>
+      </c>
+      <c r="K77" s="2">
+        <v>0.09225899999999999</v>
+      </c>
+      <c r="L77" s="2">
+        <v>0.109347</v>
+      </c>
+      <c r="M77" s="2">
+        <v>0.1681637323299192</v>
       </c>
     </row>
   </sheetData>

--- a/grafico_portafoglio.xlsx
+++ b/grafico_portafoglio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="40">
   <si>
     <t>data</t>
   </si>
@@ -236,10 +236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -467,16 +467,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$B$2:$B$77</c:f>
+              <c:f>grafico_dati!$B$2:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.0920711065543395</c:v>
                 </c:pt>
@@ -704,6 +707,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.09307</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.083483</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -731,10 +737,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -962,16 +968,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$C$2:$C$77</c:f>
+              <c:f>grafico_dati!$C$2:$C$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.039496471800196</c:v>
                 </c:pt>
@@ -1199,6 +1208,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.09513000000000001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.07953</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1226,10 +1238,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1457,16 +1469,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$D$2:$D$77</c:f>
+              <c:f>grafico_dati!$D$2:$D$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.1470227451696732</c:v>
                 </c:pt>
@@ -1694,6 +1709,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.286155</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.310584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1721,10 +1739,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -1952,16 +1970,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$E$2:$E$77</c:f>
+              <c:f>grafico_dati!$E$2:$E$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.0904940094074568</c:v>
                 </c:pt>
@@ -2189,6 +2210,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.305314</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.341934</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2216,10 +2240,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2447,16 +2471,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$F$2:$F$77</c:f>
+              <c:f>grafico_dati!$F$2:$F$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.0542565191403876</c:v>
                 </c:pt>
@@ -2678,6 +2705,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.040844</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.044134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2705,10 +2735,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -2936,16 +2966,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$G$2:$G$77</c:f>
+              <c:f>grafico_dati!$G$2:$G$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.4154770963627265</c:v>
                 </c:pt>
@@ -3173,6 +3206,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.640871</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.649386</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3200,10 +3236,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3431,16 +3467,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$H$2:$H$77</c:f>
+              <c:f>grafico_dati!$H$2:$H$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.0923096896043842</c:v>
                 </c:pt>
@@ -3668,6 +3707,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.158252</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.179322</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3695,10 +3737,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -3926,16 +3968,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$I$2:$I$77</c:f>
+              <c:f>grafico_dati!$I$2:$I$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.1132818490650631</c:v>
                 </c:pt>
@@ -4160,6 +4205,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.17849</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.182871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4187,10 +4235,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4418,16 +4466,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$J$2:$J$77</c:f>
+              <c:f>grafico_dati!$J$2:$J$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.0438985901339319</c:v>
                 </c:pt>
@@ -4655,6 +4706,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.045807</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.039936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4682,10 +4736,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -4913,16 +4967,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$K$2:$K$77</c:f>
+              <c:f>grafico_dati!$K$2:$K$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.019625083107112</c:v>
                 </c:pt>
@@ -5147,6 +5204,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.09225899999999999</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.092403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5174,10 +5234,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5405,16 +5465,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$L$2:$L$77</c:f>
+              <c:f>grafico_dati!$L$2:$L$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.0259197937957051</c:v>
                 </c:pt>
@@ -5642,6 +5705,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.109347</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.110324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5673,10 +5739,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>grafico_dati!$A$2:$A$77</c:f>
+              <c:f>grafico_dati!$A$2:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>46078</c:v>
                 </c:pt>
@@ -5904,16 +5970,19 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafico_dati!$M$2:$M$77</c:f>
+              <c:f>grafico_dati!$M$2:$M$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>0.08660208950775994</c:v>
                 </c:pt>
@@ -6141,6 +6210,9 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>0.1681637323299192</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.1738961487443309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6547,7 +6619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P833"/>
+  <dimension ref="A1:P844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -38508,6 +38580,556 @@
       </c>
       <c r="P833">
         <v>3914.342</v>
+      </c>
+    </row>
+    <row r="834" spans="1:16">
+      <c r="A834" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B834" t="s">
+        <v>16</v>
+      </c>
+      <c r="C834" t="s